--- a/processed_data_during_wm/processed_data_wide.xlsx
+++ b/processed_data_during_wm/processed_data_wide.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="59">
   <si>
     <t>Team</t>
   </si>
@@ -31,12 +31,24 @@
     <t>Shin_Wahrscheinlichkeit_in_Prozent_1</t>
   </si>
   <si>
+    <t>Datum_2</t>
+  </si>
+  <si>
+    <t>Durchsch_Quote_2</t>
+  </si>
+  <si>
+    <t>Norm_Wahrscheinlichkeit_in_Prozent_2</t>
+  </si>
+  <si>
+    <t>Shin_Wahrscheinlichkeit_in_Prozent_2</t>
+  </si>
+  <si>
+    <t>Frankreich</t>
+  </si>
+  <si>
     <t>Spanien</t>
   </si>
   <si>
-    <t>Frankreich</t>
-  </si>
-  <si>
     <t>England</t>
   </si>
   <si>
@@ -61,36 +73,36 @@
     <t>Belgien</t>
   </si>
   <si>
+    <t>USA</t>
+  </si>
+  <si>
     <t>Kolumbien</t>
   </si>
   <si>
     <t>Marokko</t>
   </si>
   <si>
+    <t>Mexiko</t>
+  </si>
+  <si>
     <t>Japan</t>
   </si>
   <si>
-    <t>USA</t>
-  </si>
-  <si>
-    <t>Mexiko</t>
+    <t>Schweiz</t>
   </si>
   <si>
     <t>Uruguay</t>
   </si>
   <si>
-    <t>Schweiz</t>
-  </si>
-  <si>
     <t>Türkei</t>
   </si>
   <si>
+    <t>Ecuador</t>
+  </si>
+  <si>
     <t>Kroatien</t>
   </si>
   <si>
-    <t>Ecuador</t>
-  </si>
-  <si>
     <t>Senegal</t>
   </si>
   <si>
@@ -103,33 +115,33 @@
     <t>Kanada</t>
   </si>
   <si>
+    <t>Südkorea</t>
+  </si>
+  <si>
+    <t>Schottland</t>
+  </si>
+  <si>
+    <t>Elfenbeinküste</t>
+  </si>
+  <si>
+    <t>Ägypten</t>
+  </si>
+  <si>
+    <t>Bosnien Herzegowina</t>
+  </si>
+  <si>
+    <t>Algerien</t>
+  </si>
+  <si>
     <t>Paraguay</t>
   </si>
   <si>
-    <t>Schottland</t>
-  </si>
-  <si>
-    <t>Elfenbeinküste</t>
+    <t>Australien</t>
   </si>
   <si>
     <t>Tschechien</t>
   </si>
   <si>
-    <t>Ägypten</t>
-  </si>
-  <si>
-    <t>Algerien</t>
-  </si>
-  <si>
-    <t>Bosnien Herzegowina</t>
-  </si>
-  <si>
-    <t>Südkorea</t>
-  </si>
-  <si>
-    <t>Australien</t>
-  </si>
-  <si>
     <t>Ghana</t>
   </si>
   <si>
@@ -145,15 +157,15 @@
     <t>Saudi Arabien</t>
   </si>
   <si>
+    <t>Katar</t>
+  </si>
+  <si>
+    <t>Irak</t>
+  </si>
+  <si>
     <t>Südafrika</t>
   </si>
   <si>
-    <t>Katar</t>
-  </si>
-  <si>
-    <t>Irak</t>
-  </si>
-  <si>
     <t>Neuseeland</t>
   </si>
   <si>
@@ -176,6 +188,9 @@
   </si>
   <si>
     <t>11.06.2026</t>
+  </si>
+  <si>
+    <t>13.06.2026</t>
   </si>
 </sst>
 </file>
@@ -533,10 +548,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -552,47 +567,83 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C2">
+        <v>6.01</v>
+      </c>
+      <c r="D2">
+        <v>14.12</v>
+      </c>
+      <c r="E2">
+        <v>15.09</v>
+      </c>
+      <c r="F2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G2">
+        <v>5.55</v>
+      </c>
+      <c r="H2">
+        <v>15.15</v>
+      </c>
+      <c r="I2">
+        <v>16.26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3">
         <v>5.58</v>
       </c>
-      <c r="D2">
+      <c r="D3">
         <v>15.22</v>
       </c>
-      <c r="E2">
+      <c r="E3">
         <v>16.29</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C3">
-        <v>6.01</v>
-      </c>
-      <c r="D3">
-        <v>14.12</v>
-      </c>
-      <c r="E3">
-        <v>15.09</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="F3" t="s">
+        <v>58</v>
+      </c>
+      <c r="G3">
+        <v>5.63</v>
+      </c>
+      <c r="H3">
+        <v>14.94</v>
+      </c>
+      <c r="I3">
+        <v>16.04</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C4">
         <v>8.15</v>
@@ -603,13 +654,25 @@
       <c r="E4">
         <v>11.06</v>
       </c>
-    </row>
-    <row r="5" spans="1:5">
+      <c r="F4" t="s">
+        <v>58</v>
+      </c>
+      <c r="G4">
+        <v>8.42</v>
+      </c>
+      <c r="H4">
+        <v>9.99</v>
+      </c>
+      <c r="I4">
+        <v>10.62</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C5">
         <v>8.85</v>
@@ -620,13 +683,25 @@
       <c r="E5">
         <v>10.17</v>
       </c>
-    </row>
-    <row r="6" spans="1:5">
+      <c r="F5" t="s">
+        <v>58</v>
+      </c>
+      <c r="G5">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="H5">
+        <v>9.66</v>
+      </c>
+      <c r="I5">
+        <v>10.26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C6">
         <v>9.970000000000001</v>
@@ -637,13 +712,25 @@
       <c r="E6">
         <v>8.99</v>
       </c>
-    </row>
-    <row r="7" spans="1:5">
+      <c r="F6" t="s">
+        <v>58</v>
+      </c>
+      <c r="G6">
+        <v>10.11</v>
+      </c>
+      <c r="H6">
+        <v>8.32</v>
+      </c>
+      <c r="I6">
+        <v>8.789999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C7">
         <v>10.19</v>
@@ -654,13 +741,25 @@
       <c r="E7">
         <v>8.800000000000001</v>
       </c>
-    </row>
-    <row r="8" spans="1:5">
+      <c r="F7" t="s">
+        <v>58</v>
+      </c>
+      <c r="G7">
+        <v>10.33</v>
+      </c>
+      <c r="H7">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="I7">
+        <v>8.6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C8">
         <v>15.6</v>
@@ -671,13 +770,25 @@
       <c r="E8">
         <v>5.65</v>
       </c>
-    </row>
-    <row r="9" spans="1:5">
+      <c r="F8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G8">
+        <v>15.67</v>
+      </c>
+      <c r="H8">
+        <v>5.37</v>
+      </c>
+      <c r="I8">
+        <v>5.57</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C9">
         <v>21.29</v>
@@ -688,13 +799,25 @@
       <c r="E9">
         <v>4.07</v>
       </c>
-    </row>
-    <row r="10" spans="1:5">
+      <c r="F9" t="s">
+        <v>58</v>
+      </c>
+      <c r="G9">
+        <v>20.29</v>
+      </c>
+      <c r="H9">
+        <v>4.15</v>
+      </c>
+      <c r="I9">
+        <v>4.24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C10">
         <v>32.29</v>
@@ -705,13 +828,25 @@
       <c r="E10">
         <v>2.6</v>
       </c>
-    </row>
-    <row r="11" spans="1:5">
+      <c r="F10" t="s">
+        <v>58</v>
+      </c>
+      <c r="G10">
+        <v>33</v>
+      </c>
+      <c r="H10">
+        <v>2.55</v>
+      </c>
+      <c r="I10">
+        <v>2.49</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C11">
         <v>37.71</v>
@@ -722,132 +857,228 @@
       <c r="E11">
         <v>2.19</v>
       </c>
-    </row>
-    <row r="12" spans="1:5">
+      <c r="F11" t="s">
+        <v>58</v>
+      </c>
+      <c r="G11">
+        <v>37.71</v>
+      </c>
+      <c r="H11">
+        <v>2.23</v>
+      </c>
+      <c r="I11">
+        <v>2.15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C12">
+        <v>63.71</v>
+      </c>
+      <c r="D12">
+        <v>1.33</v>
+      </c>
+      <c r="E12">
+        <v>1.2</v>
+      </c>
+      <c r="F12" t="s">
+        <v>58</v>
+      </c>
+      <c r="G12">
+        <v>44.57</v>
+      </c>
+      <c r="H12">
+        <v>1.89</v>
+      </c>
+      <c r="I12">
+        <v>1.78</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" t="s">
+        <v>57</v>
+      </c>
+      <c r="C13">
         <v>41.71</v>
       </c>
-      <c r="D12">
+      <c r="D13">
         <v>2.04</v>
       </c>
-      <c r="E12">
+      <c r="E13">
         <v>1.95</v>
       </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" t="s">
-        <v>53</v>
-      </c>
-      <c r="C13">
+      <c r="F13" t="s">
+        <v>58</v>
+      </c>
+      <c r="G13">
+        <v>45.57</v>
+      </c>
+      <c r="H13">
+        <v>1.85</v>
+      </c>
+      <c r="I13">
+        <v>1.73</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" t="s">
+        <v>57</v>
+      </c>
+      <c r="C14">
         <v>49.86</v>
       </c>
-      <c r="D13">
+      <c r="D14">
         <v>1.7</v>
       </c>
-      <c r="E13">
+      <c r="E14">
         <v>1.59</v>
       </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14" t="s">
-        <v>53</v>
-      </c>
-      <c r="C14">
+      <c r="F14" t="s">
+        <v>58</v>
+      </c>
+      <c r="G14">
+        <v>50.57</v>
+      </c>
+      <c r="H14">
+        <v>1.66</v>
+      </c>
+      <c r="I14">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15">
+        <v>68.43000000000001</v>
+      </c>
+      <c r="D15">
+        <v>1.24</v>
+      </c>
+      <c r="E15">
+        <v>1.1</v>
+      </c>
+      <c r="F15" t="s">
+        <v>58</v>
+      </c>
+      <c r="G15">
+        <v>52.71</v>
+      </c>
+      <c r="H15">
+        <v>1.6</v>
+      </c>
+      <c r="I15">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C16">
         <v>53.43</v>
       </c>
-      <c r="D14">
+      <c r="D16">
         <v>1.59</v>
       </c>
-      <c r="E14">
+      <c r="E16">
         <v>1.47</v>
       </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" t="s">
-        <v>18</v>
-      </c>
-      <c r="B15" t="s">
-        <v>53</v>
-      </c>
-      <c r="C15">
-        <v>63.71</v>
-      </c>
-      <c r="D15">
-        <v>1.33</v>
-      </c>
-      <c r="E15">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" t="s">
-        <v>19</v>
-      </c>
-      <c r="B16" t="s">
-        <v>53</v>
-      </c>
-      <c r="C16">
-        <v>68.43000000000001</v>
-      </c>
-      <c r="D16">
-        <v>1.24</v>
-      </c>
-      <c r="E16">
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
+      <c r="F16" t="s">
+        <v>58</v>
+      </c>
+      <c r="G16">
+        <v>53.43</v>
+      </c>
+      <c r="H16">
+        <v>1.57</v>
+      </c>
+      <c r="I16">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C17">
+        <v>74.43000000000001</v>
+      </c>
+      <c r="D17">
+        <v>1.14</v>
+      </c>
+      <c r="E17">
+        <v>0.99</v>
+      </c>
+      <c r="F17" t="s">
+        <v>58</v>
+      </c>
+      <c r="G17">
+        <v>75.14</v>
+      </c>
+      <c r="H17">
+        <v>1.12</v>
+      </c>
+      <c r="I17">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" t="s">
+        <v>57</v>
+      </c>
+      <c r="C18">
         <v>71.14</v>
       </c>
-      <c r="D17">
+      <c r="D18">
         <v>1.19</v>
       </c>
-      <c r="E17">
+      <c r="E18">
         <v>1.05</v>
       </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" t="s">
-        <v>21</v>
-      </c>
-      <c r="B18" t="s">
-        <v>53</v>
-      </c>
-      <c r="C18">
-        <v>74.43000000000001</v>
-      </c>
-      <c r="D18">
-        <v>1.14</v>
-      </c>
-      <c r="E18">
-        <v>0.99</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
+      <c r="F18" t="s">
+        <v>58</v>
+      </c>
+      <c r="G18">
+        <v>75.29000000000001</v>
+      </c>
+      <c r="H18">
+        <v>1.12</v>
+      </c>
+      <c r="I18">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C19">
         <v>80</v>
@@ -858,47 +1089,83 @@
       <c r="E19">
         <v>0.91</v>
       </c>
-    </row>
-    <row r="20" spans="1:5">
+      <c r="F19" t="s">
+        <v>58</v>
+      </c>
+      <c r="G19">
+        <v>80</v>
+      </c>
+      <c r="H19">
+        <v>1.05</v>
+      </c>
+      <c r="I19">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C20">
-        <v>88.86</v>
+        <v>89</v>
       </c>
       <c r="D20">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="E20">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="21" spans="1:5">
+      <c r="F20" t="s">
+        <v>58</v>
+      </c>
+      <c r="G20">
+        <v>90.43000000000001</v>
+      </c>
+      <c r="H20">
+        <v>0.93</v>
+      </c>
+      <c r="I20">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C21">
-        <v>89</v>
+        <v>88.86</v>
       </c>
       <c r="D21">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="E21">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="22" spans="1:5">
+      <c r="F21" t="s">
+        <v>58</v>
+      </c>
+      <c r="G21">
+        <v>91.70999999999999</v>
+      </c>
+      <c r="H21">
+        <v>0.92</v>
+      </c>
+      <c r="I21">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
       <c r="A22" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C22">
         <v>101.29</v>
@@ -909,13 +1176,25 @@
       <c r="E22">
         <v>0.67</v>
       </c>
-    </row>
-    <row r="23" spans="1:5">
+      <c r="F22" t="s">
+        <v>58</v>
+      </c>
+      <c r="G22">
+        <v>106.14</v>
+      </c>
+      <c r="H22">
+        <v>0.79</v>
+      </c>
+      <c r="I22">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
       <c r="A23" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C23">
         <v>141.29</v>
@@ -926,13 +1205,25 @@
       <c r="E23">
         <v>0.43</v>
       </c>
-    </row>
-    <row r="24" spans="1:5">
+      <c r="F23" t="s">
+        <v>58</v>
+      </c>
+      <c r="G23">
+        <v>145.57</v>
+      </c>
+      <c r="H23">
+        <v>0.58</v>
+      </c>
+      <c r="I23">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
       <c r="A24" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C24">
         <v>153</v>
@@ -943,13 +1234,25 @@
       <c r="E24">
         <v>0.39</v>
       </c>
-    </row>
-    <row r="25" spans="1:5">
+      <c r="F24" t="s">
+        <v>58</v>
+      </c>
+      <c r="G24">
+        <v>158.57</v>
+      </c>
+      <c r="H24">
+        <v>0.53</v>
+      </c>
+      <c r="I24">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
       <c r="A25" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C25">
         <v>191.71</v>
@@ -960,30 +1263,54 @@
       <c r="E25">
         <v>0.28</v>
       </c>
-    </row>
-    <row r="26" spans="1:5">
+      <c r="F25" t="s">
+        <v>58</v>
+      </c>
+      <c r="G25">
+        <v>222.71</v>
+      </c>
+      <c r="H25">
+        <v>0.38</v>
+      </c>
+      <c r="I25">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
       <c r="A26" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C26">
-        <v>243.29</v>
+        <v>376.29</v>
       </c>
       <c r="D26">
+        <v>0.23</v>
+      </c>
+      <c r="E26">
+        <v>0.09</v>
+      </c>
+      <c r="F26" t="s">
+        <v>58</v>
+      </c>
+      <c r="G26">
+        <v>241</v>
+      </c>
+      <c r="H26">
         <v>0.35</v>
       </c>
-      <c r="E26">
-        <v>0.19</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
+      <c r="I26">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
       <c r="A27" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B27" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C27">
         <v>249.71</v>
@@ -994,13 +1321,25 @@
       <c r="E27">
         <v>0.18</v>
       </c>
-    </row>
-    <row r="28" spans="1:5">
+      <c r="F27" t="s">
+        <v>58</v>
+      </c>
+      <c r="G27">
+        <v>242.57</v>
+      </c>
+      <c r="H27">
+        <v>0.35</v>
+      </c>
+      <c r="I27">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
       <c r="A28" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C28">
         <v>250</v>
@@ -1011,47 +1350,83 @@
       <c r="E28">
         <v>0.18</v>
       </c>
-    </row>
-    <row r="29" spans="1:5">
+      <c r="F28" t="s">
+        <v>58</v>
+      </c>
+      <c r="G28">
+        <v>259.86</v>
+      </c>
+      <c r="H28">
+        <v>0.32</v>
+      </c>
+      <c r="I28">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
       <c r="A29" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B29" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C29">
-        <v>299.29</v>
+        <v>320.43</v>
       </c>
       <c r="D29">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="E29">
-        <v>0.14</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
+        <v>0.12</v>
+      </c>
+      <c r="F29" t="s">
+        <v>58</v>
+      </c>
+      <c r="G29">
+        <v>351.57</v>
+      </c>
+      <c r="H29">
+        <v>0.24</v>
+      </c>
+      <c r="I29">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
       <c r="A30" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C30">
-        <v>320.43</v>
+        <v>370.43</v>
       </c>
       <c r="D30">
-        <v>0.26</v>
+        <v>0.23</v>
       </c>
       <c r="E30">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
+        <v>0.1</v>
+      </c>
+      <c r="F30" t="s">
+        <v>58</v>
+      </c>
+      <c r="G30">
+        <v>376.71</v>
+      </c>
+      <c r="H30">
+        <v>0.22</v>
+      </c>
+      <c r="I30">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
       <c r="A31" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B31" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C31">
         <v>367.57</v>
@@ -1062,64 +1437,112 @@
       <c r="E31">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="32" spans="1:5">
+      <c r="F31" t="s">
+        <v>58</v>
+      </c>
+      <c r="G31">
+        <v>383</v>
+      </c>
+      <c r="H31">
+        <v>0.22</v>
+      </c>
+      <c r="I31">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
       <c r="A32" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C32">
-        <v>370.43</v>
+        <v>243.29</v>
       </c>
       <c r="D32">
-        <v>0.23</v>
+        <v>0.35</v>
       </c>
       <c r="E32">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
+        <v>0.19</v>
+      </c>
+      <c r="F32" t="s">
+        <v>58</v>
+      </c>
+      <c r="G32">
+        <v>455.57</v>
+      </c>
+      <c r="H32">
+        <v>0.18</v>
+      </c>
+      <c r="I32">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
       <c r="A33" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B33" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C33">
-        <v>376.29</v>
+        <v>442.71</v>
       </c>
       <c r="D33">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
       <c r="E33">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="F33" t="s">
+        <v>58</v>
+      </c>
+      <c r="G33">
+        <v>462.29</v>
+      </c>
+      <c r="H33">
+        <v>0.18</v>
+      </c>
+      <c r="I33">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
       <c r="A34" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C34">
-        <v>442.71</v>
+        <v>299.29</v>
       </c>
       <c r="D34">
-        <v>0.19</v>
+        <v>0.28</v>
       </c>
       <c r="E34">
-        <v>0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
+        <v>0.14</v>
+      </c>
+      <c r="F34" t="s">
+        <v>58</v>
+      </c>
+      <c r="G34">
+        <v>497.86</v>
+      </c>
+      <c r="H34">
+        <v>0.17</v>
+      </c>
+      <c r="I34">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
       <c r="A35" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B35" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C35">
         <v>467.14</v>
@@ -1130,13 +1553,25 @@
       <c r="E35">
         <v>0.06</v>
       </c>
-    </row>
-    <row r="36" spans="1:5">
+      <c r="F35" t="s">
+        <v>58</v>
+      </c>
+      <c r="G35">
+        <v>505.29</v>
+      </c>
+      <c r="H35">
+        <v>0.17</v>
+      </c>
+      <c r="I35">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
       <c r="A36" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B36" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C36">
         <v>540.71</v>
@@ -1147,13 +1582,25 @@
       <c r="E36">
         <v>0.05</v>
       </c>
-    </row>
-    <row r="37" spans="1:5">
+      <c r="F36" t="s">
+        <v>58</v>
+      </c>
+      <c r="G36">
+        <v>576.4299999999999</v>
+      </c>
+      <c r="H36">
+        <v>0.15</v>
+      </c>
+      <c r="I36">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
       <c r="A37" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B37" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C37">
         <v>605</v>
@@ -1164,13 +1611,25 @@
       <c r="E37">
         <v>0.04</v>
       </c>
-    </row>
-    <row r="38" spans="1:5">
+      <c r="F37" t="s">
+        <v>58</v>
+      </c>
+      <c r="G37">
+        <v>640.71</v>
+      </c>
+      <c r="H37">
+        <v>0.13</v>
+      </c>
+      <c r="I37">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
       <c r="A38" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B38" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C38">
         <v>747.86</v>
@@ -1181,13 +1640,25 @@
       <c r="E38">
         <v>0.03</v>
       </c>
-    </row>
-    <row r="39" spans="1:5">
+      <c r="F38" t="s">
+        <v>58</v>
+      </c>
+      <c r="G38">
+        <v>747.86</v>
+      </c>
+      <c r="H38">
+        <v>0.11</v>
+      </c>
+      <c r="I38">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
       <c r="A39" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B39" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C39">
         <v>890.71</v>
@@ -1198,33 +1669,57 @@
       <c r="E39">
         <v>0.02</v>
       </c>
-    </row>
-    <row r="40" spans="1:5">
+      <c r="F39" t="s">
+        <v>58</v>
+      </c>
+      <c r="G39">
+        <v>890.71</v>
+      </c>
+      <c r="H39">
+        <v>0.09</v>
+      </c>
+      <c r="I39">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
       <c r="A40" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B40" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C40">
-        <v>890.71</v>
+        <v>1069.29</v>
       </c>
       <c r="D40">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="E40">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
+        <v>0.01</v>
+      </c>
+      <c r="F40" t="s">
+        <v>58</v>
+      </c>
+      <c r="G40">
+        <v>1069.29</v>
+      </c>
+      <c r="H40">
+        <v>0.08</v>
+      </c>
+      <c r="I40">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
       <c r="A41" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B41" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C41">
-        <v>1069.29</v>
+        <v>1126.43</v>
       </c>
       <c r="D41">
         <v>0.08</v>
@@ -1232,30 +1727,54 @@
       <c r="E41">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="42" spans="1:5">
+      <c r="F41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G41">
+        <v>1126.43</v>
+      </c>
+      <c r="H41">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I41">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
       <c r="A42" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B42" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C42">
-        <v>1126.43</v>
+        <v>890.71</v>
       </c>
       <c r="D42">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="E42">
+        <v>0.02</v>
+      </c>
+      <c r="F42" t="s">
+        <v>58</v>
+      </c>
+      <c r="G42">
+        <v>1176.43</v>
+      </c>
+      <c r="H42">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I42">
         <v>0.01</v>
       </c>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:9">
       <c r="A43" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B43" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C43">
         <v>1197.86</v>
@@ -1266,13 +1785,25 @@
       <c r="E43">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="44" spans="1:5">
+      <c r="F43" t="s">
+        <v>58</v>
+      </c>
+      <c r="G43">
+        <v>1197.86</v>
+      </c>
+      <c r="H43">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I43">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
       <c r="A44" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B44" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C44">
         <v>1197.86</v>
@@ -1283,13 +1814,25 @@
       <c r="E44">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="45" spans="1:5">
+      <c r="F44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G44">
+        <v>1197.86</v>
+      </c>
+      <c r="H44">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I44">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
       <c r="A45" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B45" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C45">
         <v>1197.86</v>
@@ -1300,13 +1843,25 @@
       <c r="E45">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="46" spans="1:5">
+      <c r="F45" t="s">
+        <v>58</v>
+      </c>
+      <c r="G45">
+        <v>1197.86</v>
+      </c>
+      <c r="H45">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I45">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
       <c r="A46" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B46" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C46">
         <v>1326.43</v>
@@ -1317,13 +1872,25 @@
       <c r="E46">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="47" spans="1:5">
+      <c r="F46" t="s">
+        <v>58</v>
+      </c>
+      <c r="G46">
+        <v>1326.43</v>
+      </c>
+      <c r="H46">
+        <v>0.06</v>
+      </c>
+      <c r="I46">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
       <c r="A47" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B47" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C47">
         <v>1497.86</v>
@@ -1334,13 +1901,25 @@
       <c r="E47">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="48" spans="1:5">
+      <c r="F47" t="s">
+        <v>58</v>
+      </c>
+      <c r="G47">
+        <v>1497.86</v>
+      </c>
+      <c r="H47">
+        <v>0.06</v>
+      </c>
+      <c r="I47">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
       <c r="A48" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B48" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C48">
         <v>1926.43</v>
@@ -1351,13 +1930,25 @@
       <c r="E48">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:5">
+      <c r="F48" t="s">
+        <v>58</v>
+      </c>
+      <c r="G48">
+        <v>1926.43</v>
+      </c>
+      <c r="H48">
+        <v>0.04</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
       <c r="A49" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B49" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C49">
         <v>1926.43</v>
@@ -1366,6 +1957,18 @@
         <v>0.04</v>
       </c>
       <c r="E49">
+        <v>0</v>
+      </c>
+      <c r="F49" t="s">
+        <v>58</v>
+      </c>
+      <c r="G49">
+        <v>1926.43</v>
+      </c>
+      <c r="H49">
+        <v>0.04</v>
+      </c>
+      <c r="I49">
         <v>0</v>
       </c>
     </row>

--- a/processed_data_during_wm/processed_data_wide.xlsx
+++ b/processed_data_during_wm/processed_data_wide.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="64">
   <si>
     <t>Team</t>
   </si>
@@ -43,6 +43,18 @@
     <t>Shin_Wahrscheinlichkeit_in_Prozent_2</t>
   </si>
   <si>
+    <t>Datum_3</t>
+  </si>
+  <si>
+    <t>Durchsch_Quote_3</t>
+  </si>
+  <si>
+    <t>Norm_Wahrscheinlichkeit_in_Prozent_3</t>
+  </si>
+  <si>
+    <t>Shin_Wahrscheinlichkeit_in_Prozent_3</t>
+  </si>
+  <si>
     <t>Frankreich</t>
   </si>
   <si>
@@ -55,12 +67,12 @@
     <t>Portugal</t>
   </si>
   <si>
+    <t>Argentinien</t>
+  </si>
+  <si>
     <t>Brasilien</t>
   </si>
   <si>
-    <t>Argentinien</t>
-  </si>
-  <si>
     <t>Deutschland</t>
   </si>
   <si>
@@ -70,6 +82,9 @@
     <t>Norwegen</t>
   </si>
   <si>
+    <t>Marokko</t>
+  </si>
+  <si>
     <t>Belgien</t>
   </si>
   <si>
@@ -79,19 +94,25 @@
     <t>Kolumbien</t>
   </si>
   <si>
-    <t>Marokko</t>
+    <t>Japan</t>
   </si>
   <si>
     <t>Mexiko</t>
   </si>
   <si>
-    <t>Japan</t>
+    <t>Uruguay</t>
   </si>
   <si>
     <t>Schweiz</t>
   </si>
   <si>
-    <t>Uruguay</t>
+    <t>Kroatien</t>
+  </si>
+  <si>
+    <t>Senegal</t>
+  </si>
+  <si>
+    <t>Schweden</t>
   </si>
   <si>
     <t>Türkei</t>
@@ -100,18 +121,15 @@
     <t>Ecuador</t>
   </si>
   <si>
-    <t>Kroatien</t>
-  </si>
-  <si>
-    <t>Senegal</t>
-  </si>
-  <si>
-    <t>Schweden</t>
+    <t>Elfenbeinküste</t>
   </si>
   <si>
     <t>Österreich</t>
   </si>
   <si>
+    <t>Australien</t>
+  </si>
+  <si>
     <t>Kanada</t>
   </si>
   <si>
@@ -121,24 +139,18 @@
     <t>Schottland</t>
   </si>
   <si>
-    <t>Elfenbeinküste</t>
-  </si>
-  <si>
     <t>Ägypten</t>
   </si>
   <si>
+    <t>Algerien</t>
+  </si>
+  <si>
     <t>Bosnien Herzegowina</t>
   </si>
   <si>
-    <t>Algerien</t>
-  </si>
-  <si>
     <t>Paraguay</t>
   </si>
   <si>
-    <t>Australien</t>
-  </si>
-  <si>
     <t>Tschechien</t>
   </si>
   <si>
@@ -148,15 +160,15 @@
     <t>Iran</t>
   </si>
   <si>
+    <t>DR Kongo</t>
+  </si>
+  <si>
+    <t>Saudi Arabien</t>
+  </si>
+  <si>
     <t>Tunesien</t>
   </si>
   <si>
-    <t>DR Kongo</t>
-  </si>
-  <si>
-    <t>Saudi Arabien</t>
-  </si>
-  <si>
     <t>Katar</t>
   </si>
   <si>
@@ -181,16 +193,19 @@
     <t>Jordanien</t>
   </si>
   <si>
+    <t>Haiti</t>
+  </si>
+  <si>
     <t>Curacao</t>
   </si>
   <si>
-    <t>Haiti</t>
-  </si>
-  <si>
     <t>11.06.2026</t>
   </si>
   <si>
     <t>13.06.2026</t>
+  </si>
+  <si>
+    <t>15.06.2026</t>
   </si>
 </sst>
 </file>
@@ -548,10 +563,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:M49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -579,13 +594,25 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C2">
         <v>6.01</v>
@@ -597,7 +624,7 @@
         <v>15.09</v>
       </c>
       <c r="F2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G2">
         <v>5.55</v>
@@ -608,13 +635,25 @@
       <c r="I2">
         <v>16.26</v>
       </c>
-    </row>
-    <row r="3" spans="1:9">
+      <c r="J2" t="s">
+        <v>63</v>
+      </c>
+      <c r="K2">
+        <v>5.55</v>
+      </c>
+      <c r="L2">
+        <v>15.2</v>
+      </c>
+      <c r="M2">
+        <v>16.3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C3">
         <v>5.58</v>
@@ -626,7 +665,7 @@
         <v>16.29</v>
       </c>
       <c r="F3" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G3">
         <v>5.63</v>
@@ -637,13 +676,25 @@
       <c r="I3">
         <v>16.04</v>
       </c>
-    </row>
-    <row r="4" spans="1:9">
+      <c r="J3" t="s">
+        <v>63</v>
+      </c>
+      <c r="K3">
+        <v>5.63</v>
+      </c>
+      <c r="L3">
+        <v>14.99</v>
+      </c>
+      <c r="M3">
+        <v>16.07</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C4">
         <v>8.15</v>
@@ -655,7 +706,7 @@
         <v>11.06</v>
       </c>
       <c r="F4" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G4">
         <v>8.42</v>
@@ -666,13 +717,25 @@
       <c r="I4">
         <v>10.62</v>
       </c>
-    </row>
-    <row r="5" spans="1:9">
+      <c r="J4" t="s">
+        <v>63</v>
+      </c>
+      <c r="K4">
+        <v>8.390000000000001</v>
+      </c>
+      <c r="L4">
+        <v>10.06</v>
+      </c>
+      <c r="M4">
+        <v>10.69</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C5">
         <v>8.85</v>
@@ -684,7 +747,7 @@
         <v>10.17</v>
       </c>
       <c r="F5" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G5">
         <v>8.699999999999999</v>
@@ -695,71 +758,107 @@
       <c r="I5">
         <v>10.26</v>
       </c>
-    </row>
-    <row r="6" spans="1:9">
+      <c r="J5" t="s">
+        <v>63</v>
+      </c>
+      <c r="K5">
+        <v>8.630000000000001</v>
+      </c>
+      <c r="L5">
+        <v>9.77</v>
+      </c>
+      <c r="M5">
+        <v>10.38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C6">
+        <v>10.19</v>
+      </c>
+      <c r="D6">
+        <v>8.34</v>
+      </c>
+      <c r="E6">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="F6" t="s">
+        <v>62</v>
+      </c>
+      <c r="G6">
+        <v>10.33</v>
+      </c>
+      <c r="H6">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="I6">
+        <v>8.6</v>
+      </c>
+      <c r="J6" t="s">
+        <v>63</v>
+      </c>
+      <c r="K6">
+        <v>10.61</v>
+      </c>
+      <c r="L6">
+        <v>7.95</v>
+      </c>
+      <c r="M6">
+        <v>8.390000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C7">
         <v>9.970000000000001</v>
       </c>
-      <c r="D6">
+      <c r="D7">
         <v>8.52</v>
       </c>
-      <c r="E6">
+      <c r="E7">
         <v>8.99</v>
       </c>
-      <c r="F6" t="s">
-        <v>58</v>
-      </c>
-      <c r="G6">
+      <c r="F7" t="s">
+        <v>62</v>
+      </c>
+      <c r="G7">
         <v>10.11</v>
       </c>
-      <c r="H6">
+      <c r="H7">
         <v>8.32</v>
       </c>
-      <c r="I6">
+      <c r="I7">
         <v>8.789999999999999</v>
       </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" t="s">
-        <v>57</v>
-      </c>
-      <c r="C7">
-        <v>10.19</v>
-      </c>
-      <c r="D7">
-        <v>8.34</v>
-      </c>
-      <c r="E7">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="F7" t="s">
-        <v>58</v>
-      </c>
-      <c r="G7">
-        <v>10.33</v>
-      </c>
-      <c r="H7">
-        <v>8.140000000000001</v>
-      </c>
-      <c r="I7">
-        <v>8.6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
+      <c r="J7" t="s">
+        <v>63</v>
+      </c>
+      <c r="K7">
+        <v>11.04</v>
+      </c>
+      <c r="L7">
+        <v>7.64</v>
+      </c>
+      <c r="M7">
+        <v>8.050000000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C8">
         <v>15.6</v>
@@ -771,7 +870,7 @@
         <v>5.65</v>
       </c>
       <c r="F8" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G8">
         <v>15.67</v>
@@ -782,13 +881,25 @@
       <c r="I8">
         <v>5.57</v>
       </c>
-    </row>
-    <row r="9" spans="1:9">
+      <c r="J8" t="s">
+        <v>63</v>
+      </c>
+      <c r="K8">
+        <v>15.39</v>
+      </c>
+      <c r="L8">
+        <v>5.48</v>
+      </c>
+      <c r="M8">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C9">
         <v>21.29</v>
@@ -800,7 +911,7 @@
         <v>4.07</v>
       </c>
       <c r="F9" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G9">
         <v>20.29</v>
@@ -811,13 +922,25 @@
       <c r="I9">
         <v>4.24</v>
       </c>
-    </row>
-    <row r="10" spans="1:9">
+      <c r="J9" t="s">
+        <v>63</v>
+      </c>
+      <c r="K9">
+        <v>19.71</v>
+      </c>
+      <c r="L9">
+        <v>4.28</v>
+      </c>
+      <c r="M9">
+        <v>4.38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B10" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C10">
         <v>32.29</v>
@@ -829,7 +952,7 @@
         <v>2.6</v>
       </c>
       <c r="F10" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G10">
         <v>33</v>
@@ -840,202 +963,286 @@
       <c r="I10">
         <v>2.49</v>
       </c>
-    </row>
-    <row r="11" spans="1:9">
+      <c r="J10" t="s">
+        <v>63</v>
+      </c>
+      <c r="K10">
+        <v>34.14</v>
+      </c>
+      <c r="L10">
+        <v>2.47</v>
+      </c>
+      <c r="M10">
+        <v>2.42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B11" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C11">
+        <v>49.86</v>
+      </c>
+      <c r="D11">
+        <v>1.7</v>
+      </c>
+      <c r="E11">
+        <v>1.59</v>
+      </c>
+      <c r="F11" t="s">
+        <v>62</v>
+      </c>
+      <c r="G11">
+        <v>50.57</v>
+      </c>
+      <c r="H11">
+        <v>1.66</v>
+      </c>
+      <c r="I11">
+        <v>1.54</v>
+      </c>
+      <c r="J11" t="s">
+        <v>63</v>
+      </c>
+      <c r="K11">
+        <v>38.71</v>
+      </c>
+      <c r="L11">
+        <v>2.18</v>
+      </c>
+      <c r="M11">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12">
         <v>37.71</v>
       </c>
-      <c r="D11">
+      <c r="D12">
         <v>2.25</v>
       </c>
-      <c r="E11">
+      <c r="E12">
         <v>2.19</v>
       </c>
-      <c r="F11" t="s">
-        <v>58</v>
-      </c>
-      <c r="G11">
+      <c r="F12" t="s">
+        <v>62</v>
+      </c>
+      <c r="G12">
         <v>37.71</v>
       </c>
-      <c r="H11">
+      <c r="H12">
         <v>2.23</v>
       </c>
-      <c r="I11">
+      <c r="I12">
         <v>2.15</v>
       </c>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="A12" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" t="s">
-        <v>57</v>
-      </c>
-      <c r="C12">
+      <c r="J12" t="s">
+        <v>63</v>
+      </c>
+      <c r="K12">
+        <v>39.43</v>
+      </c>
+      <c r="L12">
+        <v>2.14</v>
+      </c>
+      <c r="M12">
+        <v>2.06</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" t="s">
+        <v>61</v>
+      </c>
+      <c r="C13">
         <v>63.71</v>
       </c>
-      <c r="D12">
+      <c r="D13">
         <v>1.33</v>
       </c>
-      <c r="E12">
+      <c r="E13">
         <v>1.2</v>
       </c>
-      <c r="F12" t="s">
-        <v>58</v>
-      </c>
-      <c r="G12">
+      <c r="F13" t="s">
+        <v>62</v>
+      </c>
+      <c r="G13">
         <v>44.57</v>
       </c>
-      <c r="H12">
+      <c r="H13">
         <v>1.89</v>
       </c>
-      <c r="I12">
+      <c r="I13">
         <v>1.78</v>
       </c>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="A13" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" t="s">
-        <v>57</v>
-      </c>
-      <c r="C13">
+      <c r="J13" t="s">
+        <v>63</v>
+      </c>
+      <c r="K13">
+        <v>43.86</v>
+      </c>
+      <c r="L13">
+        <v>1.92</v>
+      </c>
+      <c r="M13">
+        <v>1.82</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="A14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" t="s">
+        <v>61</v>
+      </c>
+      <c r="C14">
         <v>41.71</v>
       </c>
-      <c r="D13">
+      <c r="D14">
         <v>2.04</v>
       </c>
-      <c r="E13">
+      <c r="E14">
         <v>1.95</v>
       </c>
-      <c r="F13" t="s">
-        <v>58</v>
-      </c>
-      <c r="G13">
+      <c r="F14" t="s">
+        <v>62</v>
+      </c>
+      <c r="G14">
         <v>45.57</v>
       </c>
-      <c r="H13">
+      <c r="H14">
         <v>1.85</v>
       </c>
-      <c r="I13">
+      <c r="I14">
         <v>1.73</v>
       </c>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="A14" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" t="s">
-        <v>57</v>
-      </c>
-      <c r="C14">
-        <v>49.86</v>
-      </c>
-      <c r="D14">
-        <v>1.7</v>
-      </c>
-      <c r="E14">
+      <c r="J14" t="s">
+        <v>63</v>
+      </c>
+      <c r="K14">
+        <v>47</v>
+      </c>
+      <c r="L14">
+        <v>1.8</v>
+      </c>
+      <c r="M14">
+        <v>1.68</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="A15" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" t="s">
+        <v>61</v>
+      </c>
+      <c r="C15">
+        <v>53.43</v>
+      </c>
+      <c r="D15">
         <v>1.59</v>
       </c>
-      <c r="F14" t="s">
-        <v>58</v>
-      </c>
-      <c r="G14">
-        <v>50.57</v>
-      </c>
-      <c r="H14">
-        <v>1.66</v>
-      </c>
-      <c r="I14">
-        <v>1.54</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
-      <c r="A15" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" t="s">
-        <v>57</v>
-      </c>
-      <c r="C15">
+      <c r="E15">
+        <v>1.47</v>
+      </c>
+      <c r="F15" t="s">
+        <v>62</v>
+      </c>
+      <c r="G15">
+        <v>53.43</v>
+      </c>
+      <c r="H15">
+        <v>1.57</v>
+      </c>
+      <c r="I15">
+        <v>1.44</v>
+      </c>
+      <c r="J15" t="s">
+        <v>63</v>
+      </c>
+      <c r="K15">
+        <v>51.29</v>
+      </c>
+      <c r="L15">
+        <v>1.64</v>
+      </c>
+      <c r="M15">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="A16" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16" t="s">
+        <v>61</v>
+      </c>
+      <c r="C16">
         <v>68.43000000000001</v>
       </c>
-      <c r="D15">
+      <c r="D16">
         <v>1.24</v>
       </c>
-      <c r="E15">
+      <c r="E16">
         <v>1.1</v>
       </c>
-      <c r="F15" t="s">
-        <v>58</v>
-      </c>
-      <c r="G15">
+      <c r="F16" t="s">
+        <v>62</v>
+      </c>
+      <c r="G16">
         <v>52.71</v>
       </c>
-      <c r="H15">
+      <c r="H16">
         <v>1.6</v>
       </c>
-      <c r="I15">
+      <c r="I16">
         <v>1.46</v>
       </c>
-    </row>
-    <row r="16" spans="1:9">
-      <c r="A16" t="s">
-        <v>23</v>
-      </c>
-      <c r="B16" t="s">
-        <v>57</v>
-      </c>
-      <c r="C16">
-        <v>53.43</v>
-      </c>
-      <c r="D16">
-        <v>1.59</v>
-      </c>
-      <c r="E16">
+      <c r="J16" t="s">
+        <v>63</v>
+      </c>
+      <c r="K16">
+        <v>52.71</v>
+      </c>
+      <c r="L16">
+        <v>1.6</v>
+      </c>
+      <c r="M16">
         <v>1.47</v>
       </c>
-      <c r="F16" t="s">
-        <v>58</v>
-      </c>
-      <c r="G16">
-        <v>53.43</v>
-      </c>
-      <c r="H16">
-        <v>1.57</v>
-      </c>
-      <c r="I16">
-        <v>1.44</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9">
+    </row>
+    <row r="17" spans="1:13">
       <c r="A17" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B17" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C17">
-        <v>74.43000000000001</v>
+        <v>71.14</v>
       </c>
       <c r="D17">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="E17">
-        <v>0.99</v>
+        <v>1.05</v>
       </c>
       <c r="F17" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G17">
-        <v>75.14</v>
+        <v>75.29000000000001</v>
       </c>
       <c r="H17">
         <v>1.12</v>
@@ -1043,28 +1250,40 @@
       <c r="I17">
         <v>0.95</v>
       </c>
-    </row>
-    <row r="18" spans="1:9">
+      <c r="J17" t="s">
+        <v>63</v>
+      </c>
+      <c r="K17">
+        <v>75.29000000000001</v>
+      </c>
+      <c r="L17">
+        <v>1.12</v>
+      </c>
+      <c r="M17">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B18" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C18">
-        <v>71.14</v>
+        <v>74.43000000000001</v>
       </c>
       <c r="D18">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="E18">
-        <v>1.05</v>
+        <v>0.99</v>
       </c>
       <c r="F18" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G18">
-        <v>75.29000000000001</v>
+        <v>75.14</v>
       </c>
       <c r="H18">
         <v>1.12</v>
@@ -1072,361 +1291,517 @@
       <c r="I18">
         <v>0.95</v>
       </c>
-    </row>
-    <row r="19" spans="1:9">
+      <c r="J18" t="s">
+        <v>63</v>
+      </c>
+      <c r="K18">
+        <v>83.56999999999999</v>
+      </c>
+      <c r="L18">
+        <v>1.01</v>
+      </c>
+      <c r="M18">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
       <c r="A19" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B19" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C19">
+        <v>88.86</v>
+      </c>
+      <c r="D19">
+        <v>0.96</v>
+      </c>
+      <c r="E19">
+        <v>0.8</v>
+      </c>
+      <c r="F19" t="s">
+        <v>62</v>
+      </c>
+      <c r="G19">
+        <v>91.70999999999999</v>
+      </c>
+      <c r="H19">
+        <v>0.92</v>
+      </c>
+      <c r="I19">
+        <v>0.74</v>
+      </c>
+      <c r="J19" t="s">
+        <v>63</v>
+      </c>
+      <c r="K19">
+        <v>91.70999999999999</v>
+      </c>
+      <c r="L19">
+        <v>0.92</v>
+      </c>
+      <c r="M19">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
+      <c r="A20" t="s">
+        <v>31</v>
+      </c>
+      <c r="B20" t="s">
+        <v>61</v>
+      </c>
+      <c r="C20">
+        <v>101.29</v>
+      </c>
+      <c r="D20">
+        <v>0.84</v>
+      </c>
+      <c r="E20">
+        <v>0.67</v>
+      </c>
+      <c r="F20" t="s">
+        <v>62</v>
+      </c>
+      <c r="G20">
+        <v>106.14</v>
+      </c>
+      <c r="H20">
+        <v>0.79</v>
+      </c>
+      <c r="I20">
+        <v>0.61</v>
+      </c>
+      <c r="J20" t="s">
+        <v>63</v>
+      </c>
+      <c r="K20">
+        <v>107.57</v>
+      </c>
+      <c r="L20">
+        <v>0.78</v>
+      </c>
+      <c r="M20">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
+      <c r="A21" t="s">
+        <v>32</v>
+      </c>
+      <c r="B21" t="s">
+        <v>61</v>
+      </c>
+      <c r="C21">
+        <v>141.29</v>
+      </c>
+      <c r="D21">
+        <v>0.6</v>
+      </c>
+      <c r="E21">
+        <v>0.43</v>
+      </c>
+      <c r="F21" t="s">
+        <v>62</v>
+      </c>
+      <c r="G21">
+        <v>145.57</v>
+      </c>
+      <c r="H21">
+        <v>0.58</v>
+      </c>
+      <c r="I21">
+        <v>0.39</v>
+      </c>
+      <c r="J21" t="s">
+        <v>63</v>
+      </c>
+      <c r="K21">
+        <v>110.14</v>
+      </c>
+      <c r="L21">
+        <v>0.77</v>
+      </c>
+      <c r="M21">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
+      <c r="A22" t="s">
+        <v>33</v>
+      </c>
+      <c r="B22" t="s">
+        <v>61</v>
+      </c>
+      <c r="C22">
         <v>80</v>
       </c>
-      <c r="D19">
+      <c r="D22">
         <v>1.06</v>
       </c>
-      <c r="E19">
+      <c r="E22">
         <v>0.91</v>
       </c>
-      <c r="F19" t="s">
-        <v>58</v>
-      </c>
-      <c r="G19">
+      <c r="F22" t="s">
+        <v>62</v>
+      </c>
+      <c r="G22">
         <v>80</v>
       </c>
-      <c r="H19">
+      <c r="H22">
         <v>1.05</v>
       </c>
-      <c r="I19">
+      <c r="I22">
         <v>0.88</v>
       </c>
-    </row>
-    <row r="20" spans="1:9">
-      <c r="A20" t="s">
-        <v>27</v>
-      </c>
-      <c r="B20" t="s">
-        <v>57</v>
-      </c>
-      <c r="C20">
+      <c r="J22" t="s">
+        <v>63</v>
+      </c>
+      <c r="K22">
+        <v>133.14</v>
+      </c>
+      <c r="L22">
+        <v>0.63</v>
+      </c>
+      <c r="M22">
+        <v>0.46</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
+      <c r="A23" t="s">
+        <v>34</v>
+      </c>
+      <c r="B23" t="s">
+        <v>61</v>
+      </c>
+      <c r="C23">
         <v>89</v>
       </c>
-      <c r="D20">
+      <c r="D23">
         <v>0.95</v>
       </c>
-      <c r="E20">
+      <c r="E23">
         <v>0.8</v>
       </c>
-      <c r="F20" t="s">
-        <v>58</v>
-      </c>
-      <c r="G20">
+      <c r="F23" t="s">
+        <v>62</v>
+      </c>
+      <c r="G23">
         <v>90.43000000000001</v>
       </c>
-      <c r="H20">
+      <c r="H23">
         <v>0.93</v>
       </c>
-      <c r="I20">
+      <c r="I23">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="21" spans="1:9">
-      <c r="A21" t="s">
-        <v>28</v>
-      </c>
-      <c r="B21" t="s">
-        <v>57</v>
-      </c>
-      <c r="C21">
-        <v>88.86</v>
-      </c>
-      <c r="D21">
-        <v>0.96</v>
-      </c>
-      <c r="E21">
-        <v>0.8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>58</v>
-      </c>
-      <c r="G21">
-        <v>91.70999999999999</v>
-      </c>
-      <c r="H21">
-        <v>0.92</v>
-      </c>
-      <c r="I21">
-        <v>0.74</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9">
-      <c r="A22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B22" t="s">
-        <v>57</v>
-      </c>
-      <c r="C22">
-        <v>101.29</v>
-      </c>
-      <c r="D22">
-        <v>0.84</v>
-      </c>
-      <c r="E22">
-        <v>0.67</v>
-      </c>
-      <c r="F22" t="s">
-        <v>58</v>
-      </c>
-      <c r="G22">
-        <v>106.14</v>
-      </c>
-      <c r="H22">
-        <v>0.79</v>
-      </c>
-      <c r="I22">
-        <v>0.61</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9">
-      <c r="A23" t="s">
-        <v>30</v>
-      </c>
-      <c r="B23" t="s">
-        <v>57</v>
-      </c>
-      <c r="C23">
-        <v>141.29</v>
-      </c>
-      <c r="D23">
-        <v>0.6</v>
-      </c>
-      <c r="E23">
-        <v>0.43</v>
-      </c>
-      <c r="F23" t="s">
-        <v>58</v>
-      </c>
-      <c r="G23">
-        <v>145.57</v>
-      </c>
-      <c r="H23">
-        <v>0.58</v>
-      </c>
-      <c r="I23">
+      <c r="J23" t="s">
+        <v>63</v>
+      </c>
+      <c r="K23">
+        <v>133.71</v>
+      </c>
+      <c r="L23">
+        <v>0.63</v>
+      </c>
+      <c r="M23">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
+      <c r="A24" t="s">
+        <v>35</v>
+      </c>
+      <c r="B24" t="s">
+        <v>61</v>
+      </c>
+      <c r="C24">
+        <v>250</v>
+      </c>
+      <c r="D24">
+        <v>0.34</v>
+      </c>
+      <c r="E24">
+        <v>0.18</v>
+      </c>
+      <c r="F24" t="s">
+        <v>62</v>
+      </c>
+      <c r="G24">
+        <v>259.86</v>
+      </c>
+      <c r="H24">
+        <v>0.32</v>
+      </c>
+      <c r="I24">
+        <v>0.16</v>
+      </c>
+      <c r="J24" t="s">
+        <v>63</v>
+      </c>
+      <c r="K24">
+        <v>153</v>
+      </c>
+      <c r="L24">
+        <v>0.55</v>
+      </c>
+      <c r="M24">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
+      <c r="A25" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25" t="s">
+        <v>61</v>
+      </c>
+      <c r="C25">
+        <v>153</v>
+      </c>
+      <c r="D25">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E25">
         <v>0.39</v>
       </c>
-    </row>
-    <row r="24" spans="1:9">
-      <c r="A24" t="s">
-        <v>31</v>
-      </c>
-      <c r="B24" t="s">
-        <v>57</v>
-      </c>
-      <c r="C24">
-        <v>153</v>
-      </c>
-      <c r="D24">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="E24">
-        <v>0.39</v>
-      </c>
-      <c r="F24" t="s">
-        <v>58</v>
-      </c>
-      <c r="G24">
+      <c r="F25" t="s">
+        <v>62</v>
+      </c>
+      <c r="G25">
         <v>158.57</v>
       </c>
-      <c r="H24">
+      <c r="H25">
         <v>0.53</v>
       </c>
-      <c r="I24">
+      <c r="I25">
         <v>0.35</v>
       </c>
-    </row>
-    <row r="25" spans="1:9">
-      <c r="A25" t="s">
-        <v>32</v>
-      </c>
-      <c r="B25" t="s">
-        <v>57</v>
-      </c>
-      <c r="C25">
+      <c r="J25" t="s">
+        <v>63</v>
+      </c>
+      <c r="K25">
+        <v>157.14</v>
+      </c>
+      <c r="L25">
+        <v>0.54</v>
+      </c>
+      <c r="M25">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13">
+      <c r="A26" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26" t="s">
+        <v>61</v>
+      </c>
+      <c r="C26">
+        <v>442.71</v>
+      </c>
+      <c r="D26">
+        <v>0.19</v>
+      </c>
+      <c r="E26">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="F26" t="s">
+        <v>62</v>
+      </c>
+      <c r="G26">
+        <v>462.29</v>
+      </c>
+      <c r="H26">
+        <v>0.18</v>
+      </c>
+      <c r="I26">
+        <v>0.06</v>
+      </c>
+      <c r="J26" t="s">
+        <v>63</v>
+      </c>
+      <c r="K26">
+        <v>186</v>
+      </c>
+      <c r="L26">
+        <v>0.45</v>
+      </c>
+      <c r="M26">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
+      <c r="A27" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" t="s">
+        <v>61</v>
+      </c>
+      <c r="C27">
         <v>191.71</v>
       </c>
-      <c r="D25">
+      <c r="D27">
         <v>0.44</v>
       </c>
-      <c r="E25">
+      <c r="E27">
         <v>0.28</v>
       </c>
-      <c r="F25" t="s">
-        <v>58</v>
-      </c>
-      <c r="G25">
+      <c r="F27" t="s">
+        <v>62</v>
+      </c>
+      <c r="G27">
         <v>222.71</v>
       </c>
-      <c r="H25">
+      <c r="H27">
         <v>0.38</v>
       </c>
-      <c r="I25">
+      <c r="I27">
         <v>0.21</v>
       </c>
-    </row>
-    <row r="26" spans="1:9">
-      <c r="A26" t="s">
-        <v>33</v>
-      </c>
-      <c r="B26" t="s">
-        <v>57</v>
-      </c>
-      <c r="C26">
+      <c r="J27" t="s">
+        <v>63</v>
+      </c>
+      <c r="K27">
+        <v>193.29</v>
+      </c>
+      <c r="L27">
+        <v>0.44</v>
+      </c>
+      <c r="M27">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13">
+      <c r="A28" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28" t="s">
+        <v>61</v>
+      </c>
+      <c r="C28">
         <v>376.29</v>
       </c>
-      <c r="D26">
+      <c r="D28">
         <v>0.23</v>
       </c>
-      <c r="E26">
+      <c r="E28">
         <v>0.09</v>
       </c>
-      <c r="F26" t="s">
-        <v>58</v>
-      </c>
-      <c r="G26">
+      <c r="F28" t="s">
+        <v>62</v>
+      </c>
+      <c r="G28">
         <v>241</v>
       </c>
-      <c r="H26">
+      <c r="H28">
         <v>0.35</v>
       </c>
-      <c r="I26">
+      <c r="I28">
         <v>0.18</v>
       </c>
-    </row>
-    <row r="27" spans="1:9">
-      <c r="A27" t="s">
-        <v>34</v>
-      </c>
-      <c r="B27" t="s">
-        <v>57</v>
-      </c>
-      <c r="C27">
+      <c r="J28" t="s">
+        <v>63</v>
+      </c>
+      <c r="K28">
+        <v>224.29</v>
+      </c>
+      <c r="L28">
+        <v>0.38</v>
+      </c>
+      <c r="M28">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13">
+      <c r="A29" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" t="s">
+        <v>61</v>
+      </c>
+      <c r="C29">
         <v>249.71</v>
       </c>
-      <c r="D27">
+      <c r="D29">
         <v>0.34</v>
       </c>
-      <c r="E27">
+      <c r="E29">
         <v>0.18</v>
       </c>
-      <c r="F27" t="s">
-        <v>58</v>
-      </c>
-      <c r="G27">
+      <c r="F29" t="s">
+        <v>62</v>
+      </c>
+      <c r="G29">
         <v>242.57</v>
       </c>
-      <c r="H27">
+      <c r="H29">
         <v>0.35</v>
       </c>
-      <c r="I27">
+      <c r="I29">
         <v>0.18</v>
       </c>
-    </row>
-    <row r="28" spans="1:9">
-      <c r="A28" t="s">
-        <v>35</v>
-      </c>
-      <c r="B28" t="s">
-        <v>57</v>
-      </c>
-      <c r="C28">
-        <v>250</v>
-      </c>
-      <c r="D28">
-        <v>0.34</v>
-      </c>
-      <c r="E28">
-        <v>0.18</v>
-      </c>
-      <c r="F28" t="s">
-        <v>58</v>
-      </c>
-      <c r="G28">
-        <v>259.86</v>
-      </c>
-      <c r="H28">
-        <v>0.32</v>
-      </c>
-      <c r="I28">
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9">
-      <c r="A29" t="s">
-        <v>36</v>
-      </c>
-      <c r="B29" t="s">
-        <v>57</v>
-      </c>
-      <c r="C29">
+      <c r="J29" t="s">
+        <v>63</v>
+      </c>
+      <c r="K29">
+        <v>228.14</v>
+      </c>
+      <c r="L29">
+        <v>0.37</v>
+      </c>
+      <c r="M29">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13">
+      <c r="A30" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" t="s">
+        <v>61</v>
+      </c>
+      <c r="C30">
         <v>320.43</v>
       </c>
-      <c r="D29">
+      <c r="D30">
         <v>0.26</v>
       </c>
-      <c r="E29">
+      <c r="E30">
         <v>0.12</v>
       </c>
-      <c r="F29" t="s">
-        <v>58</v>
-      </c>
-      <c r="G29">
+      <c r="F30" t="s">
+        <v>62</v>
+      </c>
+      <c r="G30">
         <v>351.57</v>
       </c>
-      <c r="H29">
+      <c r="H30">
         <v>0.24</v>
       </c>
-      <c r="I29">
+      <c r="I30">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="30" spans="1:9">
-      <c r="A30" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" t="s">
-        <v>57</v>
-      </c>
-      <c r="C30">
-        <v>370.43</v>
-      </c>
-      <c r="D30">
-        <v>0.23</v>
-      </c>
-      <c r="E30">
+      <c r="J30" t="s">
+        <v>63</v>
+      </c>
+      <c r="K30">
+        <v>341.71</v>
+      </c>
+      <c r="L30">
+        <v>0.25</v>
+      </c>
+      <c r="M30">
         <v>0.1</v>
       </c>
-      <c r="F30" t="s">
-        <v>58</v>
-      </c>
-      <c r="G30">
-        <v>376.71</v>
-      </c>
-      <c r="H30">
-        <v>0.22</v>
-      </c>
-      <c r="I30">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9">
+    </row>
+    <row r="31" spans="1:13">
       <c r="A31" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B31" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C31">
         <v>367.57</v>
@@ -1438,7 +1813,7 @@
         <v>0.1</v>
       </c>
       <c r="F31" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G31">
         <v>383</v>
@@ -1449,57 +1824,81 @@
       <c r="I31">
         <v>0.08</v>
       </c>
-    </row>
-    <row r="32" spans="1:9">
+      <c r="J31" t="s">
+        <v>63</v>
+      </c>
+      <c r="K31">
+        <v>378.86</v>
+      </c>
+      <c r="L31">
+        <v>0.22</v>
+      </c>
+      <c r="M31">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13">
       <c r="A32" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B32" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C32">
+        <v>370.43</v>
+      </c>
+      <c r="D32">
+        <v>0.23</v>
+      </c>
+      <c r="E32">
+        <v>0.1</v>
+      </c>
+      <c r="F32" t="s">
+        <v>62</v>
+      </c>
+      <c r="G32">
+        <v>376.71</v>
+      </c>
+      <c r="H32">
+        <v>0.22</v>
+      </c>
+      <c r="I32">
+        <v>0.08</v>
+      </c>
+      <c r="J32" t="s">
+        <v>63</v>
+      </c>
+      <c r="K32">
+        <v>383.71</v>
+      </c>
+      <c r="L32">
+        <v>0.22</v>
+      </c>
+      <c r="M32">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13">
+      <c r="A33" t="s">
+        <v>44</v>
+      </c>
+      <c r="B33" t="s">
+        <v>61</v>
+      </c>
+      <c r="C33">
         <v>243.29</v>
       </c>
-      <c r="D32">
+      <c r="D33">
         <v>0.35</v>
       </c>
-      <c r="E32">
+      <c r="E33">
         <v>0.19</v>
       </c>
-      <c r="F32" t="s">
-        <v>58</v>
-      </c>
-      <c r="G32">
+      <c r="F33" t="s">
+        <v>62</v>
+      </c>
+      <c r="G33">
         <v>455.57</v>
-      </c>
-      <c r="H32">
-        <v>0.18</v>
-      </c>
-      <c r="I32">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9">
-      <c r="A33" t="s">
-        <v>40</v>
-      </c>
-      <c r="B33" t="s">
-        <v>57</v>
-      </c>
-      <c r="C33">
-        <v>442.71</v>
-      </c>
-      <c r="D33">
-        <v>0.19</v>
-      </c>
-      <c r="E33">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="F33" t="s">
-        <v>58</v>
-      </c>
-      <c r="G33">
-        <v>462.29</v>
       </c>
       <c r="H33">
         <v>0.18</v>
@@ -1507,13 +1906,25 @@
       <c r="I33">
         <v>0.06</v>
       </c>
-    </row>
-    <row r="34" spans="1:9">
+      <c r="J33" t="s">
+        <v>63</v>
+      </c>
+      <c r="K33">
+        <v>483.57</v>
+      </c>
+      <c r="L33">
+        <v>0.17</v>
+      </c>
+      <c r="M33">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13">
       <c r="A34" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B34" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C34">
         <v>299.29</v>
@@ -1525,7 +1936,7 @@
         <v>0.14</v>
       </c>
       <c r="F34" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G34">
         <v>497.86</v>
@@ -1536,13 +1947,25 @@
       <c r="I34">
         <v>0.05</v>
       </c>
-    </row>
-    <row r="35" spans="1:9">
+      <c r="J34" t="s">
+        <v>63</v>
+      </c>
+      <c r="K34">
+        <v>486.71</v>
+      </c>
+      <c r="L34">
+        <v>0.17</v>
+      </c>
+      <c r="M34">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13">
       <c r="A35" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B35" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C35">
         <v>467.14</v>
@@ -1554,7 +1977,7 @@
         <v>0.06</v>
       </c>
       <c r="F35" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G35">
         <v>505.29</v>
@@ -1565,13 +1988,25 @@
       <c r="I35">
         <v>0.05</v>
       </c>
-    </row>
-    <row r="36" spans="1:9">
+      <c r="J35" t="s">
+        <v>63</v>
+      </c>
+      <c r="K35">
+        <v>494.14</v>
+      </c>
+      <c r="L35">
+        <v>0.17</v>
+      </c>
+      <c r="M35">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13">
       <c r="A36" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B36" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C36">
         <v>540.71</v>
@@ -1583,7 +2018,7 @@
         <v>0.05</v>
       </c>
       <c r="F36" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G36">
         <v>576.4299999999999</v>
@@ -1594,100 +2029,148 @@
       <c r="I36">
         <v>0.04</v>
       </c>
-    </row>
-    <row r="37" spans="1:9">
+      <c r="J36" t="s">
+        <v>63</v>
+      </c>
+      <c r="K36">
+        <v>576.4299999999999</v>
+      </c>
+      <c r="L36">
+        <v>0.15</v>
+      </c>
+      <c r="M36">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13">
       <c r="A37" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B37" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C37">
-        <v>605</v>
+        <v>747.86</v>
       </c>
       <c r="D37">
-        <v>0.14</v>
+        <v>0.11</v>
       </c>
       <c r="E37">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="F37" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G37">
-        <v>640.71</v>
+        <v>747.86</v>
       </c>
       <c r="H37">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="I37">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9">
+        <v>0.02</v>
+      </c>
+      <c r="J37" t="s">
+        <v>63</v>
+      </c>
+      <c r="K37">
+        <v>747.86</v>
+      </c>
+      <c r="L37">
+        <v>0.11</v>
+      </c>
+      <c r="M37">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13">
       <c r="A38" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B38" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C38">
-        <v>747.86</v>
+        <v>890.71</v>
       </c>
       <c r="D38">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="E38">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="F38" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G38">
-        <v>747.86</v>
+        <v>890.71</v>
       </c>
       <c r="H38">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="I38">
         <v>0.02</v>
       </c>
-    </row>
-    <row r="39" spans="1:9">
+      <c r="J38" t="s">
+        <v>63</v>
+      </c>
+      <c r="K38">
+        <v>890.71</v>
+      </c>
+      <c r="L38">
+        <v>0.09</v>
+      </c>
+      <c r="M38">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13">
       <c r="A39" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B39" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C39">
+        <v>605</v>
+      </c>
+      <c r="D39">
+        <v>0.14</v>
+      </c>
+      <c r="E39">
+        <v>0.04</v>
+      </c>
+      <c r="F39" t="s">
+        <v>62</v>
+      </c>
+      <c r="G39">
+        <v>640.71</v>
+      </c>
+      <c r="H39">
+        <v>0.13</v>
+      </c>
+      <c r="I39">
+        <v>0.03</v>
+      </c>
+      <c r="J39" t="s">
+        <v>63</v>
+      </c>
+      <c r="K39">
         <v>890.71</v>
       </c>
-      <c r="D39">
-        <v>0.1</v>
-      </c>
-      <c r="E39">
+      <c r="L39">
+        <v>0.09</v>
+      </c>
+      <c r="M39">
         <v>0.02</v>
       </c>
-      <c r="F39" t="s">
-        <v>58</v>
-      </c>
-      <c r="G39">
-        <v>890.71</v>
-      </c>
-      <c r="H39">
-        <v>0.09</v>
-      </c>
-      <c r="I39">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9">
+    </row>
+    <row r="40" spans="1:13">
       <c r="A40" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B40" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C40">
         <v>1069.29</v>
@@ -1699,7 +2182,7 @@
         <v>0.01</v>
       </c>
       <c r="F40" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G40">
         <v>1069.29</v>
@@ -1710,13 +2193,25 @@
       <c r="I40">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="41" spans="1:9">
+      <c r="J40" t="s">
+        <v>63</v>
+      </c>
+      <c r="K40">
+        <v>1069.29</v>
+      </c>
+      <c r="L40">
+        <v>0.08</v>
+      </c>
+      <c r="M40">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13">
       <c r="A41" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B41" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C41">
         <v>1126.43</v>
@@ -1728,7 +2223,7 @@
         <v>0.01</v>
       </c>
       <c r="F41" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G41">
         <v>1126.43</v>
@@ -1739,13 +2234,25 @@
       <c r="I41">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="42" spans="1:9">
+      <c r="J41" t="s">
+        <v>63</v>
+      </c>
+      <c r="K41">
+        <v>1126.43</v>
+      </c>
+      <c r="L41">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="M41">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13">
       <c r="A42" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B42" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C42">
         <v>890.71</v>
@@ -1757,7 +2264,7 @@
         <v>0.02</v>
       </c>
       <c r="F42" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G42">
         <v>1176.43</v>
@@ -1768,13 +2275,25 @@
       <c r="I42">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="43" spans="1:9">
+      <c r="J42" t="s">
+        <v>63</v>
+      </c>
+      <c r="K42">
+        <v>1176.43</v>
+      </c>
+      <c r="L42">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="M42">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13">
       <c r="A43" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B43" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C43">
         <v>1197.86</v>
@@ -1786,7 +2305,7 @@
         <v>0.01</v>
       </c>
       <c r="F43" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G43">
         <v>1197.86</v>
@@ -1797,13 +2316,25 @@
       <c r="I43">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="44" spans="1:9">
+      <c r="J43" t="s">
+        <v>63</v>
+      </c>
+      <c r="K43">
+        <v>1197.86</v>
+      </c>
+      <c r="L43">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="M43">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13">
       <c r="A44" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B44" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C44">
         <v>1197.86</v>
@@ -1815,7 +2346,7 @@
         <v>0.01</v>
       </c>
       <c r="F44" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G44">
         <v>1197.86</v>
@@ -1826,13 +2357,25 @@
       <c r="I44">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="45" spans="1:9">
+      <c r="J44" t="s">
+        <v>63</v>
+      </c>
+      <c r="K44">
+        <v>1197.86</v>
+      </c>
+      <c r="L44">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="M44">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13">
       <c r="A45" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B45" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C45">
         <v>1197.86</v>
@@ -1844,7 +2387,7 @@
         <v>0.01</v>
       </c>
       <c r="F45" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G45">
         <v>1197.86</v>
@@ -1855,13 +2398,25 @@
       <c r="I45">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="46" spans="1:9">
+      <c r="J45" t="s">
+        <v>63</v>
+      </c>
+      <c r="K45">
+        <v>1197.86</v>
+      </c>
+      <c r="L45">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="M45">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13">
       <c r="A46" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B46" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C46">
         <v>1326.43</v>
@@ -1873,7 +2428,7 @@
         <v>0.01</v>
       </c>
       <c r="F46" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G46">
         <v>1326.43</v>
@@ -1884,13 +2439,25 @@
       <c r="I46">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="47" spans="1:9">
+      <c r="J46" t="s">
+        <v>63</v>
+      </c>
+      <c r="K46">
+        <v>1326.43</v>
+      </c>
+      <c r="L46">
+        <v>0.06</v>
+      </c>
+      <c r="M46">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13">
       <c r="A47" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B47" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C47">
         <v>1497.86</v>
@@ -1902,7 +2469,7 @@
         <v>0.01</v>
       </c>
       <c r="F47" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G47">
         <v>1497.86</v>
@@ -1913,13 +2480,25 @@
       <c r="I47">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="48" spans="1:9">
+      <c r="J47" t="s">
+        <v>63</v>
+      </c>
+      <c r="K47">
+        <v>1497.86</v>
+      </c>
+      <c r="L47">
+        <v>0.06</v>
+      </c>
+      <c r="M47">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13">
       <c r="A48" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B48" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C48">
         <v>1926.43</v>
@@ -1931,7 +2510,7 @@
         <v>0</v>
       </c>
       <c r="F48" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G48">
         <v>1926.43</v>
@@ -1942,13 +2521,25 @@
       <c r="I48">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:9">
+      <c r="J48" t="s">
+        <v>63</v>
+      </c>
+      <c r="K48">
+        <v>2033.57</v>
+      </c>
+      <c r="L48">
+        <v>0.04</v>
+      </c>
+      <c r="M48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13">
       <c r="A49" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B49" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C49">
         <v>1926.43</v>
@@ -1960,7 +2551,7 @@
         <v>0</v>
       </c>
       <c r="F49" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G49">
         <v>1926.43</v>
@@ -1969,6 +2560,18 @@
         <v>0.04</v>
       </c>
       <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49" t="s">
+        <v>63</v>
+      </c>
+      <c r="K49">
+        <v>2355</v>
+      </c>
+      <c r="L49">
+        <v>0.04</v>
+      </c>
+      <c r="M49">
         <v>0</v>
       </c>
     </row>

--- a/processed_data_during_wm/processed_data_wide.xlsx
+++ b/processed_data_during_wm/processed_data_wide.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="69">
   <si>
     <t>Team</t>
   </si>
@@ -55,6 +55,18 @@
     <t>Shin_Wahrscheinlichkeit_in_Prozent_3</t>
   </si>
   <si>
+    <t>Datum_4</t>
+  </si>
+  <si>
+    <t>Durchsch_Quote_4</t>
+  </si>
+  <si>
+    <t>Norm_Wahrscheinlichkeit_in_Prozent_4</t>
+  </si>
+  <si>
+    <t>Shin_Wahrscheinlichkeit_in_Prozent_4</t>
+  </si>
+  <si>
     <t>Frankreich</t>
   </si>
   <si>
@@ -85,12 +97,12 @@
     <t>Marokko</t>
   </si>
   <si>
+    <t>USA</t>
+  </si>
+  <si>
     <t>Belgien</t>
   </si>
   <si>
-    <t>USA</t>
-  </si>
-  <si>
     <t>Kolumbien</t>
   </si>
   <si>
@@ -109,45 +121,45 @@
     <t>Kroatien</t>
   </si>
   <si>
+    <t>Schweden</t>
+  </si>
+  <si>
     <t>Senegal</t>
   </si>
   <si>
-    <t>Schweden</t>
+    <t>Australien</t>
+  </si>
+  <si>
+    <t>Ecuador</t>
+  </si>
+  <si>
+    <t>Österreich</t>
+  </si>
+  <si>
+    <t>Elfenbeinküste</t>
   </si>
   <si>
     <t>Türkei</t>
   </si>
   <si>
-    <t>Ecuador</t>
-  </si>
-  <si>
-    <t>Elfenbeinküste</t>
-  </si>
-  <si>
-    <t>Österreich</t>
-  </si>
-  <si>
-    <t>Australien</t>
-  </si>
-  <si>
     <t>Kanada</t>
   </si>
   <si>
+    <t>Schottland</t>
+  </si>
+  <si>
     <t>Südkorea</t>
   </si>
   <si>
-    <t>Schottland</t>
-  </si>
-  <si>
     <t>Ägypten</t>
   </si>
   <si>
+    <t>Bosnien Herzegowina</t>
+  </si>
+  <si>
     <t>Algerien</t>
   </si>
   <si>
-    <t>Bosnien Herzegowina</t>
-  </si>
-  <si>
     <t>Paraguay</t>
   </si>
   <si>
@@ -166,30 +178,30 @@
     <t>Saudi Arabien</t>
   </si>
   <si>
+    <t>Neuseeland</t>
+  </si>
+  <si>
     <t>Tunesien</t>
   </si>
   <si>
+    <t>Kap Verde</t>
+  </si>
+  <si>
     <t>Katar</t>
   </si>
   <si>
+    <t>Südafrika</t>
+  </si>
+  <si>
     <t>Irak</t>
   </si>
   <si>
-    <t>Südafrika</t>
-  </si>
-  <si>
-    <t>Neuseeland</t>
-  </si>
-  <si>
     <t>Panama</t>
   </si>
   <si>
     <t>Usbekistan</t>
   </si>
   <si>
-    <t>Kap Verde</t>
-  </si>
-  <si>
     <t>Jordanien</t>
   </si>
   <si>
@@ -206,6 +218,9 @@
   </si>
   <si>
     <t>15.06.2026</t>
+  </si>
+  <si>
+    <t>17.06.2026</t>
   </si>
 </sst>
 </file>
@@ -563,10 +578,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M49"/>
+  <dimension ref="A1:Q49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -606,13 +621,25 @@
       <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C2">
         <v>6.01</v>
@@ -624,7 +651,7 @@
         <v>15.09</v>
       </c>
       <c r="F2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G2">
         <v>5.55</v>
@@ -636,7 +663,7 @@
         <v>16.26</v>
       </c>
       <c r="J2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K2">
         <v>5.55</v>
@@ -647,13 +674,25 @@
       <c r="M2">
         <v>16.3</v>
       </c>
-    </row>
-    <row r="3" spans="1:13">
+      <c r="N2" t="s">
+        <v>68</v>
+      </c>
+      <c r="O2">
+        <v>4.97</v>
+      </c>
+      <c r="P2">
+        <v>16.81</v>
+      </c>
+      <c r="Q2">
+        <v>18.14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C3">
         <v>5.58</v>
@@ -665,7 +704,7 @@
         <v>16.29</v>
       </c>
       <c r="F3" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G3">
         <v>5.63</v>
@@ -677,7 +716,7 @@
         <v>16.04</v>
       </c>
       <c r="J3" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K3">
         <v>5.63</v>
@@ -688,13 +727,25 @@
       <c r="M3">
         <v>16.07</v>
       </c>
-    </row>
-    <row r="4" spans="1:13">
+      <c r="N3" t="s">
+        <v>68</v>
+      </c>
+      <c r="O3">
+        <v>6.51</v>
+      </c>
+      <c r="P3">
+        <v>12.83</v>
+      </c>
+      <c r="Q3">
+        <v>13.76</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C4">
         <v>8.15</v>
@@ -706,7 +757,7 @@
         <v>11.06</v>
       </c>
       <c r="F4" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G4">
         <v>8.42</v>
@@ -718,7 +769,7 @@
         <v>10.62</v>
       </c>
       <c r="J4" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K4">
         <v>8.390000000000001</v>
@@ -729,13 +780,25 @@
       <c r="M4">
         <v>10.69</v>
       </c>
-    </row>
-    <row r="5" spans="1:13">
+      <c r="N4" t="s">
+        <v>68</v>
+      </c>
+      <c r="O4">
+        <v>8.33</v>
+      </c>
+      <c r="P4">
+        <v>10.02</v>
+      </c>
+      <c r="Q4">
+        <v>10.68</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B5" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C5">
         <v>8.85</v>
@@ -747,7 +810,7 @@
         <v>10.17</v>
       </c>
       <c r="F5" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G5">
         <v>8.699999999999999</v>
@@ -759,7 +822,7 @@
         <v>10.26</v>
       </c>
       <c r="J5" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K5">
         <v>8.630000000000001</v>
@@ -770,13 +833,25 @@
       <c r="M5">
         <v>10.38</v>
       </c>
-    </row>
-    <row r="6" spans="1:13">
+      <c r="N5" t="s">
+        <v>68</v>
+      </c>
+      <c r="O5">
+        <v>8.619999999999999</v>
+      </c>
+      <c r="P5">
+        <v>9.69</v>
+      </c>
+      <c r="Q5">
+        <v>10.32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B6" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C6">
         <v>10.19</v>
@@ -788,7 +863,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="F6" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G6">
         <v>10.33</v>
@@ -800,7 +875,7 @@
         <v>8.6</v>
       </c>
       <c r="J6" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K6">
         <v>10.61</v>
@@ -811,13 +886,25 @@
       <c r="M6">
         <v>8.390000000000001</v>
       </c>
-    </row>
-    <row r="7" spans="1:13">
+      <c r="N6" t="s">
+        <v>68</v>
+      </c>
+      <c r="O6">
+        <v>9.4</v>
+      </c>
+      <c r="P6">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="Q6">
+        <v>9.44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B7" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C7">
         <v>9.970000000000001</v>
@@ -829,7 +916,7 @@
         <v>8.99</v>
       </c>
       <c r="F7" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G7">
         <v>10.11</v>
@@ -841,7 +928,7 @@
         <v>8.789999999999999</v>
       </c>
       <c r="J7" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K7">
         <v>11.04</v>
@@ -852,13 +939,25 @@
       <c r="M7">
         <v>8.050000000000001</v>
       </c>
-    </row>
-    <row r="8" spans="1:13">
+      <c r="N7" t="s">
+        <v>68</v>
+      </c>
+      <c r="O7">
+        <v>11.39</v>
+      </c>
+      <c r="P7">
+        <v>7.33</v>
+      </c>
+      <c r="Q7">
+        <v>7.74</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C8">
         <v>15.6</v>
@@ -870,7 +969,7 @@
         <v>5.65</v>
       </c>
       <c r="F8" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G8">
         <v>15.67</v>
@@ -882,7 +981,7 @@
         <v>5.57</v>
       </c>
       <c r="J8" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K8">
         <v>15.39</v>
@@ -893,13 +992,25 @@
       <c r="M8">
         <v>5.7</v>
       </c>
-    </row>
-    <row r="9" spans="1:13">
+      <c r="N8" t="s">
+        <v>68</v>
+      </c>
+      <c r="O8">
+        <v>14.67</v>
+      </c>
+      <c r="P8">
+        <v>5.69</v>
+      </c>
+      <c r="Q8">
+        <v>5.93</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B9" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C9">
         <v>21.29</v>
@@ -911,7 +1022,7 @@
         <v>4.07</v>
       </c>
       <c r="F9" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G9">
         <v>20.29</v>
@@ -923,7 +1034,7 @@
         <v>4.24</v>
       </c>
       <c r="J9" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K9">
         <v>19.71</v>
@@ -934,13 +1045,25 @@
       <c r="M9">
         <v>4.38</v>
       </c>
-    </row>
-    <row r="10" spans="1:13">
+      <c r="N9" t="s">
+        <v>68</v>
+      </c>
+      <c r="O9">
+        <v>20.14</v>
+      </c>
+      <c r="P9">
+        <v>4.15</v>
+      </c>
+      <c r="Q9">
+        <v>4.24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C10">
         <v>32.29</v>
@@ -952,7 +1075,7 @@
         <v>2.6</v>
       </c>
       <c r="F10" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G10">
         <v>33</v>
@@ -964,7 +1087,7 @@
         <v>2.49</v>
       </c>
       <c r="J10" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K10">
         <v>34.14</v>
@@ -975,13 +1098,25 @@
       <c r="M10">
         <v>2.42</v>
       </c>
-    </row>
-    <row r="11" spans="1:13">
+      <c r="N10" t="s">
+        <v>68</v>
+      </c>
+      <c r="O10">
+        <v>30.43</v>
+      </c>
+      <c r="P10">
+        <v>2.74</v>
+      </c>
+      <c r="Q10">
+        <v>2.71</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B11" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C11">
         <v>49.86</v>
@@ -993,7 +1128,7 @@
         <v>1.59</v>
       </c>
       <c r="F11" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G11">
         <v>50.57</v>
@@ -1005,7 +1140,7 @@
         <v>1.54</v>
       </c>
       <c r="J11" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K11">
         <v>38.71</v>
@@ -1016,95 +1151,131 @@
       <c r="M11">
         <v>2.1</v>
       </c>
-    </row>
-    <row r="12" spans="1:13">
+      <c r="N11" t="s">
+        <v>68</v>
+      </c>
+      <c r="O11">
+        <v>37.71</v>
+      </c>
+      <c r="P11">
+        <v>2.21</v>
+      </c>
+      <c r="Q11">
+        <v>2.13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B12" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C12">
+        <v>63.71</v>
+      </c>
+      <c r="D12">
+        <v>1.33</v>
+      </c>
+      <c r="E12">
+        <v>1.2</v>
+      </c>
+      <c r="F12" t="s">
+        <v>66</v>
+      </c>
+      <c r="G12">
+        <v>44.57</v>
+      </c>
+      <c r="H12">
+        <v>1.89</v>
+      </c>
+      <c r="I12">
+        <v>1.78</v>
+      </c>
+      <c r="J12" t="s">
+        <v>67</v>
+      </c>
+      <c r="K12">
+        <v>43.86</v>
+      </c>
+      <c r="L12">
+        <v>1.92</v>
+      </c>
+      <c r="M12">
+        <v>1.82</v>
+      </c>
+      <c r="N12" t="s">
+        <v>68</v>
+      </c>
+      <c r="O12">
+        <v>41.14</v>
+      </c>
+      <c r="P12">
+        <v>2.03</v>
+      </c>
+      <c r="Q12">
+        <v>1.93</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17">
+      <c r="A13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" t="s">
+        <v>65</v>
+      </c>
+      <c r="C13">
         <v>37.71</v>
       </c>
-      <c r="D12">
+      <c r="D13">
         <v>2.25</v>
       </c>
-      <c r="E12">
+      <c r="E13">
         <v>2.19</v>
       </c>
-      <c r="F12" t="s">
-        <v>62</v>
-      </c>
-      <c r="G12">
+      <c r="F13" t="s">
+        <v>66</v>
+      </c>
+      <c r="G13">
         <v>37.71</v>
       </c>
-      <c r="H12">
+      <c r="H13">
         <v>2.23</v>
       </c>
-      <c r="I12">
+      <c r="I13">
         <v>2.15</v>
       </c>
-      <c r="J12" t="s">
-        <v>63</v>
-      </c>
-      <c r="K12">
+      <c r="J13" t="s">
+        <v>67</v>
+      </c>
+      <c r="K13">
         <v>39.43</v>
       </c>
-      <c r="L12">
+      <c r="L13">
         <v>2.14</v>
       </c>
-      <c r="M12">
+      <c r="M13">
         <v>2.06</v>
       </c>
-    </row>
-    <row r="13" spans="1:13">
-      <c r="A13" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" t="s">
-        <v>61</v>
-      </c>
-      <c r="C13">
-        <v>63.71</v>
-      </c>
-      <c r="D13">
-        <v>1.33</v>
-      </c>
-      <c r="E13">
-        <v>1.2</v>
-      </c>
-      <c r="F13" t="s">
-        <v>62</v>
-      </c>
-      <c r="G13">
-        <v>44.57</v>
-      </c>
-      <c r="H13">
-        <v>1.89</v>
-      </c>
-      <c r="I13">
-        <v>1.78</v>
-      </c>
-      <c r="J13" t="s">
-        <v>63</v>
-      </c>
-      <c r="K13">
-        <v>43.86</v>
-      </c>
-      <c r="L13">
-        <v>1.92</v>
-      </c>
-      <c r="M13">
-        <v>1.82</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
+      <c r="N13" t="s">
+        <v>68</v>
+      </c>
+      <c r="O13">
+        <v>42</v>
+      </c>
+      <c r="P13">
+        <v>1.99</v>
+      </c>
+      <c r="Q13">
+        <v>1.88</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17">
       <c r="A14" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B14" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C14">
         <v>41.71</v>
@@ -1116,7 +1287,7 @@
         <v>1.95</v>
       </c>
       <c r="F14" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G14">
         <v>45.57</v>
@@ -1128,7 +1299,7 @@
         <v>1.73</v>
       </c>
       <c r="J14" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K14">
         <v>47</v>
@@ -1139,13 +1310,25 @@
       <c r="M14">
         <v>1.68</v>
       </c>
-    </row>
-    <row r="15" spans="1:13">
+      <c r="N14" t="s">
+        <v>68</v>
+      </c>
+      <c r="O14">
+        <v>50.43</v>
+      </c>
+      <c r="P14">
+        <v>1.66</v>
+      </c>
+      <c r="Q14">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17">
       <c r="A15" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B15" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C15">
         <v>53.43</v>
@@ -1157,7 +1340,7 @@
         <v>1.47</v>
       </c>
       <c r="F15" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G15">
         <v>53.43</v>
@@ -1169,7 +1352,7 @@
         <v>1.44</v>
       </c>
       <c r="J15" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K15">
         <v>51.29</v>
@@ -1180,13 +1363,25 @@
       <c r="M15">
         <v>1.52</v>
       </c>
-    </row>
-    <row r="16" spans="1:13">
+      <c r="N15" t="s">
+        <v>68</v>
+      </c>
+      <c r="O15">
+        <v>51.29</v>
+      </c>
+      <c r="P15">
+        <v>1.63</v>
+      </c>
+      <c r="Q15">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17">
       <c r="A16" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B16" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C16">
         <v>68.43000000000001</v>
@@ -1198,7 +1393,7 @@
         <v>1.1</v>
       </c>
       <c r="F16" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G16">
         <v>52.71</v>
@@ -1210,7 +1405,7 @@
         <v>1.46</v>
       </c>
       <c r="J16" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K16">
         <v>52.71</v>
@@ -1221,13 +1416,25 @@
       <c r="M16">
         <v>1.47</v>
       </c>
-    </row>
-    <row r="17" spans="1:13">
+      <c r="N16" t="s">
+        <v>68</v>
+      </c>
+      <c r="O16">
+        <v>57.86</v>
+      </c>
+      <c r="P16">
+        <v>1.44</v>
+      </c>
+      <c r="Q16">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17">
       <c r="A17" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B17" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C17">
         <v>71.14</v>
@@ -1239,7 +1446,7 @@
         <v>1.05</v>
       </c>
       <c r="F17" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G17">
         <v>75.29000000000001</v>
@@ -1251,7 +1458,7 @@
         <v>0.95</v>
       </c>
       <c r="J17" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K17">
         <v>75.29000000000001</v>
@@ -1262,13 +1469,25 @@
       <c r="M17">
         <v>0.96</v>
       </c>
-    </row>
-    <row r="18" spans="1:13">
+      <c r="N17" t="s">
+        <v>68</v>
+      </c>
+      <c r="O17">
+        <v>83</v>
+      </c>
+      <c r="P17">
+        <v>1.01</v>
+      </c>
+      <c r="Q17">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17">
       <c r="A18" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B18" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C18">
         <v>74.43000000000001</v>
@@ -1280,7 +1499,7 @@
         <v>0.99</v>
       </c>
       <c r="F18" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G18">
         <v>75.14</v>
@@ -1292,7 +1511,7 @@
         <v>0.95</v>
       </c>
       <c r="J18" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K18">
         <v>83.56999999999999</v>
@@ -1303,13 +1522,25 @@
       <c r="M18">
         <v>0.84</v>
       </c>
-    </row>
-    <row r="19" spans="1:13">
+      <c r="N18" t="s">
+        <v>68</v>
+      </c>
+      <c r="O18">
+        <v>87.70999999999999</v>
+      </c>
+      <c r="P18">
+        <v>0.95</v>
+      </c>
+      <c r="Q18">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17">
       <c r="A19" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C19">
         <v>88.86</v>
@@ -1321,7 +1552,7 @@
         <v>0.8</v>
       </c>
       <c r="F19" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G19">
         <v>91.70999999999999</v>
@@ -1333,7 +1564,7 @@
         <v>0.74</v>
       </c>
       <c r="J19" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K19">
         <v>91.70999999999999</v>
@@ -1344,136 +1575,184 @@
       <c r="M19">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="20" spans="1:13">
+      <c r="N19" t="s">
+        <v>68</v>
+      </c>
+      <c r="O19">
+        <v>92.43000000000001</v>
+      </c>
+      <c r="P19">
+        <v>0.9</v>
+      </c>
+      <c r="Q19">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17">
       <c r="A20" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B20" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C20">
+        <v>141.29</v>
+      </c>
+      <c r="D20">
+        <v>0.6</v>
+      </c>
+      <c r="E20">
+        <v>0.43</v>
+      </c>
+      <c r="F20" t="s">
+        <v>66</v>
+      </c>
+      <c r="G20">
+        <v>145.57</v>
+      </c>
+      <c r="H20">
+        <v>0.58</v>
+      </c>
+      <c r="I20">
+        <v>0.39</v>
+      </c>
+      <c r="J20" t="s">
+        <v>67</v>
+      </c>
+      <c r="K20">
+        <v>110.14</v>
+      </c>
+      <c r="L20">
+        <v>0.77</v>
+      </c>
+      <c r="M20">
+        <v>0.59</v>
+      </c>
+      <c r="N20" t="s">
+        <v>68</v>
+      </c>
+      <c r="O20">
+        <v>105.86</v>
+      </c>
+      <c r="P20">
+        <v>0.79</v>
+      </c>
+      <c r="Q20">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17">
+      <c r="A21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B21" t="s">
+        <v>65</v>
+      </c>
+      <c r="C21">
         <v>101.29</v>
       </c>
-      <c r="D20">
+      <c r="D21">
         <v>0.84</v>
       </c>
-      <c r="E20">
+      <c r="E21">
         <v>0.67</v>
       </c>
-      <c r="F20" t="s">
-        <v>62</v>
-      </c>
-      <c r="G20">
+      <c r="F21" t="s">
+        <v>66</v>
+      </c>
+      <c r="G21">
         <v>106.14</v>
       </c>
-      <c r="H20">
+      <c r="H21">
         <v>0.79</v>
       </c>
-      <c r="I20">
+      <c r="I21">
         <v>0.61</v>
       </c>
-      <c r="J20" t="s">
-        <v>63</v>
-      </c>
-      <c r="K20">
+      <c r="J21" t="s">
+        <v>67</v>
+      </c>
+      <c r="K21">
         <v>107.57</v>
       </c>
-      <c r="L20">
+      <c r="L21">
         <v>0.78</v>
       </c>
-      <c r="M20">
+      <c r="M21">
         <v>0.61</v>
       </c>
-    </row>
-    <row r="21" spans="1:13">
-      <c r="A21" t="s">
-        <v>32</v>
-      </c>
-      <c r="B21" t="s">
-        <v>61</v>
-      </c>
-      <c r="C21">
-        <v>141.29</v>
-      </c>
-      <c r="D21">
-        <v>0.6</v>
-      </c>
-      <c r="E21">
-        <v>0.43</v>
-      </c>
-      <c r="F21" t="s">
-        <v>62</v>
-      </c>
-      <c r="G21">
-        <v>145.57</v>
-      </c>
-      <c r="H21">
-        <v>0.58</v>
-      </c>
-      <c r="I21">
-        <v>0.39</v>
-      </c>
-      <c r="J21" t="s">
-        <v>63</v>
-      </c>
-      <c r="K21">
-        <v>110.14</v>
-      </c>
-      <c r="L21">
-        <v>0.77</v>
-      </c>
-      <c r="M21">
-        <v>0.59</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13">
+      <c r="N21" t="s">
+        <v>68</v>
+      </c>
+      <c r="O21">
+        <v>119.57</v>
+      </c>
+      <c r="P21">
+        <v>0.7</v>
+      </c>
+      <c r="Q21">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17">
       <c r="A22" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B22" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C22">
-        <v>80</v>
+        <v>442.71</v>
       </c>
       <c r="D22">
-        <v>1.06</v>
+        <v>0.19</v>
       </c>
       <c r="E22">
-        <v>0.91</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F22" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G22">
-        <v>80</v>
+        <v>462.29</v>
       </c>
       <c r="H22">
-        <v>1.05</v>
+        <v>0.18</v>
       </c>
       <c r="I22">
-        <v>0.88</v>
+        <v>0.06</v>
       </c>
       <c r="J22" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K22">
-        <v>133.14</v>
+        <v>186</v>
       </c>
       <c r="L22">
-        <v>0.63</v>
+        <v>0.45</v>
       </c>
       <c r="M22">
-        <v>0.46</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13">
+        <v>0.28</v>
+      </c>
+      <c r="N22" t="s">
+        <v>68</v>
+      </c>
+      <c r="O22">
+        <v>123.14</v>
+      </c>
+      <c r="P22">
+        <v>0.68</v>
+      </c>
+      <c r="Q22">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17">
       <c r="A23" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B23" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C23">
         <v>89</v>
@@ -1485,7 +1764,7 @@
         <v>0.8</v>
       </c>
       <c r="F23" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G23">
         <v>90.43000000000001</v>
@@ -1497,7 +1776,7 @@
         <v>0.75</v>
       </c>
       <c r="J23" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K23">
         <v>133.71</v>
@@ -1508,136 +1787,184 @@
       <c r="M23">
         <v>0.45</v>
       </c>
-    </row>
-    <row r="24" spans="1:13">
+      <c r="N23" t="s">
+        <v>68</v>
+      </c>
+      <c r="O23">
+        <v>135.14</v>
+      </c>
+      <c r="P23">
+        <v>0.62</v>
+      </c>
+      <c r="Q23">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17">
       <c r="A24" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B24" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C24">
+        <v>153</v>
+      </c>
+      <c r="D24">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E24">
+        <v>0.39</v>
+      </c>
+      <c r="F24" t="s">
+        <v>66</v>
+      </c>
+      <c r="G24">
+        <v>158.57</v>
+      </c>
+      <c r="H24">
+        <v>0.53</v>
+      </c>
+      <c r="I24">
+        <v>0.35</v>
+      </c>
+      <c r="J24" t="s">
+        <v>67</v>
+      </c>
+      <c r="K24">
+        <v>157.14</v>
+      </c>
+      <c r="L24">
+        <v>0.54</v>
+      </c>
+      <c r="M24">
+        <v>0.36</v>
+      </c>
+      <c r="N24" t="s">
+        <v>68</v>
+      </c>
+      <c r="O24">
+        <v>135.14</v>
+      </c>
+      <c r="P24">
+        <v>0.62</v>
+      </c>
+      <c r="Q24">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17">
+      <c r="A25" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" t="s">
+        <v>65</v>
+      </c>
+      <c r="C25">
         <v>250</v>
       </c>
-      <c r="D24">
+      <c r="D25">
         <v>0.34</v>
       </c>
-      <c r="E24">
+      <c r="E25">
         <v>0.18</v>
       </c>
-      <c r="F24" t="s">
-        <v>62</v>
-      </c>
-      <c r="G24">
+      <c r="F25" t="s">
+        <v>66</v>
+      </c>
+      <c r="G25">
         <v>259.86</v>
       </c>
-      <c r="H24">
+      <c r="H25">
         <v>0.32</v>
       </c>
-      <c r="I24">
+      <c r="I25">
         <v>0.16</v>
       </c>
-      <c r="J24" t="s">
-        <v>63</v>
-      </c>
-      <c r="K24">
+      <c r="J25" t="s">
+        <v>67</v>
+      </c>
+      <c r="K25">
         <v>153</v>
       </c>
-      <c r="L24">
+      <c r="L25">
         <v>0.55</v>
       </c>
-      <c r="M24">
+      <c r="M25">
         <v>0.37</v>
       </c>
-    </row>
-    <row r="25" spans="1:13">
-      <c r="A25" t="s">
-        <v>36</v>
-      </c>
-      <c r="B25" t="s">
-        <v>61</v>
-      </c>
-      <c r="C25">
-        <v>153</v>
-      </c>
-      <c r="D25">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="E25">
-        <v>0.39</v>
-      </c>
-      <c r="F25" t="s">
-        <v>62</v>
-      </c>
-      <c r="G25">
-        <v>158.57</v>
-      </c>
-      <c r="H25">
-        <v>0.53</v>
-      </c>
-      <c r="I25">
-        <v>0.35</v>
-      </c>
-      <c r="J25" t="s">
-        <v>63</v>
-      </c>
-      <c r="K25">
-        <v>157.14</v>
-      </c>
-      <c r="L25">
-        <v>0.54</v>
-      </c>
-      <c r="M25">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13">
+      <c r="N25" t="s">
+        <v>68</v>
+      </c>
+      <c r="O25">
+        <v>143</v>
+      </c>
+      <c r="P25">
+        <v>0.58</v>
+      </c>
+      <c r="Q25">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17">
       <c r="A26" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B26" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C26">
-        <v>442.71</v>
+        <v>80</v>
       </c>
       <c r="D26">
-        <v>0.19</v>
+        <v>1.06</v>
       </c>
       <c r="E26">
-        <v>0.07000000000000001</v>
+        <v>0.91</v>
       </c>
       <c r="F26" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G26">
-        <v>462.29</v>
+        <v>80</v>
       </c>
       <c r="H26">
-        <v>0.18</v>
+        <v>1.05</v>
       </c>
       <c r="I26">
-        <v>0.06</v>
+        <v>0.88</v>
       </c>
       <c r="J26" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K26">
-        <v>186</v>
+        <v>133.14</v>
       </c>
       <c r="L26">
-        <v>0.45</v>
+        <v>0.63</v>
       </c>
       <c r="M26">
-        <v>0.28</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13">
+        <v>0.46</v>
+      </c>
+      <c r="N26" t="s">
+        <v>68</v>
+      </c>
+      <c r="O26">
+        <v>145.86</v>
+      </c>
+      <c r="P26">
+        <v>0.57</v>
+      </c>
+      <c r="Q26">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17">
       <c r="A27" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B27" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C27">
         <v>191.71</v>
@@ -1649,7 +1976,7 @@
         <v>0.28</v>
       </c>
       <c r="F27" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G27">
         <v>222.71</v>
@@ -1661,7 +1988,7 @@
         <v>0.21</v>
       </c>
       <c r="J27" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K27">
         <v>193.29</v>
@@ -1672,28 +1999,40 @@
       <c r="M27">
         <v>0.26</v>
       </c>
-    </row>
-    <row r="28" spans="1:13">
+      <c r="N27" t="s">
+        <v>68</v>
+      </c>
+      <c r="O27">
+        <v>197.43</v>
+      </c>
+      <c r="P27">
+        <v>0.42</v>
+      </c>
+      <c r="Q27">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17">
       <c r="A28" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B28" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C28">
-        <v>376.29</v>
+        <v>249.71</v>
       </c>
       <c r="D28">
-        <v>0.23</v>
+        <v>0.34</v>
       </c>
       <c r="E28">
-        <v>0.09</v>
+        <v>0.18</v>
       </c>
       <c r="F28" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G28">
-        <v>241</v>
+        <v>242.57</v>
       </c>
       <c r="H28">
         <v>0.35</v>
@@ -1702,39 +2041,51 @@
         <v>0.18</v>
       </c>
       <c r="J28" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K28">
-        <v>224.29</v>
+        <v>228.14</v>
       </c>
       <c r="L28">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="M28">
+        <v>0.2</v>
+      </c>
+      <c r="N28" t="s">
+        <v>68</v>
+      </c>
+      <c r="O28">
+        <v>216.71</v>
+      </c>
+      <c r="P28">
+        <v>0.39</v>
+      </c>
+      <c r="Q28">
         <v>0.21</v>
       </c>
     </row>
-    <row r="29" spans="1:13">
+    <row r="29" spans="1:17">
       <c r="A29" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B29" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C29">
-        <v>249.71</v>
+        <v>376.29</v>
       </c>
       <c r="D29">
-        <v>0.34</v>
+        <v>0.23</v>
       </c>
       <c r="E29">
-        <v>0.18</v>
+        <v>0.09</v>
       </c>
       <c r="F29" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G29">
-        <v>242.57</v>
+        <v>241</v>
       </c>
       <c r="H29">
         <v>0.35</v>
@@ -1743,24 +2094,36 @@
         <v>0.18</v>
       </c>
       <c r="J29" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K29">
-        <v>228.14</v>
+        <v>224.29</v>
       </c>
       <c r="L29">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="M29">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13">
+        <v>0.21</v>
+      </c>
+      <c r="N29" t="s">
+        <v>68</v>
+      </c>
+      <c r="O29">
+        <v>234</v>
+      </c>
+      <c r="P29">
+        <v>0.36</v>
+      </c>
+      <c r="Q29">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17">
       <c r="A30" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B30" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C30">
         <v>320.43</v>
@@ -1772,7 +2135,7 @@
         <v>0.12</v>
       </c>
       <c r="F30" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G30">
         <v>351.57</v>
@@ -1784,7 +2147,7 @@
         <v>0.1</v>
       </c>
       <c r="J30" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K30">
         <v>341.71</v>
@@ -1795,16 +2158,28 @@
       <c r="M30">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="31" spans="1:13">
+      <c r="N30" t="s">
+        <v>68</v>
+      </c>
+      <c r="O30">
+        <v>283.71</v>
+      </c>
+      <c r="P30">
+        <v>0.29</v>
+      </c>
+      <c r="Q30">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17">
       <c r="A31" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B31" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C31">
-        <v>367.57</v>
+        <v>370.43</v>
       </c>
       <c r="D31">
         <v>0.23</v>
@@ -1813,10 +2188,10 @@
         <v>0.1</v>
       </c>
       <c r="F31" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G31">
-        <v>383</v>
+        <v>376.71</v>
       </c>
       <c r="H31">
         <v>0.22</v>
@@ -1825,27 +2200,39 @@
         <v>0.08</v>
       </c>
       <c r="J31" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K31">
-        <v>378.86</v>
+        <v>383.71</v>
       </c>
       <c r="L31">
         <v>0.22</v>
       </c>
       <c r="M31">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13">
+        <v>0.08</v>
+      </c>
+      <c r="N31" t="s">
+        <v>68</v>
+      </c>
+      <c r="O31">
+        <v>390.71</v>
+      </c>
+      <c r="P31">
+        <v>0.21</v>
+      </c>
+      <c r="Q31">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17">
       <c r="A32" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B32" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C32">
-        <v>370.43</v>
+        <v>367.57</v>
       </c>
       <c r="D32">
         <v>0.23</v>
@@ -1854,10 +2241,10 @@
         <v>0.1</v>
       </c>
       <c r="F32" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G32">
-        <v>376.71</v>
+        <v>383</v>
       </c>
       <c r="H32">
         <v>0.22</v>
@@ -1866,24 +2253,36 @@
         <v>0.08</v>
       </c>
       <c r="J32" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K32">
-        <v>383.71</v>
+        <v>378.86</v>
       </c>
       <c r="L32">
         <v>0.22</v>
       </c>
       <c r="M32">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13">
+        <v>0.09</v>
+      </c>
+      <c r="N32" t="s">
+        <v>68</v>
+      </c>
+      <c r="O32">
+        <v>474.57</v>
+      </c>
+      <c r="P32">
+        <v>0.18</v>
+      </c>
+      <c r="Q32">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17">
       <c r="A33" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B33" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C33">
         <v>243.29</v>
@@ -1895,7 +2294,7 @@
         <v>0.19</v>
       </c>
       <c r="F33" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G33">
         <v>455.57</v>
@@ -1907,7 +2306,7 @@
         <v>0.06</v>
       </c>
       <c r="J33" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K33">
         <v>483.57</v>
@@ -1918,13 +2317,25 @@
       <c r="M33">
         <v>0.06</v>
       </c>
-    </row>
-    <row r="34" spans="1:13">
+      <c r="N33" t="s">
+        <v>68</v>
+      </c>
+      <c r="O33">
+        <v>490.71</v>
+      </c>
+      <c r="P33">
+        <v>0.17</v>
+      </c>
+      <c r="Q33">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17">
       <c r="A34" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B34" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C34">
         <v>299.29</v>
@@ -1936,7 +2347,7 @@
         <v>0.14</v>
       </c>
       <c r="F34" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G34">
         <v>497.86</v>
@@ -1948,7 +2359,7 @@
         <v>0.05</v>
       </c>
       <c r="J34" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K34">
         <v>486.71</v>
@@ -1959,13 +2370,25 @@
       <c r="M34">
         <v>0.06</v>
       </c>
-    </row>
-    <row r="35" spans="1:13">
+      <c r="N34" t="s">
+        <v>68</v>
+      </c>
+      <c r="O34">
+        <v>497.86</v>
+      </c>
+      <c r="P34">
+        <v>0.17</v>
+      </c>
+      <c r="Q34">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17">
       <c r="A35" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B35" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C35">
         <v>467.14</v>
@@ -1977,7 +2400,7 @@
         <v>0.06</v>
       </c>
       <c r="F35" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G35">
         <v>505.29</v>
@@ -1989,7 +2412,7 @@
         <v>0.05</v>
       </c>
       <c r="J35" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K35">
         <v>494.14</v>
@@ -2000,13 +2423,25 @@
       <c r="M35">
         <v>0.05</v>
       </c>
-    </row>
-    <row r="36" spans="1:13">
+      <c r="N35" t="s">
+        <v>68</v>
+      </c>
+      <c r="O35">
+        <v>502.43</v>
+      </c>
+      <c r="P35">
+        <v>0.17</v>
+      </c>
+      <c r="Q35">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17">
       <c r="A36" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B36" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C36">
         <v>540.71</v>
@@ -2018,7 +2453,7 @@
         <v>0.05</v>
       </c>
       <c r="F36" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G36">
         <v>576.4299999999999</v>
@@ -2030,7 +2465,7 @@
         <v>0.04</v>
       </c>
       <c r="J36" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K36">
         <v>576.4299999999999</v>
@@ -2041,13 +2476,25 @@
       <c r="M36">
         <v>0.04</v>
       </c>
-    </row>
-    <row r="37" spans="1:13">
+      <c r="N36" t="s">
+        <v>68</v>
+      </c>
+      <c r="O36">
+        <v>612.14</v>
+      </c>
+      <c r="P36">
+        <v>0.14</v>
+      </c>
+      <c r="Q36">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17">
       <c r="A37" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B37" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C37">
         <v>747.86</v>
@@ -2059,7 +2506,7 @@
         <v>0.03</v>
       </c>
       <c r="F37" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G37">
         <v>747.86</v>
@@ -2071,7 +2518,7 @@
         <v>0.02</v>
       </c>
       <c r="J37" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K37">
         <v>747.86</v>
@@ -2082,13 +2529,25 @@
       <c r="M37">
         <v>0.02</v>
       </c>
-    </row>
-    <row r="38" spans="1:13">
+      <c r="N37" t="s">
+        <v>68</v>
+      </c>
+      <c r="O37">
+        <v>747.86</v>
+      </c>
+      <c r="P37">
+        <v>0.11</v>
+      </c>
+      <c r="Q37">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17">
       <c r="A38" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B38" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C38">
         <v>890.71</v>
@@ -2100,7 +2559,7 @@
         <v>0.02</v>
       </c>
       <c r="F38" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G38">
         <v>890.71</v>
@@ -2112,7 +2571,7 @@
         <v>0.02</v>
       </c>
       <c r="J38" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K38">
         <v>890.71</v>
@@ -2123,192 +2582,252 @@
       <c r="M38">
         <v>0.02</v>
       </c>
-    </row>
-    <row r="39" spans="1:13">
+      <c r="N38" t="s">
+        <v>68</v>
+      </c>
+      <c r="O38">
+        <v>783.5700000000001</v>
+      </c>
+      <c r="P38">
+        <v>0.11</v>
+      </c>
+      <c r="Q38">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17">
       <c r="A39" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B39" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C39">
+        <v>1197.86</v>
+      </c>
+      <c r="D39">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E39">
+        <v>0.01</v>
+      </c>
+      <c r="F39" t="s">
+        <v>66</v>
+      </c>
+      <c r="G39">
+        <v>1197.86</v>
+      </c>
+      <c r="H39">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I39">
+        <v>0.01</v>
+      </c>
+      <c r="J39" t="s">
+        <v>67</v>
+      </c>
+      <c r="K39">
+        <v>1197.86</v>
+      </c>
+      <c r="L39">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="M39">
+        <v>0.01</v>
+      </c>
+      <c r="N39" t="s">
+        <v>68</v>
+      </c>
+      <c r="O39">
+        <v>819.29</v>
+      </c>
+      <c r="P39">
+        <v>0.1</v>
+      </c>
+      <c r="Q39">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17">
+      <c r="A40" t="s">
+        <v>55</v>
+      </c>
+      <c r="B40" t="s">
+        <v>65</v>
+      </c>
+      <c r="C40">
         <v>605</v>
       </c>
-      <c r="D39">
+      <c r="D40">
         <v>0.14</v>
       </c>
-      <c r="E39">
+      <c r="E40">
         <v>0.04</v>
       </c>
-      <c r="F39" t="s">
-        <v>62</v>
-      </c>
-      <c r="G39">
+      <c r="F40" t="s">
+        <v>66</v>
+      </c>
+      <c r="G40">
         <v>640.71</v>
       </c>
-      <c r="H39">
+      <c r="H40">
         <v>0.13</v>
       </c>
-      <c r="I39">
+      <c r="I40">
         <v>0.03</v>
       </c>
-      <c r="J39" t="s">
-        <v>63</v>
-      </c>
-      <c r="K39">
+      <c r="J40" t="s">
+        <v>67</v>
+      </c>
+      <c r="K40">
         <v>890.71</v>
       </c>
-      <c r="L39">
+      <c r="L40">
         <v>0.09</v>
       </c>
-      <c r="M39">
+      <c r="M40">
         <v>0.02</v>
       </c>
-    </row>
-    <row r="40" spans="1:13">
-      <c r="A40" t="s">
-        <v>51</v>
-      </c>
-      <c r="B40" t="s">
-        <v>61</v>
-      </c>
-      <c r="C40">
-        <v>1069.29</v>
-      </c>
-      <c r="D40">
-        <v>0.08</v>
-      </c>
-      <c r="E40">
+      <c r="N40" t="s">
+        <v>68</v>
+      </c>
+      <c r="O40">
+        <v>926.4299999999999</v>
+      </c>
+      <c r="P40">
+        <v>0.09</v>
+      </c>
+      <c r="Q40">
         <v>0.01</v>
       </c>
-      <c r="F40" t="s">
-        <v>62</v>
-      </c>
-      <c r="G40">
-        <v>1069.29</v>
-      </c>
-      <c r="H40">
-        <v>0.08</v>
-      </c>
-      <c r="I40">
-        <v>0.01</v>
-      </c>
-      <c r="J40" t="s">
-        <v>63</v>
-      </c>
-      <c r="K40">
-        <v>1069.29</v>
-      </c>
-      <c r="L40">
-        <v>0.08</v>
-      </c>
-      <c r="M40">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13">
+    </row>
+    <row r="41" spans="1:17">
       <c r="A41" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B41" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C41">
-        <v>1126.43</v>
+        <v>1326.43</v>
       </c>
       <c r="D41">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="E41">
         <v>0.01</v>
       </c>
       <c r="F41" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G41">
-        <v>1126.43</v>
+        <v>1326.43</v>
       </c>
       <c r="H41">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="I41">
         <v>0.01</v>
       </c>
       <c r="J41" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K41">
-        <v>1126.43</v>
+        <v>1326.43</v>
       </c>
       <c r="L41">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="M41">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="42" spans="1:13">
+      <c r="N41" t="s">
+        <v>68</v>
+      </c>
+      <c r="O41">
+        <v>1069.29</v>
+      </c>
+      <c r="P41">
+        <v>0.08</v>
+      </c>
+      <c r="Q41">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17">
       <c r="A42" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B42" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C42">
-        <v>890.71</v>
+        <v>1069.29</v>
       </c>
       <c r="D42">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="E42">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F42" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G42">
-        <v>1176.43</v>
+        <v>1069.29</v>
       </c>
       <c r="H42">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="I42">
         <v>0.01</v>
       </c>
       <c r="J42" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K42">
-        <v>1176.43</v>
+        <v>1069.29</v>
       </c>
       <c r="L42">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="M42">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="43" spans="1:13">
+      <c r="N42" t="s">
+        <v>68</v>
+      </c>
+      <c r="O42">
+        <v>1069.29</v>
+      </c>
+      <c r="P42">
+        <v>0.08</v>
+      </c>
+      <c r="Q42">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17">
       <c r="A43" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B43" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C43">
-        <v>1197.86</v>
+        <v>890.71</v>
       </c>
       <c r="D43">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="E43">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F43" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G43">
-        <v>1197.86</v>
+        <v>1176.43</v>
       </c>
       <c r="H43">
         <v>0.07000000000000001</v>
@@ -2317,10 +2836,10 @@
         <v>0.01</v>
       </c>
       <c r="J43" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K43">
-        <v>1197.86</v>
+        <v>1176.43</v>
       </c>
       <c r="L43">
         <v>0.07000000000000001</v>
@@ -2328,28 +2847,40 @@
       <c r="M43">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="44" spans="1:13">
+      <c r="N43" t="s">
+        <v>68</v>
+      </c>
+      <c r="O43">
+        <v>1176.43</v>
+      </c>
+      <c r="P43">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="Q43">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17">
       <c r="A44" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B44" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C44">
-        <v>1197.86</v>
+        <v>1126.43</v>
       </c>
       <c r="D44">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="E44">
         <v>0.01</v>
       </c>
       <c r="F44" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G44">
-        <v>1197.86</v>
+        <v>1126.43</v>
       </c>
       <c r="H44">
         <v>0.07000000000000001</v>
@@ -2358,10 +2889,10 @@
         <v>0.01</v>
       </c>
       <c r="J44" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K44">
-        <v>1197.86</v>
+        <v>1126.43</v>
       </c>
       <c r="L44">
         <v>0.07000000000000001</v>
@@ -2369,13 +2900,25 @@
       <c r="M44">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="45" spans="1:13">
+      <c r="N44" t="s">
+        <v>68</v>
+      </c>
+      <c r="O44">
+        <v>1197.86</v>
+      </c>
+      <c r="P44">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="Q44">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17">
       <c r="A45" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B45" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C45">
         <v>1197.86</v>
@@ -2387,7 +2930,7 @@
         <v>0.01</v>
       </c>
       <c r="F45" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G45">
         <v>1197.86</v>
@@ -2399,7 +2942,7 @@
         <v>0.01</v>
       </c>
       <c r="J45" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K45">
         <v>1197.86</v>
@@ -2410,54 +2953,78 @@
       <c r="M45">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="46" spans="1:13">
+      <c r="N45" t="s">
+        <v>68</v>
+      </c>
+      <c r="O45">
+        <v>1197.86</v>
+      </c>
+      <c r="P45">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="Q45">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17">
       <c r="A46" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B46" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C46">
-        <v>1326.43</v>
+        <v>1197.86</v>
       </c>
       <c r="D46">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E46">
         <v>0.01</v>
       </c>
       <c r="F46" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G46">
-        <v>1326.43</v>
+        <v>1197.86</v>
       </c>
       <c r="H46">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I46">
         <v>0.01</v>
       </c>
       <c r="J46" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K46">
-        <v>1326.43</v>
+        <v>1197.86</v>
       </c>
       <c r="L46">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="M46">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="47" spans="1:13">
+      <c r="N46" t="s">
+        <v>68</v>
+      </c>
+      <c r="O46">
+        <v>1197.86</v>
+      </c>
+      <c r="P46">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="Q46">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17">
       <c r="A47" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B47" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C47">
         <v>1497.86</v>
@@ -2469,7 +3036,7 @@
         <v>0.01</v>
       </c>
       <c r="F47" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G47">
         <v>1497.86</v>
@@ -2481,7 +3048,7 @@
         <v>0.01</v>
       </c>
       <c r="J47" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K47">
         <v>1497.86</v>
@@ -2492,13 +3059,25 @@
       <c r="M47">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="48" spans="1:13">
+      <c r="N47" t="s">
+        <v>68</v>
+      </c>
+      <c r="O47">
+        <v>1497.86</v>
+      </c>
+      <c r="P47">
+        <v>0.06</v>
+      </c>
+      <c r="Q47">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17">
       <c r="A48" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B48" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C48">
         <v>1926.43</v>
@@ -2510,7 +3089,7 @@
         <v>0</v>
       </c>
       <c r="F48" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G48">
         <v>1926.43</v>
@@ -2522,7 +3101,7 @@
         <v>0</v>
       </c>
       <c r="J48" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K48">
         <v>2033.57</v>
@@ -2533,13 +3112,25 @@
       <c r="M48">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:13">
+      <c r="N48" t="s">
+        <v>68</v>
+      </c>
+      <c r="O48">
+        <v>2033.57</v>
+      </c>
+      <c r="P48">
+        <v>0.04</v>
+      </c>
+      <c r="Q48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17">
       <c r="A49" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B49" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C49">
         <v>1926.43</v>
@@ -2551,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="F49" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G49">
         <v>1926.43</v>
@@ -2563,7 +3154,7 @@
         <v>0</v>
       </c>
       <c r="J49" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K49">
         <v>2355</v>
@@ -2572,6 +3163,18 @@
         <v>0.04</v>
       </c>
       <c r="M49">
+        <v>0</v>
+      </c>
+      <c r="N49" t="s">
+        <v>68</v>
+      </c>
+      <c r="O49">
+        <v>2355</v>
+      </c>
+      <c r="P49">
+        <v>0.04</v>
+      </c>
+      <c r="Q49">
         <v>0</v>
       </c>
     </row>

--- a/processed_data_during_wm/processed_data_wide.xlsx
+++ b/processed_data_during_wm/processed_data_wide.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="74">
   <si>
     <t>Team</t>
   </si>
@@ -67,6 +67,18 @@
     <t>Shin_Wahrscheinlichkeit_in_Prozent_4</t>
   </si>
   <si>
+    <t>Datum_5</t>
+  </si>
+  <si>
+    <t>Durchsch_Quote_5</t>
+  </si>
+  <si>
+    <t>Norm_Wahrscheinlichkeit_in_Prozent_5</t>
+  </si>
+  <si>
+    <t>Shin_Wahrscheinlichkeit_in_Prozent_5</t>
+  </si>
+  <si>
     <t>Frankreich</t>
   </si>
   <si>
@@ -76,12 +88,12 @@
     <t>England</t>
   </si>
   <si>
+    <t>Argentinien</t>
+  </si>
+  <si>
     <t>Portugal</t>
   </si>
   <si>
-    <t>Argentinien</t>
-  </si>
-  <si>
     <t>Brasilien</t>
   </si>
   <si>
@@ -103,48 +115,48 @@
     <t>Belgien</t>
   </si>
   <si>
+    <t>Mexiko</t>
+  </si>
+  <si>
     <t>Kolumbien</t>
   </si>
   <si>
     <t>Japan</t>
   </si>
   <si>
-    <t>Mexiko</t>
+    <t>Schweiz</t>
   </si>
   <si>
     <t>Uruguay</t>
   </si>
   <si>
-    <t>Schweiz</t>
+    <t>Schweden</t>
   </si>
   <si>
     <t>Kroatien</t>
   </si>
   <si>
-    <t>Schweden</t>
-  </si>
-  <si>
     <t>Senegal</t>
   </si>
   <si>
     <t>Australien</t>
   </si>
   <si>
+    <t>Österreich</t>
+  </si>
+  <si>
+    <t>Elfenbeinküste</t>
+  </si>
+  <si>
+    <t>Kanada</t>
+  </si>
+  <si>
     <t>Ecuador</t>
   </si>
   <si>
-    <t>Österreich</t>
-  </si>
-  <si>
-    <t>Elfenbeinküste</t>
-  </si>
-  <si>
     <t>Türkei</t>
   </si>
   <si>
-    <t>Kanada</t>
-  </si>
-  <si>
     <t>Schottland</t>
   </si>
   <si>
@@ -154,27 +166,27 @@
     <t>Ägypten</t>
   </si>
   <si>
+    <t>Ghana</t>
+  </si>
+  <si>
     <t>Bosnien Herzegowina</t>
   </si>
   <si>
+    <t>Paraguay</t>
+  </si>
+  <si>
     <t>Algerien</t>
   </si>
   <si>
-    <t>Paraguay</t>
-  </si>
-  <si>
     <t>Tschechien</t>
   </si>
   <si>
-    <t>Ghana</t>
+    <t>DR Kongo</t>
   </si>
   <si>
     <t>Iran</t>
   </si>
   <si>
-    <t>DR Kongo</t>
-  </si>
-  <si>
     <t>Saudi Arabien</t>
   </si>
   <si>
@@ -187,21 +199,21 @@
     <t>Kap Verde</t>
   </si>
   <si>
+    <t>Südafrika</t>
+  </si>
+  <si>
+    <t>Panama</t>
+  </si>
+  <si>
+    <t>Irak</t>
+  </si>
+  <si>
+    <t>Usbekistan</t>
+  </si>
+  <si>
     <t>Katar</t>
   </si>
   <si>
-    <t>Südafrika</t>
-  </si>
-  <si>
-    <t>Irak</t>
-  </si>
-  <si>
-    <t>Panama</t>
-  </si>
-  <si>
-    <t>Usbekistan</t>
-  </si>
-  <si>
     <t>Jordanien</t>
   </si>
   <si>
@@ -221,6 +233,9 @@
   </si>
   <si>
     <t>17.06.2026</t>
+  </si>
+  <si>
+    <t>19.06.2026</t>
   </si>
 </sst>
 </file>
@@ -578,10 +593,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q49"/>
+  <dimension ref="A1:U49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:21">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -633,13 +648,25 @@
       <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:17">
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C2">
         <v>6.01</v>
@@ -651,7 +678,7 @@
         <v>15.09</v>
       </c>
       <c r="F2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G2">
         <v>5.55</v>
@@ -663,7 +690,7 @@
         <v>16.26</v>
       </c>
       <c r="J2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="K2">
         <v>5.55</v>
@@ -675,7 +702,7 @@
         <v>16.3</v>
       </c>
       <c r="N2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="O2">
         <v>4.97</v>
@@ -686,13 +713,25 @@
       <c r="Q2">
         <v>18.14</v>
       </c>
-    </row>
-    <row r="3" spans="1:17">
+      <c r="R2" t="s">
+        <v>73</v>
+      </c>
+      <c r="S2">
+        <v>4.82</v>
+      </c>
+      <c r="T2">
+        <v>17.48</v>
+      </c>
+      <c r="U2">
+        <v>18.8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C3">
         <v>5.58</v>
@@ -704,7 +743,7 @@
         <v>16.29</v>
       </c>
       <c r="F3" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G3">
         <v>5.63</v>
@@ -716,7 +755,7 @@
         <v>16.04</v>
       </c>
       <c r="J3" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="K3">
         <v>5.63</v>
@@ -728,7 +767,7 @@
         <v>16.07</v>
       </c>
       <c r="N3" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="O3">
         <v>6.51</v>
@@ -739,13 +778,25 @@
       <c r="Q3">
         <v>13.76</v>
       </c>
-    </row>
-    <row r="4" spans="1:17">
+      <c r="R3" t="s">
+        <v>73</v>
+      </c>
+      <c r="S3">
+        <v>6.88</v>
+      </c>
+      <c r="T3">
+        <v>12.25</v>
+      </c>
+      <c r="U3">
+        <v>13.09</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C4">
         <v>8.15</v>
@@ -757,7 +808,7 @@
         <v>11.06</v>
       </c>
       <c r="F4" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G4">
         <v>8.42</v>
@@ -769,7 +820,7 @@
         <v>10.62</v>
       </c>
       <c r="J4" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="K4">
         <v>8.390000000000001</v>
@@ -781,7 +832,7 @@
         <v>10.69</v>
       </c>
       <c r="N4" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="O4">
         <v>8.33</v>
@@ -792,119 +843,155 @@
       <c r="Q4">
         <v>10.68</v>
       </c>
-    </row>
-    <row r="5" spans="1:17">
+      <c r="R4" t="s">
+        <v>73</v>
+      </c>
+      <c r="S4">
+        <v>7.04</v>
+      </c>
+      <c r="T4">
+        <v>11.96</v>
+      </c>
+      <c r="U4">
+        <v>12.77</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C5">
+        <v>10.19</v>
+      </c>
+      <c r="D5">
+        <v>8.34</v>
+      </c>
+      <c r="E5">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="F5" t="s">
+        <v>70</v>
+      </c>
+      <c r="G5">
+        <v>10.33</v>
+      </c>
+      <c r="H5">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="I5">
+        <v>8.6</v>
+      </c>
+      <c r="J5" t="s">
+        <v>71</v>
+      </c>
+      <c r="K5">
+        <v>10.61</v>
+      </c>
+      <c r="L5">
+        <v>7.95</v>
+      </c>
+      <c r="M5">
+        <v>8.390000000000001</v>
+      </c>
+      <c r="N5" t="s">
+        <v>72</v>
+      </c>
+      <c r="O5">
+        <v>9.4</v>
+      </c>
+      <c r="P5">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="Q5">
+        <v>9.44</v>
+      </c>
+      <c r="R5" t="s">
+        <v>73</v>
+      </c>
+      <c r="S5">
+        <v>9.140000000000001</v>
+      </c>
+      <c r="T5">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="U5">
+        <v>9.779999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21">
+      <c r="A6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C6">
         <v>8.85</v>
       </c>
-      <c r="D5">
+      <c r="D6">
         <v>9.6</v>
       </c>
-      <c r="E5">
+      <c r="E6">
         <v>10.17</v>
       </c>
-      <c r="F5" t="s">
-        <v>66</v>
-      </c>
-      <c r="G5">
+      <c r="F6" t="s">
+        <v>70</v>
+      </c>
+      <c r="G6">
         <v>8.699999999999999</v>
       </c>
-      <c r="H5">
+      <c r="H6">
         <v>9.66</v>
       </c>
-      <c r="I5">
+      <c r="I6">
         <v>10.26</v>
       </c>
-      <c r="J5" t="s">
-        <v>67</v>
-      </c>
-      <c r="K5">
+      <c r="J6" t="s">
+        <v>71</v>
+      </c>
+      <c r="K6">
         <v>8.630000000000001</v>
       </c>
-      <c r="L5">
+      <c r="L6">
         <v>9.77</v>
       </c>
-      <c r="M5">
+      <c r="M6">
         <v>10.38</v>
       </c>
-      <c r="N5" t="s">
-        <v>68</v>
-      </c>
-      <c r="O5">
+      <c r="N6" t="s">
+        <v>72</v>
+      </c>
+      <c r="O6">
         <v>8.619999999999999</v>
       </c>
-      <c r="P5">
+      <c r="P6">
         <v>9.69</v>
       </c>
-      <c r="Q5">
+      <c r="Q6">
         <v>10.32</v>
       </c>
-    </row>
-    <row r="6" spans="1:17">
-      <c r="A6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C6">
-        <v>10.19</v>
-      </c>
-      <c r="D6">
-        <v>8.34</v>
-      </c>
-      <c r="E6">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="F6" t="s">
-        <v>66</v>
-      </c>
-      <c r="G6">
-        <v>10.33</v>
-      </c>
-      <c r="H6">
-        <v>8.140000000000001</v>
-      </c>
-      <c r="I6">
-        <v>8.6</v>
-      </c>
-      <c r="J6" t="s">
-        <v>67</v>
-      </c>
-      <c r="K6">
-        <v>10.61</v>
-      </c>
-      <c r="L6">
-        <v>7.95</v>
-      </c>
-      <c r="M6">
-        <v>8.390000000000001</v>
-      </c>
-      <c r="N6" t="s">
-        <v>68</v>
-      </c>
-      <c r="O6">
-        <v>9.4</v>
-      </c>
-      <c r="P6">
-        <v>8.880000000000001</v>
-      </c>
-      <c r="Q6">
-        <v>9.44</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17">
+      <c r="R6" t="s">
+        <v>73</v>
+      </c>
+      <c r="S6">
+        <v>10.63</v>
+      </c>
+      <c r="T6">
+        <v>7.92</v>
+      </c>
+      <c r="U6">
+        <v>8.359999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B7" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C7">
         <v>9.970000000000001</v>
@@ -916,7 +1003,7 @@
         <v>8.99</v>
       </c>
       <c r="F7" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G7">
         <v>10.11</v>
@@ -928,7 +1015,7 @@
         <v>8.789999999999999</v>
       </c>
       <c r="J7" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="K7">
         <v>11.04</v>
@@ -940,7 +1027,7 @@
         <v>8.050000000000001</v>
       </c>
       <c r="N7" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="O7">
         <v>11.39</v>
@@ -951,13 +1038,25 @@
       <c r="Q7">
         <v>7.74</v>
       </c>
-    </row>
-    <row r="8" spans="1:17">
+      <c r="R7" t="s">
+        <v>73</v>
+      </c>
+      <c r="S7">
+        <v>12.2</v>
+      </c>
+      <c r="T7">
+        <v>6.91</v>
+      </c>
+      <c r="U7">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B8" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C8">
         <v>15.6</v>
@@ -969,7 +1068,7 @@
         <v>5.65</v>
       </c>
       <c r="F8" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G8">
         <v>15.67</v>
@@ -981,7 +1080,7 @@
         <v>5.57</v>
       </c>
       <c r="J8" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="K8">
         <v>15.39</v>
@@ -993,7 +1092,7 @@
         <v>5.7</v>
       </c>
       <c r="N8" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="O8">
         <v>14.67</v>
@@ -1004,13 +1103,25 @@
       <c r="Q8">
         <v>5.93</v>
       </c>
-    </row>
-    <row r="9" spans="1:17">
+      <c r="R8" t="s">
+        <v>73</v>
+      </c>
+      <c r="S8">
+        <v>14.87</v>
+      </c>
+      <c r="T8">
+        <v>5.67</v>
+      </c>
+      <c r="U8">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C9">
         <v>21.29</v>
@@ -1022,7 +1133,7 @@
         <v>4.07</v>
       </c>
       <c r="F9" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G9">
         <v>20.29</v>
@@ -1034,7 +1145,7 @@
         <v>4.24</v>
       </c>
       <c r="J9" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="K9">
         <v>19.71</v>
@@ -1046,7 +1157,7 @@
         <v>4.38</v>
       </c>
       <c r="N9" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="O9">
         <v>20.14</v>
@@ -1057,13 +1168,25 @@
       <c r="Q9">
         <v>4.24</v>
       </c>
-    </row>
-    <row r="10" spans="1:17">
+      <c r="R9" t="s">
+        <v>73</v>
+      </c>
+      <c r="S9">
+        <v>21</v>
+      </c>
+      <c r="T9">
+        <v>4.01</v>
+      </c>
+      <c r="U9">
+        <v>4.09</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C10">
         <v>32.29</v>
@@ -1075,7 +1198,7 @@
         <v>2.6</v>
       </c>
       <c r="F10" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G10">
         <v>33</v>
@@ -1087,7 +1210,7 @@
         <v>2.49</v>
       </c>
       <c r="J10" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="K10">
         <v>34.14</v>
@@ -1099,7 +1222,7 @@
         <v>2.42</v>
       </c>
       <c r="N10" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="O10">
         <v>30.43</v>
@@ -1110,13 +1233,25 @@
       <c r="Q10">
         <v>2.71</v>
       </c>
-    </row>
-    <row r="11" spans="1:17">
+      <c r="R10" t="s">
+        <v>73</v>
+      </c>
+      <c r="S10">
+        <v>31.5</v>
+      </c>
+      <c r="T10">
+        <v>2.67</v>
+      </c>
+      <c r="U10">
+        <v>2.64</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B11" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C11">
         <v>49.86</v>
@@ -1128,7 +1263,7 @@
         <v>1.59</v>
       </c>
       <c r="F11" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G11">
         <v>50.57</v>
@@ -1140,7 +1275,7 @@
         <v>1.54</v>
       </c>
       <c r="J11" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="K11">
         <v>38.71</v>
@@ -1152,7 +1287,7 @@
         <v>2.1</v>
       </c>
       <c r="N11" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="O11">
         <v>37.71</v>
@@ -1163,13 +1298,25 @@
       <c r="Q11">
         <v>2.13</v>
       </c>
-    </row>
-    <row r="12" spans="1:17">
+      <c r="R11" t="s">
+        <v>73</v>
+      </c>
+      <c r="S11">
+        <v>40.67</v>
+      </c>
+      <c r="T11">
+        <v>2.07</v>
+      </c>
+      <c r="U11">
+        <v>1.98</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21">
       <c r="A12" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B12" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C12">
         <v>63.71</v>
@@ -1181,7 +1328,7 @@
         <v>1.2</v>
       </c>
       <c r="F12" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G12">
         <v>44.57</v>
@@ -1193,7 +1340,7 @@
         <v>1.78</v>
       </c>
       <c r="J12" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="K12">
         <v>43.86</v>
@@ -1205,7 +1352,7 @@
         <v>1.82</v>
       </c>
       <c r="N12" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="O12">
         <v>41.14</v>
@@ -1216,13 +1363,25 @@
       <c r="Q12">
         <v>1.93</v>
       </c>
-    </row>
-    <row r="13" spans="1:17">
+      <c r="R12" t="s">
+        <v>73</v>
+      </c>
+      <c r="S12">
+        <v>42</v>
+      </c>
+      <c r="T12">
+        <v>2.01</v>
+      </c>
+      <c r="U12">
+        <v>1.91</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21">
       <c r="A13" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B13" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C13">
         <v>37.71</v>
@@ -1234,7 +1393,7 @@
         <v>2.19</v>
       </c>
       <c r="F13" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G13">
         <v>37.71</v>
@@ -1246,7 +1405,7 @@
         <v>2.15</v>
       </c>
       <c r="J13" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="K13">
         <v>39.43</v>
@@ -1258,7 +1417,7 @@
         <v>2.06</v>
       </c>
       <c r="N13" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="O13">
         <v>42</v>
@@ -1269,187 +1428,235 @@
       <c r="Q13">
         <v>1.88</v>
       </c>
-    </row>
-    <row r="14" spans="1:17">
+      <c r="R13" t="s">
+        <v>73</v>
+      </c>
+      <c r="S13">
+        <v>42.17</v>
+      </c>
+      <c r="T13">
+        <v>2</v>
+      </c>
+      <c r="U13">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21">
       <c r="A14" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B14" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C14">
+        <v>68.43000000000001</v>
+      </c>
+      <c r="D14">
+        <v>1.24</v>
+      </c>
+      <c r="E14">
+        <v>1.1</v>
+      </c>
+      <c r="F14" t="s">
+        <v>70</v>
+      </c>
+      <c r="G14">
+        <v>52.71</v>
+      </c>
+      <c r="H14">
+        <v>1.6</v>
+      </c>
+      <c r="I14">
+        <v>1.46</v>
+      </c>
+      <c r="J14" t="s">
+        <v>71</v>
+      </c>
+      <c r="K14">
+        <v>52.71</v>
+      </c>
+      <c r="L14">
+        <v>1.6</v>
+      </c>
+      <c r="M14">
+        <v>1.47</v>
+      </c>
+      <c r="N14" t="s">
+        <v>72</v>
+      </c>
+      <c r="O14">
+        <v>57.86</v>
+      </c>
+      <c r="P14">
+        <v>1.44</v>
+      </c>
+      <c r="Q14">
+        <v>1.29</v>
+      </c>
+      <c r="R14" t="s">
+        <v>73</v>
+      </c>
+      <c r="S14">
+        <v>47.17</v>
+      </c>
+      <c r="T14">
+        <v>1.79</v>
+      </c>
+      <c r="U14">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21">
+      <c r="A15" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" t="s">
+        <v>69</v>
+      </c>
+      <c r="C15">
         <v>41.71</v>
       </c>
-      <c r="D14">
+      <c r="D15">
         <v>2.04</v>
       </c>
-      <c r="E14">
+      <c r="E15">
         <v>1.95</v>
       </c>
-      <c r="F14" t="s">
-        <v>66</v>
-      </c>
-      <c r="G14">
+      <c r="F15" t="s">
+        <v>70</v>
+      </c>
+      <c r="G15">
         <v>45.57</v>
       </c>
-      <c r="H14">
+      <c r="H15">
         <v>1.85</v>
       </c>
-      <c r="I14">
+      <c r="I15">
         <v>1.73</v>
       </c>
-      <c r="J14" t="s">
-        <v>67</v>
-      </c>
-      <c r="K14">
+      <c r="J15" t="s">
+        <v>71</v>
+      </c>
+      <c r="K15">
         <v>47</v>
       </c>
-      <c r="L14">
+      <c r="L15">
         <v>1.8</v>
       </c>
-      <c r="M14">
+      <c r="M15">
         <v>1.68</v>
       </c>
-      <c r="N14" t="s">
-        <v>68</v>
-      </c>
-      <c r="O14">
+      <c r="N15" t="s">
+        <v>72</v>
+      </c>
+      <c r="O15">
         <v>50.43</v>
       </c>
-      <c r="P14">
+      <c r="P15">
         <v>1.66</v>
       </c>
-      <c r="Q14">
+      <c r="Q15">
         <v>1.52</v>
       </c>
-    </row>
-    <row r="15" spans="1:17">
-      <c r="A15" t="s">
-        <v>30</v>
-      </c>
-      <c r="B15" t="s">
-        <v>65</v>
-      </c>
-      <c r="C15">
+      <c r="R15" t="s">
+        <v>73</v>
+      </c>
+      <c r="S15">
+        <v>48</v>
+      </c>
+      <c r="T15">
+        <v>1.76</v>
+      </c>
+      <c r="U15">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21">
+      <c r="A16" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" t="s">
+        <v>69</v>
+      </c>
+      <c r="C16">
         <v>53.43</v>
       </c>
-      <c r="D15">
+      <c r="D16">
         <v>1.59</v>
       </c>
-      <c r="E15">
+      <c r="E16">
         <v>1.47</v>
       </c>
-      <c r="F15" t="s">
-        <v>66</v>
-      </c>
-      <c r="G15">
+      <c r="F16" t="s">
+        <v>70</v>
+      </c>
+      <c r="G16">
         <v>53.43</v>
       </c>
-      <c r="H15">
+      <c r="H16">
         <v>1.57</v>
       </c>
-      <c r="I15">
+      <c r="I16">
         <v>1.44</v>
       </c>
-      <c r="J15" t="s">
-        <v>67</v>
-      </c>
-      <c r="K15">
+      <c r="J16" t="s">
+        <v>71</v>
+      </c>
+      <c r="K16">
         <v>51.29</v>
       </c>
-      <c r="L15">
+      <c r="L16">
         <v>1.64</v>
       </c>
-      <c r="M15">
+      <c r="M16">
         <v>1.52</v>
       </c>
-      <c r="N15" t="s">
-        <v>68</v>
-      </c>
-      <c r="O15">
+      <c r="N16" t="s">
+        <v>72</v>
+      </c>
+      <c r="O16">
         <v>51.29</v>
       </c>
-      <c r="P15">
+      <c r="P16">
         <v>1.63</v>
       </c>
-      <c r="Q15">
+      <c r="Q16">
         <v>1.49</v>
       </c>
-    </row>
-    <row r="16" spans="1:17">
-      <c r="A16" t="s">
-        <v>31</v>
-      </c>
-      <c r="B16" t="s">
-        <v>65</v>
-      </c>
-      <c r="C16">
-        <v>68.43000000000001</v>
-      </c>
-      <c r="D16">
-        <v>1.24</v>
-      </c>
-      <c r="E16">
-        <v>1.1</v>
-      </c>
-      <c r="F16" t="s">
-        <v>66</v>
-      </c>
-      <c r="G16">
-        <v>52.71</v>
-      </c>
-      <c r="H16">
-        <v>1.6</v>
-      </c>
-      <c r="I16">
+      <c r="R16" t="s">
+        <v>73</v>
+      </c>
+      <c r="S16">
+        <v>53</v>
+      </c>
+      <c r="T16">
+        <v>1.59</v>
+      </c>
+      <c r="U16">
         <v>1.46</v>
       </c>
-      <c r="J16" t="s">
-        <v>67</v>
-      </c>
-      <c r="K16">
-        <v>52.71</v>
-      </c>
-      <c r="L16">
-        <v>1.6</v>
-      </c>
-      <c r="M16">
-        <v>1.47</v>
-      </c>
-      <c r="N16" t="s">
-        <v>68</v>
-      </c>
-      <c r="O16">
-        <v>57.86</v>
-      </c>
-      <c r="P16">
-        <v>1.44</v>
-      </c>
-      <c r="Q16">
-        <v>1.29</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17">
+    </row>
+    <row r="17" spans="1:21">
       <c r="A17" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B17" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C17">
-        <v>71.14</v>
+        <v>74.43000000000001</v>
       </c>
       <c r="D17">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="E17">
-        <v>1.05</v>
+        <v>0.99</v>
       </c>
       <c r="F17" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G17">
-        <v>75.29000000000001</v>
+        <v>75.14</v>
       </c>
       <c r="H17">
         <v>1.12</v>
@@ -1458,51 +1665,63 @@
         <v>0.95</v>
       </c>
       <c r="J17" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="K17">
+        <v>83.56999999999999</v>
+      </c>
+      <c r="L17">
+        <v>1.01</v>
+      </c>
+      <c r="M17">
+        <v>0.84</v>
+      </c>
+      <c r="N17" t="s">
+        <v>72</v>
+      </c>
+      <c r="O17">
+        <v>87.70999999999999</v>
+      </c>
+      <c r="P17">
+        <v>0.95</v>
+      </c>
+      <c r="Q17">
+        <v>0.77</v>
+      </c>
+      <c r="R17" t="s">
+        <v>73</v>
+      </c>
+      <c r="S17">
+        <v>78</v>
+      </c>
+      <c r="T17">
+        <v>1.08</v>
+      </c>
+      <c r="U17">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21">
+      <c r="A18" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" t="s">
+        <v>69</v>
+      </c>
+      <c r="C18">
+        <v>71.14</v>
+      </c>
+      <c r="D18">
+        <v>1.19</v>
+      </c>
+      <c r="E18">
+        <v>1.05</v>
+      </c>
+      <c r="F18" t="s">
+        <v>70</v>
+      </c>
+      <c r="G18">
         <v>75.29000000000001</v>
-      </c>
-      <c r="L17">
-        <v>1.12</v>
-      </c>
-      <c r="M17">
-        <v>0.96</v>
-      </c>
-      <c r="N17" t="s">
-        <v>68</v>
-      </c>
-      <c r="O17">
-        <v>83</v>
-      </c>
-      <c r="P17">
-        <v>1.01</v>
-      </c>
-      <c r="Q17">
-        <v>0.83</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17">
-      <c r="A18" t="s">
-        <v>33</v>
-      </c>
-      <c r="B18" t="s">
-        <v>65</v>
-      </c>
-      <c r="C18">
-        <v>74.43000000000001</v>
-      </c>
-      <c r="D18">
-        <v>1.14</v>
-      </c>
-      <c r="E18">
-        <v>0.99</v>
-      </c>
-      <c r="F18" t="s">
-        <v>66</v>
-      </c>
-      <c r="G18">
-        <v>75.14</v>
       </c>
       <c r="H18">
         <v>1.12</v>
@@ -1511,142 +1730,178 @@
         <v>0.95</v>
       </c>
       <c r="J18" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="K18">
-        <v>83.56999999999999</v>
+        <v>75.29000000000001</v>
       </c>
       <c r="L18">
+        <v>1.12</v>
+      </c>
+      <c r="M18">
+        <v>0.96</v>
+      </c>
+      <c r="N18" t="s">
+        <v>72</v>
+      </c>
+      <c r="O18">
+        <v>83</v>
+      </c>
+      <c r="P18">
         <v>1.01</v>
       </c>
-      <c r="M18">
-        <v>0.84</v>
-      </c>
-      <c r="N18" t="s">
-        <v>68</v>
-      </c>
-      <c r="O18">
-        <v>87.70999999999999</v>
-      </c>
-      <c r="P18">
+      <c r="Q18">
+        <v>0.83</v>
+      </c>
+      <c r="R18" t="s">
+        <v>73</v>
+      </c>
+      <c r="S18">
+        <v>88.83</v>
+      </c>
+      <c r="T18">
         <v>0.95</v>
       </c>
-      <c r="Q18">
+      <c r="U18">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21">
+      <c r="A19" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" t="s">
+        <v>69</v>
+      </c>
+      <c r="C19">
+        <v>141.29</v>
+      </c>
+      <c r="D19">
+        <v>0.6</v>
+      </c>
+      <c r="E19">
+        <v>0.43</v>
+      </c>
+      <c r="F19" t="s">
+        <v>70</v>
+      </c>
+      <c r="G19">
+        <v>145.57</v>
+      </c>
+      <c r="H19">
+        <v>0.58</v>
+      </c>
+      <c r="I19">
+        <v>0.39</v>
+      </c>
+      <c r="J19" t="s">
+        <v>71</v>
+      </c>
+      <c r="K19">
+        <v>110.14</v>
+      </c>
+      <c r="L19">
         <v>0.77</v>
       </c>
-    </row>
-    <row r="19" spans="1:17">
-      <c r="A19" t="s">
-        <v>34</v>
-      </c>
-      <c r="B19" t="s">
-        <v>65</v>
-      </c>
-      <c r="C19">
+      <c r="M19">
+        <v>0.59</v>
+      </c>
+      <c r="N19" t="s">
+        <v>72</v>
+      </c>
+      <c r="O19">
+        <v>105.86</v>
+      </c>
+      <c r="P19">
+        <v>0.79</v>
+      </c>
+      <c r="Q19">
+        <v>0.6</v>
+      </c>
+      <c r="R19" t="s">
+        <v>73</v>
+      </c>
+      <c r="S19">
+        <v>110</v>
+      </c>
+      <c r="T19">
+        <v>0.77</v>
+      </c>
+      <c r="U19">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21">
+      <c r="A20" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" t="s">
+        <v>69</v>
+      </c>
+      <c r="C20">
         <v>88.86</v>
       </c>
-      <c r="D19">
+      <c r="D20">
         <v>0.96</v>
       </c>
-      <c r="E19">
+      <c r="E20">
         <v>0.8</v>
       </c>
-      <c r="F19" t="s">
-        <v>66</v>
-      </c>
-      <c r="G19">
+      <c r="F20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G20">
         <v>91.70999999999999</v>
       </c>
-      <c r="H19">
+      <c r="H20">
         <v>0.92</v>
       </c>
-      <c r="I19">
+      <c r="I20">
         <v>0.74</v>
       </c>
-      <c r="J19" t="s">
-        <v>67</v>
-      </c>
-      <c r="K19">
+      <c r="J20" t="s">
+        <v>71</v>
+      </c>
+      <c r="K20">
         <v>91.70999999999999</v>
       </c>
-      <c r="L19">
+      <c r="L20">
         <v>0.92</v>
       </c>
-      <c r="M19">
+      <c r="M20">
         <v>0.75</v>
       </c>
-      <c r="N19" t="s">
-        <v>68</v>
-      </c>
-      <c r="O19">
+      <c r="N20" t="s">
+        <v>72</v>
+      </c>
+      <c r="O20">
         <v>92.43000000000001</v>
       </c>
-      <c r="P19">
+      <c r="P20">
         <v>0.9</v>
       </c>
-      <c r="Q19">
+      <c r="Q20">
         <v>0.72</v>
       </c>
-    </row>
-    <row r="20" spans="1:17">
-      <c r="A20" t="s">
-        <v>35</v>
-      </c>
-      <c r="B20" t="s">
-        <v>65</v>
-      </c>
-      <c r="C20">
-        <v>141.29</v>
-      </c>
-      <c r="D20">
-        <v>0.6</v>
-      </c>
-      <c r="E20">
-        <v>0.43</v>
-      </c>
-      <c r="F20" t="s">
-        <v>66</v>
-      </c>
-      <c r="G20">
-        <v>145.57</v>
-      </c>
-      <c r="H20">
+      <c r="R20" t="s">
+        <v>73</v>
+      </c>
+      <c r="S20">
+        <v>110.83</v>
+      </c>
+      <c r="T20">
+        <v>0.76</v>
+      </c>
+      <c r="U20">
         <v>0.58</v>
       </c>
-      <c r="I20">
-        <v>0.39</v>
-      </c>
-      <c r="J20" t="s">
-        <v>67</v>
-      </c>
-      <c r="K20">
-        <v>110.14</v>
-      </c>
-      <c r="L20">
-        <v>0.77</v>
-      </c>
-      <c r="M20">
-        <v>0.59</v>
-      </c>
-      <c r="N20" t="s">
-        <v>68</v>
-      </c>
-      <c r="O20">
-        <v>105.86</v>
-      </c>
-      <c r="P20">
-        <v>0.79</v>
-      </c>
-      <c r="Q20">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17">
+    </row>
+    <row r="21" spans="1:21">
       <c r="A21" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B21" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C21">
         <v>101.29</v>
@@ -1658,7 +1913,7 @@
         <v>0.67</v>
       </c>
       <c r="F21" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G21">
         <v>106.14</v>
@@ -1670,7 +1925,7 @@
         <v>0.61</v>
       </c>
       <c r="J21" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="K21">
         <v>107.57</v>
@@ -1682,7 +1937,7 @@
         <v>0.61</v>
       </c>
       <c r="N21" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="O21">
         <v>119.57</v>
@@ -1693,13 +1948,25 @@
       <c r="Q21">
         <v>0.51</v>
       </c>
-    </row>
-    <row r="22" spans="1:17">
+      <c r="R21" t="s">
+        <v>73</v>
+      </c>
+      <c r="S21">
+        <v>115.17</v>
+      </c>
+      <c r="T21">
+        <v>0.73</v>
+      </c>
+      <c r="U21">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21">
       <c r="A22" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B22" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C22">
         <v>442.71</v>
@@ -1711,7 +1978,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="F22" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G22">
         <v>462.29</v>
@@ -1723,7 +1990,7 @@
         <v>0.06</v>
       </c>
       <c r="J22" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="K22">
         <v>186</v>
@@ -1735,7 +2002,7 @@
         <v>0.28</v>
       </c>
       <c r="N22" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="O22">
         <v>123.14</v>
@@ -1746,49 +2013,61 @@
       <c r="Q22">
         <v>0.49</v>
       </c>
-    </row>
-    <row r="23" spans="1:17">
+      <c r="R22" t="s">
+        <v>73</v>
+      </c>
+      <c r="S22">
+        <v>128.5</v>
+      </c>
+      <c r="T22">
+        <v>0.66</v>
+      </c>
+      <c r="U22">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21">
       <c r="A23" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B23" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C23">
-        <v>89</v>
+        <v>153</v>
       </c>
       <c r="D23">
-        <v>0.95</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E23">
-        <v>0.8</v>
+        <v>0.39</v>
       </c>
       <c r="F23" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G23">
-        <v>90.43000000000001</v>
+        <v>158.57</v>
       </c>
       <c r="H23">
-        <v>0.93</v>
+        <v>0.53</v>
       </c>
       <c r="I23">
-        <v>0.75</v>
+        <v>0.35</v>
       </c>
       <c r="J23" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="K23">
-        <v>133.71</v>
+        <v>157.14</v>
       </c>
       <c r="L23">
-        <v>0.63</v>
+        <v>0.54</v>
       </c>
       <c r="M23">
-        <v>0.45</v>
+        <v>0.36</v>
       </c>
       <c r="N23" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="O23">
         <v>135.14</v>
@@ -1799,225 +2078,285 @@
       <c r="Q23">
         <v>0.43</v>
       </c>
-    </row>
-    <row r="24" spans="1:17">
+      <c r="R23" t="s">
+        <v>73</v>
+      </c>
+      <c r="S23">
+        <v>144</v>
+      </c>
+      <c r="T23">
+        <v>0.59</v>
+      </c>
+      <c r="U23">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21">
       <c r="A24" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B24" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C24">
+        <v>250</v>
+      </c>
+      <c r="D24">
+        <v>0.34</v>
+      </c>
+      <c r="E24">
+        <v>0.18</v>
+      </c>
+      <c r="F24" t="s">
+        <v>70</v>
+      </c>
+      <c r="G24">
+        <v>259.86</v>
+      </c>
+      <c r="H24">
+        <v>0.32</v>
+      </c>
+      <c r="I24">
+        <v>0.16</v>
+      </c>
+      <c r="J24" t="s">
+        <v>71</v>
+      </c>
+      <c r="K24">
         <v>153</v>
       </c>
-      <c r="D24">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="E24">
+      <c r="L24">
+        <v>0.55</v>
+      </c>
+      <c r="M24">
+        <v>0.37</v>
+      </c>
+      <c r="N24" t="s">
+        <v>72</v>
+      </c>
+      <c r="O24">
+        <v>143</v>
+      </c>
+      <c r="P24">
+        <v>0.58</v>
+      </c>
+      <c r="Q24">
+        <v>0.4</v>
+      </c>
+      <c r="R24" t="s">
+        <v>73</v>
+      </c>
+      <c r="S24">
+        <v>144.83</v>
+      </c>
+      <c r="T24">
+        <v>0.58</v>
+      </c>
+      <c r="U24">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21">
+      <c r="A25" t="s">
+        <v>44</v>
+      </c>
+      <c r="B25" t="s">
+        <v>69</v>
+      </c>
+      <c r="C25">
+        <v>191.71</v>
+      </c>
+      <c r="D25">
+        <v>0.44</v>
+      </c>
+      <c r="E25">
+        <v>0.28</v>
+      </c>
+      <c r="F25" t="s">
+        <v>70</v>
+      </c>
+      <c r="G25">
+        <v>222.71</v>
+      </c>
+      <c r="H25">
+        <v>0.38</v>
+      </c>
+      <c r="I25">
+        <v>0.21</v>
+      </c>
+      <c r="J25" t="s">
+        <v>71</v>
+      </c>
+      <c r="K25">
+        <v>193.29</v>
+      </c>
+      <c r="L25">
+        <v>0.44</v>
+      </c>
+      <c r="M25">
+        <v>0.26</v>
+      </c>
+      <c r="N25" t="s">
+        <v>72</v>
+      </c>
+      <c r="O25">
+        <v>197.43</v>
+      </c>
+      <c r="P25">
+        <v>0.42</v>
+      </c>
+      <c r="Q25">
+        <v>0.24</v>
+      </c>
+      <c r="R25" t="s">
+        <v>73</v>
+      </c>
+      <c r="S25">
+        <v>148.17</v>
+      </c>
+      <c r="T25">
+        <v>0.57</v>
+      </c>
+      <c r="U25">
         <v>0.39</v>
       </c>
-      <c r="F24" t="s">
-        <v>66</v>
-      </c>
-      <c r="G24">
-        <v>158.57</v>
-      </c>
-      <c r="H24">
-        <v>0.53</v>
-      </c>
-      <c r="I24">
-        <v>0.35</v>
-      </c>
-      <c r="J24" t="s">
-        <v>67</v>
-      </c>
-      <c r="K24">
-        <v>157.14</v>
-      </c>
-      <c r="L24">
-        <v>0.54</v>
-      </c>
-      <c r="M24">
-        <v>0.36</v>
-      </c>
-      <c r="N24" t="s">
-        <v>68</v>
-      </c>
-      <c r="O24">
-        <v>135.14</v>
-      </c>
-      <c r="P24">
-        <v>0.62</v>
-      </c>
-      <c r="Q24">
-        <v>0.43</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17">
-      <c r="A25" t="s">
-        <v>40</v>
-      </c>
-      <c r="B25" t="s">
-        <v>65</v>
-      </c>
-      <c r="C25">
-        <v>250</v>
-      </c>
-      <c r="D25">
-        <v>0.34</v>
-      </c>
-      <c r="E25">
-        <v>0.18</v>
-      </c>
-      <c r="F25" t="s">
-        <v>66</v>
-      </c>
-      <c r="G25">
-        <v>259.86</v>
-      </c>
-      <c r="H25">
-        <v>0.32</v>
-      </c>
-      <c r="I25">
-        <v>0.16</v>
-      </c>
-      <c r="J25" t="s">
-        <v>67</v>
-      </c>
-      <c r="K25">
-        <v>153</v>
-      </c>
-      <c r="L25">
-        <v>0.55</v>
-      </c>
-      <c r="M25">
-        <v>0.37</v>
-      </c>
-      <c r="N25" t="s">
-        <v>68</v>
-      </c>
-      <c r="O25">
-        <v>143</v>
-      </c>
-      <c r="P25">
-        <v>0.58</v>
-      </c>
-      <c r="Q25">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17">
+    </row>
+    <row r="26" spans="1:21">
       <c r="A26" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B26" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C26">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="D26">
-        <v>1.06</v>
+        <v>0.95</v>
       </c>
       <c r="E26">
-        <v>0.91</v>
+        <v>0.8</v>
       </c>
       <c r="F26" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G26">
-        <v>80</v>
+        <v>90.43000000000001</v>
       </c>
       <c r="H26">
-        <v>1.05</v>
+        <v>0.93</v>
       </c>
       <c r="I26">
-        <v>0.88</v>
+        <v>0.75</v>
       </c>
       <c r="J26" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="K26">
-        <v>133.14</v>
+        <v>133.71</v>
       </c>
       <c r="L26">
         <v>0.63</v>
       </c>
       <c r="M26">
+        <v>0.45</v>
+      </c>
+      <c r="N26" t="s">
+        <v>72</v>
+      </c>
+      <c r="O26">
+        <v>135.14</v>
+      </c>
+      <c r="P26">
+        <v>0.62</v>
+      </c>
+      <c r="Q26">
+        <v>0.43</v>
+      </c>
+      <c r="R26" t="s">
+        <v>73</v>
+      </c>
+      <c r="S26">
+        <v>148.33</v>
+      </c>
+      <c r="T26">
+        <v>0.57</v>
+      </c>
+      <c r="U26">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21">
+      <c r="A27" t="s">
+        <v>46</v>
+      </c>
+      <c r="B27" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27">
+        <v>80</v>
+      </c>
+      <c r="D27">
+        <v>1.06</v>
+      </c>
+      <c r="E27">
+        <v>0.91</v>
+      </c>
+      <c r="F27" t="s">
+        <v>70</v>
+      </c>
+      <c r="G27">
+        <v>80</v>
+      </c>
+      <c r="H27">
+        <v>1.05</v>
+      </c>
+      <c r="I27">
+        <v>0.88</v>
+      </c>
+      <c r="J27" t="s">
+        <v>71</v>
+      </c>
+      <c r="K27">
+        <v>133.14</v>
+      </c>
+      <c r="L27">
+        <v>0.63</v>
+      </c>
+      <c r="M27">
         <v>0.46</v>
       </c>
-      <c r="N26" t="s">
-        <v>68</v>
-      </c>
-      <c r="O26">
+      <c r="N27" t="s">
+        <v>72</v>
+      </c>
+      <c r="O27">
         <v>145.86</v>
       </c>
-      <c r="P26">
+      <c r="P27">
         <v>0.57</v>
       </c>
-      <c r="Q26">
+      <c r="Q27">
         <v>0.38</v>
       </c>
-    </row>
-    <row r="27" spans="1:17">
-      <c r="A27" t="s">
-        <v>42</v>
-      </c>
-      <c r="B27" t="s">
-        <v>65</v>
-      </c>
-      <c r="C27">
-        <v>191.71</v>
-      </c>
-      <c r="D27">
-        <v>0.44</v>
-      </c>
-      <c r="E27">
-        <v>0.28</v>
-      </c>
-      <c r="F27" t="s">
-        <v>66</v>
-      </c>
-      <c r="G27">
-        <v>222.71</v>
-      </c>
-      <c r="H27">
-        <v>0.38</v>
-      </c>
-      <c r="I27">
-        <v>0.21</v>
-      </c>
-      <c r="J27" t="s">
-        <v>67</v>
-      </c>
-      <c r="K27">
-        <v>193.29</v>
-      </c>
-      <c r="L27">
-        <v>0.44</v>
-      </c>
-      <c r="M27">
-        <v>0.26</v>
-      </c>
-      <c r="N27" t="s">
-        <v>68</v>
-      </c>
-      <c r="O27">
-        <v>197.43</v>
-      </c>
-      <c r="P27">
-        <v>0.42</v>
-      </c>
-      <c r="Q27">
-        <v>0.24</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17">
+      <c r="R27" t="s">
+        <v>73</v>
+      </c>
+      <c r="S27">
+        <v>152.33</v>
+      </c>
+      <c r="T27">
+        <v>0.55</v>
+      </c>
+      <c r="U27">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21">
       <c r="A28" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B28" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C28">
         <v>249.71</v>
@@ -2029,7 +2368,7 @@
         <v>0.18</v>
       </c>
       <c r="F28" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G28">
         <v>242.57</v>
@@ -2041,7 +2380,7 @@
         <v>0.18</v>
       </c>
       <c r="J28" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="K28">
         <v>228.14</v>
@@ -2053,7 +2392,7 @@
         <v>0.2</v>
       </c>
       <c r="N28" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="O28">
         <v>216.71</v>
@@ -2064,13 +2403,25 @@
       <c r="Q28">
         <v>0.21</v>
       </c>
-    </row>
-    <row r="29" spans="1:17">
+      <c r="R28" t="s">
+        <v>73</v>
+      </c>
+      <c r="S28">
+        <v>234.17</v>
+      </c>
+      <c r="T28">
+        <v>0.36</v>
+      </c>
+      <c r="U28">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21">
       <c r="A29" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B29" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C29">
         <v>376.29</v>
@@ -2082,7 +2433,7 @@
         <v>0.09</v>
       </c>
       <c r="F29" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G29">
         <v>241</v>
@@ -2094,7 +2445,7 @@
         <v>0.18</v>
       </c>
       <c r="J29" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="K29">
         <v>224.29</v>
@@ -2106,7 +2457,7 @@
         <v>0.21</v>
       </c>
       <c r="N29" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="O29">
         <v>234</v>
@@ -2117,13 +2468,25 @@
       <c r="Q29">
         <v>0.18</v>
       </c>
-    </row>
-    <row r="30" spans="1:17">
+      <c r="R29" t="s">
+        <v>73</v>
+      </c>
+      <c r="S29">
+        <v>256.33</v>
+      </c>
+      <c r="T29">
+        <v>0.33</v>
+      </c>
+      <c r="U29">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21">
       <c r="A30" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B30" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C30">
         <v>320.43</v>
@@ -2135,7 +2498,7 @@
         <v>0.12</v>
       </c>
       <c r="F30" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G30">
         <v>351.57</v>
@@ -2147,7 +2510,7 @@
         <v>0.1</v>
       </c>
       <c r="J30" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="K30">
         <v>341.71</v>
@@ -2159,7 +2522,7 @@
         <v>0.1</v>
       </c>
       <c r="N30" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="O30">
         <v>283.71</v>
@@ -2170,69 +2533,93 @@
       <c r="Q30">
         <v>0.13</v>
       </c>
-    </row>
-    <row r="31" spans="1:17">
+      <c r="R30" t="s">
+        <v>73</v>
+      </c>
+      <c r="S30">
+        <v>302.5</v>
+      </c>
+      <c r="T30">
+        <v>0.28</v>
+      </c>
+      <c r="U30">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21">
       <c r="A31" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B31" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C31">
+        <v>467.14</v>
+      </c>
+      <c r="D31">
+        <v>0.18</v>
+      </c>
+      <c r="E31">
+        <v>0.06</v>
+      </c>
+      <c r="F31" t="s">
+        <v>70</v>
+      </c>
+      <c r="G31">
+        <v>505.29</v>
+      </c>
+      <c r="H31">
+        <v>0.17</v>
+      </c>
+      <c r="I31">
+        <v>0.05</v>
+      </c>
+      <c r="J31" t="s">
+        <v>71</v>
+      </c>
+      <c r="K31">
+        <v>494.14</v>
+      </c>
+      <c r="L31">
+        <v>0.17</v>
+      </c>
+      <c r="M31">
+        <v>0.05</v>
+      </c>
+      <c r="N31" t="s">
+        <v>72</v>
+      </c>
+      <c r="O31">
+        <v>502.43</v>
+      </c>
+      <c r="P31">
+        <v>0.17</v>
+      </c>
+      <c r="Q31">
+        <v>0.05</v>
+      </c>
+      <c r="R31" t="s">
+        <v>73</v>
+      </c>
+      <c r="S31">
+        <v>441.33</v>
+      </c>
+      <c r="T31">
+        <v>0.19</v>
+      </c>
+      <c r="U31">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21">
+      <c r="A32" t="s">
+        <v>51</v>
+      </c>
+      <c r="B32" t="s">
+        <v>69</v>
+      </c>
+      <c r="C32">
         <v>370.43</v>
-      </c>
-      <c r="D31">
-        <v>0.23</v>
-      </c>
-      <c r="E31">
-        <v>0.1</v>
-      </c>
-      <c r="F31" t="s">
-        <v>66</v>
-      </c>
-      <c r="G31">
-        <v>376.71</v>
-      </c>
-      <c r="H31">
-        <v>0.22</v>
-      </c>
-      <c r="I31">
-        <v>0.08</v>
-      </c>
-      <c r="J31" t="s">
-        <v>67</v>
-      </c>
-      <c r="K31">
-        <v>383.71</v>
-      </c>
-      <c r="L31">
-        <v>0.22</v>
-      </c>
-      <c r="M31">
-        <v>0.08</v>
-      </c>
-      <c r="N31" t="s">
-        <v>68</v>
-      </c>
-      <c r="O31">
-        <v>390.71</v>
-      </c>
-      <c r="P31">
-        <v>0.21</v>
-      </c>
-      <c r="Q31">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17">
-      <c r="A32" t="s">
-        <v>47</v>
-      </c>
-      <c r="B32" t="s">
-        <v>65</v>
-      </c>
-      <c r="C32">
-        <v>367.57</v>
       </c>
       <c r="D32">
         <v>0.23</v>
@@ -2241,10 +2628,10 @@
         <v>0.1</v>
       </c>
       <c r="F32" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G32">
-        <v>383</v>
+        <v>376.71</v>
       </c>
       <c r="H32">
         <v>0.22</v>
@@ -2253,36 +2640,48 @@
         <v>0.08</v>
       </c>
       <c r="J32" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="K32">
-        <v>378.86</v>
+        <v>383.71</v>
       </c>
       <c r="L32">
         <v>0.22</v>
       </c>
       <c r="M32">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="N32" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="O32">
-        <v>474.57</v>
+        <v>390.71</v>
       </c>
       <c r="P32">
+        <v>0.21</v>
+      </c>
+      <c r="Q32">
+        <v>0.08</v>
+      </c>
+      <c r="R32" t="s">
+        <v>73</v>
+      </c>
+      <c r="S32">
+        <v>473</v>
+      </c>
+      <c r="T32">
         <v>0.18</v>
       </c>
-      <c r="Q32">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17">
+      <c r="U32">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21">
       <c r="A33" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B33" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C33">
         <v>243.29</v>
@@ -2294,7 +2693,7 @@
         <v>0.19</v>
       </c>
       <c r="F33" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G33">
         <v>455.57</v>
@@ -2306,7 +2705,7 @@
         <v>0.06</v>
       </c>
       <c r="J33" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="K33">
         <v>483.57</v>
@@ -2318,7 +2717,7 @@
         <v>0.06</v>
       </c>
       <c r="N33" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="O33">
         <v>490.71</v>
@@ -2329,81 +2728,105 @@
       <c r="Q33">
         <v>0.05</v>
       </c>
-    </row>
-    <row r="34" spans="1:17">
+      <c r="R33" t="s">
+        <v>73</v>
+      </c>
+      <c r="S33">
+        <v>522.33</v>
+      </c>
+      <c r="T33">
+        <v>0.16</v>
+      </c>
+      <c r="U33">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21">
       <c r="A34" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B34" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C34">
-        <v>299.29</v>
+        <v>367.57</v>
       </c>
       <c r="D34">
-        <v>0.28</v>
+        <v>0.23</v>
       </c>
       <c r="E34">
-        <v>0.14</v>
+        <v>0.1</v>
       </c>
       <c r="F34" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G34">
-        <v>497.86</v>
+        <v>383</v>
       </c>
       <c r="H34">
-        <v>0.17</v>
+        <v>0.22</v>
       </c>
       <c r="I34">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="J34" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="K34">
-        <v>486.71</v>
+        <v>378.86</v>
       </c>
       <c r="L34">
-        <v>0.17</v>
+        <v>0.22</v>
       </c>
       <c r="M34">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="N34" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="O34">
-        <v>497.86</v>
+        <v>474.57</v>
       </c>
       <c r="P34">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="Q34">
         <v>0.05</v>
       </c>
-    </row>
-    <row r="35" spans="1:17">
+      <c r="R34" t="s">
+        <v>73</v>
+      </c>
+      <c r="S34">
+        <v>530.67</v>
+      </c>
+      <c r="T34">
+        <v>0.16</v>
+      </c>
+      <c r="U34">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21">
       <c r="A35" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B35" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C35">
-        <v>467.14</v>
+        <v>299.29</v>
       </c>
       <c r="D35">
-        <v>0.18</v>
+        <v>0.28</v>
       </c>
       <c r="E35">
-        <v>0.06</v>
+        <v>0.14</v>
       </c>
       <c r="F35" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G35">
-        <v>505.29</v>
+        <v>497.86</v>
       </c>
       <c r="H35">
         <v>0.17</v>
@@ -2412,22 +2835,22 @@
         <v>0.05</v>
       </c>
       <c r="J35" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="K35">
-        <v>494.14</v>
+        <v>486.71</v>
       </c>
       <c r="L35">
         <v>0.17</v>
       </c>
       <c r="M35">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="N35" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="O35">
-        <v>502.43</v>
+        <v>497.86</v>
       </c>
       <c r="P35">
         <v>0.17</v>
@@ -2435,119 +2858,155 @@
       <c r="Q35">
         <v>0.05</v>
       </c>
-    </row>
-    <row r="36" spans="1:17">
+      <c r="R35" t="s">
+        <v>73</v>
+      </c>
+      <c r="S35">
+        <v>572.33</v>
+      </c>
+      <c r="T35">
+        <v>0.15</v>
+      </c>
+      <c r="U35">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21">
       <c r="A36" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B36" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C36">
+        <v>747.86</v>
+      </c>
+      <c r="D36">
+        <v>0.11</v>
+      </c>
+      <c r="E36">
+        <v>0.03</v>
+      </c>
+      <c r="F36" t="s">
+        <v>70</v>
+      </c>
+      <c r="G36">
+        <v>747.86</v>
+      </c>
+      <c r="H36">
+        <v>0.11</v>
+      </c>
+      <c r="I36">
+        <v>0.02</v>
+      </c>
+      <c r="J36" t="s">
+        <v>71</v>
+      </c>
+      <c r="K36">
+        <v>747.86</v>
+      </c>
+      <c r="L36">
+        <v>0.11</v>
+      </c>
+      <c r="M36">
+        <v>0.02</v>
+      </c>
+      <c r="N36" t="s">
+        <v>72</v>
+      </c>
+      <c r="O36">
+        <v>747.86</v>
+      </c>
+      <c r="P36">
+        <v>0.11</v>
+      </c>
+      <c r="Q36">
+        <v>0.02</v>
+      </c>
+      <c r="R36" t="s">
+        <v>73</v>
+      </c>
+      <c r="S36">
+        <v>607.5</v>
+      </c>
+      <c r="T36">
+        <v>0.14</v>
+      </c>
+      <c r="U36">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21">
+      <c r="A37" t="s">
+        <v>56</v>
+      </c>
+      <c r="B37" t="s">
+        <v>69</v>
+      </c>
+      <c r="C37">
         <v>540.71</v>
       </c>
-      <c r="D36">
+      <c r="D37">
         <v>0.16</v>
       </c>
-      <c r="E36">
+      <c r="E37">
         <v>0.05</v>
       </c>
-      <c r="F36" t="s">
-        <v>66</v>
-      </c>
-      <c r="G36">
+      <c r="F37" t="s">
+        <v>70</v>
+      </c>
+      <c r="G37">
         <v>576.4299999999999</v>
       </c>
-      <c r="H36">
+      <c r="H37">
         <v>0.15</v>
       </c>
-      <c r="I36">
+      <c r="I37">
         <v>0.04</v>
       </c>
-      <c r="J36" t="s">
-        <v>67</v>
-      </c>
-      <c r="K36">
+      <c r="J37" t="s">
+        <v>71</v>
+      </c>
+      <c r="K37">
         <v>576.4299999999999</v>
       </c>
-      <c r="L36">
+      <c r="L37">
         <v>0.15</v>
       </c>
-      <c r="M36">
+      <c r="M37">
         <v>0.04</v>
       </c>
-      <c r="N36" t="s">
-        <v>68</v>
-      </c>
-      <c r="O36">
+      <c r="N37" t="s">
+        <v>72</v>
+      </c>
+      <c r="O37">
         <v>612.14</v>
       </c>
-      <c r="P36">
+      <c r="P37">
         <v>0.14</v>
       </c>
-      <c r="Q36">
+      <c r="Q37">
         <v>0.03</v>
       </c>
-    </row>
-    <row r="37" spans="1:17">
-      <c r="A37" t="s">
-        <v>52</v>
-      </c>
-      <c r="B37" t="s">
-        <v>65</v>
-      </c>
-      <c r="C37">
-        <v>747.86</v>
-      </c>
-      <c r="D37">
-        <v>0.11</v>
-      </c>
-      <c r="E37">
+      <c r="R37" t="s">
+        <v>73</v>
+      </c>
+      <c r="S37">
+        <v>630.67</v>
+      </c>
+      <c r="T37">
+        <v>0.13</v>
+      </c>
+      <c r="U37">
         <v>0.03</v>
       </c>
-      <c r="F37" t="s">
-        <v>66</v>
-      </c>
-      <c r="G37">
-        <v>747.86</v>
-      </c>
-      <c r="H37">
-        <v>0.11</v>
-      </c>
-      <c r="I37">
-        <v>0.02</v>
-      </c>
-      <c r="J37" t="s">
-        <v>67</v>
-      </c>
-      <c r="K37">
-        <v>747.86</v>
-      </c>
-      <c r="L37">
-        <v>0.11</v>
-      </c>
-      <c r="M37">
-        <v>0.02</v>
-      </c>
-      <c r="N37" t="s">
-        <v>68</v>
-      </c>
-      <c r="O37">
-        <v>747.86</v>
-      </c>
-      <c r="P37">
-        <v>0.11</v>
-      </c>
-      <c r="Q37">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17">
+    </row>
+    <row r="38" spans="1:21">
       <c r="A38" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B38" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C38">
         <v>890.71</v>
@@ -2559,7 +3018,7 @@
         <v>0.02</v>
       </c>
       <c r="F38" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G38">
         <v>890.71</v>
@@ -2571,7 +3030,7 @@
         <v>0.02</v>
       </c>
       <c r="J38" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="K38">
         <v>890.71</v>
@@ -2583,7 +3042,7 @@
         <v>0.02</v>
       </c>
       <c r="N38" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="O38">
         <v>783.5700000000001</v>
@@ -2594,13 +3053,25 @@
       <c r="Q38">
         <v>0.02</v>
       </c>
-    </row>
-    <row r="39" spans="1:17">
+      <c r="R38" t="s">
+        <v>73</v>
+      </c>
+      <c r="S38">
+        <v>789</v>
+      </c>
+      <c r="T38">
+        <v>0.11</v>
+      </c>
+      <c r="U38">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21">
       <c r="A39" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B39" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C39">
         <v>1197.86</v>
@@ -2612,7 +3083,7 @@
         <v>0.01</v>
       </c>
       <c r="F39" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G39">
         <v>1197.86</v>
@@ -2624,7 +3095,7 @@
         <v>0.01</v>
       </c>
       <c r="J39" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="K39">
         <v>1197.86</v>
@@ -2636,7 +3107,7 @@
         <v>0.01</v>
       </c>
       <c r="N39" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="O39">
         <v>819.29</v>
@@ -2647,13 +3118,25 @@
       <c r="Q39">
         <v>0.02</v>
       </c>
-    </row>
-    <row r="40" spans="1:17">
+      <c r="R39" t="s">
+        <v>73</v>
+      </c>
+      <c r="S39">
+        <v>872.33</v>
+      </c>
+      <c r="T39">
+        <v>0.1</v>
+      </c>
+      <c r="U39">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="40" spans="1:21">
       <c r="A40" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B40" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C40">
         <v>605</v>
@@ -2665,7 +3148,7 @@
         <v>0.04</v>
       </c>
       <c r="F40" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G40">
         <v>640.71</v>
@@ -2677,7 +3160,7 @@
         <v>0.03</v>
       </c>
       <c r="J40" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="K40">
         <v>890.71</v>
@@ -2689,7 +3172,7 @@
         <v>0.02</v>
       </c>
       <c r="N40" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="O40">
         <v>926.4299999999999</v>
@@ -2700,13 +3183,25 @@
       <c r="Q40">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="41" spans="1:17">
+      <c r="R40" t="s">
+        <v>73</v>
+      </c>
+      <c r="S40">
+        <v>955.67</v>
+      </c>
+      <c r="T40">
+        <v>0.09</v>
+      </c>
+      <c r="U40">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="41" spans="1:21">
       <c r="A41" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B41" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C41">
         <v>1326.43</v>
@@ -2718,7 +3213,7 @@
         <v>0.01</v>
       </c>
       <c r="F41" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G41">
         <v>1326.43</v>
@@ -2730,7 +3225,7 @@
         <v>0.01</v>
       </c>
       <c r="J41" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="K41">
         <v>1326.43</v>
@@ -2742,7 +3237,7 @@
         <v>0.01</v>
       </c>
       <c r="N41" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="O41">
         <v>1069.29</v>
@@ -2753,81 +3248,105 @@
       <c r="Q41">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="42" spans="1:17">
+      <c r="R41" t="s">
+        <v>73</v>
+      </c>
+      <c r="S41">
+        <v>996.6</v>
+      </c>
+      <c r="T41">
+        <v>0.08</v>
+      </c>
+      <c r="U41">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="42" spans="1:21">
       <c r="A42" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B42" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C42">
-        <v>1069.29</v>
+        <v>890.71</v>
       </c>
       <c r="D42">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="E42">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F42" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G42">
-        <v>1069.29</v>
+        <v>1176.43</v>
       </c>
       <c r="H42">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I42">
         <v>0.01</v>
       </c>
       <c r="J42" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="K42">
-        <v>1069.29</v>
+        <v>1176.43</v>
       </c>
       <c r="L42">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="M42">
         <v>0.01</v>
       </c>
       <c r="N42" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="O42">
-        <v>1069.29</v>
+        <v>1176.43</v>
       </c>
       <c r="P42">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Q42">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="43" spans="1:17">
+      <c r="R42" t="s">
+        <v>73</v>
+      </c>
+      <c r="S42">
+        <v>1205.67</v>
+      </c>
+      <c r="T42">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="U42">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="43" spans="1:21">
       <c r="A43" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B43" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C43">
-        <v>890.71</v>
+        <v>1197.86</v>
       </c>
       <c r="D43">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E43">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F43" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G43">
-        <v>1176.43</v>
+        <v>1197.86</v>
       </c>
       <c r="H43">
         <v>0.07000000000000001</v>
@@ -2836,10 +3355,10 @@
         <v>0.01</v>
       </c>
       <c r="J43" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="K43">
-        <v>1176.43</v>
+        <v>1197.86</v>
       </c>
       <c r="L43">
         <v>0.07000000000000001</v>
@@ -2848,10 +3367,10 @@
         <v>0.01</v>
       </c>
       <c r="N43" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="O43">
-        <v>1176.43</v>
+        <v>1197.86</v>
       </c>
       <c r="P43">
         <v>0.07000000000000001</v>
@@ -2859,13 +3378,25 @@
       <c r="Q43">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="44" spans="1:17">
+      <c r="R43" t="s">
+        <v>73</v>
+      </c>
+      <c r="S43">
+        <v>1247.33</v>
+      </c>
+      <c r="T43">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="U43">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="44" spans="1:21">
       <c r="A44" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B44" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C44">
         <v>1126.43</v>
@@ -2877,7 +3408,7 @@
         <v>0.01</v>
       </c>
       <c r="F44" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G44">
         <v>1126.43</v>
@@ -2889,7 +3420,7 @@
         <v>0.01</v>
       </c>
       <c r="J44" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="K44">
         <v>1126.43</v>
@@ -2901,7 +3432,7 @@
         <v>0.01</v>
       </c>
       <c r="N44" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="O44">
         <v>1197.86</v>
@@ -2912,13 +3443,25 @@
       <c r="Q44">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="45" spans="1:17">
+      <c r="R44" t="s">
+        <v>73</v>
+      </c>
+      <c r="S44">
+        <v>1296.6</v>
+      </c>
+      <c r="T44">
+        <v>0.06</v>
+      </c>
+      <c r="U44">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="45" spans="1:21">
       <c r="A45" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B45" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C45">
         <v>1197.86</v>
@@ -2930,7 +3473,7 @@
         <v>0.01</v>
       </c>
       <c r="F45" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G45">
         <v>1197.86</v>
@@ -2942,7 +3485,7 @@
         <v>0.01</v>
       </c>
       <c r="J45" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="K45">
         <v>1197.86</v>
@@ -2954,7 +3497,7 @@
         <v>0.01</v>
       </c>
       <c r="N45" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="O45">
         <v>1197.86</v>
@@ -2965,66 +3508,90 @@
       <c r="Q45">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="46" spans="1:17">
+      <c r="R45" t="s">
+        <v>73</v>
+      </c>
+      <c r="S45">
+        <v>1296.6</v>
+      </c>
+      <c r="T45">
+        <v>0.06</v>
+      </c>
+      <c r="U45">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="46" spans="1:21">
       <c r="A46" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B46" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C46">
-        <v>1197.86</v>
+        <v>1069.29</v>
       </c>
       <c r="D46">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="E46">
         <v>0.01</v>
       </c>
       <c r="F46" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G46">
-        <v>1197.86</v>
+        <v>1069.29</v>
       </c>
       <c r="H46">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="I46">
         <v>0.01</v>
       </c>
       <c r="J46" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="K46">
-        <v>1197.86</v>
+        <v>1069.29</v>
       </c>
       <c r="L46">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="M46">
         <v>0.01</v>
       </c>
       <c r="N46" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="O46">
-        <v>1197.86</v>
+        <v>1069.29</v>
       </c>
       <c r="P46">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="Q46">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="47" spans="1:17">
+      <c r="R46" t="s">
+        <v>73</v>
+      </c>
+      <c r="S46">
+        <v>1372.33</v>
+      </c>
+      <c r="T46">
+        <v>0.06</v>
+      </c>
+      <c r="U46">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="47" spans="1:21">
       <c r="A47" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B47" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C47">
         <v>1497.86</v>
@@ -3036,7 +3603,7 @@
         <v>0.01</v>
       </c>
       <c r="F47" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G47">
         <v>1497.86</v>
@@ -3048,7 +3615,7 @@
         <v>0.01</v>
       </c>
       <c r="J47" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="K47">
         <v>1497.86</v>
@@ -3060,7 +3627,7 @@
         <v>0.01</v>
       </c>
       <c r="N47" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="O47">
         <v>1497.86</v>
@@ -3071,13 +3638,25 @@
       <c r="Q47">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="48" spans="1:17">
+      <c r="R47" t="s">
+        <v>73</v>
+      </c>
+      <c r="S47">
+        <v>1696.6</v>
+      </c>
+      <c r="T47">
+        <v>0.05</v>
+      </c>
+      <c r="U47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:21">
       <c r="A48" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B48" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C48">
         <v>1926.43</v>
@@ -3089,7 +3668,7 @@
         <v>0</v>
       </c>
       <c r="F48" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G48">
         <v>1926.43</v>
@@ -3101,7 +3680,7 @@
         <v>0</v>
       </c>
       <c r="J48" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="K48">
         <v>2033.57</v>
@@ -3113,7 +3692,7 @@
         <v>0</v>
       </c>
       <c r="N48" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="O48">
         <v>2033.57</v>
@@ -3124,13 +3703,25 @@
       <c r="Q48">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:17">
+      <c r="R48" t="s">
+        <v>73</v>
+      </c>
+      <c r="S48">
+        <v>2296.6</v>
+      </c>
+      <c r="T48">
+        <v>0.04</v>
+      </c>
+      <c r="U48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:21">
       <c r="A49" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B49" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C49">
         <v>1926.43</v>
@@ -3142,7 +3733,7 @@
         <v>0</v>
       </c>
       <c r="F49" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G49">
         <v>1926.43</v>
@@ -3154,7 +3745,7 @@
         <v>0</v>
       </c>
       <c r="J49" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="K49">
         <v>2355</v>
@@ -3166,7 +3757,7 @@
         <v>0</v>
       </c>
       <c r="N49" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="O49">
         <v>2355</v>
@@ -3175,6 +3766,18 @@
         <v>0.04</v>
       </c>
       <c r="Q49">
+        <v>0</v>
+      </c>
+      <c r="R49" t="s">
+        <v>73</v>
+      </c>
+      <c r="S49">
+        <v>2596.6</v>
+      </c>
+      <c r="T49">
+        <v>0.03</v>
+      </c>
+      <c r="U49">
         <v>0</v>
       </c>
     </row>

--- a/processed_data_during_wm/processed_data_wide.xlsx
+++ b/processed_data_during_wm/processed_data_wide.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="76">
   <si>
     <t>Team</t>
   </si>
@@ -79,6 +79,18 @@
     <t>Shin_Wahrscheinlichkeit_in_Prozent_5</t>
   </si>
   <si>
+    <t>Datum_6</t>
+  </si>
+  <si>
+    <t>Durchsch_Quote_6</t>
+  </si>
+  <si>
+    <t>Norm_Wahrscheinlichkeit_in_Prozent_6</t>
+  </si>
+  <si>
+    <t>Shin_Wahrscheinlichkeit_in_Prozent_6</t>
+  </si>
+  <si>
     <t>Frankreich</t>
   </si>
   <si>
@@ -103,67 +115,67 @@
     <t>Niederlande</t>
   </si>
   <si>
+    <t>USA</t>
+  </si>
+  <si>
+    <t>Marokko</t>
+  </si>
+  <si>
     <t>Norwegen</t>
   </si>
   <si>
-    <t>Marokko</t>
-  </si>
-  <si>
-    <t>USA</t>
+    <t>Japan</t>
   </si>
   <si>
     <t>Belgien</t>
   </si>
   <si>
+    <t>Kolumbien</t>
+  </si>
+  <si>
     <t>Mexiko</t>
   </si>
   <si>
-    <t>Kolumbien</t>
-  </si>
-  <si>
-    <t>Japan</t>
-  </si>
-  <si>
     <t>Schweiz</t>
   </si>
   <si>
+    <t>Kroatien</t>
+  </si>
+  <si>
+    <t>Senegal</t>
+  </si>
+  <si>
+    <t>Elfenbeinküste</t>
+  </si>
+  <si>
+    <t>Österreich</t>
+  </si>
+  <si>
+    <t>Kanada</t>
+  </si>
+  <si>
     <t>Uruguay</t>
   </si>
   <si>
     <t>Schweden</t>
   </si>
   <si>
-    <t>Kroatien</t>
-  </si>
-  <si>
-    <t>Senegal</t>
-  </si>
-  <si>
     <t>Australien</t>
   </si>
   <si>
-    <t>Österreich</t>
-  </si>
-  <si>
-    <t>Elfenbeinküste</t>
-  </si>
-  <si>
-    <t>Kanada</t>
+    <t>Ägypten</t>
   </si>
   <si>
     <t>Ecuador</t>
   </si>
   <si>
-    <t>Türkei</t>
+    <t>Südkorea</t>
   </si>
   <si>
     <t>Schottland</t>
   </si>
   <si>
-    <t>Südkorea</t>
-  </si>
-  <si>
-    <t>Ägypten</t>
+    <t>Paraguay</t>
   </si>
   <si>
     <t>Ghana</t>
@@ -172,9 +184,6 @@
     <t>Bosnien Herzegowina</t>
   </si>
   <si>
-    <t>Paraguay</t>
-  </si>
-  <si>
     <t>Algerien</t>
   </si>
   <si>
@@ -187,39 +196,33 @@
     <t>Iran</t>
   </si>
   <si>
+    <t>Kap Verde</t>
+  </si>
+  <si>
     <t>Saudi Arabien</t>
   </si>
   <si>
     <t>Neuseeland</t>
   </si>
   <si>
-    <t>Tunesien</t>
-  </si>
-  <si>
-    <t>Kap Verde</t>
+    <t>Panama</t>
+  </si>
+  <si>
+    <t>Irak</t>
   </si>
   <si>
     <t>Südafrika</t>
   </si>
   <si>
-    <t>Panama</t>
-  </si>
-  <si>
-    <t>Irak</t>
-  </si>
-  <si>
     <t>Usbekistan</t>
   </si>
   <si>
+    <t>Jordanien</t>
+  </si>
+  <si>
     <t>Katar</t>
   </si>
   <si>
-    <t>Jordanien</t>
-  </si>
-  <si>
-    <t>Haiti</t>
-  </si>
-  <si>
     <t>Curacao</t>
   </si>
   <si>
@@ -236,6 +239,9 @@
   </si>
   <si>
     <t>19.06.2026</t>
+  </si>
+  <si>
+    <t>22.06.2026</t>
   </si>
 </sst>
 </file>
@@ -593,10 +599,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U49"/>
+  <dimension ref="A1:Y46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:21">
+    <row r="1" spans="1:25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -660,13 +666,25 @@
       <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="2" spans="1:21">
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C2">
         <v>6.01</v>
@@ -678,7 +696,7 @@
         <v>15.09</v>
       </c>
       <c r="F2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G2">
         <v>5.55</v>
@@ -690,7 +708,7 @@
         <v>16.26</v>
       </c>
       <c r="J2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K2">
         <v>5.55</v>
@@ -702,7 +720,7 @@
         <v>16.3</v>
       </c>
       <c r="N2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O2">
         <v>4.97</v>
@@ -714,7 +732,7 @@
         <v>18.14</v>
       </c>
       <c r="R2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="S2">
         <v>4.82</v>
@@ -725,13 +743,25 @@
       <c r="U2">
         <v>18.8</v>
       </c>
-    </row>
-    <row r="3" spans="1:21">
+      <c r="V2" t="s">
+        <v>75</v>
+      </c>
+      <c r="W2">
+        <v>4.87</v>
+      </c>
+      <c r="X2">
+        <v>17.32</v>
+      </c>
+      <c r="Y2">
+        <v>18.6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25">
       <c r="A3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C3">
         <v>5.58</v>
@@ -743,7 +773,7 @@
         <v>16.29</v>
       </c>
       <c r="F3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G3">
         <v>5.63</v>
@@ -755,7 +785,7 @@
         <v>16.04</v>
       </c>
       <c r="J3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K3">
         <v>5.63</v>
@@ -767,7 +797,7 @@
         <v>16.07</v>
       </c>
       <c r="N3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O3">
         <v>6.51</v>
@@ -779,7 +809,7 @@
         <v>13.76</v>
       </c>
       <c r="R3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="S3">
         <v>6.88</v>
@@ -790,13 +820,25 @@
       <c r="U3">
         <v>13.09</v>
       </c>
-    </row>
-    <row r="4" spans="1:21">
+      <c r="V3" t="s">
+        <v>75</v>
+      </c>
+      <c r="W3">
+        <v>6.34</v>
+      </c>
+      <c r="X3">
+        <v>13.32</v>
+      </c>
+      <c r="Y3">
+        <v>14.23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C4">
         <v>8.15</v>
@@ -808,7 +850,7 @@
         <v>11.06</v>
       </c>
       <c r="F4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G4">
         <v>8.42</v>
@@ -820,7 +862,7 @@
         <v>10.62</v>
       </c>
       <c r="J4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K4">
         <v>8.390000000000001</v>
@@ -832,7 +874,7 @@
         <v>10.69</v>
       </c>
       <c r="N4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O4">
         <v>8.33</v>
@@ -844,7 +886,7 @@
         <v>10.68</v>
       </c>
       <c r="R4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="S4">
         <v>7.04</v>
@@ -855,13 +897,25 @@
       <c r="U4">
         <v>12.77</v>
       </c>
-    </row>
-    <row r="5" spans="1:21">
+      <c r="V4" t="s">
+        <v>75</v>
+      </c>
+      <c r="W4">
+        <v>7.11</v>
+      </c>
+      <c r="X4">
+        <v>11.88</v>
+      </c>
+      <c r="Y4">
+        <v>12.65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C5">
         <v>10.19</v>
@@ -873,7 +927,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="F5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G5">
         <v>10.33</v>
@@ -885,7 +939,7 @@
         <v>8.6</v>
       </c>
       <c r="J5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K5">
         <v>10.61</v>
@@ -897,7 +951,7 @@
         <v>8.390000000000001</v>
       </c>
       <c r="N5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O5">
         <v>9.4</v>
@@ -909,7 +963,7 @@
         <v>9.44</v>
       </c>
       <c r="R5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="S5">
         <v>9.140000000000001</v>
@@ -920,13 +974,25 @@
       <c r="U5">
         <v>9.779999999999999</v>
       </c>
-    </row>
-    <row r="6" spans="1:21">
+      <c r="V5" t="s">
+        <v>75</v>
+      </c>
+      <c r="W5">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="X5">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="Y5">
+        <v>10.27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C6">
         <v>8.85</v>
@@ -938,7 +1004,7 @@
         <v>10.17</v>
       </c>
       <c r="F6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G6">
         <v>8.699999999999999</v>
@@ -950,7 +1016,7 @@
         <v>10.26</v>
       </c>
       <c r="J6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K6">
         <v>8.630000000000001</v>
@@ -962,7 +1028,7 @@
         <v>10.38</v>
       </c>
       <c r="N6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O6">
         <v>8.619999999999999</v>
@@ -974,7 +1040,7 @@
         <v>10.32</v>
       </c>
       <c r="R6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="S6">
         <v>10.63</v>
@@ -985,13 +1051,25 @@
       <c r="U6">
         <v>8.359999999999999</v>
       </c>
-    </row>
-    <row r="7" spans="1:21">
+      <c r="V6" t="s">
+        <v>75</v>
+      </c>
+      <c r="W6">
+        <v>11.67</v>
+      </c>
+      <c r="X6">
+        <v>7.23</v>
+      </c>
+      <c r="Y6">
+        <v>7.59</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25">
       <c r="A7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C7">
         <v>9.970000000000001</v>
@@ -1003,7 +1081,7 @@
         <v>8.99</v>
       </c>
       <c r="F7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G7">
         <v>10.11</v>
@@ -1015,7 +1093,7 @@
         <v>8.789999999999999</v>
       </c>
       <c r="J7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K7">
         <v>11.04</v>
@@ -1027,7 +1105,7 @@
         <v>8.050000000000001</v>
       </c>
       <c r="N7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O7">
         <v>11.39</v>
@@ -1039,7 +1117,7 @@
         <v>7.74</v>
       </c>
       <c r="R7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="S7">
         <v>12.2</v>
@@ -1050,13 +1128,25 @@
       <c r="U7">
         <v>7.25</v>
       </c>
-    </row>
-    <row r="8" spans="1:21">
+      <c r="V7" t="s">
+        <v>75</v>
+      </c>
+      <c r="W7">
+        <v>13.17</v>
+      </c>
+      <c r="X7">
+        <v>6.41</v>
+      </c>
+      <c r="Y7">
+        <v>6.69</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25">
       <c r="A8" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C8">
         <v>15.6</v>
@@ -1068,7 +1158,7 @@
         <v>5.65</v>
       </c>
       <c r="F8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G8">
         <v>15.67</v>
@@ -1080,7 +1170,7 @@
         <v>5.57</v>
       </c>
       <c r="J8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K8">
         <v>15.39</v>
@@ -1092,7 +1182,7 @@
         <v>5.7</v>
       </c>
       <c r="N8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O8">
         <v>14.67</v>
@@ -1104,7 +1194,7 @@
         <v>5.93</v>
       </c>
       <c r="R8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="S8">
         <v>14.87</v>
@@ -1115,13 +1205,25 @@
       <c r="U8">
         <v>5.9</v>
       </c>
-    </row>
-    <row r="9" spans="1:21">
+      <c r="V8" t="s">
+        <v>75</v>
+      </c>
+      <c r="W8">
+        <v>14.53</v>
+      </c>
+      <c r="X8">
+        <v>5.81</v>
+      </c>
+      <c r="Y8">
+        <v>6.03</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25">
       <c r="A9" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C9">
         <v>21.29</v>
@@ -1133,7 +1235,7 @@
         <v>4.07</v>
       </c>
       <c r="F9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G9">
         <v>20.29</v>
@@ -1145,7 +1247,7 @@
         <v>4.24</v>
       </c>
       <c r="J9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K9">
         <v>19.71</v>
@@ -1157,7 +1259,7 @@
         <v>4.38</v>
       </c>
       <c r="N9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O9">
         <v>20.14</v>
@@ -1169,7 +1271,7 @@
         <v>4.24</v>
       </c>
       <c r="R9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="S9">
         <v>21</v>
@@ -1180,78 +1282,102 @@
       <c r="U9">
         <v>4.09</v>
       </c>
-    </row>
-    <row r="10" spans="1:21">
+      <c r="V9" t="s">
+        <v>75</v>
+      </c>
+      <c r="W9">
+        <v>17.53</v>
+      </c>
+      <c r="X9">
+        <v>4.82</v>
+      </c>
+      <c r="Y9">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25">
       <c r="A10" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C10">
-        <v>32.29</v>
+        <v>63.71</v>
       </c>
       <c r="D10">
+        <v>1.33</v>
+      </c>
+      <c r="E10">
+        <v>1.2</v>
+      </c>
+      <c r="F10" t="s">
+        <v>71</v>
+      </c>
+      <c r="G10">
+        <v>44.57</v>
+      </c>
+      <c r="H10">
+        <v>1.89</v>
+      </c>
+      <c r="I10">
+        <v>1.78</v>
+      </c>
+      <c r="J10" t="s">
+        <v>72</v>
+      </c>
+      <c r="K10">
+        <v>43.86</v>
+      </c>
+      <c r="L10">
+        <v>1.92</v>
+      </c>
+      <c r="M10">
+        <v>1.82</v>
+      </c>
+      <c r="N10" t="s">
+        <v>73</v>
+      </c>
+      <c r="O10">
+        <v>41.14</v>
+      </c>
+      <c r="P10">
+        <v>2.03</v>
+      </c>
+      <c r="Q10">
+        <v>1.93</v>
+      </c>
+      <c r="R10" t="s">
+        <v>74</v>
+      </c>
+      <c r="S10">
+        <v>42</v>
+      </c>
+      <c r="T10">
+        <v>2.01</v>
+      </c>
+      <c r="U10">
+        <v>1.91</v>
+      </c>
+      <c r="V10" t="s">
+        <v>75</v>
+      </c>
+      <c r="W10">
+        <v>31.43</v>
+      </c>
+      <c r="X10">
+        <v>2.69</v>
+      </c>
+      <c r="Y10">
         <v>2.63</v>
       </c>
-      <c r="E10">
-        <v>2.6</v>
-      </c>
-      <c r="F10" t="s">
-        <v>70</v>
-      </c>
-      <c r="G10">
-        <v>33</v>
-      </c>
-      <c r="H10">
-        <v>2.55</v>
-      </c>
-      <c r="I10">
-        <v>2.49</v>
-      </c>
-      <c r="J10" t="s">
-        <v>71</v>
-      </c>
-      <c r="K10">
-        <v>34.14</v>
-      </c>
-      <c r="L10">
-        <v>2.47</v>
-      </c>
-      <c r="M10">
-        <v>2.42</v>
-      </c>
-      <c r="N10" t="s">
-        <v>72</v>
-      </c>
-      <c r="O10">
-        <v>30.43</v>
-      </c>
-      <c r="P10">
-        <v>2.74</v>
-      </c>
-      <c r="Q10">
-        <v>2.71</v>
-      </c>
-      <c r="R10" t="s">
-        <v>73</v>
-      </c>
-      <c r="S10">
-        <v>31.5</v>
-      </c>
-      <c r="T10">
-        <v>2.67</v>
-      </c>
-      <c r="U10">
-        <v>2.64</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21">
+    </row>
+    <row r="11" spans="1:25">
       <c r="A11" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C11">
         <v>49.86</v>
@@ -1263,7 +1389,7 @@
         <v>1.59</v>
       </c>
       <c r="F11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G11">
         <v>50.57</v>
@@ -1275,7 +1401,7 @@
         <v>1.54</v>
       </c>
       <c r="J11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K11">
         <v>38.71</v>
@@ -1287,7 +1413,7 @@
         <v>2.1</v>
       </c>
       <c r="N11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O11">
         <v>37.71</v>
@@ -1299,7 +1425,7 @@
         <v>2.13</v>
       </c>
       <c r="R11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="S11">
         <v>40.67</v>
@@ -1310,208 +1436,256 @@
       <c r="U11">
         <v>1.98</v>
       </c>
-    </row>
-    <row r="12" spans="1:21">
+      <c r="V11" t="s">
+        <v>75</v>
+      </c>
+      <c r="W11">
+        <v>32.86</v>
+      </c>
+      <c r="X11">
+        <v>2.57</v>
+      </c>
+      <c r="Y11">
+        <v>2.51</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25">
       <c r="A12" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C12">
-        <v>63.71</v>
+        <v>32.29</v>
       </c>
       <c r="D12">
-        <v>1.33</v>
+        <v>2.63</v>
       </c>
       <c r="E12">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="F12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G12">
-        <v>44.57</v>
+        <v>33</v>
       </c>
       <c r="H12">
-        <v>1.89</v>
+        <v>2.55</v>
       </c>
       <c r="I12">
-        <v>1.78</v>
+        <v>2.49</v>
       </c>
       <c r="J12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K12">
-        <v>43.86</v>
+        <v>34.14</v>
       </c>
       <c r="L12">
-        <v>1.92</v>
+        <v>2.47</v>
       </c>
       <c r="M12">
-        <v>1.82</v>
+        <v>2.42</v>
       </c>
       <c r="N12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O12">
-        <v>41.14</v>
+        <v>30.43</v>
       </c>
       <c r="P12">
-        <v>2.03</v>
+        <v>2.74</v>
       </c>
       <c r="Q12">
-        <v>1.93</v>
+        <v>2.71</v>
       </c>
       <c r="R12" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="S12">
+        <v>31.5</v>
+      </c>
+      <c r="T12">
+        <v>2.67</v>
+      </c>
+      <c r="U12">
+        <v>2.64</v>
+      </c>
+      <c r="V12" t="s">
+        <v>75</v>
+      </c>
+      <c r="W12">
+        <v>36.57</v>
+      </c>
+      <c r="X12">
+        <v>2.31</v>
+      </c>
+      <c r="Y12">
+        <v>2.22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25">
+      <c r="A13" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C13">
+        <v>53.43</v>
+      </c>
+      <c r="D13">
+        <v>1.59</v>
+      </c>
+      <c r="E13">
+        <v>1.47</v>
+      </c>
+      <c r="F13" t="s">
+        <v>71</v>
+      </c>
+      <c r="G13">
+        <v>53.43</v>
+      </c>
+      <c r="H13">
+        <v>1.57</v>
+      </c>
+      <c r="I13">
+        <v>1.44</v>
+      </c>
+      <c r="J13" t="s">
+        <v>72</v>
+      </c>
+      <c r="K13">
+        <v>51.29</v>
+      </c>
+      <c r="L13">
+        <v>1.64</v>
+      </c>
+      <c r="M13">
+        <v>1.52</v>
+      </c>
+      <c r="N13" t="s">
+        <v>73</v>
+      </c>
+      <c r="O13">
+        <v>51.29</v>
+      </c>
+      <c r="P13">
+        <v>1.63</v>
+      </c>
+      <c r="Q13">
+        <v>1.49</v>
+      </c>
+      <c r="R13" t="s">
+        <v>74</v>
+      </c>
+      <c r="S13">
+        <v>53</v>
+      </c>
+      <c r="T13">
+        <v>1.59</v>
+      </c>
+      <c r="U13">
+        <v>1.46</v>
+      </c>
+      <c r="V13" t="s">
+        <v>75</v>
+      </c>
+      <c r="W13">
+        <v>42.86</v>
+      </c>
+      <c r="X13">
+        <v>1.97</v>
+      </c>
+      <c r="Y13">
+        <v>1.86</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25">
+      <c r="A14" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14">
+        <v>37.71</v>
+      </c>
+      <c r="D14">
+        <v>2.25</v>
+      </c>
+      <c r="E14">
+        <v>2.19</v>
+      </c>
+      <c r="F14" t="s">
+        <v>71</v>
+      </c>
+      <c r="G14">
+        <v>37.71</v>
+      </c>
+      <c r="H14">
+        <v>2.23</v>
+      </c>
+      <c r="I14">
+        <v>2.15</v>
+      </c>
+      <c r="J14" t="s">
+        <v>72</v>
+      </c>
+      <c r="K14">
+        <v>39.43</v>
+      </c>
+      <c r="L14">
+        <v>2.14</v>
+      </c>
+      <c r="M14">
+        <v>2.06</v>
+      </c>
+      <c r="N14" t="s">
+        <v>73</v>
+      </c>
+      <c r="O14">
         <v>42</v>
       </c>
-      <c r="T12">
-        <v>2.01</v>
-      </c>
-      <c r="U12">
-        <v>1.91</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21">
-      <c r="A13" t="s">
-        <v>32</v>
-      </c>
-      <c r="B13" t="s">
-        <v>69</v>
-      </c>
-      <c r="C13">
-        <v>37.71</v>
-      </c>
-      <c r="D13">
-        <v>2.25</v>
-      </c>
-      <c r="E13">
-        <v>2.19</v>
-      </c>
-      <c r="F13" t="s">
-        <v>70</v>
-      </c>
-      <c r="G13">
-        <v>37.71</v>
-      </c>
-      <c r="H13">
-        <v>2.23</v>
-      </c>
-      <c r="I13">
-        <v>2.15</v>
-      </c>
-      <c r="J13" t="s">
-        <v>71</v>
-      </c>
-      <c r="K13">
-        <v>39.43</v>
-      </c>
-      <c r="L13">
-        <v>2.14</v>
-      </c>
-      <c r="M13">
-        <v>2.06</v>
-      </c>
-      <c r="N13" t="s">
-        <v>72</v>
-      </c>
-      <c r="O13">
-        <v>42</v>
-      </c>
-      <c r="P13">
+      <c r="P14">
         <v>1.99</v>
       </c>
-      <c r="Q13">
+      <c r="Q14">
         <v>1.88</v>
       </c>
-      <c r="R13" t="s">
-        <v>73</v>
-      </c>
-      <c r="S13">
+      <c r="R14" t="s">
+        <v>74</v>
+      </c>
+      <c r="S14">
         <v>42.17</v>
       </c>
-      <c r="T13">
+      <c r="T14">
         <v>2</v>
       </c>
-      <c r="U13">
+      <c r="U14">
         <v>1.9</v>
       </c>
-    </row>
-    <row r="14" spans="1:21">
-      <c r="A14" t="s">
-        <v>33</v>
-      </c>
-      <c r="B14" t="s">
-        <v>69</v>
-      </c>
-      <c r="C14">
-        <v>68.43000000000001</v>
-      </c>
-      <c r="D14">
-        <v>1.24</v>
-      </c>
-      <c r="E14">
-        <v>1.1</v>
-      </c>
-      <c r="F14" t="s">
-        <v>70</v>
-      </c>
-      <c r="G14">
-        <v>52.71</v>
-      </c>
-      <c r="H14">
-        <v>1.6</v>
-      </c>
-      <c r="I14">
-        <v>1.46</v>
-      </c>
-      <c r="J14" t="s">
-        <v>71</v>
-      </c>
-      <c r="K14">
-        <v>52.71</v>
-      </c>
-      <c r="L14">
-        <v>1.6</v>
-      </c>
-      <c r="M14">
-        <v>1.47</v>
-      </c>
-      <c r="N14" t="s">
-        <v>72</v>
-      </c>
-      <c r="O14">
-        <v>57.86</v>
-      </c>
-      <c r="P14">
-        <v>1.44</v>
-      </c>
-      <c r="Q14">
-        <v>1.29</v>
-      </c>
-      <c r="R14" t="s">
-        <v>73</v>
-      </c>
-      <c r="S14">
-        <v>47.17</v>
-      </c>
-      <c r="T14">
-        <v>1.79</v>
-      </c>
-      <c r="U14">
-        <v>1.67</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21">
+      <c r="V14" t="s">
+        <v>75</v>
+      </c>
+      <c r="W14">
+        <v>47.71</v>
+      </c>
+      <c r="X14">
+        <v>1.77</v>
+      </c>
+      <c r="Y14">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25">
       <c r="A15" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B15" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C15">
         <v>41.71</v>
@@ -1523,7 +1697,7 @@
         <v>1.95</v>
       </c>
       <c r="F15" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G15">
         <v>45.57</v>
@@ -1535,7 +1709,7 @@
         <v>1.73</v>
       </c>
       <c r="J15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K15">
         <v>47</v>
@@ -1547,7 +1721,7 @@
         <v>1.68</v>
       </c>
       <c r="N15" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O15">
         <v>50.43</v>
@@ -1559,7 +1733,7 @@
         <v>1.52</v>
       </c>
       <c r="R15" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="S15">
         <v>48</v>
@@ -1570,78 +1744,102 @@
       <c r="U15">
         <v>1.64</v>
       </c>
-    </row>
-    <row r="16" spans="1:21">
+      <c r="V15" t="s">
+        <v>75</v>
+      </c>
+      <c r="W15">
+        <v>49.86</v>
+      </c>
+      <c r="X15">
+        <v>1.69</v>
+      </c>
+      <c r="Y15">
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25">
       <c r="A16" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C16">
-        <v>53.43</v>
+        <v>68.43000000000001</v>
       </c>
       <c r="D16">
-        <v>1.59</v>
+        <v>1.24</v>
       </c>
       <c r="E16">
+        <v>1.1</v>
+      </c>
+      <c r="F16" t="s">
+        <v>71</v>
+      </c>
+      <c r="G16">
+        <v>52.71</v>
+      </c>
+      <c r="H16">
+        <v>1.6</v>
+      </c>
+      <c r="I16">
+        <v>1.46</v>
+      </c>
+      <c r="J16" t="s">
+        <v>72</v>
+      </c>
+      <c r="K16">
+        <v>52.71</v>
+      </c>
+      <c r="L16">
+        <v>1.6</v>
+      </c>
+      <c r="M16">
         <v>1.47</v>
       </c>
-      <c r="F16" t="s">
-        <v>70</v>
-      </c>
-      <c r="G16">
-        <v>53.43</v>
-      </c>
-      <c r="H16">
-        <v>1.57</v>
-      </c>
-      <c r="I16">
+      <c r="N16" t="s">
+        <v>73</v>
+      </c>
+      <c r="O16">
+        <v>57.86</v>
+      </c>
+      <c r="P16">
         <v>1.44</v>
       </c>
-      <c r="J16" t="s">
-        <v>71</v>
-      </c>
-      <c r="K16">
-        <v>51.29</v>
-      </c>
-      <c r="L16">
-        <v>1.64</v>
-      </c>
-      <c r="M16">
-        <v>1.52</v>
-      </c>
-      <c r="N16" t="s">
-        <v>72</v>
-      </c>
-      <c r="O16">
-        <v>51.29</v>
-      </c>
-      <c r="P16">
-        <v>1.63</v>
-      </c>
       <c r="Q16">
-        <v>1.49</v>
+        <v>1.29</v>
       </c>
       <c r="R16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="S16">
-        <v>53</v>
+        <v>47.17</v>
       </c>
       <c r="T16">
-        <v>1.59</v>
+        <v>1.79</v>
       </c>
       <c r="U16">
-        <v>1.46</v>
-      </c>
-    </row>
-    <row r="17" spans="1:21">
+        <v>1.67</v>
+      </c>
+      <c r="V16" t="s">
+        <v>75</v>
+      </c>
+      <c r="W16">
+        <v>51.14</v>
+      </c>
+      <c r="X16">
+        <v>1.65</v>
+      </c>
+      <c r="Y16">
+        <v>1.51</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25">
       <c r="A17" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B17" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C17">
         <v>74.43000000000001</v>
@@ -1653,7 +1851,7 @@
         <v>0.99</v>
       </c>
       <c r="F17" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G17">
         <v>75.14</v>
@@ -1665,7 +1863,7 @@
         <v>0.95</v>
       </c>
       <c r="J17" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K17">
         <v>83.56999999999999</v>
@@ -1677,7 +1875,7 @@
         <v>0.84</v>
       </c>
       <c r="N17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O17">
         <v>87.70999999999999</v>
@@ -1689,7 +1887,7 @@
         <v>0.77</v>
       </c>
       <c r="R17" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="S17">
         <v>78</v>
@@ -1700,678 +1898,810 @@
       <c r="U17">
         <v>0.92</v>
       </c>
-    </row>
-    <row r="18" spans="1:21">
+      <c r="V17" t="s">
+        <v>75</v>
+      </c>
+      <c r="W17">
+        <v>81.43000000000001</v>
+      </c>
+      <c r="X17">
+        <v>1.04</v>
+      </c>
+      <c r="Y17">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25">
       <c r="A18" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B18" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C18">
+        <v>88.86</v>
+      </c>
+      <c r="D18">
+        <v>0.96</v>
+      </c>
+      <c r="E18">
+        <v>0.8</v>
+      </c>
+      <c r="F18" t="s">
+        <v>71</v>
+      </c>
+      <c r="G18">
+        <v>91.70999999999999</v>
+      </c>
+      <c r="H18">
+        <v>0.92</v>
+      </c>
+      <c r="I18">
+        <v>0.74</v>
+      </c>
+      <c r="J18" t="s">
+        <v>72</v>
+      </c>
+      <c r="K18">
+        <v>91.70999999999999</v>
+      </c>
+      <c r="L18">
+        <v>0.92</v>
+      </c>
+      <c r="M18">
+        <v>0.75</v>
+      </c>
+      <c r="N18" t="s">
+        <v>73</v>
+      </c>
+      <c r="O18">
+        <v>92.43000000000001</v>
+      </c>
+      <c r="P18">
+        <v>0.9</v>
+      </c>
+      <c r="Q18">
+        <v>0.72</v>
+      </c>
+      <c r="R18" t="s">
+        <v>74</v>
+      </c>
+      <c r="S18">
+        <v>110.83</v>
+      </c>
+      <c r="T18">
+        <v>0.76</v>
+      </c>
+      <c r="U18">
+        <v>0.58</v>
+      </c>
+      <c r="V18" t="s">
+        <v>75</v>
+      </c>
+      <c r="W18">
+        <v>123</v>
+      </c>
+      <c r="X18">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="Y18">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25">
+      <c r="A19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" t="s">
+        <v>70</v>
+      </c>
+      <c r="C19">
+        <v>101.29</v>
+      </c>
+      <c r="D19">
+        <v>0.84</v>
+      </c>
+      <c r="E19">
+        <v>0.67</v>
+      </c>
+      <c r="F19" t="s">
+        <v>71</v>
+      </c>
+      <c r="G19">
+        <v>106.14</v>
+      </c>
+      <c r="H19">
+        <v>0.79</v>
+      </c>
+      <c r="I19">
+        <v>0.61</v>
+      </c>
+      <c r="J19" t="s">
+        <v>72</v>
+      </c>
+      <c r="K19">
+        <v>107.57</v>
+      </c>
+      <c r="L19">
+        <v>0.78</v>
+      </c>
+      <c r="M19">
+        <v>0.61</v>
+      </c>
+      <c r="N19" t="s">
+        <v>73</v>
+      </c>
+      <c r="O19">
+        <v>119.57</v>
+      </c>
+      <c r="P19">
+        <v>0.7</v>
+      </c>
+      <c r="Q19">
+        <v>0.51</v>
+      </c>
+      <c r="R19" t="s">
+        <v>74</v>
+      </c>
+      <c r="S19">
+        <v>115.17</v>
+      </c>
+      <c r="T19">
+        <v>0.73</v>
+      </c>
+      <c r="U19">
+        <v>0.55</v>
+      </c>
+      <c r="V19" t="s">
+        <v>75</v>
+      </c>
+      <c r="W19">
+        <v>125.86</v>
+      </c>
+      <c r="X19">
+        <v>0.67</v>
+      </c>
+      <c r="Y19">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25">
+      <c r="A20" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" t="s">
+        <v>70</v>
+      </c>
+      <c r="C20">
+        <v>250</v>
+      </c>
+      <c r="D20">
+        <v>0.34</v>
+      </c>
+      <c r="E20">
+        <v>0.18</v>
+      </c>
+      <c r="F20" t="s">
+        <v>71</v>
+      </c>
+      <c r="G20">
+        <v>259.86</v>
+      </c>
+      <c r="H20">
+        <v>0.32</v>
+      </c>
+      <c r="I20">
+        <v>0.16</v>
+      </c>
+      <c r="J20" t="s">
+        <v>72</v>
+      </c>
+      <c r="K20">
+        <v>153</v>
+      </c>
+      <c r="L20">
+        <v>0.55</v>
+      </c>
+      <c r="M20">
+        <v>0.37</v>
+      </c>
+      <c r="N20" t="s">
+        <v>73</v>
+      </c>
+      <c r="O20">
+        <v>143</v>
+      </c>
+      <c r="P20">
+        <v>0.58</v>
+      </c>
+      <c r="Q20">
+        <v>0.4</v>
+      </c>
+      <c r="R20" t="s">
+        <v>74</v>
+      </c>
+      <c r="S20">
+        <v>144.83</v>
+      </c>
+      <c r="T20">
+        <v>0.58</v>
+      </c>
+      <c r="U20">
+        <v>0.4</v>
+      </c>
+      <c r="V20" t="s">
+        <v>75</v>
+      </c>
+      <c r="W20">
+        <v>133.71</v>
+      </c>
+      <c r="X20">
+        <v>0.63</v>
+      </c>
+      <c r="Y20">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25">
+      <c r="A21" t="s">
+        <v>44</v>
+      </c>
+      <c r="B21" t="s">
+        <v>70</v>
+      </c>
+      <c r="C21">
+        <v>153</v>
+      </c>
+      <c r="D21">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E21">
+        <v>0.39</v>
+      </c>
+      <c r="F21" t="s">
+        <v>71</v>
+      </c>
+      <c r="G21">
+        <v>158.57</v>
+      </c>
+      <c r="H21">
+        <v>0.53</v>
+      </c>
+      <c r="I21">
+        <v>0.35</v>
+      </c>
+      <c r="J21" t="s">
+        <v>72</v>
+      </c>
+      <c r="K21">
+        <v>157.14</v>
+      </c>
+      <c r="L21">
+        <v>0.54</v>
+      </c>
+      <c r="M21">
+        <v>0.36</v>
+      </c>
+      <c r="N21" t="s">
+        <v>73</v>
+      </c>
+      <c r="O21">
+        <v>135.14</v>
+      </c>
+      <c r="P21">
+        <v>0.62</v>
+      </c>
+      <c r="Q21">
+        <v>0.43</v>
+      </c>
+      <c r="R21" t="s">
+        <v>74</v>
+      </c>
+      <c r="S21">
+        <v>144</v>
+      </c>
+      <c r="T21">
+        <v>0.59</v>
+      </c>
+      <c r="U21">
+        <v>0.4</v>
+      </c>
+      <c r="V21" t="s">
+        <v>75</v>
+      </c>
+      <c r="W21">
+        <v>139.29</v>
+      </c>
+      <c r="X21">
+        <v>0.61</v>
+      </c>
+      <c r="Y21">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25">
+      <c r="A22" t="s">
+        <v>45</v>
+      </c>
+      <c r="B22" t="s">
+        <v>70</v>
+      </c>
+      <c r="C22">
+        <v>191.71</v>
+      </c>
+      <c r="D22">
+        <v>0.44</v>
+      </c>
+      <c r="E22">
+        <v>0.28</v>
+      </c>
+      <c r="F22" t="s">
+        <v>71</v>
+      </c>
+      <c r="G22">
+        <v>222.71</v>
+      </c>
+      <c r="H22">
+        <v>0.38</v>
+      </c>
+      <c r="I22">
+        <v>0.21</v>
+      </c>
+      <c r="J22" t="s">
+        <v>72</v>
+      </c>
+      <c r="K22">
+        <v>193.29</v>
+      </c>
+      <c r="L22">
+        <v>0.44</v>
+      </c>
+      <c r="M22">
+        <v>0.26</v>
+      </c>
+      <c r="N22" t="s">
+        <v>73</v>
+      </c>
+      <c r="O22">
+        <v>197.43</v>
+      </c>
+      <c r="P22">
+        <v>0.42</v>
+      </c>
+      <c r="Q22">
+        <v>0.24</v>
+      </c>
+      <c r="R22" t="s">
+        <v>74</v>
+      </c>
+      <c r="S22">
+        <v>148.17</v>
+      </c>
+      <c r="T22">
+        <v>0.57</v>
+      </c>
+      <c r="U22">
+        <v>0.39</v>
+      </c>
+      <c r="V22" t="s">
+        <v>75</v>
+      </c>
+      <c r="W22">
+        <v>140</v>
+      </c>
+      <c r="X22">
+        <v>0.6</v>
+      </c>
+      <c r="Y22">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25">
+      <c r="A23" t="s">
+        <v>46</v>
+      </c>
+      <c r="B23" t="s">
+        <v>70</v>
+      </c>
+      <c r="C23">
         <v>71.14</v>
       </c>
-      <c r="D18">
+      <c r="D23">
         <v>1.19</v>
       </c>
-      <c r="E18">
+      <c r="E23">
         <v>1.05</v>
       </c>
-      <c r="F18" t="s">
-        <v>70</v>
-      </c>
-      <c r="G18">
+      <c r="F23" t="s">
+        <v>71</v>
+      </c>
+      <c r="G23">
         <v>75.29000000000001</v>
       </c>
-      <c r="H18">
+      <c r="H23">
         <v>1.12</v>
       </c>
-      <c r="I18">
+      <c r="I23">
         <v>0.95</v>
       </c>
-      <c r="J18" t="s">
-        <v>71</v>
-      </c>
-      <c r="K18">
+      <c r="J23" t="s">
+        <v>72</v>
+      </c>
+      <c r="K23">
         <v>75.29000000000001</v>
       </c>
-      <c r="L18">
+      <c r="L23">
         <v>1.12</v>
       </c>
-      <c r="M18">
+      <c r="M23">
         <v>0.96</v>
       </c>
-      <c r="N18" t="s">
-        <v>72</v>
-      </c>
-      <c r="O18">
+      <c r="N23" t="s">
+        <v>73</v>
+      </c>
+      <c r="O23">
         <v>83</v>
       </c>
-      <c r="P18">
+      <c r="P23">
         <v>1.01</v>
       </c>
-      <c r="Q18">
+      <c r="Q23">
         <v>0.83</v>
       </c>
-      <c r="R18" t="s">
-        <v>73</v>
-      </c>
-      <c r="S18">
+      <c r="R23" t="s">
+        <v>74</v>
+      </c>
+      <c r="S23">
         <v>88.83</v>
       </c>
-      <c r="T18">
+      <c r="T23">
         <v>0.95</v>
       </c>
-      <c r="U18">
+      <c r="U23">
         <v>0.78</v>
       </c>
-    </row>
-    <row r="19" spans="1:21">
-      <c r="A19" t="s">
-        <v>38</v>
-      </c>
-      <c r="B19" t="s">
-        <v>69</v>
-      </c>
-      <c r="C19">
+      <c r="V23" t="s">
+        <v>75</v>
+      </c>
+      <c r="W23">
+        <v>162.86</v>
+      </c>
+      <c r="X23">
+        <v>0.52</v>
+      </c>
+      <c r="Y23">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25">
+      <c r="A24" t="s">
+        <v>47</v>
+      </c>
+      <c r="B24" t="s">
+        <v>70</v>
+      </c>
+      <c r="C24">
         <v>141.29</v>
       </c>
-      <c r="D19">
+      <c r="D24">
         <v>0.6</v>
       </c>
-      <c r="E19">
+      <c r="E24">
         <v>0.43</v>
       </c>
-      <c r="F19" t="s">
-        <v>70</v>
-      </c>
-      <c r="G19">
+      <c r="F24" t="s">
+        <v>71</v>
+      </c>
+      <c r="G24">
         <v>145.57</v>
       </c>
-      <c r="H19">
+      <c r="H24">
         <v>0.58</v>
       </c>
-      <c r="I19">
+      <c r="I24">
         <v>0.39</v>
       </c>
-      <c r="J19" t="s">
-        <v>71</v>
-      </c>
-      <c r="K19">
+      <c r="J24" t="s">
+        <v>72</v>
+      </c>
+      <c r="K24">
         <v>110.14</v>
       </c>
-      <c r="L19">
+      <c r="L24">
         <v>0.77</v>
       </c>
-      <c r="M19">
+      <c r="M24">
         <v>0.59</v>
       </c>
-      <c r="N19" t="s">
-        <v>72</v>
-      </c>
-      <c r="O19">
+      <c r="N24" t="s">
+        <v>73</v>
+      </c>
+      <c r="O24">
         <v>105.86</v>
       </c>
-      <c r="P19">
+      <c r="P24">
         <v>0.79</v>
       </c>
-      <c r="Q19">
+      <c r="Q24">
         <v>0.6</v>
       </c>
-      <c r="R19" t="s">
-        <v>73</v>
-      </c>
-      <c r="S19">
+      <c r="R24" t="s">
+        <v>74</v>
+      </c>
+      <c r="S24">
         <v>110</v>
       </c>
-      <c r="T19">
+      <c r="T24">
         <v>0.77</v>
       </c>
-      <c r="U19">
+      <c r="U24">
         <v>0.59</v>
       </c>
-    </row>
-    <row r="20" spans="1:21">
-      <c r="A20" t="s">
-        <v>39</v>
-      </c>
-      <c r="B20" t="s">
-        <v>69</v>
-      </c>
-      <c r="C20">
-        <v>88.86</v>
-      </c>
-      <c r="D20">
-        <v>0.96</v>
-      </c>
-      <c r="E20">
+      <c r="V24" t="s">
+        <v>75</v>
+      </c>
+      <c r="W24">
+        <v>171.86</v>
+      </c>
+      <c r="X24">
+        <v>0.49</v>
+      </c>
+      <c r="Y24">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25">
+      <c r="A25" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25">
+        <v>442.71</v>
+      </c>
+      <c r="D25">
+        <v>0.19</v>
+      </c>
+      <c r="E25">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="F25" t="s">
+        <v>71</v>
+      </c>
+      <c r="G25">
+        <v>462.29</v>
+      </c>
+      <c r="H25">
+        <v>0.18</v>
+      </c>
+      <c r="I25">
+        <v>0.06</v>
+      </c>
+      <c r="J25" t="s">
+        <v>72</v>
+      </c>
+      <c r="K25">
+        <v>186</v>
+      </c>
+      <c r="L25">
+        <v>0.45</v>
+      </c>
+      <c r="M25">
+        <v>0.28</v>
+      </c>
+      <c r="N25" t="s">
+        <v>73</v>
+      </c>
+      <c r="O25">
+        <v>123.14</v>
+      </c>
+      <c r="P25">
+        <v>0.68</v>
+      </c>
+      <c r="Q25">
+        <v>0.49</v>
+      </c>
+      <c r="R25" t="s">
+        <v>74</v>
+      </c>
+      <c r="S25">
+        <v>128.5</v>
+      </c>
+      <c r="T25">
+        <v>0.66</v>
+      </c>
+      <c r="U25">
+        <v>0.47</v>
+      </c>
+      <c r="V25" t="s">
+        <v>75</v>
+      </c>
+      <c r="W25">
+        <v>174.43</v>
+      </c>
+      <c r="X25">
+        <v>0.48</v>
+      </c>
+      <c r="Y25">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25">
+      <c r="A26" t="s">
+        <v>49</v>
+      </c>
+      <c r="B26" t="s">
+        <v>70</v>
+      </c>
+      <c r="C26">
+        <v>320.43</v>
+      </c>
+      <c r="D26">
+        <v>0.26</v>
+      </c>
+      <c r="E26">
+        <v>0.12</v>
+      </c>
+      <c r="F26" t="s">
+        <v>71</v>
+      </c>
+      <c r="G26">
+        <v>351.57</v>
+      </c>
+      <c r="H26">
+        <v>0.24</v>
+      </c>
+      <c r="I26">
+        <v>0.1</v>
+      </c>
+      <c r="J26" t="s">
+        <v>72</v>
+      </c>
+      <c r="K26">
+        <v>341.71</v>
+      </c>
+      <c r="L26">
+        <v>0.25</v>
+      </c>
+      <c r="M26">
+        <v>0.1</v>
+      </c>
+      <c r="N26" t="s">
+        <v>73</v>
+      </c>
+      <c r="O26">
+        <v>283.71</v>
+      </c>
+      <c r="P26">
+        <v>0.29</v>
+      </c>
+      <c r="Q26">
+        <v>0.13</v>
+      </c>
+      <c r="R26" t="s">
+        <v>74</v>
+      </c>
+      <c r="S26">
+        <v>302.5</v>
+      </c>
+      <c r="T26">
+        <v>0.28</v>
+      </c>
+      <c r="U26">
+        <v>0.13</v>
+      </c>
+      <c r="V26" t="s">
+        <v>75</v>
+      </c>
+      <c r="W26">
+        <v>261.14</v>
+      </c>
+      <c r="X26">
+        <v>0.32</v>
+      </c>
+      <c r="Y26">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25">
+      <c r="A27" t="s">
+        <v>50</v>
+      </c>
+      <c r="B27" t="s">
+        <v>70</v>
+      </c>
+      <c r="C27">
+        <v>89</v>
+      </c>
+      <c r="D27">
+        <v>0.95</v>
+      </c>
+      <c r="E27">
         <v>0.8</v>
       </c>
-      <c r="F20" t="s">
-        <v>70</v>
-      </c>
-      <c r="G20">
-        <v>91.70999999999999</v>
-      </c>
-      <c r="H20">
-        <v>0.92</v>
-      </c>
-      <c r="I20">
-        <v>0.74</v>
-      </c>
-      <c r="J20" t="s">
-        <v>71</v>
-      </c>
-      <c r="K20">
-        <v>91.70999999999999</v>
-      </c>
-      <c r="L20">
-        <v>0.92</v>
-      </c>
-      <c r="M20">
+      <c r="F27" t="s">
+        <v>71</v>
+      </c>
+      <c r="G27">
+        <v>90.43000000000001</v>
+      </c>
+      <c r="H27">
+        <v>0.93</v>
+      </c>
+      <c r="I27">
         <v>0.75</v>
       </c>
-      <c r="N20" t="s">
-        <v>72</v>
-      </c>
-      <c r="O20">
-        <v>92.43000000000001</v>
-      </c>
-      <c r="P20">
-        <v>0.9</v>
-      </c>
-      <c r="Q20">
-        <v>0.72</v>
-      </c>
-      <c r="R20" t="s">
-        <v>73</v>
-      </c>
-      <c r="S20">
-        <v>110.83</v>
-      </c>
-      <c r="T20">
-        <v>0.76</v>
-      </c>
-      <c r="U20">
-        <v>0.58</v>
-      </c>
-    </row>
-    <row r="21" spans="1:21">
-      <c r="A21" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21" t="s">
-        <v>69</v>
-      </c>
-      <c r="C21">
-        <v>101.29</v>
-      </c>
-      <c r="D21">
-        <v>0.84</v>
-      </c>
-      <c r="E21">
-        <v>0.67</v>
-      </c>
-      <c r="F21" t="s">
-        <v>70</v>
-      </c>
-      <c r="G21">
-        <v>106.14</v>
-      </c>
-      <c r="H21">
-        <v>0.79</v>
-      </c>
-      <c r="I21">
-        <v>0.61</v>
-      </c>
-      <c r="J21" t="s">
-        <v>71</v>
-      </c>
-      <c r="K21">
-        <v>107.57</v>
-      </c>
-      <c r="L21">
-        <v>0.78</v>
-      </c>
-      <c r="M21">
-        <v>0.61</v>
-      </c>
-      <c r="N21" t="s">
-        <v>72</v>
-      </c>
-      <c r="O21">
-        <v>119.57</v>
-      </c>
-      <c r="P21">
-        <v>0.7</v>
-      </c>
-      <c r="Q21">
-        <v>0.51</v>
-      </c>
-      <c r="R21" t="s">
-        <v>73</v>
-      </c>
-      <c r="S21">
-        <v>115.17</v>
-      </c>
-      <c r="T21">
-        <v>0.73</v>
-      </c>
-      <c r="U21">
-        <v>0.55</v>
-      </c>
-    </row>
-    <row r="22" spans="1:21">
-      <c r="A22" t="s">
-        <v>41</v>
-      </c>
-      <c r="B22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C22">
-        <v>442.71</v>
-      </c>
-      <c r="D22">
-        <v>0.19</v>
-      </c>
-      <c r="E22">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="F22" t="s">
-        <v>70</v>
-      </c>
-      <c r="G22">
-        <v>462.29</v>
-      </c>
-      <c r="H22">
-        <v>0.18</v>
-      </c>
-      <c r="I22">
-        <v>0.06</v>
-      </c>
-      <c r="J22" t="s">
-        <v>71</v>
-      </c>
-      <c r="K22">
-        <v>186</v>
-      </c>
-      <c r="L22">
-        <v>0.45</v>
-      </c>
-      <c r="M22">
-        <v>0.28</v>
-      </c>
-      <c r="N22" t="s">
-        <v>72</v>
-      </c>
-      <c r="O22">
-        <v>123.14</v>
-      </c>
-      <c r="P22">
-        <v>0.68</v>
-      </c>
-      <c r="Q22">
-        <v>0.49</v>
-      </c>
-      <c r="R22" t="s">
-        <v>73</v>
-      </c>
-      <c r="S22">
-        <v>128.5</v>
-      </c>
-      <c r="T22">
-        <v>0.66</v>
-      </c>
-      <c r="U22">
-        <v>0.47</v>
-      </c>
-    </row>
-    <row r="23" spans="1:21">
-      <c r="A23" t="s">
-        <v>42</v>
-      </c>
-      <c r="B23" t="s">
-        <v>69</v>
-      </c>
-      <c r="C23">
-        <v>153</v>
-      </c>
-      <c r="D23">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="E23">
-        <v>0.39</v>
-      </c>
-      <c r="F23" t="s">
-        <v>70</v>
-      </c>
-      <c r="G23">
-        <v>158.57</v>
-      </c>
-      <c r="H23">
-        <v>0.53</v>
-      </c>
-      <c r="I23">
-        <v>0.35</v>
-      </c>
-      <c r="J23" t="s">
-        <v>71</v>
-      </c>
-      <c r="K23">
-        <v>157.14</v>
-      </c>
-      <c r="L23">
-        <v>0.54</v>
-      </c>
-      <c r="M23">
-        <v>0.36</v>
-      </c>
-      <c r="N23" t="s">
-        <v>72</v>
-      </c>
-      <c r="O23">
-        <v>135.14</v>
-      </c>
-      <c r="P23">
-        <v>0.62</v>
-      </c>
-      <c r="Q23">
-        <v>0.43</v>
-      </c>
-      <c r="R23" t="s">
-        <v>73</v>
-      </c>
-      <c r="S23">
-        <v>144</v>
-      </c>
-      <c r="T23">
-        <v>0.59</v>
-      </c>
-      <c r="U23">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="24" spans="1:21">
-      <c r="A24" t="s">
-        <v>43</v>
-      </c>
-      <c r="B24" t="s">
-        <v>69</v>
-      </c>
-      <c r="C24">
-        <v>250</v>
-      </c>
-      <c r="D24">
-        <v>0.34</v>
-      </c>
-      <c r="E24">
-        <v>0.18</v>
-      </c>
-      <c r="F24" t="s">
-        <v>70</v>
-      </c>
-      <c r="G24">
-        <v>259.86</v>
-      </c>
-      <c r="H24">
-        <v>0.32</v>
-      </c>
-      <c r="I24">
-        <v>0.16</v>
-      </c>
-      <c r="J24" t="s">
-        <v>71</v>
-      </c>
-      <c r="K24">
-        <v>153</v>
-      </c>
-      <c r="L24">
-        <v>0.55</v>
-      </c>
-      <c r="M24">
-        <v>0.37</v>
-      </c>
-      <c r="N24" t="s">
-        <v>72</v>
-      </c>
-      <c r="O24">
-        <v>143</v>
-      </c>
-      <c r="P24">
-        <v>0.58</v>
-      </c>
-      <c r="Q24">
-        <v>0.4</v>
-      </c>
-      <c r="R24" t="s">
-        <v>73</v>
-      </c>
-      <c r="S24">
-        <v>144.83</v>
-      </c>
-      <c r="T24">
-        <v>0.58</v>
-      </c>
-      <c r="U24">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="25" spans="1:21">
-      <c r="A25" t="s">
-        <v>44</v>
-      </c>
-      <c r="B25" t="s">
-        <v>69</v>
-      </c>
-      <c r="C25">
-        <v>191.71</v>
-      </c>
-      <c r="D25">
-        <v>0.44</v>
-      </c>
-      <c r="E25">
-        <v>0.28</v>
-      </c>
-      <c r="F25" t="s">
-        <v>70</v>
-      </c>
-      <c r="G25">
-        <v>222.71</v>
-      </c>
-      <c r="H25">
-        <v>0.38</v>
-      </c>
-      <c r="I25">
-        <v>0.21</v>
-      </c>
-      <c r="J25" t="s">
-        <v>71</v>
-      </c>
-      <c r="K25">
-        <v>193.29</v>
-      </c>
-      <c r="L25">
-        <v>0.44</v>
-      </c>
-      <c r="M25">
-        <v>0.26</v>
-      </c>
-      <c r="N25" t="s">
-        <v>72</v>
-      </c>
-      <c r="O25">
-        <v>197.43</v>
-      </c>
-      <c r="P25">
-        <v>0.42</v>
-      </c>
-      <c r="Q25">
-        <v>0.24</v>
-      </c>
-      <c r="R25" t="s">
-        <v>73</v>
-      </c>
-      <c r="S25">
-        <v>148.17</v>
-      </c>
-      <c r="T25">
-        <v>0.57</v>
-      </c>
-      <c r="U25">
-        <v>0.39</v>
-      </c>
-    </row>
-    <row r="26" spans="1:21">
-      <c r="A26" t="s">
-        <v>45</v>
-      </c>
-      <c r="B26" t="s">
-        <v>69</v>
-      </c>
-      <c r="C26">
-        <v>89</v>
-      </c>
-      <c r="D26">
-        <v>0.95</v>
-      </c>
-      <c r="E26">
-        <v>0.8</v>
-      </c>
-      <c r="F26" t="s">
-        <v>70</v>
-      </c>
-      <c r="G26">
-        <v>90.43000000000001</v>
-      </c>
-      <c r="H26">
-        <v>0.93</v>
-      </c>
-      <c r="I26">
-        <v>0.75</v>
-      </c>
-      <c r="J26" t="s">
-        <v>71</v>
-      </c>
-      <c r="K26">
+      <c r="J27" t="s">
+        <v>72</v>
+      </c>
+      <c r="K27">
         <v>133.71</v>
-      </c>
-      <c r="L26">
-        <v>0.63</v>
-      </c>
-      <c r="M26">
-        <v>0.45</v>
-      </c>
-      <c r="N26" t="s">
-        <v>72</v>
-      </c>
-      <c r="O26">
-        <v>135.14</v>
-      </c>
-      <c r="P26">
-        <v>0.62</v>
-      </c>
-      <c r="Q26">
-        <v>0.43</v>
-      </c>
-      <c r="R26" t="s">
-        <v>73</v>
-      </c>
-      <c r="S26">
-        <v>148.33</v>
-      </c>
-      <c r="T26">
-        <v>0.57</v>
-      </c>
-      <c r="U26">
-        <v>0.39</v>
-      </c>
-    </row>
-    <row r="27" spans="1:21">
-      <c r="A27" t="s">
-        <v>46</v>
-      </c>
-      <c r="B27" t="s">
-        <v>69</v>
-      </c>
-      <c r="C27">
-        <v>80</v>
-      </c>
-      <c r="D27">
-        <v>1.06</v>
-      </c>
-      <c r="E27">
-        <v>0.91</v>
-      </c>
-      <c r="F27" t="s">
-        <v>70</v>
-      </c>
-      <c r="G27">
-        <v>80</v>
-      </c>
-      <c r="H27">
-        <v>1.05</v>
-      </c>
-      <c r="I27">
-        <v>0.88</v>
-      </c>
-      <c r="J27" t="s">
-        <v>71</v>
-      </c>
-      <c r="K27">
-        <v>133.14</v>
       </c>
       <c r="L27">
         <v>0.63</v>
       </c>
       <c r="M27">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="N27" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O27">
-        <v>145.86</v>
+        <v>135.14</v>
       </c>
       <c r="P27">
+        <v>0.62</v>
+      </c>
+      <c r="Q27">
+        <v>0.43</v>
+      </c>
+      <c r="R27" t="s">
+        <v>74</v>
+      </c>
+      <c r="S27">
+        <v>148.33</v>
+      </c>
+      <c r="T27">
         <v>0.57</v>
       </c>
-      <c r="Q27">
-        <v>0.38</v>
-      </c>
-      <c r="R27" t="s">
-        <v>73</v>
-      </c>
-      <c r="S27">
-        <v>152.33</v>
-      </c>
-      <c r="T27">
-        <v>0.55</v>
-      </c>
       <c r="U27">
-        <v>0.37</v>
-      </c>
-    </row>
-    <row r="28" spans="1:21">
+        <v>0.39</v>
+      </c>
+      <c r="V27" t="s">
+        <v>75</v>
+      </c>
+      <c r="W27">
+        <v>279.29</v>
+      </c>
+      <c r="X27">
+        <v>0.3</v>
+      </c>
+      <c r="Y27">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25">
       <c r="A28" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B28" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C28">
-        <v>249.71</v>
+        <v>376.29</v>
       </c>
       <c r="D28">
-        <v>0.34</v>
+        <v>0.23</v>
       </c>
       <c r="E28">
-        <v>0.18</v>
+        <v>0.09</v>
       </c>
       <c r="F28" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G28">
-        <v>242.57</v>
+        <v>241</v>
       </c>
       <c r="H28">
         <v>0.35</v>
@@ -2380,63 +2710,75 @@
         <v>0.18</v>
       </c>
       <c r="J28" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K28">
-        <v>228.14</v>
+        <v>224.29</v>
       </c>
       <c r="L28">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="M28">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="N28" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O28">
-        <v>216.71</v>
+        <v>234</v>
       </c>
       <c r="P28">
-        <v>0.39</v>
+        <v>0.36</v>
       </c>
       <c r="Q28">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="R28" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="S28">
-        <v>234.17</v>
+        <v>256.33</v>
       </c>
       <c r="T28">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="U28">
-        <v>0.19</v>
-      </c>
-    </row>
-    <row r="29" spans="1:21">
+        <v>0.17</v>
+      </c>
+      <c r="V28" t="s">
+        <v>75</v>
+      </c>
+      <c r="W28">
+        <v>293.57</v>
+      </c>
+      <c r="X28">
+        <v>0.29</v>
+      </c>
+      <c r="Y28">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25">
       <c r="A29" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B29" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C29">
-        <v>376.29</v>
+        <v>249.71</v>
       </c>
       <c r="D29">
-        <v>0.23</v>
+        <v>0.34</v>
       </c>
       <c r="E29">
-        <v>0.09</v>
+        <v>0.18</v>
       </c>
       <c r="F29" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G29">
-        <v>241</v>
+        <v>242.57</v>
       </c>
       <c r="H29">
         <v>0.35</v>
@@ -2445,113 +2787,137 @@
         <v>0.18</v>
       </c>
       <c r="J29" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K29">
-        <v>224.29</v>
+        <v>228.14</v>
       </c>
       <c r="L29">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="M29">
+        <v>0.2</v>
+      </c>
+      <c r="N29" t="s">
+        <v>73</v>
+      </c>
+      <c r="O29">
+        <v>216.71</v>
+      </c>
+      <c r="P29">
+        <v>0.39</v>
+      </c>
+      <c r="Q29">
         <v>0.21</v>
       </c>
-      <c r="N29" t="s">
-        <v>72</v>
-      </c>
-      <c r="O29">
-        <v>234</v>
-      </c>
-      <c r="P29">
+      <c r="R29" t="s">
+        <v>74</v>
+      </c>
+      <c r="S29">
+        <v>234.17</v>
+      </c>
+      <c r="T29">
         <v>0.36</v>
       </c>
-      <c r="Q29">
+      <c r="U29">
+        <v>0.19</v>
+      </c>
+      <c r="V29" t="s">
+        <v>75</v>
+      </c>
+      <c r="W29">
+        <v>305.57</v>
+      </c>
+      <c r="X29">
+        <v>0.28</v>
+      </c>
+      <c r="Y29">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25">
+      <c r="A30" t="s">
+        <v>53</v>
+      </c>
+      <c r="B30" t="s">
+        <v>70</v>
+      </c>
+      <c r="C30">
+        <v>243.29</v>
+      </c>
+      <c r="D30">
+        <v>0.35</v>
+      </c>
+      <c r="E30">
+        <v>0.19</v>
+      </c>
+      <c r="F30" t="s">
+        <v>71</v>
+      </c>
+      <c r="G30">
+        <v>455.57</v>
+      </c>
+      <c r="H30">
         <v>0.18</v>
       </c>
-      <c r="R29" t="s">
-        <v>73</v>
-      </c>
-      <c r="S29">
-        <v>256.33</v>
-      </c>
-      <c r="T29">
-        <v>0.33</v>
-      </c>
-      <c r="U29">
+      <c r="I30">
+        <v>0.06</v>
+      </c>
+      <c r="J30" t="s">
+        <v>72</v>
+      </c>
+      <c r="K30">
+        <v>483.57</v>
+      </c>
+      <c r="L30">
         <v>0.17</v>
       </c>
-    </row>
-    <row r="30" spans="1:21">
-      <c r="A30" t="s">
-        <v>49</v>
-      </c>
-      <c r="B30" t="s">
-        <v>69</v>
-      </c>
-      <c r="C30">
-        <v>320.43</v>
-      </c>
-      <c r="D30">
+      <c r="M30">
+        <v>0.06</v>
+      </c>
+      <c r="N30" t="s">
+        <v>73</v>
+      </c>
+      <c r="O30">
+        <v>490.71</v>
+      </c>
+      <c r="P30">
+        <v>0.17</v>
+      </c>
+      <c r="Q30">
+        <v>0.05</v>
+      </c>
+      <c r="R30" t="s">
+        <v>74</v>
+      </c>
+      <c r="S30">
+        <v>522.33</v>
+      </c>
+      <c r="T30">
+        <v>0.16</v>
+      </c>
+      <c r="U30">
+        <v>0.05</v>
+      </c>
+      <c r="V30" t="s">
+        <v>75</v>
+      </c>
+      <c r="W30">
+        <v>324.29</v>
+      </c>
+      <c r="X30">
         <v>0.26</v>
       </c>
-      <c r="E30">
-        <v>0.12</v>
-      </c>
-      <c r="F30" t="s">
-        <v>70</v>
-      </c>
-      <c r="G30">
-        <v>351.57</v>
-      </c>
-      <c r="H30">
-        <v>0.24</v>
-      </c>
-      <c r="I30">
-        <v>0.1</v>
-      </c>
-      <c r="J30" t="s">
-        <v>71</v>
-      </c>
-      <c r="K30">
-        <v>341.71</v>
-      </c>
-      <c r="L30">
-        <v>0.25</v>
-      </c>
-      <c r="M30">
-        <v>0.1</v>
-      </c>
-      <c r="N30" t="s">
-        <v>72</v>
-      </c>
-      <c r="O30">
-        <v>283.71</v>
-      </c>
-      <c r="P30">
-        <v>0.29</v>
-      </c>
-      <c r="Q30">
-        <v>0.13</v>
-      </c>
-      <c r="R30" t="s">
-        <v>73</v>
-      </c>
-      <c r="S30">
-        <v>302.5</v>
-      </c>
-      <c r="T30">
-        <v>0.28</v>
-      </c>
-      <c r="U30">
-        <v>0.13</v>
-      </c>
-    </row>
-    <row r="31" spans="1:21">
+      <c r="Y30">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25">
       <c r="A31" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B31" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C31">
         <v>467.14</v>
@@ -2563,7 +2929,7 @@
         <v>0.06</v>
       </c>
       <c r="F31" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G31">
         <v>505.29</v>
@@ -2575,7 +2941,7 @@
         <v>0.05</v>
       </c>
       <c r="J31" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K31">
         <v>494.14</v>
@@ -2587,7 +2953,7 @@
         <v>0.05</v>
       </c>
       <c r="N31" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O31">
         <v>502.43</v>
@@ -2599,7 +2965,7 @@
         <v>0.05</v>
       </c>
       <c r="R31" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="S31">
         <v>441.33</v>
@@ -2610,13 +2976,25 @@
       <c r="U31">
         <v>0.06</v>
       </c>
-    </row>
-    <row r="32" spans="1:21">
+      <c r="V31" t="s">
+        <v>75</v>
+      </c>
+      <c r="W31">
+        <v>433.86</v>
+      </c>
+      <c r="X31">
+        <v>0.19</v>
+      </c>
+      <c r="Y31">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25">
       <c r="A32" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C32">
         <v>370.43</v>
@@ -2628,7 +3006,7 @@
         <v>0.1</v>
       </c>
       <c r="F32" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G32">
         <v>376.71</v>
@@ -2640,7 +3018,7 @@
         <v>0.08</v>
       </c>
       <c r="J32" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K32">
         <v>383.71</v>
@@ -2652,7 +3030,7 @@
         <v>0.08</v>
       </c>
       <c r="N32" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O32">
         <v>390.71</v>
@@ -2664,7 +3042,7 @@
         <v>0.08</v>
       </c>
       <c r="R32" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="S32">
         <v>473</v>
@@ -2675,64 +3053,76 @@
       <c r="U32">
         <v>0.06</v>
       </c>
-    </row>
-    <row r="33" spans="1:21">
+      <c r="V32" t="s">
+        <v>75</v>
+      </c>
+      <c r="W32">
+        <v>514</v>
+      </c>
+      <c r="X32">
+        <v>0.16</v>
+      </c>
+      <c r="Y32">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="33" spans="1:25">
       <c r="A33" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B33" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C33">
-        <v>243.29</v>
+        <v>367.57</v>
       </c>
       <c r="D33">
-        <v>0.35</v>
+        <v>0.23</v>
       </c>
       <c r="E33">
-        <v>0.19</v>
+        <v>0.1</v>
       </c>
       <c r="F33" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G33">
-        <v>455.57</v>
+        <v>383</v>
       </c>
       <c r="H33">
+        <v>0.22</v>
+      </c>
+      <c r="I33">
+        <v>0.08</v>
+      </c>
+      <c r="J33" t="s">
+        <v>72</v>
+      </c>
+      <c r="K33">
+        <v>378.86</v>
+      </c>
+      <c r="L33">
+        <v>0.22</v>
+      </c>
+      <c r="M33">
+        <v>0.09</v>
+      </c>
+      <c r="N33" t="s">
+        <v>73</v>
+      </c>
+      <c r="O33">
+        <v>474.57</v>
+      </c>
+      <c r="P33">
         <v>0.18</v>
-      </c>
-      <c r="I33">
-        <v>0.06</v>
-      </c>
-      <c r="J33" t="s">
-        <v>71</v>
-      </c>
-      <c r="K33">
-        <v>483.57</v>
-      </c>
-      <c r="L33">
-        <v>0.17</v>
-      </c>
-      <c r="M33">
-        <v>0.06</v>
-      </c>
-      <c r="N33" t="s">
-        <v>72</v>
-      </c>
-      <c r="O33">
-        <v>490.71</v>
-      </c>
-      <c r="P33">
-        <v>0.17</v>
       </c>
       <c r="Q33">
         <v>0.05</v>
       </c>
       <c r="R33" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="S33">
-        <v>522.33</v>
+        <v>530.67</v>
       </c>
       <c r="T33">
         <v>0.16</v>
@@ -2740,273 +3130,333 @@
       <c r="U33">
         <v>0.05</v>
       </c>
-    </row>
-    <row r="34" spans="1:21">
+      <c r="V33" t="s">
+        <v>75</v>
+      </c>
+      <c r="W33">
+        <v>518</v>
+      </c>
+      <c r="X33">
+        <v>0.16</v>
+      </c>
+      <c r="Y33">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="34" spans="1:25">
       <c r="A34" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B34" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C34">
-        <v>367.57</v>
+        <v>299.29</v>
       </c>
       <c r="D34">
-        <v>0.23</v>
+        <v>0.28</v>
       </c>
       <c r="E34">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="F34" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G34">
-        <v>383</v>
+        <v>497.86</v>
       </c>
       <c r="H34">
-        <v>0.22</v>
+        <v>0.17</v>
       </c>
       <c r="I34">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="J34" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K34">
-        <v>378.86</v>
+        <v>486.71</v>
       </c>
       <c r="L34">
-        <v>0.22</v>
+        <v>0.17</v>
       </c>
       <c r="M34">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="N34" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O34">
-        <v>474.57</v>
+        <v>497.86</v>
       </c>
       <c r="P34">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="Q34">
         <v>0.05</v>
       </c>
       <c r="R34" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="S34">
-        <v>530.67</v>
+        <v>572.33</v>
       </c>
       <c r="T34">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="U34">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="35" spans="1:21">
+        <v>0.04</v>
+      </c>
+      <c r="V34" t="s">
+        <v>75</v>
+      </c>
+      <c r="W34">
+        <v>547.86</v>
+      </c>
+      <c r="X34">
+        <v>0.15</v>
+      </c>
+      <c r="Y34">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="35" spans="1:25">
       <c r="A35" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B35" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C35">
-        <v>299.29</v>
+        <v>747.86</v>
       </c>
       <c r="D35">
-        <v>0.28</v>
+        <v>0.11</v>
       </c>
       <c r="E35">
+        <v>0.03</v>
+      </c>
+      <c r="F35" t="s">
+        <v>71</v>
+      </c>
+      <c r="G35">
+        <v>747.86</v>
+      </c>
+      <c r="H35">
+        <v>0.11</v>
+      </c>
+      <c r="I35">
+        <v>0.02</v>
+      </c>
+      <c r="J35" t="s">
+        <v>72</v>
+      </c>
+      <c r="K35">
+        <v>747.86</v>
+      </c>
+      <c r="L35">
+        <v>0.11</v>
+      </c>
+      <c r="M35">
+        <v>0.02</v>
+      </c>
+      <c r="N35" t="s">
+        <v>73</v>
+      </c>
+      <c r="O35">
+        <v>747.86</v>
+      </c>
+      <c r="P35">
+        <v>0.11</v>
+      </c>
+      <c r="Q35">
+        <v>0.02</v>
+      </c>
+      <c r="R35" t="s">
+        <v>74</v>
+      </c>
+      <c r="S35">
+        <v>607.5</v>
+      </c>
+      <c r="T35">
         <v>0.14</v>
-      </c>
-      <c r="F35" t="s">
-        <v>70</v>
-      </c>
-      <c r="G35">
-        <v>497.86</v>
-      </c>
-      <c r="H35">
-        <v>0.17</v>
-      </c>
-      <c r="I35">
-        <v>0.05</v>
-      </c>
-      <c r="J35" t="s">
-        <v>71</v>
-      </c>
-      <c r="K35">
-        <v>486.71</v>
-      </c>
-      <c r="L35">
-        <v>0.17</v>
-      </c>
-      <c r="M35">
-        <v>0.06</v>
-      </c>
-      <c r="N35" t="s">
-        <v>72</v>
-      </c>
-      <c r="O35">
-        <v>497.86</v>
-      </c>
-      <c r="P35">
-        <v>0.17</v>
-      </c>
-      <c r="Q35">
-        <v>0.05</v>
-      </c>
-      <c r="R35" t="s">
-        <v>73</v>
-      </c>
-      <c r="S35">
-        <v>572.33</v>
-      </c>
-      <c r="T35">
-        <v>0.15</v>
       </c>
       <c r="U35">
         <v>0.04</v>
       </c>
-    </row>
-    <row r="36" spans="1:21">
+      <c r="V35" t="s">
+        <v>75</v>
+      </c>
+      <c r="W35">
+        <v>569.29</v>
+      </c>
+      <c r="X35">
+        <v>0.15</v>
+      </c>
+      <c r="Y35">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25">
       <c r="A36" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B36" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C36">
-        <v>747.86</v>
+        <v>540.71</v>
       </c>
       <c r="D36">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="E36">
+        <v>0.05</v>
+      </c>
+      <c r="F36" t="s">
+        <v>71</v>
+      </c>
+      <c r="G36">
+        <v>576.4299999999999</v>
+      </c>
+      <c r="H36">
+        <v>0.15</v>
+      </c>
+      <c r="I36">
+        <v>0.04</v>
+      </c>
+      <c r="J36" t="s">
+        <v>72</v>
+      </c>
+      <c r="K36">
+        <v>576.4299999999999</v>
+      </c>
+      <c r="L36">
+        <v>0.15</v>
+      </c>
+      <c r="M36">
+        <v>0.04</v>
+      </c>
+      <c r="N36" t="s">
+        <v>73</v>
+      </c>
+      <c r="O36">
+        <v>612.14</v>
+      </c>
+      <c r="P36">
+        <v>0.14</v>
+      </c>
+      <c r="Q36">
         <v>0.03</v>
       </c>
-      <c r="F36" t="s">
-        <v>70</v>
-      </c>
-      <c r="G36">
-        <v>747.86</v>
-      </c>
-      <c r="H36">
-        <v>0.11</v>
-      </c>
-      <c r="I36">
-        <v>0.02</v>
-      </c>
-      <c r="J36" t="s">
-        <v>71</v>
-      </c>
-      <c r="K36">
-        <v>747.86</v>
-      </c>
-      <c r="L36">
-        <v>0.11</v>
-      </c>
-      <c r="M36">
-        <v>0.02</v>
-      </c>
-      <c r="N36" t="s">
-        <v>72</v>
-      </c>
-      <c r="O36">
-        <v>747.86</v>
-      </c>
-      <c r="P36">
-        <v>0.11</v>
-      </c>
-      <c r="Q36">
-        <v>0.02</v>
-      </c>
       <c r="R36" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="S36">
-        <v>607.5</v>
+        <v>630.67</v>
       </c>
       <c r="T36">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="U36">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="37" spans="1:21">
+        <v>0.03</v>
+      </c>
+      <c r="V36" t="s">
+        <v>75</v>
+      </c>
+      <c r="W36">
+        <v>647.86</v>
+      </c>
+      <c r="X36">
+        <v>0.13</v>
+      </c>
+      <c r="Y36">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="37" spans="1:25">
       <c r="A37" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B37" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C37">
-        <v>540.71</v>
+        <v>1326.43</v>
       </c>
       <c r="D37">
-        <v>0.16</v>
+        <v>0.06</v>
       </c>
       <c r="E37">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="F37" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G37">
-        <v>576.4299999999999</v>
+        <v>1326.43</v>
       </c>
       <c r="H37">
-        <v>0.15</v>
+        <v>0.06</v>
       </c>
       <c r="I37">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="J37" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K37">
-        <v>576.4299999999999</v>
+        <v>1326.43</v>
       </c>
       <c r="L37">
-        <v>0.15</v>
+        <v>0.06</v>
       </c>
       <c r="M37">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="N37" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O37">
-        <v>612.14</v>
+        <v>1069.29</v>
       </c>
       <c r="P37">
-        <v>0.14</v>
+        <v>0.08</v>
       </c>
       <c r="Q37">
+        <v>0.01</v>
+      </c>
+      <c r="R37" t="s">
+        <v>74</v>
+      </c>
+      <c r="S37">
+        <v>996.6</v>
+      </c>
+      <c r="T37">
+        <v>0.08</v>
+      </c>
+      <c r="U37">
+        <v>0.01</v>
+      </c>
+      <c r="V37" t="s">
+        <v>75</v>
+      </c>
+      <c r="W37">
+        <v>705.67</v>
+      </c>
+      <c r="X37">
+        <v>0.12</v>
+      </c>
+      <c r="Y37">
         <v>0.03</v>
       </c>
-      <c r="R37" t="s">
-        <v>73</v>
-      </c>
-      <c r="S37">
-        <v>630.67</v>
-      </c>
-      <c r="T37">
-        <v>0.13</v>
-      </c>
-      <c r="U37">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="38" spans="1:21">
+    </row>
+    <row r="38" spans="1:25">
       <c r="A38" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B38" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C38">
         <v>890.71</v>
@@ -3018,7 +3468,7 @@
         <v>0.02</v>
       </c>
       <c r="F38" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G38">
         <v>890.71</v>
@@ -3030,7 +3480,7 @@
         <v>0.02</v>
       </c>
       <c r="J38" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K38">
         <v>890.71</v>
@@ -3042,7 +3492,7 @@
         <v>0.02</v>
       </c>
       <c r="N38" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O38">
         <v>783.5700000000001</v>
@@ -3054,7 +3504,7 @@
         <v>0.02</v>
       </c>
       <c r="R38" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="S38">
         <v>789</v>
@@ -3065,13 +3515,25 @@
       <c r="U38">
         <v>0.02</v>
       </c>
-    </row>
-    <row r="39" spans="1:21">
+      <c r="V38" t="s">
+        <v>75</v>
+      </c>
+      <c r="W38">
+        <v>855</v>
+      </c>
+      <c r="X38">
+        <v>0.1</v>
+      </c>
+      <c r="Y38">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="39" spans="1:25">
       <c r="A39" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B39" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C39">
         <v>1197.86</v>
@@ -3083,7 +3545,7 @@
         <v>0.01</v>
       </c>
       <c r="F39" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G39">
         <v>1197.86</v>
@@ -3095,7 +3557,7 @@
         <v>0.01</v>
       </c>
       <c r="J39" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K39">
         <v>1197.86</v>
@@ -3107,7 +3569,7 @@
         <v>0.01</v>
       </c>
       <c r="N39" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O39">
         <v>819.29</v>
@@ -3119,7 +3581,7 @@
         <v>0.02</v>
       </c>
       <c r="R39" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="S39">
         <v>872.33</v>
@@ -3130,143 +3592,179 @@
       <c r="U39">
         <v>0.02</v>
       </c>
-    </row>
-    <row r="40" spans="1:21">
+      <c r="V39" t="s">
+        <v>75</v>
+      </c>
+      <c r="W39">
+        <v>890.71</v>
+      </c>
+      <c r="X39">
+        <v>0.09</v>
+      </c>
+      <c r="Y39">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="40" spans="1:25">
       <c r="A40" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B40" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C40">
-        <v>605</v>
+        <v>1197.86</v>
       </c>
       <c r="D40">
-        <v>0.14</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E40">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="F40" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G40">
-        <v>640.71</v>
+        <v>1197.86</v>
       </c>
       <c r="H40">
-        <v>0.13</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I40">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="J40" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K40">
-        <v>890.71</v>
+        <v>1197.86</v>
       </c>
       <c r="L40">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="M40">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="N40" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O40">
-        <v>926.4299999999999</v>
+        <v>1197.86</v>
       </c>
       <c r="P40">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Q40">
         <v>0.01</v>
       </c>
       <c r="R40" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="S40">
-        <v>955.67</v>
+        <v>1247.33</v>
       </c>
       <c r="T40">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="U40">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="41" spans="1:21">
+      <c r="V40" t="s">
+        <v>75</v>
+      </c>
+      <c r="W40">
+        <v>1212.14</v>
+      </c>
+      <c r="X40">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="Y40">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="41" spans="1:25">
       <c r="A41" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B41" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C41">
-        <v>1326.43</v>
+        <v>1126.43</v>
       </c>
       <c r="D41">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="E41">
         <v>0.01</v>
       </c>
       <c r="F41" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G41">
-        <v>1326.43</v>
+        <v>1126.43</v>
       </c>
       <c r="H41">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I41">
         <v>0.01</v>
       </c>
       <c r="J41" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K41">
-        <v>1326.43</v>
+        <v>1126.43</v>
       </c>
       <c r="L41">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="M41">
         <v>0.01</v>
       </c>
       <c r="N41" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O41">
-        <v>1069.29</v>
+        <v>1197.86</v>
       </c>
       <c r="P41">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Q41">
         <v>0.01</v>
       </c>
       <c r="R41" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="S41">
-        <v>996.6</v>
+        <v>1296.6</v>
       </c>
       <c r="T41">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="U41">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="42" spans="1:21">
+      <c r="V41" t="s">
+        <v>75</v>
+      </c>
+      <c r="W41">
+        <v>1247.33</v>
+      </c>
+      <c r="X41">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="Y41">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="42" spans="1:25">
       <c r="A42" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B42" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C42">
         <v>890.71</v>
@@ -3278,7 +3776,7 @@
         <v>0.02</v>
       </c>
       <c r="F42" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G42">
         <v>1176.43</v>
@@ -3290,7 +3788,7 @@
         <v>0.01</v>
       </c>
       <c r="J42" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K42">
         <v>1176.43</v>
@@ -3302,7 +3800,7 @@
         <v>0.01</v>
       </c>
       <c r="N42" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O42">
         <v>1176.43</v>
@@ -3314,7 +3812,7 @@
         <v>0.01</v>
       </c>
       <c r="R42" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="S42">
         <v>1205.67</v>
@@ -3325,13 +3823,25 @@
       <c r="U42">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="43" spans="1:21">
+      <c r="V42" t="s">
+        <v>75</v>
+      </c>
+      <c r="W42">
+        <v>1247.86</v>
+      </c>
+      <c r="X42">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="Y42">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="43" spans="1:25">
       <c r="A43" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B43" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C43">
         <v>1197.86</v>
@@ -3343,7 +3853,7 @@
         <v>0.01</v>
       </c>
       <c r="F43" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G43">
         <v>1197.86</v>
@@ -3355,7 +3865,7 @@
         <v>0.01</v>
       </c>
       <c r="J43" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K43">
         <v>1197.86</v>
@@ -3367,7 +3877,7 @@
         <v>0.01</v>
       </c>
       <c r="N43" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O43">
         <v>1197.86</v>
@@ -3379,140 +3889,164 @@
         <v>0.01</v>
       </c>
       <c r="R43" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="S43">
-        <v>1247.33</v>
+        <v>1296.6</v>
       </c>
       <c r="T43">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="U43">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="44" spans="1:21">
+      <c r="V43" t="s">
+        <v>75</v>
+      </c>
+      <c r="W43">
+        <v>1247.33</v>
+      </c>
+      <c r="X43">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="Y43">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="44" spans="1:25">
       <c r="A44" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B44" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C44">
-        <v>1126.43</v>
+        <v>1497.86</v>
       </c>
       <c r="D44">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="E44">
         <v>0.01</v>
       </c>
       <c r="F44" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G44">
-        <v>1126.43</v>
+        <v>1497.86</v>
       </c>
       <c r="H44">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="I44">
         <v>0.01</v>
       </c>
       <c r="J44" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K44">
-        <v>1126.43</v>
+        <v>1497.86</v>
       </c>
       <c r="L44">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="M44">
         <v>0.01</v>
       </c>
       <c r="N44" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O44">
-        <v>1197.86</v>
+        <v>1497.86</v>
       </c>
       <c r="P44">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="Q44">
         <v>0.01</v>
       </c>
       <c r="R44" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="S44">
-        <v>1296.6</v>
+        <v>1696.6</v>
       </c>
       <c r="T44">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="U44">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="45" spans="1:21">
+        <v>0</v>
+      </c>
+      <c r="V44" t="s">
+        <v>75</v>
+      </c>
+      <c r="W44">
+        <v>1664</v>
+      </c>
+      <c r="X44">
+        <v>0.05</v>
+      </c>
+      <c r="Y44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:25">
       <c r="A45" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B45" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C45">
-        <v>1197.86</v>
+        <v>1069.29</v>
       </c>
       <c r="D45">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="E45">
         <v>0.01</v>
       </c>
       <c r="F45" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G45">
-        <v>1197.86</v>
+        <v>1069.29</v>
       </c>
       <c r="H45">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="I45">
         <v>0.01</v>
       </c>
       <c r="J45" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K45">
-        <v>1197.86</v>
+        <v>1069.29</v>
       </c>
       <c r="L45">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="M45">
         <v>0.01</v>
       </c>
       <c r="N45" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O45">
-        <v>1197.86</v>
+        <v>1069.29</v>
       </c>
       <c r="P45">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="Q45">
         <v>0.01</v>
       </c>
       <c r="R45" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="S45">
-        <v>1296.6</v>
+        <v>1372.33</v>
       </c>
       <c r="T45">
         <v>0.06</v>
@@ -3520,264 +4054,93 @@
       <c r="U45">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="46" spans="1:21">
+      <c r="V45" t="s">
+        <v>75</v>
+      </c>
+      <c r="W45">
+        <v>1926.43</v>
+      </c>
+      <c r="X45">
+        <v>0.04</v>
+      </c>
+      <c r="Y45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:25">
       <c r="A46" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B46" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C46">
-        <v>1069.29</v>
+        <v>1926.43</v>
       </c>
       <c r="D46">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="E46">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="F46" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G46">
-        <v>1069.29</v>
+        <v>1926.43</v>
       </c>
       <c r="H46">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="I46">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="J46" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K46">
-        <v>1069.29</v>
+        <v>2355</v>
       </c>
       <c r="L46">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="M46">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="N46" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O46">
-        <v>1069.29</v>
+        <v>2355</v>
       </c>
       <c r="P46">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="Q46">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="R46" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="S46">
-        <v>1372.33</v>
+        <v>2596.6</v>
       </c>
       <c r="T46">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="U46">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="47" spans="1:21">
-      <c r="A47" t="s">
-        <v>66</v>
-      </c>
-      <c r="B47" t="s">
-        <v>69</v>
-      </c>
-      <c r="C47">
-        <v>1497.86</v>
-      </c>
-      <c r="D47">
-        <v>0.06</v>
-      </c>
-      <c r="E47">
-        <v>0.01</v>
-      </c>
-      <c r="F47" t="s">
-        <v>70</v>
-      </c>
-      <c r="G47">
-        <v>1497.86</v>
-      </c>
-      <c r="H47">
-        <v>0.06</v>
-      </c>
-      <c r="I47">
-        <v>0.01</v>
-      </c>
-      <c r="J47" t="s">
-        <v>71</v>
-      </c>
-      <c r="K47">
-        <v>1497.86</v>
-      </c>
-      <c r="L47">
-        <v>0.06</v>
-      </c>
-      <c r="M47">
-        <v>0.01</v>
-      </c>
-      <c r="N47" t="s">
-        <v>72</v>
-      </c>
-      <c r="O47">
-        <v>1497.86</v>
-      </c>
-      <c r="P47">
-        <v>0.06</v>
-      </c>
-      <c r="Q47">
-        <v>0.01</v>
-      </c>
-      <c r="R47" t="s">
-        <v>73</v>
-      </c>
-      <c r="S47">
-        <v>1696.6</v>
-      </c>
-      <c r="T47">
-        <v>0.05</v>
-      </c>
-      <c r="U47">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="1:21">
-      <c r="A48" t="s">
-        <v>67</v>
-      </c>
-      <c r="B48" t="s">
-        <v>69</v>
-      </c>
-      <c r="C48">
-        <v>1926.43</v>
-      </c>
-      <c r="D48">
+      <c r="V46" t="s">
+        <v>75</v>
+      </c>
+      <c r="W46">
+        <v>1997.33</v>
+      </c>
+      <c r="X46">
         <v>0.04</v>
       </c>
-      <c r="E48">
-        <v>0</v>
-      </c>
-      <c r="F48" t="s">
-        <v>70</v>
-      </c>
-      <c r="G48">
-        <v>1926.43</v>
-      </c>
-      <c r="H48">
-        <v>0.04</v>
-      </c>
-      <c r="I48">
-        <v>0</v>
-      </c>
-      <c r="J48" t="s">
-        <v>71</v>
-      </c>
-      <c r="K48">
-        <v>2033.57</v>
-      </c>
-      <c r="L48">
-        <v>0.04</v>
-      </c>
-      <c r="M48">
-        <v>0</v>
-      </c>
-      <c r="N48" t="s">
-        <v>72</v>
-      </c>
-      <c r="O48">
-        <v>2033.57</v>
-      </c>
-      <c r="P48">
-        <v>0.04</v>
-      </c>
-      <c r="Q48">
-        <v>0</v>
-      </c>
-      <c r="R48" t="s">
-        <v>73</v>
-      </c>
-      <c r="S48">
-        <v>2296.6</v>
-      </c>
-      <c r="T48">
-        <v>0.04</v>
-      </c>
-      <c r="U48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:21">
-      <c r="A49" t="s">
-        <v>68</v>
-      </c>
-      <c r="B49" t="s">
-        <v>69</v>
-      </c>
-      <c r="C49">
-        <v>1926.43</v>
-      </c>
-      <c r="D49">
-        <v>0.04</v>
-      </c>
-      <c r="E49">
-        <v>0</v>
-      </c>
-      <c r="F49" t="s">
-        <v>70</v>
-      </c>
-      <c r="G49">
-        <v>1926.43</v>
-      </c>
-      <c r="H49">
-        <v>0.04</v>
-      </c>
-      <c r="I49">
-        <v>0</v>
-      </c>
-      <c r="J49" t="s">
-        <v>71</v>
-      </c>
-      <c r="K49">
-        <v>2355</v>
-      </c>
-      <c r="L49">
-        <v>0.04</v>
-      </c>
-      <c r="M49">
-        <v>0</v>
-      </c>
-      <c r="N49" t="s">
-        <v>72</v>
-      </c>
-      <c r="O49">
-        <v>2355</v>
-      </c>
-      <c r="P49">
-        <v>0.04</v>
-      </c>
-      <c r="Q49">
-        <v>0</v>
-      </c>
-      <c r="R49" t="s">
-        <v>73</v>
-      </c>
-      <c r="S49">
-        <v>2596.6</v>
-      </c>
-      <c r="T49">
-        <v>0.03</v>
-      </c>
-      <c r="U49">
+      <c r="Y46">
         <v>0</v>
       </c>
     </row>

--- a/processed_data_during_wm/processed_data_wide.xlsx
+++ b/processed_data_during_wm/processed_data_wide.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="80">
   <si>
     <t>Team</t>
   </si>
@@ -91,87 +91,99 @@
     <t>Shin_Wahrscheinlichkeit_in_Prozent_6</t>
   </si>
   <si>
+    <t>Datum_7</t>
+  </si>
+  <si>
+    <t>Durchsch_Quote_7</t>
+  </si>
+  <si>
+    <t>Norm_Wahrscheinlichkeit_in_Prozent_7</t>
+  </si>
+  <si>
+    <t>Shin_Wahrscheinlichkeit_in_Prozent_7</t>
+  </si>
+  <si>
     <t>Frankreich</t>
   </si>
   <si>
     <t>Spanien</t>
   </si>
   <si>
+    <t>Argentinien</t>
+  </si>
+  <si>
     <t>England</t>
   </si>
   <si>
-    <t>Argentinien</t>
-  </si>
-  <si>
     <t>Portugal</t>
   </si>
   <si>
+    <t>Deutschland</t>
+  </si>
+  <si>
     <t>Brasilien</t>
   </si>
   <si>
-    <t>Deutschland</t>
-  </si>
-  <si>
     <t>Niederlande</t>
   </si>
   <si>
     <t>USA</t>
   </si>
   <si>
+    <t>Norwegen</t>
+  </si>
+  <si>
     <t>Marokko</t>
   </si>
   <si>
-    <t>Norwegen</t>
-  </si>
-  <si>
     <t>Japan</t>
   </si>
   <si>
+    <t>Kolumbien</t>
+  </si>
+  <si>
+    <t>Mexiko</t>
+  </si>
+  <si>
     <t>Belgien</t>
   </si>
   <si>
-    <t>Kolumbien</t>
-  </si>
-  <si>
-    <t>Mexiko</t>
-  </si>
-  <si>
     <t>Schweiz</t>
   </si>
   <si>
     <t>Kroatien</t>
   </si>
   <si>
+    <t>Elfenbeinküste</t>
+  </si>
+  <si>
+    <t>Kanada</t>
+  </si>
+  <si>
     <t>Senegal</t>
   </si>
   <si>
-    <t>Elfenbeinküste</t>
-  </si>
-  <si>
     <t>Österreich</t>
   </si>
   <si>
-    <t>Kanada</t>
+    <t>Schweden</t>
   </si>
   <si>
     <t>Uruguay</t>
   </si>
   <si>
-    <t>Schweden</t>
-  </si>
-  <si>
     <t>Australien</t>
   </si>
   <si>
     <t>Ägypten</t>
   </si>
   <si>
+    <t>Südkorea</t>
+  </si>
+  <si>
     <t>Ecuador</t>
   </si>
   <si>
-    <t>Südkorea</t>
-  </si>
-  <si>
     <t>Schottland</t>
   </si>
   <si>
@@ -181,12 +193,12 @@
     <t>Ghana</t>
   </si>
   <si>
+    <t>Algerien</t>
+  </si>
+  <si>
     <t>Bosnien Herzegowina</t>
   </si>
   <si>
-    <t>Algerien</t>
-  </si>
-  <si>
     <t>Tschechien</t>
   </si>
   <si>
@@ -205,27 +217,24 @@
     <t>Neuseeland</t>
   </si>
   <si>
+    <t>Usbekistan</t>
+  </si>
+  <si>
+    <t>Südafrika</t>
+  </si>
+  <si>
+    <t>Irak</t>
+  </si>
+  <si>
     <t>Panama</t>
   </si>
   <si>
-    <t>Irak</t>
-  </si>
-  <si>
-    <t>Südafrika</t>
-  </si>
-  <si>
-    <t>Usbekistan</t>
-  </si>
-  <si>
-    <t>Jordanien</t>
+    <t>Curacao</t>
   </si>
   <si>
     <t>Katar</t>
   </si>
   <si>
-    <t>Curacao</t>
-  </si>
-  <si>
     <t>11.06.2026</t>
   </si>
   <si>
@@ -242,6 +251,9 @@
   </si>
   <si>
     <t>22.06.2026</t>
+  </si>
+  <si>
+    <t>24.06.2026</t>
   </si>
 </sst>
 </file>
@@ -599,10 +611,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y46"/>
+  <dimension ref="A1:AC45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:25">
+    <row r="1" spans="1:29">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -678,13 +690,25 @@
       <c r="Y1" s="1" t="s">
         <v>24</v>
       </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:29">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C2">
         <v>6.01</v>
@@ -696,7 +720,7 @@
         <v>15.09</v>
       </c>
       <c r="F2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G2">
         <v>5.55</v>
@@ -708,7 +732,7 @@
         <v>16.26</v>
       </c>
       <c r="J2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K2">
         <v>5.55</v>
@@ -720,7 +744,7 @@
         <v>16.3</v>
       </c>
       <c r="N2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="O2">
         <v>4.97</v>
@@ -732,7 +756,7 @@
         <v>18.14</v>
       </c>
       <c r="R2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="S2">
         <v>4.82</v>
@@ -744,7 +768,7 @@
         <v>18.8</v>
       </c>
       <c r="V2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="W2">
         <v>4.87</v>
@@ -755,13 +779,25 @@
       <c r="Y2">
         <v>18.6</v>
       </c>
+      <c r="Z2" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA2">
+        <v>4.87</v>
+      </c>
+      <c r="AB2">
+        <v>17.31</v>
+      </c>
+      <c r="AC2">
+        <v>18.58</v>
+      </c>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:29">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C3">
         <v>5.58</v>
@@ -773,7 +809,7 @@
         <v>16.29</v>
       </c>
       <c r="F3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G3">
         <v>5.63</v>
@@ -785,7 +821,7 @@
         <v>16.04</v>
       </c>
       <c r="J3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K3">
         <v>5.63</v>
@@ -797,7 +833,7 @@
         <v>16.07</v>
       </c>
       <c r="N3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="O3">
         <v>6.51</v>
@@ -809,7 +845,7 @@
         <v>13.76</v>
       </c>
       <c r="R3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="S3">
         <v>6.88</v>
@@ -821,7 +857,7 @@
         <v>13.09</v>
       </c>
       <c r="V3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="W3">
         <v>6.34</v>
@@ -832,167 +868,203 @@
       <c r="Y3">
         <v>14.23</v>
       </c>
+      <c r="Z3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA3">
+        <v>6.48</v>
+      </c>
+      <c r="AB3">
+        <v>13.01</v>
+      </c>
+      <c r="AC3">
+        <v>13.89</v>
+      </c>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:29">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C4">
+        <v>10.19</v>
+      </c>
+      <c r="D4">
+        <v>8.34</v>
+      </c>
+      <c r="E4">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="F4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G4">
+        <v>10.33</v>
+      </c>
+      <c r="H4">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="I4">
+        <v>8.6</v>
+      </c>
+      <c r="J4" t="s">
+        <v>75</v>
+      </c>
+      <c r="K4">
+        <v>10.61</v>
+      </c>
+      <c r="L4">
+        <v>7.95</v>
+      </c>
+      <c r="M4">
+        <v>8.390000000000001</v>
+      </c>
+      <c r="N4" t="s">
+        <v>76</v>
+      </c>
+      <c r="O4">
+        <v>9.4</v>
+      </c>
+      <c r="P4">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="Q4">
+        <v>9.44</v>
+      </c>
+      <c r="R4" t="s">
+        <v>77</v>
+      </c>
+      <c r="S4">
+        <v>9.140000000000001</v>
+      </c>
+      <c r="T4">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="U4">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="V4" t="s">
+        <v>78</v>
+      </c>
+      <c r="W4">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="X4">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="Y4">
+        <v>10.27</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA4">
+        <v>7.45</v>
+      </c>
+      <c r="AB4">
+        <v>11.32</v>
+      </c>
+      <c r="AC4">
+        <v>12.04</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29">
+      <c r="A5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C5">
         <v>8.15</v>
       </c>
-      <c r="D4">
+      <c r="D5">
         <v>10.42</v>
       </c>
-      <c r="E4">
+      <c r="E5">
         <v>11.06</v>
       </c>
-      <c r="F4" t="s">
-        <v>71</v>
-      </c>
-      <c r="G4">
+      <c r="F5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G5">
         <v>8.42</v>
       </c>
-      <c r="H4">
+      <c r="H5">
         <v>9.99</v>
       </c>
-      <c r="I4">
+      <c r="I5">
         <v>10.62</v>
       </c>
-      <c r="J4" t="s">
-        <v>72</v>
-      </c>
-      <c r="K4">
+      <c r="J5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K5">
         <v>8.390000000000001</v>
       </c>
-      <c r="L4">
+      <c r="L5">
         <v>10.06</v>
       </c>
-      <c r="M4">
+      <c r="M5">
         <v>10.69</v>
       </c>
-      <c r="N4" t="s">
+      <c r="N5" t="s">
+        <v>76</v>
+      </c>
+      <c r="O5">
+        <v>8.33</v>
+      </c>
+      <c r="P5">
+        <v>10.02</v>
+      </c>
+      <c r="Q5">
+        <v>10.68</v>
+      </c>
+      <c r="R5" t="s">
+        <v>77</v>
+      </c>
+      <c r="S5">
+        <v>7.04</v>
+      </c>
+      <c r="T5">
+        <v>11.96</v>
+      </c>
+      <c r="U5">
+        <v>12.77</v>
+      </c>
+      <c r="V5" t="s">
+        <v>78</v>
+      </c>
+      <c r="W5">
+        <v>7.11</v>
+      </c>
+      <c r="X5">
+        <v>11.88</v>
+      </c>
+      <c r="Y5">
+        <v>12.65</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA5">
+        <v>7.61</v>
+      </c>
+      <c r="AB5">
+        <v>11.09</v>
+      </c>
+      <c r="AC5">
+        <v>11.79</v>
+      </c>
+    </row>
+    <row r="6" spans="1:29">
+      <c r="A6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" t="s">
         <v>73</v>
-      </c>
-      <c r="O4">
-        <v>8.33</v>
-      </c>
-      <c r="P4">
-        <v>10.02</v>
-      </c>
-      <c r="Q4">
-        <v>10.68</v>
-      </c>
-      <c r="R4" t="s">
-        <v>74</v>
-      </c>
-      <c r="S4">
-        <v>7.04</v>
-      </c>
-      <c r="T4">
-        <v>11.96</v>
-      </c>
-      <c r="U4">
-        <v>12.77</v>
-      </c>
-      <c r="V4" t="s">
-        <v>75</v>
-      </c>
-      <c r="W4">
-        <v>7.11</v>
-      </c>
-      <c r="X4">
-        <v>11.88</v>
-      </c>
-      <c r="Y4">
-        <v>12.65</v>
-      </c>
-    </row>
-    <row r="5" spans="1:25">
-      <c r="A5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B5" t="s">
-        <v>70</v>
-      </c>
-      <c r="C5">
-        <v>10.19</v>
-      </c>
-      <c r="D5">
-        <v>8.34</v>
-      </c>
-      <c r="E5">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="F5" t="s">
-        <v>71</v>
-      </c>
-      <c r="G5">
-        <v>10.33</v>
-      </c>
-      <c r="H5">
-        <v>8.140000000000001</v>
-      </c>
-      <c r="I5">
-        <v>8.6</v>
-      </c>
-      <c r="J5" t="s">
-        <v>72</v>
-      </c>
-      <c r="K5">
-        <v>10.61</v>
-      </c>
-      <c r="L5">
-        <v>7.95</v>
-      </c>
-      <c r="M5">
-        <v>8.390000000000001</v>
-      </c>
-      <c r="N5" t="s">
-        <v>73</v>
-      </c>
-      <c r="O5">
-        <v>9.4</v>
-      </c>
-      <c r="P5">
-        <v>8.880000000000001</v>
-      </c>
-      <c r="Q5">
-        <v>9.44</v>
-      </c>
-      <c r="R5" t="s">
-        <v>74</v>
-      </c>
-      <c r="S5">
-        <v>9.140000000000001</v>
-      </c>
-      <c r="T5">
-        <v>9.220000000000001</v>
-      </c>
-      <c r="U5">
-        <v>9.779999999999999</v>
-      </c>
-      <c r="V5" t="s">
-        <v>75</v>
-      </c>
-      <c r="W5">
-        <v>8.710000000000001</v>
-      </c>
-      <c r="X5">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="Y5">
-        <v>10.27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25">
-      <c r="A6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" t="s">
-        <v>70</v>
       </c>
       <c r="C6">
         <v>8.85</v>
@@ -1004,7 +1076,7 @@
         <v>10.17</v>
       </c>
       <c r="F6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G6">
         <v>8.699999999999999</v>
@@ -1016,7 +1088,7 @@
         <v>10.26</v>
       </c>
       <c r="J6" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K6">
         <v>8.630000000000001</v>
@@ -1028,7 +1100,7 @@
         <v>10.38</v>
       </c>
       <c r="N6" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="O6">
         <v>8.619999999999999</v>
@@ -1040,7 +1112,7 @@
         <v>10.32</v>
       </c>
       <c r="R6" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="S6">
         <v>10.63</v>
@@ -1052,7 +1124,7 @@
         <v>8.359999999999999</v>
       </c>
       <c r="V6" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="W6">
         <v>11.67</v>
@@ -1063,167 +1135,203 @@
       <c r="Y6">
         <v>7.59</v>
       </c>
+      <c r="Z6" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA6">
+        <v>10.83</v>
+      </c>
+      <c r="AB6">
+        <v>7.79</v>
+      </c>
+      <c r="AC6">
+        <v>8.19</v>
+      </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:29">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C7">
+        <v>15.6</v>
+      </c>
+      <c r="D7">
+        <v>5.44</v>
+      </c>
+      <c r="E7">
+        <v>5.65</v>
+      </c>
+      <c r="F7" t="s">
+        <v>74</v>
+      </c>
+      <c r="G7">
+        <v>15.67</v>
+      </c>
+      <c r="H7">
+        <v>5.37</v>
+      </c>
+      <c r="I7">
+        <v>5.57</v>
+      </c>
+      <c r="J7" t="s">
+        <v>75</v>
+      </c>
+      <c r="K7">
+        <v>15.39</v>
+      </c>
+      <c r="L7">
+        <v>5.48</v>
+      </c>
+      <c r="M7">
+        <v>5.7</v>
+      </c>
+      <c r="N7" t="s">
+        <v>76</v>
+      </c>
+      <c r="O7">
+        <v>14.67</v>
+      </c>
+      <c r="P7">
+        <v>5.69</v>
+      </c>
+      <c r="Q7">
+        <v>5.93</v>
+      </c>
+      <c r="R7" t="s">
+        <v>77</v>
+      </c>
+      <c r="S7">
+        <v>14.87</v>
+      </c>
+      <c r="T7">
+        <v>5.67</v>
+      </c>
+      <c r="U7">
+        <v>5.9</v>
+      </c>
+      <c r="V7" t="s">
+        <v>78</v>
+      </c>
+      <c r="W7">
+        <v>14.53</v>
+      </c>
+      <c r="X7">
+        <v>5.81</v>
+      </c>
+      <c r="Y7">
+        <v>6.03</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA7">
+        <v>14.6</v>
+      </c>
+      <c r="AB7">
+        <v>5.78</v>
+      </c>
+      <c r="AC7">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29">
+      <c r="A8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" t="s">
+        <v>73</v>
+      </c>
+      <c r="C8">
         <v>9.970000000000001</v>
       </c>
-      <c r="D7">
+      <c r="D8">
         <v>8.52</v>
       </c>
-      <c r="E7">
+      <c r="E8">
         <v>8.99</v>
       </c>
-      <c r="F7" t="s">
-        <v>71</v>
-      </c>
-      <c r="G7">
+      <c r="F8" t="s">
+        <v>74</v>
+      </c>
+      <c r="G8">
         <v>10.11</v>
       </c>
-      <c r="H7">
+      <c r="H8">
         <v>8.32</v>
       </c>
-      <c r="I7">
+      <c r="I8">
         <v>8.789999999999999</v>
       </c>
-      <c r="J7" t="s">
-        <v>72</v>
-      </c>
-      <c r="K7">
+      <c r="J8" t="s">
+        <v>75</v>
+      </c>
+      <c r="K8">
         <v>11.04</v>
       </c>
-      <c r="L7">
+      <c r="L8">
         <v>7.64</v>
       </c>
-      <c r="M7">
+      <c r="M8">
         <v>8.050000000000001</v>
       </c>
-      <c r="N7" t="s">
+      <c r="N8" t="s">
+        <v>76</v>
+      </c>
+      <c r="O8">
+        <v>11.39</v>
+      </c>
+      <c r="P8">
+        <v>7.33</v>
+      </c>
+      <c r="Q8">
+        <v>7.74</v>
+      </c>
+      <c r="R8" t="s">
+        <v>77</v>
+      </c>
+      <c r="S8">
+        <v>12.2</v>
+      </c>
+      <c r="T8">
+        <v>6.91</v>
+      </c>
+      <c r="U8">
+        <v>7.25</v>
+      </c>
+      <c r="V8" t="s">
+        <v>78</v>
+      </c>
+      <c r="W8">
+        <v>13.17</v>
+      </c>
+      <c r="X8">
+        <v>6.41</v>
+      </c>
+      <c r="Y8">
+        <v>6.69</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA8">
+        <v>14.94</v>
+      </c>
+      <c r="AB8">
+        <v>5.65</v>
+      </c>
+      <c r="AC8">
+        <v>5.85</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29">
+      <c r="A9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" t="s">
         <v>73</v>
-      </c>
-      <c r="O7">
-        <v>11.39</v>
-      </c>
-      <c r="P7">
-        <v>7.33</v>
-      </c>
-      <c r="Q7">
-        <v>7.74</v>
-      </c>
-      <c r="R7" t="s">
-        <v>74</v>
-      </c>
-      <c r="S7">
-        <v>12.2</v>
-      </c>
-      <c r="T7">
-        <v>6.91</v>
-      </c>
-      <c r="U7">
-        <v>7.25</v>
-      </c>
-      <c r="V7" t="s">
-        <v>75</v>
-      </c>
-      <c r="W7">
-        <v>13.17</v>
-      </c>
-      <c r="X7">
-        <v>6.41</v>
-      </c>
-      <c r="Y7">
-        <v>6.69</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25">
-      <c r="A8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B8" t="s">
-        <v>70</v>
-      </c>
-      <c r="C8">
-        <v>15.6</v>
-      </c>
-      <c r="D8">
-        <v>5.44</v>
-      </c>
-      <c r="E8">
-        <v>5.65</v>
-      </c>
-      <c r="F8" t="s">
-        <v>71</v>
-      </c>
-      <c r="G8">
-        <v>15.67</v>
-      </c>
-      <c r="H8">
-        <v>5.37</v>
-      </c>
-      <c r="I8">
-        <v>5.57</v>
-      </c>
-      <c r="J8" t="s">
-        <v>72</v>
-      </c>
-      <c r="K8">
-        <v>15.39</v>
-      </c>
-      <c r="L8">
-        <v>5.48</v>
-      </c>
-      <c r="M8">
-        <v>5.7</v>
-      </c>
-      <c r="N8" t="s">
-        <v>73</v>
-      </c>
-      <c r="O8">
-        <v>14.67</v>
-      </c>
-      <c r="P8">
-        <v>5.69</v>
-      </c>
-      <c r="Q8">
-        <v>5.93</v>
-      </c>
-      <c r="R8" t="s">
-        <v>74</v>
-      </c>
-      <c r="S8">
-        <v>14.87</v>
-      </c>
-      <c r="T8">
-        <v>5.67</v>
-      </c>
-      <c r="U8">
-        <v>5.9</v>
-      </c>
-      <c r="V8" t="s">
-        <v>75</v>
-      </c>
-      <c r="W8">
-        <v>14.53</v>
-      </c>
-      <c r="X8">
-        <v>5.81</v>
-      </c>
-      <c r="Y8">
-        <v>6.03</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25">
-      <c r="A9" t="s">
-        <v>32</v>
-      </c>
-      <c r="B9" t="s">
-        <v>70</v>
       </c>
       <c r="C9">
         <v>21.29</v>
@@ -1235,7 +1343,7 @@
         <v>4.07</v>
       </c>
       <c r="F9" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G9">
         <v>20.29</v>
@@ -1247,7 +1355,7 @@
         <v>4.24</v>
       </c>
       <c r="J9" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K9">
         <v>19.71</v>
@@ -1259,7 +1367,7 @@
         <v>4.38</v>
       </c>
       <c r="N9" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="O9">
         <v>20.14</v>
@@ -1271,7 +1379,7 @@
         <v>4.24</v>
       </c>
       <c r="R9" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="S9">
         <v>21</v>
@@ -1283,7 +1391,7 @@
         <v>4.09</v>
       </c>
       <c r="V9" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="W9">
         <v>17.53</v>
@@ -1294,13 +1402,25 @@
       <c r="Y9">
         <v>4.95</v>
       </c>
+      <c r="Z9" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA9">
+        <v>17.23</v>
+      </c>
+      <c r="AB9">
+        <v>4.9</v>
+      </c>
+      <c r="AC9">
+        <v>5.03</v>
+      </c>
     </row>
-    <row r="10" spans="1:25">
+    <row r="10" spans="1:29">
       <c r="A10" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C10">
         <v>63.71</v>
@@ -1312,7 +1432,7 @@
         <v>1.2</v>
       </c>
       <c r="F10" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G10">
         <v>44.57</v>
@@ -1324,7 +1444,7 @@
         <v>1.78</v>
       </c>
       <c r="J10" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K10">
         <v>43.86</v>
@@ -1336,7 +1456,7 @@
         <v>1.82</v>
       </c>
       <c r="N10" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="O10">
         <v>41.14</v>
@@ -1348,7 +1468,7 @@
         <v>1.93</v>
       </c>
       <c r="R10" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="S10">
         <v>42</v>
@@ -1360,7 +1480,7 @@
         <v>1.91</v>
       </c>
       <c r="V10" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="W10">
         <v>31.43</v>
@@ -1371,167 +1491,203 @@
       <c r="Y10">
         <v>2.63</v>
       </c>
+      <c r="Z10" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA10">
+        <v>32.14</v>
+      </c>
+      <c r="AB10">
+        <v>2.62</v>
+      </c>
+      <c r="AC10">
+        <v>2.56</v>
+      </c>
     </row>
-    <row r="11" spans="1:25">
+    <row r="11" spans="1:29">
       <c r="A11" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B11" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C11">
+        <v>32.29</v>
+      </c>
+      <c r="D11">
+        <v>2.63</v>
+      </c>
+      <c r="E11">
+        <v>2.6</v>
+      </c>
+      <c r="F11" t="s">
+        <v>74</v>
+      </c>
+      <c r="G11">
+        <v>33</v>
+      </c>
+      <c r="H11">
+        <v>2.55</v>
+      </c>
+      <c r="I11">
+        <v>2.49</v>
+      </c>
+      <c r="J11" t="s">
+        <v>75</v>
+      </c>
+      <c r="K11">
+        <v>34.14</v>
+      </c>
+      <c r="L11">
+        <v>2.47</v>
+      </c>
+      <c r="M11">
+        <v>2.42</v>
+      </c>
+      <c r="N11" t="s">
+        <v>76</v>
+      </c>
+      <c r="O11">
+        <v>30.43</v>
+      </c>
+      <c r="P11">
+        <v>2.74</v>
+      </c>
+      <c r="Q11">
+        <v>2.71</v>
+      </c>
+      <c r="R11" t="s">
+        <v>77</v>
+      </c>
+      <c r="S11">
+        <v>31.5</v>
+      </c>
+      <c r="T11">
+        <v>2.67</v>
+      </c>
+      <c r="U11">
+        <v>2.64</v>
+      </c>
+      <c r="V11" t="s">
+        <v>78</v>
+      </c>
+      <c r="W11">
+        <v>36.57</v>
+      </c>
+      <c r="X11">
+        <v>2.31</v>
+      </c>
+      <c r="Y11">
+        <v>2.22</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA11">
+        <v>32.43</v>
+      </c>
+      <c r="AB11">
+        <v>2.6</v>
+      </c>
+      <c r="AC11">
+        <v>2.53</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29">
+      <c r="A12" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C12">
         <v>49.86</v>
       </c>
-      <c r="D11">
+      <c r="D12">
         <v>1.7</v>
       </c>
-      <c r="E11">
+      <c r="E12">
         <v>1.59</v>
       </c>
-      <c r="F11" t="s">
-        <v>71</v>
-      </c>
-      <c r="G11">
+      <c r="F12" t="s">
+        <v>74</v>
+      </c>
+      <c r="G12">
         <v>50.57</v>
       </c>
-      <c r="H11">
+      <c r="H12">
         <v>1.66</v>
       </c>
-      <c r="I11">
+      <c r="I12">
         <v>1.54</v>
       </c>
-      <c r="J11" t="s">
-        <v>72</v>
-      </c>
-      <c r="K11">
+      <c r="J12" t="s">
+        <v>75</v>
+      </c>
+      <c r="K12">
         <v>38.71</v>
       </c>
-      <c r="L11">
+      <c r="L12">
         <v>2.18</v>
       </c>
-      <c r="M11">
+      <c r="M12">
         <v>2.1</v>
       </c>
-      <c r="N11" t="s">
+      <c r="N12" t="s">
+        <v>76</v>
+      </c>
+      <c r="O12">
+        <v>37.71</v>
+      </c>
+      <c r="P12">
+        <v>2.21</v>
+      </c>
+      <c r="Q12">
+        <v>2.13</v>
+      </c>
+      <c r="R12" t="s">
+        <v>77</v>
+      </c>
+      <c r="S12">
+        <v>40.67</v>
+      </c>
+      <c r="T12">
+        <v>2.07</v>
+      </c>
+      <c r="U12">
+        <v>1.98</v>
+      </c>
+      <c r="V12" t="s">
+        <v>78</v>
+      </c>
+      <c r="W12">
+        <v>32.86</v>
+      </c>
+      <c r="X12">
+        <v>2.57</v>
+      </c>
+      <c r="Y12">
+        <v>2.51</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA12">
+        <v>35.14</v>
+      </c>
+      <c r="AB12">
+        <v>2.4</v>
+      </c>
+      <c r="AC12">
+        <v>2.32</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29">
+      <c r="A13" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" t="s">
         <v>73</v>
-      </c>
-      <c r="O11">
-        <v>37.71</v>
-      </c>
-      <c r="P11">
-        <v>2.21</v>
-      </c>
-      <c r="Q11">
-        <v>2.13</v>
-      </c>
-      <c r="R11" t="s">
-        <v>74</v>
-      </c>
-      <c r="S11">
-        <v>40.67</v>
-      </c>
-      <c r="T11">
-        <v>2.07</v>
-      </c>
-      <c r="U11">
-        <v>1.98</v>
-      </c>
-      <c r="V11" t="s">
-        <v>75</v>
-      </c>
-      <c r="W11">
-        <v>32.86</v>
-      </c>
-      <c r="X11">
-        <v>2.57</v>
-      </c>
-      <c r="Y11">
-        <v>2.51</v>
-      </c>
-    </row>
-    <row r="12" spans="1:25">
-      <c r="A12" t="s">
-        <v>35</v>
-      </c>
-      <c r="B12" t="s">
-        <v>70</v>
-      </c>
-      <c r="C12">
-        <v>32.29</v>
-      </c>
-      <c r="D12">
-        <v>2.63</v>
-      </c>
-      <c r="E12">
-        <v>2.6</v>
-      </c>
-      <c r="F12" t="s">
-        <v>71</v>
-      </c>
-      <c r="G12">
-        <v>33</v>
-      </c>
-      <c r="H12">
-        <v>2.55</v>
-      </c>
-      <c r="I12">
-        <v>2.49</v>
-      </c>
-      <c r="J12" t="s">
-        <v>72</v>
-      </c>
-      <c r="K12">
-        <v>34.14</v>
-      </c>
-      <c r="L12">
-        <v>2.47</v>
-      </c>
-      <c r="M12">
-        <v>2.42</v>
-      </c>
-      <c r="N12" t="s">
-        <v>73</v>
-      </c>
-      <c r="O12">
-        <v>30.43</v>
-      </c>
-      <c r="P12">
-        <v>2.74</v>
-      </c>
-      <c r="Q12">
-        <v>2.71</v>
-      </c>
-      <c r="R12" t="s">
-        <v>74</v>
-      </c>
-      <c r="S12">
-        <v>31.5</v>
-      </c>
-      <c r="T12">
-        <v>2.67</v>
-      </c>
-      <c r="U12">
-        <v>2.64</v>
-      </c>
-      <c r="V12" t="s">
-        <v>75</v>
-      </c>
-      <c r="W12">
-        <v>36.57</v>
-      </c>
-      <c r="X12">
-        <v>2.31</v>
-      </c>
-      <c r="Y12">
-        <v>2.22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25">
-      <c r="A13" t="s">
-        <v>36</v>
-      </c>
-      <c r="B13" t="s">
-        <v>70</v>
       </c>
       <c r="C13">
         <v>53.43</v>
@@ -1543,7 +1699,7 @@
         <v>1.47</v>
       </c>
       <c r="F13" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G13">
         <v>53.43</v>
@@ -1555,7 +1711,7 @@
         <v>1.44</v>
       </c>
       <c r="J13" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K13">
         <v>51.29</v>
@@ -1567,7 +1723,7 @@
         <v>1.52</v>
       </c>
       <c r="N13" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="O13">
         <v>51.29</v>
@@ -1579,7 +1735,7 @@
         <v>1.49</v>
       </c>
       <c r="R13" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="S13">
         <v>53</v>
@@ -1591,7 +1747,7 @@
         <v>1.46</v>
       </c>
       <c r="V13" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="W13">
         <v>42.86</v>
@@ -1602,244 +1758,292 @@
       <c r="Y13">
         <v>1.86</v>
       </c>
+      <c r="Z13" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA13">
+        <v>40</v>
+      </c>
+      <c r="AB13">
+        <v>2.11</v>
+      </c>
+      <c r="AC13">
+        <v>2</v>
+      </c>
     </row>
-    <row r="14" spans="1:25">
+    <row r="14" spans="1:29">
       <c r="A14" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B14" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C14">
+        <v>41.71</v>
+      </c>
+      <c r="D14">
+        <v>2.04</v>
+      </c>
+      <c r="E14">
+        <v>1.95</v>
+      </c>
+      <c r="F14" t="s">
+        <v>74</v>
+      </c>
+      <c r="G14">
+        <v>45.57</v>
+      </c>
+      <c r="H14">
+        <v>1.85</v>
+      </c>
+      <c r="I14">
+        <v>1.73</v>
+      </c>
+      <c r="J14" t="s">
+        <v>75</v>
+      </c>
+      <c r="K14">
+        <v>47</v>
+      </c>
+      <c r="L14">
+        <v>1.8</v>
+      </c>
+      <c r="M14">
+        <v>1.68</v>
+      </c>
+      <c r="N14" t="s">
+        <v>76</v>
+      </c>
+      <c r="O14">
+        <v>50.43</v>
+      </c>
+      <c r="P14">
+        <v>1.66</v>
+      </c>
+      <c r="Q14">
+        <v>1.52</v>
+      </c>
+      <c r="R14" t="s">
+        <v>77</v>
+      </c>
+      <c r="S14">
+        <v>48</v>
+      </c>
+      <c r="T14">
+        <v>1.76</v>
+      </c>
+      <c r="U14">
+        <v>1.64</v>
+      </c>
+      <c r="V14" t="s">
+        <v>78</v>
+      </c>
+      <c r="W14">
+        <v>49.86</v>
+      </c>
+      <c r="X14">
+        <v>1.69</v>
+      </c>
+      <c r="Y14">
+        <v>1.56</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA14">
+        <v>47</v>
+      </c>
+      <c r="AB14">
+        <v>1.8</v>
+      </c>
+      <c r="AC14">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29">
+      <c r="A15" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15">
+        <v>68.43000000000001</v>
+      </c>
+      <c r="D15">
+        <v>1.24</v>
+      </c>
+      <c r="E15">
+        <v>1.1</v>
+      </c>
+      <c r="F15" t="s">
+        <v>74</v>
+      </c>
+      <c r="G15">
+        <v>52.71</v>
+      </c>
+      <c r="H15">
+        <v>1.6</v>
+      </c>
+      <c r="I15">
+        <v>1.46</v>
+      </c>
+      <c r="J15" t="s">
+        <v>75</v>
+      </c>
+      <c r="K15">
+        <v>52.71</v>
+      </c>
+      <c r="L15">
+        <v>1.6</v>
+      </c>
+      <c r="M15">
+        <v>1.47</v>
+      </c>
+      <c r="N15" t="s">
+        <v>76</v>
+      </c>
+      <c r="O15">
+        <v>57.86</v>
+      </c>
+      <c r="P15">
+        <v>1.44</v>
+      </c>
+      <c r="Q15">
+        <v>1.29</v>
+      </c>
+      <c r="R15" t="s">
+        <v>77</v>
+      </c>
+      <c r="S15">
+        <v>47.17</v>
+      </c>
+      <c r="T15">
+        <v>1.79</v>
+      </c>
+      <c r="U15">
+        <v>1.67</v>
+      </c>
+      <c r="V15" t="s">
+        <v>78</v>
+      </c>
+      <c r="W15">
+        <v>51.14</v>
+      </c>
+      <c r="X15">
+        <v>1.65</v>
+      </c>
+      <c r="Y15">
+        <v>1.51</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA15">
+        <v>52.57</v>
+      </c>
+      <c r="AB15">
+        <v>1.6</v>
+      </c>
+      <c r="AC15">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29">
+      <c r="A16" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" t="s">
+        <v>73</v>
+      </c>
+      <c r="C16">
         <v>37.71</v>
       </c>
-      <c r="D14">
+      <c r="D16">
         <v>2.25</v>
       </c>
-      <c r="E14">
+      <c r="E16">
         <v>2.19</v>
       </c>
-      <c r="F14" t="s">
-        <v>71</v>
-      </c>
-      <c r="G14">
+      <c r="F16" t="s">
+        <v>74</v>
+      </c>
+      <c r="G16">
         <v>37.71</v>
       </c>
-      <c r="H14">
+      <c r="H16">
         <v>2.23</v>
       </c>
-      <c r="I14">
+      <c r="I16">
         <v>2.15</v>
       </c>
-      <c r="J14" t="s">
-        <v>72</v>
-      </c>
-      <c r="K14">
+      <c r="J16" t="s">
+        <v>75</v>
+      </c>
+      <c r="K16">
         <v>39.43</v>
       </c>
-      <c r="L14">
+      <c r="L16">
         <v>2.14</v>
       </c>
-      <c r="M14">
+      <c r="M16">
         <v>2.06</v>
       </c>
-      <c r="N14" t="s">
+      <c r="N16" t="s">
+        <v>76</v>
+      </c>
+      <c r="O16">
+        <v>42</v>
+      </c>
+      <c r="P16">
+        <v>1.99</v>
+      </c>
+      <c r="Q16">
+        <v>1.88</v>
+      </c>
+      <c r="R16" t="s">
+        <v>77</v>
+      </c>
+      <c r="S16">
+        <v>42.17</v>
+      </c>
+      <c r="T16">
+        <v>2</v>
+      </c>
+      <c r="U16">
+        <v>1.9</v>
+      </c>
+      <c r="V16" t="s">
+        <v>78</v>
+      </c>
+      <c r="W16">
+        <v>47.71</v>
+      </c>
+      <c r="X16">
+        <v>1.77</v>
+      </c>
+      <c r="Y16">
+        <v>1.64</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA16">
+        <v>52.71</v>
+      </c>
+      <c r="AB16">
+        <v>1.6</v>
+      </c>
+      <c r="AC16">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="17" spans="1:29">
+      <c r="A17" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" t="s">
         <v>73</v>
-      </c>
-      <c r="O14">
-        <v>42</v>
-      </c>
-      <c r="P14">
-        <v>1.99</v>
-      </c>
-      <c r="Q14">
-        <v>1.88</v>
-      </c>
-      <c r="R14" t="s">
-        <v>74</v>
-      </c>
-      <c r="S14">
-        <v>42.17</v>
-      </c>
-      <c r="T14">
-        <v>2</v>
-      </c>
-      <c r="U14">
-        <v>1.9</v>
-      </c>
-      <c r="V14" t="s">
-        <v>75</v>
-      </c>
-      <c r="W14">
-        <v>47.71</v>
-      </c>
-      <c r="X14">
-        <v>1.77</v>
-      </c>
-      <c r="Y14">
-        <v>1.64</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25">
-      <c r="A15" t="s">
-        <v>38</v>
-      </c>
-      <c r="B15" t="s">
-        <v>70</v>
-      </c>
-      <c r="C15">
-        <v>41.71</v>
-      </c>
-      <c r="D15">
-        <v>2.04</v>
-      </c>
-      <c r="E15">
-        <v>1.95</v>
-      </c>
-      <c r="F15" t="s">
-        <v>71</v>
-      </c>
-      <c r="G15">
-        <v>45.57</v>
-      </c>
-      <c r="H15">
-        <v>1.85</v>
-      </c>
-      <c r="I15">
-        <v>1.73</v>
-      </c>
-      <c r="J15" t="s">
-        <v>72</v>
-      </c>
-      <c r="K15">
-        <v>47</v>
-      </c>
-      <c r="L15">
-        <v>1.8</v>
-      </c>
-      <c r="M15">
-        <v>1.68</v>
-      </c>
-      <c r="N15" t="s">
-        <v>73</v>
-      </c>
-      <c r="O15">
-        <v>50.43</v>
-      </c>
-      <c r="P15">
-        <v>1.66</v>
-      </c>
-      <c r="Q15">
-        <v>1.52</v>
-      </c>
-      <c r="R15" t="s">
-        <v>74</v>
-      </c>
-      <c r="S15">
-        <v>48</v>
-      </c>
-      <c r="T15">
-        <v>1.76</v>
-      </c>
-      <c r="U15">
-        <v>1.64</v>
-      </c>
-      <c r="V15" t="s">
-        <v>75</v>
-      </c>
-      <c r="W15">
-        <v>49.86</v>
-      </c>
-      <c r="X15">
-        <v>1.69</v>
-      </c>
-      <c r="Y15">
-        <v>1.56</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25">
-      <c r="A16" t="s">
-        <v>39</v>
-      </c>
-      <c r="B16" t="s">
-        <v>70</v>
-      </c>
-      <c r="C16">
-        <v>68.43000000000001</v>
-      </c>
-      <c r="D16">
-        <v>1.24</v>
-      </c>
-      <c r="E16">
-        <v>1.1</v>
-      </c>
-      <c r="F16" t="s">
-        <v>71</v>
-      </c>
-      <c r="G16">
-        <v>52.71</v>
-      </c>
-      <c r="H16">
-        <v>1.6</v>
-      </c>
-      <c r="I16">
-        <v>1.46</v>
-      </c>
-      <c r="J16" t="s">
-        <v>72</v>
-      </c>
-      <c r="K16">
-        <v>52.71</v>
-      </c>
-      <c r="L16">
-        <v>1.6</v>
-      </c>
-      <c r="M16">
-        <v>1.47</v>
-      </c>
-      <c r="N16" t="s">
-        <v>73</v>
-      </c>
-      <c r="O16">
-        <v>57.86</v>
-      </c>
-      <c r="P16">
-        <v>1.44</v>
-      </c>
-      <c r="Q16">
-        <v>1.29</v>
-      </c>
-      <c r="R16" t="s">
-        <v>74</v>
-      </c>
-      <c r="S16">
-        <v>47.17</v>
-      </c>
-      <c r="T16">
-        <v>1.79</v>
-      </c>
-      <c r="U16">
-        <v>1.67</v>
-      </c>
-      <c r="V16" t="s">
-        <v>75</v>
-      </c>
-      <c r="W16">
-        <v>51.14</v>
-      </c>
-      <c r="X16">
-        <v>1.65</v>
-      </c>
-      <c r="Y16">
-        <v>1.51</v>
-      </c>
-    </row>
-    <row r="17" spans="1:25">
-      <c r="A17" t="s">
-        <v>40</v>
-      </c>
-      <c r="B17" t="s">
-        <v>70</v>
       </c>
       <c r="C17">
         <v>74.43000000000001</v>
@@ -1851,7 +2055,7 @@
         <v>0.99</v>
       </c>
       <c r="F17" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G17">
         <v>75.14</v>
@@ -1863,7 +2067,7 @@
         <v>0.95</v>
       </c>
       <c r="J17" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K17">
         <v>83.56999999999999</v>
@@ -1875,7 +2079,7 @@
         <v>0.84</v>
       </c>
       <c r="N17" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="O17">
         <v>87.70999999999999</v>
@@ -1887,7 +2091,7 @@
         <v>0.77</v>
       </c>
       <c r="R17" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="S17">
         <v>78</v>
@@ -1899,7 +2103,7 @@
         <v>0.92</v>
       </c>
       <c r="V17" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="W17">
         <v>81.43000000000001</v>
@@ -1910,13 +2114,25 @@
       <c r="Y17">
         <v>0.86</v>
       </c>
+      <c r="Z17" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA17">
+        <v>80.14</v>
+      </c>
+      <c r="AB17">
+        <v>1.05</v>
+      </c>
+      <c r="AC17">
+        <v>0.87</v>
+      </c>
     </row>
-    <row r="18" spans="1:25">
+    <row r="18" spans="1:29">
       <c r="A18" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B18" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C18">
         <v>88.86</v>
@@ -1928,7 +2144,7 @@
         <v>0.8</v>
       </c>
       <c r="F18" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G18">
         <v>91.70999999999999</v>
@@ -1940,7 +2156,7 @@
         <v>0.74</v>
       </c>
       <c r="J18" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K18">
         <v>91.70999999999999</v>
@@ -1952,7 +2168,7 @@
         <v>0.75</v>
       </c>
       <c r="N18" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="O18">
         <v>92.43000000000001</v>
@@ -1964,7 +2180,7 @@
         <v>0.72</v>
       </c>
       <c r="R18" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="S18">
         <v>110.83</v>
@@ -1976,7 +2192,7 @@
         <v>0.58</v>
       </c>
       <c r="V18" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="W18">
         <v>123</v>
@@ -1987,475 +2203,559 @@
       <c r="Y18">
         <v>0.5</v>
       </c>
+      <c r="Z18" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA18">
+        <v>112.29</v>
+      </c>
+      <c r="AB18">
+        <v>0.75</v>
+      </c>
+      <c r="AC18">
+        <v>0.5600000000000001</v>
+      </c>
     </row>
-    <row r="19" spans="1:25">
+    <row r="19" spans="1:29">
       <c r="A19" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B19" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C19">
+        <v>250</v>
+      </c>
+      <c r="D19">
+        <v>0.34</v>
+      </c>
+      <c r="E19">
+        <v>0.18</v>
+      </c>
+      <c r="F19" t="s">
+        <v>74</v>
+      </c>
+      <c r="G19">
+        <v>259.86</v>
+      </c>
+      <c r="H19">
+        <v>0.32</v>
+      </c>
+      <c r="I19">
+        <v>0.16</v>
+      </c>
+      <c r="J19" t="s">
+        <v>75</v>
+      </c>
+      <c r="K19">
+        <v>153</v>
+      </c>
+      <c r="L19">
+        <v>0.55</v>
+      </c>
+      <c r="M19">
+        <v>0.37</v>
+      </c>
+      <c r="N19" t="s">
+        <v>76</v>
+      </c>
+      <c r="O19">
+        <v>143</v>
+      </c>
+      <c r="P19">
+        <v>0.58</v>
+      </c>
+      <c r="Q19">
+        <v>0.4</v>
+      </c>
+      <c r="R19" t="s">
+        <v>77</v>
+      </c>
+      <c r="S19">
+        <v>144.83</v>
+      </c>
+      <c r="T19">
+        <v>0.58</v>
+      </c>
+      <c r="U19">
+        <v>0.4</v>
+      </c>
+      <c r="V19" t="s">
+        <v>78</v>
+      </c>
+      <c r="W19">
+        <v>133.71</v>
+      </c>
+      <c r="X19">
+        <v>0.63</v>
+      </c>
+      <c r="Y19">
+        <v>0.44</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA19">
+        <v>137.86</v>
+      </c>
+      <c r="AB19">
+        <v>0.61</v>
+      </c>
+      <c r="AC19">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="20" spans="1:29">
+      <c r="A20" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" t="s">
+        <v>73</v>
+      </c>
+      <c r="C20">
+        <v>191.71</v>
+      </c>
+      <c r="D20">
+        <v>0.44</v>
+      </c>
+      <c r="E20">
+        <v>0.28</v>
+      </c>
+      <c r="F20" t="s">
+        <v>74</v>
+      </c>
+      <c r="G20">
+        <v>222.71</v>
+      </c>
+      <c r="H20">
+        <v>0.38</v>
+      </c>
+      <c r="I20">
+        <v>0.21</v>
+      </c>
+      <c r="J20" t="s">
+        <v>75</v>
+      </c>
+      <c r="K20">
+        <v>193.29</v>
+      </c>
+      <c r="L20">
+        <v>0.44</v>
+      </c>
+      <c r="M20">
+        <v>0.26</v>
+      </c>
+      <c r="N20" t="s">
+        <v>76</v>
+      </c>
+      <c r="O20">
+        <v>197.43</v>
+      </c>
+      <c r="P20">
+        <v>0.42</v>
+      </c>
+      <c r="Q20">
+        <v>0.24</v>
+      </c>
+      <c r="R20" t="s">
+        <v>77</v>
+      </c>
+      <c r="S20">
+        <v>148.17</v>
+      </c>
+      <c r="T20">
+        <v>0.57</v>
+      </c>
+      <c r="U20">
+        <v>0.39</v>
+      </c>
+      <c r="V20" t="s">
+        <v>78</v>
+      </c>
+      <c r="W20">
+        <v>140</v>
+      </c>
+      <c r="X20">
+        <v>0.6</v>
+      </c>
+      <c r="Y20">
+        <v>0.41</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA20">
+        <v>138.57</v>
+      </c>
+      <c r="AB20">
+        <v>0.61</v>
+      </c>
+      <c r="AC20">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="21" spans="1:29">
+      <c r="A21" t="s">
+        <v>48</v>
+      </c>
+      <c r="B21" t="s">
+        <v>73</v>
+      </c>
+      <c r="C21">
         <v>101.29</v>
       </c>
-      <c r="D19">
+      <c r="D21">
         <v>0.84</v>
       </c>
-      <c r="E19">
+      <c r="E21">
         <v>0.67</v>
       </c>
-      <c r="F19" t="s">
-        <v>71</v>
-      </c>
-      <c r="G19">
+      <c r="F21" t="s">
+        <v>74</v>
+      </c>
+      <c r="G21">
         <v>106.14</v>
       </c>
-      <c r="H19">
+      <c r="H21">
         <v>0.79</v>
       </c>
-      <c r="I19">
+      <c r="I21">
         <v>0.61</v>
       </c>
-      <c r="J19" t="s">
-        <v>72</v>
-      </c>
-      <c r="K19">
+      <c r="J21" t="s">
+        <v>75</v>
+      </c>
+      <c r="K21">
         <v>107.57</v>
       </c>
-      <c r="L19">
+      <c r="L21">
         <v>0.78</v>
       </c>
-      <c r="M19">
+      <c r="M21">
         <v>0.61</v>
       </c>
-      <c r="N19" t="s">
+      <c r="N21" t="s">
+        <v>76</v>
+      </c>
+      <c r="O21">
+        <v>119.57</v>
+      </c>
+      <c r="P21">
+        <v>0.7</v>
+      </c>
+      <c r="Q21">
+        <v>0.51</v>
+      </c>
+      <c r="R21" t="s">
+        <v>77</v>
+      </c>
+      <c r="S21">
+        <v>115.17</v>
+      </c>
+      <c r="T21">
+        <v>0.73</v>
+      </c>
+      <c r="U21">
+        <v>0.55</v>
+      </c>
+      <c r="V21" t="s">
+        <v>78</v>
+      </c>
+      <c r="W21">
+        <v>125.86</v>
+      </c>
+      <c r="X21">
+        <v>0.67</v>
+      </c>
+      <c r="Y21">
+        <v>0.48</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA21">
+        <v>153.57</v>
+      </c>
+      <c r="AB21">
+        <v>0.55</v>
+      </c>
+      <c r="AC21">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="22" spans="1:29">
+      <c r="A22" t="s">
+        <v>49</v>
+      </c>
+      <c r="B22" t="s">
         <v>73</v>
       </c>
-      <c r="O19">
-        <v>119.57</v>
-      </c>
-      <c r="P19">
-        <v>0.7</v>
-      </c>
-      <c r="Q19">
-        <v>0.51</v>
-      </c>
-      <c r="R19" t="s">
+      <c r="C22">
+        <v>153</v>
+      </c>
+      <c r="D22">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E22">
+        <v>0.39</v>
+      </c>
+      <c r="F22" t="s">
         <v>74</v>
       </c>
-      <c r="S19">
-        <v>115.17</v>
-      </c>
-      <c r="T19">
-        <v>0.73</v>
-      </c>
-      <c r="U19">
-        <v>0.55</v>
-      </c>
-      <c r="V19" t="s">
+      <c r="G22">
+        <v>158.57</v>
+      </c>
+      <c r="H22">
+        <v>0.53</v>
+      </c>
+      <c r="I22">
+        <v>0.35</v>
+      </c>
+      <c r="J22" t="s">
         <v>75</v>
       </c>
-      <c r="W19">
-        <v>125.86</v>
-      </c>
-      <c r="X19">
-        <v>0.67</v>
-      </c>
-      <c r="Y19">
-        <v>0.48</v>
+      <c r="K22">
+        <v>157.14</v>
+      </c>
+      <c r="L22">
+        <v>0.54</v>
+      </c>
+      <c r="M22">
+        <v>0.36</v>
+      </c>
+      <c r="N22" t="s">
+        <v>76</v>
+      </c>
+      <c r="O22">
+        <v>135.14</v>
+      </c>
+      <c r="P22">
+        <v>0.62</v>
+      </c>
+      <c r="Q22">
+        <v>0.43</v>
+      </c>
+      <c r="R22" t="s">
+        <v>77</v>
+      </c>
+      <c r="S22">
+        <v>144</v>
+      </c>
+      <c r="T22">
+        <v>0.59</v>
+      </c>
+      <c r="U22">
+        <v>0.4</v>
+      </c>
+      <c r="V22" t="s">
+        <v>78</v>
+      </c>
+      <c r="W22">
+        <v>139.29</v>
+      </c>
+      <c r="X22">
+        <v>0.61</v>
+      </c>
+      <c r="Y22">
+        <v>0.42</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA22">
+        <v>187.29</v>
+      </c>
+      <c r="AB22">
+        <v>0.45</v>
+      </c>
+      <c r="AC22">
+        <v>0.26</v>
       </c>
     </row>
-    <row r="20" spans="1:25">
-      <c r="A20" t="s">
-        <v>43</v>
-      </c>
-      <c r="B20" t="s">
-        <v>70</v>
-      </c>
-      <c r="C20">
-        <v>250</v>
-      </c>
-      <c r="D20">
-        <v>0.34</v>
-      </c>
-      <c r="E20">
-        <v>0.18</v>
-      </c>
-      <c r="F20" t="s">
-        <v>71</v>
-      </c>
-      <c r="G20">
-        <v>259.86</v>
-      </c>
-      <c r="H20">
-        <v>0.32</v>
-      </c>
-      <c r="I20">
-        <v>0.16</v>
-      </c>
-      <c r="J20" t="s">
-        <v>72</v>
-      </c>
-      <c r="K20">
-        <v>153</v>
-      </c>
-      <c r="L20">
-        <v>0.55</v>
-      </c>
-      <c r="M20">
-        <v>0.37</v>
-      </c>
-      <c r="N20" t="s">
+    <row r="23" spans="1:29">
+      <c r="A23" t="s">
+        <v>50</v>
+      </c>
+      <c r="B23" t="s">
         <v>73</v>
       </c>
-      <c r="O20">
-        <v>143</v>
-      </c>
-      <c r="P20">
+      <c r="C23">
+        <v>141.29</v>
+      </c>
+      <c r="D23">
+        <v>0.6</v>
+      </c>
+      <c r="E23">
+        <v>0.43</v>
+      </c>
+      <c r="F23" t="s">
+        <v>74</v>
+      </c>
+      <c r="G23">
+        <v>145.57</v>
+      </c>
+      <c r="H23">
         <v>0.58</v>
       </c>
-      <c r="Q20">
-        <v>0.4</v>
-      </c>
-      <c r="R20" t="s">
+      <c r="I23">
+        <v>0.39</v>
+      </c>
+      <c r="J23" t="s">
+        <v>75</v>
+      </c>
+      <c r="K23">
+        <v>110.14</v>
+      </c>
+      <c r="L23">
+        <v>0.77</v>
+      </c>
+      <c r="M23">
+        <v>0.59</v>
+      </c>
+      <c r="N23" t="s">
+        <v>76</v>
+      </c>
+      <c r="O23">
+        <v>105.86</v>
+      </c>
+      <c r="P23">
+        <v>0.79</v>
+      </c>
+      <c r="Q23">
+        <v>0.6</v>
+      </c>
+      <c r="R23" t="s">
+        <v>77</v>
+      </c>
+      <c r="S23">
+        <v>110</v>
+      </c>
+      <c r="T23">
+        <v>0.77</v>
+      </c>
+      <c r="U23">
+        <v>0.59</v>
+      </c>
+      <c r="V23" t="s">
+        <v>78</v>
+      </c>
+      <c r="W23">
+        <v>171.86</v>
+      </c>
+      <c r="X23">
+        <v>0.49</v>
+      </c>
+      <c r="Y23">
+        <v>0.31</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA23">
+        <v>188.29</v>
+      </c>
+      <c r="AB23">
+        <v>0.45</v>
+      </c>
+      <c r="AC23">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="24" spans="1:29">
+      <c r="A24" t="s">
+        <v>51</v>
+      </c>
+      <c r="B24" t="s">
+        <v>73</v>
+      </c>
+      <c r="C24">
+        <v>71.14</v>
+      </c>
+      <c r="D24">
+        <v>1.19</v>
+      </c>
+      <c r="E24">
+        <v>1.05</v>
+      </c>
+      <c r="F24" t="s">
         <v>74</v>
       </c>
-      <c r="S20">
-        <v>144.83</v>
-      </c>
-      <c r="T20">
-        <v>0.58</v>
-      </c>
-      <c r="U20">
-        <v>0.4</v>
-      </c>
-      <c r="V20" t="s">
+      <c r="G24">
+        <v>75.29000000000001</v>
+      </c>
+      <c r="H24">
+        <v>1.12</v>
+      </c>
+      <c r="I24">
+        <v>0.95</v>
+      </c>
+      <c r="J24" t="s">
         <v>75</v>
       </c>
-      <c r="W20">
-        <v>133.71</v>
-      </c>
-      <c r="X20">
-        <v>0.63</v>
-      </c>
-      <c r="Y20">
+      <c r="K24">
+        <v>75.29000000000001</v>
+      </c>
+      <c r="L24">
+        <v>1.12</v>
+      </c>
+      <c r="M24">
+        <v>0.96</v>
+      </c>
+      <c r="N24" t="s">
+        <v>76</v>
+      </c>
+      <c r="O24">
+        <v>83</v>
+      </c>
+      <c r="P24">
+        <v>1.01</v>
+      </c>
+      <c r="Q24">
+        <v>0.83</v>
+      </c>
+      <c r="R24" t="s">
+        <v>77</v>
+      </c>
+      <c r="S24">
+        <v>88.83</v>
+      </c>
+      <c r="T24">
+        <v>0.95</v>
+      </c>
+      <c r="U24">
+        <v>0.78</v>
+      </c>
+      <c r="V24" t="s">
+        <v>78</v>
+      </c>
+      <c r="W24">
+        <v>162.86</v>
+      </c>
+      <c r="X24">
+        <v>0.52</v>
+      </c>
+      <c r="Y24">
+        <v>0.33</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA24">
+        <v>190</v>
+      </c>
+      <c r="AB24">
         <v>0.44</v>
       </c>
+      <c r="AC24">
+        <v>0.26</v>
+      </c>
     </row>
-    <row r="21" spans="1:25">
-      <c r="A21" t="s">
-        <v>44</v>
-      </c>
-      <c r="B21" t="s">
-        <v>70</v>
-      </c>
-      <c r="C21">
-        <v>153</v>
-      </c>
-      <c r="D21">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="E21">
-        <v>0.39</v>
-      </c>
-      <c r="F21" t="s">
-        <v>71</v>
-      </c>
-      <c r="G21">
-        <v>158.57</v>
-      </c>
-      <c r="H21">
-        <v>0.53</v>
-      </c>
-      <c r="I21">
-        <v>0.35</v>
-      </c>
-      <c r="J21" t="s">
-        <v>72</v>
-      </c>
-      <c r="K21">
-        <v>157.14</v>
-      </c>
-      <c r="L21">
-        <v>0.54</v>
-      </c>
-      <c r="M21">
-        <v>0.36</v>
-      </c>
-      <c r="N21" t="s">
+    <row r="25" spans="1:29">
+      <c r="A25" t="s">
+        <v>52</v>
+      </c>
+      <c r="B25" t="s">
         <v>73</v>
-      </c>
-      <c r="O21">
-        <v>135.14</v>
-      </c>
-      <c r="P21">
-        <v>0.62</v>
-      </c>
-      <c r="Q21">
-        <v>0.43</v>
-      </c>
-      <c r="R21" t="s">
-        <v>74</v>
-      </c>
-      <c r="S21">
-        <v>144</v>
-      </c>
-      <c r="T21">
-        <v>0.59</v>
-      </c>
-      <c r="U21">
-        <v>0.4</v>
-      </c>
-      <c r="V21" t="s">
-        <v>75</v>
-      </c>
-      <c r="W21">
-        <v>139.29</v>
-      </c>
-      <c r="X21">
-        <v>0.61</v>
-      </c>
-      <c r="Y21">
-        <v>0.42</v>
-      </c>
-    </row>
-    <row r="22" spans="1:25">
-      <c r="A22" t="s">
-        <v>45</v>
-      </c>
-      <c r="B22" t="s">
-        <v>70</v>
-      </c>
-      <c r="C22">
-        <v>191.71</v>
-      </c>
-      <c r="D22">
-        <v>0.44</v>
-      </c>
-      <c r="E22">
-        <v>0.28</v>
-      </c>
-      <c r="F22" t="s">
-        <v>71</v>
-      </c>
-      <c r="G22">
-        <v>222.71</v>
-      </c>
-      <c r="H22">
-        <v>0.38</v>
-      </c>
-      <c r="I22">
-        <v>0.21</v>
-      </c>
-      <c r="J22" t="s">
-        <v>72</v>
-      </c>
-      <c r="K22">
-        <v>193.29</v>
-      </c>
-      <c r="L22">
-        <v>0.44</v>
-      </c>
-      <c r="M22">
-        <v>0.26</v>
-      </c>
-      <c r="N22" t="s">
-        <v>73</v>
-      </c>
-      <c r="O22">
-        <v>197.43</v>
-      </c>
-      <c r="P22">
-        <v>0.42</v>
-      </c>
-      <c r="Q22">
-        <v>0.24</v>
-      </c>
-      <c r="R22" t="s">
-        <v>74</v>
-      </c>
-      <c r="S22">
-        <v>148.17</v>
-      </c>
-      <c r="T22">
-        <v>0.57</v>
-      </c>
-      <c r="U22">
-        <v>0.39</v>
-      </c>
-      <c r="V22" t="s">
-        <v>75</v>
-      </c>
-      <c r="W22">
-        <v>140</v>
-      </c>
-      <c r="X22">
-        <v>0.6</v>
-      </c>
-      <c r="Y22">
-        <v>0.41</v>
-      </c>
-    </row>
-    <row r="23" spans="1:25">
-      <c r="A23" t="s">
-        <v>46</v>
-      </c>
-      <c r="B23" t="s">
-        <v>70</v>
-      </c>
-      <c r="C23">
-        <v>71.14</v>
-      </c>
-      <c r="D23">
-        <v>1.19</v>
-      </c>
-      <c r="E23">
-        <v>1.05</v>
-      </c>
-      <c r="F23" t="s">
-        <v>71</v>
-      </c>
-      <c r="G23">
-        <v>75.29000000000001</v>
-      </c>
-      <c r="H23">
-        <v>1.12</v>
-      </c>
-      <c r="I23">
-        <v>0.95</v>
-      </c>
-      <c r="J23" t="s">
-        <v>72</v>
-      </c>
-      <c r="K23">
-        <v>75.29000000000001</v>
-      </c>
-      <c r="L23">
-        <v>1.12</v>
-      </c>
-      <c r="M23">
-        <v>0.96</v>
-      </c>
-      <c r="N23" t="s">
-        <v>73</v>
-      </c>
-      <c r="O23">
-        <v>83</v>
-      </c>
-      <c r="P23">
-        <v>1.01</v>
-      </c>
-      <c r="Q23">
-        <v>0.83</v>
-      </c>
-      <c r="R23" t="s">
-        <v>74</v>
-      </c>
-      <c r="S23">
-        <v>88.83</v>
-      </c>
-      <c r="T23">
-        <v>0.95</v>
-      </c>
-      <c r="U23">
-        <v>0.78</v>
-      </c>
-      <c r="V23" t="s">
-        <v>75</v>
-      </c>
-      <c r="W23">
-        <v>162.86</v>
-      </c>
-      <c r="X23">
-        <v>0.52</v>
-      </c>
-      <c r="Y23">
-        <v>0.33</v>
-      </c>
-    </row>
-    <row r="24" spans="1:25">
-      <c r="A24" t="s">
-        <v>47</v>
-      </c>
-      <c r="B24" t="s">
-        <v>70</v>
-      </c>
-      <c r="C24">
-        <v>141.29</v>
-      </c>
-      <c r="D24">
-        <v>0.6</v>
-      </c>
-      <c r="E24">
-        <v>0.43</v>
-      </c>
-      <c r="F24" t="s">
-        <v>71</v>
-      </c>
-      <c r="G24">
-        <v>145.57</v>
-      </c>
-      <c r="H24">
-        <v>0.58</v>
-      </c>
-      <c r="I24">
-        <v>0.39</v>
-      </c>
-      <c r="J24" t="s">
-        <v>72</v>
-      </c>
-      <c r="K24">
-        <v>110.14</v>
-      </c>
-      <c r="L24">
-        <v>0.77</v>
-      </c>
-      <c r="M24">
-        <v>0.59</v>
-      </c>
-      <c r="N24" t="s">
-        <v>73</v>
-      </c>
-      <c r="O24">
-        <v>105.86</v>
-      </c>
-      <c r="P24">
-        <v>0.79</v>
-      </c>
-      <c r="Q24">
-        <v>0.6</v>
-      </c>
-      <c r="R24" t="s">
-        <v>74</v>
-      </c>
-      <c r="S24">
-        <v>110</v>
-      </c>
-      <c r="T24">
-        <v>0.77</v>
-      </c>
-      <c r="U24">
-        <v>0.59</v>
-      </c>
-      <c r="V24" t="s">
-        <v>75</v>
-      </c>
-      <c r="W24">
-        <v>171.86</v>
-      </c>
-      <c r="X24">
-        <v>0.49</v>
-      </c>
-      <c r="Y24">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="25" spans="1:25">
-      <c r="A25" t="s">
-        <v>48</v>
-      </c>
-      <c r="B25" t="s">
-        <v>70</v>
       </c>
       <c r="C25">
         <v>442.71</v>
@@ -2467,7 +2767,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="F25" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G25">
         <v>462.29</v>
@@ -2479,7 +2779,7 @@
         <v>0.06</v>
       </c>
       <c r="J25" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K25">
         <v>186</v>
@@ -2491,7 +2791,7 @@
         <v>0.28</v>
       </c>
       <c r="N25" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="O25">
         <v>123.14</v>
@@ -2503,7 +2803,7 @@
         <v>0.49</v>
       </c>
       <c r="R25" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="S25">
         <v>128.5</v>
@@ -2515,7 +2815,7 @@
         <v>0.47</v>
       </c>
       <c r="V25" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="W25">
         <v>174.43</v>
@@ -2526,13 +2826,25 @@
       <c r="Y25">
         <v>0.3</v>
       </c>
+      <c r="Z25" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA25">
+        <v>206.33</v>
+      </c>
+      <c r="AB25">
+        <v>0.41</v>
+      </c>
+      <c r="AC25">
+        <v>0.23</v>
+      </c>
     </row>
-    <row r="26" spans="1:25">
+    <row r="26" spans="1:29">
       <c r="A26" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B26" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C26">
         <v>320.43</v>
@@ -2544,7 +2856,7 @@
         <v>0.12</v>
       </c>
       <c r="F26" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G26">
         <v>351.57</v>
@@ -2556,7 +2868,7 @@
         <v>0.1</v>
       </c>
       <c r="J26" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K26">
         <v>341.71</v>
@@ -2568,7 +2880,7 @@
         <v>0.1</v>
       </c>
       <c r="N26" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="O26">
         <v>283.71</v>
@@ -2580,7 +2892,7 @@
         <v>0.13</v>
       </c>
       <c r="R26" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="S26">
         <v>302.5</v>
@@ -2592,7 +2904,7 @@
         <v>0.13</v>
       </c>
       <c r="V26" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="W26">
         <v>261.14</v>
@@ -2603,167 +2915,203 @@
       <c r="Y26">
         <v>0.16</v>
       </c>
+      <c r="Z26" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA26">
+        <v>232.57</v>
+      </c>
+      <c r="AB26">
+        <v>0.36</v>
+      </c>
+      <c r="AC26">
+        <v>0.19</v>
+      </c>
     </row>
-    <row r="27" spans="1:25">
+    <row r="27" spans="1:29">
       <c r="A27" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B27" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C27">
+        <v>376.29</v>
+      </c>
+      <c r="D27">
+        <v>0.23</v>
+      </c>
+      <c r="E27">
+        <v>0.09</v>
+      </c>
+      <c r="F27" t="s">
+        <v>74</v>
+      </c>
+      <c r="G27">
+        <v>241</v>
+      </c>
+      <c r="H27">
+        <v>0.35</v>
+      </c>
+      <c r="I27">
+        <v>0.18</v>
+      </c>
+      <c r="J27" t="s">
+        <v>75</v>
+      </c>
+      <c r="K27">
+        <v>224.29</v>
+      </c>
+      <c r="L27">
+        <v>0.38</v>
+      </c>
+      <c r="M27">
+        <v>0.21</v>
+      </c>
+      <c r="N27" t="s">
+        <v>76</v>
+      </c>
+      <c r="O27">
+        <v>234</v>
+      </c>
+      <c r="P27">
+        <v>0.36</v>
+      </c>
+      <c r="Q27">
+        <v>0.18</v>
+      </c>
+      <c r="R27" t="s">
+        <v>77</v>
+      </c>
+      <c r="S27">
+        <v>256.33</v>
+      </c>
+      <c r="T27">
+        <v>0.33</v>
+      </c>
+      <c r="U27">
+        <v>0.17</v>
+      </c>
+      <c r="V27" t="s">
+        <v>78</v>
+      </c>
+      <c r="W27">
+        <v>293.57</v>
+      </c>
+      <c r="X27">
+        <v>0.29</v>
+      </c>
+      <c r="Y27">
+        <v>0.13</v>
+      </c>
+      <c r="Z27" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA27">
+        <v>288</v>
+      </c>
+      <c r="AB27">
+        <v>0.29</v>
+      </c>
+      <c r="AC27">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="28" spans="1:29">
+      <c r="A28" t="s">
+        <v>55</v>
+      </c>
+      <c r="B28" t="s">
+        <v>73</v>
+      </c>
+      <c r="C28">
         <v>89</v>
       </c>
-      <c r="D27">
+      <c r="D28">
         <v>0.95</v>
       </c>
-      <c r="E27">
+      <c r="E28">
         <v>0.8</v>
       </c>
-      <c r="F27" t="s">
-        <v>71</v>
-      </c>
-      <c r="G27">
+      <c r="F28" t="s">
+        <v>74</v>
+      </c>
+      <c r="G28">
         <v>90.43000000000001</v>
       </c>
-      <c r="H27">
+      <c r="H28">
         <v>0.93</v>
       </c>
-      <c r="I27">
+      <c r="I28">
         <v>0.75</v>
       </c>
-      <c r="J27" t="s">
-        <v>72</v>
-      </c>
-      <c r="K27">
+      <c r="J28" t="s">
+        <v>75</v>
+      </c>
+      <c r="K28">
         <v>133.71</v>
       </c>
-      <c r="L27">
+      <c r="L28">
         <v>0.63</v>
       </c>
-      <c r="M27">
+      <c r="M28">
         <v>0.45</v>
       </c>
-      <c r="N27" t="s">
+      <c r="N28" t="s">
+        <v>76</v>
+      </c>
+      <c r="O28">
+        <v>135.14</v>
+      </c>
+      <c r="P28">
+        <v>0.62</v>
+      </c>
+      <c r="Q28">
+        <v>0.43</v>
+      </c>
+      <c r="R28" t="s">
+        <v>77</v>
+      </c>
+      <c r="S28">
+        <v>148.33</v>
+      </c>
+      <c r="T28">
+        <v>0.57</v>
+      </c>
+      <c r="U28">
+        <v>0.39</v>
+      </c>
+      <c r="V28" t="s">
+        <v>78</v>
+      </c>
+      <c r="W28">
+        <v>279.29</v>
+      </c>
+      <c r="X28">
+        <v>0.3</v>
+      </c>
+      <c r="Y28">
+        <v>0.14</v>
+      </c>
+      <c r="Z28" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA28">
+        <v>289.29</v>
+      </c>
+      <c r="AB28">
+        <v>0.29</v>
+      </c>
+      <c r="AC28">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="29" spans="1:29">
+      <c r="A29" t="s">
+        <v>56</v>
+      </c>
+      <c r="B29" t="s">
         <v>73</v>
-      </c>
-      <c r="O27">
-        <v>135.14</v>
-      </c>
-      <c r="P27">
-        <v>0.62</v>
-      </c>
-      <c r="Q27">
-        <v>0.43</v>
-      </c>
-      <c r="R27" t="s">
-        <v>74</v>
-      </c>
-      <c r="S27">
-        <v>148.33</v>
-      </c>
-      <c r="T27">
-        <v>0.57</v>
-      </c>
-      <c r="U27">
-        <v>0.39</v>
-      </c>
-      <c r="V27" t="s">
-        <v>75</v>
-      </c>
-      <c r="W27">
-        <v>279.29</v>
-      </c>
-      <c r="X27">
-        <v>0.3</v>
-      </c>
-      <c r="Y27">
-        <v>0.14</v>
-      </c>
-    </row>
-    <row r="28" spans="1:25">
-      <c r="A28" t="s">
-        <v>51</v>
-      </c>
-      <c r="B28" t="s">
-        <v>70</v>
-      </c>
-      <c r="C28">
-        <v>376.29</v>
-      </c>
-      <c r="D28">
-        <v>0.23</v>
-      </c>
-      <c r="E28">
-        <v>0.09</v>
-      </c>
-      <c r="F28" t="s">
-        <v>71</v>
-      </c>
-      <c r="G28">
-        <v>241</v>
-      </c>
-      <c r="H28">
-        <v>0.35</v>
-      </c>
-      <c r="I28">
-        <v>0.18</v>
-      </c>
-      <c r="J28" t="s">
-        <v>72</v>
-      </c>
-      <c r="K28">
-        <v>224.29</v>
-      </c>
-      <c r="L28">
-        <v>0.38</v>
-      </c>
-      <c r="M28">
-        <v>0.21</v>
-      </c>
-      <c r="N28" t="s">
-        <v>73</v>
-      </c>
-      <c r="O28">
-        <v>234</v>
-      </c>
-      <c r="P28">
-        <v>0.36</v>
-      </c>
-      <c r="Q28">
-        <v>0.18</v>
-      </c>
-      <c r="R28" t="s">
-        <v>74</v>
-      </c>
-      <c r="S28">
-        <v>256.33</v>
-      </c>
-      <c r="T28">
-        <v>0.33</v>
-      </c>
-      <c r="U28">
-        <v>0.17</v>
-      </c>
-      <c r="V28" t="s">
-        <v>75</v>
-      </c>
-      <c r="W28">
-        <v>293.57</v>
-      </c>
-      <c r="X28">
-        <v>0.29</v>
-      </c>
-      <c r="Y28">
-        <v>0.13</v>
-      </c>
-    </row>
-    <row r="29" spans="1:25">
-      <c r="A29" t="s">
-        <v>52</v>
-      </c>
-      <c r="B29" t="s">
-        <v>70</v>
       </c>
       <c r="C29">
         <v>249.71</v>
@@ -2775,7 +3123,7 @@
         <v>0.18</v>
       </c>
       <c r="F29" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G29">
         <v>242.57</v>
@@ -2787,7 +3135,7 @@
         <v>0.18</v>
       </c>
       <c r="J29" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K29">
         <v>228.14</v>
@@ -2799,7 +3147,7 @@
         <v>0.2</v>
       </c>
       <c r="N29" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="O29">
         <v>216.71</v>
@@ -2811,7 +3159,7 @@
         <v>0.21</v>
       </c>
       <c r="R29" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="S29">
         <v>234.17</v>
@@ -2823,7 +3171,7 @@
         <v>0.19</v>
       </c>
       <c r="V29" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="W29">
         <v>305.57</v>
@@ -2834,13 +3182,25 @@
       <c r="Y29">
         <v>0.12</v>
       </c>
+      <c r="Z29" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA29">
+        <v>314.43</v>
+      </c>
+      <c r="AB29">
+        <v>0.27</v>
+      </c>
+      <c r="AC29">
+        <v>0.11</v>
+      </c>
     </row>
-    <row r="30" spans="1:25">
+    <row r="30" spans="1:29">
       <c r="A30" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B30" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C30">
         <v>243.29</v>
@@ -2852,7 +3212,7 @@
         <v>0.19</v>
       </c>
       <c r="F30" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G30">
         <v>455.57</v>
@@ -2864,7 +3224,7 @@
         <v>0.06</v>
       </c>
       <c r="J30" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K30">
         <v>483.57</v>
@@ -2876,7 +3236,7 @@
         <v>0.06</v>
       </c>
       <c r="N30" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="O30">
         <v>490.71</v>
@@ -2888,7 +3248,7 @@
         <v>0.05</v>
       </c>
       <c r="R30" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="S30">
         <v>522.33</v>
@@ -2900,7 +3260,7 @@
         <v>0.05</v>
       </c>
       <c r="V30" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="W30">
         <v>324.29</v>
@@ -2911,13 +3271,25 @@
       <c r="Y30">
         <v>0.11</v>
       </c>
+      <c r="Z30" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA30">
+        <v>320.14</v>
+      </c>
+      <c r="AB30">
+        <v>0.26</v>
+      </c>
+      <c r="AC30">
+        <v>0.11</v>
+      </c>
     </row>
-    <row r="31" spans="1:25">
+    <row r="31" spans="1:29">
       <c r="A31" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B31" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C31">
         <v>467.14</v>
@@ -2929,7 +3301,7 @@
         <v>0.06</v>
       </c>
       <c r="F31" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G31">
         <v>505.29</v>
@@ -2941,7 +3313,7 @@
         <v>0.05</v>
       </c>
       <c r="J31" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K31">
         <v>494.14</v>
@@ -2953,7 +3325,7 @@
         <v>0.05</v>
       </c>
       <c r="N31" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="O31">
         <v>502.43</v>
@@ -2965,7 +3337,7 @@
         <v>0.05</v>
       </c>
       <c r="R31" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="S31">
         <v>441.33</v>
@@ -2977,7 +3349,7 @@
         <v>0.06</v>
       </c>
       <c r="V31" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="W31">
         <v>433.86</v>
@@ -2988,16 +3360,28 @@
       <c r="Y31">
         <v>0.06</v>
       </c>
+      <c r="Z31" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA31">
+        <v>331</v>
+      </c>
+      <c r="AB31">
+        <v>0.25</v>
+      </c>
+      <c r="AC31">
+        <v>0.1</v>
+      </c>
     </row>
-    <row r="32" spans="1:25">
+    <row r="32" spans="1:29">
       <c r="A32" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B32" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C32">
-        <v>370.43</v>
+        <v>367.57</v>
       </c>
       <c r="D32">
         <v>0.23</v>
@@ -3006,10 +3390,10 @@
         <v>0.1</v>
       </c>
       <c r="F32" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G32">
-        <v>376.71</v>
+        <v>383</v>
       </c>
       <c r="H32">
         <v>0.22</v>
@@ -3018,46 +3402,46 @@
         <v>0.08</v>
       </c>
       <c r="J32" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K32">
-        <v>383.71</v>
+        <v>378.86</v>
       </c>
       <c r="L32">
         <v>0.22</v>
       </c>
       <c r="M32">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="N32" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="O32">
-        <v>390.71</v>
+        <v>474.57</v>
       </c>
       <c r="P32">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="Q32">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="R32" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="S32">
-        <v>473</v>
+        <v>530.67</v>
       </c>
       <c r="T32">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="U32">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="V32" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="W32">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="X32">
         <v>0.16</v>
@@ -3065,16 +3449,28 @@
       <c r="Y32">
         <v>0.05</v>
       </c>
+      <c r="Z32" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA32">
+        <v>529.5700000000001</v>
+      </c>
+      <c r="AB32">
+        <v>0.16</v>
+      </c>
+      <c r="AC32">
+        <v>0.04</v>
+      </c>
     </row>
-    <row r="33" spans="1:25">
+    <row r="33" spans="1:29">
       <c r="A33" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B33" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C33">
-        <v>367.57</v>
+        <v>370.43</v>
       </c>
       <c r="D33">
         <v>0.23</v>
@@ -3083,10 +3479,10 @@
         <v>0.1</v>
       </c>
       <c r="F33" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G33">
-        <v>383</v>
+        <v>376.71</v>
       </c>
       <c r="H33">
         <v>0.22</v>
@@ -3095,46 +3491,46 @@
         <v>0.08</v>
       </c>
       <c r="J33" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K33">
-        <v>378.86</v>
+        <v>383.71</v>
       </c>
       <c r="L33">
         <v>0.22</v>
       </c>
       <c r="M33">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="N33" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="O33">
-        <v>474.57</v>
+        <v>390.71</v>
       </c>
       <c r="P33">
+        <v>0.21</v>
+      </c>
+      <c r="Q33">
+        <v>0.08</v>
+      </c>
+      <c r="R33" t="s">
+        <v>77</v>
+      </c>
+      <c r="S33">
+        <v>473</v>
+      </c>
+      <c r="T33">
         <v>0.18</v>
       </c>
-      <c r="Q33">
-        <v>0.05</v>
-      </c>
-      <c r="R33" t="s">
-        <v>74</v>
-      </c>
-      <c r="S33">
-        <v>530.67</v>
-      </c>
-      <c r="T33">
-        <v>0.16</v>
-      </c>
       <c r="U33">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="V33" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="W33">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="X33">
         <v>0.16</v>
@@ -3142,13 +3538,25 @@
       <c r="Y33">
         <v>0.05</v>
       </c>
+      <c r="Z33" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA33">
+        <v>547.86</v>
+      </c>
+      <c r="AB33">
+        <v>0.15</v>
+      </c>
+      <c r="AC33">
+        <v>0.04</v>
+      </c>
     </row>
-    <row r="34" spans="1:25">
+    <row r="34" spans="1:29">
       <c r="A34" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B34" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C34">
         <v>299.29</v>
@@ -3160,7 +3568,7 @@
         <v>0.14</v>
       </c>
       <c r="F34" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G34">
         <v>497.86</v>
@@ -3172,7 +3580,7 @@
         <v>0.05</v>
       </c>
       <c r="J34" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K34">
         <v>486.71</v>
@@ -3184,7 +3592,7 @@
         <v>0.06</v>
       </c>
       <c r="N34" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="O34">
         <v>497.86</v>
@@ -3196,7 +3604,7 @@
         <v>0.05</v>
       </c>
       <c r="R34" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="S34">
         <v>572.33</v>
@@ -3208,7 +3616,7 @@
         <v>0.04</v>
       </c>
       <c r="V34" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="W34">
         <v>547.86</v>
@@ -3219,13 +3627,25 @@
       <c r="Y34">
         <v>0.04</v>
       </c>
+      <c r="Z34" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA34">
+        <v>583.5700000000001</v>
+      </c>
+      <c r="AB34">
+        <v>0.14</v>
+      </c>
+      <c r="AC34">
+        <v>0.04</v>
+      </c>
     </row>
-    <row r="35" spans="1:25">
+    <row r="35" spans="1:29">
       <c r="A35" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B35" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C35">
         <v>747.86</v>
@@ -3237,7 +3657,7 @@
         <v>0.03</v>
       </c>
       <c r="F35" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G35">
         <v>747.86</v>
@@ -3249,7 +3669,7 @@
         <v>0.02</v>
       </c>
       <c r="J35" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K35">
         <v>747.86</v>
@@ -3261,7 +3681,7 @@
         <v>0.02</v>
       </c>
       <c r="N35" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="O35">
         <v>747.86</v>
@@ -3273,7 +3693,7 @@
         <v>0.02</v>
       </c>
       <c r="R35" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="S35">
         <v>607.5</v>
@@ -3285,7 +3705,7 @@
         <v>0.04</v>
       </c>
       <c r="V35" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="W35">
         <v>569.29</v>
@@ -3296,13 +3716,25 @@
       <c r="Y35">
         <v>0.04</v>
       </c>
+      <c r="Z35" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA35">
+        <v>647.86</v>
+      </c>
+      <c r="AB35">
+        <v>0.13</v>
+      </c>
+      <c r="AC35">
+        <v>0.03</v>
+      </c>
     </row>
-    <row r="36" spans="1:25">
+    <row r="36" spans="1:29">
       <c r="A36" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B36" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C36">
         <v>540.71</v>
@@ -3314,7 +3746,7 @@
         <v>0.05</v>
       </c>
       <c r="F36" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G36">
         <v>576.4299999999999</v>
@@ -3326,7 +3758,7 @@
         <v>0.04</v>
       </c>
       <c r="J36" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K36">
         <v>576.4299999999999</v>
@@ -3338,7 +3770,7 @@
         <v>0.04</v>
       </c>
       <c r="N36" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="O36">
         <v>612.14</v>
@@ -3350,7 +3782,7 @@
         <v>0.03</v>
       </c>
       <c r="R36" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="S36">
         <v>630.67</v>
@@ -3362,7 +3794,7 @@
         <v>0.03</v>
       </c>
       <c r="V36" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="W36">
         <v>647.86</v>
@@ -3373,13 +3805,25 @@
       <c r="Y36">
         <v>0.03</v>
       </c>
+      <c r="Z36" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA36">
+        <v>647.86</v>
+      </c>
+      <c r="AB36">
+        <v>0.13</v>
+      </c>
+      <c r="AC36">
+        <v>0.03</v>
+      </c>
     </row>
-    <row r="37" spans="1:25">
+    <row r="37" spans="1:29">
       <c r="A37" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B37" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C37">
         <v>1326.43</v>
@@ -3391,7 +3835,7 @@
         <v>0.01</v>
       </c>
       <c r="F37" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G37">
         <v>1326.43</v>
@@ -3403,7 +3847,7 @@
         <v>0.01</v>
       </c>
       <c r="J37" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K37">
         <v>1326.43</v>
@@ -3415,7 +3859,7 @@
         <v>0.01</v>
       </c>
       <c r="N37" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="O37">
         <v>1069.29</v>
@@ -3427,7 +3871,7 @@
         <v>0.01</v>
       </c>
       <c r="R37" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="S37">
         <v>996.6</v>
@@ -3439,7 +3883,7 @@
         <v>0.01</v>
       </c>
       <c r="V37" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="W37">
         <v>705.67</v>
@@ -3450,13 +3894,25 @@
       <c r="Y37">
         <v>0.03</v>
       </c>
+      <c r="Z37" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA37">
+        <v>747.86</v>
+      </c>
+      <c r="AB37">
+        <v>0.11</v>
+      </c>
+      <c r="AC37">
+        <v>0.02</v>
+      </c>
     </row>
-    <row r="38" spans="1:25">
+    <row r="38" spans="1:29">
       <c r="A38" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B38" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C38">
         <v>890.71</v>
@@ -3468,7 +3924,7 @@
         <v>0.02</v>
       </c>
       <c r="F38" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G38">
         <v>890.71</v>
@@ -3480,7 +3936,7 @@
         <v>0.02</v>
       </c>
       <c r="J38" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K38">
         <v>890.71</v>
@@ -3492,7 +3948,7 @@
         <v>0.02</v>
       </c>
       <c r="N38" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="O38">
         <v>783.5700000000001</v>
@@ -3504,7 +3960,7 @@
         <v>0.02</v>
       </c>
       <c r="R38" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="S38">
         <v>789</v>
@@ -3516,7 +3972,7 @@
         <v>0.02</v>
       </c>
       <c r="V38" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="W38">
         <v>855</v>
@@ -3527,13 +3983,25 @@
       <c r="Y38">
         <v>0.02</v>
       </c>
+      <c r="Z38" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA38">
+        <v>855</v>
+      </c>
+      <c r="AB38">
+        <v>0.1</v>
+      </c>
+      <c r="AC38">
+        <v>0.02</v>
+      </c>
     </row>
-    <row r="39" spans="1:25">
+    <row r="39" spans="1:29">
       <c r="A39" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B39" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C39">
         <v>1197.86</v>
@@ -3545,7 +4013,7 @@
         <v>0.01</v>
       </c>
       <c r="F39" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G39">
         <v>1197.86</v>
@@ -3557,7 +4025,7 @@
         <v>0.01</v>
       </c>
       <c r="J39" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K39">
         <v>1197.86</v>
@@ -3569,7 +4037,7 @@
         <v>0.01</v>
       </c>
       <c r="N39" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="O39">
         <v>819.29</v>
@@ -3581,7 +4049,7 @@
         <v>0.02</v>
       </c>
       <c r="R39" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="S39">
         <v>872.33</v>
@@ -3593,7 +4061,7 @@
         <v>0.02</v>
       </c>
       <c r="V39" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="W39">
         <v>890.71</v>
@@ -3604,13 +4072,25 @@
       <c r="Y39">
         <v>0.02</v>
       </c>
+      <c r="Z39" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA39">
+        <v>890.71</v>
+      </c>
+      <c r="AB39">
+        <v>0.09</v>
+      </c>
+      <c r="AC39">
+        <v>0.02</v>
+      </c>
     </row>
-    <row r="40" spans="1:25">
+    <row r="40" spans="1:29">
       <c r="A40" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B40" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C40">
         <v>1197.86</v>
@@ -3622,7 +4102,7 @@
         <v>0.01</v>
       </c>
       <c r="F40" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G40">
         <v>1197.86</v>
@@ -3634,7 +4114,7 @@
         <v>0.01</v>
       </c>
       <c r="J40" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K40">
         <v>1197.86</v>
@@ -3646,7 +4126,7 @@
         <v>0.01</v>
       </c>
       <c r="N40" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="O40">
         <v>1197.86</v>
@@ -3658,22 +4138,22 @@
         <v>0.01</v>
       </c>
       <c r="R40" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="S40">
-        <v>1247.33</v>
+        <v>1296.6</v>
       </c>
       <c r="T40">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="U40">
         <v>0.01</v>
       </c>
       <c r="V40" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="W40">
-        <v>1212.14</v>
+        <v>1247.33</v>
       </c>
       <c r="X40">
         <v>0.07000000000000001</v>
@@ -3681,28 +4161,40 @@
       <c r="Y40">
         <v>0.01</v>
       </c>
+      <c r="Z40" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA40">
+        <v>1212.14</v>
+      </c>
+      <c r="AB40">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AC40">
+        <v>0.01</v>
+      </c>
     </row>
-    <row r="41" spans="1:25">
+    <row r="41" spans="1:29">
       <c r="A41" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B41" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C41">
-        <v>1126.43</v>
+        <v>890.71</v>
       </c>
       <c r="D41">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="E41">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F41" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G41">
-        <v>1126.43</v>
+        <v>1176.43</v>
       </c>
       <c r="H41">
         <v>0.07000000000000001</v>
@@ -3711,10 +4203,10 @@
         <v>0.01</v>
       </c>
       <c r="J41" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K41">
-        <v>1126.43</v>
+        <v>1176.43</v>
       </c>
       <c r="L41">
         <v>0.07000000000000001</v>
@@ -3723,10 +4215,10 @@
         <v>0.01</v>
       </c>
       <c r="N41" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="O41">
-        <v>1197.86</v>
+        <v>1176.43</v>
       </c>
       <c r="P41">
         <v>0.07000000000000001</v>
@@ -3735,22 +4227,22 @@
         <v>0.01</v>
       </c>
       <c r="R41" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="S41">
-        <v>1296.6</v>
+        <v>1205.67</v>
       </c>
       <c r="T41">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="U41">
         <v>0.01</v>
       </c>
       <c r="V41" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="W41">
-        <v>1247.33</v>
+        <v>1247.86</v>
       </c>
       <c r="X41">
         <v>0.07000000000000001</v>
@@ -3758,28 +4250,40 @@
       <c r="Y41">
         <v>0.01</v>
       </c>
+      <c r="Z41" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA41">
+        <v>1247.86</v>
+      </c>
+      <c r="AB41">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AC41">
+        <v>0.01</v>
+      </c>
     </row>
-    <row r="42" spans="1:25">
+    <row r="42" spans="1:29">
       <c r="A42" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B42" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C42">
-        <v>890.71</v>
+        <v>1126.43</v>
       </c>
       <c r="D42">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="E42">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F42" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G42">
-        <v>1176.43</v>
+        <v>1126.43</v>
       </c>
       <c r="H42">
         <v>0.07000000000000001</v>
@@ -3788,10 +4292,10 @@
         <v>0.01</v>
       </c>
       <c r="J42" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K42">
-        <v>1176.43</v>
+        <v>1126.43</v>
       </c>
       <c r="L42">
         <v>0.07000000000000001</v>
@@ -3800,10 +4304,10 @@
         <v>0.01</v>
       </c>
       <c r="N42" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="O42">
-        <v>1176.43</v>
+        <v>1197.86</v>
       </c>
       <c r="P42">
         <v>0.07000000000000001</v>
@@ -3812,22 +4316,22 @@
         <v>0.01</v>
       </c>
       <c r="R42" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="S42">
-        <v>1205.67</v>
+        <v>1296.6</v>
       </c>
       <c r="T42">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="U42">
         <v>0.01</v>
       </c>
       <c r="V42" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="W42">
-        <v>1247.86</v>
+        <v>1247.33</v>
       </c>
       <c r="X42">
         <v>0.07000000000000001</v>
@@ -3835,13 +4339,25 @@
       <c r="Y42">
         <v>0.01</v>
       </c>
+      <c r="Z42" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA42">
+        <v>1569.29</v>
+      </c>
+      <c r="AB42">
+        <v>0.05</v>
+      </c>
+      <c r="AC42">
+        <v>0.01</v>
+      </c>
     </row>
-    <row r="43" spans="1:25">
+    <row r="43" spans="1:29">
       <c r="A43" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B43" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C43">
         <v>1197.86</v>
@@ -3853,7 +4369,7 @@
         <v>0.01</v>
       </c>
       <c r="F43" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G43">
         <v>1197.86</v>
@@ -3865,7 +4381,7 @@
         <v>0.01</v>
       </c>
       <c r="J43" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K43">
         <v>1197.86</v>
@@ -3877,7 +4393,7 @@
         <v>0.01</v>
       </c>
       <c r="N43" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="O43">
         <v>1197.86</v>
@@ -3889,22 +4405,22 @@
         <v>0.01</v>
       </c>
       <c r="R43" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="S43">
-        <v>1296.6</v>
+        <v>1247.33</v>
       </c>
       <c r="T43">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="U43">
         <v>0.01</v>
       </c>
       <c r="V43" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="W43">
-        <v>1247.33</v>
+        <v>1212.14</v>
       </c>
       <c r="X43">
         <v>0.07000000000000001</v>
@@ -3912,90 +4428,114 @@
       <c r="Y43">
         <v>0.01</v>
       </c>
+      <c r="Z43" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA43">
+        <v>1664</v>
+      </c>
+      <c r="AB43">
+        <v>0.05</v>
+      </c>
+      <c r="AC43">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="1:25">
+    <row r="44" spans="1:29">
       <c r="A44" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B44" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C44">
-        <v>1497.86</v>
+        <v>1926.43</v>
       </c>
       <c r="D44">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="E44">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="F44" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G44">
-        <v>1497.86</v>
+        <v>1926.43</v>
       </c>
       <c r="H44">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="I44">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="J44" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K44">
-        <v>1497.86</v>
+        <v>2355</v>
       </c>
       <c r="L44">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="M44">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="N44" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="O44">
-        <v>1497.86</v>
+        <v>2355</v>
       </c>
       <c r="P44">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="Q44">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="R44" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="S44">
-        <v>1696.6</v>
+        <v>2596.6</v>
       </c>
       <c r="T44">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="U44">
         <v>0</v>
       </c>
       <c r="V44" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="W44">
-        <v>1664</v>
+        <v>1997.33</v>
       </c>
       <c r="X44">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="Y44">
         <v>0</v>
       </c>
+      <c r="Z44" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA44">
+        <v>1855</v>
+      </c>
+      <c r="AB44">
+        <v>0.05</v>
+      </c>
+      <c r="AC44">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="1:25">
+    <row r="45" spans="1:29">
       <c r="A45" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B45" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C45">
         <v>1069.29</v>
@@ -4007,7 +4547,7 @@
         <v>0.01</v>
       </c>
       <c r="F45" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G45">
         <v>1069.29</v>
@@ -4019,7 +4559,7 @@
         <v>0.01</v>
       </c>
       <c r="J45" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K45">
         <v>1069.29</v>
@@ -4031,7 +4571,7 @@
         <v>0.01</v>
       </c>
       <c r="N45" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="O45">
         <v>1069.29</v>
@@ -4043,7 +4583,7 @@
         <v>0.01</v>
       </c>
       <c r="R45" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="S45">
         <v>1372.33</v>
@@ -4055,7 +4595,7 @@
         <v>0.01</v>
       </c>
       <c r="V45" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="W45">
         <v>1926.43</v>
@@ -4066,81 +4606,16 @@
       <c r="Y45">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:25">
-      <c r="A46" t="s">
-        <v>69</v>
-      </c>
-      <c r="B46" t="s">
-        <v>70</v>
-      </c>
-      <c r="C46">
+      <c r="Z45" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA45">
         <v>1926.43</v>
       </c>
-      <c r="D46">
+      <c r="AB45">
         <v>0.04</v>
       </c>
-      <c r="E46">
-        <v>0</v>
-      </c>
-      <c r="F46" t="s">
-        <v>71</v>
-      </c>
-      <c r="G46">
-        <v>1926.43</v>
-      </c>
-      <c r="H46">
-        <v>0.04</v>
-      </c>
-      <c r="I46">
-        <v>0</v>
-      </c>
-      <c r="J46" t="s">
-        <v>72</v>
-      </c>
-      <c r="K46">
-        <v>2355</v>
-      </c>
-      <c r="L46">
-        <v>0.04</v>
-      </c>
-      <c r="M46">
-        <v>0</v>
-      </c>
-      <c r="N46" t="s">
-        <v>73</v>
-      </c>
-      <c r="O46">
-        <v>2355</v>
-      </c>
-      <c r="P46">
-        <v>0.04</v>
-      </c>
-      <c r="Q46">
-        <v>0</v>
-      </c>
-      <c r="R46" t="s">
-        <v>74</v>
-      </c>
-      <c r="S46">
-        <v>2596.6</v>
-      </c>
-      <c r="T46">
-        <v>0.03</v>
-      </c>
-      <c r="U46">
-        <v>0</v>
-      </c>
-      <c r="V46" t="s">
-        <v>75</v>
-      </c>
-      <c r="W46">
-        <v>1997.33</v>
-      </c>
-      <c r="X46">
-        <v>0.04</v>
-      </c>
-      <c r="Y46">
+      <c r="AC45">
         <v>0</v>
       </c>
     </row>

--- a/processed_data_during_wm/processed_data_wide.xlsx
+++ b/processed_data_during_wm/processed_data_wide.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="829" uniqueCount="124">
   <si>
     <t>Team</t>
   </si>
@@ -187,6 +187,18 @@
     <t>Shin_Wahrscheinlichkeit_in_Prozent_14</t>
   </si>
   <si>
+    <t>Datum_15</t>
+  </si>
+  <si>
+    <t>Durchsch_Quote_15</t>
+  </si>
+  <si>
+    <t>Norm_Wahrscheinlichkeit_in_Prozent_15</t>
+  </si>
+  <si>
+    <t>Shin_Wahrscheinlichkeit_in_Prozent_15</t>
+  </si>
+  <si>
     <t>Frankreich</t>
   </si>
   <si>
@@ -202,75 +214,75 @@
     <t>Norwegen</t>
   </si>
   <si>
+    <t>Belgien</t>
+  </si>
+  <si>
+    <t>Schweiz</t>
+  </si>
+  <si>
+    <t>Algerien</t>
+  </si>
+  <si>
+    <t>Australien</t>
+  </si>
+  <si>
+    <t>Bosnien Herzegowina</t>
+  </si>
+  <si>
+    <t>Brasilien</t>
+  </si>
+  <si>
+    <t>Curacao</t>
+  </si>
+  <si>
+    <t>DR Kongo</t>
+  </si>
+  <si>
+    <t>Deutschland</t>
+  </si>
+  <si>
+    <t>Ecuador</t>
+  </si>
+  <si>
+    <t>Elfenbeinküste</t>
+  </si>
+  <si>
+    <t>Ghana</t>
+  </si>
+  <si>
+    <t>Haiti</t>
+  </si>
+  <si>
+    <t>Irak</t>
+  </si>
+  <si>
+    <t>Iran</t>
+  </si>
+  <si>
+    <t>Japan</t>
+  </si>
+  <si>
+    <t>Jordanien</t>
+  </si>
+  <si>
+    <t>Kanada</t>
+  </si>
+  <si>
+    <t>Kap Verde</t>
+  </si>
+  <si>
+    <t>Katar</t>
+  </si>
+  <si>
+    <t>Kolumbien</t>
+  </si>
+  <si>
+    <t>Kroatien</t>
+  </si>
+  <si>
     <t>Marokko</t>
   </si>
   <si>
-    <t>Belgien</t>
-  </si>
-  <si>
-    <t>Schweiz</t>
-  </si>
-  <si>
-    <t>Algerien</t>
-  </si>
-  <si>
-    <t>Australien</t>
-  </si>
-  <si>
-    <t>Bosnien Herzegowina</t>
-  </si>
-  <si>
-    <t>Brasilien</t>
-  </si>
-  <si>
-    <t>Curacao</t>
-  </si>
-  <si>
-    <t>DR Kongo</t>
-  </si>
-  <si>
-    <t>Deutschland</t>
-  </si>
-  <si>
-    <t>Ecuador</t>
-  </si>
-  <si>
-    <t>Elfenbeinküste</t>
-  </si>
-  <si>
-    <t>Ghana</t>
-  </si>
-  <si>
-    <t>Haiti</t>
-  </si>
-  <si>
-    <t>Irak</t>
-  </si>
-  <si>
-    <t>Iran</t>
-  </si>
-  <si>
-    <t>Japan</t>
-  </si>
-  <si>
-    <t>Jordanien</t>
-  </si>
-  <si>
-    <t>Kanada</t>
-  </si>
-  <si>
-    <t>Kap Verde</t>
-  </si>
-  <si>
-    <t>Katar</t>
-  </si>
-  <si>
-    <t>Kolumbien</t>
-  </si>
-  <si>
-    <t>Kroatien</t>
-  </si>
-  <si>
     <t>Mexiko</t>
   </si>
   <si>
@@ -371,6 +383,9 @@
   </si>
   <si>
     <t>08.07.2026</t>
+  </si>
+  <si>
+    <t>10.07.2026</t>
   </si>
 </sst>
 </file>
@@ -728,10 +743,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BE49"/>
+  <dimension ref="A1:BI49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:57">
+    <row r="1" spans="1:61">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -903,13 +918,25 @@
       <c r="BE1" s="1" t="s">
         <v>56</v>
       </c>
+      <c r="BF1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="BG1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="BH1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="BI1" s="1" t="s">
+        <v>60</v>
+      </c>
     </row>
-    <row r="2" spans="1:57">
+    <row r="2" spans="1:61">
       <c r="A2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B2" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C2">
         <v>6.01</v>
@@ -921,7 +948,7 @@
         <v>15.09</v>
       </c>
       <c r="F2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="G2">
         <v>5.55</v>
@@ -933,7 +960,7 @@
         <v>16.26</v>
       </c>
       <c r="J2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="K2">
         <v>5.55</v>
@@ -945,7 +972,7 @@
         <v>16.3</v>
       </c>
       <c r="N2" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="O2">
         <v>4.97</v>
@@ -957,7 +984,7 @@
         <v>18.14</v>
       </c>
       <c r="R2" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="S2">
         <v>4.82</v>
@@ -969,7 +996,7 @@
         <v>18.8</v>
       </c>
       <c r="V2" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="W2">
         <v>4.87</v>
@@ -981,7 +1008,7 @@
         <v>18.6</v>
       </c>
       <c r="Z2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="AA2">
         <v>4.87</v>
@@ -993,7 +1020,7 @@
         <v>18.58</v>
       </c>
       <c r="AD2" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="AE2">
         <v>4.96</v>
@@ -1005,7 +1032,7 @@
         <v>18.46</v>
       </c>
       <c r="AH2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="AI2">
         <v>4.34</v>
@@ -1017,7 +1044,7 @@
         <v>21.1</v>
       </c>
       <c r="AL2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="AM2">
         <v>3.62</v>
@@ -1029,7 +1056,7 @@
         <v>24.41</v>
       </c>
       <c r="AP2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="AQ2">
         <v>2.86</v>
@@ -1041,7 +1068,7 @@
         <v>32.47</v>
       </c>
       <c r="AT2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="AU2">
         <v>2.88</v>
@@ -1053,7 +1080,7 @@
         <v>32.36</v>
       </c>
       <c r="AX2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="AY2">
         <v>2.79</v>
@@ -1065,7 +1092,7 @@
         <v>33.86</v>
       </c>
       <c r="BB2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="BC2">
         <v>2.88</v>
@@ -1076,13 +1103,25 @@
       <c r="BE2">
         <v>33.08</v>
       </c>
+      <c r="BF2" t="s">
+        <v>123</v>
+      </c>
+      <c r="BG2">
+        <v>2.49</v>
+      </c>
+      <c r="BH2">
+        <v>37.54</v>
+      </c>
+      <c r="BI2">
+        <v>38.47</v>
+      </c>
     </row>
-    <row r="3" spans="1:57">
+    <row r="3" spans="1:61">
       <c r="A3" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B3" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C3">
         <v>5.58</v>
@@ -1094,7 +1133,7 @@
         <v>16.29</v>
       </c>
       <c r="F3" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="G3">
         <v>5.63</v>
@@ -1106,7 +1145,7 @@
         <v>16.04</v>
       </c>
       <c r="J3" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="K3">
         <v>5.63</v>
@@ -1118,7 +1157,7 @@
         <v>16.07</v>
       </c>
       <c r="N3" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="O3">
         <v>6.51</v>
@@ -1130,7 +1169,7 @@
         <v>13.76</v>
       </c>
       <c r="R3" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="S3">
         <v>6.88</v>
@@ -1142,7 +1181,7 @@
         <v>13.09</v>
       </c>
       <c r="V3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="W3">
         <v>6.34</v>
@@ -1154,7 +1193,7 @@
         <v>14.23</v>
       </c>
       <c r="Z3" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="AA3">
         <v>6.48</v>
@@ -1166,7 +1205,7 @@
         <v>13.89</v>
       </c>
       <c r="AD3" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="AE3">
         <v>6.63</v>
@@ -1178,7 +1217,7 @@
         <v>13.74</v>
       </c>
       <c r="AH3" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="AI3">
         <v>8.02</v>
@@ -1190,7 +1229,7 @@
         <v>11.26</v>
       </c>
       <c r="AL3" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="AM3">
         <v>8.140000000000001</v>
@@ -1202,7 +1241,7 @@
         <v>10.55</v>
       </c>
       <c r="AP3" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="AQ3">
         <v>8.59</v>
@@ -1214,7 +1253,7 @@
         <v>10.5</v>
       </c>
       <c r="AT3" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="AU3">
         <v>7.04</v>
@@ -1226,7 +1265,7 @@
         <v>12.93</v>
       </c>
       <c r="AX3" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="AY3">
         <v>6.98</v>
@@ -1238,7 +1277,7 @@
         <v>13.27</v>
       </c>
       <c r="BB3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="BC3">
         <v>4.75</v>
@@ -1249,13 +1288,25 @@
       <c r="BE3">
         <v>19.84</v>
       </c>
+      <c r="BF3" t="s">
+        <v>123</v>
+      </c>
+      <c r="BG3">
+        <v>5.25</v>
+      </c>
+      <c r="BH3">
+        <v>17.79</v>
+      </c>
+      <c r="BI3">
+        <v>17.91</v>
+      </c>
     </row>
-    <row r="4" spans="1:57">
+    <row r="4" spans="1:61">
       <c r="A4" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B4" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C4">
         <v>10.19</v>
@@ -1267,7 +1318,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="F4" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="G4">
         <v>10.33</v>
@@ -1279,7 +1330,7 @@
         <v>8.6</v>
       </c>
       <c r="J4" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="K4">
         <v>10.61</v>
@@ -1291,7 +1342,7 @@
         <v>8.390000000000001</v>
       </c>
       <c r="N4" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="O4">
         <v>9.4</v>
@@ -1303,7 +1354,7 @@
         <v>9.44</v>
       </c>
       <c r="R4" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="S4">
         <v>9.140000000000001</v>
@@ -1315,7 +1366,7 @@
         <v>9.779999999999999</v>
       </c>
       <c r="V4" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="W4">
         <v>8.710000000000001</v>
@@ -1327,7 +1378,7 @@
         <v>10.27</v>
       </c>
       <c r="Z4" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="AA4">
         <v>7.45</v>
@@ -1339,7 +1390,7 @@
         <v>12.04</v>
       </c>
       <c r="AD4" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="AE4">
         <v>7.04</v>
@@ -1351,7 +1402,7 @@
         <v>12.92</v>
       </c>
       <c r="AH4" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="AI4">
         <v>5.2</v>
@@ -1363,7 +1414,7 @@
         <v>17.53</v>
       </c>
       <c r="AL4" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="AM4">
         <v>4.84</v>
@@ -1375,7 +1426,7 @@
         <v>18.12</v>
       </c>
       <c r="AP4" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="AQ4">
         <v>5.11</v>
@@ -1387,7 +1438,7 @@
         <v>17.95</v>
       </c>
       <c r="AT4" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="AU4">
         <v>5.31</v>
@@ -1399,7 +1450,7 @@
         <v>17.31</v>
       </c>
       <c r="AX4" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="AY4">
         <v>5.53</v>
@@ -1411,7 +1462,7 @@
         <v>16.85</v>
       </c>
       <c r="BB4" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="BC4">
         <v>5.05</v>
@@ -1422,13 +1473,25 @@
       <c r="BE4">
         <v>18.63</v>
       </c>
+      <c r="BF4" t="s">
+        <v>123</v>
+      </c>
+      <c r="BG4">
+        <v>5.34</v>
+      </c>
+      <c r="BH4">
+        <v>17.51</v>
+      </c>
+      <c r="BI4">
+        <v>17.62</v>
+      </c>
     </row>
-    <row r="5" spans="1:57">
+    <row r="5" spans="1:61">
       <c r="A5" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B5" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C5">
         <v>8.15</v>
@@ -1440,7 +1503,7 @@
         <v>11.06</v>
       </c>
       <c r="F5" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="G5">
         <v>8.42</v>
@@ -1452,7 +1515,7 @@
         <v>10.62</v>
       </c>
       <c r="J5" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="K5">
         <v>8.390000000000001</v>
@@ -1464,7 +1527,7 @@
         <v>10.69</v>
       </c>
       <c r="N5" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="O5">
         <v>8.33</v>
@@ -1476,7 +1539,7 @@
         <v>10.68</v>
       </c>
       <c r="R5" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="S5">
         <v>7.04</v>
@@ -1488,7 +1551,7 @@
         <v>12.77</v>
       </c>
       <c r="V5" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="W5">
         <v>7.11</v>
@@ -1500,7 +1563,7 @@
         <v>12.65</v>
       </c>
       <c r="Z5" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="AA5">
         <v>7.61</v>
@@ -1512,7 +1575,7 @@
         <v>11.79</v>
       </c>
       <c r="AD5" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="AE5">
         <v>8.43</v>
@@ -1524,7 +1587,7 @@
         <v>10.74</v>
       </c>
       <c r="AH5" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="AI5">
         <v>8.19</v>
@@ -1536,7 +1599,7 @@
         <v>11.02</v>
       </c>
       <c r="AL5" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="AM5">
         <v>8.220000000000001</v>
@@ -1548,7 +1611,7 @@
         <v>10.43</v>
       </c>
       <c r="AP5" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="AQ5">
         <v>9.800000000000001</v>
@@ -1560,7 +1623,7 @@
         <v>9.15</v>
       </c>
       <c r="AT5" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="AU5">
         <v>11.05</v>
@@ -1572,7 +1635,7 @@
         <v>8.07</v>
       </c>
       <c r="AX5" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="AY5">
         <v>7.4</v>
@@ -1584,7 +1647,7 @@
         <v>12.49</v>
       </c>
       <c r="BB5" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="BC5">
         <v>5.89</v>
@@ -1595,13 +1658,25 @@
       <c r="BE5">
         <v>15.9</v>
       </c>
+      <c r="BF5" t="s">
+        <v>123</v>
+      </c>
+      <c r="BG5">
+        <v>5.73</v>
+      </c>
+      <c r="BH5">
+        <v>16.29</v>
+      </c>
+      <c r="BI5">
+        <v>16.36</v>
+      </c>
     </row>
-    <row r="6" spans="1:57">
+    <row r="6" spans="1:61">
       <c r="A6" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B6" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C6">
         <v>32.29</v>
@@ -1613,7 +1688,7 @@
         <v>2.6</v>
       </c>
       <c r="F6" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="G6">
         <v>33</v>
@@ -1625,7 +1700,7 @@
         <v>2.49</v>
       </c>
       <c r="J6" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="K6">
         <v>34.14</v>
@@ -1637,7 +1712,7 @@
         <v>2.42</v>
       </c>
       <c r="N6" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="O6">
         <v>30.43</v>
@@ -1649,7 +1724,7 @@
         <v>2.71</v>
       </c>
       <c r="R6" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="S6">
         <v>31.5</v>
@@ -1661,7 +1736,7 @@
         <v>2.64</v>
       </c>
       <c r="V6" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="W6">
         <v>36.57</v>
@@ -1673,7 +1748,7 @@
         <v>2.22</v>
       </c>
       <c r="Z6" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="AA6">
         <v>32.43</v>
@@ -1685,7 +1760,7 @@
         <v>2.53</v>
       </c>
       <c r="AD6" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="AE6">
         <v>32.71</v>
@@ -1697,7 +1772,7 @@
         <v>2.56</v>
       </c>
       <c r="AH6" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="AI6">
         <v>35.71</v>
@@ -1709,7 +1784,7 @@
         <v>2.29</v>
       </c>
       <c r="AL6" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="AM6">
         <v>37.71</v>
@@ -1721,7 +1796,7 @@
         <v>1.88</v>
       </c>
       <c r="AP6" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="AQ6">
         <v>37</v>
@@ -1733,7 +1808,7 @@
         <v>2.13</v>
       </c>
       <c r="AT6" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="AU6">
         <v>38.5</v>
@@ -1745,7 +1820,7 @@
         <v>2</v>
       </c>
       <c r="AX6" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="AY6">
         <v>21</v>
@@ -1757,7 +1832,7 @@
         <v>4.12</v>
       </c>
       <c r="BB6" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="BC6">
         <v>16.2</v>
@@ -1768,2706 +1843,2766 @@
       <c r="BE6">
         <v>5.44</v>
       </c>
+      <c r="BF6" t="s">
+        <v>123</v>
+      </c>
+      <c r="BG6">
+        <v>16.28</v>
+      </c>
+      <c r="BH6">
+        <v>5.74</v>
+      </c>
+      <c r="BI6">
+        <v>5.39</v>
+      </c>
     </row>
-    <row r="7" spans="1:57">
+    <row r="7" spans="1:61">
       <c r="A7" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B7" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C7">
+        <v>37.71</v>
+      </c>
+      <c r="D7">
+        <v>2.25</v>
+      </c>
+      <c r="E7">
+        <v>2.19</v>
+      </c>
+      <c r="F7" t="s">
+        <v>110</v>
+      </c>
+      <c r="G7">
+        <v>37.71</v>
+      </c>
+      <c r="H7">
+        <v>2.23</v>
+      </c>
+      <c r="I7">
+        <v>2.15</v>
+      </c>
+      <c r="J7" t="s">
+        <v>111</v>
+      </c>
+      <c r="K7">
+        <v>39.43</v>
+      </c>
+      <c r="L7">
+        <v>2.14</v>
+      </c>
+      <c r="M7">
+        <v>2.06</v>
+      </c>
+      <c r="N7" t="s">
+        <v>112</v>
+      </c>
+      <c r="O7">
+        <v>42</v>
+      </c>
+      <c r="P7">
+        <v>1.99</v>
+      </c>
+      <c r="Q7">
+        <v>1.88</v>
+      </c>
+      <c r="R7" t="s">
+        <v>113</v>
+      </c>
+      <c r="S7">
+        <v>42.17</v>
+      </c>
+      <c r="T7">
+        <v>2</v>
+      </c>
+      <c r="U7">
+        <v>1.9</v>
+      </c>
+      <c r="V7" t="s">
+        <v>114</v>
+      </c>
+      <c r="W7">
+        <v>47.71</v>
+      </c>
+      <c r="X7">
+        <v>1.77</v>
+      </c>
+      <c r="Y7">
+        <v>1.64</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>115</v>
+      </c>
+      <c r="AA7">
+        <v>52.71</v>
+      </c>
+      <c r="AB7">
+        <v>1.6</v>
+      </c>
+      <c r="AC7">
+        <v>1.45</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>116</v>
+      </c>
+      <c r="AE7">
+        <v>54.14</v>
+      </c>
+      <c r="AF7">
+        <v>1.59</v>
+      </c>
+      <c r="AG7">
+        <v>1.45</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>117</v>
+      </c>
+      <c r="AI7">
+        <v>49.14</v>
+      </c>
+      <c r="AJ7">
+        <v>1.75</v>
+      </c>
+      <c r="AK7">
+        <v>1.59</v>
+      </c>
+      <c r="AL7" t="s">
+        <v>118</v>
+      </c>
+      <c r="AM7">
+        <v>52</v>
+      </c>
+      <c r="AN7">
+        <v>1.55</v>
+      </c>
+      <c r="AO7">
+        <v>1.25</v>
+      </c>
+      <c r="AP7" t="s">
+        <v>119</v>
+      </c>
+      <c r="AQ7">
+        <v>41.83</v>
+      </c>
+      <c r="AR7">
+        <v>2.09</v>
+      </c>
+      <c r="AS7">
+        <v>1.84</v>
+      </c>
+      <c r="AT7" t="s">
+        <v>120</v>
+      </c>
+      <c r="AU7">
+        <v>48.5</v>
+      </c>
+      <c r="AV7">
+        <v>1.83</v>
+      </c>
+      <c r="AW7">
+        <v>1.51</v>
+      </c>
+      <c r="AX7" t="s">
+        <v>121</v>
+      </c>
+      <c r="AY7">
+        <v>49.33</v>
+      </c>
+      <c r="AZ7">
+        <v>1.84</v>
+      </c>
+      <c r="BA7">
+        <v>1.54</v>
+      </c>
+      <c r="BB7" t="s">
+        <v>122</v>
+      </c>
+      <c r="BC7">
+        <v>32</v>
+      </c>
+      <c r="BD7">
+        <v>2.9</v>
+      </c>
+      <c r="BE7">
+        <v>2.51</v>
+      </c>
+      <c r="BF7" t="s">
+        <v>123</v>
+      </c>
+      <c r="BG7">
+        <v>35.17</v>
+      </c>
+      <c r="BH7">
+        <v>2.66</v>
+      </c>
+      <c r="BI7">
+        <v>2.22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:61">
+      <c r="A8" t="s">
+        <v>67</v>
+      </c>
+      <c r="B8" t="s">
+        <v>109</v>
+      </c>
+      <c r="C8">
+        <v>74.43000000000001</v>
+      </c>
+      <c r="D8">
+        <v>1.14</v>
+      </c>
+      <c r="E8">
+        <v>0.99</v>
+      </c>
+      <c r="F8" t="s">
+        <v>110</v>
+      </c>
+      <c r="G8">
+        <v>75.14</v>
+      </c>
+      <c r="H8">
+        <v>1.12</v>
+      </c>
+      <c r="I8">
+        <v>0.95</v>
+      </c>
+      <c r="J8" t="s">
+        <v>111</v>
+      </c>
+      <c r="K8">
+        <v>83.56999999999999</v>
+      </c>
+      <c r="L8">
+        <v>1.01</v>
+      </c>
+      <c r="M8">
+        <v>0.84</v>
+      </c>
+      <c r="N8" t="s">
+        <v>112</v>
+      </c>
+      <c r="O8">
+        <v>87.70999999999999</v>
+      </c>
+      <c r="P8">
+        <v>0.95</v>
+      </c>
+      <c r="Q8">
+        <v>0.77</v>
+      </c>
+      <c r="R8" t="s">
+        <v>113</v>
+      </c>
+      <c r="S8">
+        <v>78</v>
+      </c>
+      <c r="T8">
+        <v>1.08</v>
+      </c>
+      <c r="U8">
+        <v>0.92</v>
+      </c>
+      <c r="V8" t="s">
+        <v>114</v>
+      </c>
+      <c r="W8">
+        <v>81.43000000000001</v>
+      </c>
+      <c r="X8">
+        <v>1.04</v>
+      </c>
+      <c r="Y8">
+        <v>0.86</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>115</v>
+      </c>
+      <c r="AA8">
+        <v>80.14</v>
+      </c>
+      <c r="AB8">
+        <v>1.05</v>
+      </c>
+      <c r="AC8">
+        <v>0.87</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>116</v>
+      </c>
+      <c r="AE8">
+        <v>76.43000000000001</v>
+      </c>
+      <c r="AF8">
+        <v>1.12</v>
+      </c>
+      <c r="AG8">
+        <v>0.96</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>117</v>
+      </c>
+      <c r="AI8">
+        <v>73.70999999999999</v>
+      </c>
+      <c r="AJ8">
+        <v>1.16</v>
+      </c>
+      <c r="AK8">
+        <v>0.97</v>
+      </c>
+      <c r="AL8" t="s">
+        <v>118</v>
+      </c>
+      <c r="AM8">
+        <v>78.70999999999999</v>
+      </c>
+      <c r="AN8">
+        <v>1.03</v>
+      </c>
+      <c r="AO8">
+        <v>0.7</v>
+      </c>
+      <c r="AP8" t="s">
+        <v>119</v>
+      </c>
+      <c r="AQ8">
+        <v>86.33</v>
+      </c>
+      <c r="AR8">
+        <v>1.01</v>
+      </c>
+      <c r="AS8">
+        <v>0.73</v>
+      </c>
+      <c r="AT8" t="s">
+        <v>120</v>
+      </c>
+      <c r="AU8">
+        <v>66</v>
+      </c>
+      <c r="AV8">
+        <v>1.34</v>
+      </c>
+      <c r="AW8">
+        <v>1.01</v>
+      </c>
+      <c r="AX8" t="s">
+        <v>121</v>
+      </c>
+      <c r="AY8">
+        <v>71.33</v>
+      </c>
+      <c r="AZ8">
+        <v>1.27</v>
+      </c>
+      <c r="BA8">
+        <v>0.96</v>
+      </c>
+      <c r="BB8" t="s">
+        <v>122</v>
+      </c>
+      <c r="BC8">
+        <v>38.5</v>
+      </c>
+      <c r="BD8">
+        <v>2.41</v>
+      </c>
+      <c r="BE8">
+        <v>2.01</v>
+      </c>
+      <c r="BF8" t="s">
+        <v>123</v>
+      </c>
+      <c r="BG8">
+        <v>37.83</v>
+      </c>
+      <c r="BH8">
+        <v>2.47</v>
+      </c>
+      <c r="BI8">
+        <v>2.03</v>
+      </c>
+    </row>
+    <row r="9" spans="1:61">
+      <c r="A9" t="s">
+        <v>68</v>
+      </c>
+      <c r="B9" t="s">
+        <v>109</v>
+      </c>
+      <c r="C9">
+        <v>367.57</v>
+      </c>
+      <c r="D9">
+        <v>0.23</v>
+      </c>
+      <c r="E9">
+        <v>0.1</v>
+      </c>
+      <c r="F9" t="s">
+        <v>110</v>
+      </c>
+      <c r="G9">
+        <v>383</v>
+      </c>
+      <c r="H9">
+        <v>0.22</v>
+      </c>
+      <c r="I9">
+        <v>0.08</v>
+      </c>
+      <c r="J9" t="s">
+        <v>111</v>
+      </c>
+      <c r="K9">
+        <v>378.86</v>
+      </c>
+      <c r="L9">
+        <v>0.22</v>
+      </c>
+      <c r="M9">
+        <v>0.09</v>
+      </c>
+      <c r="N9" t="s">
+        <v>112</v>
+      </c>
+      <c r="O9">
+        <v>474.57</v>
+      </c>
+      <c r="P9">
+        <v>0.18</v>
+      </c>
+      <c r="Q9">
+        <v>0.05</v>
+      </c>
+      <c r="R9" t="s">
+        <v>113</v>
+      </c>
+      <c r="S9">
+        <v>530.67</v>
+      </c>
+      <c r="T9">
+        <v>0.16</v>
+      </c>
+      <c r="U9">
+        <v>0.05</v>
+      </c>
+      <c r="V9" t="s">
+        <v>114</v>
+      </c>
+      <c r="W9">
+        <v>518</v>
+      </c>
+      <c r="X9">
+        <v>0.16</v>
+      </c>
+      <c r="Y9">
+        <v>0.05</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>115</v>
+      </c>
+      <c r="AA9">
+        <v>529.5700000000001</v>
+      </c>
+      <c r="AB9">
+        <v>0.16</v>
+      </c>
+      <c r="AC9">
+        <v>0.04</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>116</v>
+      </c>
+      <c r="AE9">
+        <v>576.4299999999999</v>
+      </c>
+      <c r="AF9">
+        <v>0.15</v>
+      </c>
+      <c r="AG9">
+        <v>0.04</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>117</v>
+      </c>
+      <c r="AI9">
+        <v>458.71</v>
+      </c>
+      <c r="AJ9">
+        <v>0.19</v>
+      </c>
+      <c r="AK9">
+        <v>0.06</v>
+      </c>
+      <c r="AL9" t="s">
+        <v>118</v>
+      </c>
+      <c r="AM9">
+        <v>391.29</v>
+      </c>
+      <c r="AN9">
+        <v>0.21</v>
+      </c>
+      <c r="AO9">
+        <v>0.04</v>
+      </c>
+      <c r="AP9" t="s">
+        <v>119</v>
+      </c>
+      <c r="AQ9">
+        <v>437.83</v>
+      </c>
+      <c r="AR9">
+        <v>0.2</v>
+      </c>
+      <c r="AS9">
+        <v>0.05</v>
+      </c>
+      <c r="AT9" t="s">
+        <v>120</v>
+      </c>
+      <c r="AX9" t="s">
+        <v>121</v>
+      </c>
+      <c r="BB9" t="s">
+        <v>122</v>
+      </c>
+      <c r="BF9" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="10" spans="1:61">
+      <c r="A10" t="s">
+        <v>69</v>
+      </c>
+      <c r="B10" t="s">
+        <v>109</v>
+      </c>
+      <c r="C10">
+        <v>442.71</v>
+      </c>
+      <c r="D10">
+        <v>0.19</v>
+      </c>
+      <c r="E10">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="F10" t="s">
+        <v>110</v>
+      </c>
+      <c r="G10">
+        <v>462.29</v>
+      </c>
+      <c r="H10">
+        <v>0.18</v>
+      </c>
+      <c r="I10">
+        <v>0.06</v>
+      </c>
+      <c r="J10" t="s">
+        <v>111</v>
+      </c>
+      <c r="K10">
+        <v>186</v>
+      </c>
+      <c r="L10">
+        <v>0.45</v>
+      </c>
+      <c r="M10">
+        <v>0.28</v>
+      </c>
+      <c r="N10" t="s">
+        <v>112</v>
+      </c>
+      <c r="O10">
+        <v>123.14</v>
+      </c>
+      <c r="P10">
+        <v>0.68</v>
+      </c>
+      <c r="Q10">
+        <v>0.49</v>
+      </c>
+      <c r="R10" t="s">
+        <v>113</v>
+      </c>
+      <c r="S10">
+        <v>128.5</v>
+      </c>
+      <c r="T10">
+        <v>0.66</v>
+      </c>
+      <c r="U10">
+        <v>0.47</v>
+      </c>
+      <c r="V10" t="s">
+        <v>114</v>
+      </c>
+      <c r="W10">
+        <v>174.43</v>
+      </c>
+      <c r="X10">
+        <v>0.48</v>
+      </c>
+      <c r="Y10">
+        <v>0.3</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>115</v>
+      </c>
+      <c r="AA10">
+        <v>206.33</v>
+      </c>
+      <c r="AB10">
+        <v>0.41</v>
+      </c>
+      <c r="AC10">
+        <v>0.23</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>116</v>
+      </c>
+      <c r="AE10">
+        <v>199.83</v>
+      </c>
+      <c r="AF10">
+        <v>0.43</v>
+      </c>
+      <c r="AG10">
+        <v>0.26</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>117</v>
+      </c>
+      <c r="AI10">
+        <v>249.14</v>
+      </c>
+      <c r="AJ10">
+        <v>0.34</v>
+      </c>
+      <c r="AK10">
+        <v>0.17</v>
+      </c>
+      <c r="AL10" t="s">
+        <v>118</v>
+      </c>
+      <c r="AM10">
+        <v>290.57</v>
+      </c>
+      <c r="AN10">
+        <v>0.28</v>
+      </c>
+      <c r="AO10">
+        <v>0.08</v>
+      </c>
+      <c r="AP10" t="s">
+        <v>119</v>
+      </c>
+      <c r="AQ10">
+        <v>333.67</v>
+      </c>
+      <c r="AR10">
+        <v>0.26</v>
+      </c>
+      <c r="AS10">
+        <v>0.08</v>
+      </c>
+      <c r="AT10" t="s">
+        <v>120</v>
+      </c>
+      <c r="AX10" t="s">
+        <v>121</v>
+      </c>
+      <c r="BB10" t="s">
+        <v>122</v>
+      </c>
+      <c r="BF10" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="11" spans="1:61">
+      <c r="A11" t="s">
+        <v>70</v>
+      </c>
+      <c r="B11" t="s">
+        <v>109</v>
+      </c>
+      <c r="C11">
+        <v>370.43</v>
+      </c>
+      <c r="D11">
+        <v>0.23</v>
+      </c>
+      <c r="E11">
+        <v>0.1</v>
+      </c>
+      <c r="F11" t="s">
+        <v>110</v>
+      </c>
+      <c r="G11">
+        <v>376.71</v>
+      </c>
+      <c r="H11">
+        <v>0.22</v>
+      </c>
+      <c r="I11">
+        <v>0.08</v>
+      </c>
+      <c r="J11" t="s">
+        <v>111</v>
+      </c>
+      <c r="K11">
+        <v>383.71</v>
+      </c>
+      <c r="L11">
+        <v>0.22</v>
+      </c>
+      <c r="M11">
+        <v>0.08</v>
+      </c>
+      <c r="N11" t="s">
+        <v>112</v>
+      </c>
+      <c r="O11">
+        <v>390.71</v>
+      </c>
+      <c r="P11">
+        <v>0.21</v>
+      </c>
+      <c r="Q11">
+        <v>0.08</v>
+      </c>
+      <c r="R11" t="s">
+        <v>113</v>
+      </c>
+      <c r="S11">
+        <v>473</v>
+      </c>
+      <c r="T11">
+        <v>0.18</v>
+      </c>
+      <c r="U11">
+        <v>0.06</v>
+      </c>
+      <c r="V11" t="s">
+        <v>114</v>
+      </c>
+      <c r="W11">
+        <v>514</v>
+      </c>
+      <c r="X11">
+        <v>0.16</v>
+      </c>
+      <c r="Y11">
+        <v>0.05</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>115</v>
+      </c>
+      <c r="AA11">
+        <v>547.86</v>
+      </c>
+      <c r="AB11">
+        <v>0.15</v>
+      </c>
+      <c r="AC11">
+        <v>0.04</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>116</v>
+      </c>
+      <c r="AE11">
+        <v>509.43</v>
+      </c>
+      <c r="AF11">
+        <v>0.17</v>
+      </c>
+      <c r="AG11">
+        <v>0.05</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>117</v>
+      </c>
+      <c r="AI11">
+        <v>503.71</v>
+      </c>
+      <c r="AJ11">
+        <v>0.17</v>
+      </c>
+      <c r="AK11">
+        <v>0.05</v>
+      </c>
+      <c r="AL11" t="s">
+        <v>118</v>
+      </c>
+      <c r="AM11">
+        <v>576.4299999999999</v>
+      </c>
+      <c r="AN11">
+        <v>0.14</v>
+      </c>
+      <c r="AO11">
+        <v>0.02</v>
+      </c>
+      <c r="AP11" t="s">
+        <v>119</v>
+      </c>
+      <c r="AT11" t="s">
+        <v>120</v>
+      </c>
+      <c r="AX11" t="s">
+        <v>121</v>
+      </c>
+      <c r="BB11" t="s">
+        <v>122</v>
+      </c>
+      <c r="BF11" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="12" spans="1:61">
+      <c r="A12" t="s">
+        <v>71</v>
+      </c>
+      <c r="B12" t="s">
+        <v>109</v>
+      </c>
+      <c r="C12">
+        <v>9.970000000000001</v>
+      </c>
+      <c r="D12">
+        <v>8.52</v>
+      </c>
+      <c r="E12">
+        <v>8.99</v>
+      </c>
+      <c r="F12" t="s">
+        <v>110</v>
+      </c>
+      <c r="G12">
+        <v>10.11</v>
+      </c>
+      <c r="H12">
+        <v>8.32</v>
+      </c>
+      <c r="I12">
+        <v>8.789999999999999</v>
+      </c>
+      <c r="J12" t="s">
+        <v>111</v>
+      </c>
+      <c r="K12">
+        <v>11.04</v>
+      </c>
+      <c r="L12">
+        <v>7.64</v>
+      </c>
+      <c r="M12">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="N12" t="s">
+        <v>112</v>
+      </c>
+      <c r="O12">
+        <v>11.39</v>
+      </c>
+      <c r="P12">
+        <v>7.33</v>
+      </c>
+      <c r="Q12">
+        <v>7.74</v>
+      </c>
+      <c r="R12" t="s">
+        <v>113</v>
+      </c>
+      <c r="S12">
+        <v>12.2</v>
+      </c>
+      <c r="T12">
+        <v>6.91</v>
+      </c>
+      <c r="U12">
+        <v>7.25</v>
+      </c>
+      <c r="V12" t="s">
+        <v>114</v>
+      </c>
+      <c r="W12">
+        <v>13.17</v>
+      </c>
+      <c r="X12">
+        <v>6.41</v>
+      </c>
+      <c r="Y12">
+        <v>6.69</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>115</v>
+      </c>
+      <c r="AA12">
+        <v>14.94</v>
+      </c>
+      <c r="AB12">
+        <v>5.65</v>
+      </c>
+      <c r="AC12">
+        <v>5.85</v>
+      </c>
+      <c r="AD12" t="s">
+        <v>116</v>
+      </c>
+      <c r="AE12">
+        <v>13.31</v>
+      </c>
+      <c r="AF12">
+        <v>6.46</v>
+      </c>
+      <c r="AG12">
+        <v>6.7</v>
+      </c>
+      <c r="AH12" t="s">
+        <v>117</v>
+      </c>
+      <c r="AI12">
+        <v>13.81</v>
+      </c>
+      <c r="AJ12">
+        <v>6.21</v>
+      </c>
+      <c r="AK12">
+        <v>6.4</v>
+      </c>
+      <c r="AL12" t="s">
+        <v>118</v>
+      </c>
+      <c r="AM12">
+        <v>11.47</v>
+      </c>
+      <c r="AN12">
+        <v>7.05</v>
+      </c>
+      <c r="AO12">
+        <v>7.32</v>
+      </c>
+      <c r="AP12" t="s">
+        <v>119</v>
+      </c>
+      <c r="AQ12">
+        <v>12.28</v>
+      </c>
+      <c r="AR12">
+        <v>7.13</v>
+      </c>
+      <c r="AS12">
+        <v>7.22</v>
+      </c>
+      <c r="AT12" t="s">
+        <v>120</v>
+      </c>
+      <c r="AU12">
+        <v>12.7</v>
+      </c>
+      <c r="AV12">
+        <v>6.97</v>
+      </c>
+      <c r="AW12">
+        <v>6.96</v>
+      </c>
+      <c r="AX12" t="s">
+        <v>121</v>
+      </c>
+      <c r="BB12" t="s">
+        <v>122</v>
+      </c>
+      <c r="BF12" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="13" spans="1:61">
+      <c r="A13" t="s">
+        <v>72</v>
+      </c>
+      <c r="B13" t="s">
+        <v>109</v>
+      </c>
+      <c r="C13">
+        <v>1926.43</v>
+      </c>
+      <c r="D13">
+        <v>0.04</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13" t="s">
+        <v>110</v>
+      </c>
+      <c r="G13">
+        <v>1926.43</v>
+      </c>
+      <c r="H13">
+        <v>0.04</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13" t="s">
+        <v>111</v>
+      </c>
+      <c r="K13">
+        <v>2355</v>
+      </c>
+      <c r="L13">
+        <v>0.04</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s">
+        <v>112</v>
+      </c>
+      <c r="O13">
+        <v>2355</v>
+      </c>
+      <c r="P13">
+        <v>0.04</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13" t="s">
+        <v>113</v>
+      </c>
+      <c r="S13">
+        <v>2596.6</v>
+      </c>
+      <c r="T13">
+        <v>0.03</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13" t="s">
+        <v>114</v>
+      </c>
+      <c r="W13">
+        <v>1997.33</v>
+      </c>
+      <c r="X13">
+        <v>0.04</v>
+      </c>
+      <c r="Y13">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>115</v>
+      </c>
+      <c r="AA13">
+        <v>1855</v>
+      </c>
+      <c r="AB13">
+        <v>0.05</v>
+      </c>
+      <c r="AC13">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="s">
+        <v>116</v>
+      </c>
+      <c r="AE13">
+        <v>2001</v>
+      </c>
+      <c r="AF13">
+        <v>0.04</v>
+      </c>
+      <c r="AG13">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="s">
+        <v>117</v>
+      </c>
+      <c r="AL13" t="s">
+        <v>118</v>
+      </c>
+      <c r="AP13" t="s">
+        <v>119</v>
+      </c>
+      <c r="AT13" t="s">
+        <v>120</v>
+      </c>
+      <c r="AX13" t="s">
+        <v>121</v>
+      </c>
+      <c r="BB13" t="s">
+        <v>122</v>
+      </c>
+      <c r="BF13" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="14" spans="1:61">
+      <c r="A14" t="s">
+        <v>73</v>
+      </c>
+      <c r="B14" t="s">
+        <v>109</v>
+      </c>
+      <c r="C14">
+        <v>747.86</v>
+      </c>
+      <c r="D14">
+        <v>0.11</v>
+      </c>
+      <c r="E14">
+        <v>0.03</v>
+      </c>
+      <c r="F14" t="s">
+        <v>110</v>
+      </c>
+      <c r="G14">
+        <v>747.86</v>
+      </c>
+      <c r="H14">
+        <v>0.11</v>
+      </c>
+      <c r="I14">
+        <v>0.02</v>
+      </c>
+      <c r="J14" t="s">
+        <v>111</v>
+      </c>
+      <c r="K14">
+        <v>747.86</v>
+      </c>
+      <c r="L14">
+        <v>0.11</v>
+      </c>
+      <c r="M14">
+        <v>0.02</v>
+      </c>
+      <c r="N14" t="s">
+        <v>112</v>
+      </c>
+      <c r="O14">
+        <v>747.86</v>
+      </c>
+      <c r="P14">
+        <v>0.11</v>
+      </c>
+      <c r="Q14">
+        <v>0.02</v>
+      </c>
+      <c r="R14" t="s">
+        <v>113</v>
+      </c>
+      <c r="S14">
+        <v>607.5</v>
+      </c>
+      <c r="T14">
+        <v>0.14</v>
+      </c>
+      <c r="U14">
+        <v>0.04</v>
+      </c>
+      <c r="V14" t="s">
+        <v>114</v>
+      </c>
+      <c r="W14">
+        <v>569.29</v>
+      </c>
+      <c r="X14">
+        <v>0.15</v>
+      </c>
+      <c r="Y14">
+        <v>0.04</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>115</v>
+      </c>
+      <c r="AA14">
+        <v>647.86</v>
+      </c>
+      <c r="AB14">
+        <v>0.13</v>
+      </c>
+      <c r="AC14">
+        <v>0.03</v>
+      </c>
+      <c r="AD14" t="s">
+        <v>116</v>
+      </c>
+      <c r="AE14">
+        <v>647.86</v>
+      </c>
+      <c r="AF14">
+        <v>0.13</v>
+      </c>
+      <c r="AG14">
+        <v>0.03</v>
+      </c>
+      <c r="AH14" t="s">
+        <v>117</v>
+      </c>
+      <c r="AI14">
+        <v>612.14</v>
+      </c>
+      <c r="AJ14">
+        <v>0.14</v>
+      </c>
+      <c r="AK14">
+        <v>0.03</v>
+      </c>
+      <c r="AL14" t="s">
+        <v>118</v>
+      </c>
+      <c r="AM14">
+        <v>551</v>
+      </c>
+      <c r="AN14">
+        <v>0.15</v>
+      </c>
+      <c r="AO14">
+        <v>0.02</v>
+      </c>
+      <c r="AP14" t="s">
+        <v>119</v>
+      </c>
+      <c r="AT14" t="s">
+        <v>120</v>
+      </c>
+      <c r="AX14" t="s">
+        <v>121</v>
+      </c>
+      <c r="BB14" t="s">
+        <v>122</v>
+      </c>
+      <c r="BF14" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="15" spans="1:61">
+      <c r="A15" t="s">
+        <v>74</v>
+      </c>
+      <c r="B15" t="s">
+        <v>109</v>
+      </c>
+      <c r="C15">
+        <v>15.6</v>
+      </c>
+      <c r="D15">
+        <v>5.44</v>
+      </c>
+      <c r="E15">
+        <v>5.65</v>
+      </c>
+      <c r="F15" t="s">
+        <v>110</v>
+      </c>
+      <c r="G15">
+        <v>15.67</v>
+      </c>
+      <c r="H15">
+        <v>5.37</v>
+      </c>
+      <c r="I15">
+        <v>5.57</v>
+      </c>
+      <c r="J15" t="s">
+        <v>111</v>
+      </c>
+      <c r="K15">
+        <v>15.39</v>
+      </c>
+      <c r="L15">
+        <v>5.48</v>
+      </c>
+      <c r="M15">
+        <v>5.7</v>
+      </c>
+      <c r="N15" t="s">
+        <v>112</v>
+      </c>
+      <c r="O15">
+        <v>14.67</v>
+      </c>
+      <c r="P15">
+        <v>5.69</v>
+      </c>
+      <c r="Q15">
+        <v>5.93</v>
+      </c>
+      <c r="R15" t="s">
+        <v>113</v>
+      </c>
+      <c r="S15">
+        <v>14.87</v>
+      </c>
+      <c r="T15">
+        <v>5.67</v>
+      </c>
+      <c r="U15">
+        <v>5.9</v>
+      </c>
+      <c r="V15" t="s">
+        <v>114</v>
+      </c>
+      <c r="W15">
+        <v>14.53</v>
+      </c>
+      <c r="X15">
+        <v>5.81</v>
+      </c>
+      <c r="Y15">
+        <v>6.03</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>115</v>
+      </c>
+      <c r="AA15">
+        <v>14.6</v>
+      </c>
+      <c r="AB15">
+        <v>5.78</v>
+      </c>
+      <c r="AC15">
+        <v>5.99</v>
+      </c>
+      <c r="AD15" t="s">
+        <v>116</v>
+      </c>
+      <c r="AE15">
+        <v>17.8</v>
+      </c>
+      <c r="AF15">
+        <v>4.83</v>
+      </c>
+      <c r="AG15">
+        <v>4.94</v>
+      </c>
+      <c r="AH15" t="s">
+        <v>117</v>
+      </c>
+      <c r="AI15">
+        <v>21.14</v>
+      </c>
+      <c r="AJ15">
+        <v>4.06</v>
+      </c>
+      <c r="AK15">
+        <v>4.08</v>
+      </c>
+      <c r="AL15" t="s">
+        <v>118</v>
+      </c>
+      <c r="AM15">
+        <v>26</v>
+      </c>
+      <c r="AN15">
+        <v>3.11</v>
+      </c>
+      <c r="AO15">
+        <v>2.94</v>
+      </c>
+      <c r="AP15" t="s">
+        <v>119</v>
+      </c>
+      <c r="AT15" t="s">
+        <v>120</v>
+      </c>
+      <c r="AX15" t="s">
+        <v>121</v>
+      </c>
+      <c r="BB15" t="s">
+        <v>122</v>
+      </c>
+      <c r="BF15" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="16" spans="1:61">
+      <c r="A16" t="s">
+        <v>75</v>
+      </c>
+      <c r="B16" t="s">
+        <v>109</v>
+      </c>
+      <c r="C16">
+        <v>89</v>
+      </c>
+      <c r="D16">
+        <v>0.95</v>
+      </c>
+      <c r="E16">
+        <v>0.8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>110</v>
+      </c>
+      <c r="G16">
+        <v>90.43000000000001</v>
+      </c>
+      <c r="H16">
+        <v>0.93</v>
+      </c>
+      <c r="I16">
+        <v>0.75</v>
+      </c>
+      <c r="J16" t="s">
+        <v>111</v>
+      </c>
+      <c r="K16">
+        <v>133.71</v>
+      </c>
+      <c r="L16">
+        <v>0.63</v>
+      </c>
+      <c r="M16">
+        <v>0.45</v>
+      </c>
+      <c r="N16" t="s">
+        <v>112</v>
+      </c>
+      <c r="O16">
+        <v>135.14</v>
+      </c>
+      <c r="P16">
+        <v>0.62</v>
+      </c>
+      <c r="Q16">
+        <v>0.43</v>
+      </c>
+      <c r="R16" t="s">
+        <v>113</v>
+      </c>
+      <c r="S16">
+        <v>148.33</v>
+      </c>
+      <c r="T16">
+        <v>0.57</v>
+      </c>
+      <c r="U16">
+        <v>0.39</v>
+      </c>
+      <c r="V16" t="s">
+        <v>114</v>
+      </c>
+      <c r="W16">
+        <v>279.29</v>
+      </c>
+      <c r="X16">
+        <v>0.3</v>
+      </c>
+      <c r="Y16">
+        <v>0.14</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>115</v>
+      </c>
+      <c r="AA16">
+        <v>289.29</v>
+      </c>
+      <c r="AB16">
+        <v>0.29</v>
+      </c>
+      <c r="AC16">
+        <v>0.13</v>
+      </c>
+      <c r="AD16" t="s">
+        <v>116</v>
+      </c>
+      <c r="AE16">
+        <v>123.86</v>
+      </c>
+      <c r="AF16">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AG16">
+        <v>0.51</v>
+      </c>
+      <c r="AH16" t="s">
+        <v>117</v>
+      </c>
+      <c r="AI16">
+        <v>127.43</v>
+      </c>
+      <c r="AJ16">
+        <v>0.67</v>
+      </c>
+      <c r="AK16">
+        <v>0.47</v>
+      </c>
+      <c r="AL16" t="s">
+        <v>118</v>
+      </c>
+      <c r="AM16">
+        <v>129.57</v>
+      </c>
+      <c r="AN16">
+        <v>0.62</v>
+      </c>
+      <c r="AO16">
+        <v>0.33</v>
+      </c>
+      <c r="AP16" t="s">
+        <v>119</v>
+      </c>
+      <c r="AT16" t="s">
+        <v>120</v>
+      </c>
+      <c r="AX16" t="s">
+        <v>121</v>
+      </c>
+      <c r="BB16" t="s">
+        <v>122</v>
+      </c>
+      <c r="BF16" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="17" spans="1:58">
+      <c r="A17" t="s">
+        <v>76</v>
+      </c>
+      <c r="B17" t="s">
+        <v>109</v>
+      </c>
+      <c r="C17">
+        <v>250</v>
+      </c>
+      <c r="D17">
+        <v>0.34</v>
+      </c>
+      <c r="E17">
+        <v>0.18</v>
+      </c>
+      <c r="F17" t="s">
+        <v>110</v>
+      </c>
+      <c r="G17">
+        <v>259.86</v>
+      </c>
+      <c r="H17">
+        <v>0.32</v>
+      </c>
+      <c r="I17">
+        <v>0.16</v>
+      </c>
+      <c r="J17" t="s">
+        <v>111</v>
+      </c>
+      <c r="K17">
+        <v>153</v>
+      </c>
+      <c r="L17">
+        <v>0.55</v>
+      </c>
+      <c r="M17">
+        <v>0.37</v>
+      </c>
+      <c r="N17" t="s">
+        <v>112</v>
+      </c>
+      <c r="O17">
+        <v>143</v>
+      </c>
+      <c r="P17">
+        <v>0.58</v>
+      </c>
+      <c r="Q17">
+        <v>0.4</v>
+      </c>
+      <c r="R17" t="s">
+        <v>113</v>
+      </c>
+      <c r="S17">
+        <v>144.83</v>
+      </c>
+      <c r="T17">
+        <v>0.58</v>
+      </c>
+      <c r="U17">
+        <v>0.4</v>
+      </c>
+      <c r="V17" t="s">
+        <v>114</v>
+      </c>
+      <c r="W17">
+        <v>133.71</v>
+      </c>
+      <c r="X17">
+        <v>0.63</v>
+      </c>
+      <c r="Y17">
+        <v>0.44</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>115</v>
+      </c>
+      <c r="AA17">
+        <v>137.86</v>
+      </c>
+      <c r="AB17">
+        <v>0.61</v>
+      </c>
+      <c r="AC17">
+        <v>0.42</v>
+      </c>
+      <c r="AD17" t="s">
+        <v>116</v>
+      </c>
+      <c r="AE17">
+        <v>150.57</v>
+      </c>
+      <c r="AF17">
+        <v>0.57</v>
+      </c>
+      <c r="AG17">
+        <v>0.39</v>
+      </c>
+      <c r="AH17" t="s">
+        <v>117</v>
+      </c>
+      <c r="AI17">
+        <v>174.86</v>
+      </c>
+      <c r="AJ17">
+        <v>0.49</v>
+      </c>
+      <c r="AK17">
+        <v>0.29</v>
+      </c>
+      <c r="AL17" t="s">
+        <v>118</v>
+      </c>
+      <c r="AM17">
+        <v>179.29</v>
+      </c>
+      <c r="AN17">
+        <v>0.45</v>
+      </c>
+      <c r="AO17">
+        <v>0.19</v>
+      </c>
+      <c r="AP17" t="s">
+        <v>119</v>
+      </c>
+      <c r="AT17" t="s">
+        <v>120</v>
+      </c>
+      <c r="AX17" t="s">
+        <v>121</v>
+      </c>
+      <c r="BB17" t="s">
+        <v>122</v>
+      </c>
+      <c r="BF17" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="18" spans="1:58">
+      <c r="A18" t="s">
+        <v>77</v>
+      </c>
+      <c r="B18" t="s">
+        <v>109</v>
+      </c>
+      <c r="C18">
+        <v>467.14</v>
+      </c>
+      <c r="D18">
+        <v>0.18</v>
+      </c>
+      <c r="E18">
+        <v>0.06</v>
+      </c>
+      <c r="F18" t="s">
+        <v>110</v>
+      </c>
+      <c r="G18">
+        <v>505.29</v>
+      </c>
+      <c r="H18">
+        <v>0.17</v>
+      </c>
+      <c r="I18">
+        <v>0.05</v>
+      </c>
+      <c r="J18" t="s">
+        <v>111</v>
+      </c>
+      <c r="K18">
+        <v>494.14</v>
+      </c>
+      <c r="L18">
+        <v>0.17</v>
+      </c>
+      <c r="M18">
+        <v>0.05</v>
+      </c>
+      <c r="N18" t="s">
+        <v>112</v>
+      </c>
+      <c r="O18">
+        <v>502.43</v>
+      </c>
+      <c r="P18">
+        <v>0.17</v>
+      </c>
+      <c r="Q18">
+        <v>0.05</v>
+      </c>
+      <c r="R18" t="s">
+        <v>113</v>
+      </c>
+      <c r="S18">
+        <v>441.33</v>
+      </c>
+      <c r="T18">
+        <v>0.19</v>
+      </c>
+      <c r="U18">
+        <v>0.06</v>
+      </c>
+      <c r="V18" t="s">
+        <v>114</v>
+      </c>
+      <c r="W18">
+        <v>433.86</v>
+      </c>
+      <c r="X18">
+        <v>0.19</v>
+      </c>
+      <c r="Y18">
+        <v>0.06</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>115</v>
+      </c>
+      <c r="AA18">
+        <v>331</v>
+      </c>
+      <c r="AB18">
+        <v>0.25</v>
+      </c>
+      <c r="AC18">
+        <v>0.1</v>
+      </c>
+      <c r="AD18" t="s">
+        <v>116</v>
+      </c>
+      <c r="AE18">
+        <v>337.71</v>
+      </c>
+      <c r="AF18">
+        <v>0.25</v>
+      </c>
+      <c r="AG18">
+        <v>0.11</v>
+      </c>
+      <c r="AH18" t="s">
+        <v>117</v>
+      </c>
+      <c r="AI18">
+        <v>373.71</v>
+      </c>
+      <c r="AJ18">
+        <v>0.23</v>
+      </c>
+      <c r="AK18">
+        <v>0.08</v>
+      </c>
+      <c r="AL18" t="s">
+        <v>118</v>
+      </c>
+      <c r="AM18">
+        <v>429.43</v>
+      </c>
+      <c r="AN18">
+        <v>0.19</v>
+      </c>
+      <c r="AO18">
+        <v>0.04</v>
+      </c>
+      <c r="AP18" t="s">
+        <v>119</v>
+      </c>
+      <c r="AQ18">
+        <v>458.5</v>
+      </c>
+      <c r="AR18">
+        <v>0.19</v>
+      </c>
+      <c r="AS18">
+        <v>0.04</v>
+      </c>
+      <c r="AT18" t="s">
+        <v>120</v>
+      </c>
+      <c r="AX18" t="s">
+        <v>121</v>
+      </c>
+      <c r="BB18" t="s">
+        <v>122</v>
+      </c>
+      <c r="BF18" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="19" spans="1:58">
+      <c r="A19" t="s">
+        <v>78</v>
+      </c>
+      <c r="B19" t="s">
+        <v>109</v>
+      </c>
+      <c r="C19">
+        <v>1926.43</v>
+      </c>
+      <c r="D19">
+        <v>0.04</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19" t="s">
+        <v>110</v>
+      </c>
+      <c r="G19">
+        <v>1926.43</v>
+      </c>
+      <c r="H19">
+        <v>0.04</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19" t="s">
+        <v>111</v>
+      </c>
+      <c r="K19">
+        <v>2033.57</v>
+      </c>
+      <c r="L19">
+        <v>0.04</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19" t="s">
+        <v>112</v>
+      </c>
+      <c r="O19">
+        <v>2033.57</v>
+      </c>
+      <c r="P19">
+        <v>0.04</v>
+      </c>
+      <c r="Q19">
+        <v>0</v>
+      </c>
+      <c r="R19" t="s">
+        <v>113</v>
+      </c>
+      <c r="S19">
+        <v>2296.6</v>
+      </c>
+      <c r="T19">
+        <v>0.04</v>
+      </c>
+      <c r="U19">
+        <v>0</v>
+      </c>
+      <c r="V19" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>115</v>
+      </c>
+      <c r="AD19" t="s">
+        <v>116</v>
+      </c>
+      <c r="AH19" t="s">
+        <v>117</v>
+      </c>
+      <c r="AL19" t="s">
+        <v>118</v>
+      </c>
+      <c r="AP19" t="s">
+        <v>119</v>
+      </c>
+      <c r="AT19" t="s">
+        <v>120</v>
+      </c>
+      <c r="AX19" t="s">
+        <v>121</v>
+      </c>
+      <c r="BB19" t="s">
+        <v>122</v>
+      </c>
+      <c r="BF19" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="20" spans="1:58">
+      <c r="A20" t="s">
+        <v>79</v>
+      </c>
+      <c r="B20" t="s">
+        <v>109</v>
+      </c>
+      <c r="C20">
+        <v>1126.43</v>
+      </c>
+      <c r="D20">
+        <v>0.08</v>
+      </c>
+      <c r="E20">
+        <v>0.01</v>
+      </c>
+      <c r="F20" t="s">
+        <v>110</v>
+      </c>
+      <c r="G20">
+        <v>1126.43</v>
+      </c>
+      <c r="H20">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I20">
+        <v>0.01</v>
+      </c>
+      <c r="J20" t="s">
+        <v>111</v>
+      </c>
+      <c r="K20">
+        <v>1126.43</v>
+      </c>
+      <c r="L20">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="M20">
+        <v>0.01</v>
+      </c>
+      <c r="N20" t="s">
+        <v>112</v>
+      </c>
+      <c r="O20">
+        <v>1197.86</v>
+      </c>
+      <c r="P20">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="Q20">
+        <v>0.01</v>
+      </c>
+      <c r="R20" t="s">
+        <v>113</v>
+      </c>
+      <c r="S20">
+        <v>1296.6</v>
+      </c>
+      <c r="T20">
+        <v>0.06</v>
+      </c>
+      <c r="U20">
+        <v>0.01</v>
+      </c>
+      <c r="V20" t="s">
+        <v>114</v>
+      </c>
+      <c r="W20">
+        <v>1247.33</v>
+      </c>
+      <c r="X20">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="Y20">
+        <v>0.01</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>115</v>
+      </c>
+      <c r="AA20">
+        <v>1569.29</v>
+      </c>
+      <c r="AB20">
+        <v>0.05</v>
+      </c>
+      <c r="AC20">
+        <v>0.01</v>
+      </c>
+      <c r="AD20" t="s">
+        <v>116</v>
+      </c>
+      <c r="AE20">
+        <v>2140.71</v>
+      </c>
+      <c r="AF20">
+        <v>0.04</v>
+      </c>
+      <c r="AG20">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="s">
+        <v>117</v>
+      </c>
+      <c r="AI20">
+        <v>2001</v>
+      </c>
+      <c r="AJ20">
+        <v>0.04</v>
+      </c>
+      <c r="AK20">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="s">
+        <v>118</v>
+      </c>
+      <c r="AM20">
+        <v>2001</v>
+      </c>
+      <c r="AN20">
+        <v>0.04</v>
+      </c>
+      <c r="AO20">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="s">
+        <v>119</v>
+      </c>
+      <c r="AT20" t="s">
+        <v>120</v>
+      </c>
+      <c r="AX20" t="s">
+        <v>121</v>
+      </c>
+      <c r="BB20" t="s">
+        <v>122</v>
+      </c>
+      <c r="BF20" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="21" spans="1:58">
+      <c r="A21" t="s">
+        <v>80</v>
+      </c>
+      <c r="B21" t="s">
+        <v>109</v>
+      </c>
+      <c r="C21">
+        <v>540.71</v>
+      </c>
+      <c r="D21">
+        <v>0.16</v>
+      </c>
+      <c r="E21">
+        <v>0.05</v>
+      </c>
+      <c r="F21" t="s">
+        <v>110</v>
+      </c>
+      <c r="G21">
+        <v>576.4299999999999</v>
+      </c>
+      <c r="H21">
+        <v>0.15</v>
+      </c>
+      <c r="I21">
+        <v>0.04</v>
+      </c>
+      <c r="J21" t="s">
+        <v>111</v>
+      </c>
+      <c r="K21">
+        <v>576.4299999999999</v>
+      </c>
+      <c r="L21">
+        <v>0.15</v>
+      </c>
+      <c r="M21">
+        <v>0.04</v>
+      </c>
+      <c r="N21" t="s">
+        <v>112</v>
+      </c>
+      <c r="O21">
+        <v>612.14</v>
+      </c>
+      <c r="P21">
+        <v>0.14</v>
+      </c>
+      <c r="Q21">
+        <v>0.03</v>
+      </c>
+      <c r="R21" t="s">
+        <v>113</v>
+      </c>
+      <c r="S21">
+        <v>630.67</v>
+      </c>
+      <c r="T21">
+        <v>0.13</v>
+      </c>
+      <c r="U21">
+        <v>0.03</v>
+      </c>
+      <c r="V21" t="s">
+        <v>114</v>
+      </c>
+      <c r="W21">
+        <v>647.86</v>
+      </c>
+      <c r="X21">
+        <v>0.13</v>
+      </c>
+      <c r="Y21">
+        <v>0.03</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>115</v>
+      </c>
+      <c r="AA21">
+        <v>647.86</v>
+      </c>
+      <c r="AB21">
+        <v>0.13</v>
+      </c>
+      <c r="AC21">
+        <v>0.03</v>
+      </c>
+      <c r="AD21" t="s">
+        <v>116</v>
+      </c>
+      <c r="AE21">
+        <v>647.86</v>
+      </c>
+      <c r="AF21">
+        <v>0.13</v>
+      </c>
+      <c r="AG21">
+        <v>0.03</v>
+      </c>
+      <c r="AH21" t="s">
+        <v>117</v>
+      </c>
+      <c r="AI21">
+        <v>1219.29</v>
+      </c>
+      <c r="AJ21">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AK21">
+        <v>0.01</v>
+      </c>
+      <c r="AL21" t="s">
+        <v>118</v>
+      </c>
+      <c r="AP21" t="s">
+        <v>119</v>
+      </c>
+      <c r="AT21" t="s">
+        <v>120</v>
+      </c>
+      <c r="AX21" t="s">
+        <v>121</v>
+      </c>
+      <c r="BB21" t="s">
+        <v>122</v>
+      </c>
+      <c r="BF21" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="22" spans="1:58">
+      <c r="A22" t="s">
+        <v>81</v>
+      </c>
+      <c r="B22" t="s">
+        <v>109</v>
+      </c>
+      <c r="C22">
+        <v>53.43</v>
+      </c>
+      <c r="D22">
+        <v>1.59</v>
+      </c>
+      <c r="E22">
+        <v>1.47</v>
+      </c>
+      <c r="F22" t="s">
+        <v>110</v>
+      </c>
+      <c r="G22">
+        <v>53.43</v>
+      </c>
+      <c r="H22">
+        <v>1.57</v>
+      </c>
+      <c r="I22">
+        <v>1.44</v>
+      </c>
+      <c r="J22" t="s">
+        <v>111</v>
+      </c>
+      <c r="K22">
+        <v>51.29</v>
+      </c>
+      <c r="L22">
+        <v>1.64</v>
+      </c>
+      <c r="M22">
+        <v>1.52</v>
+      </c>
+      <c r="N22" t="s">
+        <v>112</v>
+      </c>
+      <c r="O22">
+        <v>51.29</v>
+      </c>
+      <c r="P22">
+        <v>1.63</v>
+      </c>
+      <c r="Q22">
+        <v>1.49</v>
+      </c>
+      <c r="R22" t="s">
+        <v>113</v>
+      </c>
+      <c r="S22">
+        <v>53</v>
+      </c>
+      <c r="T22">
+        <v>1.59</v>
+      </c>
+      <c r="U22">
+        <v>1.46</v>
+      </c>
+      <c r="V22" t="s">
+        <v>114</v>
+      </c>
+      <c r="W22">
+        <v>42.86</v>
+      </c>
+      <c r="X22">
+        <v>1.97</v>
+      </c>
+      <c r="Y22">
+        <v>1.86</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>115</v>
+      </c>
+      <c r="AA22">
+        <v>40</v>
+      </c>
+      <c r="AB22">
+        <v>2.11</v>
+      </c>
+      <c r="AC22">
+        <v>2</v>
+      </c>
+      <c r="AD22" t="s">
+        <v>116</v>
+      </c>
+      <c r="AE22">
         <v>49.86</v>
       </c>
-      <c r="D7">
-        <v>1.7</v>
-      </c>
-      <c r="E7">
+      <c r="AF22">
+        <v>1.72</v>
+      </c>
+      <c r="AG22">
         <v>1.59</v>
       </c>
-      <c r="F7" t="s">
-        <v>106</v>
-      </c>
-      <c r="G7">
-        <v>50.57</v>
-      </c>
-      <c r="H7">
-        <v>1.66</v>
-      </c>
-      <c r="I7">
-        <v>1.54</v>
-      </c>
-      <c r="J7" t="s">
-        <v>107</v>
-      </c>
-      <c r="K7">
-        <v>38.71</v>
-      </c>
-      <c r="L7">
-        <v>2.18</v>
-      </c>
-      <c r="M7">
-        <v>2.1</v>
-      </c>
-      <c r="N7" t="s">
-        <v>108</v>
-      </c>
-      <c r="O7">
-        <v>37.71</v>
-      </c>
-      <c r="P7">
-        <v>2.21</v>
-      </c>
-      <c r="Q7">
-        <v>2.13</v>
-      </c>
-      <c r="R7" t="s">
+      <c r="AH22" t="s">
+        <v>117</v>
+      </c>
+      <c r="AI22">
+        <v>58</v>
+      </c>
+      <c r="AJ22">
+        <v>1.48</v>
+      </c>
+      <c r="AK22">
+        <v>1.3</v>
+      </c>
+      <c r="AL22" t="s">
+        <v>118</v>
+      </c>
+      <c r="AP22" t="s">
+        <v>119</v>
+      </c>
+      <c r="AT22" t="s">
+        <v>120</v>
+      </c>
+      <c r="AX22" t="s">
+        <v>121</v>
+      </c>
+      <c r="BB22" t="s">
+        <v>122</v>
+      </c>
+      <c r="BF22" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="23" spans="1:58">
+      <c r="A23" t="s">
+        <v>82</v>
+      </c>
+      <c r="B23" t="s">
         <v>109</v>
       </c>
-      <c r="S7">
-        <v>40.67</v>
-      </c>
-      <c r="T7">
-        <v>2.07</v>
-      </c>
-      <c r="U7">
-        <v>1.98</v>
-      </c>
-      <c r="V7" t="s">
+      <c r="C23">
+        <v>1497.86</v>
+      </c>
+      <c r="D23">
+        <v>0.06</v>
+      </c>
+      <c r="E23">
+        <v>0.01</v>
+      </c>
+      <c r="F23" t="s">
         <v>110</v>
       </c>
-      <c r="W7">
-        <v>32.86</v>
-      </c>
-      <c r="X7">
-        <v>2.57</v>
-      </c>
-      <c r="Y7">
-        <v>2.51</v>
-      </c>
-      <c r="Z7" t="s">
+      <c r="G23">
+        <v>1497.86</v>
+      </c>
+      <c r="H23">
+        <v>0.06</v>
+      </c>
+      <c r="I23">
+        <v>0.01</v>
+      </c>
+      <c r="J23" t="s">
         <v>111</v>
       </c>
-      <c r="AA7">
-        <v>35.14</v>
-      </c>
-      <c r="AB7">
-        <v>2.4</v>
-      </c>
-      <c r="AC7">
-        <v>2.32</v>
-      </c>
-      <c r="AD7" t="s">
+      <c r="K23">
+        <v>1497.86</v>
+      </c>
+      <c r="L23">
+        <v>0.06</v>
+      </c>
+      <c r="M23">
+        <v>0.01</v>
+      </c>
+      <c r="N23" t="s">
         <v>112</v>
       </c>
-      <c r="AE7">
-        <v>43.14</v>
-      </c>
-      <c r="AF7">
-        <v>1.99</v>
-      </c>
-      <c r="AG7">
-        <v>1.88</v>
-      </c>
-      <c r="AH7" t="s">
+      <c r="O23">
+        <v>1497.86</v>
+      </c>
+      <c r="P23">
+        <v>0.06</v>
+      </c>
+      <c r="Q23">
+        <v>0.01</v>
+      </c>
+      <c r="R23" t="s">
         <v>113</v>
       </c>
-      <c r="AI7">
-        <v>51.29</v>
-      </c>
-      <c r="AJ7">
-        <v>1.67</v>
-      </c>
-      <c r="AK7">
-        <v>1.51</v>
-      </c>
-      <c r="AL7" t="s">
+      <c r="S23">
+        <v>1696.6</v>
+      </c>
+      <c r="T23">
+        <v>0.05</v>
+      </c>
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23" t="s">
         <v>114</v>
       </c>
-      <c r="AM7">
-        <v>21.57</v>
-      </c>
-      <c r="AN7">
-        <v>3.75</v>
-      </c>
-      <c r="AO7">
-        <v>3.65</v>
-      </c>
-      <c r="AP7" t="s">
+      <c r="W23">
+        <v>1664</v>
+      </c>
+      <c r="X23">
+        <v>0.05</v>
+      </c>
+      <c r="Y23">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="s">
         <v>115</v>
       </c>
-      <c r="AQ7">
-        <v>27.33</v>
-      </c>
-      <c r="AR7">
-        <v>3.21</v>
-      </c>
-      <c r="AS7">
-        <v>3.02</v>
-      </c>
-      <c r="AT7" t="s">
+      <c r="AD23" t="s">
         <v>116</v>
       </c>
-      <c r="AU7">
-        <v>31.83</v>
-      </c>
-      <c r="AV7">
-        <v>2.78</v>
-      </c>
-      <c r="AW7">
-        <v>2.51</v>
-      </c>
-      <c r="AX7" t="s">
+      <c r="AH23" t="s">
         <v>117</v>
       </c>
-      <c r="AY7">
-        <v>30.5</v>
-      </c>
-      <c r="AZ7">
-        <v>2.98</v>
-      </c>
-      <c r="BA7">
-        <v>2.71</v>
-      </c>
-      <c r="BB7" t="s">
+      <c r="AL23" t="s">
         <v>118</v>
       </c>
-      <c r="BC7">
-        <v>31.33</v>
-      </c>
-      <c r="BD7">
-        <v>2.97</v>
-      </c>
-      <c r="BE7">
-        <v>2.58</v>
+      <c r="AP23" t="s">
+        <v>119</v>
+      </c>
+      <c r="AT23" t="s">
+        <v>120</v>
+      </c>
+      <c r="AX23" t="s">
+        <v>121</v>
+      </c>
+      <c r="BB23" t="s">
+        <v>122</v>
+      </c>
+      <c r="BF23" t="s">
+        <v>123</v>
       </c>
     </row>
-    <row r="8" spans="1:57">
-      <c r="A8" t="s">
-        <v>63</v>
-      </c>
-      <c r="B8" t="s">
-        <v>105</v>
-      </c>
-      <c r="C8">
-        <v>37.71</v>
-      </c>
-      <c r="D8">
-        <v>2.25</v>
-      </c>
-      <c r="E8">
-        <v>2.19</v>
-      </c>
-      <c r="F8" t="s">
-        <v>106</v>
-      </c>
-      <c r="G8">
-        <v>37.71</v>
-      </c>
-      <c r="H8">
-        <v>2.23</v>
-      </c>
-      <c r="I8">
-        <v>2.15</v>
-      </c>
-      <c r="J8" t="s">
-        <v>107</v>
-      </c>
-      <c r="K8">
-        <v>39.43</v>
-      </c>
-      <c r="L8">
-        <v>2.14</v>
-      </c>
-      <c r="M8">
-        <v>2.06</v>
-      </c>
-      <c r="N8" t="s">
-        <v>108</v>
-      </c>
-      <c r="O8">
-        <v>42</v>
-      </c>
-      <c r="P8">
-        <v>1.99</v>
-      </c>
-      <c r="Q8">
-        <v>1.88</v>
-      </c>
-      <c r="R8" t="s">
+    <row r="24" spans="1:58">
+      <c r="A24" t="s">
+        <v>83</v>
+      </c>
+      <c r="B24" t="s">
         <v>109</v>
       </c>
-      <c r="S8">
-        <v>42.17</v>
-      </c>
-      <c r="T8">
-        <v>2</v>
-      </c>
-      <c r="U8">
-        <v>1.9</v>
-      </c>
-      <c r="V8" t="s">
+      <c r="C24">
+        <v>191.71</v>
+      </c>
+      <c r="D24">
+        <v>0.44</v>
+      </c>
+      <c r="E24">
+        <v>0.28</v>
+      </c>
+      <c r="F24" t="s">
         <v>110</v>
       </c>
-      <c r="W8">
-        <v>47.71</v>
-      </c>
-      <c r="X8">
-        <v>1.77</v>
-      </c>
-      <c r="Y8">
-        <v>1.64</v>
-      </c>
-      <c r="Z8" t="s">
+      <c r="G24">
+        <v>222.71</v>
+      </c>
+      <c r="H24">
+        <v>0.38</v>
+      </c>
+      <c r="I24">
+        <v>0.21</v>
+      </c>
+      <c r="J24" t="s">
         <v>111</v>
       </c>
-      <c r="AA8">
-        <v>52.71</v>
-      </c>
-      <c r="AB8">
-        <v>1.6</v>
-      </c>
-      <c r="AC8">
-        <v>1.45</v>
-      </c>
-      <c r="AD8" t="s">
+      <c r="K24">
+        <v>193.29</v>
+      </c>
+      <c r="L24">
+        <v>0.44</v>
+      </c>
+      <c r="M24">
+        <v>0.26</v>
+      </c>
+      <c r="N24" t="s">
         <v>112</v>
       </c>
-      <c r="AE8">
-        <v>54.14</v>
-      </c>
-      <c r="AF8">
-        <v>1.59</v>
-      </c>
-      <c r="AG8">
-        <v>1.45</v>
-      </c>
-      <c r="AH8" t="s">
+      <c r="O24">
+        <v>197.43</v>
+      </c>
+      <c r="P24">
+        <v>0.42</v>
+      </c>
+      <c r="Q24">
+        <v>0.24</v>
+      </c>
+      <c r="R24" t="s">
         <v>113</v>
       </c>
-      <c r="AI8">
-        <v>49.14</v>
-      </c>
-      <c r="AJ8">
-        <v>1.75</v>
-      </c>
-      <c r="AK8">
-        <v>1.59</v>
-      </c>
-      <c r="AL8" t="s">
+      <c r="S24">
+        <v>148.17</v>
+      </c>
+      <c r="T24">
+        <v>0.57</v>
+      </c>
+      <c r="U24">
+        <v>0.39</v>
+      </c>
+      <c r="V24" t="s">
         <v>114</v>
       </c>
-      <c r="AM8">
-        <v>52</v>
-      </c>
-      <c r="AN8">
-        <v>1.55</v>
-      </c>
-      <c r="AO8">
-        <v>1.25</v>
-      </c>
-      <c r="AP8" t="s">
+      <c r="W24">
+        <v>140</v>
+      </c>
+      <c r="X24">
+        <v>0.6</v>
+      </c>
+      <c r="Y24">
+        <v>0.41</v>
+      </c>
+      <c r="Z24" t="s">
         <v>115</v>
       </c>
-      <c r="AQ8">
-        <v>41.83</v>
-      </c>
-      <c r="AR8">
-        <v>2.09</v>
-      </c>
-      <c r="AS8">
-        <v>1.84</v>
-      </c>
-      <c r="AT8" t="s">
+      <c r="AA24">
+        <v>138.57</v>
+      </c>
+      <c r="AB24">
+        <v>0.61</v>
+      </c>
+      <c r="AC24">
+        <v>0.41</v>
+      </c>
+      <c r="AD24" t="s">
         <v>116</v>
       </c>
-      <c r="AU8">
-        <v>48.5</v>
-      </c>
-      <c r="AV8">
-        <v>1.83</v>
-      </c>
-      <c r="AW8">
-        <v>1.51</v>
-      </c>
-      <c r="AX8" t="s">
+      <c r="AE24">
+        <v>180.57</v>
+      </c>
+      <c r="AF24">
+        <v>0.48</v>
+      </c>
+      <c r="AG24">
+        <v>0.3</v>
+      </c>
+      <c r="AH24" t="s">
         <v>117</v>
       </c>
-      <c r="AY8">
-        <v>49.33</v>
-      </c>
-      <c r="AZ8">
-        <v>1.84</v>
-      </c>
-      <c r="BA8">
-        <v>1.54</v>
-      </c>
-      <c r="BB8" t="s">
+      <c r="AI24">
+        <v>189.07</v>
+      </c>
+      <c r="AJ24">
+        <v>0.45</v>
+      </c>
+      <c r="AK24">
+        <v>0.26</v>
+      </c>
+      <c r="AL24" t="s">
         <v>118</v>
       </c>
-      <c r="BC8">
-        <v>32</v>
-      </c>
-      <c r="BD8">
-        <v>2.9</v>
-      </c>
-      <c r="BE8">
-        <v>2.51</v>
+      <c r="AM24">
+        <v>165.36</v>
+      </c>
+      <c r="AN24">
+        <v>0.49</v>
+      </c>
+      <c r="AO24">
+        <v>0.22</v>
+      </c>
+      <c r="AP24" t="s">
+        <v>119</v>
+      </c>
+      <c r="AQ24">
+        <v>238.33</v>
+      </c>
+      <c r="AR24">
+        <v>0.37</v>
+      </c>
+      <c r="AS24">
+        <v>0.15</v>
+      </c>
+      <c r="AT24" t="s">
+        <v>120</v>
+      </c>
+      <c r="AU24">
+        <v>249.83</v>
+      </c>
+      <c r="AV24">
+        <v>0.35</v>
+      </c>
+      <c r="AW24">
+        <v>0.13</v>
+      </c>
+      <c r="AX24" t="s">
+        <v>121</v>
+      </c>
+      <c r="BB24" t="s">
+        <v>122</v>
+      </c>
+      <c r="BF24" t="s">
+        <v>123</v>
       </c>
     </row>
-    <row r="9" spans="1:57">
-      <c r="A9" t="s">
-        <v>64</v>
-      </c>
-      <c r="B9" t="s">
-        <v>105</v>
-      </c>
-      <c r="C9">
-        <v>74.43000000000001</v>
-      </c>
-      <c r="D9">
-        <v>1.14</v>
-      </c>
-      <c r="E9">
-        <v>0.99</v>
-      </c>
-      <c r="F9" t="s">
-        <v>106</v>
-      </c>
-      <c r="G9">
-        <v>75.14</v>
-      </c>
-      <c r="H9">
-        <v>1.12</v>
-      </c>
-      <c r="I9">
-        <v>0.95</v>
-      </c>
-      <c r="J9" t="s">
-        <v>107</v>
-      </c>
-      <c r="K9">
-        <v>83.56999999999999</v>
-      </c>
-      <c r="L9">
-        <v>1.01</v>
-      </c>
-      <c r="M9">
-        <v>0.84</v>
-      </c>
-      <c r="N9" t="s">
-        <v>108</v>
-      </c>
-      <c r="O9">
-        <v>87.70999999999999</v>
-      </c>
-      <c r="P9">
-        <v>0.95</v>
-      </c>
-      <c r="Q9">
-        <v>0.77</v>
-      </c>
-      <c r="R9" t="s">
+    <row r="25" spans="1:58">
+      <c r="A25" t="s">
+        <v>84</v>
+      </c>
+      <c r="B25" t="s">
         <v>109</v>
       </c>
-      <c r="S9">
-        <v>78</v>
-      </c>
-      <c r="T9">
-        <v>1.08</v>
-      </c>
-      <c r="U9">
-        <v>0.92</v>
-      </c>
-      <c r="V9" t="s">
+      <c r="C25">
+        <v>1326.43</v>
+      </c>
+      <c r="D25">
+        <v>0.06</v>
+      </c>
+      <c r="E25">
+        <v>0.01</v>
+      </c>
+      <c r="F25" t="s">
         <v>110</v>
       </c>
-      <c r="W9">
-        <v>81.43000000000001</v>
-      </c>
-      <c r="X9">
-        <v>1.04</v>
-      </c>
-      <c r="Y9">
-        <v>0.86</v>
-      </c>
-      <c r="Z9" t="s">
+      <c r="G25">
+        <v>1326.43</v>
+      </c>
+      <c r="H25">
+        <v>0.06</v>
+      </c>
+      <c r="I25">
+        <v>0.01</v>
+      </c>
+      <c r="J25" t="s">
         <v>111</v>
       </c>
-      <c r="AA9">
-        <v>80.14</v>
-      </c>
-      <c r="AB9">
-        <v>1.05</v>
-      </c>
-      <c r="AC9">
-        <v>0.87</v>
-      </c>
-      <c r="AD9" t="s">
+      <c r="K25">
+        <v>1326.43</v>
+      </c>
+      <c r="L25">
+        <v>0.06</v>
+      </c>
+      <c r="M25">
+        <v>0.01</v>
+      </c>
+      <c r="N25" t="s">
         <v>112</v>
       </c>
-      <c r="AE9">
-        <v>76.43000000000001</v>
-      </c>
-      <c r="AF9">
-        <v>1.12</v>
-      </c>
-      <c r="AG9">
-        <v>0.96</v>
-      </c>
-      <c r="AH9" t="s">
+      <c r="O25">
+        <v>1069.29</v>
+      </c>
+      <c r="P25">
+        <v>0.08</v>
+      </c>
+      <c r="Q25">
+        <v>0.01</v>
+      </c>
+      <c r="R25" t="s">
         <v>113</v>
       </c>
-      <c r="AI9">
-        <v>73.70999999999999</v>
-      </c>
-      <c r="AJ9">
-        <v>1.16</v>
-      </c>
-      <c r="AK9">
-        <v>0.97</v>
-      </c>
-      <c r="AL9" t="s">
+      <c r="S25">
+        <v>996.6</v>
+      </c>
+      <c r="T25">
+        <v>0.08</v>
+      </c>
+      <c r="U25">
+        <v>0.01</v>
+      </c>
+      <c r="V25" t="s">
         <v>114</v>
       </c>
-      <c r="AM9">
-        <v>78.70999999999999</v>
-      </c>
-      <c r="AN9">
-        <v>1.03</v>
-      </c>
-      <c r="AO9">
-        <v>0.7</v>
-      </c>
-      <c r="AP9" t="s">
+      <c r="W25">
+        <v>705.67</v>
+      </c>
+      <c r="X25">
+        <v>0.12</v>
+      </c>
+      <c r="Y25">
+        <v>0.03</v>
+      </c>
+      <c r="Z25" t="s">
         <v>115</v>
       </c>
-      <c r="AQ9">
-        <v>86.33</v>
-      </c>
-      <c r="AR9">
-        <v>1.01</v>
-      </c>
-      <c r="AS9">
-        <v>0.73</v>
-      </c>
-      <c r="AT9" t="s">
+      <c r="AA25">
+        <v>747.86</v>
+      </c>
+      <c r="AB25">
+        <v>0.11</v>
+      </c>
+      <c r="AC25">
+        <v>0.02</v>
+      </c>
+      <c r="AD25" t="s">
         <v>116</v>
       </c>
-      <c r="AU9">
-        <v>66</v>
-      </c>
-      <c r="AV9">
-        <v>1.34</v>
-      </c>
-      <c r="AW9">
-        <v>1.01</v>
-      </c>
-      <c r="AX9" t="s">
+      <c r="AE25">
+        <v>783.5700000000001</v>
+      </c>
+      <c r="AF25">
+        <v>0.11</v>
+      </c>
+      <c r="AG25">
+        <v>0.02</v>
+      </c>
+      <c r="AH25" t="s">
         <v>117</v>
       </c>
-      <c r="AY9">
-        <v>71.33</v>
-      </c>
-      <c r="AZ9">
-        <v>1.27</v>
-      </c>
-      <c r="BA9">
-        <v>0.96</v>
-      </c>
-      <c r="BB9" t="s">
+      <c r="AI25">
+        <v>526.4299999999999</v>
+      </c>
+      <c r="AJ25">
+        <v>0.16</v>
+      </c>
+      <c r="AK25">
+        <v>0.04</v>
+      </c>
+      <c r="AL25" t="s">
         <v>118</v>
       </c>
-      <c r="BC9">
-        <v>38.5</v>
-      </c>
-      <c r="BD9">
-        <v>2.41</v>
-      </c>
-      <c r="BE9">
-        <v>2.01</v>
+      <c r="AM25">
+        <v>583.5700000000001</v>
+      </c>
+      <c r="AN25">
+        <v>0.14</v>
+      </c>
+      <c r="AO25">
+        <v>0.02</v>
+      </c>
+      <c r="AP25" t="s">
+        <v>119</v>
+      </c>
+      <c r="AQ25">
+        <v>664</v>
+      </c>
+      <c r="AR25">
+        <v>0.13</v>
+      </c>
+      <c r="AS25">
+        <v>0.02</v>
+      </c>
+      <c r="AT25" t="s">
+        <v>120</v>
+      </c>
+      <c r="AX25" t="s">
+        <v>121</v>
+      </c>
+      <c r="BB25" t="s">
+        <v>122</v>
+      </c>
+      <c r="BF25" t="s">
+        <v>123</v>
       </c>
     </row>
-    <row r="10" spans="1:57">
-      <c r="A10" t="s">
-        <v>65</v>
-      </c>
-      <c r="B10" t="s">
-        <v>105</v>
-      </c>
-      <c r="C10">
-        <v>367.57</v>
-      </c>
-      <c r="D10">
-        <v>0.23</v>
-      </c>
-      <c r="E10">
-        <v>0.1</v>
-      </c>
-      <c r="F10" t="s">
-        <v>106</v>
-      </c>
-      <c r="G10">
-        <v>383</v>
-      </c>
-      <c r="H10">
-        <v>0.22</v>
-      </c>
-      <c r="I10">
+    <row r="26" spans="1:58">
+      <c r="A26" t="s">
+        <v>85</v>
+      </c>
+      <c r="B26" t="s">
+        <v>109</v>
+      </c>
+      <c r="C26">
+        <v>1069.29</v>
+      </c>
+      <c r="D26">
         <v>0.08</v>
-      </c>
-      <c r="J10" t="s">
-        <v>107</v>
-      </c>
-      <c r="K10">
-        <v>378.86</v>
-      </c>
-      <c r="L10">
-        <v>0.22</v>
-      </c>
-      <c r="M10">
-        <v>0.09</v>
-      </c>
-      <c r="N10" t="s">
-        <v>108</v>
-      </c>
-      <c r="O10">
-        <v>474.57</v>
-      </c>
-      <c r="P10">
-        <v>0.18</v>
-      </c>
-      <c r="Q10">
-        <v>0.05</v>
-      </c>
-      <c r="R10" t="s">
-        <v>109</v>
-      </c>
-      <c r="S10">
-        <v>530.67</v>
-      </c>
-      <c r="T10">
-        <v>0.16</v>
-      </c>
-      <c r="U10">
-        <v>0.05</v>
-      </c>
-      <c r="V10" t="s">
-        <v>110</v>
-      </c>
-      <c r="W10">
-        <v>518</v>
-      </c>
-      <c r="X10">
-        <v>0.16</v>
-      </c>
-      <c r="Y10">
-        <v>0.05</v>
-      </c>
-      <c r="Z10" t="s">
-        <v>111</v>
-      </c>
-      <c r="AA10">
-        <v>529.5700000000001</v>
-      </c>
-      <c r="AB10">
-        <v>0.16</v>
-      </c>
-      <c r="AC10">
-        <v>0.04</v>
-      </c>
-      <c r="AD10" t="s">
-        <v>112</v>
-      </c>
-      <c r="AE10">
-        <v>576.4299999999999</v>
-      </c>
-      <c r="AF10">
-        <v>0.15</v>
-      </c>
-      <c r="AG10">
-        <v>0.04</v>
-      </c>
-      <c r="AH10" t="s">
-        <v>113</v>
-      </c>
-      <c r="AI10">
-        <v>458.71</v>
-      </c>
-      <c r="AJ10">
-        <v>0.19</v>
-      </c>
-      <c r="AK10">
-        <v>0.06</v>
-      </c>
-      <c r="AL10" t="s">
-        <v>114</v>
-      </c>
-      <c r="AM10">
-        <v>391.29</v>
-      </c>
-      <c r="AN10">
-        <v>0.21</v>
-      </c>
-      <c r="AO10">
-        <v>0.04</v>
-      </c>
-      <c r="AP10" t="s">
-        <v>115</v>
-      </c>
-      <c r="AQ10">
-        <v>437.83</v>
-      </c>
-      <c r="AR10">
-        <v>0.2</v>
-      </c>
-      <c r="AS10">
-        <v>0.05</v>
-      </c>
-      <c r="AT10" t="s">
-        <v>116</v>
-      </c>
-      <c r="AX10" t="s">
-        <v>117</v>
-      </c>
-      <c r="BB10" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="11" spans="1:57">
-      <c r="A11" t="s">
-        <v>66</v>
-      </c>
-      <c r="B11" t="s">
-        <v>105</v>
-      </c>
-      <c r="C11">
-        <v>442.71</v>
-      </c>
-      <c r="D11">
-        <v>0.19</v>
-      </c>
-      <c r="E11">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="F11" t="s">
-        <v>106</v>
-      </c>
-      <c r="G11">
-        <v>462.29</v>
-      </c>
-      <c r="H11">
-        <v>0.18</v>
-      </c>
-      <c r="I11">
-        <v>0.06</v>
-      </c>
-      <c r="J11" t="s">
-        <v>107</v>
-      </c>
-      <c r="K11">
-        <v>186</v>
-      </c>
-      <c r="L11">
-        <v>0.45</v>
-      </c>
-      <c r="M11">
-        <v>0.28</v>
-      </c>
-      <c r="N11" t="s">
-        <v>108</v>
-      </c>
-      <c r="O11">
-        <v>123.14</v>
-      </c>
-      <c r="P11">
-        <v>0.68</v>
-      </c>
-      <c r="Q11">
-        <v>0.49</v>
-      </c>
-      <c r="R11" t="s">
-        <v>109</v>
-      </c>
-      <c r="S11">
-        <v>128.5</v>
-      </c>
-      <c r="T11">
-        <v>0.66</v>
-      </c>
-      <c r="U11">
-        <v>0.47</v>
-      </c>
-      <c r="V11" t="s">
-        <v>110</v>
-      </c>
-      <c r="W11">
-        <v>174.43</v>
-      </c>
-      <c r="X11">
-        <v>0.48</v>
-      </c>
-      <c r="Y11">
-        <v>0.3</v>
-      </c>
-      <c r="Z11" t="s">
-        <v>111</v>
-      </c>
-      <c r="AA11">
-        <v>206.33</v>
-      </c>
-      <c r="AB11">
-        <v>0.41</v>
-      </c>
-      <c r="AC11">
-        <v>0.23</v>
-      </c>
-      <c r="AD11" t="s">
-        <v>112</v>
-      </c>
-      <c r="AE11">
-        <v>199.83</v>
-      </c>
-      <c r="AF11">
-        <v>0.43</v>
-      </c>
-      <c r="AG11">
-        <v>0.26</v>
-      </c>
-      <c r="AH11" t="s">
-        <v>113</v>
-      </c>
-      <c r="AI11">
-        <v>249.14</v>
-      </c>
-      <c r="AJ11">
-        <v>0.34</v>
-      </c>
-      <c r="AK11">
-        <v>0.17</v>
-      </c>
-      <c r="AL11" t="s">
-        <v>114</v>
-      </c>
-      <c r="AM11">
-        <v>290.57</v>
-      </c>
-      <c r="AN11">
-        <v>0.28</v>
-      </c>
-      <c r="AO11">
-        <v>0.08</v>
-      </c>
-      <c r="AP11" t="s">
-        <v>115</v>
-      </c>
-      <c r="AQ11">
-        <v>333.67</v>
-      </c>
-      <c r="AR11">
-        <v>0.26</v>
-      </c>
-      <c r="AS11">
-        <v>0.08</v>
-      </c>
-      <c r="AT11" t="s">
-        <v>116</v>
-      </c>
-      <c r="AX11" t="s">
-        <v>117</v>
-      </c>
-      <c r="BB11" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="12" spans="1:57">
-      <c r="A12" t="s">
-        <v>67</v>
-      </c>
-      <c r="B12" t="s">
-        <v>105</v>
-      </c>
-      <c r="C12">
-        <v>370.43</v>
-      </c>
-      <c r="D12">
-        <v>0.23</v>
-      </c>
-      <c r="E12">
-        <v>0.1</v>
-      </c>
-      <c r="F12" t="s">
-        <v>106</v>
-      </c>
-      <c r="G12">
-        <v>376.71</v>
-      </c>
-      <c r="H12">
-        <v>0.22</v>
-      </c>
-      <c r="I12">
-        <v>0.08</v>
-      </c>
-      <c r="J12" t="s">
-        <v>107</v>
-      </c>
-      <c r="K12">
-        <v>383.71</v>
-      </c>
-      <c r="L12">
-        <v>0.22</v>
-      </c>
-      <c r="M12">
-        <v>0.08</v>
-      </c>
-      <c r="N12" t="s">
-        <v>108</v>
-      </c>
-      <c r="O12">
-        <v>390.71</v>
-      </c>
-      <c r="P12">
-        <v>0.21</v>
-      </c>
-      <c r="Q12">
-        <v>0.08</v>
-      </c>
-      <c r="R12" t="s">
-        <v>109</v>
-      </c>
-      <c r="S12">
-        <v>473</v>
-      </c>
-      <c r="T12">
-        <v>0.18</v>
-      </c>
-      <c r="U12">
-        <v>0.06</v>
-      </c>
-      <c r="V12" t="s">
-        <v>110</v>
-      </c>
-      <c r="W12">
-        <v>514</v>
-      </c>
-      <c r="X12">
-        <v>0.16</v>
-      </c>
-      <c r="Y12">
-        <v>0.05</v>
-      </c>
-      <c r="Z12" t="s">
-        <v>111</v>
-      </c>
-      <c r="AA12">
-        <v>547.86</v>
-      </c>
-      <c r="AB12">
-        <v>0.15</v>
-      </c>
-      <c r="AC12">
-        <v>0.04</v>
-      </c>
-      <c r="AD12" t="s">
-        <v>112</v>
-      </c>
-      <c r="AE12">
-        <v>509.43</v>
-      </c>
-      <c r="AF12">
-        <v>0.17</v>
-      </c>
-      <c r="AG12">
-        <v>0.05</v>
-      </c>
-      <c r="AH12" t="s">
-        <v>113</v>
-      </c>
-      <c r="AI12">
-        <v>503.71</v>
-      </c>
-      <c r="AJ12">
-        <v>0.17</v>
-      </c>
-      <c r="AK12">
-        <v>0.05</v>
-      </c>
-      <c r="AL12" t="s">
-        <v>114</v>
-      </c>
-      <c r="AM12">
-        <v>576.4299999999999</v>
-      </c>
-      <c r="AN12">
-        <v>0.14</v>
-      </c>
-      <c r="AO12">
-        <v>0.02</v>
-      </c>
-      <c r="AP12" t="s">
-        <v>115</v>
-      </c>
-      <c r="AT12" t="s">
-        <v>116</v>
-      </c>
-      <c r="AX12" t="s">
-        <v>117</v>
-      </c>
-      <c r="BB12" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="13" spans="1:57">
-      <c r="A13" t="s">
-        <v>68</v>
-      </c>
-      <c r="B13" t="s">
-        <v>105</v>
-      </c>
-      <c r="C13">
-        <v>9.970000000000001</v>
-      </c>
-      <c r="D13">
-        <v>8.52</v>
-      </c>
-      <c r="E13">
-        <v>8.99</v>
-      </c>
-      <c r="F13" t="s">
-        <v>106</v>
-      </c>
-      <c r="G13">
-        <v>10.11</v>
-      </c>
-      <c r="H13">
-        <v>8.32</v>
-      </c>
-      <c r="I13">
-        <v>8.789999999999999</v>
-      </c>
-      <c r="J13" t="s">
-        <v>107</v>
-      </c>
-      <c r="K13">
-        <v>11.04</v>
-      </c>
-      <c r="L13">
-        <v>7.64</v>
-      </c>
-      <c r="M13">
-        <v>8.050000000000001</v>
-      </c>
-      <c r="N13" t="s">
-        <v>108</v>
-      </c>
-      <c r="O13">
-        <v>11.39</v>
-      </c>
-      <c r="P13">
-        <v>7.33</v>
-      </c>
-      <c r="Q13">
-        <v>7.74</v>
-      </c>
-      <c r="R13" t="s">
-        <v>109</v>
-      </c>
-      <c r="S13">
-        <v>12.2</v>
-      </c>
-      <c r="T13">
-        <v>6.91</v>
-      </c>
-      <c r="U13">
-        <v>7.25</v>
-      </c>
-      <c r="V13" t="s">
-        <v>110</v>
-      </c>
-      <c r="W13">
-        <v>13.17</v>
-      </c>
-      <c r="X13">
-        <v>6.41</v>
-      </c>
-      <c r="Y13">
-        <v>6.69</v>
-      </c>
-      <c r="Z13" t="s">
-        <v>111</v>
-      </c>
-      <c r="AA13">
-        <v>14.94</v>
-      </c>
-      <c r="AB13">
-        <v>5.65</v>
-      </c>
-      <c r="AC13">
-        <v>5.85</v>
-      </c>
-      <c r="AD13" t="s">
-        <v>112</v>
-      </c>
-      <c r="AE13">
-        <v>13.31</v>
-      </c>
-      <c r="AF13">
-        <v>6.46</v>
-      </c>
-      <c r="AG13">
-        <v>6.7</v>
-      </c>
-      <c r="AH13" t="s">
-        <v>113</v>
-      </c>
-      <c r="AI13">
-        <v>13.81</v>
-      </c>
-      <c r="AJ13">
-        <v>6.21</v>
-      </c>
-      <c r="AK13">
-        <v>6.4</v>
-      </c>
-      <c r="AL13" t="s">
-        <v>114</v>
-      </c>
-      <c r="AM13">
-        <v>11.47</v>
-      </c>
-      <c r="AN13">
-        <v>7.05</v>
-      </c>
-      <c r="AO13">
-        <v>7.32</v>
-      </c>
-      <c r="AP13" t="s">
-        <v>115</v>
-      </c>
-      <c r="AQ13">
-        <v>12.28</v>
-      </c>
-      <c r="AR13">
-        <v>7.13</v>
-      </c>
-      <c r="AS13">
-        <v>7.22</v>
-      </c>
-      <c r="AT13" t="s">
-        <v>116</v>
-      </c>
-      <c r="AU13">
-        <v>12.7</v>
-      </c>
-      <c r="AV13">
-        <v>6.97</v>
-      </c>
-      <c r="AW13">
-        <v>6.96</v>
-      </c>
-      <c r="AX13" t="s">
-        <v>117</v>
-      </c>
-      <c r="BB13" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="14" spans="1:57">
-      <c r="A14" t="s">
-        <v>69</v>
-      </c>
-      <c r="B14" t="s">
-        <v>105</v>
-      </c>
-      <c r="C14">
-        <v>1926.43</v>
-      </c>
-      <c r="D14">
-        <v>0.04</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="F14" t="s">
-        <v>106</v>
-      </c>
-      <c r="G14">
-        <v>1926.43</v>
-      </c>
-      <c r="H14">
-        <v>0.04</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14" t="s">
-        <v>107</v>
-      </c>
-      <c r="K14">
-        <v>2355</v>
-      </c>
-      <c r="L14">
-        <v>0.04</v>
-      </c>
-      <c r="M14">
-        <v>0</v>
-      </c>
-      <c r="N14" t="s">
-        <v>108</v>
-      </c>
-      <c r="O14">
-        <v>2355</v>
-      </c>
-      <c r="P14">
-        <v>0.04</v>
-      </c>
-      <c r="Q14">
-        <v>0</v>
-      </c>
-      <c r="R14" t="s">
-        <v>109</v>
-      </c>
-      <c r="S14">
-        <v>2596.6</v>
-      </c>
-      <c r="T14">
-        <v>0.03</v>
-      </c>
-      <c r="U14">
-        <v>0</v>
-      </c>
-      <c r="V14" t="s">
-        <v>110</v>
-      </c>
-      <c r="W14">
-        <v>1997.33</v>
-      </c>
-      <c r="X14">
-        <v>0.04</v>
-      </c>
-      <c r="Y14">
-        <v>0</v>
-      </c>
-      <c r="Z14" t="s">
-        <v>111</v>
-      </c>
-      <c r="AA14">
-        <v>1855</v>
-      </c>
-      <c r="AB14">
-        <v>0.05</v>
-      </c>
-      <c r="AC14">
-        <v>0</v>
-      </c>
-      <c r="AD14" t="s">
-        <v>112</v>
-      </c>
-      <c r="AE14">
-        <v>2001</v>
-      </c>
-      <c r="AF14">
-        <v>0.04</v>
-      </c>
-      <c r="AG14">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="s">
-        <v>113</v>
-      </c>
-      <c r="AL14" t="s">
-        <v>114</v>
-      </c>
-      <c r="AP14" t="s">
-        <v>115</v>
-      </c>
-      <c r="AT14" t="s">
-        <v>116</v>
-      </c>
-      <c r="AX14" t="s">
-        <v>117</v>
-      </c>
-      <c r="BB14" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="15" spans="1:57">
-      <c r="A15" t="s">
-        <v>70</v>
-      </c>
-      <c r="B15" t="s">
-        <v>105</v>
-      </c>
-      <c r="C15">
-        <v>747.86</v>
-      </c>
-      <c r="D15">
-        <v>0.11</v>
-      </c>
-      <c r="E15">
-        <v>0.03</v>
-      </c>
-      <c r="F15" t="s">
-        <v>106</v>
-      </c>
-      <c r="G15">
-        <v>747.86</v>
-      </c>
-      <c r="H15">
-        <v>0.11</v>
-      </c>
-      <c r="I15">
-        <v>0.02</v>
-      </c>
-      <c r="J15" t="s">
-        <v>107</v>
-      </c>
-      <c r="K15">
-        <v>747.86</v>
-      </c>
-      <c r="L15">
-        <v>0.11</v>
-      </c>
-      <c r="M15">
-        <v>0.02</v>
-      </c>
-      <c r="N15" t="s">
-        <v>108</v>
-      </c>
-      <c r="O15">
-        <v>747.86</v>
-      </c>
-      <c r="P15">
-        <v>0.11</v>
-      </c>
-      <c r="Q15">
-        <v>0.02</v>
-      </c>
-      <c r="R15" t="s">
-        <v>109</v>
-      </c>
-      <c r="S15">
-        <v>607.5</v>
-      </c>
-      <c r="T15">
-        <v>0.14</v>
-      </c>
-      <c r="U15">
-        <v>0.04</v>
-      </c>
-      <c r="V15" t="s">
-        <v>110</v>
-      </c>
-      <c r="W15">
-        <v>569.29</v>
-      </c>
-      <c r="X15">
-        <v>0.15</v>
-      </c>
-      <c r="Y15">
-        <v>0.04</v>
-      </c>
-      <c r="Z15" t="s">
-        <v>111</v>
-      </c>
-      <c r="AA15">
-        <v>647.86</v>
-      </c>
-      <c r="AB15">
-        <v>0.13</v>
-      </c>
-      <c r="AC15">
-        <v>0.03</v>
-      </c>
-      <c r="AD15" t="s">
-        <v>112</v>
-      </c>
-      <c r="AE15">
-        <v>647.86</v>
-      </c>
-      <c r="AF15">
-        <v>0.13</v>
-      </c>
-      <c r="AG15">
-        <v>0.03</v>
-      </c>
-      <c r="AH15" t="s">
-        <v>113</v>
-      </c>
-      <c r="AI15">
-        <v>612.14</v>
-      </c>
-      <c r="AJ15">
-        <v>0.14</v>
-      </c>
-      <c r="AK15">
-        <v>0.03</v>
-      </c>
-      <c r="AL15" t="s">
-        <v>114</v>
-      </c>
-      <c r="AM15">
-        <v>551</v>
-      </c>
-      <c r="AN15">
-        <v>0.15</v>
-      </c>
-      <c r="AO15">
-        <v>0.02</v>
-      </c>
-      <c r="AP15" t="s">
-        <v>115</v>
-      </c>
-      <c r="AT15" t="s">
-        <v>116</v>
-      </c>
-      <c r="AX15" t="s">
-        <v>117</v>
-      </c>
-      <c r="BB15" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="16" spans="1:57">
-      <c r="A16" t="s">
-        <v>71</v>
-      </c>
-      <c r="B16" t="s">
-        <v>105</v>
-      </c>
-      <c r="C16">
-        <v>15.6</v>
-      </c>
-      <c r="D16">
-        <v>5.44</v>
-      </c>
-      <c r="E16">
-        <v>5.65</v>
-      </c>
-      <c r="F16" t="s">
-        <v>106</v>
-      </c>
-      <c r="G16">
-        <v>15.67</v>
-      </c>
-      <c r="H16">
-        <v>5.37</v>
-      </c>
-      <c r="I16">
-        <v>5.57</v>
-      </c>
-      <c r="J16" t="s">
-        <v>107</v>
-      </c>
-      <c r="K16">
-        <v>15.39</v>
-      </c>
-      <c r="L16">
-        <v>5.48</v>
-      </c>
-      <c r="M16">
-        <v>5.7</v>
-      </c>
-      <c r="N16" t="s">
-        <v>108</v>
-      </c>
-      <c r="O16">
-        <v>14.67</v>
-      </c>
-      <c r="P16">
-        <v>5.69</v>
-      </c>
-      <c r="Q16">
-        <v>5.93</v>
-      </c>
-      <c r="R16" t="s">
-        <v>109</v>
-      </c>
-      <c r="S16">
-        <v>14.87</v>
-      </c>
-      <c r="T16">
-        <v>5.67</v>
-      </c>
-      <c r="U16">
-        <v>5.9</v>
-      </c>
-      <c r="V16" t="s">
-        <v>110</v>
-      </c>
-      <c r="W16">
-        <v>14.53</v>
-      </c>
-      <c r="X16">
-        <v>5.81</v>
-      </c>
-      <c r="Y16">
-        <v>6.03</v>
-      </c>
-      <c r="Z16" t="s">
-        <v>111</v>
-      </c>
-      <c r="AA16">
-        <v>14.6</v>
-      </c>
-      <c r="AB16">
-        <v>5.78</v>
-      </c>
-      <c r="AC16">
-        <v>5.99</v>
-      </c>
-      <c r="AD16" t="s">
-        <v>112</v>
-      </c>
-      <c r="AE16">
-        <v>17.8</v>
-      </c>
-      <c r="AF16">
-        <v>4.83</v>
-      </c>
-      <c r="AG16">
-        <v>4.94</v>
-      </c>
-      <c r="AH16" t="s">
-        <v>113</v>
-      </c>
-      <c r="AI16">
-        <v>21.14</v>
-      </c>
-      <c r="AJ16">
-        <v>4.06</v>
-      </c>
-      <c r="AK16">
-        <v>4.08</v>
-      </c>
-      <c r="AL16" t="s">
-        <v>114</v>
-      </c>
-      <c r="AM16">
-        <v>26</v>
-      </c>
-      <c r="AN16">
-        <v>3.11</v>
-      </c>
-      <c r="AO16">
-        <v>2.94</v>
-      </c>
-      <c r="AP16" t="s">
-        <v>115</v>
-      </c>
-      <c r="AT16" t="s">
-        <v>116</v>
-      </c>
-      <c r="AX16" t="s">
-        <v>117</v>
-      </c>
-      <c r="BB16" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="17" spans="1:54">
-      <c r="A17" t="s">
-        <v>72</v>
-      </c>
-      <c r="B17" t="s">
-        <v>105</v>
-      </c>
-      <c r="C17">
-        <v>89</v>
-      </c>
-      <c r="D17">
-        <v>0.95</v>
-      </c>
-      <c r="E17">
-        <v>0.8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>106</v>
-      </c>
-      <c r="G17">
-        <v>90.43000000000001</v>
-      </c>
-      <c r="H17">
-        <v>0.93</v>
-      </c>
-      <c r="I17">
-        <v>0.75</v>
-      </c>
-      <c r="J17" t="s">
-        <v>107</v>
-      </c>
-      <c r="K17">
-        <v>133.71</v>
-      </c>
-      <c r="L17">
-        <v>0.63</v>
-      </c>
-      <c r="M17">
-        <v>0.45</v>
-      </c>
-      <c r="N17" t="s">
-        <v>108</v>
-      </c>
-      <c r="O17">
-        <v>135.14</v>
-      </c>
-      <c r="P17">
-        <v>0.62</v>
-      </c>
-      <c r="Q17">
-        <v>0.43</v>
-      </c>
-      <c r="R17" t="s">
-        <v>109</v>
-      </c>
-      <c r="S17">
-        <v>148.33</v>
-      </c>
-      <c r="T17">
-        <v>0.57</v>
-      </c>
-      <c r="U17">
-        <v>0.39</v>
-      </c>
-      <c r="V17" t="s">
-        <v>110</v>
-      </c>
-      <c r="W17">
-        <v>279.29</v>
-      </c>
-      <c r="X17">
-        <v>0.3</v>
-      </c>
-      <c r="Y17">
-        <v>0.14</v>
-      </c>
-      <c r="Z17" t="s">
-        <v>111</v>
-      </c>
-      <c r="AA17">
-        <v>289.29</v>
-      </c>
-      <c r="AB17">
-        <v>0.29</v>
-      </c>
-      <c r="AC17">
-        <v>0.13</v>
-      </c>
-      <c r="AD17" t="s">
-        <v>112</v>
-      </c>
-      <c r="AE17">
-        <v>123.86</v>
-      </c>
-      <c r="AF17">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="AG17">
-        <v>0.51</v>
-      </c>
-      <c r="AH17" t="s">
-        <v>113</v>
-      </c>
-      <c r="AI17">
-        <v>127.43</v>
-      </c>
-      <c r="AJ17">
-        <v>0.67</v>
-      </c>
-      <c r="AK17">
-        <v>0.47</v>
-      </c>
-      <c r="AL17" t="s">
-        <v>114</v>
-      </c>
-      <c r="AM17">
-        <v>129.57</v>
-      </c>
-      <c r="AN17">
-        <v>0.62</v>
-      </c>
-      <c r="AO17">
-        <v>0.33</v>
-      </c>
-      <c r="AP17" t="s">
-        <v>115</v>
-      </c>
-      <c r="AT17" t="s">
-        <v>116</v>
-      </c>
-      <c r="AX17" t="s">
-        <v>117</v>
-      </c>
-      <c r="BB17" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="18" spans="1:54">
-      <c r="A18" t="s">
-        <v>73</v>
-      </c>
-      <c r="B18" t="s">
-        <v>105</v>
-      </c>
-      <c r="C18">
-        <v>250</v>
-      </c>
-      <c r="D18">
-        <v>0.34</v>
-      </c>
-      <c r="E18">
-        <v>0.18</v>
-      </c>
-      <c r="F18" t="s">
-        <v>106</v>
-      </c>
-      <c r="G18">
-        <v>259.86</v>
-      </c>
-      <c r="H18">
-        <v>0.32</v>
-      </c>
-      <c r="I18">
-        <v>0.16</v>
-      </c>
-      <c r="J18" t="s">
-        <v>107</v>
-      </c>
-      <c r="K18">
-        <v>153</v>
-      </c>
-      <c r="L18">
-        <v>0.55</v>
-      </c>
-      <c r="M18">
-        <v>0.37</v>
-      </c>
-      <c r="N18" t="s">
-        <v>108</v>
-      </c>
-      <c r="O18">
-        <v>143</v>
-      </c>
-      <c r="P18">
-        <v>0.58</v>
-      </c>
-      <c r="Q18">
-        <v>0.4</v>
-      </c>
-      <c r="R18" t="s">
-        <v>109</v>
-      </c>
-      <c r="S18">
-        <v>144.83</v>
-      </c>
-      <c r="T18">
-        <v>0.58</v>
-      </c>
-      <c r="U18">
-        <v>0.4</v>
-      </c>
-      <c r="V18" t="s">
-        <v>110</v>
-      </c>
-      <c r="W18">
-        <v>133.71</v>
-      </c>
-      <c r="X18">
-        <v>0.63</v>
-      </c>
-      <c r="Y18">
-        <v>0.44</v>
-      </c>
-      <c r="Z18" t="s">
-        <v>111</v>
-      </c>
-      <c r="AA18">
-        <v>137.86</v>
-      </c>
-      <c r="AB18">
-        <v>0.61</v>
-      </c>
-      <c r="AC18">
-        <v>0.42</v>
-      </c>
-      <c r="AD18" t="s">
-        <v>112</v>
-      </c>
-      <c r="AE18">
-        <v>150.57</v>
-      </c>
-      <c r="AF18">
-        <v>0.57</v>
-      </c>
-      <c r="AG18">
-        <v>0.39</v>
-      </c>
-      <c r="AH18" t="s">
-        <v>113</v>
-      </c>
-      <c r="AI18">
-        <v>174.86</v>
-      </c>
-      <c r="AJ18">
-        <v>0.49</v>
-      </c>
-      <c r="AK18">
-        <v>0.29</v>
-      </c>
-      <c r="AL18" t="s">
-        <v>114</v>
-      </c>
-      <c r="AM18">
-        <v>179.29</v>
-      </c>
-      <c r="AN18">
-        <v>0.45</v>
-      </c>
-      <c r="AO18">
-        <v>0.19</v>
-      </c>
-      <c r="AP18" t="s">
-        <v>115</v>
-      </c>
-      <c r="AT18" t="s">
-        <v>116</v>
-      </c>
-      <c r="AX18" t="s">
-        <v>117</v>
-      </c>
-      <c r="BB18" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="19" spans="1:54">
-      <c r="A19" t="s">
-        <v>74</v>
-      </c>
-      <c r="B19" t="s">
-        <v>105</v>
-      </c>
-      <c r="C19">
-        <v>467.14</v>
-      </c>
-      <c r="D19">
-        <v>0.18</v>
-      </c>
-      <c r="E19">
-        <v>0.06</v>
-      </c>
-      <c r="F19" t="s">
-        <v>106</v>
-      </c>
-      <c r="G19">
-        <v>505.29</v>
-      </c>
-      <c r="H19">
-        <v>0.17</v>
-      </c>
-      <c r="I19">
-        <v>0.05</v>
-      </c>
-      <c r="J19" t="s">
-        <v>107</v>
-      </c>
-      <c r="K19">
-        <v>494.14</v>
-      </c>
-      <c r="L19">
-        <v>0.17</v>
-      </c>
-      <c r="M19">
-        <v>0.05</v>
-      </c>
-      <c r="N19" t="s">
-        <v>108</v>
-      </c>
-      <c r="O19">
-        <v>502.43</v>
-      </c>
-      <c r="P19">
-        <v>0.17</v>
-      </c>
-      <c r="Q19">
-        <v>0.05</v>
-      </c>
-      <c r="R19" t="s">
-        <v>109</v>
-      </c>
-      <c r="S19">
-        <v>441.33</v>
-      </c>
-      <c r="T19">
-        <v>0.19</v>
-      </c>
-      <c r="U19">
-        <v>0.06</v>
-      </c>
-      <c r="V19" t="s">
-        <v>110</v>
-      </c>
-      <c r="W19">
-        <v>433.86</v>
-      </c>
-      <c r="X19">
-        <v>0.19</v>
-      </c>
-      <c r="Y19">
-        <v>0.06</v>
-      </c>
-      <c r="Z19" t="s">
-        <v>111</v>
-      </c>
-      <c r="AA19">
-        <v>331</v>
-      </c>
-      <c r="AB19">
-        <v>0.25</v>
-      </c>
-      <c r="AC19">
-        <v>0.1</v>
-      </c>
-      <c r="AD19" t="s">
-        <v>112</v>
-      </c>
-      <c r="AE19">
-        <v>337.71</v>
-      </c>
-      <c r="AF19">
-        <v>0.25</v>
-      </c>
-      <c r="AG19">
-        <v>0.11</v>
-      </c>
-      <c r="AH19" t="s">
-        <v>113</v>
-      </c>
-      <c r="AI19">
-        <v>373.71</v>
-      </c>
-      <c r="AJ19">
-        <v>0.23</v>
-      </c>
-      <c r="AK19">
-        <v>0.08</v>
-      </c>
-      <c r="AL19" t="s">
-        <v>114</v>
-      </c>
-      <c r="AM19">
-        <v>429.43</v>
-      </c>
-      <c r="AN19">
-        <v>0.19</v>
-      </c>
-      <c r="AO19">
-        <v>0.04</v>
-      </c>
-      <c r="AP19" t="s">
-        <v>115</v>
-      </c>
-      <c r="AQ19">
-        <v>458.5</v>
-      </c>
-      <c r="AR19">
-        <v>0.19</v>
-      </c>
-      <c r="AS19">
-        <v>0.04</v>
-      </c>
-      <c r="AT19" t="s">
-        <v>116</v>
-      </c>
-      <c r="AX19" t="s">
-        <v>117</v>
-      </c>
-      <c r="BB19" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="20" spans="1:54">
-      <c r="A20" t="s">
-        <v>75</v>
-      </c>
-      <c r="B20" t="s">
-        <v>105</v>
-      </c>
-      <c r="C20">
-        <v>1926.43</v>
-      </c>
-      <c r="D20">
-        <v>0.04</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-      <c r="F20" t="s">
-        <v>106</v>
-      </c>
-      <c r="G20">
-        <v>1926.43</v>
-      </c>
-      <c r="H20">
-        <v>0.04</v>
-      </c>
-      <c r="I20">
-        <v>0</v>
-      </c>
-      <c r="J20" t="s">
-        <v>107</v>
-      </c>
-      <c r="K20">
-        <v>2033.57</v>
-      </c>
-      <c r="L20">
-        <v>0.04</v>
-      </c>
-      <c r="M20">
-        <v>0</v>
-      </c>
-      <c r="N20" t="s">
-        <v>108</v>
-      </c>
-      <c r="O20">
-        <v>2033.57</v>
-      </c>
-      <c r="P20">
-        <v>0.04</v>
-      </c>
-      <c r="Q20">
-        <v>0</v>
-      </c>
-      <c r="R20" t="s">
-        <v>109</v>
-      </c>
-      <c r="S20">
-        <v>2296.6</v>
-      </c>
-      <c r="T20">
-        <v>0.04</v>
-      </c>
-      <c r="U20">
-        <v>0</v>
-      </c>
-      <c r="V20" t="s">
-        <v>110</v>
-      </c>
-      <c r="Z20" t="s">
-        <v>111</v>
-      </c>
-      <c r="AD20" t="s">
-        <v>112</v>
-      </c>
-      <c r="AH20" t="s">
-        <v>113</v>
-      </c>
-      <c r="AL20" t="s">
-        <v>114</v>
-      </c>
-      <c r="AP20" t="s">
-        <v>115</v>
-      </c>
-      <c r="AT20" t="s">
-        <v>116</v>
-      </c>
-      <c r="AX20" t="s">
-        <v>117</v>
-      </c>
-      <c r="BB20" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="21" spans="1:54">
-      <c r="A21" t="s">
-        <v>76</v>
-      </c>
-      <c r="B21" t="s">
-        <v>105</v>
-      </c>
-      <c r="C21">
-        <v>1126.43</v>
-      </c>
-      <c r="D21">
-        <v>0.08</v>
-      </c>
-      <c r="E21">
-        <v>0.01</v>
-      </c>
-      <c r="F21" t="s">
-        <v>106</v>
-      </c>
-      <c r="G21">
-        <v>1126.43</v>
-      </c>
-      <c r="H21">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="I21">
-        <v>0.01</v>
-      </c>
-      <c r="J21" t="s">
-        <v>107</v>
-      </c>
-      <c r="K21">
-        <v>1126.43</v>
-      </c>
-      <c r="L21">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="M21">
-        <v>0.01</v>
-      </c>
-      <c r="N21" t="s">
-        <v>108</v>
-      </c>
-      <c r="O21">
-        <v>1197.86</v>
-      </c>
-      <c r="P21">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="Q21">
-        <v>0.01</v>
-      </c>
-      <c r="R21" t="s">
-        <v>109</v>
-      </c>
-      <c r="S21">
-        <v>1296.6</v>
-      </c>
-      <c r="T21">
-        <v>0.06</v>
-      </c>
-      <c r="U21">
-        <v>0.01</v>
-      </c>
-      <c r="V21" t="s">
-        <v>110</v>
-      </c>
-      <c r="W21">
-        <v>1247.33</v>
-      </c>
-      <c r="X21">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="Y21">
-        <v>0.01</v>
-      </c>
-      <c r="Z21" t="s">
-        <v>111</v>
-      </c>
-      <c r="AA21">
-        <v>1569.29</v>
-      </c>
-      <c r="AB21">
-        <v>0.05</v>
-      </c>
-      <c r="AC21">
-        <v>0.01</v>
-      </c>
-      <c r="AD21" t="s">
-        <v>112</v>
-      </c>
-      <c r="AE21">
-        <v>2140.71</v>
-      </c>
-      <c r="AF21">
-        <v>0.04</v>
-      </c>
-      <c r="AG21">
-        <v>0</v>
-      </c>
-      <c r="AH21" t="s">
-        <v>113</v>
-      </c>
-      <c r="AI21">
-        <v>2001</v>
-      </c>
-      <c r="AJ21">
-        <v>0.04</v>
-      </c>
-      <c r="AK21">
-        <v>0</v>
-      </c>
-      <c r="AL21" t="s">
-        <v>114</v>
-      </c>
-      <c r="AM21">
-        <v>2001</v>
-      </c>
-      <c r="AN21">
-        <v>0.04</v>
-      </c>
-      <c r="AO21">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="s">
-        <v>115</v>
-      </c>
-      <c r="AT21" t="s">
-        <v>116</v>
-      </c>
-      <c r="AX21" t="s">
-        <v>117</v>
-      </c>
-      <c r="BB21" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="22" spans="1:54">
-      <c r="A22" t="s">
-        <v>77</v>
-      </c>
-      <c r="B22" t="s">
-        <v>105</v>
-      </c>
-      <c r="C22">
-        <v>540.71</v>
-      </c>
-      <c r="D22">
-        <v>0.16</v>
-      </c>
-      <c r="E22">
-        <v>0.05</v>
-      </c>
-      <c r="F22" t="s">
-        <v>106</v>
-      </c>
-      <c r="G22">
-        <v>576.4299999999999</v>
-      </c>
-      <c r="H22">
-        <v>0.15</v>
-      </c>
-      <c r="I22">
-        <v>0.04</v>
-      </c>
-      <c r="J22" t="s">
-        <v>107</v>
-      </c>
-      <c r="K22">
-        <v>576.4299999999999</v>
-      </c>
-      <c r="L22">
-        <v>0.15</v>
-      </c>
-      <c r="M22">
-        <v>0.04</v>
-      </c>
-      <c r="N22" t="s">
-        <v>108</v>
-      </c>
-      <c r="O22">
-        <v>612.14</v>
-      </c>
-      <c r="P22">
-        <v>0.14</v>
-      </c>
-      <c r="Q22">
-        <v>0.03</v>
-      </c>
-      <c r="R22" t="s">
-        <v>109</v>
-      </c>
-      <c r="S22">
-        <v>630.67</v>
-      </c>
-      <c r="T22">
-        <v>0.13</v>
-      </c>
-      <c r="U22">
-        <v>0.03</v>
-      </c>
-      <c r="V22" t="s">
-        <v>110</v>
-      </c>
-      <c r="W22">
-        <v>647.86</v>
-      </c>
-      <c r="X22">
-        <v>0.13</v>
-      </c>
-      <c r="Y22">
-        <v>0.03</v>
-      </c>
-      <c r="Z22" t="s">
-        <v>111</v>
-      </c>
-      <c r="AA22">
-        <v>647.86</v>
-      </c>
-      <c r="AB22">
-        <v>0.13</v>
-      </c>
-      <c r="AC22">
-        <v>0.03</v>
-      </c>
-      <c r="AD22" t="s">
-        <v>112</v>
-      </c>
-      <c r="AE22">
-        <v>647.86</v>
-      </c>
-      <c r="AF22">
-        <v>0.13</v>
-      </c>
-      <c r="AG22">
-        <v>0.03</v>
-      </c>
-      <c r="AH22" t="s">
-        <v>113</v>
-      </c>
-      <c r="AI22">
-        <v>1219.29</v>
-      </c>
-      <c r="AJ22">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK22">
-        <v>0.01</v>
-      </c>
-      <c r="AL22" t="s">
-        <v>114</v>
-      </c>
-      <c r="AP22" t="s">
-        <v>115</v>
-      </c>
-      <c r="AT22" t="s">
-        <v>116</v>
-      </c>
-      <c r="AX22" t="s">
-        <v>117</v>
-      </c>
-      <c r="BB22" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="23" spans="1:54">
-      <c r="A23" t="s">
-        <v>78</v>
-      </c>
-      <c r="B23" t="s">
-        <v>105</v>
-      </c>
-      <c r="C23">
-        <v>53.43</v>
-      </c>
-      <c r="D23">
-        <v>1.59</v>
-      </c>
-      <c r="E23">
-        <v>1.47</v>
-      </c>
-      <c r="F23" t="s">
-        <v>106</v>
-      </c>
-      <c r="G23">
-        <v>53.43</v>
-      </c>
-      <c r="H23">
-        <v>1.57</v>
-      </c>
-      <c r="I23">
-        <v>1.44</v>
-      </c>
-      <c r="J23" t="s">
-        <v>107</v>
-      </c>
-      <c r="K23">
-        <v>51.29</v>
-      </c>
-      <c r="L23">
-        <v>1.64</v>
-      </c>
-      <c r="M23">
-        <v>1.52</v>
-      </c>
-      <c r="N23" t="s">
-        <v>108</v>
-      </c>
-      <c r="O23">
-        <v>51.29</v>
-      </c>
-      <c r="P23">
-        <v>1.63</v>
-      </c>
-      <c r="Q23">
-        <v>1.49</v>
-      </c>
-      <c r="R23" t="s">
-        <v>109</v>
-      </c>
-      <c r="S23">
-        <v>53</v>
-      </c>
-      <c r="T23">
-        <v>1.59</v>
-      </c>
-      <c r="U23">
-        <v>1.46</v>
-      </c>
-      <c r="V23" t="s">
-        <v>110</v>
-      </c>
-      <c r="W23">
-        <v>42.86</v>
-      </c>
-      <c r="X23">
-        <v>1.97</v>
-      </c>
-      <c r="Y23">
-        <v>1.86</v>
-      </c>
-      <c r="Z23" t="s">
-        <v>111</v>
-      </c>
-      <c r="AA23">
-        <v>40</v>
-      </c>
-      <c r="AB23">
-        <v>2.11</v>
-      </c>
-      <c r="AC23">
-        <v>2</v>
-      </c>
-      <c r="AD23" t="s">
-        <v>112</v>
-      </c>
-      <c r="AE23">
-        <v>49.86</v>
-      </c>
-      <c r="AF23">
-        <v>1.72</v>
-      </c>
-      <c r="AG23">
-        <v>1.59</v>
-      </c>
-      <c r="AH23" t="s">
-        <v>113</v>
-      </c>
-      <c r="AI23">
-        <v>58</v>
-      </c>
-      <c r="AJ23">
-        <v>1.48</v>
-      </c>
-      <c r="AK23">
-        <v>1.3</v>
-      </c>
-      <c r="AL23" t="s">
-        <v>114</v>
-      </c>
-      <c r="AP23" t="s">
-        <v>115</v>
-      </c>
-      <c r="AT23" t="s">
-        <v>116</v>
-      </c>
-      <c r="AX23" t="s">
-        <v>117</v>
-      </c>
-      <c r="BB23" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="24" spans="1:54">
-      <c r="A24" t="s">
-        <v>79</v>
-      </c>
-      <c r="B24" t="s">
-        <v>105</v>
-      </c>
-      <c r="C24">
-        <v>1497.86</v>
-      </c>
-      <c r="D24">
-        <v>0.06</v>
-      </c>
-      <c r="E24">
-        <v>0.01</v>
-      </c>
-      <c r="F24" t="s">
-        <v>106</v>
-      </c>
-      <c r="G24">
-        <v>1497.86</v>
-      </c>
-      <c r="H24">
-        <v>0.06</v>
-      </c>
-      <c r="I24">
-        <v>0.01</v>
-      </c>
-      <c r="J24" t="s">
-        <v>107</v>
-      </c>
-      <c r="K24">
-        <v>1497.86</v>
-      </c>
-      <c r="L24">
-        <v>0.06</v>
-      </c>
-      <c r="M24">
-        <v>0.01</v>
-      </c>
-      <c r="N24" t="s">
-        <v>108</v>
-      </c>
-      <c r="O24">
-        <v>1497.86</v>
-      </c>
-      <c r="P24">
-        <v>0.06</v>
-      </c>
-      <c r="Q24">
-        <v>0.01</v>
-      </c>
-      <c r="R24" t="s">
-        <v>109</v>
-      </c>
-      <c r="S24">
-        <v>1696.6</v>
-      </c>
-      <c r="T24">
-        <v>0.05</v>
-      </c>
-      <c r="U24">
-        <v>0</v>
-      </c>
-      <c r="V24" t="s">
-        <v>110</v>
-      </c>
-      <c r="W24">
-        <v>1664</v>
-      </c>
-      <c r="X24">
-        <v>0.05</v>
-      </c>
-      <c r="Y24">
-        <v>0</v>
-      </c>
-      <c r="Z24" t="s">
-        <v>111</v>
-      </c>
-      <c r="AD24" t="s">
-        <v>112</v>
-      </c>
-      <c r="AH24" t="s">
-        <v>113</v>
-      </c>
-      <c r="AL24" t="s">
-        <v>114</v>
-      </c>
-      <c r="AP24" t="s">
-        <v>115</v>
-      </c>
-      <c r="AT24" t="s">
-        <v>116</v>
-      </c>
-      <c r="AX24" t="s">
-        <v>117</v>
-      </c>
-      <c r="BB24" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="25" spans="1:54">
-      <c r="A25" t="s">
-        <v>80</v>
-      </c>
-      <c r="B25" t="s">
-        <v>105</v>
-      </c>
-      <c r="C25">
-        <v>191.71</v>
-      </c>
-      <c r="D25">
-        <v>0.44</v>
-      </c>
-      <c r="E25">
-        <v>0.28</v>
-      </c>
-      <c r="F25" t="s">
-        <v>106</v>
-      </c>
-      <c r="G25">
-        <v>222.71</v>
-      </c>
-      <c r="H25">
-        <v>0.38</v>
-      </c>
-      <c r="I25">
-        <v>0.21</v>
-      </c>
-      <c r="J25" t="s">
-        <v>107</v>
-      </c>
-      <c r="K25">
-        <v>193.29</v>
-      </c>
-      <c r="L25">
-        <v>0.44</v>
-      </c>
-      <c r="M25">
-        <v>0.26</v>
-      </c>
-      <c r="N25" t="s">
-        <v>108</v>
-      </c>
-      <c r="O25">
-        <v>197.43</v>
-      </c>
-      <c r="P25">
-        <v>0.42</v>
-      </c>
-      <c r="Q25">
-        <v>0.24</v>
-      </c>
-      <c r="R25" t="s">
-        <v>109</v>
-      </c>
-      <c r="S25">
-        <v>148.17</v>
-      </c>
-      <c r="T25">
-        <v>0.57</v>
-      </c>
-      <c r="U25">
-        <v>0.39</v>
-      </c>
-      <c r="V25" t="s">
-        <v>110</v>
-      </c>
-      <c r="W25">
-        <v>140</v>
-      </c>
-      <c r="X25">
-        <v>0.6</v>
-      </c>
-      <c r="Y25">
-        <v>0.41</v>
-      </c>
-      <c r="Z25" t="s">
-        <v>111</v>
-      </c>
-      <c r="AA25">
-        <v>138.57</v>
-      </c>
-      <c r="AB25">
-        <v>0.61</v>
-      </c>
-      <c r="AC25">
-        <v>0.41</v>
-      </c>
-      <c r="AD25" t="s">
-        <v>112</v>
-      </c>
-      <c r="AE25">
-        <v>180.57</v>
-      </c>
-      <c r="AF25">
-        <v>0.48</v>
-      </c>
-      <c r="AG25">
-        <v>0.3</v>
-      </c>
-      <c r="AH25" t="s">
-        <v>113</v>
-      </c>
-      <c r="AI25">
-        <v>189.07</v>
-      </c>
-      <c r="AJ25">
-        <v>0.45</v>
-      </c>
-      <c r="AK25">
-        <v>0.26</v>
-      </c>
-      <c r="AL25" t="s">
-        <v>114</v>
-      </c>
-      <c r="AM25">
-        <v>165.36</v>
-      </c>
-      <c r="AN25">
-        <v>0.49</v>
-      </c>
-      <c r="AO25">
-        <v>0.22</v>
-      </c>
-      <c r="AP25" t="s">
-        <v>115</v>
-      </c>
-      <c r="AQ25">
-        <v>238.33</v>
-      </c>
-      <c r="AR25">
-        <v>0.37</v>
-      </c>
-      <c r="AS25">
-        <v>0.15</v>
-      </c>
-      <c r="AT25" t="s">
-        <v>116</v>
-      </c>
-      <c r="AU25">
-        <v>249.83</v>
-      </c>
-      <c r="AV25">
-        <v>0.35</v>
-      </c>
-      <c r="AW25">
-        <v>0.13</v>
-      </c>
-      <c r="AX25" t="s">
-        <v>117</v>
-      </c>
-      <c r="BB25" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="26" spans="1:54">
-      <c r="A26" t="s">
-        <v>81</v>
-      </c>
-      <c r="B26" t="s">
-        <v>105</v>
-      </c>
-      <c r="C26">
-        <v>1326.43</v>
-      </c>
-      <c r="D26">
-        <v>0.06</v>
       </c>
       <c r="E26">
         <v>0.01</v>
       </c>
       <c r="F26" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="G26">
-        <v>1326.43</v>
+        <v>1069.29</v>
       </c>
       <c r="H26">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="I26">
         <v>0.01</v>
       </c>
       <c r="J26" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="K26">
-        <v>1326.43</v>
+        <v>1069.29</v>
       </c>
       <c r="L26">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="M26">
         <v>0.01</v>
       </c>
       <c r="N26" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="O26">
         <v>1069.29</v>
@@ -4479,525 +4614,564 @@
         <v>0.01</v>
       </c>
       <c r="R26" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="S26">
-        <v>996.6</v>
+        <v>1372.33</v>
       </c>
       <c r="T26">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="U26">
         <v>0.01</v>
       </c>
       <c r="V26" t="s">
+        <v>114</v>
+      </c>
+      <c r="W26">
+        <v>1926.43</v>
+      </c>
+      <c r="X26">
+        <v>0.04</v>
+      </c>
+      <c r="Y26">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="s">
+        <v>115</v>
+      </c>
+      <c r="AA26">
+        <v>1926.43</v>
+      </c>
+      <c r="AB26">
+        <v>0.04</v>
+      </c>
+      <c r="AC26">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="s">
+        <v>116</v>
+      </c>
+      <c r="AH26" t="s">
+        <v>117</v>
+      </c>
+      <c r="AL26" t="s">
+        <v>118</v>
+      </c>
+      <c r="AP26" t="s">
+        <v>119</v>
+      </c>
+      <c r="AT26" t="s">
+        <v>120</v>
+      </c>
+      <c r="AX26" t="s">
+        <v>121</v>
+      </c>
+      <c r="BB26" t="s">
+        <v>122</v>
+      </c>
+      <c r="BF26" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="27" spans="1:58">
+      <c r="A27" t="s">
+        <v>86</v>
+      </c>
+      <c r="B27" t="s">
+        <v>109</v>
+      </c>
+      <c r="C27">
+        <v>41.71</v>
+      </c>
+      <c r="D27">
+        <v>2.04</v>
+      </c>
+      <c r="E27">
+        <v>1.95</v>
+      </c>
+      <c r="F27" t="s">
         <v>110</v>
       </c>
-      <c r="W26">
-        <v>705.67</v>
-      </c>
-      <c r="X26">
-        <v>0.12</v>
-      </c>
-      <c r="Y26">
-        <v>0.03</v>
-      </c>
-      <c r="Z26" t="s">
+      <c r="G27">
+        <v>45.57</v>
+      </c>
+      <c r="H27">
+        <v>1.85</v>
+      </c>
+      <c r="I27">
+        <v>1.73</v>
+      </c>
+      <c r="J27" t="s">
         <v>111</v>
       </c>
-      <c r="AA26">
-        <v>747.86</v>
-      </c>
-      <c r="AB26">
-        <v>0.11</v>
-      </c>
-      <c r="AC26">
-        <v>0.02</v>
-      </c>
-      <c r="AD26" t="s">
+      <c r="K27">
+        <v>47</v>
+      </c>
+      <c r="L27">
+        <v>1.8</v>
+      </c>
+      <c r="M27">
+        <v>1.68</v>
+      </c>
+      <c r="N27" t="s">
         <v>112</v>
       </c>
-      <c r="AE26">
-        <v>783.5700000000001</v>
-      </c>
-      <c r="AF26">
-        <v>0.11</v>
-      </c>
-      <c r="AG26">
-        <v>0.02</v>
-      </c>
-      <c r="AH26" t="s">
+      <c r="O27">
+        <v>50.43</v>
+      </c>
+      <c r="P27">
+        <v>1.66</v>
+      </c>
+      <c r="Q27">
+        <v>1.52</v>
+      </c>
+      <c r="R27" t="s">
         <v>113</v>
       </c>
-      <c r="AI26">
-        <v>526.4299999999999</v>
-      </c>
-      <c r="AJ26">
-        <v>0.16</v>
-      </c>
-      <c r="AK26">
-        <v>0.04</v>
-      </c>
-      <c r="AL26" t="s">
+      <c r="S27">
+        <v>48</v>
+      </c>
+      <c r="T27">
+        <v>1.76</v>
+      </c>
+      <c r="U27">
+        <v>1.64</v>
+      </c>
+      <c r="V27" t="s">
         <v>114</v>
       </c>
-      <c r="AM26">
-        <v>583.5700000000001</v>
-      </c>
-      <c r="AN26">
-        <v>0.14</v>
-      </c>
-      <c r="AO26">
-        <v>0.02</v>
-      </c>
-      <c r="AP26" t="s">
+      <c r="W27">
+        <v>49.86</v>
+      </c>
+      <c r="X27">
+        <v>1.69</v>
+      </c>
+      <c r="Y27">
+        <v>1.56</v>
+      </c>
+      <c r="Z27" t="s">
         <v>115</v>
       </c>
-      <c r="AQ26">
-        <v>664</v>
-      </c>
-      <c r="AR26">
-        <v>0.13</v>
-      </c>
-      <c r="AS26">
-        <v>0.02</v>
-      </c>
-      <c r="AT26" t="s">
+      <c r="AA27">
+        <v>47</v>
+      </c>
+      <c r="AB27">
+        <v>1.8</v>
+      </c>
+      <c r="AC27">
+        <v>1.66</v>
+      </c>
+      <c r="AD27" t="s">
         <v>116</v>
       </c>
-      <c r="AX26" t="s">
+      <c r="AE27">
+        <v>53.43</v>
+      </c>
+      <c r="AF27">
+        <v>1.61</v>
+      </c>
+      <c r="AG27">
+        <v>1.47</v>
+      </c>
+      <c r="AH27" t="s">
         <v>117</v>
       </c>
-      <c r="BB26" t="s">
+      <c r="AI27">
+        <v>37.29</v>
+      </c>
+      <c r="AJ27">
+        <v>2.3</v>
+      </c>
+      <c r="AK27">
+        <v>2.18</v>
+      </c>
+      <c r="AL27" t="s">
         <v>118</v>
       </c>
+      <c r="AM27">
+        <v>31.86</v>
+      </c>
+      <c r="AN27">
+        <v>2.54</v>
+      </c>
+      <c r="AO27">
+        <v>2.31</v>
+      </c>
+      <c r="AP27" t="s">
+        <v>119</v>
+      </c>
+      <c r="AQ27">
+        <v>29.33</v>
+      </c>
+      <c r="AR27">
+        <v>2.99</v>
+      </c>
+      <c r="AS27">
+        <v>2.79</v>
+      </c>
+      <c r="AT27" t="s">
+        <v>120</v>
+      </c>
+      <c r="AU27">
+        <v>25.5</v>
+      </c>
+      <c r="AV27">
+        <v>3.47</v>
+      </c>
+      <c r="AW27">
+        <v>3.24</v>
+      </c>
+      <c r="AX27" t="s">
+        <v>121</v>
+      </c>
+      <c r="AY27">
+        <v>25</v>
+      </c>
+      <c r="AZ27">
+        <v>3.63</v>
+      </c>
+      <c r="BA27">
+        <v>3.4</v>
+      </c>
+      <c r="BB27" t="s">
+        <v>122</v>
+      </c>
+      <c r="BF27" t="s">
+        <v>123</v>
+      </c>
     </row>
-    <row r="27" spans="1:54">
-      <c r="A27" t="s">
-        <v>82</v>
-      </c>
-      <c r="B27" t="s">
-        <v>105</v>
-      </c>
-      <c r="C27">
-        <v>1069.29</v>
-      </c>
-      <c r="D27">
-        <v>0.08</v>
-      </c>
-      <c r="E27">
-        <v>0.01</v>
-      </c>
-      <c r="F27" t="s">
-        <v>106</v>
-      </c>
-      <c r="G27">
-        <v>1069.29</v>
-      </c>
-      <c r="H27">
-        <v>0.08</v>
-      </c>
-      <c r="I27">
-        <v>0.01</v>
-      </c>
-      <c r="J27" t="s">
-        <v>107</v>
-      </c>
-      <c r="K27">
-        <v>1069.29</v>
-      </c>
-      <c r="L27">
-        <v>0.08</v>
-      </c>
-      <c r="M27">
-        <v>0.01</v>
-      </c>
-      <c r="N27" t="s">
-        <v>108</v>
-      </c>
-      <c r="O27">
-        <v>1069.29</v>
-      </c>
-      <c r="P27">
-        <v>0.08</v>
-      </c>
-      <c r="Q27">
-        <v>0.01</v>
-      </c>
-      <c r="R27" t="s">
+    <row r="28" spans="1:58">
+      <c r="A28" t="s">
+        <v>87</v>
+      </c>
+      <c r="B28" t="s">
         <v>109</v>
       </c>
-      <c r="S27">
-        <v>1372.33</v>
-      </c>
-      <c r="T27">
-        <v>0.06</v>
-      </c>
-      <c r="U27">
-        <v>0.01</v>
-      </c>
-      <c r="V27" t="s">
+      <c r="C28">
+        <v>88.86</v>
+      </c>
+      <c r="D28">
+        <v>0.96</v>
+      </c>
+      <c r="E28">
+        <v>0.8</v>
+      </c>
+      <c r="F28" t="s">
         <v>110</v>
       </c>
-      <c r="W27">
-        <v>1926.43</v>
-      </c>
-      <c r="X27">
-        <v>0.04</v>
-      </c>
-      <c r="Y27">
-        <v>0</v>
-      </c>
-      <c r="Z27" t="s">
+      <c r="G28">
+        <v>91.70999999999999</v>
+      </c>
+      <c r="H28">
+        <v>0.92</v>
+      </c>
+      <c r="I28">
+        <v>0.74</v>
+      </c>
+      <c r="J28" t="s">
         <v>111</v>
       </c>
-      <c r="AA27">
-        <v>1926.43</v>
-      </c>
-      <c r="AB27">
-        <v>0.04</v>
-      </c>
-      <c r="AC27">
-        <v>0</v>
-      </c>
-      <c r="AD27" t="s">
+      <c r="K28">
+        <v>91.70999999999999</v>
+      </c>
+      <c r="L28">
+        <v>0.92</v>
+      </c>
+      <c r="M28">
+        <v>0.75</v>
+      </c>
+      <c r="N28" t="s">
         <v>112</v>
       </c>
-      <c r="AH27" t="s">
+      <c r="O28">
+        <v>92.43000000000001</v>
+      </c>
+      <c r="P28">
+        <v>0.9</v>
+      </c>
+      <c r="Q28">
+        <v>0.72</v>
+      </c>
+      <c r="R28" t="s">
         <v>113</v>
       </c>
-      <c r="AL27" t="s">
+      <c r="S28">
+        <v>110.83</v>
+      </c>
+      <c r="T28">
+        <v>0.76</v>
+      </c>
+      <c r="U28">
+        <v>0.58</v>
+      </c>
+      <c r="V28" t="s">
         <v>114</v>
       </c>
-      <c r="AP27" t="s">
+      <c r="W28">
+        <v>123</v>
+      </c>
+      <c r="X28">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="Y28">
+        <v>0.5</v>
+      </c>
+      <c r="Z28" t="s">
         <v>115</v>
       </c>
-      <c r="AT27" t="s">
+      <c r="AA28">
+        <v>112.29</v>
+      </c>
+      <c r="AB28">
+        <v>0.75</v>
+      </c>
+      <c r="AC28">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AD28" t="s">
         <v>116</v>
       </c>
-      <c r="AX27" t="s">
+      <c r="AE28">
+        <v>132.29</v>
+      </c>
+      <c r="AF28">
+        <v>0.65</v>
+      </c>
+      <c r="AG28">
+        <v>0.47</v>
+      </c>
+      <c r="AH28" t="s">
         <v>117</v>
       </c>
-      <c r="BB27" t="s">
+      <c r="AI28">
+        <v>144.64</v>
+      </c>
+      <c r="AJ28">
+        <v>0.59</v>
+      </c>
+      <c r="AK28">
+        <v>0.39</v>
+      </c>
+      <c r="AL28" t="s">
         <v>118</v>
       </c>
+      <c r="AM28">
+        <v>146.07</v>
+      </c>
+      <c r="AN28">
+        <v>0.55</v>
+      </c>
+      <c r="AO28">
+        <v>0.27</v>
+      </c>
+      <c r="AP28" t="s">
+        <v>119</v>
+      </c>
+      <c r="AQ28">
+        <v>173</v>
+      </c>
+      <c r="AR28">
+        <v>0.51</v>
+      </c>
+      <c r="AS28">
+        <v>0.26</v>
+      </c>
+      <c r="AT28" t="s">
+        <v>120</v>
+      </c>
+      <c r="AX28" t="s">
+        <v>121</v>
+      </c>
+      <c r="BB28" t="s">
+        <v>122</v>
+      </c>
+      <c r="BF28" t="s">
+        <v>123</v>
+      </c>
     </row>
-    <row r="28" spans="1:54">
-      <c r="A28" t="s">
-        <v>83</v>
-      </c>
-      <c r="B28" t="s">
-        <v>105</v>
-      </c>
-      <c r="C28">
-        <v>41.71</v>
-      </c>
-      <c r="D28">
-        <v>2.04</v>
-      </c>
-      <c r="E28">
-        <v>1.95</v>
-      </c>
-      <c r="F28" t="s">
-        <v>106</v>
-      </c>
-      <c r="G28">
-        <v>45.57</v>
-      </c>
-      <c r="H28">
-        <v>1.85</v>
-      </c>
-      <c r="I28">
-        <v>1.73</v>
-      </c>
-      <c r="J28" t="s">
-        <v>107</v>
-      </c>
-      <c r="K28">
-        <v>47</v>
-      </c>
-      <c r="L28">
-        <v>1.8</v>
-      </c>
-      <c r="M28">
-        <v>1.68</v>
-      </c>
-      <c r="N28" t="s">
-        <v>108</v>
-      </c>
-      <c r="O28">
-        <v>50.43</v>
-      </c>
-      <c r="P28">
+    <row r="29" spans="1:58">
+      <c r="A29" t="s">
+        <v>88</v>
+      </c>
+      <c r="B29" t="s">
+        <v>109</v>
+      </c>
+      <c r="C29">
+        <v>49.86</v>
+      </c>
+      <c r="D29">
+        <v>1.7</v>
+      </c>
+      <c r="E29">
+        <v>1.59</v>
+      </c>
+      <c r="F29" t="s">
+        <v>110</v>
+      </c>
+      <c r="G29">
+        <v>50.57</v>
+      </c>
+      <c r="H29">
         <v>1.66</v>
       </c>
-      <c r="Q28">
-        <v>1.52</v>
-      </c>
-      <c r="R28" t="s">
+      <c r="I29">
+        <v>1.54</v>
+      </c>
+      <c r="J29" t="s">
+        <v>111</v>
+      </c>
+      <c r="K29">
+        <v>38.71</v>
+      </c>
+      <c r="L29">
+        <v>2.18</v>
+      </c>
+      <c r="M29">
+        <v>2.1</v>
+      </c>
+      <c r="N29" t="s">
+        <v>112</v>
+      </c>
+      <c r="O29">
+        <v>37.71</v>
+      </c>
+      <c r="P29">
+        <v>2.21</v>
+      </c>
+      <c r="Q29">
+        <v>2.13</v>
+      </c>
+      <c r="R29" t="s">
+        <v>113</v>
+      </c>
+      <c r="S29">
+        <v>40.67</v>
+      </c>
+      <c r="T29">
+        <v>2.07</v>
+      </c>
+      <c r="U29">
+        <v>1.98</v>
+      </c>
+      <c r="V29" t="s">
+        <v>114</v>
+      </c>
+      <c r="W29">
+        <v>32.86</v>
+      </c>
+      <c r="X29">
+        <v>2.57</v>
+      </c>
+      <c r="Y29">
+        <v>2.51</v>
+      </c>
+      <c r="Z29" t="s">
+        <v>115</v>
+      </c>
+      <c r="AA29">
+        <v>35.14</v>
+      </c>
+      <c r="AB29">
+        <v>2.4</v>
+      </c>
+      <c r="AC29">
+        <v>2.32</v>
+      </c>
+      <c r="AD29" t="s">
+        <v>116</v>
+      </c>
+      <c r="AE29">
+        <v>43.14</v>
+      </c>
+      <c r="AF29">
+        <v>1.99</v>
+      </c>
+      <c r="AG29">
+        <v>1.88</v>
+      </c>
+      <c r="AH29" t="s">
+        <v>117</v>
+      </c>
+      <c r="AI29">
+        <v>51.29</v>
+      </c>
+      <c r="AJ29">
+        <v>1.67</v>
+      </c>
+      <c r="AK29">
+        <v>1.51</v>
+      </c>
+      <c r="AL29" t="s">
+        <v>118</v>
+      </c>
+      <c r="AM29">
+        <v>21.57</v>
+      </c>
+      <c r="AN29">
+        <v>3.75</v>
+      </c>
+      <c r="AO29">
+        <v>3.65</v>
+      </c>
+      <c r="AP29" t="s">
+        <v>119</v>
+      </c>
+      <c r="AQ29">
+        <v>27.33</v>
+      </c>
+      <c r="AR29">
+        <v>3.21</v>
+      </c>
+      <c r="AS29">
+        <v>3.02</v>
+      </c>
+      <c r="AT29" t="s">
+        <v>120</v>
+      </c>
+      <c r="AU29">
+        <v>31.83</v>
+      </c>
+      <c r="AV29">
+        <v>2.78</v>
+      </c>
+      <c r="AW29">
+        <v>2.51</v>
+      </c>
+      <c r="AX29" t="s">
+        <v>121</v>
+      </c>
+      <c r="AY29">
+        <v>30.5</v>
+      </c>
+      <c r="AZ29">
+        <v>2.98</v>
+      </c>
+      <c r="BA29">
+        <v>2.71</v>
+      </c>
+      <c r="BB29" t="s">
+        <v>122</v>
+      </c>
+      <c r="BC29">
+        <v>31.33</v>
+      </c>
+      <c r="BD29">
+        <v>2.97</v>
+      </c>
+      <c r="BE29">
+        <v>2.58</v>
+      </c>
+      <c r="BF29" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="30" spans="1:58">
+      <c r="A30" t="s">
+        <v>89</v>
+      </c>
+      <c r="B30" t="s">
         <v>109</v>
-      </c>
-      <c r="S28">
-        <v>48</v>
-      </c>
-      <c r="T28">
-        <v>1.76</v>
-      </c>
-      <c r="U28">
-        <v>1.64</v>
-      </c>
-      <c r="V28" t="s">
-        <v>110</v>
-      </c>
-      <c r="W28">
-        <v>49.86</v>
-      </c>
-      <c r="X28">
-        <v>1.69</v>
-      </c>
-      <c r="Y28">
-        <v>1.56</v>
-      </c>
-      <c r="Z28" t="s">
-        <v>111</v>
-      </c>
-      <c r="AA28">
-        <v>47</v>
-      </c>
-      <c r="AB28">
-        <v>1.8</v>
-      </c>
-      <c r="AC28">
-        <v>1.66</v>
-      </c>
-      <c r="AD28" t="s">
-        <v>112</v>
-      </c>
-      <c r="AE28">
-        <v>53.43</v>
-      </c>
-      <c r="AF28">
-        <v>1.61</v>
-      </c>
-      <c r="AG28">
-        <v>1.47</v>
-      </c>
-      <c r="AH28" t="s">
-        <v>113</v>
-      </c>
-      <c r="AI28">
-        <v>37.29</v>
-      </c>
-      <c r="AJ28">
-        <v>2.3</v>
-      </c>
-      <c r="AK28">
-        <v>2.18</v>
-      </c>
-      <c r="AL28" t="s">
-        <v>114</v>
-      </c>
-      <c r="AM28">
-        <v>31.86</v>
-      </c>
-      <c r="AN28">
-        <v>2.54</v>
-      </c>
-      <c r="AO28">
-        <v>2.31</v>
-      </c>
-      <c r="AP28" t="s">
-        <v>115</v>
-      </c>
-      <c r="AQ28">
-        <v>29.33</v>
-      </c>
-      <c r="AR28">
-        <v>2.99</v>
-      </c>
-      <c r="AS28">
-        <v>2.79</v>
-      </c>
-      <c r="AT28" t="s">
-        <v>116</v>
-      </c>
-      <c r="AU28">
-        <v>25.5</v>
-      </c>
-      <c r="AV28">
-        <v>3.47</v>
-      </c>
-      <c r="AW28">
-        <v>3.24</v>
-      </c>
-      <c r="AX28" t="s">
-        <v>117</v>
-      </c>
-      <c r="AY28">
-        <v>25</v>
-      </c>
-      <c r="AZ28">
-        <v>3.63</v>
-      </c>
-      <c r="BA28">
-        <v>3.4</v>
-      </c>
-      <c r="BB28" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="29" spans="1:54">
-      <c r="A29" t="s">
-        <v>84</v>
-      </c>
-      <c r="B29" t="s">
-        <v>105</v>
-      </c>
-      <c r="C29">
-        <v>88.86</v>
-      </c>
-      <c r="D29">
-        <v>0.96</v>
-      </c>
-      <c r="E29">
-        <v>0.8</v>
-      </c>
-      <c r="F29" t="s">
-        <v>106</v>
-      </c>
-      <c r="G29">
-        <v>91.70999999999999</v>
-      </c>
-      <c r="H29">
-        <v>0.92</v>
-      </c>
-      <c r="I29">
-        <v>0.74</v>
-      </c>
-      <c r="J29" t="s">
-        <v>107</v>
-      </c>
-      <c r="K29">
-        <v>91.70999999999999</v>
-      </c>
-      <c r="L29">
-        <v>0.92</v>
-      </c>
-      <c r="M29">
-        <v>0.75</v>
-      </c>
-      <c r="N29" t="s">
-        <v>108</v>
-      </c>
-      <c r="O29">
-        <v>92.43000000000001</v>
-      </c>
-      <c r="P29">
-        <v>0.9</v>
-      </c>
-      <c r="Q29">
-        <v>0.72</v>
-      </c>
-      <c r="R29" t="s">
-        <v>109</v>
-      </c>
-      <c r="S29">
-        <v>110.83</v>
-      </c>
-      <c r="T29">
-        <v>0.76</v>
-      </c>
-      <c r="U29">
-        <v>0.58</v>
-      </c>
-      <c r="V29" t="s">
-        <v>110</v>
-      </c>
-      <c r="W29">
-        <v>123</v>
-      </c>
-      <c r="X29">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="Y29">
-        <v>0.5</v>
-      </c>
-      <c r="Z29" t="s">
-        <v>111</v>
-      </c>
-      <c r="AA29">
-        <v>112.29</v>
-      </c>
-      <c r="AB29">
-        <v>0.75</v>
-      </c>
-      <c r="AC29">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="AD29" t="s">
-        <v>112</v>
-      </c>
-      <c r="AE29">
-        <v>132.29</v>
-      </c>
-      <c r="AF29">
-        <v>0.65</v>
-      </c>
-      <c r="AG29">
-        <v>0.47</v>
-      </c>
-      <c r="AH29" t="s">
-        <v>113</v>
-      </c>
-      <c r="AI29">
-        <v>144.64</v>
-      </c>
-      <c r="AJ29">
-        <v>0.59</v>
-      </c>
-      <c r="AK29">
-        <v>0.39</v>
-      </c>
-      <c r="AL29" t="s">
-        <v>114</v>
-      </c>
-      <c r="AM29">
-        <v>146.07</v>
-      </c>
-      <c r="AN29">
-        <v>0.55</v>
-      </c>
-      <c r="AO29">
-        <v>0.27</v>
-      </c>
-      <c r="AP29" t="s">
-        <v>115</v>
-      </c>
-      <c r="AQ29">
-        <v>173</v>
-      </c>
-      <c r="AR29">
-        <v>0.51</v>
-      </c>
-      <c r="AS29">
-        <v>0.26</v>
-      </c>
-      <c r="AT29" t="s">
-        <v>116</v>
-      </c>
-      <c r="AX29" t="s">
-        <v>117</v>
-      </c>
-      <c r="BB29" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="30" spans="1:54">
-      <c r="A30" t="s">
-        <v>85</v>
-      </c>
-      <c r="B30" t="s">
-        <v>105</v>
       </c>
       <c r="C30">
         <v>68.43000000000001</v>
@@ -5009,7 +5183,7 @@
         <v>1.1</v>
       </c>
       <c r="F30" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="G30">
         <v>52.71</v>
@@ -5021,7 +5195,7 @@
         <v>1.46</v>
       </c>
       <c r="J30" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="K30">
         <v>52.71</v>
@@ -5033,7 +5207,7 @@
         <v>1.47</v>
       </c>
       <c r="N30" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="O30">
         <v>57.86</v>
@@ -5045,7 +5219,7 @@
         <v>1.29</v>
       </c>
       <c r="R30" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="S30">
         <v>47.17</v>
@@ -5057,7 +5231,7 @@
         <v>1.67</v>
       </c>
       <c r="V30" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="W30">
         <v>51.14</v>
@@ -5069,7 +5243,7 @@
         <v>1.51</v>
       </c>
       <c r="Z30" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="AA30">
         <v>52.57</v>
@@ -5081,7 +5255,7 @@
         <v>1.46</v>
       </c>
       <c r="AD30" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="AE30">
         <v>45.71</v>
@@ -5093,7 +5267,7 @@
         <v>1.76</v>
       </c>
       <c r="AH30" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="AI30">
         <v>50.57</v>
@@ -5105,7 +5279,7 @@
         <v>1.54</v>
       </c>
       <c r="AL30" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="AM30">
         <v>50.29</v>
@@ -5117,7 +5291,7 @@
         <v>1.31</v>
       </c>
       <c r="AP30" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="AQ30">
         <v>28.33</v>
@@ -5129,7 +5303,7 @@
         <v>2.9</v>
       </c>
       <c r="AT30" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="AU30">
         <v>28.83</v>
@@ -5141,7 +5315,7 @@
         <v>2.81</v>
       </c>
       <c r="AX30" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="AY30">
         <v>51</v>
@@ -5153,15 +5327,18 @@
         <v>1.47</v>
       </c>
       <c r="BB30" t="s">
-        <v>118</v>
+        <v>122</v>
+      </c>
+      <c r="BF30" t="s">
+        <v>123</v>
       </c>
     </row>
-    <row r="31" spans="1:54">
+    <row r="31" spans="1:58">
       <c r="A31" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B31" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C31">
         <v>1197.86</v>
@@ -5173,7 +5350,7 @@
         <v>0.01</v>
       </c>
       <c r="F31" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="G31">
         <v>1197.86</v>
@@ -5185,7 +5362,7 @@
         <v>0.01</v>
       </c>
       <c r="J31" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="K31">
         <v>1197.86</v>
@@ -5197,7 +5374,7 @@
         <v>0.01</v>
       </c>
       <c r="N31" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="O31">
         <v>819.29</v>
@@ -5209,7 +5386,7 @@
         <v>0.02</v>
       </c>
       <c r="R31" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="S31">
         <v>872.33</v>
@@ -5221,7 +5398,7 @@
         <v>0.02</v>
       </c>
       <c r="V31" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="W31">
         <v>890.71</v>
@@ -5233,7 +5410,7 @@
         <v>0.02</v>
       </c>
       <c r="Z31" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="AA31">
         <v>890.71</v>
@@ -5245,7 +5422,7 @@
         <v>0.02</v>
       </c>
       <c r="AD31" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="AE31">
         <v>926.4299999999999</v>
@@ -5257,30 +5434,33 @@
         <v>0.02</v>
       </c>
       <c r="AH31" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="AL31" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="AP31" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="AT31" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="AX31" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="BB31" t="s">
-        <v>118</v>
+        <v>122</v>
+      </c>
+      <c r="BF31" t="s">
+        <v>123</v>
       </c>
     </row>
-    <row r="32" spans="1:54">
+    <row r="32" spans="1:58">
       <c r="A32" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B32" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C32">
         <v>21.29</v>
@@ -5292,7 +5472,7 @@
         <v>4.07</v>
       </c>
       <c r="F32" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="G32">
         <v>20.29</v>
@@ -5304,7 +5484,7 @@
         <v>4.24</v>
       </c>
       <c r="J32" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="K32">
         <v>19.71</v>
@@ -5316,7 +5496,7 @@
         <v>4.38</v>
       </c>
       <c r="N32" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="O32">
         <v>20.14</v>
@@ -5328,7 +5508,7 @@
         <v>4.24</v>
       </c>
       <c r="R32" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="S32">
         <v>21</v>
@@ -5340,7 +5520,7 @@
         <v>4.09</v>
       </c>
       <c r="V32" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="W32">
         <v>17.53</v>
@@ -5352,7 +5532,7 @@
         <v>4.95</v>
       </c>
       <c r="Z32" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="AA32">
         <v>17.23</v>
@@ -5364,7 +5544,7 @@
         <v>5.03</v>
       </c>
       <c r="AD32" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="AE32">
         <v>15.96</v>
@@ -5376,7 +5556,7 @@
         <v>5.54</v>
       </c>
       <c r="AH32" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="AI32">
         <v>17.43</v>
@@ -5388,7 +5568,7 @@
         <v>5.01</v>
       </c>
       <c r="AL32" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="AM32">
         <v>17</v>
@@ -5400,24 +5580,27 @@
         <v>4.77</v>
       </c>
       <c r="AP32" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="AT32" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="AX32" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="BB32" t="s">
-        <v>118</v>
+        <v>122</v>
+      </c>
+      <c r="BF32" t="s">
+        <v>123</v>
       </c>
     </row>
-    <row r="33" spans="1:54">
+    <row r="33" spans="1:58">
       <c r="A33" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B33" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C33">
         <v>1197.86</v>
@@ -5429,7 +5612,7 @@
         <v>0.01</v>
       </c>
       <c r="F33" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="G33">
         <v>1197.86</v>
@@ -5441,7 +5624,7 @@
         <v>0.01</v>
       </c>
       <c r="J33" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="K33">
         <v>1197.86</v>
@@ -5453,7 +5636,7 @@
         <v>0.01</v>
       </c>
       <c r="N33" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="O33">
         <v>1197.86</v>
@@ -5465,7 +5648,7 @@
         <v>0.01</v>
       </c>
       <c r="R33" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="S33">
         <v>1247.33</v>
@@ -5477,7 +5660,7 @@
         <v>0.01</v>
       </c>
       <c r="V33" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="W33">
         <v>1212.14</v>
@@ -5489,7 +5672,7 @@
         <v>0.01</v>
       </c>
       <c r="Z33" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="AA33">
         <v>1664</v>
@@ -5501,33 +5684,36 @@
         <v>0</v>
       </c>
       <c r="AD33" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="AH33" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="AL33" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="AP33" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="AT33" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="AX33" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="BB33" t="s">
-        <v>118</v>
+        <v>122</v>
+      </c>
+      <c r="BF33" t="s">
+        <v>123</v>
       </c>
     </row>
-    <row r="34" spans="1:54">
+    <row r="34" spans="1:58">
       <c r="A34" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B34" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C34">
         <v>243.29</v>
@@ -5539,7 +5725,7 @@
         <v>0.19</v>
       </c>
       <c r="F34" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="G34">
         <v>455.57</v>
@@ -5551,7 +5737,7 @@
         <v>0.06</v>
       </c>
       <c r="J34" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="K34">
         <v>483.57</v>
@@ -5563,7 +5749,7 @@
         <v>0.06</v>
       </c>
       <c r="N34" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="O34">
         <v>490.71</v>
@@ -5575,7 +5761,7 @@
         <v>0.05</v>
       </c>
       <c r="R34" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="S34">
         <v>522.33</v>
@@ -5587,7 +5773,7 @@
         <v>0.05</v>
       </c>
       <c r="V34" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="W34">
         <v>324.29</v>
@@ -5599,7 +5785,7 @@
         <v>0.11</v>
       </c>
       <c r="Z34" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="AA34">
         <v>320.14</v>
@@ -5611,7 +5797,7 @@
         <v>0.11</v>
       </c>
       <c r="AD34" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="AE34">
         <v>327.14</v>
@@ -5623,7 +5809,7 @@
         <v>0.11</v>
       </c>
       <c r="AH34" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="AI34">
         <v>448.14</v>
@@ -5635,7 +5821,7 @@
         <v>0.06</v>
       </c>
       <c r="AL34" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="AM34">
         <v>212.57</v>
@@ -5647,7 +5833,7 @@
         <v>0.14</v>
       </c>
       <c r="AP34" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="AQ34">
         <v>302.17</v>
@@ -5659,7 +5845,7 @@
         <v>0.1</v>
       </c>
       <c r="AT34" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="AU34">
         <v>370.33</v>
@@ -5671,18 +5857,21 @@
         <v>0.06</v>
       </c>
       <c r="AX34" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="BB34" t="s">
-        <v>118</v>
+        <v>122</v>
+      </c>
+      <c r="BF34" t="s">
+        <v>123</v>
       </c>
     </row>
-    <row r="35" spans="1:54">
+    <row r="35" spans="1:58">
       <c r="A35" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B35" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C35">
         <v>8.85</v>
@@ -5694,7 +5883,7 @@
         <v>10.17</v>
       </c>
       <c r="F35" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="G35">
         <v>8.699999999999999</v>
@@ -5706,7 +5895,7 @@
         <v>10.26</v>
       </c>
       <c r="J35" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="K35">
         <v>8.630000000000001</v>
@@ -5718,7 +5907,7 @@
         <v>10.38</v>
       </c>
       <c r="N35" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="O35">
         <v>8.619999999999999</v>
@@ -5730,7 +5919,7 @@
         <v>10.32</v>
       </c>
       <c r="R35" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="S35">
         <v>10.63</v>
@@ -5742,7 +5931,7 @@
         <v>8.359999999999999</v>
       </c>
       <c r="V35" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="W35">
         <v>11.67</v>
@@ -5754,7 +5943,7 @@
         <v>7.59</v>
       </c>
       <c r="Z35" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="AA35">
         <v>10.83</v>
@@ -5766,7 +5955,7 @@
         <v>8.19</v>
       </c>
       <c r="AD35" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="AE35">
         <v>10.54</v>
@@ -5778,7 +5967,7 @@
         <v>8.529999999999999</v>
       </c>
       <c r="AH35" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="AI35">
         <v>13.39</v>
@@ -5790,7 +5979,7 @@
         <v>6.62</v>
       </c>
       <c r="AL35" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="AM35">
         <v>13.6</v>
@@ -5802,7 +5991,7 @@
         <v>6.09</v>
       </c>
       <c r="AP35" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="AQ35">
         <v>15.52</v>
@@ -5814,7 +6003,7 @@
         <v>5.62</v>
       </c>
       <c r="AT35" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="AU35">
         <v>13.95</v>
@@ -5826,7 +6015,7 @@
         <v>6.29</v>
       </c>
       <c r="AX35" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="AY35">
         <v>14.2</v>
@@ -5838,15 +6027,18 @@
         <v>6.3</v>
       </c>
       <c r="BB35" t="s">
-        <v>118</v>
+        <v>122</v>
+      </c>
+      <c r="BF35" t="s">
+        <v>123</v>
       </c>
     </row>
-    <row r="36" spans="1:54">
+    <row r="36" spans="1:58">
       <c r="A36" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B36" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C36">
         <v>890.71</v>
@@ -5858,7 +6050,7 @@
         <v>0.02</v>
       </c>
       <c r="F36" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="G36">
         <v>890.71</v>
@@ -5870,7 +6062,7 @@
         <v>0.02</v>
       </c>
       <c r="J36" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="K36">
         <v>890.71</v>
@@ -5882,7 +6074,7 @@
         <v>0.02</v>
       </c>
       <c r="N36" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="O36">
         <v>783.5700000000001</v>
@@ -5894,7 +6086,7 @@
         <v>0.02</v>
       </c>
       <c r="R36" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="S36">
         <v>789</v>
@@ -5906,7 +6098,7 @@
         <v>0.02</v>
       </c>
       <c r="V36" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="W36">
         <v>855</v>
@@ -5918,7 +6110,7 @@
         <v>0.02</v>
       </c>
       <c r="Z36" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="AA36">
         <v>855</v>
@@ -5930,7 +6122,7 @@
         <v>0.02</v>
       </c>
       <c r="AD36" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="AE36">
         <v>855</v>
@@ -5942,30 +6134,33 @@
         <v>0.02</v>
       </c>
       <c r="AH36" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="AL36" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="AP36" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="AT36" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="AX36" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="BB36" t="s">
-        <v>118</v>
+        <v>122</v>
+      </c>
+      <c r="BF36" t="s">
+        <v>123</v>
       </c>
     </row>
-    <row r="37" spans="1:54">
+    <row r="37" spans="1:58">
       <c r="A37" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B37" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C37">
         <v>249.71</v>
@@ -5977,7 +6172,7 @@
         <v>0.18</v>
       </c>
       <c r="F37" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="G37">
         <v>242.57</v>
@@ -5989,7 +6184,7 @@
         <v>0.18</v>
       </c>
       <c r="J37" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="K37">
         <v>228.14</v>
@@ -6001,7 +6196,7 @@
         <v>0.2</v>
       </c>
       <c r="N37" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="O37">
         <v>216.71</v>
@@ -6013,7 +6208,7 @@
         <v>0.21</v>
       </c>
       <c r="R37" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="S37">
         <v>234.17</v>
@@ -6025,7 +6220,7 @@
         <v>0.19</v>
       </c>
       <c r="V37" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="W37">
         <v>305.57</v>
@@ -6037,7 +6232,7 @@
         <v>0.12</v>
       </c>
       <c r="Z37" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="AA37">
         <v>314.43</v>
@@ -6049,7 +6244,7 @@
         <v>0.11</v>
       </c>
       <c r="AD37" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="AE37">
         <v>1569.29</v>
@@ -6061,7 +6256,7 @@
         <v>0.01</v>
       </c>
       <c r="AH37" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="AI37">
         <v>2539</v>
@@ -6073,27 +6268,30 @@
         <v>0</v>
       </c>
       <c r="AL37" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="AP37" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="AT37" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="AX37" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="BB37" t="s">
-        <v>118</v>
+        <v>122</v>
+      </c>
+      <c r="BF37" t="s">
+        <v>123</v>
       </c>
     </row>
-    <row r="38" spans="1:54">
+    <row r="38" spans="1:58">
       <c r="A38" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B38" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C38">
         <v>141.29</v>
@@ -6105,7 +6303,7 @@
         <v>0.43</v>
       </c>
       <c r="F38" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="G38">
         <v>145.57</v>
@@ -6117,7 +6315,7 @@
         <v>0.39</v>
       </c>
       <c r="J38" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="K38">
         <v>110.14</v>
@@ -6129,7 +6327,7 @@
         <v>0.59</v>
       </c>
       <c r="N38" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="O38">
         <v>105.86</v>
@@ -6141,7 +6339,7 @@
         <v>0.6</v>
       </c>
       <c r="R38" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="S38">
         <v>110</v>
@@ -6153,7 +6351,7 @@
         <v>0.59</v>
       </c>
       <c r="V38" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="W38">
         <v>171.86</v>
@@ -6165,7 +6363,7 @@
         <v>0.31</v>
       </c>
       <c r="Z38" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="AA38">
         <v>188.29</v>
@@ -6177,7 +6375,7 @@
         <v>0.26</v>
       </c>
       <c r="AD38" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="AE38">
         <v>205.43</v>
@@ -6189,7 +6387,7 @@
         <v>0.25</v>
       </c>
       <c r="AH38" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="AI38">
         <v>260.71</v>
@@ -6201,7 +6399,7 @@
         <v>0.16</v>
       </c>
       <c r="AL38" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="AM38">
         <v>229.71</v>
@@ -6213,24 +6411,27 @@
         <v>0.12</v>
       </c>
       <c r="AP38" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="AT38" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="AX38" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="BB38" t="s">
-        <v>118</v>
+        <v>122</v>
+      </c>
+      <c r="BF38" t="s">
+        <v>123</v>
       </c>
     </row>
-    <row r="39" spans="1:54">
+    <row r="39" spans="1:58">
       <c r="A39" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B39" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C39">
         <v>101.29</v>
@@ -6242,7 +6443,7 @@
         <v>0.67</v>
       </c>
       <c r="F39" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="G39">
         <v>106.14</v>
@@ -6254,7 +6455,7 @@
         <v>0.61</v>
       </c>
       <c r="J39" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="K39">
         <v>107.57</v>
@@ -6266,7 +6467,7 @@
         <v>0.61</v>
       </c>
       <c r="N39" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="O39">
         <v>119.57</v>
@@ -6278,7 +6479,7 @@
         <v>0.51</v>
       </c>
       <c r="R39" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="S39">
         <v>115.17</v>
@@ -6290,7 +6491,7 @@
         <v>0.55</v>
       </c>
       <c r="V39" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="W39">
         <v>125.86</v>
@@ -6302,7 +6503,7 @@
         <v>0.48</v>
       </c>
       <c r="Z39" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="AA39">
         <v>153.57</v>
@@ -6314,7 +6515,7 @@
         <v>0.36</v>
       </c>
       <c r="AD39" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="AE39">
         <v>165.71</v>
@@ -6326,7 +6527,7 @@
         <v>0.34</v>
       </c>
       <c r="AH39" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="AI39">
         <v>120.29</v>
@@ -6338,7 +6539,7 @@
         <v>0.51</v>
       </c>
       <c r="AL39" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="AM39">
         <v>121.71</v>
@@ -6350,24 +6551,27 @@
         <v>0.36</v>
       </c>
       <c r="AP39" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="AT39" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="AX39" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="BB39" t="s">
-        <v>118</v>
+        <v>122</v>
+      </c>
+      <c r="BF39" t="s">
+        <v>123</v>
       </c>
     </row>
-    <row r="40" spans="1:54">
+    <row r="40" spans="1:58">
       <c r="A40" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B40" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C40">
         <v>890.71</v>
@@ -6379,7 +6583,7 @@
         <v>0.02</v>
       </c>
       <c r="F40" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="G40">
         <v>1176.43</v>
@@ -6391,7 +6595,7 @@
         <v>0.01</v>
       </c>
       <c r="J40" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="K40">
         <v>1176.43</v>
@@ -6403,7 +6607,7 @@
         <v>0.01</v>
       </c>
       <c r="N40" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="O40">
         <v>1176.43</v>
@@ -6415,7 +6619,7 @@
         <v>0.01</v>
       </c>
       <c r="R40" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="S40">
         <v>1205.67</v>
@@ -6427,7 +6631,7 @@
         <v>0.01</v>
       </c>
       <c r="V40" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="W40">
         <v>1247.86</v>
@@ -6439,7 +6643,7 @@
         <v>0.01</v>
       </c>
       <c r="Z40" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="AA40">
         <v>1247.86</v>
@@ -6451,7 +6655,7 @@
         <v>0.01</v>
       </c>
       <c r="AD40" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="AE40">
         <v>569.29</v>
@@ -6463,7 +6667,7 @@
         <v>0.04</v>
       </c>
       <c r="AH40" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="AI40">
         <v>630</v>
@@ -6475,27 +6679,30 @@
         <v>0.03</v>
       </c>
       <c r="AL40" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="AP40" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="AT40" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="AX40" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="BB40" t="s">
-        <v>118</v>
+        <v>122</v>
+      </c>
+      <c r="BF40" t="s">
+        <v>123</v>
       </c>
     </row>
-    <row r="41" spans="1:54">
+    <row r="41" spans="1:58">
       <c r="A41" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B41" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C41">
         <v>376.29</v>
@@ -6507,7 +6714,7 @@
         <v>0.09</v>
       </c>
       <c r="F41" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="G41">
         <v>241</v>
@@ -6519,7 +6726,7 @@
         <v>0.18</v>
       </c>
       <c r="J41" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="K41">
         <v>224.29</v>
@@ -6531,7 +6738,7 @@
         <v>0.21</v>
       </c>
       <c r="N41" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="O41">
         <v>234</v>
@@ -6543,7 +6750,7 @@
         <v>0.18</v>
       </c>
       <c r="R41" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="S41">
         <v>256.33</v>
@@ -6555,7 +6762,7 @@
         <v>0.17</v>
       </c>
       <c r="V41" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="W41">
         <v>293.57</v>
@@ -6567,7 +6774,7 @@
         <v>0.13</v>
       </c>
       <c r="Z41" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="AA41">
         <v>288</v>
@@ -6579,7 +6786,7 @@
         <v>0.13</v>
       </c>
       <c r="AD41" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="AE41">
         <v>570</v>
@@ -6591,7 +6798,7 @@
         <v>0.04</v>
       </c>
       <c r="AH41" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="AI41">
         <v>964</v>
@@ -6603,27 +6810,30 @@
         <v>0.01</v>
       </c>
       <c r="AL41" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="AP41" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="AT41" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="AX41" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="BB41" t="s">
-        <v>118</v>
+        <v>122</v>
+      </c>
+      <c r="BF41" t="s">
+        <v>123</v>
       </c>
     </row>
-    <row r="42" spans="1:54">
+    <row r="42" spans="1:58">
       <c r="A42" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B42" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C42">
         <v>299.29</v>
@@ -6635,7 +6845,7 @@
         <v>0.14</v>
       </c>
       <c r="F42" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="G42">
         <v>497.86</v>
@@ -6647,7 +6857,7 @@
         <v>0.05</v>
       </c>
       <c r="J42" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="K42">
         <v>486.71</v>
@@ -6659,7 +6869,7 @@
         <v>0.06</v>
       </c>
       <c r="N42" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="O42">
         <v>497.86</v>
@@ -6671,7 +6881,7 @@
         <v>0.05</v>
       </c>
       <c r="R42" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="S42">
         <v>572.33</v>
@@ -6683,7 +6893,7 @@
         <v>0.04</v>
       </c>
       <c r="V42" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="W42">
         <v>547.86</v>
@@ -6695,7 +6905,7 @@
         <v>0.04</v>
       </c>
       <c r="Z42" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="AA42">
         <v>583.5700000000001</v>
@@ -6707,33 +6917,36 @@
         <v>0.04</v>
       </c>
       <c r="AD42" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="AH42" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="AL42" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="AP42" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="AT42" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="AX42" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="BB42" t="s">
-        <v>118</v>
+        <v>122</v>
+      </c>
+      <c r="BF42" t="s">
+        <v>123</v>
       </c>
     </row>
-    <row r="43" spans="1:54">
+    <row r="43" spans="1:58">
       <c r="A43" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B43" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C43">
         <v>605</v>
@@ -6745,7 +6958,7 @@
         <v>0.04</v>
       </c>
       <c r="F43" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="G43">
         <v>640.71</v>
@@ -6757,7 +6970,7 @@
         <v>0.03</v>
       </c>
       <c r="J43" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="K43">
         <v>890.71</v>
@@ -6769,7 +6982,7 @@
         <v>0.02</v>
       </c>
       <c r="N43" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="O43">
         <v>926.4299999999999</v>
@@ -6781,7 +6994,7 @@
         <v>0.01</v>
       </c>
       <c r="R43" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="S43">
         <v>955.67</v>
@@ -6793,39 +7006,42 @@
         <v>0.01</v>
       </c>
       <c r="V43" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="Z43" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="AD43" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="AH43" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="AL43" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="AP43" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="AT43" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="AX43" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="BB43" t="s">
-        <v>118</v>
+        <v>122</v>
+      </c>
+      <c r="BF43" t="s">
+        <v>123</v>
       </c>
     </row>
-    <row r="44" spans="1:54">
+    <row r="44" spans="1:58">
       <c r="A44" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B44" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C44">
         <v>80</v>
@@ -6837,7 +7053,7 @@
         <v>0.91</v>
       </c>
       <c r="F44" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="G44">
         <v>80</v>
@@ -6849,7 +7065,7 @@
         <v>0.88</v>
       </c>
       <c r="J44" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="K44">
         <v>133.14</v>
@@ -6861,7 +7077,7 @@
         <v>0.46</v>
       </c>
       <c r="N44" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="O44">
         <v>145.86</v>
@@ -6873,7 +7089,7 @@
         <v>0.38</v>
       </c>
       <c r="R44" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="S44">
         <v>152.33</v>
@@ -6885,39 +7101,42 @@
         <v>0.37</v>
       </c>
       <c r="V44" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="Z44" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="AD44" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="AH44" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="AL44" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="AP44" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="AT44" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="AX44" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="BB44" t="s">
-        <v>118</v>
+        <v>122</v>
+      </c>
+      <c r="BF44" t="s">
+        <v>123</v>
       </c>
     </row>
-    <row r="45" spans="1:54">
+    <row r="45" spans="1:58">
       <c r="A45" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B45" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C45">
         <v>63.71</v>
@@ -6929,7 +7148,7 @@
         <v>1.2</v>
       </c>
       <c r="F45" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="G45">
         <v>44.57</v>
@@ -6941,7 +7160,7 @@
         <v>1.78</v>
       </c>
       <c r="J45" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="K45">
         <v>43.86</v>
@@ -6953,7 +7172,7 @@
         <v>1.82</v>
       </c>
       <c r="N45" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="O45">
         <v>41.14</v>
@@ -6965,7 +7184,7 @@
         <v>1.93</v>
       </c>
       <c r="R45" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="S45">
         <v>42</v>
@@ -6977,7 +7196,7 @@
         <v>1.91</v>
       </c>
       <c r="V45" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="W45">
         <v>31.43</v>
@@ -6989,7 +7208,7 @@
         <v>2.63</v>
       </c>
       <c r="Z45" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="AA45">
         <v>32.14</v>
@@ -7001,7 +7220,7 @@
         <v>2.56</v>
       </c>
       <c r="AD45" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="AE45">
         <v>28.29</v>
@@ -7013,7 +7232,7 @@
         <v>3.01</v>
       </c>
       <c r="AH45" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="AI45">
         <v>31</v>
@@ -7025,7 +7244,7 @@
         <v>2.68</v>
       </c>
       <c r="AL45" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="AM45">
         <v>32.57</v>
@@ -7037,7 +7256,7 @@
         <v>2.25</v>
       </c>
       <c r="AP45" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="AQ45">
         <v>29.17</v>
@@ -7049,7 +7268,7 @@
         <v>2.8</v>
       </c>
       <c r="AT45" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="AU45">
         <v>29.83</v>
@@ -7061,7 +7280,7 @@
         <v>2.7</v>
       </c>
       <c r="AX45" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="AY45">
         <v>28.83</v>
@@ -7073,15 +7292,18 @@
         <v>2.89</v>
       </c>
       <c r="BB45" t="s">
-        <v>118</v>
+        <v>122</v>
+      </c>
+      <c r="BF45" t="s">
+        <v>123</v>
       </c>
     </row>
-    <row r="46" spans="1:54">
+    <row r="46" spans="1:58">
       <c r="A46" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B46" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C46">
         <v>71.14</v>
@@ -7093,7 +7315,7 @@
         <v>1.05</v>
       </c>
       <c r="F46" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="G46">
         <v>75.29000000000001</v>
@@ -7105,7 +7327,7 @@
         <v>0.95</v>
       </c>
       <c r="J46" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="K46">
         <v>75.29000000000001</v>
@@ -7117,7 +7339,7 @@
         <v>0.96</v>
       </c>
       <c r="N46" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="O46">
         <v>83</v>
@@ -7129,7 +7351,7 @@
         <v>0.83</v>
       </c>
       <c r="R46" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="S46">
         <v>88.83</v>
@@ -7141,7 +7363,7 @@
         <v>0.78</v>
       </c>
       <c r="V46" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="W46">
         <v>162.86</v>
@@ -7153,7 +7375,7 @@
         <v>0.33</v>
       </c>
       <c r="Z46" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="AA46">
         <v>190</v>
@@ -7165,7 +7387,7 @@
         <v>0.26</v>
       </c>
       <c r="AD46" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="AE46">
         <v>216.57</v>
@@ -7177,30 +7399,33 @@
         <v>0.23</v>
       </c>
       <c r="AH46" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="AL46" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="AP46" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="AT46" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="AX46" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="BB46" t="s">
-        <v>118</v>
+        <v>122</v>
+      </c>
+      <c r="BF46" t="s">
+        <v>123</v>
       </c>
     </row>
-    <row r="47" spans="1:54">
+    <row r="47" spans="1:58">
       <c r="A47" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B47" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C47">
         <v>1197.86</v>
@@ -7212,7 +7437,7 @@
         <v>0.01</v>
       </c>
       <c r="F47" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="G47">
         <v>1197.86</v>
@@ -7224,7 +7449,7 @@
         <v>0.01</v>
       </c>
       <c r="J47" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="K47">
         <v>1197.86</v>
@@ -7236,7 +7461,7 @@
         <v>0.01</v>
       </c>
       <c r="N47" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="O47">
         <v>1197.86</v>
@@ -7248,7 +7473,7 @@
         <v>0.01</v>
       </c>
       <c r="R47" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="S47">
         <v>1296.6</v>
@@ -7260,7 +7485,7 @@
         <v>0.01</v>
       </c>
       <c r="V47" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="W47">
         <v>1247.33</v>
@@ -7272,7 +7497,7 @@
         <v>0.01</v>
       </c>
       <c r="Z47" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="AA47">
         <v>1212.14</v>
@@ -7284,7 +7509,7 @@
         <v>0.01</v>
       </c>
       <c r="AD47" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="AE47">
         <v>1355</v>
@@ -7296,7 +7521,7 @@
         <v>0.01</v>
       </c>
       <c r="AH47" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="AI47">
         <v>2330.67</v>
@@ -7308,27 +7533,30 @@
         <v>0</v>
       </c>
       <c r="AL47" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="AP47" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="AT47" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="AX47" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="BB47" t="s">
-        <v>118</v>
+        <v>122</v>
+      </c>
+      <c r="BF47" t="s">
+        <v>123</v>
       </c>
     </row>
-    <row r="48" spans="1:54">
+    <row r="48" spans="1:58">
       <c r="A48" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B48" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C48">
         <v>320.43</v>
@@ -7340,7 +7568,7 @@
         <v>0.12</v>
       </c>
       <c r="F48" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="G48">
         <v>351.57</v>
@@ -7352,7 +7580,7 @@
         <v>0.1</v>
       </c>
       <c r="J48" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="K48">
         <v>341.71</v>
@@ -7364,7 +7592,7 @@
         <v>0.1</v>
       </c>
       <c r="N48" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="O48">
         <v>283.71</v>
@@ -7376,7 +7604,7 @@
         <v>0.13</v>
       </c>
       <c r="R48" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="S48">
         <v>302.5</v>
@@ -7388,7 +7616,7 @@
         <v>0.13</v>
       </c>
       <c r="V48" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="W48">
         <v>261.14</v>
@@ -7400,7 +7628,7 @@
         <v>0.16</v>
       </c>
       <c r="Z48" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="AA48">
         <v>232.57</v>
@@ -7412,7 +7640,7 @@
         <v>0.19</v>
       </c>
       <c r="AD48" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="AE48">
         <v>260.71</v>
@@ -7424,7 +7652,7 @@
         <v>0.17</v>
       </c>
       <c r="AH48" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="AI48">
         <v>273.57</v>
@@ -7436,7 +7664,7 @@
         <v>0.14</v>
       </c>
       <c r="AL48" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="AM48">
         <v>287.86</v>
@@ -7448,7 +7676,7 @@
         <v>0.08</v>
       </c>
       <c r="AP48" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="AQ48">
         <v>300.5</v>
@@ -7460,7 +7688,7 @@
         <v>0.1</v>
       </c>
       <c r="AT48" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="AU48">
         <v>272.33</v>
@@ -7472,7 +7700,7 @@
         <v>0.11</v>
       </c>
       <c r="AX48" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="AY48">
         <v>257.83</v>
@@ -7484,15 +7712,18 @@
         <v>0.13</v>
       </c>
       <c r="BB48" t="s">
-        <v>118</v>
+        <v>122</v>
+      </c>
+      <c r="BF48" t="s">
+        <v>123</v>
       </c>
     </row>
-    <row r="49" spans="1:54">
+    <row r="49" spans="1:58">
       <c r="A49" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B49" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C49">
         <v>153</v>
@@ -7504,7 +7735,7 @@
         <v>0.39</v>
       </c>
       <c r="F49" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="G49">
         <v>158.57</v>
@@ -7516,7 +7747,7 @@
         <v>0.35</v>
       </c>
       <c r="J49" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="K49">
         <v>157.14</v>
@@ -7528,7 +7759,7 @@
         <v>0.36</v>
       </c>
       <c r="N49" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="O49">
         <v>135.14</v>
@@ -7540,7 +7771,7 @@
         <v>0.43</v>
       </c>
       <c r="R49" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="S49">
         <v>144</v>
@@ -7552,7 +7783,7 @@
         <v>0.4</v>
       </c>
       <c r="V49" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="W49">
         <v>139.29</v>
@@ -7564,7 +7795,7 @@
         <v>0.42</v>
       </c>
       <c r="Z49" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="AA49">
         <v>187.29</v>
@@ -7576,7 +7807,7 @@
         <v>0.26</v>
       </c>
       <c r="AD49" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="AE49">
         <v>181.14</v>
@@ -7588,7 +7819,7 @@
         <v>0.3</v>
       </c>
       <c r="AH49" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="AI49">
         <v>272.29</v>
@@ -7600,7 +7831,7 @@
         <v>0.14</v>
       </c>
       <c r="AL49" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="AM49">
         <v>284.86</v>
@@ -7612,7 +7843,7 @@
         <v>0.08</v>
       </c>
       <c r="AP49" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="AQ49">
         <v>333.67</v>
@@ -7624,13 +7855,16 @@
         <v>0.08</v>
       </c>
       <c r="AT49" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="AX49" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="BB49" t="s">
-        <v>118</v>
+        <v>122</v>
+      </c>
+      <c r="BF49" t="s">
+        <v>123</v>
       </c>
     </row>
   </sheetData>

--- a/processed_data_during_wm/processed_data_wide.xlsx
+++ b/processed_data_during_wm/processed_data_wide.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="881" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="933" uniqueCount="134">
   <si>
     <t>Team</t>
   </si>
@@ -211,6 +211,18 @@
     <t>Shin_Wahrscheinlichkeit_in_Prozent_16</t>
   </si>
   <si>
+    <t>Datum_17</t>
+  </si>
+  <si>
+    <t>Durchsch_Quote_17</t>
+  </si>
+  <si>
+    <t>Norm_Wahrscheinlichkeit_in_Prozent_17</t>
+  </si>
+  <si>
+    <t>Shin_Wahrscheinlichkeit_in_Prozent_17</t>
+  </si>
+  <si>
     <t>Frankreich</t>
   </si>
   <si>
@@ -401,6 +413,9 @@
   </si>
   <si>
     <t>12.07.2026</t>
+  </si>
+  <si>
+    <t>14.07.2026</t>
   </si>
 </sst>
 </file>
@@ -758,10 +773,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BM49"/>
+  <dimension ref="A1:BQ49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:65">
+    <row r="1" spans="1:69">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -957,13 +972,25 @@
       <c r="BM1" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="BN1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="BO1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="BP1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="BQ1" s="1" t="s">
+        <v>68</v>
+      </c>
     </row>
-    <row r="2" spans="1:65">
+    <row r="2" spans="1:69">
       <c r="A2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C2">
         <v>6.01</v>
@@ -975,7 +1002,7 @@
         <v>15.09</v>
       </c>
       <c r="F2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G2">
         <v>5.55</v>
@@ -987,7 +1014,7 @@
         <v>16.26</v>
       </c>
       <c r="J2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="K2">
         <v>5.55</v>
@@ -999,7 +1026,7 @@
         <v>16.3</v>
       </c>
       <c r="N2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="O2">
         <v>4.97</v>
@@ -1011,7 +1038,7 @@
         <v>18.14</v>
       </c>
       <c r="R2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="S2">
         <v>4.82</v>
@@ -1023,7 +1050,7 @@
         <v>18.8</v>
       </c>
       <c r="V2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="W2">
         <v>4.87</v>
@@ -1035,7 +1062,7 @@
         <v>18.6</v>
       </c>
       <c r="Z2" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="AA2">
         <v>4.87</v>
@@ -1047,7 +1074,7 @@
         <v>18.58</v>
       </c>
       <c r="AD2" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AE2">
         <v>4.96</v>
@@ -1059,7 +1086,7 @@
         <v>18.46</v>
       </c>
       <c r="AH2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AI2">
         <v>4.34</v>
@@ -1071,7 +1098,7 @@
         <v>21.1</v>
       </c>
       <c r="AL2" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AM2">
         <v>3.62</v>
@@ -1083,7 +1110,7 @@
         <v>24.41</v>
       </c>
       <c r="AP2" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AQ2">
         <v>2.86</v>
@@ -1095,7 +1122,7 @@
         <v>32.47</v>
       </c>
       <c r="AT2" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AU2">
         <v>2.88</v>
@@ -1107,7 +1134,7 @@
         <v>32.36</v>
       </c>
       <c r="AX2" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="AY2">
         <v>2.79</v>
@@ -1119,7 +1146,7 @@
         <v>33.86</v>
       </c>
       <c r="BB2" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="BC2">
         <v>2.88</v>
@@ -1131,7 +1158,7 @@
         <v>33.08</v>
       </c>
       <c r="BF2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="BG2">
         <v>2.49</v>
@@ -1143,7 +1170,7 @@
         <v>38.47</v>
       </c>
       <c r="BJ2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="BK2">
         <v>2.51</v>
@@ -1154,13 +1181,25 @@
       <c r="BM2">
         <v>38.25</v>
       </c>
+      <c r="BN2" t="s">
+        <v>133</v>
+      </c>
+      <c r="BO2">
+        <v>2.43</v>
+      </c>
+      <c r="BP2">
+        <v>38.93</v>
+      </c>
+      <c r="BQ2">
+        <v>39.45</v>
+      </c>
     </row>
-    <row r="3" spans="1:65">
+    <row r="3" spans="1:69">
       <c r="A3" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B3" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C3">
         <v>5.58</v>
@@ -1172,7 +1211,7 @@
         <v>16.29</v>
       </c>
       <c r="F3" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G3">
         <v>5.63</v>
@@ -1184,7 +1223,7 @@
         <v>16.04</v>
       </c>
       <c r="J3" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="K3">
         <v>5.63</v>
@@ -1196,7 +1235,7 @@
         <v>16.07</v>
       </c>
       <c r="N3" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="O3">
         <v>6.51</v>
@@ -1208,7 +1247,7 @@
         <v>13.76</v>
       </c>
       <c r="R3" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="S3">
         <v>6.88</v>
@@ -1220,7 +1259,7 @@
         <v>13.09</v>
       </c>
       <c r="V3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="W3">
         <v>6.34</v>
@@ -1232,7 +1271,7 @@
         <v>14.23</v>
       </c>
       <c r="Z3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="AA3">
         <v>6.48</v>
@@ -1244,7 +1283,7 @@
         <v>13.89</v>
       </c>
       <c r="AD3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AE3">
         <v>6.63</v>
@@ -1256,7 +1295,7 @@
         <v>13.74</v>
       </c>
       <c r="AH3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AI3">
         <v>8.02</v>
@@ -1268,7 +1307,7 @@
         <v>11.26</v>
       </c>
       <c r="AL3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AM3">
         <v>8.140000000000001</v>
@@ -1280,7 +1319,7 @@
         <v>10.55</v>
       </c>
       <c r="AP3" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AQ3">
         <v>8.59</v>
@@ -1292,7 +1331,7 @@
         <v>10.5</v>
       </c>
       <c r="AT3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AU3">
         <v>7.04</v>
@@ -1304,7 +1343,7 @@
         <v>12.93</v>
       </c>
       <c r="AX3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="AY3">
         <v>6.98</v>
@@ -1316,7 +1355,7 @@
         <v>13.27</v>
       </c>
       <c r="BB3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="BC3">
         <v>4.75</v>
@@ -1328,7 +1367,7 @@
         <v>19.84</v>
       </c>
       <c r="BF3" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="BG3">
         <v>5.25</v>
@@ -1340,7 +1379,7 @@
         <v>17.91</v>
       </c>
       <c r="BJ3" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="BK3">
         <v>4.36</v>
@@ -1351,13 +1390,25 @@
       <c r="BM3">
         <v>21.61</v>
       </c>
+      <c r="BN3" t="s">
+        <v>133</v>
+      </c>
+      <c r="BO3">
+        <v>4.33</v>
+      </c>
+      <c r="BP3">
+        <v>21.87</v>
+      </c>
+      <c r="BQ3">
+        <v>21.75</v>
+      </c>
     </row>
-    <row r="4" spans="1:65">
+    <row r="4" spans="1:69">
       <c r="A4" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B4" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C4">
         <v>8.15</v>
@@ -1369,7 +1420,7 @@
         <v>11.06</v>
       </c>
       <c r="F4" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G4">
         <v>8.42</v>
@@ -1381,7 +1432,7 @@
         <v>10.62</v>
       </c>
       <c r="J4" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="K4">
         <v>8.390000000000001</v>
@@ -1393,7 +1444,7 @@
         <v>10.69</v>
       </c>
       <c r="N4" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="O4">
         <v>8.33</v>
@@ -1405,7 +1456,7 @@
         <v>10.68</v>
       </c>
       <c r="R4" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="S4">
         <v>7.04</v>
@@ -1417,7 +1468,7 @@
         <v>12.77</v>
       </c>
       <c r="V4" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="W4">
         <v>7.11</v>
@@ -1429,7 +1480,7 @@
         <v>12.65</v>
       </c>
       <c r="Z4" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="AA4">
         <v>7.61</v>
@@ -1441,7 +1492,7 @@
         <v>11.79</v>
       </c>
       <c r="AD4" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AE4">
         <v>8.43</v>
@@ -1453,7 +1504,7 @@
         <v>10.74</v>
       </c>
       <c r="AH4" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AI4">
         <v>8.19</v>
@@ -1465,7 +1516,7 @@
         <v>11.02</v>
       </c>
       <c r="AL4" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AM4">
         <v>8.220000000000001</v>
@@ -1477,7 +1528,7 @@
         <v>10.43</v>
       </c>
       <c r="AP4" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AQ4">
         <v>9.800000000000001</v>
@@ -1489,7 +1540,7 @@
         <v>9.15</v>
       </c>
       <c r="AT4" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AU4">
         <v>11.05</v>
@@ -1501,7 +1552,7 @@
         <v>8.07</v>
       </c>
       <c r="AX4" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="AY4">
         <v>7.4</v>
@@ -1513,7 +1564,7 @@
         <v>12.49</v>
       </c>
       <c r="BB4" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="BC4">
         <v>5.89</v>
@@ -1525,7 +1576,7 @@
         <v>15.9</v>
       </c>
       <c r="BF4" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="BG4">
         <v>5.73</v>
@@ -1537,7 +1588,7 @@
         <v>16.36</v>
       </c>
       <c r="BJ4" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="BK4">
         <v>4.43</v>
@@ -1548,13 +1599,25 @@
       <c r="BM4">
         <v>21.25</v>
       </c>
+      <c r="BN4" t="s">
+        <v>133</v>
+      </c>
+      <c r="BO4">
+        <v>4.36</v>
+      </c>
+      <c r="BP4">
+        <v>21.7</v>
+      </c>
+      <c r="BQ4">
+        <v>21.58</v>
+      </c>
     </row>
-    <row r="5" spans="1:65">
+    <row r="5" spans="1:69">
       <c r="A5" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B5" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C5">
         <v>10.19</v>
@@ -1566,7 +1629,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="F5" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G5">
         <v>10.33</v>
@@ -1578,7 +1641,7 @@
         <v>8.6</v>
       </c>
       <c r="J5" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="K5">
         <v>10.61</v>
@@ -1590,7 +1653,7 @@
         <v>8.390000000000001</v>
       </c>
       <c r="N5" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="O5">
         <v>9.4</v>
@@ -1602,7 +1665,7 @@
         <v>9.44</v>
       </c>
       <c r="R5" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="S5">
         <v>9.140000000000001</v>
@@ -1614,7 +1677,7 @@
         <v>9.779999999999999</v>
       </c>
       <c r="V5" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="W5">
         <v>8.710000000000001</v>
@@ -1626,7 +1689,7 @@
         <v>10.27</v>
       </c>
       <c r="Z5" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="AA5">
         <v>7.45</v>
@@ -1638,7 +1701,7 @@
         <v>12.04</v>
       </c>
       <c r="AD5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AE5">
         <v>7.04</v>
@@ -1650,7 +1713,7 @@
         <v>12.92</v>
       </c>
       <c r="AH5" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AI5">
         <v>5.2</v>
@@ -1662,7 +1725,7 @@
         <v>17.53</v>
       </c>
       <c r="AL5" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AM5">
         <v>4.84</v>
@@ -1674,7 +1737,7 @@
         <v>18.12</v>
       </c>
       <c r="AP5" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AQ5">
         <v>5.11</v>
@@ -1686,7 +1749,7 @@
         <v>17.95</v>
       </c>
       <c r="AT5" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AU5">
         <v>5.31</v>
@@ -1698,7 +1761,7 @@
         <v>17.31</v>
       </c>
       <c r="AX5" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="AY5">
         <v>5.53</v>
@@ -1710,7 +1773,7 @@
         <v>16.85</v>
       </c>
       <c r="BB5" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="BC5">
         <v>5.05</v>
@@ -1722,7 +1785,7 @@
         <v>18.63</v>
       </c>
       <c r="BF5" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="BG5">
         <v>5.34</v>
@@ -1734,7 +1797,7 @@
         <v>17.62</v>
       </c>
       <c r="BJ5" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="BK5">
         <v>4.96</v>
@@ -1745,13 +1808,25 @@
       <c r="BM5">
         <v>18.89</v>
       </c>
+      <c r="BN5" t="s">
+        <v>133</v>
+      </c>
+      <c r="BO5">
+        <v>5.41</v>
+      </c>
+      <c r="BP5">
+        <v>17.5</v>
+      </c>
+      <c r="BQ5">
+        <v>17.22</v>
+      </c>
     </row>
-    <row r="6" spans="1:65">
+    <row r="6" spans="1:69">
       <c r="A6" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B6" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C6">
         <v>367.57</v>
@@ -1763,7 +1838,7 @@
         <v>0.1</v>
       </c>
       <c r="F6" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G6">
         <v>383</v>
@@ -1775,7 +1850,7 @@
         <v>0.08</v>
       </c>
       <c r="J6" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="K6">
         <v>378.86</v>
@@ -1787,7 +1862,7 @@
         <v>0.09</v>
       </c>
       <c r="N6" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="O6">
         <v>474.57</v>
@@ -1799,7 +1874,7 @@
         <v>0.05</v>
       </c>
       <c r="R6" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="S6">
         <v>530.67</v>
@@ -1811,7 +1886,7 @@
         <v>0.05</v>
       </c>
       <c r="V6" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="W6">
         <v>518</v>
@@ -1823,7 +1898,7 @@
         <v>0.05</v>
       </c>
       <c r="Z6" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="AA6">
         <v>529.5700000000001</v>
@@ -1835,7 +1910,7 @@
         <v>0.04</v>
       </c>
       <c r="AD6" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AE6">
         <v>576.4299999999999</v>
@@ -1847,7 +1922,7 @@
         <v>0.04</v>
       </c>
       <c r="AH6" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AI6">
         <v>458.71</v>
@@ -1859,7 +1934,7 @@
         <v>0.06</v>
       </c>
       <c r="AL6" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AM6">
         <v>391.29</v>
@@ -1871,7 +1946,7 @@
         <v>0.04</v>
       </c>
       <c r="AP6" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AQ6">
         <v>437.83</v>
@@ -1883,27 +1958,30 @@
         <v>0.05</v>
       </c>
       <c r="AT6" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AX6" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="BB6" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="BF6" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="BJ6" t="s">
-        <v>128</v>
+        <v>132</v>
+      </c>
+      <c r="BN6" t="s">
+        <v>133</v>
       </c>
     </row>
-    <row r="7" spans="1:65">
+    <row r="7" spans="1:69">
       <c r="A7" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B7" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C7">
         <v>442.71</v>
@@ -1915,7 +1993,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="F7" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G7">
         <v>462.29</v>
@@ -1927,7 +2005,7 @@
         <v>0.06</v>
       </c>
       <c r="J7" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="K7">
         <v>186</v>
@@ -1939,7 +2017,7 @@
         <v>0.28</v>
       </c>
       <c r="N7" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="O7">
         <v>123.14</v>
@@ -1951,7 +2029,7 @@
         <v>0.49</v>
       </c>
       <c r="R7" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="S7">
         <v>128.5</v>
@@ -1963,7 +2041,7 @@
         <v>0.47</v>
       </c>
       <c r="V7" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="W7">
         <v>174.43</v>
@@ -1975,7 +2053,7 @@
         <v>0.3</v>
       </c>
       <c r="Z7" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="AA7">
         <v>206.33</v>
@@ -1987,7 +2065,7 @@
         <v>0.23</v>
       </c>
       <c r="AD7" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AE7">
         <v>199.83</v>
@@ -1999,7 +2077,7 @@
         <v>0.26</v>
       </c>
       <c r="AH7" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AI7">
         <v>249.14</v>
@@ -2011,7 +2089,7 @@
         <v>0.17</v>
       </c>
       <c r="AL7" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AM7">
         <v>290.57</v>
@@ -2023,7 +2101,7 @@
         <v>0.08</v>
       </c>
       <c r="AP7" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AQ7">
         <v>333.67</v>
@@ -2035,27 +2113,30 @@
         <v>0.08</v>
       </c>
       <c r="AT7" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AX7" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="BB7" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="BF7" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="BJ7" t="s">
-        <v>128</v>
+        <v>132</v>
+      </c>
+      <c r="BN7" t="s">
+        <v>133</v>
       </c>
     </row>
-    <row r="8" spans="1:65">
+    <row r="8" spans="1:69">
       <c r="A8" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B8" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C8">
         <v>37.71</v>
@@ -2067,7 +2148,7 @@
         <v>2.19</v>
       </c>
       <c r="F8" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G8">
         <v>37.71</v>
@@ -2079,7 +2160,7 @@
         <v>2.15</v>
       </c>
       <c r="J8" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="K8">
         <v>39.43</v>
@@ -2091,7 +2172,7 @@
         <v>2.06</v>
       </c>
       <c r="N8" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="O8">
         <v>42</v>
@@ -2103,7 +2184,7 @@
         <v>1.88</v>
       </c>
       <c r="R8" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="S8">
         <v>42.17</v>
@@ -2115,7 +2196,7 @@
         <v>1.9</v>
       </c>
       <c r="V8" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="W8">
         <v>47.71</v>
@@ -2127,7 +2208,7 @@
         <v>1.64</v>
       </c>
       <c r="Z8" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="AA8">
         <v>52.71</v>
@@ -2139,7 +2220,7 @@
         <v>1.45</v>
       </c>
       <c r="AD8" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AE8">
         <v>54.14</v>
@@ -2151,7 +2232,7 @@
         <v>1.45</v>
       </c>
       <c r="AH8" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AI8">
         <v>49.14</v>
@@ -2163,7 +2244,7 @@
         <v>1.59</v>
       </c>
       <c r="AL8" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AM8">
         <v>52</v>
@@ -2175,7 +2256,7 @@
         <v>1.25</v>
       </c>
       <c r="AP8" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AQ8">
         <v>41.83</v>
@@ -2187,7 +2268,7 @@
         <v>1.84</v>
       </c>
       <c r="AT8" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AU8">
         <v>48.5</v>
@@ -2199,7 +2280,7 @@
         <v>1.51</v>
       </c>
       <c r="AX8" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="AY8">
         <v>49.33</v>
@@ -2211,7 +2292,7 @@
         <v>1.54</v>
       </c>
       <c r="BB8" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="BC8">
         <v>32</v>
@@ -2223,7 +2304,7 @@
         <v>2.51</v>
       </c>
       <c r="BF8" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="BG8">
         <v>35.17</v>
@@ -2235,15 +2316,18 @@
         <v>2.22</v>
       </c>
       <c r="BJ8" t="s">
-        <v>128</v>
+        <v>132</v>
+      </c>
+      <c r="BN8" t="s">
+        <v>133</v>
       </c>
     </row>
-    <row r="9" spans="1:65">
+    <row r="9" spans="1:69">
       <c r="A9" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B9" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C9">
         <v>370.43</v>
@@ -2255,7 +2339,7 @@
         <v>0.1</v>
       </c>
       <c r="F9" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G9">
         <v>376.71</v>
@@ -2267,7 +2351,7 @@
         <v>0.08</v>
       </c>
       <c r="J9" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="K9">
         <v>383.71</v>
@@ -2279,7 +2363,7 @@
         <v>0.08</v>
       </c>
       <c r="N9" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="O9">
         <v>390.71</v>
@@ -2291,7 +2375,7 @@
         <v>0.08</v>
       </c>
       <c r="R9" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="S9">
         <v>473</v>
@@ -2303,7 +2387,7 @@
         <v>0.06</v>
       </c>
       <c r="V9" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="W9">
         <v>514</v>
@@ -2315,7 +2399,7 @@
         <v>0.05</v>
       </c>
       <c r="Z9" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="AA9">
         <v>547.86</v>
@@ -2327,7 +2411,7 @@
         <v>0.04</v>
       </c>
       <c r="AD9" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AE9">
         <v>509.43</v>
@@ -2339,7 +2423,7 @@
         <v>0.05</v>
       </c>
       <c r="AH9" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AI9">
         <v>503.71</v>
@@ -2351,7 +2435,7 @@
         <v>0.05</v>
       </c>
       <c r="AL9" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AM9">
         <v>576.4299999999999</v>
@@ -2363,30 +2447,33 @@
         <v>0.02</v>
       </c>
       <c r="AP9" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AT9" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AX9" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="BB9" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="BF9" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="BJ9" t="s">
-        <v>128</v>
+        <v>132</v>
+      </c>
+      <c r="BN9" t="s">
+        <v>133</v>
       </c>
     </row>
-    <row r="10" spans="1:65">
+    <row r="10" spans="1:69">
       <c r="A10" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B10" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C10">
         <v>9.970000000000001</v>
@@ -2398,7 +2485,7 @@
         <v>8.99</v>
       </c>
       <c r="F10" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G10">
         <v>10.11</v>
@@ -2410,7 +2497,7 @@
         <v>8.789999999999999</v>
       </c>
       <c r="J10" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="K10">
         <v>11.04</v>
@@ -2422,7 +2509,7 @@
         <v>8.050000000000001</v>
       </c>
       <c r="N10" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="O10">
         <v>11.39</v>
@@ -2434,7 +2521,7 @@
         <v>7.74</v>
       </c>
       <c r="R10" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="S10">
         <v>12.2</v>
@@ -2446,7 +2533,7 @@
         <v>7.25</v>
       </c>
       <c r="V10" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="W10">
         <v>13.17</v>
@@ -2458,7 +2545,7 @@
         <v>6.69</v>
       </c>
       <c r="Z10" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="AA10">
         <v>14.94</v>
@@ -2470,7 +2557,7 @@
         <v>5.85</v>
       </c>
       <c r="AD10" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AE10">
         <v>13.31</v>
@@ -2482,7 +2569,7 @@
         <v>6.7</v>
       </c>
       <c r="AH10" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AI10">
         <v>13.81</v>
@@ -2494,7 +2581,7 @@
         <v>6.4</v>
       </c>
       <c r="AL10" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AM10">
         <v>11.47</v>
@@ -2506,7 +2593,7 @@
         <v>7.32</v>
       </c>
       <c r="AP10" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AQ10">
         <v>12.28</v>
@@ -2518,7 +2605,7 @@
         <v>7.22</v>
       </c>
       <c r="AT10" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AU10">
         <v>12.7</v>
@@ -2530,24 +2617,27 @@
         <v>6.96</v>
       </c>
       <c r="AX10" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="BB10" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="BF10" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="BJ10" t="s">
-        <v>128</v>
+        <v>132</v>
+      </c>
+      <c r="BN10" t="s">
+        <v>133</v>
       </c>
     </row>
-    <row r="11" spans="1:65">
+    <row r="11" spans="1:69">
       <c r="A11" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B11" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C11">
         <v>1926.43</v>
@@ -2559,7 +2649,7 @@
         <v>0</v>
       </c>
       <c r="F11" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G11">
         <v>1926.43</v>
@@ -2571,7 +2661,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="K11">
         <v>2355</v>
@@ -2583,7 +2673,7 @@
         <v>0</v>
       </c>
       <c r="N11" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="O11">
         <v>2355</v>
@@ -2595,7 +2685,7 @@
         <v>0</v>
       </c>
       <c r="R11" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="S11">
         <v>2596.6</v>
@@ -2607,7 +2697,7 @@
         <v>0</v>
       </c>
       <c r="V11" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="W11">
         <v>1997.33</v>
@@ -2619,7 +2709,7 @@
         <v>0</v>
       </c>
       <c r="Z11" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="AA11">
         <v>1855</v>
@@ -2631,7 +2721,7 @@
         <v>0</v>
       </c>
       <c r="AD11" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AE11">
         <v>2001</v>
@@ -2643,36 +2733,39 @@
         <v>0</v>
       </c>
       <c r="AH11" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AL11" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AP11" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AT11" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AX11" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="BB11" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="BF11" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="BJ11" t="s">
-        <v>128</v>
+        <v>132</v>
+      </c>
+      <c r="BN11" t="s">
+        <v>133</v>
       </c>
     </row>
-    <row r="12" spans="1:65">
+    <row r="12" spans="1:69">
       <c r="A12" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B12" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C12">
         <v>747.86</v>
@@ -2684,7 +2777,7 @@
         <v>0.03</v>
       </c>
       <c r="F12" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G12">
         <v>747.86</v>
@@ -2696,7 +2789,7 @@
         <v>0.02</v>
       </c>
       <c r="J12" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="K12">
         <v>747.86</v>
@@ -2708,7 +2801,7 @@
         <v>0.02</v>
       </c>
       <c r="N12" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="O12">
         <v>747.86</v>
@@ -2720,7 +2813,7 @@
         <v>0.02</v>
       </c>
       <c r="R12" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="S12">
         <v>607.5</v>
@@ -2732,7 +2825,7 @@
         <v>0.04</v>
       </c>
       <c r="V12" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="W12">
         <v>569.29</v>
@@ -2744,7 +2837,7 @@
         <v>0.04</v>
       </c>
       <c r="Z12" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="AA12">
         <v>647.86</v>
@@ -2756,7 +2849,7 @@
         <v>0.03</v>
       </c>
       <c r="AD12" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AE12">
         <v>647.86</v>
@@ -2768,7 +2861,7 @@
         <v>0.03</v>
       </c>
       <c r="AH12" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AI12">
         <v>612.14</v>
@@ -2780,7 +2873,7 @@
         <v>0.03</v>
       </c>
       <c r="AL12" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AM12">
         <v>551</v>
@@ -2792,30 +2885,33 @@
         <v>0.02</v>
       </c>
       <c r="AP12" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AT12" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AX12" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="BB12" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="BF12" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="BJ12" t="s">
-        <v>128</v>
+        <v>132</v>
+      </c>
+      <c r="BN12" t="s">
+        <v>133</v>
       </c>
     </row>
-    <row r="13" spans="1:65">
+    <row r="13" spans="1:69">
       <c r="A13" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B13" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C13">
         <v>15.6</v>
@@ -2827,7 +2923,7 @@
         <v>5.65</v>
       </c>
       <c r="F13" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G13">
         <v>15.67</v>
@@ -2839,7 +2935,7 @@
         <v>5.57</v>
       </c>
       <c r="J13" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="K13">
         <v>15.39</v>
@@ -2851,7 +2947,7 @@
         <v>5.7</v>
       </c>
       <c r="N13" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="O13">
         <v>14.67</v>
@@ -2863,7 +2959,7 @@
         <v>5.93</v>
       </c>
       <c r="R13" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="S13">
         <v>14.87</v>
@@ -2875,7 +2971,7 @@
         <v>5.9</v>
       </c>
       <c r="V13" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="W13">
         <v>14.53</v>
@@ -2887,7 +2983,7 @@
         <v>6.03</v>
       </c>
       <c r="Z13" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="AA13">
         <v>14.6</v>
@@ -2899,7 +2995,7 @@
         <v>5.99</v>
       </c>
       <c r="AD13" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AE13">
         <v>17.8</v>
@@ -2911,7 +3007,7 @@
         <v>4.94</v>
       </c>
       <c r="AH13" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AI13">
         <v>21.14</v>
@@ -2923,7 +3019,7 @@
         <v>4.08</v>
       </c>
       <c r="AL13" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AM13">
         <v>26</v>
@@ -2935,30 +3031,33 @@
         <v>2.94</v>
       </c>
       <c r="AP13" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AT13" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AX13" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="BB13" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="BF13" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="BJ13" t="s">
-        <v>128</v>
+        <v>132</v>
+      </c>
+      <c r="BN13" t="s">
+        <v>133</v>
       </c>
     </row>
-    <row r="14" spans="1:65">
+    <row r="14" spans="1:69">
       <c r="A14" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B14" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C14">
         <v>89</v>
@@ -2970,7 +3069,7 @@
         <v>0.8</v>
       </c>
       <c r="F14" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G14">
         <v>90.43000000000001</v>
@@ -2982,7 +3081,7 @@
         <v>0.75</v>
       </c>
       <c r="J14" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="K14">
         <v>133.71</v>
@@ -2994,7 +3093,7 @@
         <v>0.45</v>
       </c>
       <c r="N14" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="O14">
         <v>135.14</v>
@@ -3006,7 +3105,7 @@
         <v>0.43</v>
       </c>
       <c r="R14" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="S14">
         <v>148.33</v>
@@ -3018,7 +3117,7 @@
         <v>0.39</v>
       </c>
       <c r="V14" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="W14">
         <v>279.29</v>
@@ -3030,7 +3129,7 @@
         <v>0.14</v>
       </c>
       <c r="Z14" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="AA14">
         <v>289.29</v>
@@ -3042,7 +3141,7 @@
         <v>0.13</v>
       </c>
       <c r="AD14" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AE14">
         <v>123.86</v>
@@ -3054,7 +3153,7 @@
         <v>0.51</v>
       </c>
       <c r="AH14" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AI14">
         <v>127.43</v>
@@ -3066,7 +3165,7 @@
         <v>0.47</v>
       </c>
       <c r="AL14" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AM14">
         <v>129.57</v>
@@ -3078,30 +3177,33 @@
         <v>0.33</v>
       </c>
       <c r="AP14" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AT14" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AX14" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="BB14" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="BF14" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="BJ14" t="s">
-        <v>128</v>
+        <v>132</v>
+      </c>
+      <c r="BN14" t="s">
+        <v>133</v>
       </c>
     </row>
-    <row r="15" spans="1:65">
+    <row r="15" spans="1:69">
       <c r="A15" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B15" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C15">
         <v>250</v>
@@ -3113,7 +3215,7 @@
         <v>0.18</v>
       </c>
       <c r="F15" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G15">
         <v>259.86</v>
@@ -3125,7 +3227,7 @@
         <v>0.16</v>
       </c>
       <c r="J15" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="K15">
         <v>153</v>
@@ -3137,7 +3239,7 @@
         <v>0.37</v>
       </c>
       <c r="N15" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="O15">
         <v>143</v>
@@ -3149,7 +3251,7 @@
         <v>0.4</v>
       </c>
       <c r="R15" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="S15">
         <v>144.83</v>
@@ -3161,7 +3263,7 @@
         <v>0.4</v>
       </c>
       <c r="V15" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="W15">
         <v>133.71</v>
@@ -3173,7 +3275,7 @@
         <v>0.44</v>
       </c>
       <c r="Z15" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="AA15">
         <v>137.86</v>
@@ -3185,7 +3287,7 @@
         <v>0.42</v>
       </c>
       <c r="AD15" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AE15">
         <v>150.57</v>
@@ -3197,7 +3299,7 @@
         <v>0.39</v>
       </c>
       <c r="AH15" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AI15">
         <v>174.86</v>
@@ -3209,7 +3311,7 @@
         <v>0.29</v>
       </c>
       <c r="AL15" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AM15">
         <v>179.29</v>
@@ -3221,30 +3323,33 @@
         <v>0.19</v>
       </c>
       <c r="AP15" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AT15" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AX15" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="BB15" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="BF15" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="BJ15" t="s">
-        <v>128</v>
+        <v>132</v>
+      </c>
+      <c r="BN15" t="s">
+        <v>133</v>
       </c>
     </row>
-    <row r="16" spans="1:65">
+    <row r="16" spans="1:69">
       <c r="A16" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B16" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C16">
         <v>467.14</v>
@@ -3256,7 +3361,7 @@
         <v>0.06</v>
       </c>
       <c r="F16" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G16">
         <v>505.29</v>
@@ -3268,7 +3373,7 @@
         <v>0.05</v>
       </c>
       <c r="J16" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="K16">
         <v>494.14</v>
@@ -3280,7 +3385,7 @@
         <v>0.05</v>
       </c>
       <c r="N16" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="O16">
         <v>502.43</v>
@@ -3292,7 +3397,7 @@
         <v>0.05</v>
       </c>
       <c r="R16" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="S16">
         <v>441.33</v>
@@ -3304,7 +3409,7 @@
         <v>0.06</v>
       </c>
       <c r="V16" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="W16">
         <v>433.86</v>
@@ -3316,7 +3421,7 @@
         <v>0.06</v>
       </c>
       <c r="Z16" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="AA16">
         <v>331</v>
@@ -3328,7 +3433,7 @@
         <v>0.1</v>
       </c>
       <c r="AD16" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AE16">
         <v>337.71</v>
@@ -3340,7 +3445,7 @@
         <v>0.11</v>
       </c>
       <c r="AH16" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AI16">
         <v>373.71</v>
@@ -3352,7 +3457,7 @@
         <v>0.08</v>
       </c>
       <c r="AL16" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AM16">
         <v>429.43</v>
@@ -3364,7 +3469,7 @@
         <v>0.04</v>
       </c>
       <c r="AP16" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AQ16">
         <v>458.5</v>
@@ -3376,27 +3481,30 @@
         <v>0.04</v>
       </c>
       <c r="AT16" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AX16" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="BB16" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="BF16" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="BJ16" t="s">
-        <v>128</v>
+        <v>132</v>
+      </c>
+      <c r="BN16" t="s">
+        <v>133</v>
       </c>
     </row>
-    <row r="17" spans="1:62">
+    <row r="17" spans="1:66">
       <c r="A17" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B17" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C17">
         <v>1926.43</v>
@@ -3408,7 +3516,7 @@
         <v>0</v>
       </c>
       <c r="F17" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G17">
         <v>1926.43</v>
@@ -3420,7 +3528,7 @@
         <v>0</v>
       </c>
       <c r="J17" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="K17">
         <v>2033.57</v>
@@ -3432,7 +3540,7 @@
         <v>0</v>
       </c>
       <c r="N17" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="O17">
         <v>2033.57</v>
@@ -3444,7 +3552,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="S17">
         <v>2296.6</v>
@@ -3456,45 +3564,48 @@
         <v>0</v>
       </c>
       <c r="V17" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="Z17" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="AD17" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AH17" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AL17" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AP17" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AT17" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AX17" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="BB17" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="BF17" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="BJ17" t="s">
-        <v>128</v>
+        <v>132</v>
+      </c>
+      <c r="BN17" t="s">
+        <v>133</v>
       </c>
     </row>
-    <row r="18" spans="1:62">
+    <row r="18" spans="1:66">
       <c r="A18" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B18" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C18">
         <v>1126.43</v>
@@ -3506,7 +3617,7 @@
         <v>0.01</v>
       </c>
       <c r="F18" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G18">
         <v>1126.43</v>
@@ -3518,7 +3629,7 @@
         <v>0.01</v>
       </c>
       <c r="J18" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="K18">
         <v>1126.43</v>
@@ -3530,7 +3641,7 @@
         <v>0.01</v>
       </c>
       <c r="N18" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="O18">
         <v>1197.86</v>
@@ -3542,7 +3653,7 @@
         <v>0.01</v>
       </c>
       <c r="R18" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="S18">
         <v>1296.6</v>
@@ -3554,7 +3665,7 @@
         <v>0.01</v>
       </c>
       <c r="V18" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="W18">
         <v>1247.33</v>
@@ -3566,7 +3677,7 @@
         <v>0.01</v>
       </c>
       <c r="Z18" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="AA18">
         <v>1569.29</v>
@@ -3578,7 +3689,7 @@
         <v>0.01</v>
       </c>
       <c r="AD18" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AE18">
         <v>2140.71</v>
@@ -3590,7 +3701,7 @@
         <v>0</v>
       </c>
       <c r="AH18" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AI18">
         <v>2001</v>
@@ -3602,7 +3713,7 @@
         <v>0</v>
       </c>
       <c r="AL18" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AM18">
         <v>2001</v>
@@ -3614,30 +3725,33 @@
         <v>0</v>
       </c>
       <c r="AP18" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AT18" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AX18" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="BB18" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="BF18" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="BJ18" t="s">
-        <v>128</v>
+        <v>132</v>
+      </c>
+      <c r="BN18" t="s">
+        <v>133</v>
       </c>
     </row>
-    <row r="19" spans="1:62">
+    <row r="19" spans="1:66">
       <c r="A19" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B19" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C19">
         <v>540.71</v>
@@ -3649,7 +3763,7 @@
         <v>0.05</v>
       </c>
       <c r="F19" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G19">
         <v>576.4299999999999</v>
@@ -3661,7 +3775,7 @@
         <v>0.04</v>
       </c>
       <c r="J19" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="K19">
         <v>576.4299999999999</v>
@@ -3673,7 +3787,7 @@
         <v>0.04</v>
       </c>
       <c r="N19" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="O19">
         <v>612.14</v>
@@ -3685,7 +3799,7 @@
         <v>0.03</v>
       </c>
       <c r="R19" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="S19">
         <v>630.67</v>
@@ -3697,7 +3811,7 @@
         <v>0.03</v>
       </c>
       <c r="V19" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="W19">
         <v>647.86</v>
@@ -3709,7 +3823,7 @@
         <v>0.03</v>
       </c>
       <c r="Z19" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="AA19">
         <v>647.86</v>
@@ -3721,7 +3835,7 @@
         <v>0.03</v>
       </c>
       <c r="AD19" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AE19">
         <v>647.86</v>
@@ -3733,7 +3847,7 @@
         <v>0.03</v>
       </c>
       <c r="AH19" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AI19">
         <v>1219.29</v>
@@ -3745,33 +3859,36 @@
         <v>0.01</v>
       </c>
       <c r="AL19" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AP19" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AT19" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AX19" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="BB19" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="BF19" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="BJ19" t="s">
-        <v>128</v>
+        <v>132</v>
+      </c>
+      <c r="BN19" t="s">
+        <v>133</v>
       </c>
     </row>
-    <row r="20" spans="1:62">
+    <row r="20" spans="1:66">
       <c r="A20" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B20" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C20">
         <v>53.43</v>
@@ -3783,7 +3900,7 @@
         <v>1.47</v>
       </c>
       <c r="F20" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G20">
         <v>53.43</v>
@@ -3795,7 +3912,7 @@
         <v>1.44</v>
       </c>
       <c r="J20" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="K20">
         <v>51.29</v>
@@ -3807,7 +3924,7 @@
         <v>1.52</v>
       </c>
       <c r="N20" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="O20">
         <v>51.29</v>
@@ -3819,7 +3936,7 @@
         <v>1.49</v>
       </c>
       <c r="R20" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="S20">
         <v>53</v>
@@ -3831,7 +3948,7 @@
         <v>1.46</v>
       </c>
       <c r="V20" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="W20">
         <v>42.86</v>
@@ -3843,7 +3960,7 @@
         <v>1.86</v>
       </c>
       <c r="Z20" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="AA20">
         <v>40</v>
@@ -3855,7 +3972,7 @@
         <v>2</v>
       </c>
       <c r="AD20" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AE20">
         <v>49.86</v>
@@ -3867,7 +3984,7 @@
         <v>1.59</v>
       </c>
       <c r="AH20" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AI20">
         <v>58</v>
@@ -3879,33 +3996,36 @@
         <v>1.3</v>
       </c>
       <c r="AL20" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AP20" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AT20" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AX20" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="BB20" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="BF20" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="BJ20" t="s">
-        <v>128</v>
+        <v>132</v>
+      </c>
+      <c r="BN20" t="s">
+        <v>133</v>
       </c>
     </row>
-    <row r="21" spans="1:62">
+    <row r="21" spans="1:66">
       <c r="A21" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B21" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C21">
         <v>1497.86</v>
@@ -3917,7 +4037,7 @@
         <v>0.01</v>
       </c>
       <c r="F21" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G21">
         <v>1497.86</v>
@@ -3929,7 +4049,7 @@
         <v>0.01</v>
       </c>
       <c r="J21" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="K21">
         <v>1497.86</v>
@@ -3941,7 +4061,7 @@
         <v>0.01</v>
       </c>
       <c r="N21" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="O21">
         <v>1497.86</v>
@@ -3953,7 +4073,7 @@
         <v>0.01</v>
       </c>
       <c r="R21" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="S21">
         <v>1696.6</v>
@@ -3965,7 +4085,7 @@
         <v>0</v>
       </c>
       <c r="V21" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="W21">
         <v>1664</v>
@@ -3977,42 +4097,45 @@
         <v>0</v>
       </c>
       <c r="Z21" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="AD21" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AH21" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AL21" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AP21" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AT21" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AX21" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="BB21" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="BF21" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="BJ21" t="s">
-        <v>128</v>
+        <v>132</v>
+      </c>
+      <c r="BN21" t="s">
+        <v>133</v>
       </c>
     </row>
-    <row r="22" spans="1:62">
+    <row r="22" spans="1:66">
       <c r="A22" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B22" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C22">
         <v>191.71</v>
@@ -4024,7 +4147,7 @@
         <v>0.28</v>
       </c>
       <c r="F22" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G22">
         <v>222.71</v>
@@ -4036,7 +4159,7 @@
         <v>0.21</v>
       </c>
       <c r="J22" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="K22">
         <v>193.29</v>
@@ -4048,7 +4171,7 @@
         <v>0.26</v>
       </c>
       <c r="N22" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="O22">
         <v>197.43</v>
@@ -4060,7 +4183,7 @@
         <v>0.24</v>
       </c>
       <c r="R22" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="S22">
         <v>148.17</v>
@@ -4072,7 +4195,7 @@
         <v>0.39</v>
       </c>
       <c r="V22" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="W22">
         <v>140</v>
@@ -4084,7 +4207,7 @@
         <v>0.41</v>
       </c>
       <c r="Z22" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="AA22">
         <v>138.57</v>
@@ -4096,7 +4219,7 @@
         <v>0.41</v>
       </c>
       <c r="AD22" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AE22">
         <v>180.57</v>
@@ -4108,7 +4231,7 @@
         <v>0.3</v>
       </c>
       <c r="AH22" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AI22">
         <v>189.07</v>
@@ -4120,7 +4243,7 @@
         <v>0.26</v>
       </c>
       <c r="AL22" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AM22">
         <v>165.36</v>
@@ -4132,7 +4255,7 @@
         <v>0.22</v>
       </c>
       <c r="AP22" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AQ22">
         <v>238.33</v>
@@ -4144,7 +4267,7 @@
         <v>0.15</v>
       </c>
       <c r="AT22" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AU22">
         <v>249.83</v>
@@ -4156,24 +4279,27 @@
         <v>0.13</v>
       </c>
       <c r="AX22" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="BB22" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="BF22" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="BJ22" t="s">
-        <v>128</v>
+        <v>132</v>
+      </c>
+      <c r="BN22" t="s">
+        <v>133</v>
       </c>
     </row>
-    <row r="23" spans="1:62">
+    <row r="23" spans="1:66">
       <c r="A23" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B23" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C23">
         <v>1326.43</v>
@@ -4185,7 +4311,7 @@
         <v>0.01</v>
       </c>
       <c r="F23" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G23">
         <v>1326.43</v>
@@ -4197,7 +4323,7 @@
         <v>0.01</v>
       </c>
       <c r="J23" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="K23">
         <v>1326.43</v>
@@ -4209,7 +4335,7 @@
         <v>0.01</v>
       </c>
       <c r="N23" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="O23">
         <v>1069.29</v>
@@ -4221,7 +4347,7 @@
         <v>0.01</v>
       </c>
       <c r="R23" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="S23">
         <v>996.6</v>
@@ -4233,7 +4359,7 @@
         <v>0.01</v>
       </c>
       <c r="V23" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="W23">
         <v>705.67</v>
@@ -4245,7 +4371,7 @@
         <v>0.03</v>
       </c>
       <c r="Z23" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="AA23">
         <v>747.86</v>
@@ -4257,7 +4383,7 @@
         <v>0.02</v>
       </c>
       <c r="AD23" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AE23">
         <v>783.5700000000001</v>
@@ -4269,7 +4395,7 @@
         <v>0.02</v>
       </c>
       <c r="AH23" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AI23">
         <v>526.4299999999999</v>
@@ -4281,7 +4407,7 @@
         <v>0.04</v>
       </c>
       <c r="AL23" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AM23">
         <v>583.5700000000001</v>
@@ -4293,7 +4419,7 @@
         <v>0.02</v>
       </c>
       <c r="AP23" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AQ23">
         <v>664</v>
@@ -4305,27 +4431,30 @@
         <v>0.02</v>
       </c>
       <c r="AT23" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AX23" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="BB23" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="BF23" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="BJ23" t="s">
-        <v>128</v>
+        <v>132</v>
+      </c>
+      <c r="BN23" t="s">
+        <v>133</v>
       </c>
     </row>
-    <row r="24" spans="1:62">
+    <row r="24" spans="1:66">
       <c r="A24" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B24" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C24">
         <v>1069.29</v>
@@ -4337,7 +4466,7 @@
         <v>0.01</v>
       </c>
       <c r="F24" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G24">
         <v>1069.29</v>
@@ -4349,7 +4478,7 @@
         <v>0.01</v>
       </c>
       <c r="J24" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="K24">
         <v>1069.29</v>
@@ -4361,7 +4490,7 @@
         <v>0.01</v>
       </c>
       <c r="N24" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="O24">
         <v>1069.29</v>
@@ -4373,7 +4502,7 @@
         <v>0.01</v>
       </c>
       <c r="R24" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="S24">
         <v>1372.33</v>
@@ -4385,7 +4514,7 @@
         <v>0.01</v>
       </c>
       <c r="V24" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="W24">
         <v>1926.43</v>
@@ -4397,7 +4526,7 @@
         <v>0</v>
       </c>
       <c r="Z24" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="AA24">
         <v>1926.43</v>
@@ -4409,39 +4538,42 @@
         <v>0</v>
       </c>
       <c r="AD24" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AH24" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AL24" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AP24" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AT24" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AX24" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="BB24" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="BF24" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="BJ24" t="s">
-        <v>128</v>
+        <v>132</v>
+      </c>
+      <c r="BN24" t="s">
+        <v>133</v>
       </c>
     </row>
-    <row r="25" spans="1:62">
+    <row r="25" spans="1:66">
       <c r="A25" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B25" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C25">
         <v>41.71</v>
@@ -4453,7 +4585,7 @@
         <v>1.95</v>
       </c>
       <c r="F25" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G25">
         <v>45.57</v>
@@ -4465,7 +4597,7 @@
         <v>1.73</v>
       </c>
       <c r="J25" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="K25">
         <v>47</v>
@@ -4477,7 +4609,7 @@
         <v>1.68</v>
       </c>
       <c r="N25" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="O25">
         <v>50.43</v>
@@ -4489,7 +4621,7 @@
         <v>1.52</v>
       </c>
       <c r="R25" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="S25">
         <v>48</v>
@@ -4501,7 +4633,7 @@
         <v>1.64</v>
       </c>
       <c r="V25" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="W25">
         <v>49.86</v>
@@ -4513,7 +4645,7 @@
         <v>1.56</v>
       </c>
       <c r="Z25" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="AA25">
         <v>47</v>
@@ -4525,7 +4657,7 @@
         <v>1.66</v>
       </c>
       <c r="AD25" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AE25">
         <v>53.43</v>
@@ -4537,7 +4669,7 @@
         <v>1.47</v>
       </c>
       <c r="AH25" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AI25">
         <v>37.29</v>
@@ -4549,7 +4681,7 @@
         <v>2.18</v>
       </c>
       <c r="AL25" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AM25">
         <v>31.86</v>
@@ -4561,7 +4693,7 @@
         <v>2.31</v>
       </c>
       <c r="AP25" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AQ25">
         <v>29.33</v>
@@ -4573,7 +4705,7 @@
         <v>2.79</v>
       </c>
       <c r="AT25" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AU25">
         <v>25.5</v>
@@ -4585,7 +4717,7 @@
         <v>3.24</v>
       </c>
       <c r="AX25" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="AY25">
         <v>25</v>
@@ -4597,21 +4729,24 @@
         <v>3.4</v>
       </c>
       <c r="BB25" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="BF25" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="BJ25" t="s">
-        <v>128</v>
+        <v>132</v>
+      </c>
+      <c r="BN25" t="s">
+        <v>133</v>
       </c>
     </row>
-    <row r="26" spans="1:62">
+    <row r="26" spans="1:66">
       <c r="A26" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B26" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C26">
         <v>88.86</v>
@@ -4623,7 +4758,7 @@
         <v>0.8</v>
       </c>
       <c r="F26" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G26">
         <v>91.70999999999999</v>
@@ -4635,7 +4770,7 @@
         <v>0.74</v>
       </c>
       <c r="J26" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="K26">
         <v>91.70999999999999</v>
@@ -4647,7 +4782,7 @@
         <v>0.75</v>
       </c>
       <c r="N26" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="O26">
         <v>92.43000000000001</v>
@@ -4659,7 +4794,7 @@
         <v>0.72</v>
       </c>
       <c r="R26" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="S26">
         <v>110.83</v>
@@ -4671,7 +4806,7 @@
         <v>0.58</v>
       </c>
       <c r="V26" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="W26">
         <v>123</v>
@@ -4683,7 +4818,7 @@
         <v>0.5</v>
       </c>
       <c r="Z26" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="AA26">
         <v>112.29</v>
@@ -4695,7 +4830,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AD26" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AE26">
         <v>132.29</v>
@@ -4707,7 +4842,7 @@
         <v>0.47</v>
       </c>
       <c r="AH26" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AI26">
         <v>144.64</v>
@@ -4719,7 +4854,7 @@
         <v>0.39</v>
       </c>
       <c r="AL26" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AM26">
         <v>146.07</v>
@@ -4731,7 +4866,7 @@
         <v>0.27</v>
       </c>
       <c r="AP26" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AQ26">
         <v>173</v>
@@ -4743,27 +4878,30 @@
         <v>0.26</v>
       </c>
       <c r="AT26" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AX26" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="BB26" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="BF26" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="BJ26" t="s">
-        <v>128</v>
+        <v>132</v>
+      </c>
+      <c r="BN26" t="s">
+        <v>133</v>
       </c>
     </row>
-    <row r="27" spans="1:62">
+    <row r="27" spans="1:66">
       <c r="A27" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B27" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C27">
         <v>49.86</v>
@@ -4775,7 +4913,7 @@
         <v>1.59</v>
       </c>
       <c r="F27" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G27">
         <v>50.57</v>
@@ -4787,7 +4925,7 @@
         <v>1.54</v>
       </c>
       <c r="J27" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="K27">
         <v>38.71</v>
@@ -4799,7 +4937,7 @@
         <v>2.1</v>
       </c>
       <c r="N27" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="O27">
         <v>37.71</v>
@@ -4811,7 +4949,7 @@
         <v>2.13</v>
       </c>
       <c r="R27" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="S27">
         <v>40.67</v>
@@ -4823,7 +4961,7 @@
         <v>1.98</v>
       </c>
       <c r="V27" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="W27">
         <v>32.86</v>
@@ -4835,7 +4973,7 @@
         <v>2.51</v>
       </c>
       <c r="Z27" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="AA27">
         <v>35.14</v>
@@ -4847,7 +4985,7 @@
         <v>2.32</v>
       </c>
       <c r="AD27" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AE27">
         <v>43.14</v>
@@ -4859,7 +4997,7 @@
         <v>1.88</v>
       </c>
       <c r="AH27" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AI27">
         <v>51.29</v>
@@ -4871,7 +5009,7 @@
         <v>1.51</v>
       </c>
       <c r="AL27" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AM27">
         <v>21.57</v>
@@ -4883,7 +5021,7 @@
         <v>3.65</v>
       </c>
       <c r="AP27" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AQ27">
         <v>27.33</v>
@@ -4895,7 +5033,7 @@
         <v>3.02</v>
       </c>
       <c r="AT27" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AU27">
         <v>31.83</v>
@@ -4907,7 +5045,7 @@
         <v>2.51</v>
       </c>
       <c r="AX27" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="AY27">
         <v>30.5</v>
@@ -4919,7 +5057,7 @@
         <v>2.71</v>
       </c>
       <c r="BB27" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="BC27">
         <v>31.33</v>
@@ -4931,18 +5069,21 @@
         <v>2.58</v>
       </c>
       <c r="BF27" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="BJ27" t="s">
-        <v>128</v>
+        <v>132</v>
+      </c>
+      <c r="BN27" t="s">
+        <v>133</v>
       </c>
     </row>
-    <row r="28" spans="1:62">
+    <row r="28" spans="1:66">
       <c r="A28" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B28" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C28">
         <v>68.43000000000001</v>
@@ -4954,7 +5095,7 @@
         <v>1.1</v>
       </c>
       <c r="F28" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G28">
         <v>52.71</v>
@@ -4966,7 +5107,7 @@
         <v>1.46</v>
       </c>
       <c r="J28" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="K28">
         <v>52.71</v>
@@ -4978,7 +5119,7 @@
         <v>1.47</v>
       </c>
       <c r="N28" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="O28">
         <v>57.86</v>
@@ -4990,7 +5131,7 @@
         <v>1.29</v>
       </c>
       <c r="R28" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="S28">
         <v>47.17</v>
@@ -5002,7 +5143,7 @@
         <v>1.67</v>
       </c>
       <c r="V28" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="W28">
         <v>51.14</v>
@@ -5014,7 +5155,7 @@
         <v>1.51</v>
       </c>
       <c r="Z28" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="AA28">
         <v>52.57</v>
@@ -5026,7 +5167,7 @@
         <v>1.46</v>
       </c>
       <c r="AD28" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AE28">
         <v>45.71</v>
@@ -5038,7 +5179,7 @@
         <v>1.76</v>
       </c>
       <c r="AH28" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AI28">
         <v>50.57</v>
@@ -5050,7 +5191,7 @@
         <v>1.54</v>
       </c>
       <c r="AL28" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AM28">
         <v>50.29</v>
@@ -5062,7 +5203,7 @@
         <v>1.31</v>
       </c>
       <c r="AP28" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AQ28">
         <v>28.33</v>
@@ -5074,7 +5215,7 @@
         <v>2.9</v>
       </c>
       <c r="AT28" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AU28">
         <v>28.83</v>
@@ -5086,7 +5227,7 @@
         <v>2.81</v>
       </c>
       <c r="AX28" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="AY28">
         <v>51</v>
@@ -5098,21 +5239,24 @@
         <v>1.47</v>
       </c>
       <c r="BB28" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="BF28" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="BJ28" t="s">
-        <v>128</v>
+        <v>132</v>
+      </c>
+      <c r="BN28" t="s">
+        <v>133</v>
       </c>
     </row>
-    <row r="29" spans="1:62">
+    <row r="29" spans="1:66">
       <c r="A29" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B29" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C29">
         <v>1197.86</v>
@@ -5124,7 +5268,7 @@
         <v>0.01</v>
       </c>
       <c r="F29" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G29">
         <v>1197.86</v>
@@ -5136,7 +5280,7 @@
         <v>0.01</v>
       </c>
       <c r="J29" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="K29">
         <v>1197.86</v>
@@ -5148,7 +5292,7 @@
         <v>0.01</v>
       </c>
       <c r="N29" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="O29">
         <v>819.29</v>
@@ -5160,7 +5304,7 @@
         <v>0.02</v>
       </c>
       <c r="R29" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="S29">
         <v>872.33</v>
@@ -5172,7 +5316,7 @@
         <v>0.02</v>
       </c>
       <c r="V29" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="W29">
         <v>890.71</v>
@@ -5184,7 +5328,7 @@
         <v>0.02</v>
       </c>
       <c r="Z29" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="AA29">
         <v>890.71</v>
@@ -5196,7 +5340,7 @@
         <v>0.02</v>
       </c>
       <c r="AD29" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AE29">
         <v>926.4299999999999</v>
@@ -5208,36 +5352,39 @@
         <v>0.02</v>
       </c>
       <c r="AH29" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AL29" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AP29" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AT29" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AX29" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="BB29" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="BF29" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="BJ29" t="s">
-        <v>128</v>
+        <v>132</v>
+      </c>
+      <c r="BN29" t="s">
+        <v>133</v>
       </c>
     </row>
-    <row r="30" spans="1:62">
+    <row r="30" spans="1:66">
       <c r="A30" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B30" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C30">
         <v>21.29</v>
@@ -5249,7 +5396,7 @@
         <v>4.07</v>
       </c>
       <c r="F30" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G30">
         <v>20.29</v>
@@ -5261,7 +5408,7 @@
         <v>4.24</v>
       </c>
       <c r="J30" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="K30">
         <v>19.71</v>
@@ -5273,7 +5420,7 @@
         <v>4.38</v>
       </c>
       <c r="N30" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="O30">
         <v>20.14</v>
@@ -5285,7 +5432,7 @@
         <v>4.24</v>
       </c>
       <c r="R30" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="S30">
         <v>21</v>
@@ -5297,7 +5444,7 @@
         <v>4.09</v>
       </c>
       <c r="V30" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="W30">
         <v>17.53</v>
@@ -5309,7 +5456,7 @@
         <v>4.95</v>
       </c>
       <c r="Z30" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="AA30">
         <v>17.23</v>
@@ -5321,7 +5468,7 @@
         <v>5.03</v>
       </c>
       <c r="AD30" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AE30">
         <v>15.96</v>
@@ -5333,7 +5480,7 @@
         <v>5.54</v>
       </c>
       <c r="AH30" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AI30">
         <v>17.43</v>
@@ -5345,7 +5492,7 @@
         <v>5.01</v>
       </c>
       <c r="AL30" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AM30">
         <v>17</v>
@@ -5357,30 +5504,33 @@
         <v>4.77</v>
       </c>
       <c r="AP30" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AT30" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AX30" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="BB30" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="BF30" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="BJ30" t="s">
-        <v>128</v>
+        <v>132</v>
+      </c>
+      <c r="BN30" t="s">
+        <v>133</v>
       </c>
     </row>
-    <row r="31" spans="1:62">
+    <row r="31" spans="1:66">
       <c r="A31" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B31" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C31">
         <v>32.29</v>
@@ -5392,7 +5542,7 @@
         <v>2.6</v>
       </c>
       <c r="F31" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G31">
         <v>33</v>
@@ -5404,7 +5554,7 @@
         <v>2.49</v>
       </c>
       <c r="J31" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="K31">
         <v>34.14</v>
@@ -5416,7 +5566,7 @@
         <v>2.42</v>
       </c>
       <c r="N31" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="O31">
         <v>30.43</v>
@@ -5428,7 +5578,7 @@
         <v>2.71</v>
       </c>
       <c r="R31" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="S31">
         <v>31.5</v>
@@ -5440,7 +5590,7 @@
         <v>2.64</v>
       </c>
       <c r="V31" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="W31">
         <v>36.57</v>
@@ -5452,7 +5602,7 @@
         <v>2.22</v>
       </c>
       <c r="Z31" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="AA31">
         <v>32.43</v>
@@ -5464,7 +5614,7 @@
         <v>2.53</v>
       </c>
       <c r="AD31" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AE31">
         <v>32.71</v>
@@ -5476,7 +5626,7 @@
         <v>2.56</v>
       </c>
       <c r="AH31" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AI31">
         <v>35.71</v>
@@ -5488,7 +5638,7 @@
         <v>2.29</v>
       </c>
       <c r="AL31" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AM31">
         <v>37.71</v>
@@ -5500,7 +5650,7 @@
         <v>1.88</v>
       </c>
       <c r="AP31" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AQ31">
         <v>37</v>
@@ -5512,7 +5662,7 @@
         <v>2.13</v>
       </c>
       <c r="AT31" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AU31">
         <v>38.5</v>
@@ -5524,7 +5674,7 @@
         <v>2</v>
       </c>
       <c r="AX31" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="AY31">
         <v>21</v>
@@ -5536,7 +5686,7 @@
         <v>4.12</v>
       </c>
       <c r="BB31" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="BC31">
         <v>16.2</v>
@@ -5548,7 +5698,7 @@
         <v>5.44</v>
       </c>
       <c r="BF31" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="BG31">
         <v>16.28</v>
@@ -5560,15 +5710,18 @@
         <v>5.39</v>
       </c>
       <c r="BJ31" t="s">
-        <v>128</v>
+        <v>132</v>
+      </c>
+      <c r="BN31" t="s">
+        <v>133</v>
       </c>
     </row>
-    <row r="32" spans="1:62">
+    <row r="32" spans="1:66">
       <c r="A32" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B32" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C32">
         <v>1197.86</v>
@@ -5580,7 +5733,7 @@
         <v>0.01</v>
       </c>
       <c r="F32" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G32">
         <v>1197.86</v>
@@ -5592,7 +5745,7 @@
         <v>0.01</v>
       </c>
       <c r="J32" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="K32">
         <v>1197.86</v>
@@ -5604,7 +5757,7 @@
         <v>0.01</v>
       </c>
       <c r="N32" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="O32">
         <v>1197.86</v>
@@ -5616,7 +5769,7 @@
         <v>0.01</v>
       </c>
       <c r="R32" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="S32">
         <v>1247.33</v>
@@ -5628,7 +5781,7 @@
         <v>0.01</v>
       </c>
       <c r="V32" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="W32">
         <v>1212.14</v>
@@ -5640,7 +5793,7 @@
         <v>0.01</v>
       </c>
       <c r="Z32" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="AA32">
         <v>1664</v>
@@ -5652,39 +5805,42 @@
         <v>0</v>
       </c>
       <c r="AD32" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AH32" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AL32" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AP32" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AT32" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AX32" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="BB32" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="BF32" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="BJ32" t="s">
-        <v>128</v>
+        <v>132</v>
+      </c>
+      <c r="BN32" t="s">
+        <v>133</v>
       </c>
     </row>
-    <row r="33" spans="1:62">
+    <row r="33" spans="1:66">
       <c r="A33" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B33" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C33">
         <v>243.29</v>
@@ -5696,7 +5852,7 @@
         <v>0.19</v>
       </c>
       <c r="F33" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G33">
         <v>455.57</v>
@@ -5708,7 +5864,7 @@
         <v>0.06</v>
       </c>
       <c r="J33" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="K33">
         <v>483.57</v>
@@ -5720,7 +5876,7 @@
         <v>0.06</v>
       </c>
       <c r="N33" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="O33">
         <v>490.71</v>
@@ -5732,7 +5888,7 @@
         <v>0.05</v>
       </c>
       <c r="R33" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="S33">
         <v>522.33</v>
@@ -5744,7 +5900,7 @@
         <v>0.05</v>
       </c>
       <c r="V33" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="W33">
         <v>324.29</v>
@@ -5756,7 +5912,7 @@
         <v>0.11</v>
       </c>
       <c r="Z33" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="AA33">
         <v>320.14</v>
@@ -5768,7 +5924,7 @@
         <v>0.11</v>
       </c>
       <c r="AD33" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AE33">
         <v>327.14</v>
@@ -5780,7 +5936,7 @@
         <v>0.11</v>
       </c>
       <c r="AH33" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AI33">
         <v>448.14</v>
@@ -5792,7 +5948,7 @@
         <v>0.06</v>
       </c>
       <c r="AL33" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AM33">
         <v>212.57</v>
@@ -5804,7 +5960,7 @@
         <v>0.14</v>
       </c>
       <c r="AP33" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AQ33">
         <v>302.17</v>
@@ -5816,7 +5972,7 @@
         <v>0.1</v>
       </c>
       <c r="AT33" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AU33">
         <v>370.33</v>
@@ -5828,24 +5984,27 @@
         <v>0.06</v>
       </c>
       <c r="AX33" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="BB33" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="BF33" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="BJ33" t="s">
-        <v>128</v>
+        <v>132</v>
+      </c>
+      <c r="BN33" t="s">
+        <v>133</v>
       </c>
     </row>
-    <row r="34" spans="1:62">
+    <row r="34" spans="1:66">
       <c r="A34" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B34" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C34">
         <v>8.85</v>
@@ -5857,7 +6016,7 @@
         <v>10.17</v>
       </c>
       <c r="F34" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G34">
         <v>8.699999999999999</v>
@@ -5869,7 +6028,7 @@
         <v>10.26</v>
       </c>
       <c r="J34" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="K34">
         <v>8.630000000000001</v>
@@ -5881,7 +6040,7 @@
         <v>10.38</v>
       </c>
       <c r="N34" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="O34">
         <v>8.619999999999999</v>
@@ -5893,7 +6052,7 @@
         <v>10.32</v>
       </c>
       <c r="R34" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="S34">
         <v>10.63</v>
@@ -5905,7 +6064,7 @@
         <v>8.359999999999999</v>
       </c>
       <c r="V34" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="W34">
         <v>11.67</v>
@@ -5917,7 +6076,7 @@
         <v>7.59</v>
       </c>
       <c r="Z34" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="AA34">
         <v>10.83</v>
@@ -5929,7 +6088,7 @@
         <v>8.19</v>
       </c>
       <c r="AD34" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AE34">
         <v>10.54</v>
@@ -5941,7 +6100,7 @@
         <v>8.529999999999999</v>
       </c>
       <c r="AH34" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AI34">
         <v>13.39</v>
@@ -5953,7 +6112,7 @@
         <v>6.62</v>
       </c>
       <c r="AL34" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AM34">
         <v>13.6</v>
@@ -5965,7 +6124,7 @@
         <v>6.09</v>
       </c>
       <c r="AP34" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AQ34">
         <v>15.52</v>
@@ -5977,7 +6136,7 @@
         <v>5.62</v>
       </c>
       <c r="AT34" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AU34">
         <v>13.95</v>
@@ -5989,7 +6148,7 @@
         <v>6.29</v>
       </c>
       <c r="AX34" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="AY34">
         <v>14.2</v>
@@ -6001,21 +6160,24 @@
         <v>6.3</v>
       </c>
       <c r="BB34" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="BF34" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="BJ34" t="s">
-        <v>128</v>
+        <v>132</v>
+      </c>
+      <c r="BN34" t="s">
+        <v>133</v>
       </c>
     </row>
-    <row r="35" spans="1:62">
+    <row r="35" spans="1:66">
       <c r="A35" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B35" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C35">
         <v>890.71</v>
@@ -6027,7 +6189,7 @@
         <v>0.02</v>
       </c>
       <c r="F35" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G35">
         <v>890.71</v>
@@ -6039,7 +6201,7 @@
         <v>0.02</v>
       </c>
       <c r="J35" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="K35">
         <v>890.71</v>
@@ -6051,7 +6213,7 @@
         <v>0.02</v>
       </c>
       <c r="N35" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="O35">
         <v>783.5700000000001</v>
@@ -6063,7 +6225,7 @@
         <v>0.02</v>
       </c>
       <c r="R35" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="S35">
         <v>789</v>
@@ -6075,7 +6237,7 @@
         <v>0.02</v>
       </c>
       <c r="V35" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="W35">
         <v>855</v>
@@ -6087,7 +6249,7 @@
         <v>0.02</v>
       </c>
       <c r="Z35" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="AA35">
         <v>855</v>
@@ -6099,7 +6261,7 @@
         <v>0.02</v>
       </c>
       <c r="AD35" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AE35">
         <v>855</v>
@@ -6111,36 +6273,39 @@
         <v>0.02</v>
       </c>
       <c r="AH35" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AL35" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AP35" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AT35" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AX35" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="BB35" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="BF35" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="BJ35" t="s">
-        <v>128</v>
+        <v>132</v>
+      </c>
+      <c r="BN35" t="s">
+        <v>133</v>
       </c>
     </row>
-    <row r="36" spans="1:62">
+    <row r="36" spans="1:66">
       <c r="A36" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B36" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C36">
         <v>249.71</v>
@@ -6152,7 +6317,7 @@
         <v>0.18</v>
       </c>
       <c r="F36" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G36">
         <v>242.57</v>
@@ -6164,7 +6329,7 @@
         <v>0.18</v>
       </c>
       <c r="J36" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="K36">
         <v>228.14</v>
@@ -6176,7 +6341,7 @@
         <v>0.2</v>
       </c>
       <c r="N36" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="O36">
         <v>216.71</v>
@@ -6188,7 +6353,7 @@
         <v>0.21</v>
       </c>
       <c r="R36" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="S36">
         <v>234.17</v>
@@ -6200,7 +6365,7 @@
         <v>0.19</v>
       </c>
       <c r="V36" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="W36">
         <v>305.57</v>
@@ -6212,7 +6377,7 @@
         <v>0.12</v>
       </c>
       <c r="Z36" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="AA36">
         <v>314.43</v>
@@ -6224,7 +6389,7 @@
         <v>0.11</v>
       </c>
       <c r="AD36" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AE36">
         <v>1569.29</v>
@@ -6236,7 +6401,7 @@
         <v>0.01</v>
       </c>
       <c r="AH36" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AI36">
         <v>2539</v>
@@ -6248,33 +6413,36 @@
         <v>0</v>
       </c>
       <c r="AL36" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AP36" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AT36" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AX36" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="BB36" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="BF36" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="BJ36" t="s">
-        <v>128</v>
+        <v>132</v>
+      </c>
+      <c r="BN36" t="s">
+        <v>133</v>
       </c>
     </row>
-    <row r="37" spans="1:62">
+    <row r="37" spans="1:66">
       <c r="A37" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B37" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C37">
         <v>141.29</v>
@@ -6286,7 +6454,7 @@
         <v>0.43</v>
       </c>
       <c r="F37" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G37">
         <v>145.57</v>
@@ -6298,7 +6466,7 @@
         <v>0.39</v>
       </c>
       <c r="J37" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="K37">
         <v>110.14</v>
@@ -6310,7 +6478,7 @@
         <v>0.59</v>
       </c>
       <c r="N37" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="O37">
         <v>105.86</v>
@@ -6322,7 +6490,7 @@
         <v>0.6</v>
       </c>
       <c r="R37" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="S37">
         <v>110</v>
@@ -6334,7 +6502,7 @@
         <v>0.59</v>
       </c>
       <c r="V37" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="W37">
         <v>171.86</v>
@@ -6346,7 +6514,7 @@
         <v>0.31</v>
       </c>
       <c r="Z37" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="AA37">
         <v>188.29</v>
@@ -6358,7 +6526,7 @@
         <v>0.26</v>
       </c>
       <c r="AD37" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AE37">
         <v>205.43</v>
@@ -6370,7 +6538,7 @@
         <v>0.25</v>
       </c>
       <c r="AH37" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AI37">
         <v>260.71</v>
@@ -6382,7 +6550,7 @@
         <v>0.16</v>
       </c>
       <c r="AL37" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AM37">
         <v>229.71</v>
@@ -6394,30 +6562,33 @@
         <v>0.12</v>
       </c>
       <c r="AP37" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AT37" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AX37" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="BB37" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="BF37" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="BJ37" t="s">
-        <v>128</v>
+        <v>132</v>
+      </c>
+      <c r="BN37" t="s">
+        <v>133</v>
       </c>
     </row>
-    <row r="38" spans="1:62">
+    <row r="38" spans="1:66">
       <c r="A38" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B38" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C38">
         <v>74.43000000000001</v>
@@ -6429,7 +6600,7 @@
         <v>0.99</v>
       </c>
       <c r="F38" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G38">
         <v>75.14</v>
@@ -6441,7 +6612,7 @@
         <v>0.95</v>
       </c>
       <c r="J38" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="K38">
         <v>83.56999999999999</v>
@@ -6453,7 +6624,7 @@
         <v>0.84</v>
       </c>
       <c r="N38" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="O38">
         <v>87.70999999999999</v>
@@ -6465,7 +6636,7 @@
         <v>0.77</v>
       </c>
       <c r="R38" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="S38">
         <v>78</v>
@@ -6477,7 +6648,7 @@
         <v>0.92</v>
       </c>
       <c r="V38" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="W38">
         <v>81.43000000000001</v>
@@ -6489,7 +6660,7 @@
         <v>0.86</v>
       </c>
       <c r="Z38" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="AA38">
         <v>80.14</v>
@@ -6501,7 +6672,7 @@
         <v>0.87</v>
       </c>
       <c r="AD38" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AE38">
         <v>76.43000000000001</v>
@@ -6513,7 +6684,7 @@
         <v>0.96</v>
       </c>
       <c r="AH38" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AI38">
         <v>73.70999999999999</v>
@@ -6525,7 +6696,7 @@
         <v>0.97</v>
       </c>
       <c r="AL38" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AM38">
         <v>78.70999999999999</v>
@@ -6537,7 +6708,7 @@
         <v>0.7</v>
       </c>
       <c r="AP38" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AQ38">
         <v>86.33</v>
@@ -6549,7 +6720,7 @@
         <v>0.73</v>
       </c>
       <c r="AT38" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AU38">
         <v>66</v>
@@ -6561,7 +6732,7 @@
         <v>1.01</v>
       </c>
       <c r="AX38" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="AY38">
         <v>71.33</v>
@@ -6573,7 +6744,7 @@
         <v>0.96</v>
       </c>
       <c r="BB38" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="BC38">
         <v>38.5</v>
@@ -6585,7 +6756,7 @@
         <v>2.01</v>
       </c>
       <c r="BF38" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="BG38">
         <v>37.83</v>
@@ -6597,15 +6768,18 @@
         <v>2.03</v>
       </c>
       <c r="BJ38" t="s">
-        <v>128</v>
+        <v>132</v>
+      </c>
+      <c r="BN38" t="s">
+        <v>133</v>
       </c>
     </row>
-    <row r="39" spans="1:62">
+    <row r="39" spans="1:66">
       <c r="A39" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B39" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C39">
         <v>101.29</v>
@@ -6617,7 +6791,7 @@
         <v>0.67</v>
       </c>
       <c r="F39" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G39">
         <v>106.14</v>
@@ -6629,7 +6803,7 @@
         <v>0.61</v>
       </c>
       <c r="J39" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="K39">
         <v>107.57</v>
@@ -6641,7 +6815,7 @@
         <v>0.61</v>
       </c>
       <c r="N39" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="O39">
         <v>119.57</v>
@@ -6653,7 +6827,7 @@
         <v>0.51</v>
       </c>
       <c r="R39" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="S39">
         <v>115.17</v>
@@ -6665,7 +6839,7 @@
         <v>0.55</v>
       </c>
       <c r="V39" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="W39">
         <v>125.86</v>
@@ -6677,7 +6851,7 @@
         <v>0.48</v>
       </c>
       <c r="Z39" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="AA39">
         <v>153.57</v>
@@ -6689,7 +6863,7 @@
         <v>0.36</v>
       </c>
       <c r="AD39" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AE39">
         <v>165.71</v>
@@ -6701,7 +6875,7 @@
         <v>0.34</v>
       </c>
       <c r="AH39" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AI39">
         <v>120.29</v>
@@ -6713,7 +6887,7 @@
         <v>0.51</v>
       </c>
       <c r="AL39" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AM39">
         <v>121.71</v>
@@ -6725,30 +6899,33 @@
         <v>0.36</v>
       </c>
       <c r="AP39" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AT39" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AX39" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="BB39" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="BF39" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="BJ39" t="s">
-        <v>128</v>
+        <v>132</v>
+      </c>
+      <c r="BN39" t="s">
+        <v>133</v>
       </c>
     </row>
-    <row r="40" spans="1:62">
+    <row r="40" spans="1:66">
       <c r="A40" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B40" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C40">
         <v>890.71</v>
@@ -6760,7 +6937,7 @@
         <v>0.02</v>
       </c>
       <c r="F40" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G40">
         <v>1176.43</v>
@@ -6772,7 +6949,7 @@
         <v>0.01</v>
       </c>
       <c r="J40" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="K40">
         <v>1176.43</v>
@@ -6784,7 +6961,7 @@
         <v>0.01</v>
       </c>
       <c r="N40" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="O40">
         <v>1176.43</v>
@@ -6796,7 +6973,7 @@
         <v>0.01</v>
       </c>
       <c r="R40" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="S40">
         <v>1205.67</v>
@@ -6808,7 +6985,7 @@
         <v>0.01</v>
       </c>
       <c r="V40" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="W40">
         <v>1247.86</v>
@@ -6820,7 +6997,7 @@
         <v>0.01</v>
       </c>
       <c r="Z40" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="AA40">
         <v>1247.86</v>
@@ -6832,7 +7009,7 @@
         <v>0.01</v>
       </c>
       <c r="AD40" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AE40">
         <v>569.29</v>
@@ -6844,7 +7021,7 @@
         <v>0.04</v>
       </c>
       <c r="AH40" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AI40">
         <v>630</v>
@@ -6856,33 +7033,36 @@
         <v>0.03</v>
       </c>
       <c r="AL40" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AP40" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AT40" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AX40" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="BB40" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="BF40" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="BJ40" t="s">
-        <v>128</v>
+        <v>132</v>
+      </c>
+      <c r="BN40" t="s">
+        <v>133</v>
       </c>
     </row>
-    <row r="41" spans="1:62">
+    <row r="41" spans="1:66">
       <c r="A41" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B41" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C41">
         <v>376.29</v>
@@ -6894,7 +7074,7 @@
         <v>0.09</v>
       </c>
       <c r="F41" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G41">
         <v>241</v>
@@ -6906,7 +7086,7 @@
         <v>0.18</v>
       </c>
       <c r="J41" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="K41">
         <v>224.29</v>
@@ -6918,7 +7098,7 @@
         <v>0.21</v>
       </c>
       <c r="N41" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="O41">
         <v>234</v>
@@ -6930,7 +7110,7 @@
         <v>0.18</v>
       </c>
       <c r="R41" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="S41">
         <v>256.33</v>
@@ -6942,7 +7122,7 @@
         <v>0.17</v>
       </c>
       <c r="V41" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="W41">
         <v>293.57</v>
@@ -6954,7 +7134,7 @@
         <v>0.13</v>
       </c>
       <c r="Z41" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="AA41">
         <v>288</v>
@@ -6966,7 +7146,7 @@
         <v>0.13</v>
       </c>
       <c r="AD41" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AE41">
         <v>570</v>
@@ -6978,7 +7158,7 @@
         <v>0.04</v>
       </c>
       <c r="AH41" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AI41">
         <v>964</v>
@@ -6990,33 +7170,36 @@
         <v>0.01</v>
       </c>
       <c r="AL41" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AP41" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AT41" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AX41" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="BB41" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="BF41" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="BJ41" t="s">
-        <v>128</v>
+        <v>132</v>
+      </c>
+      <c r="BN41" t="s">
+        <v>133</v>
       </c>
     </row>
-    <row r="42" spans="1:62">
+    <row r="42" spans="1:66">
       <c r="A42" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B42" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C42">
         <v>299.29</v>
@@ -7028,7 +7211,7 @@
         <v>0.14</v>
       </c>
       <c r="F42" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G42">
         <v>497.86</v>
@@ -7040,7 +7223,7 @@
         <v>0.05</v>
       </c>
       <c r="J42" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="K42">
         <v>486.71</v>
@@ -7052,7 +7235,7 @@
         <v>0.06</v>
       </c>
       <c r="N42" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="O42">
         <v>497.86</v>
@@ -7064,7 +7247,7 @@
         <v>0.05</v>
       </c>
       <c r="R42" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="S42">
         <v>572.33</v>
@@ -7076,7 +7259,7 @@
         <v>0.04</v>
       </c>
       <c r="V42" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="W42">
         <v>547.86</v>
@@ -7088,7 +7271,7 @@
         <v>0.04</v>
       </c>
       <c r="Z42" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="AA42">
         <v>583.5700000000001</v>
@@ -7100,39 +7283,42 @@
         <v>0.04</v>
       </c>
       <c r="AD42" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AH42" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AL42" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AP42" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AT42" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AX42" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="BB42" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="BF42" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="BJ42" t="s">
-        <v>128</v>
+        <v>132</v>
+      </c>
+      <c r="BN42" t="s">
+        <v>133</v>
       </c>
     </row>
-    <row r="43" spans="1:62">
+    <row r="43" spans="1:66">
       <c r="A43" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B43" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C43">
         <v>605</v>
@@ -7144,7 +7330,7 @@
         <v>0.04</v>
       </c>
       <c r="F43" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G43">
         <v>640.71</v>
@@ -7156,7 +7342,7 @@
         <v>0.03</v>
       </c>
       <c r="J43" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="K43">
         <v>890.71</v>
@@ -7168,7 +7354,7 @@
         <v>0.02</v>
       </c>
       <c r="N43" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="O43">
         <v>926.4299999999999</v>
@@ -7180,7 +7366,7 @@
         <v>0.01</v>
       </c>
       <c r="R43" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="S43">
         <v>955.67</v>
@@ -7192,45 +7378,48 @@
         <v>0.01</v>
       </c>
       <c r="V43" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="Z43" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="AD43" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AH43" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AL43" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AP43" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AT43" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AX43" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="BB43" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="BF43" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="BJ43" t="s">
-        <v>128</v>
+        <v>132</v>
+      </c>
+      <c r="BN43" t="s">
+        <v>133</v>
       </c>
     </row>
-    <row r="44" spans="1:62">
+    <row r="44" spans="1:66">
       <c r="A44" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B44" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C44">
         <v>80</v>
@@ -7242,7 +7431,7 @@
         <v>0.91</v>
       </c>
       <c r="F44" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G44">
         <v>80</v>
@@ -7254,7 +7443,7 @@
         <v>0.88</v>
       </c>
       <c r="J44" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="K44">
         <v>133.14</v>
@@ -7266,7 +7455,7 @@
         <v>0.46</v>
       </c>
       <c r="N44" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="O44">
         <v>145.86</v>
@@ -7278,7 +7467,7 @@
         <v>0.38</v>
       </c>
       <c r="R44" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="S44">
         <v>152.33</v>
@@ -7290,45 +7479,48 @@
         <v>0.37</v>
       </c>
       <c r="V44" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="Z44" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="AD44" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AH44" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AL44" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AP44" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AT44" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AX44" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="BB44" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="BF44" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="BJ44" t="s">
-        <v>128</v>
+        <v>132</v>
+      </c>
+      <c r="BN44" t="s">
+        <v>133</v>
       </c>
     </row>
-    <row r="45" spans="1:62">
+    <row r="45" spans="1:66">
       <c r="A45" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B45" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C45">
         <v>63.71</v>
@@ -7340,7 +7532,7 @@
         <v>1.2</v>
       </c>
       <c r="F45" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G45">
         <v>44.57</v>
@@ -7352,7 +7544,7 @@
         <v>1.78</v>
       </c>
       <c r="J45" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="K45">
         <v>43.86</v>
@@ -7364,7 +7556,7 @@
         <v>1.82</v>
       </c>
       <c r="N45" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="O45">
         <v>41.14</v>
@@ -7376,7 +7568,7 @@
         <v>1.93</v>
       </c>
       <c r="R45" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="S45">
         <v>42</v>
@@ -7388,7 +7580,7 @@
         <v>1.91</v>
       </c>
       <c r="V45" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="W45">
         <v>31.43</v>
@@ -7400,7 +7592,7 @@
         <v>2.63</v>
       </c>
       <c r="Z45" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="AA45">
         <v>32.14</v>
@@ -7412,7 +7604,7 @@
         <v>2.56</v>
       </c>
       <c r="AD45" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AE45">
         <v>28.29</v>
@@ -7424,7 +7616,7 @@
         <v>3.01</v>
       </c>
       <c r="AH45" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AI45">
         <v>31</v>
@@ -7436,7 +7628,7 @@
         <v>2.68</v>
       </c>
       <c r="AL45" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AM45">
         <v>32.57</v>
@@ -7448,7 +7640,7 @@
         <v>2.25</v>
       </c>
       <c r="AP45" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AQ45">
         <v>29.17</v>
@@ -7460,7 +7652,7 @@
         <v>2.8</v>
       </c>
       <c r="AT45" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AU45">
         <v>29.83</v>
@@ -7472,7 +7664,7 @@
         <v>2.7</v>
       </c>
       <c r="AX45" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="AY45">
         <v>28.83</v>
@@ -7484,21 +7676,24 @@
         <v>2.89</v>
       </c>
       <c r="BB45" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="BF45" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="BJ45" t="s">
-        <v>128</v>
+        <v>132</v>
+      </c>
+      <c r="BN45" t="s">
+        <v>133</v>
       </c>
     </row>
-    <row r="46" spans="1:62">
+    <row r="46" spans="1:66">
       <c r="A46" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B46" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C46">
         <v>71.14</v>
@@ -7510,7 +7705,7 @@
         <v>1.05</v>
       </c>
       <c r="F46" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G46">
         <v>75.29000000000001</v>
@@ -7522,7 +7717,7 @@
         <v>0.95</v>
       </c>
       <c r="J46" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="K46">
         <v>75.29000000000001</v>
@@ -7534,7 +7729,7 @@
         <v>0.96</v>
       </c>
       <c r="N46" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="O46">
         <v>83</v>
@@ -7546,7 +7741,7 @@
         <v>0.83</v>
       </c>
       <c r="R46" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="S46">
         <v>88.83</v>
@@ -7558,7 +7753,7 @@
         <v>0.78</v>
       </c>
       <c r="V46" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="W46">
         <v>162.86</v>
@@ -7570,7 +7765,7 @@
         <v>0.33</v>
       </c>
       <c r="Z46" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="AA46">
         <v>190</v>
@@ -7582,7 +7777,7 @@
         <v>0.26</v>
       </c>
       <c r="AD46" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AE46">
         <v>216.57</v>
@@ -7594,36 +7789,39 @@
         <v>0.23</v>
       </c>
       <c r="AH46" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AL46" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AP46" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AT46" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AX46" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="BB46" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="BF46" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="BJ46" t="s">
-        <v>128</v>
+        <v>132</v>
+      </c>
+      <c r="BN46" t="s">
+        <v>133</v>
       </c>
     </row>
-    <row r="47" spans="1:62">
+    <row r="47" spans="1:66">
       <c r="A47" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B47" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C47">
         <v>1197.86</v>
@@ -7635,7 +7833,7 @@
         <v>0.01</v>
       </c>
       <c r="F47" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G47">
         <v>1197.86</v>
@@ -7647,7 +7845,7 @@
         <v>0.01</v>
       </c>
       <c r="J47" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="K47">
         <v>1197.86</v>
@@ -7659,7 +7857,7 @@
         <v>0.01</v>
       </c>
       <c r="N47" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="O47">
         <v>1197.86</v>
@@ -7671,7 +7869,7 @@
         <v>0.01</v>
       </c>
       <c r="R47" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="S47">
         <v>1296.6</v>
@@ -7683,7 +7881,7 @@
         <v>0.01</v>
       </c>
       <c r="V47" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="W47">
         <v>1247.33</v>
@@ -7695,7 +7893,7 @@
         <v>0.01</v>
       </c>
       <c r="Z47" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="AA47">
         <v>1212.14</v>
@@ -7707,7 +7905,7 @@
         <v>0.01</v>
       </c>
       <c r="AD47" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AE47">
         <v>1355</v>
@@ -7719,7 +7917,7 @@
         <v>0.01</v>
       </c>
       <c r="AH47" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AI47">
         <v>2330.67</v>
@@ -7731,33 +7929,36 @@
         <v>0</v>
       </c>
       <c r="AL47" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AP47" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AT47" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AX47" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="BB47" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="BF47" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="BJ47" t="s">
-        <v>128</v>
+        <v>132</v>
+      </c>
+      <c r="BN47" t="s">
+        <v>133</v>
       </c>
     </row>
-    <row r="48" spans="1:62">
+    <row r="48" spans="1:66">
       <c r="A48" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B48" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C48">
         <v>320.43</v>
@@ -7769,7 +7970,7 @@
         <v>0.12</v>
       </c>
       <c r="F48" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G48">
         <v>351.57</v>
@@ -7781,7 +7982,7 @@
         <v>0.1</v>
       </c>
       <c r="J48" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="K48">
         <v>341.71</v>
@@ -7793,7 +7994,7 @@
         <v>0.1</v>
       </c>
       <c r="N48" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="O48">
         <v>283.71</v>
@@ -7805,7 +8006,7 @@
         <v>0.13</v>
       </c>
       <c r="R48" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="S48">
         <v>302.5</v>
@@ -7817,7 +8018,7 @@
         <v>0.13</v>
       </c>
       <c r="V48" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="W48">
         <v>261.14</v>
@@ -7829,7 +8030,7 @@
         <v>0.16</v>
       </c>
       <c r="Z48" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="AA48">
         <v>232.57</v>
@@ -7841,7 +8042,7 @@
         <v>0.19</v>
       </c>
       <c r="AD48" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AE48">
         <v>260.71</v>
@@ -7853,7 +8054,7 @@
         <v>0.17</v>
       </c>
       <c r="AH48" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AI48">
         <v>273.57</v>
@@ -7865,7 +8066,7 @@
         <v>0.14</v>
       </c>
       <c r="AL48" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AM48">
         <v>287.86</v>
@@ -7877,7 +8078,7 @@
         <v>0.08</v>
       </c>
       <c r="AP48" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AQ48">
         <v>300.5</v>
@@ -7889,7 +8090,7 @@
         <v>0.1</v>
       </c>
       <c r="AT48" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AU48">
         <v>272.33</v>
@@ -7901,7 +8102,7 @@
         <v>0.11</v>
       </c>
       <c r="AX48" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="AY48">
         <v>257.83</v>
@@ -7913,21 +8114,24 @@
         <v>0.13</v>
       </c>
       <c r="BB48" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="BF48" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="BJ48" t="s">
-        <v>128</v>
+        <v>132</v>
+      </c>
+      <c r="BN48" t="s">
+        <v>133</v>
       </c>
     </row>
-    <row r="49" spans="1:62">
+    <row r="49" spans="1:66">
       <c r="A49" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B49" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C49">
         <v>153</v>
@@ -7939,7 +8143,7 @@
         <v>0.39</v>
       </c>
       <c r="F49" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G49">
         <v>158.57</v>
@@ -7951,7 +8155,7 @@
         <v>0.35</v>
       </c>
       <c r="J49" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="K49">
         <v>157.14</v>
@@ -7963,7 +8167,7 @@
         <v>0.36</v>
       </c>
       <c r="N49" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="O49">
         <v>135.14</v>
@@ -7975,7 +8179,7 @@
         <v>0.43</v>
       </c>
       <c r="R49" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="S49">
         <v>144</v>
@@ -7987,7 +8191,7 @@
         <v>0.4</v>
       </c>
       <c r="V49" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="W49">
         <v>139.29</v>
@@ -7999,7 +8203,7 @@
         <v>0.42</v>
       </c>
       <c r="Z49" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="AA49">
         <v>187.29</v>
@@ -8011,7 +8215,7 @@
         <v>0.26</v>
       </c>
       <c r="AD49" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AE49">
         <v>181.14</v>
@@ -8023,7 +8227,7 @@
         <v>0.3</v>
       </c>
       <c r="AH49" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AI49">
         <v>272.29</v>
@@ -8035,7 +8239,7 @@
         <v>0.14</v>
       </c>
       <c r="AL49" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AM49">
         <v>284.86</v>
@@ -8047,7 +8251,7 @@
         <v>0.08</v>
       </c>
       <c r="AP49" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AQ49">
         <v>333.67</v>
@@ -8059,19 +8263,22 @@
         <v>0.08</v>
       </c>
       <c r="AT49" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AX49" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="BB49" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="BF49" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="BJ49" t="s">
-        <v>128</v>
+        <v>132</v>
+      </c>
+      <c r="BN49" t="s">
+        <v>133</v>
       </c>
     </row>
   </sheetData>

--- a/processed_data_during_wm/processed_data_wide.xlsx
+++ b/processed_data_during_wm/processed_data_wide.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="933" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="985" uniqueCount="139">
   <si>
     <t>Team</t>
   </si>
@@ -223,48 +223,60 @@
     <t>Shin_Wahrscheinlichkeit_in_Prozent_17</t>
   </si>
   <si>
+    <t>Datum_18</t>
+  </si>
+  <si>
+    <t>Durchsch_Quote_18</t>
+  </si>
+  <si>
+    <t>Norm_Wahrscheinlichkeit_in_Prozent_18</t>
+  </si>
+  <si>
+    <t>Shin_Wahrscheinlichkeit_in_Prozent_18</t>
+  </si>
+  <si>
+    <t>Spanien</t>
+  </si>
+  <si>
+    <t>Argentinien</t>
+  </si>
+  <si>
+    <t>Algerien</t>
+  </si>
+  <si>
+    <t>Australien</t>
+  </si>
+  <si>
+    <t>Belgien</t>
+  </si>
+  <si>
+    <t>Bosnien Herzegowina</t>
+  </si>
+  <si>
+    <t>Brasilien</t>
+  </si>
+  <si>
+    <t>Curacao</t>
+  </si>
+  <si>
+    <t>DR Kongo</t>
+  </si>
+  <si>
+    <t>Deutschland</t>
+  </si>
+  <si>
+    <t>Ecuador</t>
+  </si>
+  <si>
+    <t>Elfenbeinküste</t>
+  </si>
+  <si>
+    <t>England</t>
+  </si>
+  <si>
     <t>Frankreich</t>
   </si>
   <si>
-    <t>Spanien</t>
-  </si>
-  <si>
-    <t>England</t>
-  </si>
-  <si>
-    <t>Argentinien</t>
-  </si>
-  <si>
-    <t>Algerien</t>
-  </si>
-  <si>
-    <t>Australien</t>
-  </si>
-  <si>
-    <t>Belgien</t>
-  </si>
-  <si>
-    <t>Bosnien Herzegowina</t>
-  </si>
-  <si>
-    <t>Brasilien</t>
-  </si>
-  <si>
-    <t>Curacao</t>
-  </si>
-  <si>
-    <t>DR Kongo</t>
-  </si>
-  <si>
-    <t>Deutschland</t>
-  </si>
-  <si>
-    <t>Ecuador</t>
-  </si>
-  <si>
-    <t>Elfenbeinküste</t>
-  </si>
-  <si>
     <t>Ghana</t>
   </si>
   <si>
@@ -416,6 +428,9 @@
   </si>
   <si>
     <t>14.07.2026</t>
+  </si>
+  <si>
+    <t>16.07.2026</t>
   </si>
 </sst>
 </file>
@@ -773,10 +788,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BQ49"/>
+  <dimension ref="A1:BU49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:69">
+    <row r="1" spans="1:73">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -984,2372 +999,2444 @@
       <c r="BQ1" s="1" t="s">
         <v>68</v>
       </c>
+      <c r="BR1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="BS1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="BT1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="BU1" s="1" t="s">
+        <v>72</v>
+      </c>
     </row>
-    <row r="2" spans="1:69">
+    <row r="2" spans="1:73">
       <c r="A2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C2">
+        <v>5.58</v>
+      </c>
+      <c r="D2">
+        <v>15.22</v>
+      </c>
+      <c r="E2">
+        <v>16.29</v>
+      </c>
+      <c r="F2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G2">
+        <v>5.63</v>
+      </c>
+      <c r="H2">
+        <v>14.94</v>
+      </c>
+      <c r="I2">
+        <v>16.04</v>
+      </c>
+      <c r="J2" t="s">
+        <v>123</v>
+      </c>
+      <c r="K2">
+        <v>5.63</v>
+      </c>
+      <c r="L2">
+        <v>14.99</v>
+      </c>
+      <c r="M2">
+        <v>16.07</v>
+      </c>
+      <c r="N2" t="s">
+        <v>124</v>
+      </c>
+      <c r="O2">
+        <v>6.51</v>
+      </c>
+      <c r="P2">
+        <v>12.83</v>
+      </c>
+      <c r="Q2">
+        <v>13.76</v>
+      </c>
+      <c r="R2" t="s">
+        <v>125</v>
+      </c>
+      <c r="S2">
+        <v>6.88</v>
+      </c>
+      <c r="T2">
+        <v>12.25</v>
+      </c>
+      <c r="U2">
+        <v>13.09</v>
+      </c>
+      <c r="V2" t="s">
+        <v>126</v>
+      </c>
+      <c r="W2">
+        <v>6.34</v>
+      </c>
+      <c r="X2">
+        <v>13.32</v>
+      </c>
+      <c r="Y2">
+        <v>14.23</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>127</v>
+      </c>
+      <c r="AA2">
+        <v>6.48</v>
+      </c>
+      <c r="AB2">
+        <v>13.01</v>
+      </c>
+      <c r="AC2">
+        <v>13.89</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE2">
+        <v>6.63</v>
+      </c>
+      <c r="AF2">
+        <v>12.98</v>
+      </c>
+      <c r="AG2">
+        <v>13.74</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>129</v>
+      </c>
+      <c r="AI2">
+        <v>8.02</v>
+      </c>
+      <c r="AJ2">
+        <v>10.7</v>
+      </c>
+      <c r="AK2">
+        <v>11.26</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>130</v>
+      </c>
+      <c r="AM2">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="AN2">
+        <v>9.94</v>
+      </c>
+      <c r="AO2">
+        <v>10.55</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>131</v>
+      </c>
+      <c r="AQ2">
+        <v>8.59</v>
+      </c>
+      <c r="AR2">
+        <v>10.2</v>
+      </c>
+      <c r="AS2">
+        <v>10.5</v>
+      </c>
+      <c r="AT2" t="s">
+        <v>132</v>
+      </c>
+      <c r="AU2">
+        <v>7.04</v>
+      </c>
+      <c r="AV2">
+        <v>12.57</v>
+      </c>
+      <c r="AW2">
+        <v>12.93</v>
+      </c>
+      <c r="AX2" t="s">
+        <v>133</v>
+      </c>
+      <c r="AY2">
+        <v>6.98</v>
+      </c>
+      <c r="AZ2">
+        <v>13.01</v>
+      </c>
+      <c r="BA2">
+        <v>13.27</v>
+      </c>
+      <c r="BB2" t="s">
+        <v>134</v>
+      </c>
+      <c r="BC2">
+        <v>4.75</v>
+      </c>
+      <c r="BD2">
+        <v>19.55</v>
+      </c>
+      <c r="BE2">
+        <v>19.84</v>
+      </c>
+      <c r="BF2" t="s">
+        <v>135</v>
+      </c>
+      <c r="BG2">
+        <v>5.25</v>
+      </c>
+      <c r="BH2">
+        <v>17.79</v>
+      </c>
+      <c r="BI2">
+        <v>17.91</v>
+      </c>
+      <c r="BJ2" t="s">
+        <v>136</v>
+      </c>
+      <c r="BK2">
+        <v>4.36</v>
+      </c>
+      <c r="BL2">
+        <v>21.73</v>
+      </c>
+      <c r="BM2">
+        <v>21.61</v>
+      </c>
+      <c r="BN2" t="s">
+        <v>137</v>
+      </c>
+      <c r="BO2">
+        <v>4.33</v>
+      </c>
+      <c r="BP2">
+        <v>21.87</v>
+      </c>
+      <c r="BQ2">
+        <v>21.75</v>
+      </c>
+      <c r="BR2" t="s">
+        <v>138</v>
+      </c>
+      <c r="BS2">
+        <v>1.64</v>
+      </c>
+      <c r="BT2">
+        <v>58.06</v>
+      </c>
+      <c r="BU2">
+        <v>58.47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:73">
+      <c r="A3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C3">
+        <v>10.19</v>
+      </c>
+      <c r="D3">
+        <v>8.34</v>
+      </c>
+      <c r="E3">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="F3" t="s">
+        <v>122</v>
+      </c>
+      <c r="G3">
+        <v>10.33</v>
+      </c>
+      <c r="H3">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="I3">
+        <v>8.6</v>
+      </c>
+      <c r="J3" t="s">
+        <v>123</v>
+      </c>
+      <c r="K3">
+        <v>10.61</v>
+      </c>
+      <c r="L3">
+        <v>7.95</v>
+      </c>
+      <c r="M3">
+        <v>8.390000000000001</v>
+      </c>
+      <c r="N3" t="s">
+        <v>124</v>
+      </c>
+      <c r="O3">
+        <v>9.4</v>
+      </c>
+      <c r="P3">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="Q3">
+        <v>9.44</v>
+      </c>
+      <c r="R3" t="s">
+        <v>125</v>
+      </c>
+      <c r="S3">
+        <v>9.140000000000001</v>
+      </c>
+      <c r="T3">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="U3">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="V3" t="s">
+        <v>126</v>
+      </c>
+      <c r="W3">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="X3">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="Y3">
+        <v>10.27</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>127</v>
+      </c>
+      <c r="AA3">
+        <v>7.45</v>
+      </c>
+      <c r="AB3">
+        <v>11.32</v>
+      </c>
+      <c r="AC3">
+        <v>12.04</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE3">
+        <v>7.04</v>
+      </c>
+      <c r="AF3">
+        <v>12.21</v>
+      </c>
+      <c r="AG3">
+        <v>12.92</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>129</v>
+      </c>
+      <c r="AI3">
+        <v>5.2</v>
+      </c>
+      <c r="AJ3">
+        <v>16.49</v>
+      </c>
+      <c r="AK3">
+        <v>17.53</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>130</v>
+      </c>
+      <c r="AM3">
+        <v>4.84</v>
+      </c>
+      <c r="AN3">
+        <v>16.71</v>
+      </c>
+      <c r="AO3">
+        <v>18.12</v>
+      </c>
+      <c r="AP3" t="s">
+        <v>131</v>
+      </c>
+      <c r="AQ3">
+        <v>5.11</v>
+      </c>
+      <c r="AR3">
+        <v>17.14</v>
+      </c>
+      <c r="AS3">
+        <v>17.95</v>
+      </c>
+      <c r="AT3" t="s">
+        <v>132</v>
+      </c>
+      <c r="AU3">
+        <v>5.31</v>
+      </c>
+      <c r="AV3">
+        <v>16.67</v>
+      </c>
+      <c r="AW3">
+        <v>17.31</v>
+      </c>
+      <c r="AX3" t="s">
+        <v>133</v>
+      </c>
+      <c r="AY3">
+        <v>5.53</v>
+      </c>
+      <c r="AZ3">
+        <v>16.42</v>
+      </c>
+      <c r="BA3">
+        <v>16.85</v>
+      </c>
+      <c r="BB3" t="s">
+        <v>134</v>
+      </c>
+      <c r="BC3">
+        <v>5.05</v>
+      </c>
+      <c r="BD3">
+        <v>18.4</v>
+      </c>
+      <c r="BE3">
+        <v>18.63</v>
+      </c>
+      <c r="BF3" t="s">
+        <v>135</v>
+      </c>
+      <c r="BG3">
+        <v>5.34</v>
+      </c>
+      <c r="BH3">
+        <v>17.51</v>
+      </c>
+      <c r="BI3">
+        <v>17.62</v>
+      </c>
+      <c r="BJ3" t="s">
+        <v>136</v>
+      </c>
+      <c r="BK3">
+        <v>4.96</v>
+      </c>
+      <c r="BL3">
+        <v>19.11</v>
+      </c>
+      <c r="BM3">
+        <v>18.89</v>
+      </c>
+      <c r="BN3" t="s">
+        <v>137</v>
+      </c>
+      <c r="BO3">
+        <v>5.41</v>
+      </c>
+      <c r="BP3">
+        <v>17.5</v>
+      </c>
+      <c r="BQ3">
+        <v>17.22</v>
+      </c>
+      <c r="BR3" t="s">
+        <v>138</v>
+      </c>
+      <c r="BS3">
+        <v>2.27</v>
+      </c>
+      <c r="BT3">
+        <v>41.94</v>
+      </c>
+      <c r="BU3">
+        <v>41.53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:73">
+      <c r="A4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C4">
+        <v>367.57</v>
+      </c>
+      <c r="D4">
+        <v>0.23</v>
+      </c>
+      <c r="E4">
+        <v>0.1</v>
+      </c>
+      <c r="F4" t="s">
+        <v>122</v>
+      </c>
+      <c r="G4">
+        <v>383</v>
+      </c>
+      <c r="H4">
+        <v>0.22</v>
+      </c>
+      <c r="I4">
+        <v>0.08</v>
+      </c>
+      <c r="J4" t="s">
+        <v>123</v>
+      </c>
+      <c r="K4">
+        <v>378.86</v>
+      </c>
+      <c r="L4">
+        <v>0.22</v>
+      </c>
+      <c r="M4">
+        <v>0.09</v>
+      </c>
+      <c r="N4" t="s">
+        <v>124</v>
+      </c>
+      <c r="O4">
+        <v>474.57</v>
+      </c>
+      <c r="P4">
+        <v>0.18</v>
+      </c>
+      <c r="Q4">
+        <v>0.05</v>
+      </c>
+      <c r="R4" t="s">
+        <v>125</v>
+      </c>
+      <c r="S4">
+        <v>530.67</v>
+      </c>
+      <c r="T4">
+        <v>0.16</v>
+      </c>
+      <c r="U4">
+        <v>0.05</v>
+      </c>
+      <c r="V4" t="s">
+        <v>126</v>
+      </c>
+      <c r="W4">
+        <v>518</v>
+      </c>
+      <c r="X4">
+        <v>0.16</v>
+      </c>
+      <c r="Y4">
+        <v>0.05</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>127</v>
+      </c>
+      <c r="AA4">
+        <v>529.5700000000001</v>
+      </c>
+      <c r="AB4">
+        <v>0.16</v>
+      </c>
+      <c r="AC4">
+        <v>0.04</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE4">
+        <v>576.4299999999999</v>
+      </c>
+      <c r="AF4">
+        <v>0.15</v>
+      </c>
+      <c r="AG4">
+        <v>0.04</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>129</v>
+      </c>
+      <c r="AI4">
+        <v>458.71</v>
+      </c>
+      <c r="AJ4">
+        <v>0.19</v>
+      </c>
+      <c r="AK4">
+        <v>0.06</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>130</v>
+      </c>
+      <c r="AM4">
+        <v>391.29</v>
+      </c>
+      <c r="AN4">
+        <v>0.21</v>
+      </c>
+      <c r="AO4">
+        <v>0.04</v>
+      </c>
+      <c r="AP4" t="s">
+        <v>131</v>
+      </c>
+      <c r="AQ4">
+        <v>437.83</v>
+      </c>
+      <c r="AR4">
+        <v>0.2</v>
+      </c>
+      <c r="AS4">
+        <v>0.05</v>
+      </c>
+      <c r="AT4" t="s">
+        <v>132</v>
+      </c>
+      <c r="AX4" t="s">
+        <v>133</v>
+      </c>
+      <c r="BB4" t="s">
+        <v>134</v>
+      </c>
+      <c r="BF4" t="s">
+        <v>135</v>
+      </c>
+      <c r="BJ4" t="s">
+        <v>136</v>
+      </c>
+      <c r="BN4" t="s">
+        <v>137</v>
+      </c>
+      <c r="BR4" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="5" spans="1:73">
+      <c r="A5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B5" t="s">
+        <v>121</v>
+      </c>
+      <c r="C5">
+        <v>442.71</v>
+      </c>
+      <c r="D5">
+        <v>0.19</v>
+      </c>
+      <c r="E5">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="F5" t="s">
+        <v>122</v>
+      </c>
+      <c r="G5">
+        <v>462.29</v>
+      </c>
+      <c r="H5">
+        <v>0.18</v>
+      </c>
+      <c r="I5">
+        <v>0.06</v>
+      </c>
+      <c r="J5" t="s">
+        <v>123</v>
+      </c>
+      <c r="K5">
+        <v>186</v>
+      </c>
+      <c r="L5">
+        <v>0.45</v>
+      </c>
+      <c r="M5">
+        <v>0.28</v>
+      </c>
+      <c r="N5" t="s">
+        <v>124</v>
+      </c>
+      <c r="O5">
+        <v>123.14</v>
+      </c>
+      <c r="P5">
+        <v>0.68</v>
+      </c>
+      <c r="Q5">
+        <v>0.49</v>
+      </c>
+      <c r="R5" t="s">
+        <v>125</v>
+      </c>
+      <c r="S5">
+        <v>128.5</v>
+      </c>
+      <c r="T5">
+        <v>0.66</v>
+      </c>
+      <c r="U5">
+        <v>0.47</v>
+      </c>
+      <c r="V5" t="s">
+        <v>126</v>
+      </c>
+      <c r="W5">
+        <v>174.43</v>
+      </c>
+      <c r="X5">
+        <v>0.48</v>
+      </c>
+      <c r="Y5">
+        <v>0.3</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>127</v>
+      </c>
+      <c r="AA5">
+        <v>206.33</v>
+      </c>
+      <c r="AB5">
+        <v>0.41</v>
+      </c>
+      <c r="AC5">
+        <v>0.23</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE5">
+        <v>199.83</v>
+      </c>
+      <c r="AF5">
+        <v>0.43</v>
+      </c>
+      <c r="AG5">
+        <v>0.26</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>129</v>
+      </c>
+      <c r="AI5">
+        <v>249.14</v>
+      </c>
+      <c r="AJ5">
+        <v>0.34</v>
+      </c>
+      <c r="AK5">
+        <v>0.17</v>
+      </c>
+      <c r="AL5" t="s">
+        <v>130</v>
+      </c>
+      <c r="AM5">
+        <v>290.57</v>
+      </c>
+      <c r="AN5">
+        <v>0.28</v>
+      </c>
+      <c r="AO5">
+        <v>0.08</v>
+      </c>
+      <c r="AP5" t="s">
+        <v>131</v>
+      </c>
+      <c r="AQ5">
+        <v>333.67</v>
+      </c>
+      <c r="AR5">
+        <v>0.26</v>
+      </c>
+      <c r="AS5">
+        <v>0.08</v>
+      </c>
+      <c r="AT5" t="s">
+        <v>132</v>
+      </c>
+      <c r="AX5" t="s">
+        <v>133</v>
+      </c>
+      <c r="BB5" t="s">
+        <v>134</v>
+      </c>
+      <c r="BF5" t="s">
+        <v>135</v>
+      </c>
+      <c r="BJ5" t="s">
+        <v>136</v>
+      </c>
+      <c r="BN5" t="s">
+        <v>137</v>
+      </c>
+      <c r="BR5" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="6" spans="1:73">
+      <c r="A6" t="s">
+        <v>77</v>
+      </c>
+      <c r="B6" t="s">
+        <v>121</v>
+      </c>
+      <c r="C6">
+        <v>37.71</v>
+      </c>
+      <c r="D6">
+        <v>2.25</v>
+      </c>
+      <c r="E6">
+        <v>2.19</v>
+      </c>
+      <c r="F6" t="s">
+        <v>122</v>
+      </c>
+      <c r="G6">
+        <v>37.71</v>
+      </c>
+      <c r="H6">
+        <v>2.23</v>
+      </c>
+      <c r="I6">
+        <v>2.15</v>
+      </c>
+      <c r="J6" t="s">
+        <v>123</v>
+      </c>
+      <c r="K6">
+        <v>39.43</v>
+      </c>
+      <c r="L6">
+        <v>2.14</v>
+      </c>
+      <c r="M6">
+        <v>2.06</v>
+      </c>
+      <c r="N6" t="s">
+        <v>124</v>
+      </c>
+      <c r="O6">
+        <v>42</v>
+      </c>
+      <c r="P6">
+        <v>1.99</v>
+      </c>
+      <c r="Q6">
+        <v>1.88</v>
+      </c>
+      <c r="R6" t="s">
+        <v>125</v>
+      </c>
+      <c r="S6">
+        <v>42.17</v>
+      </c>
+      <c r="T6">
+        <v>2</v>
+      </c>
+      <c r="U6">
+        <v>1.9</v>
+      </c>
+      <c r="V6" t="s">
+        <v>126</v>
+      </c>
+      <c r="W6">
+        <v>47.71</v>
+      </c>
+      <c r="X6">
+        <v>1.77</v>
+      </c>
+      <c r="Y6">
+        <v>1.64</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>127</v>
+      </c>
+      <c r="AA6">
+        <v>52.71</v>
+      </c>
+      <c r="AB6">
+        <v>1.6</v>
+      </c>
+      <c r="AC6">
+        <v>1.45</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE6">
+        <v>54.14</v>
+      </c>
+      <c r="AF6">
+        <v>1.59</v>
+      </c>
+      <c r="AG6">
+        <v>1.45</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>129</v>
+      </c>
+      <c r="AI6">
+        <v>49.14</v>
+      </c>
+      <c r="AJ6">
+        <v>1.75</v>
+      </c>
+      <c r="AK6">
+        <v>1.59</v>
+      </c>
+      <c r="AL6" t="s">
+        <v>130</v>
+      </c>
+      <c r="AM6">
+        <v>52</v>
+      </c>
+      <c r="AN6">
+        <v>1.55</v>
+      </c>
+      <c r="AO6">
+        <v>1.25</v>
+      </c>
+      <c r="AP6" t="s">
+        <v>131</v>
+      </c>
+      <c r="AQ6">
+        <v>41.83</v>
+      </c>
+      <c r="AR6">
+        <v>2.09</v>
+      </c>
+      <c r="AS6">
+        <v>1.84</v>
+      </c>
+      <c r="AT6" t="s">
+        <v>132</v>
+      </c>
+      <c r="AU6">
+        <v>48.5</v>
+      </c>
+      <c r="AV6">
+        <v>1.83</v>
+      </c>
+      <c r="AW6">
+        <v>1.51</v>
+      </c>
+      <c r="AX6" t="s">
+        <v>133</v>
+      </c>
+      <c r="AY6">
+        <v>49.33</v>
+      </c>
+      <c r="AZ6">
+        <v>1.84</v>
+      </c>
+      <c r="BA6">
+        <v>1.54</v>
+      </c>
+      <c r="BB6" t="s">
+        <v>134</v>
+      </c>
+      <c r="BC6">
+        <v>32</v>
+      </c>
+      <c r="BD6">
+        <v>2.9</v>
+      </c>
+      <c r="BE6">
+        <v>2.51</v>
+      </c>
+      <c r="BF6" t="s">
+        <v>135</v>
+      </c>
+      <c r="BG6">
+        <v>35.17</v>
+      </c>
+      <c r="BH6">
+        <v>2.66</v>
+      </c>
+      <c r="BI6">
+        <v>2.22</v>
+      </c>
+      <c r="BJ6" t="s">
+        <v>136</v>
+      </c>
+      <c r="BN6" t="s">
+        <v>137</v>
+      </c>
+      <c r="BR6" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="7" spans="1:73">
+      <c r="A7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B7" t="s">
+        <v>121</v>
+      </c>
+      <c r="C7">
+        <v>370.43</v>
+      </c>
+      <c r="D7">
+        <v>0.23</v>
+      </c>
+      <c r="E7">
+        <v>0.1</v>
+      </c>
+      <c r="F7" t="s">
+        <v>122</v>
+      </c>
+      <c r="G7">
+        <v>376.71</v>
+      </c>
+      <c r="H7">
+        <v>0.22</v>
+      </c>
+      <c r="I7">
+        <v>0.08</v>
+      </c>
+      <c r="J7" t="s">
+        <v>123</v>
+      </c>
+      <c r="K7">
+        <v>383.71</v>
+      </c>
+      <c r="L7">
+        <v>0.22</v>
+      </c>
+      <c r="M7">
+        <v>0.08</v>
+      </c>
+      <c r="N7" t="s">
+        <v>124</v>
+      </c>
+      <c r="O7">
+        <v>390.71</v>
+      </c>
+      <c r="P7">
+        <v>0.21</v>
+      </c>
+      <c r="Q7">
+        <v>0.08</v>
+      </c>
+      <c r="R7" t="s">
+        <v>125</v>
+      </c>
+      <c r="S7">
+        <v>473</v>
+      </c>
+      <c r="T7">
+        <v>0.18</v>
+      </c>
+      <c r="U7">
+        <v>0.06</v>
+      </c>
+      <c r="V7" t="s">
+        <v>126</v>
+      </c>
+      <c r="W7">
+        <v>514</v>
+      </c>
+      <c r="X7">
+        <v>0.16</v>
+      </c>
+      <c r="Y7">
+        <v>0.05</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>127</v>
+      </c>
+      <c r="AA7">
+        <v>547.86</v>
+      </c>
+      <c r="AB7">
+        <v>0.15</v>
+      </c>
+      <c r="AC7">
+        <v>0.04</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE7">
+        <v>509.43</v>
+      </c>
+      <c r="AF7">
+        <v>0.17</v>
+      </c>
+      <c r="AG7">
+        <v>0.05</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>129</v>
+      </c>
+      <c r="AI7">
+        <v>503.71</v>
+      </c>
+      <c r="AJ7">
+        <v>0.17</v>
+      </c>
+      <c r="AK7">
+        <v>0.05</v>
+      </c>
+      <c r="AL7" t="s">
+        <v>130</v>
+      </c>
+      <c r="AM7">
+        <v>576.4299999999999</v>
+      </c>
+      <c r="AN7">
+        <v>0.14</v>
+      </c>
+      <c r="AO7">
+        <v>0.02</v>
+      </c>
+      <c r="AP7" t="s">
+        <v>131</v>
+      </c>
+      <c r="AT7" t="s">
+        <v>132</v>
+      </c>
+      <c r="AX7" t="s">
+        <v>133</v>
+      </c>
+      <c r="BB7" t="s">
+        <v>134</v>
+      </c>
+      <c r="BF7" t="s">
+        <v>135</v>
+      </c>
+      <c r="BJ7" t="s">
+        <v>136</v>
+      </c>
+      <c r="BN7" t="s">
+        <v>137</v>
+      </c>
+      <c r="BR7" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="8" spans="1:73">
+      <c r="A8" t="s">
+        <v>79</v>
+      </c>
+      <c r="B8" t="s">
+        <v>121</v>
+      </c>
+      <c r="C8">
+        <v>9.970000000000001</v>
+      </c>
+      <c r="D8">
+        <v>8.52</v>
+      </c>
+      <c r="E8">
+        <v>8.99</v>
+      </c>
+      <c r="F8" t="s">
+        <v>122</v>
+      </c>
+      <c r="G8">
+        <v>10.11</v>
+      </c>
+      <c r="H8">
+        <v>8.32</v>
+      </c>
+      <c r="I8">
+        <v>8.789999999999999</v>
+      </c>
+      <c r="J8" t="s">
+        <v>123</v>
+      </c>
+      <c r="K8">
+        <v>11.04</v>
+      </c>
+      <c r="L8">
+        <v>7.64</v>
+      </c>
+      <c r="M8">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="N8" t="s">
+        <v>124</v>
+      </c>
+      <c r="O8">
+        <v>11.39</v>
+      </c>
+      <c r="P8">
+        <v>7.33</v>
+      </c>
+      <c r="Q8">
+        <v>7.74</v>
+      </c>
+      <c r="R8" t="s">
+        <v>125</v>
+      </c>
+      <c r="S8">
+        <v>12.2</v>
+      </c>
+      <c r="T8">
+        <v>6.91</v>
+      </c>
+      <c r="U8">
+        <v>7.25</v>
+      </c>
+      <c r="V8" t="s">
+        <v>126</v>
+      </c>
+      <c r="W8">
+        <v>13.17</v>
+      </c>
+      <c r="X8">
+        <v>6.41</v>
+      </c>
+      <c r="Y8">
+        <v>6.69</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>127</v>
+      </c>
+      <c r="AA8">
+        <v>14.94</v>
+      </c>
+      <c r="AB8">
+        <v>5.65</v>
+      </c>
+      <c r="AC8">
+        <v>5.85</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE8">
+        <v>13.31</v>
+      </c>
+      <c r="AF8">
+        <v>6.46</v>
+      </c>
+      <c r="AG8">
+        <v>6.7</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>129</v>
+      </c>
+      <c r="AI8">
+        <v>13.81</v>
+      </c>
+      <c r="AJ8">
+        <v>6.21</v>
+      </c>
+      <c r="AK8">
+        <v>6.4</v>
+      </c>
+      <c r="AL8" t="s">
+        <v>130</v>
+      </c>
+      <c r="AM8">
+        <v>11.47</v>
+      </c>
+      <c r="AN8">
+        <v>7.05</v>
+      </c>
+      <c r="AO8">
+        <v>7.32</v>
+      </c>
+      <c r="AP8" t="s">
+        <v>131</v>
+      </c>
+      <c r="AQ8">
+        <v>12.28</v>
+      </c>
+      <c r="AR8">
+        <v>7.13</v>
+      </c>
+      <c r="AS8">
+        <v>7.22</v>
+      </c>
+      <c r="AT8" t="s">
+        <v>132</v>
+      </c>
+      <c r="AU8">
+        <v>12.7</v>
+      </c>
+      <c r="AV8">
+        <v>6.97</v>
+      </c>
+      <c r="AW8">
+        <v>6.96</v>
+      </c>
+      <c r="AX8" t="s">
+        <v>133</v>
+      </c>
+      <c r="BB8" t="s">
+        <v>134</v>
+      </c>
+      <c r="BF8" t="s">
+        <v>135</v>
+      </c>
+      <c r="BJ8" t="s">
+        <v>136</v>
+      </c>
+      <c r="BN8" t="s">
+        <v>137</v>
+      </c>
+      <c r="BR8" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="9" spans="1:73">
+      <c r="A9" t="s">
+        <v>80</v>
+      </c>
+      <c r="B9" t="s">
+        <v>121</v>
+      </c>
+      <c r="C9">
+        <v>1926.43</v>
+      </c>
+      <c r="D9">
+        <v>0.04</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9" t="s">
+        <v>122</v>
+      </c>
+      <c r="G9">
+        <v>1926.43</v>
+      </c>
+      <c r="H9">
+        <v>0.04</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9" t="s">
+        <v>123</v>
+      </c>
+      <c r="K9">
+        <v>2355</v>
+      </c>
+      <c r="L9">
+        <v>0.04</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>124</v>
+      </c>
+      <c r="O9">
+        <v>2355</v>
+      </c>
+      <c r="P9">
+        <v>0.04</v>
+      </c>
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9" t="s">
+        <v>125</v>
+      </c>
+      <c r="S9">
+        <v>2596.6</v>
+      </c>
+      <c r="T9">
+        <v>0.03</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9" t="s">
+        <v>126</v>
+      </c>
+      <c r="W9">
+        <v>1997.33</v>
+      </c>
+      <c r="X9">
+        <v>0.04</v>
+      </c>
+      <c r="Y9">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>127</v>
+      </c>
+      <c r="AA9">
+        <v>1855</v>
+      </c>
+      <c r="AB9">
+        <v>0.05</v>
+      </c>
+      <c r="AC9">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE9">
+        <v>2001</v>
+      </c>
+      <c r="AF9">
+        <v>0.04</v>
+      </c>
+      <c r="AG9">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>129</v>
+      </c>
+      <c r="AL9" t="s">
+        <v>130</v>
+      </c>
+      <c r="AP9" t="s">
+        <v>131</v>
+      </c>
+      <c r="AT9" t="s">
+        <v>132</v>
+      </c>
+      <c r="AX9" t="s">
+        <v>133</v>
+      </c>
+      <c r="BB9" t="s">
+        <v>134</v>
+      </c>
+      <c r="BF9" t="s">
+        <v>135</v>
+      </c>
+      <c r="BJ9" t="s">
+        <v>136</v>
+      </c>
+      <c r="BN9" t="s">
+        <v>137</v>
+      </c>
+      <c r="BR9" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="10" spans="1:73">
+      <c r="A10" t="s">
+        <v>81</v>
+      </c>
+      <c r="B10" t="s">
+        <v>121</v>
+      </c>
+      <c r="C10">
+        <v>747.86</v>
+      </c>
+      <c r="D10">
+        <v>0.11</v>
+      </c>
+      <c r="E10">
+        <v>0.03</v>
+      </c>
+      <c r="F10" t="s">
+        <v>122</v>
+      </c>
+      <c r="G10">
+        <v>747.86</v>
+      </c>
+      <c r="H10">
+        <v>0.11</v>
+      </c>
+      <c r="I10">
+        <v>0.02</v>
+      </c>
+      <c r="J10" t="s">
+        <v>123</v>
+      </c>
+      <c r="K10">
+        <v>747.86</v>
+      </c>
+      <c r="L10">
+        <v>0.11</v>
+      </c>
+      <c r="M10">
+        <v>0.02</v>
+      </c>
+      <c r="N10" t="s">
+        <v>124</v>
+      </c>
+      <c r="O10">
+        <v>747.86</v>
+      </c>
+      <c r="P10">
+        <v>0.11</v>
+      </c>
+      <c r="Q10">
+        <v>0.02</v>
+      </c>
+      <c r="R10" t="s">
+        <v>125</v>
+      </c>
+      <c r="S10">
+        <v>607.5</v>
+      </c>
+      <c r="T10">
+        <v>0.14</v>
+      </c>
+      <c r="U10">
+        <v>0.04</v>
+      </c>
+      <c r="V10" t="s">
+        <v>126</v>
+      </c>
+      <c r="W10">
+        <v>569.29</v>
+      </c>
+      <c r="X10">
+        <v>0.15</v>
+      </c>
+      <c r="Y10">
+        <v>0.04</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>127</v>
+      </c>
+      <c r="AA10">
+        <v>647.86</v>
+      </c>
+      <c r="AB10">
+        <v>0.13</v>
+      </c>
+      <c r="AC10">
+        <v>0.03</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE10">
+        <v>647.86</v>
+      </c>
+      <c r="AF10">
+        <v>0.13</v>
+      </c>
+      <c r="AG10">
+        <v>0.03</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>129</v>
+      </c>
+      <c r="AI10">
+        <v>612.14</v>
+      </c>
+      <c r="AJ10">
+        <v>0.14</v>
+      </c>
+      <c r="AK10">
+        <v>0.03</v>
+      </c>
+      <c r="AL10" t="s">
+        <v>130</v>
+      </c>
+      <c r="AM10">
+        <v>551</v>
+      </c>
+      <c r="AN10">
+        <v>0.15</v>
+      </c>
+      <c r="AO10">
+        <v>0.02</v>
+      </c>
+      <c r="AP10" t="s">
+        <v>131</v>
+      </c>
+      <c r="AT10" t="s">
+        <v>132</v>
+      </c>
+      <c r="AX10" t="s">
+        <v>133</v>
+      </c>
+      <c r="BB10" t="s">
+        <v>134</v>
+      </c>
+      <c r="BF10" t="s">
+        <v>135</v>
+      </c>
+      <c r="BJ10" t="s">
+        <v>136</v>
+      </c>
+      <c r="BN10" t="s">
+        <v>137</v>
+      </c>
+      <c r="BR10" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="11" spans="1:73">
+      <c r="A11" t="s">
+        <v>82</v>
+      </c>
+      <c r="B11" t="s">
+        <v>121</v>
+      </c>
+      <c r="C11">
+        <v>15.6</v>
+      </c>
+      <c r="D11">
+        <v>5.44</v>
+      </c>
+      <c r="E11">
+        <v>5.65</v>
+      </c>
+      <c r="F11" t="s">
+        <v>122</v>
+      </c>
+      <c r="G11">
+        <v>15.67</v>
+      </c>
+      <c r="H11">
+        <v>5.37</v>
+      </c>
+      <c r="I11">
+        <v>5.57</v>
+      </c>
+      <c r="J11" t="s">
+        <v>123</v>
+      </c>
+      <c r="K11">
+        <v>15.39</v>
+      </c>
+      <c r="L11">
+        <v>5.48</v>
+      </c>
+      <c r="M11">
+        <v>5.7</v>
+      </c>
+      <c r="N11" t="s">
+        <v>124</v>
+      </c>
+      <c r="O11">
+        <v>14.67</v>
+      </c>
+      <c r="P11">
+        <v>5.69</v>
+      </c>
+      <c r="Q11">
+        <v>5.93</v>
+      </c>
+      <c r="R11" t="s">
+        <v>125</v>
+      </c>
+      <c r="S11">
+        <v>14.87</v>
+      </c>
+      <c r="T11">
+        <v>5.67</v>
+      </c>
+      <c r="U11">
+        <v>5.9</v>
+      </c>
+      <c r="V11" t="s">
+        <v>126</v>
+      </c>
+      <c r="W11">
+        <v>14.53</v>
+      </c>
+      <c r="X11">
+        <v>5.81</v>
+      </c>
+      <c r="Y11">
+        <v>6.03</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>127</v>
+      </c>
+      <c r="AA11">
+        <v>14.6</v>
+      </c>
+      <c r="AB11">
+        <v>5.78</v>
+      </c>
+      <c r="AC11">
+        <v>5.99</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE11">
+        <v>17.8</v>
+      </c>
+      <c r="AF11">
+        <v>4.83</v>
+      </c>
+      <c r="AG11">
+        <v>4.94</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AI11">
+        <v>21.14</v>
+      </c>
+      <c r="AJ11">
+        <v>4.06</v>
+      </c>
+      <c r="AK11">
+        <v>4.08</v>
+      </c>
+      <c r="AL11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AM11">
+        <v>26</v>
+      </c>
+      <c r="AN11">
+        <v>3.11</v>
+      </c>
+      <c r="AO11">
+        <v>2.94</v>
+      </c>
+      <c r="AP11" t="s">
+        <v>131</v>
+      </c>
+      <c r="AT11" t="s">
+        <v>132</v>
+      </c>
+      <c r="AX11" t="s">
+        <v>133</v>
+      </c>
+      <c r="BB11" t="s">
+        <v>134</v>
+      </c>
+      <c r="BF11" t="s">
+        <v>135</v>
+      </c>
+      <c r="BJ11" t="s">
+        <v>136</v>
+      </c>
+      <c r="BN11" t="s">
+        <v>137</v>
+      </c>
+      <c r="BR11" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="12" spans="1:73">
+      <c r="A12" t="s">
+        <v>83</v>
+      </c>
+      <c r="B12" t="s">
+        <v>121</v>
+      </c>
+      <c r="C12">
+        <v>89</v>
+      </c>
+      <c r="D12">
+        <v>0.95</v>
+      </c>
+      <c r="E12">
+        <v>0.8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>122</v>
+      </c>
+      <c r="G12">
+        <v>90.43000000000001</v>
+      </c>
+      <c r="H12">
+        <v>0.93</v>
+      </c>
+      <c r="I12">
+        <v>0.75</v>
+      </c>
+      <c r="J12" t="s">
+        <v>123</v>
+      </c>
+      <c r="K12">
+        <v>133.71</v>
+      </c>
+      <c r="L12">
+        <v>0.63</v>
+      </c>
+      <c r="M12">
+        <v>0.45</v>
+      </c>
+      <c r="N12" t="s">
+        <v>124</v>
+      </c>
+      <c r="O12">
+        <v>135.14</v>
+      </c>
+      <c r="P12">
+        <v>0.62</v>
+      </c>
+      <c r="Q12">
+        <v>0.43</v>
+      </c>
+      <c r="R12" t="s">
+        <v>125</v>
+      </c>
+      <c r="S12">
+        <v>148.33</v>
+      </c>
+      <c r="T12">
+        <v>0.57</v>
+      </c>
+      <c r="U12">
+        <v>0.39</v>
+      </c>
+      <c r="V12" t="s">
+        <v>126</v>
+      </c>
+      <c r="W12">
+        <v>279.29</v>
+      </c>
+      <c r="X12">
+        <v>0.3</v>
+      </c>
+      <c r="Y12">
+        <v>0.14</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>127</v>
+      </c>
+      <c r="AA12">
+        <v>289.29</v>
+      </c>
+      <c r="AB12">
+        <v>0.29</v>
+      </c>
+      <c r="AC12">
+        <v>0.13</v>
+      </c>
+      <c r="AD12" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE12">
+        <v>123.86</v>
+      </c>
+      <c r="AF12">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AG12">
+        <v>0.51</v>
+      </c>
+      <c r="AH12" t="s">
+        <v>129</v>
+      </c>
+      <c r="AI12">
+        <v>127.43</v>
+      </c>
+      <c r="AJ12">
+        <v>0.67</v>
+      </c>
+      <c r="AK12">
+        <v>0.47</v>
+      </c>
+      <c r="AL12" t="s">
+        <v>130</v>
+      </c>
+      <c r="AM12">
+        <v>129.57</v>
+      </c>
+      <c r="AN12">
+        <v>0.62</v>
+      </c>
+      <c r="AO12">
+        <v>0.33</v>
+      </c>
+      <c r="AP12" t="s">
+        <v>131</v>
+      </c>
+      <c r="AT12" t="s">
+        <v>132</v>
+      </c>
+      <c r="AX12" t="s">
+        <v>133</v>
+      </c>
+      <c r="BB12" t="s">
+        <v>134</v>
+      </c>
+      <c r="BF12" t="s">
+        <v>135</v>
+      </c>
+      <c r="BJ12" t="s">
+        <v>136</v>
+      </c>
+      <c r="BN12" t="s">
+        <v>137</v>
+      </c>
+      <c r="BR12" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="13" spans="1:73">
+      <c r="A13" t="s">
+        <v>84</v>
+      </c>
+      <c r="B13" t="s">
+        <v>121</v>
+      </c>
+      <c r="C13">
+        <v>250</v>
+      </c>
+      <c r="D13">
+        <v>0.34</v>
+      </c>
+      <c r="E13">
+        <v>0.18</v>
+      </c>
+      <c r="F13" t="s">
+        <v>122</v>
+      </c>
+      <c r="G13">
+        <v>259.86</v>
+      </c>
+      <c r="H13">
+        <v>0.32</v>
+      </c>
+      <c r="I13">
+        <v>0.16</v>
+      </c>
+      <c r="J13" t="s">
+        <v>123</v>
+      </c>
+      <c r="K13">
+        <v>153</v>
+      </c>
+      <c r="L13">
+        <v>0.55</v>
+      </c>
+      <c r="M13">
+        <v>0.37</v>
+      </c>
+      <c r="N13" t="s">
+        <v>124</v>
+      </c>
+      <c r="O13">
+        <v>143</v>
+      </c>
+      <c r="P13">
+        <v>0.58</v>
+      </c>
+      <c r="Q13">
+        <v>0.4</v>
+      </c>
+      <c r="R13" t="s">
+        <v>125</v>
+      </c>
+      <c r="S13">
+        <v>144.83</v>
+      </c>
+      <c r="T13">
+        <v>0.58</v>
+      </c>
+      <c r="U13">
+        <v>0.4</v>
+      </c>
+      <c r="V13" t="s">
+        <v>126</v>
+      </c>
+      <c r="W13">
+        <v>133.71</v>
+      </c>
+      <c r="X13">
+        <v>0.63</v>
+      </c>
+      <c r="Y13">
+        <v>0.44</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>127</v>
+      </c>
+      <c r="AA13">
+        <v>137.86</v>
+      </c>
+      <c r="AB13">
+        <v>0.61</v>
+      </c>
+      <c r="AC13">
+        <v>0.42</v>
+      </c>
+      <c r="AD13" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE13">
+        <v>150.57</v>
+      </c>
+      <c r="AF13">
+        <v>0.57</v>
+      </c>
+      <c r="AG13">
+        <v>0.39</v>
+      </c>
+      <c r="AH13" t="s">
+        <v>129</v>
+      </c>
+      <c r="AI13">
+        <v>174.86</v>
+      </c>
+      <c r="AJ13">
+        <v>0.49</v>
+      </c>
+      <c r="AK13">
+        <v>0.29</v>
+      </c>
+      <c r="AL13" t="s">
+        <v>130</v>
+      </c>
+      <c r="AM13">
+        <v>179.29</v>
+      </c>
+      <c r="AN13">
+        <v>0.45</v>
+      </c>
+      <c r="AO13">
+        <v>0.19</v>
+      </c>
+      <c r="AP13" t="s">
+        <v>131</v>
+      </c>
+      <c r="AT13" t="s">
+        <v>132</v>
+      </c>
+      <c r="AX13" t="s">
+        <v>133</v>
+      </c>
+      <c r="BB13" t="s">
+        <v>134</v>
+      </c>
+      <c r="BF13" t="s">
+        <v>135</v>
+      </c>
+      <c r="BJ13" t="s">
+        <v>136</v>
+      </c>
+      <c r="BN13" t="s">
+        <v>137</v>
+      </c>
+      <c r="BR13" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="14" spans="1:73">
+      <c r="A14" t="s">
+        <v>85</v>
+      </c>
+      <c r="B14" t="s">
+        <v>121</v>
+      </c>
+      <c r="C14">
+        <v>8.15</v>
+      </c>
+      <c r="D14">
+        <v>10.42</v>
+      </c>
+      <c r="E14">
+        <v>11.06</v>
+      </c>
+      <c r="F14" t="s">
+        <v>122</v>
+      </c>
+      <c r="G14">
+        <v>8.42</v>
+      </c>
+      <c r="H14">
+        <v>9.99</v>
+      </c>
+      <c r="I14">
+        <v>10.62</v>
+      </c>
+      <c r="J14" t="s">
+        <v>123</v>
+      </c>
+      <c r="K14">
+        <v>8.390000000000001</v>
+      </c>
+      <c r="L14">
+        <v>10.06</v>
+      </c>
+      <c r="M14">
+        <v>10.69</v>
+      </c>
+      <c r="N14" t="s">
+        <v>124</v>
+      </c>
+      <c r="O14">
+        <v>8.33</v>
+      </c>
+      <c r="P14">
+        <v>10.02</v>
+      </c>
+      <c r="Q14">
+        <v>10.68</v>
+      </c>
+      <c r="R14" t="s">
+        <v>125</v>
+      </c>
+      <c r="S14">
+        <v>7.04</v>
+      </c>
+      <c r="T14">
+        <v>11.96</v>
+      </c>
+      <c r="U14">
+        <v>12.77</v>
+      </c>
+      <c r="V14" t="s">
+        <v>126</v>
+      </c>
+      <c r="W14">
+        <v>7.11</v>
+      </c>
+      <c r="X14">
+        <v>11.88</v>
+      </c>
+      <c r="Y14">
+        <v>12.65</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>127</v>
+      </c>
+      <c r="AA14">
+        <v>7.61</v>
+      </c>
+      <c r="AB14">
+        <v>11.09</v>
+      </c>
+      <c r="AC14">
+        <v>11.79</v>
+      </c>
+      <c r="AD14" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE14">
+        <v>8.43</v>
+      </c>
+      <c r="AF14">
+        <v>10.19</v>
+      </c>
+      <c r="AG14">
+        <v>10.74</v>
+      </c>
+      <c r="AH14" t="s">
+        <v>129</v>
+      </c>
+      <c r="AI14">
+        <v>8.19</v>
+      </c>
+      <c r="AJ14">
+        <v>10.48</v>
+      </c>
+      <c r="AK14">
+        <v>11.02</v>
+      </c>
+      <c r="AL14" t="s">
+        <v>130</v>
+      </c>
+      <c r="AM14">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="AN14">
+        <v>9.84</v>
+      </c>
+      <c r="AO14">
+        <v>10.43</v>
+      </c>
+      <c r="AP14" t="s">
+        <v>131</v>
+      </c>
+      <c r="AQ14">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR14">
+        <v>8.94</v>
+      </c>
+      <c r="AS14">
+        <v>9.15</v>
+      </c>
+      <c r="AT14" t="s">
+        <v>132</v>
+      </c>
+      <c r="AU14">
+        <v>11.05</v>
+      </c>
+      <c r="AV14">
+        <v>8.01</v>
+      </c>
+      <c r="AW14">
+        <v>8.07</v>
+      </c>
+      <c r="AX14" t="s">
+        <v>133</v>
+      </c>
+      <c r="AY14">
+        <v>7.4</v>
+      </c>
+      <c r="AZ14">
+        <v>12.28</v>
+      </c>
+      <c r="BA14">
+        <v>12.49</v>
+      </c>
+      <c r="BB14" t="s">
+        <v>134</v>
+      </c>
+      <c r="BC14">
+        <v>5.89</v>
+      </c>
+      <c r="BD14">
+        <v>15.78</v>
+      </c>
+      <c r="BE14">
+        <v>15.9</v>
+      </c>
+      <c r="BF14" t="s">
+        <v>135</v>
+      </c>
+      <c r="BG14">
+        <v>5.73</v>
+      </c>
+      <c r="BH14">
+        <v>16.29</v>
+      </c>
+      <c r="BI14">
+        <v>16.36</v>
+      </c>
+      <c r="BJ14" t="s">
+        <v>136</v>
+      </c>
+      <c r="BK14">
+        <v>4.43</v>
+      </c>
+      <c r="BL14">
+        <v>21.38</v>
+      </c>
+      <c r="BM14">
+        <v>21.25</v>
+      </c>
+      <c r="BN14" t="s">
+        <v>137</v>
+      </c>
+      <c r="BO14">
+        <v>4.36</v>
+      </c>
+      <c r="BP14">
+        <v>21.7</v>
+      </c>
+      <c r="BQ14">
+        <v>21.58</v>
+      </c>
+      <c r="BR14" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="15" spans="1:73">
+      <c r="A15" t="s">
+        <v>86</v>
+      </c>
+      <c r="B15" t="s">
+        <v>121</v>
+      </c>
+      <c r="C15">
         <v>6.01</v>
       </c>
-      <c r="D2">
+      <c r="D15">
         <v>14.12</v>
       </c>
-      <c r="E2">
+      <c r="E15">
         <v>15.09</v>
       </c>
-      <c r="F2" t="s">
-        <v>118</v>
-      </c>
-      <c r="G2">
+      <c r="F15" t="s">
+        <v>122</v>
+      </c>
+      <c r="G15">
         <v>5.55</v>
       </c>
-      <c r="H2">
+      <c r="H15">
         <v>15.15</v>
       </c>
-      <c r="I2">
+      <c r="I15">
         <v>16.26</v>
       </c>
-      <c r="J2" t="s">
-        <v>119</v>
-      </c>
-      <c r="K2">
+      <c r="J15" t="s">
+        <v>123</v>
+      </c>
+      <c r="K15">
         <v>5.55</v>
       </c>
-      <c r="L2">
+      <c r="L15">
         <v>15.2</v>
       </c>
-      <c r="M2">
+      <c r="M15">
         <v>16.3</v>
       </c>
-      <c r="N2" t="s">
-        <v>120</v>
-      </c>
-      <c r="O2">
+      <c r="N15" t="s">
+        <v>124</v>
+      </c>
+      <c r="O15">
         <v>4.97</v>
       </c>
-      <c r="P2">
+      <c r="P15">
         <v>16.81</v>
       </c>
-      <c r="Q2">
+      <c r="Q15">
         <v>18.14</v>
       </c>
-      <c r="R2" t="s">
+      <c r="R15" t="s">
+        <v>125</v>
+      </c>
+      <c r="S15">
+        <v>4.82</v>
+      </c>
+      <c r="T15">
+        <v>17.48</v>
+      </c>
+      <c r="U15">
+        <v>18.8</v>
+      </c>
+      <c r="V15" t="s">
+        <v>126</v>
+      </c>
+      <c r="W15">
+        <v>4.87</v>
+      </c>
+      <c r="X15">
+        <v>17.32</v>
+      </c>
+      <c r="Y15">
+        <v>18.6</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>127</v>
+      </c>
+      <c r="AA15">
+        <v>4.87</v>
+      </c>
+      <c r="AB15">
+        <v>17.31</v>
+      </c>
+      <c r="AC15">
+        <v>18.58</v>
+      </c>
+      <c r="AD15" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE15">
+        <v>4.96</v>
+      </c>
+      <c r="AF15">
+        <v>17.34</v>
+      </c>
+      <c r="AG15">
+        <v>18.46</v>
+      </c>
+      <c r="AH15" t="s">
+        <v>129</v>
+      </c>
+      <c r="AI15">
+        <v>4.34</v>
+      </c>
+      <c r="AJ15">
+        <v>19.78</v>
+      </c>
+      <c r="AK15">
+        <v>21.1</v>
+      </c>
+      <c r="AL15" t="s">
+        <v>130</v>
+      </c>
+      <c r="AM15">
+        <v>3.62</v>
+      </c>
+      <c r="AN15">
+        <v>22.34</v>
+      </c>
+      <c r="AO15">
+        <v>24.41</v>
+      </c>
+      <c r="AP15" t="s">
+        <v>131</v>
+      </c>
+      <c r="AQ15">
+        <v>2.86</v>
+      </c>
+      <c r="AR15">
+        <v>30.67</v>
+      </c>
+      <c r="AS15">
+        <v>32.47</v>
+      </c>
+      <c r="AT15" t="s">
+        <v>132</v>
+      </c>
+      <c r="AU15">
+        <v>2.88</v>
+      </c>
+      <c r="AV15">
+        <v>30.76</v>
+      </c>
+      <c r="AW15">
+        <v>32.36</v>
+      </c>
+      <c r="AX15" t="s">
+        <v>133</v>
+      </c>
+      <c r="AY15">
+        <v>2.79</v>
+      </c>
+      <c r="AZ15">
+        <v>32.56</v>
+      </c>
+      <c r="BA15">
+        <v>33.86</v>
+      </c>
+      <c r="BB15" t="s">
+        <v>134</v>
+      </c>
+      <c r="BC15">
+        <v>2.88</v>
+      </c>
+      <c r="BD15">
+        <v>32.25</v>
+      </c>
+      <c r="BE15">
+        <v>33.08</v>
+      </c>
+      <c r="BF15" t="s">
+        <v>135</v>
+      </c>
+      <c r="BG15">
+        <v>2.49</v>
+      </c>
+      <c r="BH15">
+        <v>37.54</v>
+      </c>
+      <c r="BI15">
+        <v>38.47</v>
+      </c>
+      <c r="BJ15" t="s">
+        <v>136</v>
+      </c>
+      <c r="BK15">
+        <v>2.51</v>
+      </c>
+      <c r="BL15">
+        <v>37.78</v>
+      </c>
+      <c r="BM15">
+        <v>38.25</v>
+      </c>
+      <c r="BN15" t="s">
+        <v>137</v>
+      </c>
+      <c r="BO15">
+        <v>2.43</v>
+      </c>
+      <c r="BP15">
+        <v>38.93</v>
+      </c>
+      <c r="BQ15">
+        <v>39.45</v>
+      </c>
+      <c r="BR15" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="16" spans="1:73">
+      <c r="A16" t="s">
+        <v>87</v>
+      </c>
+      <c r="B16" t="s">
         <v>121</v>
-      </c>
-      <c r="S2">
-        <v>4.82</v>
-      </c>
-      <c r="T2">
-        <v>17.48</v>
-      </c>
-      <c r="U2">
-        <v>18.8</v>
-      </c>
-      <c r="V2" t="s">
-        <v>122</v>
-      </c>
-      <c r="W2">
-        <v>4.87</v>
-      </c>
-      <c r="X2">
-        <v>17.32</v>
-      </c>
-      <c r="Y2">
-        <v>18.6</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>123</v>
-      </c>
-      <c r="AA2">
-        <v>4.87</v>
-      </c>
-      <c r="AB2">
-        <v>17.31</v>
-      </c>
-      <c r="AC2">
-        <v>18.58</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>124</v>
-      </c>
-      <c r="AE2">
-        <v>4.96</v>
-      </c>
-      <c r="AF2">
-        <v>17.34</v>
-      </c>
-      <c r="AG2">
-        <v>18.46</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>125</v>
-      </c>
-      <c r="AI2">
-        <v>4.34</v>
-      </c>
-      <c r="AJ2">
-        <v>19.78</v>
-      </c>
-      <c r="AK2">
-        <v>21.1</v>
-      </c>
-      <c r="AL2" t="s">
-        <v>126</v>
-      </c>
-      <c r="AM2">
-        <v>3.62</v>
-      </c>
-      <c r="AN2">
-        <v>22.34</v>
-      </c>
-      <c r="AO2">
-        <v>24.41</v>
-      </c>
-      <c r="AP2" t="s">
-        <v>127</v>
-      </c>
-      <c r="AQ2">
-        <v>2.86</v>
-      </c>
-      <c r="AR2">
-        <v>30.67</v>
-      </c>
-      <c r="AS2">
-        <v>32.47</v>
-      </c>
-      <c r="AT2" t="s">
-        <v>128</v>
-      </c>
-      <c r="AU2">
-        <v>2.88</v>
-      </c>
-      <c r="AV2">
-        <v>30.76</v>
-      </c>
-      <c r="AW2">
-        <v>32.36</v>
-      </c>
-      <c r="AX2" t="s">
-        <v>129</v>
-      </c>
-      <c r="AY2">
-        <v>2.79</v>
-      </c>
-      <c r="AZ2">
-        <v>32.56</v>
-      </c>
-      <c r="BA2">
-        <v>33.86</v>
-      </c>
-      <c r="BB2" t="s">
-        <v>130</v>
-      </c>
-      <c r="BC2">
-        <v>2.88</v>
-      </c>
-      <c r="BD2">
-        <v>32.25</v>
-      </c>
-      <c r="BE2">
-        <v>33.08</v>
-      </c>
-      <c r="BF2" t="s">
-        <v>131</v>
-      </c>
-      <c r="BG2">
-        <v>2.49</v>
-      </c>
-      <c r="BH2">
-        <v>37.54</v>
-      </c>
-      <c r="BI2">
-        <v>38.47</v>
-      </c>
-      <c r="BJ2" t="s">
-        <v>132</v>
-      </c>
-      <c r="BK2">
-        <v>2.51</v>
-      </c>
-      <c r="BL2">
-        <v>37.78</v>
-      </c>
-      <c r="BM2">
-        <v>38.25</v>
-      </c>
-      <c r="BN2" t="s">
-        <v>133</v>
-      </c>
-      <c r="BO2">
-        <v>2.43</v>
-      </c>
-      <c r="BP2">
-        <v>38.93</v>
-      </c>
-      <c r="BQ2">
-        <v>39.45</v>
-      </c>
-    </row>
-    <row r="3" spans="1:69">
-      <c r="A3" t="s">
-        <v>70</v>
-      </c>
-      <c r="B3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C3">
-        <v>5.58</v>
-      </c>
-      <c r="D3">
-        <v>15.22</v>
-      </c>
-      <c r="E3">
-        <v>16.29</v>
-      </c>
-      <c r="F3" t="s">
-        <v>118</v>
-      </c>
-      <c r="G3">
-        <v>5.63</v>
-      </c>
-      <c r="H3">
-        <v>14.94</v>
-      </c>
-      <c r="I3">
-        <v>16.04</v>
-      </c>
-      <c r="J3" t="s">
-        <v>119</v>
-      </c>
-      <c r="K3">
-        <v>5.63</v>
-      </c>
-      <c r="L3">
-        <v>14.99</v>
-      </c>
-      <c r="M3">
-        <v>16.07</v>
-      </c>
-      <c r="N3" t="s">
-        <v>120</v>
-      </c>
-      <c r="O3">
-        <v>6.51</v>
-      </c>
-      <c r="P3">
-        <v>12.83</v>
-      </c>
-      <c r="Q3">
-        <v>13.76</v>
-      </c>
-      <c r="R3" t="s">
-        <v>121</v>
-      </c>
-      <c r="S3">
-        <v>6.88</v>
-      </c>
-      <c r="T3">
-        <v>12.25</v>
-      </c>
-      <c r="U3">
-        <v>13.09</v>
-      </c>
-      <c r="V3" t="s">
-        <v>122</v>
-      </c>
-      <c r="W3">
-        <v>6.34</v>
-      </c>
-      <c r="X3">
-        <v>13.32</v>
-      </c>
-      <c r="Y3">
-        <v>14.23</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>123</v>
-      </c>
-      <c r="AA3">
-        <v>6.48</v>
-      </c>
-      <c r="AB3">
-        <v>13.01</v>
-      </c>
-      <c r="AC3">
-        <v>13.89</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>124</v>
-      </c>
-      <c r="AE3">
-        <v>6.63</v>
-      </c>
-      <c r="AF3">
-        <v>12.98</v>
-      </c>
-      <c r="AG3">
-        <v>13.74</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>125</v>
-      </c>
-      <c r="AI3">
-        <v>8.02</v>
-      </c>
-      <c r="AJ3">
-        <v>10.7</v>
-      </c>
-      <c r="AK3">
-        <v>11.26</v>
-      </c>
-      <c r="AL3" t="s">
-        <v>126</v>
-      </c>
-      <c r="AM3">
-        <v>8.140000000000001</v>
-      </c>
-      <c r="AN3">
-        <v>9.94</v>
-      </c>
-      <c r="AO3">
-        <v>10.55</v>
-      </c>
-      <c r="AP3" t="s">
-        <v>127</v>
-      </c>
-      <c r="AQ3">
-        <v>8.59</v>
-      </c>
-      <c r="AR3">
-        <v>10.2</v>
-      </c>
-      <c r="AS3">
-        <v>10.5</v>
-      </c>
-      <c r="AT3" t="s">
-        <v>128</v>
-      </c>
-      <c r="AU3">
-        <v>7.04</v>
-      </c>
-      <c r="AV3">
-        <v>12.57</v>
-      </c>
-      <c r="AW3">
-        <v>12.93</v>
-      </c>
-      <c r="AX3" t="s">
-        <v>129</v>
-      </c>
-      <c r="AY3">
-        <v>6.98</v>
-      </c>
-      <c r="AZ3">
-        <v>13.01</v>
-      </c>
-      <c r="BA3">
-        <v>13.27</v>
-      </c>
-      <c r="BB3" t="s">
-        <v>130</v>
-      </c>
-      <c r="BC3">
-        <v>4.75</v>
-      </c>
-      <c r="BD3">
-        <v>19.55</v>
-      </c>
-      <c r="BE3">
-        <v>19.84</v>
-      </c>
-      <c r="BF3" t="s">
-        <v>131</v>
-      </c>
-      <c r="BG3">
-        <v>5.25</v>
-      </c>
-      <c r="BH3">
-        <v>17.79</v>
-      </c>
-      <c r="BI3">
-        <v>17.91</v>
-      </c>
-      <c r="BJ3" t="s">
-        <v>132</v>
-      </c>
-      <c r="BK3">
-        <v>4.36</v>
-      </c>
-      <c r="BL3">
-        <v>21.73</v>
-      </c>
-      <c r="BM3">
-        <v>21.61</v>
-      </c>
-      <c r="BN3" t="s">
-        <v>133</v>
-      </c>
-      <c r="BO3">
-        <v>4.33</v>
-      </c>
-      <c r="BP3">
-        <v>21.87</v>
-      </c>
-      <c r="BQ3">
-        <v>21.75</v>
-      </c>
-    </row>
-    <row r="4" spans="1:69">
-      <c r="A4" t="s">
-        <v>71</v>
-      </c>
-      <c r="B4" t="s">
-        <v>117</v>
-      </c>
-      <c r="C4">
-        <v>8.15</v>
-      </c>
-      <c r="D4">
-        <v>10.42</v>
-      </c>
-      <c r="E4">
-        <v>11.06</v>
-      </c>
-      <c r="F4" t="s">
-        <v>118</v>
-      </c>
-      <c r="G4">
-        <v>8.42</v>
-      </c>
-      <c r="H4">
-        <v>9.99</v>
-      </c>
-      <c r="I4">
-        <v>10.62</v>
-      </c>
-      <c r="J4" t="s">
-        <v>119</v>
-      </c>
-      <c r="K4">
-        <v>8.390000000000001</v>
-      </c>
-      <c r="L4">
-        <v>10.06</v>
-      </c>
-      <c r="M4">
-        <v>10.69</v>
-      </c>
-      <c r="N4" t="s">
-        <v>120</v>
-      </c>
-      <c r="O4">
-        <v>8.33</v>
-      </c>
-      <c r="P4">
-        <v>10.02</v>
-      </c>
-      <c r="Q4">
-        <v>10.68</v>
-      </c>
-      <c r="R4" t="s">
-        <v>121</v>
-      </c>
-      <c r="S4">
-        <v>7.04</v>
-      </c>
-      <c r="T4">
-        <v>11.96</v>
-      </c>
-      <c r="U4">
-        <v>12.77</v>
-      </c>
-      <c r="V4" t="s">
-        <v>122</v>
-      </c>
-      <c r="W4">
-        <v>7.11</v>
-      </c>
-      <c r="X4">
-        <v>11.88</v>
-      </c>
-      <c r="Y4">
-        <v>12.65</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>123</v>
-      </c>
-      <c r="AA4">
-        <v>7.61</v>
-      </c>
-      <c r="AB4">
-        <v>11.09</v>
-      </c>
-      <c r="AC4">
-        <v>11.79</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>124</v>
-      </c>
-      <c r="AE4">
-        <v>8.43</v>
-      </c>
-      <c r="AF4">
-        <v>10.19</v>
-      </c>
-      <c r="AG4">
-        <v>10.74</v>
-      </c>
-      <c r="AH4" t="s">
-        <v>125</v>
-      </c>
-      <c r="AI4">
-        <v>8.19</v>
-      </c>
-      <c r="AJ4">
-        <v>10.48</v>
-      </c>
-      <c r="AK4">
-        <v>11.02</v>
-      </c>
-      <c r="AL4" t="s">
-        <v>126</v>
-      </c>
-      <c r="AM4">
-        <v>8.220000000000001</v>
-      </c>
-      <c r="AN4">
-        <v>9.84</v>
-      </c>
-      <c r="AO4">
-        <v>10.43</v>
-      </c>
-      <c r="AP4" t="s">
-        <v>127</v>
-      </c>
-      <c r="AQ4">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AR4">
-        <v>8.94</v>
-      </c>
-      <c r="AS4">
-        <v>9.15</v>
-      </c>
-      <c r="AT4" t="s">
-        <v>128</v>
-      </c>
-      <c r="AU4">
-        <v>11.05</v>
-      </c>
-      <c r="AV4">
-        <v>8.01</v>
-      </c>
-      <c r="AW4">
-        <v>8.07</v>
-      </c>
-      <c r="AX4" t="s">
-        <v>129</v>
-      </c>
-      <c r="AY4">
-        <v>7.4</v>
-      </c>
-      <c r="AZ4">
-        <v>12.28</v>
-      </c>
-      <c r="BA4">
-        <v>12.49</v>
-      </c>
-      <c r="BB4" t="s">
-        <v>130</v>
-      </c>
-      <c r="BC4">
-        <v>5.89</v>
-      </c>
-      <c r="BD4">
-        <v>15.78</v>
-      </c>
-      <c r="BE4">
-        <v>15.9</v>
-      </c>
-      <c r="BF4" t="s">
-        <v>131</v>
-      </c>
-      <c r="BG4">
-        <v>5.73</v>
-      </c>
-      <c r="BH4">
-        <v>16.29</v>
-      </c>
-      <c r="BI4">
-        <v>16.36</v>
-      </c>
-      <c r="BJ4" t="s">
-        <v>132</v>
-      </c>
-      <c r="BK4">
-        <v>4.43</v>
-      </c>
-      <c r="BL4">
-        <v>21.38</v>
-      </c>
-      <c r="BM4">
-        <v>21.25</v>
-      </c>
-      <c r="BN4" t="s">
-        <v>133</v>
-      </c>
-      <c r="BO4">
-        <v>4.36</v>
-      </c>
-      <c r="BP4">
-        <v>21.7</v>
-      </c>
-      <c r="BQ4">
-        <v>21.58</v>
-      </c>
-    </row>
-    <row r="5" spans="1:69">
-      <c r="A5" t="s">
-        <v>72</v>
-      </c>
-      <c r="B5" t="s">
-        <v>117</v>
-      </c>
-      <c r="C5">
-        <v>10.19</v>
-      </c>
-      <c r="D5">
-        <v>8.34</v>
-      </c>
-      <c r="E5">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="F5" t="s">
-        <v>118</v>
-      </c>
-      <c r="G5">
-        <v>10.33</v>
-      </c>
-      <c r="H5">
-        <v>8.140000000000001</v>
-      </c>
-      <c r="I5">
-        <v>8.6</v>
-      </c>
-      <c r="J5" t="s">
-        <v>119</v>
-      </c>
-      <c r="K5">
-        <v>10.61</v>
-      </c>
-      <c r="L5">
-        <v>7.95</v>
-      </c>
-      <c r="M5">
-        <v>8.390000000000001</v>
-      </c>
-      <c r="N5" t="s">
-        <v>120</v>
-      </c>
-      <c r="O5">
-        <v>9.4</v>
-      </c>
-      <c r="P5">
-        <v>8.880000000000001</v>
-      </c>
-      <c r="Q5">
-        <v>9.44</v>
-      </c>
-      <c r="R5" t="s">
-        <v>121</v>
-      </c>
-      <c r="S5">
-        <v>9.140000000000001</v>
-      </c>
-      <c r="T5">
-        <v>9.220000000000001</v>
-      </c>
-      <c r="U5">
-        <v>9.779999999999999</v>
-      </c>
-      <c r="V5" t="s">
-        <v>122</v>
-      </c>
-      <c r="W5">
-        <v>8.710000000000001</v>
-      </c>
-      <c r="X5">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="Y5">
-        <v>10.27</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>123</v>
-      </c>
-      <c r="AA5">
-        <v>7.45</v>
-      </c>
-      <c r="AB5">
-        <v>11.32</v>
-      </c>
-      <c r="AC5">
-        <v>12.04</v>
-      </c>
-      <c r="AD5" t="s">
-        <v>124</v>
-      </c>
-      <c r="AE5">
-        <v>7.04</v>
-      </c>
-      <c r="AF5">
-        <v>12.21</v>
-      </c>
-      <c r="AG5">
-        <v>12.92</v>
-      </c>
-      <c r="AH5" t="s">
-        <v>125</v>
-      </c>
-      <c r="AI5">
-        <v>5.2</v>
-      </c>
-      <c r="AJ5">
-        <v>16.49</v>
-      </c>
-      <c r="AK5">
-        <v>17.53</v>
-      </c>
-      <c r="AL5" t="s">
-        <v>126</v>
-      </c>
-      <c r="AM5">
-        <v>4.84</v>
-      </c>
-      <c r="AN5">
-        <v>16.71</v>
-      </c>
-      <c r="AO5">
-        <v>18.12</v>
-      </c>
-      <c r="AP5" t="s">
-        <v>127</v>
-      </c>
-      <c r="AQ5">
-        <v>5.11</v>
-      </c>
-      <c r="AR5">
-        <v>17.14</v>
-      </c>
-      <c r="AS5">
-        <v>17.95</v>
-      </c>
-      <c r="AT5" t="s">
-        <v>128</v>
-      </c>
-      <c r="AU5">
-        <v>5.31</v>
-      </c>
-      <c r="AV5">
-        <v>16.67</v>
-      </c>
-      <c r="AW5">
-        <v>17.31</v>
-      </c>
-      <c r="AX5" t="s">
-        <v>129</v>
-      </c>
-      <c r="AY5">
-        <v>5.53</v>
-      </c>
-      <c r="AZ5">
-        <v>16.42</v>
-      </c>
-      <c r="BA5">
-        <v>16.85</v>
-      </c>
-      <c r="BB5" t="s">
-        <v>130</v>
-      </c>
-      <c r="BC5">
-        <v>5.05</v>
-      </c>
-      <c r="BD5">
-        <v>18.4</v>
-      </c>
-      <c r="BE5">
-        <v>18.63</v>
-      </c>
-      <c r="BF5" t="s">
-        <v>131</v>
-      </c>
-      <c r="BG5">
-        <v>5.34</v>
-      </c>
-      <c r="BH5">
-        <v>17.51</v>
-      </c>
-      <c r="BI5">
-        <v>17.62</v>
-      </c>
-      <c r="BJ5" t="s">
-        <v>132</v>
-      </c>
-      <c r="BK5">
-        <v>4.96</v>
-      </c>
-      <c r="BL5">
-        <v>19.11</v>
-      </c>
-      <c r="BM5">
-        <v>18.89</v>
-      </c>
-      <c r="BN5" t="s">
-        <v>133</v>
-      </c>
-      <c r="BO5">
-        <v>5.41</v>
-      </c>
-      <c r="BP5">
-        <v>17.5</v>
-      </c>
-      <c r="BQ5">
-        <v>17.22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:69">
-      <c r="A6" t="s">
-        <v>73</v>
-      </c>
-      <c r="B6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C6">
-        <v>367.57</v>
-      </c>
-      <c r="D6">
-        <v>0.23</v>
-      </c>
-      <c r="E6">
-        <v>0.1</v>
-      </c>
-      <c r="F6" t="s">
-        <v>118</v>
-      </c>
-      <c r="G6">
-        <v>383</v>
-      </c>
-      <c r="H6">
-        <v>0.22</v>
-      </c>
-      <c r="I6">
-        <v>0.08</v>
-      </c>
-      <c r="J6" t="s">
-        <v>119</v>
-      </c>
-      <c r="K6">
-        <v>378.86</v>
-      </c>
-      <c r="L6">
-        <v>0.22</v>
-      </c>
-      <c r="M6">
-        <v>0.09</v>
-      </c>
-      <c r="N6" t="s">
-        <v>120</v>
-      </c>
-      <c r="O6">
-        <v>474.57</v>
-      </c>
-      <c r="P6">
-        <v>0.18</v>
-      </c>
-      <c r="Q6">
-        <v>0.05</v>
-      </c>
-      <c r="R6" t="s">
-        <v>121</v>
-      </c>
-      <c r="S6">
-        <v>530.67</v>
-      </c>
-      <c r="T6">
-        <v>0.16</v>
-      </c>
-      <c r="U6">
-        <v>0.05</v>
-      </c>
-      <c r="V6" t="s">
-        <v>122</v>
-      </c>
-      <c r="W6">
-        <v>518</v>
-      </c>
-      <c r="X6">
-        <v>0.16</v>
-      </c>
-      <c r="Y6">
-        <v>0.05</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>123</v>
-      </c>
-      <c r="AA6">
-        <v>529.5700000000001</v>
-      </c>
-      <c r="AB6">
-        <v>0.16</v>
-      </c>
-      <c r="AC6">
-        <v>0.04</v>
-      </c>
-      <c r="AD6" t="s">
-        <v>124</v>
-      </c>
-      <c r="AE6">
-        <v>576.4299999999999</v>
-      </c>
-      <c r="AF6">
-        <v>0.15</v>
-      </c>
-      <c r="AG6">
-        <v>0.04</v>
-      </c>
-      <c r="AH6" t="s">
-        <v>125</v>
-      </c>
-      <c r="AI6">
-        <v>458.71</v>
-      </c>
-      <c r="AJ6">
-        <v>0.19</v>
-      </c>
-      <c r="AK6">
-        <v>0.06</v>
-      </c>
-      <c r="AL6" t="s">
-        <v>126</v>
-      </c>
-      <c r="AM6">
-        <v>391.29</v>
-      </c>
-      <c r="AN6">
-        <v>0.21</v>
-      </c>
-      <c r="AO6">
-        <v>0.04</v>
-      </c>
-      <c r="AP6" t="s">
-        <v>127</v>
-      </c>
-      <c r="AQ6">
-        <v>437.83</v>
-      </c>
-      <c r="AR6">
-        <v>0.2</v>
-      </c>
-      <c r="AS6">
-        <v>0.05</v>
-      </c>
-      <c r="AT6" t="s">
-        <v>128</v>
-      </c>
-      <c r="AX6" t="s">
-        <v>129</v>
-      </c>
-      <c r="BB6" t="s">
-        <v>130</v>
-      </c>
-      <c r="BF6" t="s">
-        <v>131</v>
-      </c>
-      <c r="BJ6" t="s">
-        <v>132</v>
-      </c>
-      <c r="BN6" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="7" spans="1:69">
-      <c r="A7" t="s">
-        <v>74</v>
-      </c>
-      <c r="B7" t="s">
-        <v>117</v>
-      </c>
-      <c r="C7">
-        <v>442.71</v>
-      </c>
-      <c r="D7">
-        <v>0.19</v>
-      </c>
-      <c r="E7">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="F7" t="s">
-        <v>118</v>
-      </c>
-      <c r="G7">
-        <v>462.29</v>
-      </c>
-      <c r="H7">
-        <v>0.18</v>
-      </c>
-      <c r="I7">
-        <v>0.06</v>
-      </c>
-      <c r="J7" t="s">
-        <v>119</v>
-      </c>
-      <c r="K7">
-        <v>186</v>
-      </c>
-      <c r="L7">
-        <v>0.45</v>
-      </c>
-      <c r="M7">
-        <v>0.28</v>
-      </c>
-      <c r="N7" t="s">
-        <v>120</v>
-      </c>
-      <c r="O7">
-        <v>123.14</v>
-      </c>
-      <c r="P7">
-        <v>0.68</v>
-      </c>
-      <c r="Q7">
-        <v>0.49</v>
-      </c>
-      <c r="R7" t="s">
-        <v>121</v>
-      </c>
-      <c r="S7">
-        <v>128.5</v>
-      </c>
-      <c r="T7">
-        <v>0.66</v>
-      </c>
-      <c r="U7">
-        <v>0.47</v>
-      </c>
-      <c r="V7" t="s">
-        <v>122</v>
-      </c>
-      <c r="W7">
-        <v>174.43</v>
-      </c>
-      <c r="X7">
-        <v>0.48</v>
-      </c>
-      <c r="Y7">
-        <v>0.3</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>123</v>
-      </c>
-      <c r="AA7">
-        <v>206.33</v>
-      </c>
-      <c r="AB7">
-        <v>0.41</v>
-      </c>
-      <c r="AC7">
-        <v>0.23</v>
-      </c>
-      <c r="AD7" t="s">
-        <v>124</v>
-      </c>
-      <c r="AE7">
-        <v>199.83</v>
-      </c>
-      <c r="AF7">
-        <v>0.43</v>
-      </c>
-      <c r="AG7">
-        <v>0.26</v>
-      </c>
-      <c r="AH7" t="s">
-        <v>125</v>
-      </c>
-      <c r="AI7">
-        <v>249.14</v>
-      </c>
-      <c r="AJ7">
-        <v>0.34</v>
-      </c>
-      <c r="AK7">
-        <v>0.17</v>
-      </c>
-      <c r="AL7" t="s">
-        <v>126</v>
-      </c>
-      <c r="AM7">
-        <v>290.57</v>
-      </c>
-      <c r="AN7">
-        <v>0.28</v>
-      </c>
-      <c r="AO7">
-        <v>0.08</v>
-      </c>
-      <c r="AP7" t="s">
-        <v>127</v>
-      </c>
-      <c r="AQ7">
-        <v>333.67</v>
-      </c>
-      <c r="AR7">
-        <v>0.26</v>
-      </c>
-      <c r="AS7">
-        <v>0.08</v>
-      </c>
-      <c r="AT7" t="s">
-        <v>128</v>
-      </c>
-      <c r="AX7" t="s">
-        <v>129</v>
-      </c>
-      <c r="BB7" t="s">
-        <v>130</v>
-      </c>
-      <c r="BF7" t="s">
-        <v>131</v>
-      </c>
-      <c r="BJ7" t="s">
-        <v>132</v>
-      </c>
-      <c r="BN7" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="8" spans="1:69">
-      <c r="A8" t="s">
-        <v>75</v>
-      </c>
-      <c r="B8" t="s">
-        <v>117</v>
-      </c>
-      <c r="C8">
-        <v>37.71</v>
-      </c>
-      <c r="D8">
-        <v>2.25</v>
-      </c>
-      <c r="E8">
-        <v>2.19</v>
-      </c>
-      <c r="F8" t="s">
-        <v>118</v>
-      </c>
-      <c r="G8">
-        <v>37.71</v>
-      </c>
-      <c r="H8">
-        <v>2.23</v>
-      </c>
-      <c r="I8">
-        <v>2.15</v>
-      </c>
-      <c r="J8" t="s">
-        <v>119</v>
-      </c>
-      <c r="K8">
-        <v>39.43</v>
-      </c>
-      <c r="L8">
-        <v>2.14</v>
-      </c>
-      <c r="M8">
-        <v>2.06</v>
-      </c>
-      <c r="N8" t="s">
-        <v>120</v>
-      </c>
-      <c r="O8">
-        <v>42</v>
-      </c>
-      <c r="P8">
-        <v>1.99</v>
-      </c>
-      <c r="Q8">
-        <v>1.88</v>
-      </c>
-      <c r="R8" t="s">
-        <v>121</v>
-      </c>
-      <c r="S8">
-        <v>42.17</v>
-      </c>
-      <c r="T8">
-        <v>2</v>
-      </c>
-      <c r="U8">
-        <v>1.9</v>
-      </c>
-      <c r="V8" t="s">
-        <v>122</v>
-      </c>
-      <c r="W8">
-        <v>47.71</v>
-      </c>
-      <c r="X8">
-        <v>1.77</v>
-      </c>
-      <c r="Y8">
-        <v>1.64</v>
-      </c>
-      <c r="Z8" t="s">
-        <v>123</v>
-      </c>
-      <c r="AA8">
-        <v>52.71</v>
-      </c>
-      <c r="AB8">
-        <v>1.6</v>
-      </c>
-      <c r="AC8">
-        <v>1.45</v>
-      </c>
-      <c r="AD8" t="s">
-        <v>124</v>
-      </c>
-      <c r="AE8">
-        <v>54.14</v>
-      </c>
-      <c r="AF8">
-        <v>1.59</v>
-      </c>
-      <c r="AG8">
-        <v>1.45</v>
-      </c>
-      <c r="AH8" t="s">
-        <v>125</v>
-      </c>
-      <c r="AI8">
-        <v>49.14</v>
-      </c>
-      <c r="AJ8">
-        <v>1.75</v>
-      </c>
-      <c r="AK8">
-        <v>1.59</v>
-      </c>
-      <c r="AL8" t="s">
-        <v>126</v>
-      </c>
-      <c r="AM8">
-        <v>52</v>
-      </c>
-      <c r="AN8">
-        <v>1.55</v>
-      </c>
-      <c r="AO8">
-        <v>1.25</v>
-      </c>
-      <c r="AP8" t="s">
-        <v>127</v>
-      </c>
-      <c r="AQ8">
-        <v>41.83</v>
-      </c>
-      <c r="AR8">
-        <v>2.09</v>
-      </c>
-      <c r="AS8">
-        <v>1.84</v>
-      </c>
-      <c r="AT8" t="s">
-        <v>128</v>
-      </c>
-      <c r="AU8">
-        <v>48.5</v>
-      </c>
-      <c r="AV8">
-        <v>1.83</v>
-      </c>
-      <c r="AW8">
-        <v>1.51</v>
-      </c>
-      <c r="AX8" t="s">
-        <v>129</v>
-      </c>
-      <c r="AY8">
-        <v>49.33</v>
-      </c>
-      <c r="AZ8">
-        <v>1.84</v>
-      </c>
-      <c r="BA8">
-        <v>1.54</v>
-      </c>
-      <c r="BB8" t="s">
-        <v>130</v>
-      </c>
-      <c r="BC8">
-        <v>32</v>
-      </c>
-      <c r="BD8">
-        <v>2.9</v>
-      </c>
-      <c r="BE8">
-        <v>2.51</v>
-      </c>
-      <c r="BF8" t="s">
-        <v>131</v>
-      </c>
-      <c r="BG8">
-        <v>35.17</v>
-      </c>
-      <c r="BH8">
-        <v>2.66</v>
-      </c>
-      <c r="BI8">
-        <v>2.22</v>
-      </c>
-      <c r="BJ8" t="s">
-        <v>132</v>
-      </c>
-      <c r="BN8" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="9" spans="1:69">
-      <c r="A9" t="s">
-        <v>76</v>
-      </c>
-      <c r="B9" t="s">
-        <v>117</v>
-      </c>
-      <c r="C9">
-        <v>370.43</v>
-      </c>
-      <c r="D9">
-        <v>0.23</v>
-      </c>
-      <c r="E9">
-        <v>0.1</v>
-      </c>
-      <c r="F9" t="s">
-        <v>118</v>
-      </c>
-      <c r="G9">
-        <v>376.71</v>
-      </c>
-      <c r="H9">
-        <v>0.22</v>
-      </c>
-      <c r="I9">
-        <v>0.08</v>
-      </c>
-      <c r="J9" t="s">
-        <v>119</v>
-      </c>
-      <c r="K9">
-        <v>383.71</v>
-      </c>
-      <c r="L9">
-        <v>0.22</v>
-      </c>
-      <c r="M9">
-        <v>0.08</v>
-      </c>
-      <c r="N9" t="s">
-        <v>120</v>
-      </c>
-      <c r="O9">
-        <v>390.71</v>
-      </c>
-      <c r="P9">
-        <v>0.21</v>
-      </c>
-      <c r="Q9">
-        <v>0.08</v>
-      </c>
-      <c r="R9" t="s">
-        <v>121</v>
-      </c>
-      <c r="S9">
-        <v>473</v>
-      </c>
-      <c r="T9">
-        <v>0.18</v>
-      </c>
-      <c r="U9">
-        <v>0.06</v>
-      </c>
-      <c r="V9" t="s">
-        <v>122</v>
-      </c>
-      <c r="W9">
-        <v>514</v>
-      </c>
-      <c r="X9">
-        <v>0.16</v>
-      </c>
-      <c r="Y9">
-        <v>0.05</v>
-      </c>
-      <c r="Z9" t="s">
-        <v>123</v>
-      </c>
-      <c r="AA9">
-        <v>547.86</v>
-      </c>
-      <c r="AB9">
-        <v>0.15</v>
-      </c>
-      <c r="AC9">
-        <v>0.04</v>
-      </c>
-      <c r="AD9" t="s">
-        <v>124</v>
-      </c>
-      <c r="AE9">
-        <v>509.43</v>
-      </c>
-      <c r="AF9">
-        <v>0.17</v>
-      </c>
-      <c r="AG9">
-        <v>0.05</v>
-      </c>
-      <c r="AH9" t="s">
-        <v>125</v>
-      </c>
-      <c r="AI9">
-        <v>503.71</v>
-      </c>
-      <c r="AJ9">
-        <v>0.17</v>
-      </c>
-      <c r="AK9">
-        <v>0.05</v>
-      </c>
-      <c r="AL9" t="s">
-        <v>126</v>
-      </c>
-      <c r="AM9">
-        <v>576.4299999999999</v>
-      </c>
-      <c r="AN9">
-        <v>0.14</v>
-      </c>
-      <c r="AO9">
-        <v>0.02</v>
-      </c>
-      <c r="AP9" t="s">
-        <v>127</v>
-      </c>
-      <c r="AT9" t="s">
-        <v>128</v>
-      </c>
-      <c r="AX9" t="s">
-        <v>129</v>
-      </c>
-      <c r="BB9" t="s">
-        <v>130</v>
-      </c>
-      <c r="BF9" t="s">
-        <v>131</v>
-      </c>
-      <c r="BJ9" t="s">
-        <v>132</v>
-      </c>
-      <c r="BN9" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="10" spans="1:69">
-      <c r="A10" t="s">
-        <v>77</v>
-      </c>
-      <c r="B10" t="s">
-        <v>117</v>
-      </c>
-      <c r="C10">
-        <v>9.970000000000001</v>
-      </c>
-      <c r="D10">
-        <v>8.52</v>
-      </c>
-      <c r="E10">
-        <v>8.99</v>
-      </c>
-      <c r="F10" t="s">
-        <v>118</v>
-      </c>
-      <c r="G10">
-        <v>10.11</v>
-      </c>
-      <c r="H10">
-        <v>8.32</v>
-      </c>
-      <c r="I10">
-        <v>8.789999999999999</v>
-      </c>
-      <c r="J10" t="s">
-        <v>119</v>
-      </c>
-      <c r="K10">
-        <v>11.04</v>
-      </c>
-      <c r="L10">
-        <v>7.64</v>
-      </c>
-      <c r="M10">
-        <v>8.050000000000001</v>
-      </c>
-      <c r="N10" t="s">
-        <v>120</v>
-      </c>
-      <c r="O10">
-        <v>11.39</v>
-      </c>
-      <c r="P10">
-        <v>7.33</v>
-      </c>
-      <c r="Q10">
-        <v>7.74</v>
-      </c>
-      <c r="R10" t="s">
-        <v>121</v>
-      </c>
-      <c r="S10">
-        <v>12.2</v>
-      </c>
-      <c r="T10">
-        <v>6.91</v>
-      </c>
-      <c r="U10">
-        <v>7.25</v>
-      </c>
-      <c r="V10" t="s">
-        <v>122</v>
-      </c>
-      <c r="W10">
-        <v>13.17</v>
-      </c>
-      <c r="X10">
-        <v>6.41</v>
-      </c>
-      <c r="Y10">
-        <v>6.69</v>
-      </c>
-      <c r="Z10" t="s">
-        <v>123</v>
-      </c>
-      <c r="AA10">
-        <v>14.94</v>
-      </c>
-      <c r="AB10">
-        <v>5.65</v>
-      </c>
-      <c r="AC10">
-        <v>5.85</v>
-      </c>
-      <c r="AD10" t="s">
-        <v>124</v>
-      </c>
-      <c r="AE10">
-        <v>13.31</v>
-      </c>
-      <c r="AF10">
-        <v>6.46</v>
-      </c>
-      <c r="AG10">
-        <v>6.7</v>
-      </c>
-      <c r="AH10" t="s">
-        <v>125</v>
-      </c>
-      <c r="AI10">
-        <v>13.81</v>
-      </c>
-      <c r="AJ10">
-        <v>6.21</v>
-      </c>
-      <c r="AK10">
-        <v>6.4</v>
-      </c>
-      <c r="AL10" t="s">
-        <v>126</v>
-      </c>
-      <c r="AM10">
-        <v>11.47</v>
-      </c>
-      <c r="AN10">
-        <v>7.05</v>
-      </c>
-      <c r="AO10">
-        <v>7.32</v>
-      </c>
-      <c r="AP10" t="s">
-        <v>127</v>
-      </c>
-      <c r="AQ10">
-        <v>12.28</v>
-      </c>
-      <c r="AR10">
-        <v>7.13</v>
-      </c>
-      <c r="AS10">
-        <v>7.22</v>
-      </c>
-      <c r="AT10" t="s">
-        <v>128</v>
-      </c>
-      <c r="AU10">
-        <v>12.7</v>
-      </c>
-      <c r="AV10">
-        <v>6.97</v>
-      </c>
-      <c r="AW10">
-        <v>6.96</v>
-      </c>
-      <c r="AX10" t="s">
-        <v>129</v>
-      </c>
-      <c r="BB10" t="s">
-        <v>130</v>
-      </c>
-      <c r="BF10" t="s">
-        <v>131</v>
-      </c>
-      <c r="BJ10" t="s">
-        <v>132</v>
-      </c>
-      <c r="BN10" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="11" spans="1:69">
-      <c r="A11" t="s">
-        <v>78</v>
-      </c>
-      <c r="B11" t="s">
-        <v>117</v>
-      </c>
-      <c r="C11">
-        <v>1926.43</v>
-      </c>
-      <c r="D11">
-        <v>0.04</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11" t="s">
-        <v>118</v>
-      </c>
-      <c r="G11">
-        <v>1926.43</v>
-      </c>
-      <c r="H11">
-        <v>0.04</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11" t="s">
-        <v>119</v>
-      </c>
-      <c r="K11">
-        <v>2355</v>
-      </c>
-      <c r="L11">
-        <v>0.04</v>
-      </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-      <c r="N11" t="s">
-        <v>120</v>
-      </c>
-      <c r="O11">
-        <v>2355</v>
-      </c>
-      <c r="P11">
-        <v>0.04</v>
-      </c>
-      <c r="Q11">
-        <v>0</v>
-      </c>
-      <c r="R11" t="s">
-        <v>121</v>
-      </c>
-      <c r="S11">
-        <v>2596.6</v>
-      </c>
-      <c r="T11">
-        <v>0.03</v>
-      </c>
-      <c r="U11">
-        <v>0</v>
-      </c>
-      <c r="V11" t="s">
-        <v>122</v>
-      </c>
-      <c r="W11">
-        <v>1997.33</v>
-      </c>
-      <c r="X11">
-        <v>0.04</v>
-      </c>
-      <c r="Y11">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="s">
-        <v>123</v>
-      </c>
-      <c r="AA11">
-        <v>1855</v>
-      </c>
-      <c r="AB11">
-        <v>0.05</v>
-      </c>
-      <c r="AC11">
-        <v>0</v>
-      </c>
-      <c r="AD11" t="s">
-        <v>124</v>
-      </c>
-      <c r="AE11">
-        <v>2001</v>
-      </c>
-      <c r="AF11">
-        <v>0.04</v>
-      </c>
-      <c r="AG11">
-        <v>0</v>
-      </c>
-      <c r="AH11" t="s">
-        <v>125</v>
-      </c>
-      <c r="AL11" t="s">
-        <v>126</v>
-      </c>
-      <c r="AP11" t="s">
-        <v>127</v>
-      </c>
-      <c r="AT11" t="s">
-        <v>128</v>
-      </c>
-      <c r="AX11" t="s">
-        <v>129</v>
-      </c>
-      <c r="BB11" t="s">
-        <v>130</v>
-      </c>
-      <c r="BF11" t="s">
-        <v>131</v>
-      </c>
-      <c r="BJ11" t="s">
-        <v>132</v>
-      </c>
-      <c r="BN11" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="12" spans="1:69">
-      <c r="A12" t="s">
-        <v>79</v>
-      </c>
-      <c r="B12" t="s">
-        <v>117</v>
-      </c>
-      <c r="C12">
-        <v>747.86</v>
-      </c>
-      <c r="D12">
-        <v>0.11</v>
-      </c>
-      <c r="E12">
-        <v>0.03</v>
-      </c>
-      <c r="F12" t="s">
-        <v>118</v>
-      </c>
-      <c r="G12">
-        <v>747.86</v>
-      </c>
-      <c r="H12">
-        <v>0.11</v>
-      </c>
-      <c r="I12">
-        <v>0.02</v>
-      </c>
-      <c r="J12" t="s">
-        <v>119</v>
-      </c>
-      <c r="K12">
-        <v>747.86</v>
-      </c>
-      <c r="L12">
-        <v>0.11</v>
-      </c>
-      <c r="M12">
-        <v>0.02</v>
-      </c>
-      <c r="N12" t="s">
-        <v>120</v>
-      </c>
-      <c r="O12">
-        <v>747.86</v>
-      </c>
-      <c r="P12">
-        <v>0.11</v>
-      </c>
-      <c r="Q12">
-        <v>0.02</v>
-      </c>
-      <c r="R12" t="s">
-        <v>121</v>
-      </c>
-      <c r="S12">
-        <v>607.5</v>
-      </c>
-      <c r="T12">
-        <v>0.14</v>
-      </c>
-      <c r="U12">
-        <v>0.04</v>
-      </c>
-      <c r="V12" t="s">
-        <v>122</v>
-      </c>
-      <c r="W12">
-        <v>569.29</v>
-      </c>
-      <c r="X12">
-        <v>0.15</v>
-      </c>
-      <c r="Y12">
-        <v>0.04</v>
-      </c>
-      <c r="Z12" t="s">
-        <v>123</v>
-      </c>
-      <c r="AA12">
-        <v>647.86</v>
-      </c>
-      <c r="AB12">
-        <v>0.13</v>
-      </c>
-      <c r="AC12">
-        <v>0.03</v>
-      </c>
-      <c r="AD12" t="s">
-        <v>124</v>
-      </c>
-      <c r="AE12">
-        <v>647.86</v>
-      </c>
-      <c r="AF12">
-        <v>0.13</v>
-      </c>
-      <c r="AG12">
-        <v>0.03</v>
-      </c>
-      <c r="AH12" t="s">
-        <v>125</v>
-      </c>
-      <c r="AI12">
-        <v>612.14</v>
-      </c>
-      <c r="AJ12">
-        <v>0.14</v>
-      </c>
-      <c r="AK12">
-        <v>0.03</v>
-      </c>
-      <c r="AL12" t="s">
-        <v>126</v>
-      </c>
-      <c r="AM12">
-        <v>551</v>
-      </c>
-      <c r="AN12">
-        <v>0.15</v>
-      </c>
-      <c r="AO12">
-        <v>0.02</v>
-      </c>
-      <c r="AP12" t="s">
-        <v>127</v>
-      </c>
-      <c r="AT12" t="s">
-        <v>128</v>
-      </c>
-      <c r="AX12" t="s">
-        <v>129</v>
-      </c>
-      <c r="BB12" t="s">
-        <v>130</v>
-      </c>
-      <c r="BF12" t="s">
-        <v>131</v>
-      </c>
-      <c r="BJ12" t="s">
-        <v>132</v>
-      </c>
-      <c r="BN12" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="13" spans="1:69">
-      <c r="A13" t="s">
-        <v>80</v>
-      </c>
-      <c r="B13" t="s">
-        <v>117</v>
-      </c>
-      <c r="C13">
-        <v>15.6</v>
-      </c>
-      <c r="D13">
-        <v>5.44</v>
-      </c>
-      <c r="E13">
-        <v>5.65</v>
-      </c>
-      <c r="F13" t="s">
-        <v>118</v>
-      </c>
-      <c r="G13">
-        <v>15.67</v>
-      </c>
-      <c r="H13">
-        <v>5.37</v>
-      </c>
-      <c r="I13">
-        <v>5.57</v>
-      </c>
-      <c r="J13" t="s">
-        <v>119</v>
-      </c>
-      <c r="K13">
-        <v>15.39</v>
-      </c>
-      <c r="L13">
-        <v>5.48</v>
-      </c>
-      <c r="M13">
-        <v>5.7</v>
-      </c>
-      <c r="N13" t="s">
-        <v>120</v>
-      </c>
-      <c r="O13">
-        <v>14.67</v>
-      </c>
-      <c r="P13">
-        <v>5.69</v>
-      </c>
-      <c r="Q13">
-        <v>5.93</v>
-      </c>
-      <c r="R13" t="s">
-        <v>121</v>
-      </c>
-      <c r="S13">
-        <v>14.87</v>
-      </c>
-      <c r="T13">
-        <v>5.67</v>
-      </c>
-      <c r="U13">
-        <v>5.9</v>
-      </c>
-      <c r="V13" t="s">
-        <v>122</v>
-      </c>
-      <c r="W13">
-        <v>14.53</v>
-      </c>
-      <c r="X13">
-        <v>5.81</v>
-      </c>
-      <c r="Y13">
-        <v>6.03</v>
-      </c>
-      <c r="Z13" t="s">
-        <v>123</v>
-      </c>
-      <c r="AA13">
-        <v>14.6</v>
-      </c>
-      <c r="AB13">
-        <v>5.78</v>
-      </c>
-      <c r="AC13">
-        <v>5.99</v>
-      </c>
-      <c r="AD13" t="s">
-        <v>124</v>
-      </c>
-      <c r="AE13">
-        <v>17.8</v>
-      </c>
-      <c r="AF13">
-        <v>4.83</v>
-      </c>
-      <c r="AG13">
-        <v>4.94</v>
-      </c>
-      <c r="AH13" t="s">
-        <v>125</v>
-      </c>
-      <c r="AI13">
-        <v>21.14</v>
-      </c>
-      <c r="AJ13">
-        <v>4.06</v>
-      </c>
-      <c r="AK13">
-        <v>4.08</v>
-      </c>
-      <c r="AL13" t="s">
-        <v>126</v>
-      </c>
-      <c r="AM13">
-        <v>26</v>
-      </c>
-      <c r="AN13">
-        <v>3.11</v>
-      </c>
-      <c r="AO13">
-        <v>2.94</v>
-      </c>
-      <c r="AP13" t="s">
-        <v>127</v>
-      </c>
-      <c r="AT13" t="s">
-        <v>128</v>
-      </c>
-      <c r="AX13" t="s">
-        <v>129</v>
-      </c>
-      <c r="BB13" t="s">
-        <v>130</v>
-      </c>
-      <c r="BF13" t="s">
-        <v>131</v>
-      </c>
-      <c r="BJ13" t="s">
-        <v>132</v>
-      </c>
-      <c r="BN13" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="14" spans="1:69">
-      <c r="A14" t="s">
-        <v>81</v>
-      </c>
-      <c r="B14" t="s">
-        <v>117</v>
-      </c>
-      <c r="C14">
-        <v>89</v>
-      </c>
-      <c r="D14">
-        <v>0.95</v>
-      </c>
-      <c r="E14">
-        <v>0.8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>118</v>
-      </c>
-      <c r="G14">
-        <v>90.43000000000001</v>
-      </c>
-      <c r="H14">
-        <v>0.93</v>
-      </c>
-      <c r="I14">
-        <v>0.75</v>
-      </c>
-      <c r="J14" t="s">
-        <v>119</v>
-      </c>
-      <c r="K14">
-        <v>133.71</v>
-      </c>
-      <c r="L14">
-        <v>0.63</v>
-      </c>
-      <c r="M14">
-        <v>0.45</v>
-      </c>
-      <c r="N14" t="s">
-        <v>120</v>
-      </c>
-      <c r="O14">
-        <v>135.14</v>
-      </c>
-      <c r="P14">
-        <v>0.62</v>
-      </c>
-      <c r="Q14">
-        <v>0.43</v>
-      </c>
-      <c r="R14" t="s">
-        <v>121</v>
-      </c>
-      <c r="S14">
-        <v>148.33</v>
-      </c>
-      <c r="T14">
-        <v>0.57</v>
-      </c>
-      <c r="U14">
-        <v>0.39</v>
-      </c>
-      <c r="V14" t="s">
-        <v>122</v>
-      </c>
-      <c r="W14">
-        <v>279.29</v>
-      </c>
-      <c r="X14">
-        <v>0.3</v>
-      </c>
-      <c r="Y14">
-        <v>0.14</v>
-      </c>
-      <c r="Z14" t="s">
-        <v>123</v>
-      </c>
-      <c r="AA14">
-        <v>289.29</v>
-      </c>
-      <c r="AB14">
-        <v>0.29</v>
-      </c>
-      <c r="AC14">
-        <v>0.13</v>
-      </c>
-      <c r="AD14" t="s">
-        <v>124</v>
-      </c>
-      <c r="AE14">
-        <v>123.86</v>
-      </c>
-      <c r="AF14">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="AG14">
-        <v>0.51</v>
-      </c>
-      <c r="AH14" t="s">
-        <v>125</v>
-      </c>
-      <c r="AI14">
-        <v>127.43</v>
-      </c>
-      <c r="AJ14">
-        <v>0.67</v>
-      </c>
-      <c r="AK14">
-        <v>0.47</v>
-      </c>
-      <c r="AL14" t="s">
-        <v>126</v>
-      </c>
-      <c r="AM14">
-        <v>129.57</v>
-      </c>
-      <c r="AN14">
-        <v>0.62</v>
-      </c>
-      <c r="AO14">
-        <v>0.33</v>
-      </c>
-      <c r="AP14" t="s">
-        <v>127</v>
-      </c>
-      <c r="AT14" t="s">
-        <v>128</v>
-      </c>
-      <c r="AX14" t="s">
-        <v>129</v>
-      </c>
-      <c r="BB14" t="s">
-        <v>130</v>
-      </c>
-      <c r="BF14" t="s">
-        <v>131</v>
-      </c>
-      <c r="BJ14" t="s">
-        <v>132</v>
-      </c>
-      <c r="BN14" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="15" spans="1:69">
-      <c r="A15" t="s">
-        <v>82</v>
-      </c>
-      <c r="B15" t="s">
-        <v>117</v>
-      </c>
-      <c r="C15">
-        <v>250</v>
-      </c>
-      <c r="D15">
-        <v>0.34</v>
-      </c>
-      <c r="E15">
-        <v>0.18</v>
-      </c>
-      <c r="F15" t="s">
-        <v>118</v>
-      </c>
-      <c r="G15">
-        <v>259.86</v>
-      </c>
-      <c r="H15">
-        <v>0.32</v>
-      </c>
-      <c r="I15">
-        <v>0.16</v>
-      </c>
-      <c r="J15" t="s">
-        <v>119</v>
-      </c>
-      <c r="K15">
-        <v>153</v>
-      </c>
-      <c r="L15">
-        <v>0.55</v>
-      </c>
-      <c r="M15">
-        <v>0.37</v>
-      </c>
-      <c r="N15" t="s">
-        <v>120</v>
-      </c>
-      <c r="O15">
-        <v>143</v>
-      </c>
-      <c r="P15">
-        <v>0.58</v>
-      </c>
-      <c r="Q15">
-        <v>0.4</v>
-      </c>
-      <c r="R15" t="s">
-        <v>121</v>
-      </c>
-      <c r="S15">
-        <v>144.83</v>
-      </c>
-      <c r="T15">
-        <v>0.58</v>
-      </c>
-      <c r="U15">
-        <v>0.4</v>
-      </c>
-      <c r="V15" t="s">
-        <v>122</v>
-      </c>
-      <c r="W15">
-        <v>133.71</v>
-      </c>
-      <c r="X15">
-        <v>0.63</v>
-      </c>
-      <c r="Y15">
-        <v>0.44</v>
-      </c>
-      <c r="Z15" t="s">
-        <v>123</v>
-      </c>
-      <c r="AA15">
-        <v>137.86</v>
-      </c>
-      <c r="AB15">
-        <v>0.61</v>
-      </c>
-      <c r="AC15">
-        <v>0.42</v>
-      </c>
-      <c r="AD15" t="s">
-        <v>124</v>
-      </c>
-      <c r="AE15">
-        <v>150.57</v>
-      </c>
-      <c r="AF15">
-        <v>0.57</v>
-      </c>
-      <c r="AG15">
-        <v>0.39</v>
-      </c>
-      <c r="AH15" t="s">
-        <v>125</v>
-      </c>
-      <c r="AI15">
-        <v>174.86</v>
-      </c>
-      <c r="AJ15">
-        <v>0.49</v>
-      </c>
-      <c r="AK15">
-        <v>0.29</v>
-      </c>
-      <c r="AL15" t="s">
-        <v>126</v>
-      </c>
-      <c r="AM15">
-        <v>179.29</v>
-      </c>
-      <c r="AN15">
-        <v>0.45</v>
-      </c>
-      <c r="AO15">
-        <v>0.19</v>
-      </c>
-      <c r="AP15" t="s">
-        <v>127</v>
-      </c>
-      <c r="AT15" t="s">
-        <v>128</v>
-      </c>
-      <c r="AX15" t="s">
-        <v>129</v>
-      </c>
-      <c r="BB15" t="s">
-        <v>130</v>
-      </c>
-      <c r="BF15" t="s">
-        <v>131</v>
-      </c>
-      <c r="BJ15" t="s">
-        <v>132</v>
-      </c>
-      <c r="BN15" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="16" spans="1:69">
-      <c r="A16" t="s">
-        <v>83</v>
-      </c>
-      <c r="B16" t="s">
-        <v>117</v>
       </c>
       <c r="C16">
         <v>467.14</v>
@@ -3361,7 +3448,7 @@
         <v>0.06</v>
       </c>
       <c r="F16" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G16">
         <v>505.29</v>
@@ -3373,7 +3460,7 @@
         <v>0.05</v>
       </c>
       <c r="J16" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="K16">
         <v>494.14</v>
@@ -3385,7 +3472,7 @@
         <v>0.05</v>
       </c>
       <c r="N16" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="O16">
         <v>502.43</v>
@@ -3397,7 +3484,7 @@
         <v>0.05</v>
       </c>
       <c r="R16" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="S16">
         <v>441.33</v>
@@ -3409,7 +3496,7 @@
         <v>0.06</v>
       </c>
       <c r="V16" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="W16">
         <v>433.86</v>
@@ -3421,7 +3508,7 @@
         <v>0.06</v>
       </c>
       <c r="Z16" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AA16">
         <v>331</v>
@@ -3433,7 +3520,7 @@
         <v>0.1</v>
       </c>
       <c r="AD16" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AE16">
         <v>337.71</v>
@@ -3445,7 +3532,7 @@
         <v>0.11</v>
       </c>
       <c r="AH16" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="AI16">
         <v>373.71</v>
@@ -3457,7 +3544,7 @@
         <v>0.08</v>
       </c>
       <c r="AL16" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="AM16">
         <v>429.43</v>
@@ -3469,7 +3556,7 @@
         <v>0.04</v>
       </c>
       <c r="AP16" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="AQ16">
         <v>458.5</v>
@@ -3481,30 +3568,33 @@
         <v>0.04</v>
       </c>
       <c r="AT16" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="AX16" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="BB16" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="BF16" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="BJ16" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="BN16" t="s">
-        <v>133</v>
+        <v>137</v>
+      </c>
+      <c r="BR16" t="s">
+        <v>138</v>
       </c>
     </row>
-    <row r="17" spans="1:66">
+    <row r="17" spans="1:70">
       <c r="A17" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B17" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C17">
         <v>1926.43</v>
@@ -3516,7 +3606,7 @@
         <v>0</v>
       </c>
       <c r="F17" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G17">
         <v>1926.43</v>
@@ -3528,7 +3618,7 @@
         <v>0</v>
       </c>
       <c r="J17" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="K17">
         <v>2033.57</v>
@@ -3540,7 +3630,7 @@
         <v>0</v>
       </c>
       <c r="N17" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="O17">
         <v>2033.57</v>
@@ -3552,7 +3642,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="S17">
         <v>2296.6</v>
@@ -3564,48 +3654,51 @@
         <v>0</v>
       </c>
       <c r="V17" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="Z17" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AD17" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AH17" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="AL17" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="AP17" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="AT17" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="AX17" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="BB17" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="BF17" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="BJ17" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="BN17" t="s">
-        <v>133</v>
+        <v>137</v>
+      </c>
+      <c r="BR17" t="s">
+        <v>138</v>
       </c>
     </row>
-    <row r="18" spans="1:66">
+    <row r="18" spans="1:70">
       <c r="A18" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B18" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C18">
         <v>1126.43</v>
@@ -3617,7 +3710,7 @@
         <v>0.01</v>
       </c>
       <c r="F18" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G18">
         <v>1126.43</v>
@@ -3629,7 +3722,7 @@
         <v>0.01</v>
       </c>
       <c r="J18" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="K18">
         <v>1126.43</v>
@@ -3641,7 +3734,7 @@
         <v>0.01</v>
       </c>
       <c r="N18" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="O18">
         <v>1197.86</v>
@@ -3653,7 +3746,7 @@
         <v>0.01</v>
       </c>
       <c r="R18" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="S18">
         <v>1296.6</v>
@@ -3665,7 +3758,7 @@
         <v>0.01</v>
       </c>
       <c r="V18" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="W18">
         <v>1247.33</v>
@@ -3677,7 +3770,7 @@
         <v>0.01</v>
       </c>
       <c r="Z18" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AA18">
         <v>1569.29</v>
@@ -3689,7 +3782,7 @@
         <v>0.01</v>
       </c>
       <c r="AD18" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AE18">
         <v>2140.71</v>
@@ -3701,7 +3794,7 @@
         <v>0</v>
       </c>
       <c r="AH18" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="AI18">
         <v>2001</v>
@@ -3713,7 +3806,7 @@
         <v>0</v>
       </c>
       <c r="AL18" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="AM18">
         <v>2001</v>
@@ -3725,33 +3818,36 @@
         <v>0</v>
       </c>
       <c r="AP18" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="AT18" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="AX18" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="BB18" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="BF18" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="BJ18" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="BN18" t="s">
-        <v>133</v>
+        <v>137</v>
+      </c>
+      <c r="BR18" t="s">
+        <v>138</v>
       </c>
     </row>
-    <row r="19" spans="1:66">
+    <row r="19" spans="1:70">
       <c r="A19" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B19" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C19">
         <v>540.71</v>
@@ -3763,7 +3859,7 @@
         <v>0.05</v>
       </c>
       <c r="F19" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G19">
         <v>576.4299999999999</v>
@@ -3775,7 +3871,7 @@
         <v>0.04</v>
       </c>
       <c r="J19" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="K19">
         <v>576.4299999999999</v>
@@ -3787,7 +3883,7 @@
         <v>0.04</v>
       </c>
       <c r="N19" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="O19">
         <v>612.14</v>
@@ -3799,7 +3895,7 @@
         <v>0.03</v>
       </c>
       <c r="R19" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="S19">
         <v>630.67</v>
@@ -3811,7 +3907,7 @@
         <v>0.03</v>
       </c>
       <c r="V19" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="W19">
         <v>647.86</v>
@@ -3823,7 +3919,7 @@
         <v>0.03</v>
       </c>
       <c r="Z19" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AA19">
         <v>647.86</v>
@@ -3835,7 +3931,7 @@
         <v>0.03</v>
       </c>
       <c r="AD19" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AE19">
         <v>647.86</v>
@@ -3847,7 +3943,7 @@
         <v>0.03</v>
       </c>
       <c r="AH19" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="AI19">
         <v>1219.29</v>
@@ -3859,36 +3955,39 @@
         <v>0.01</v>
       </c>
       <c r="AL19" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="AP19" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="AT19" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="AX19" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="BB19" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="BF19" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="BJ19" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="BN19" t="s">
-        <v>133</v>
+        <v>137</v>
+      </c>
+      <c r="BR19" t="s">
+        <v>138</v>
       </c>
     </row>
-    <row r="20" spans="1:66">
+    <row r="20" spans="1:70">
       <c r="A20" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B20" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C20">
         <v>53.43</v>
@@ -3900,7 +3999,7 @@
         <v>1.47</v>
       </c>
       <c r="F20" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G20">
         <v>53.43</v>
@@ -3912,7 +4011,7 @@
         <v>1.44</v>
       </c>
       <c r="J20" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="K20">
         <v>51.29</v>
@@ -3924,7 +4023,7 @@
         <v>1.52</v>
       </c>
       <c r="N20" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="O20">
         <v>51.29</v>
@@ -3936,7 +4035,7 @@
         <v>1.49</v>
       </c>
       <c r="R20" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="S20">
         <v>53</v>
@@ -3948,7 +4047,7 @@
         <v>1.46</v>
       </c>
       <c r="V20" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="W20">
         <v>42.86</v>
@@ -3960,7 +4059,7 @@
         <v>1.86</v>
       </c>
       <c r="Z20" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AA20">
         <v>40</v>
@@ -3972,7 +4071,7 @@
         <v>2</v>
       </c>
       <c r="AD20" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AE20">
         <v>49.86</v>
@@ -3984,7 +4083,7 @@
         <v>1.59</v>
       </c>
       <c r="AH20" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="AI20">
         <v>58</v>
@@ -3996,36 +4095,39 @@
         <v>1.3</v>
       </c>
       <c r="AL20" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="AP20" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="AT20" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="AX20" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="BB20" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="BF20" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="BJ20" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="BN20" t="s">
-        <v>133</v>
+        <v>137</v>
+      </c>
+      <c r="BR20" t="s">
+        <v>138</v>
       </c>
     </row>
-    <row r="21" spans="1:66">
+    <row r="21" spans="1:70">
       <c r="A21" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B21" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C21">
         <v>1497.86</v>
@@ -4037,7 +4139,7 @@
         <v>0.01</v>
       </c>
       <c r="F21" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G21">
         <v>1497.86</v>
@@ -4049,7 +4151,7 @@
         <v>0.01</v>
       </c>
       <c r="J21" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="K21">
         <v>1497.86</v>
@@ -4061,7 +4163,7 @@
         <v>0.01</v>
       </c>
       <c r="N21" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="O21">
         <v>1497.86</v>
@@ -4073,7 +4175,7 @@
         <v>0.01</v>
       </c>
       <c r="R21" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="S21">
         <v>1696.6</v>
@@ -4085,7 +4187,7 @@
         <v>0</v>
       </c>
       <c r="V21" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="W21">
         <v>1664</v>
@@ -4097,45 +4199,48 @@
         <v>0</v>
       </c>
       <c r="Z21" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AD21" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AH21" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="AL21" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="AP21" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="AT21" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="AX21" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="BB21" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="BF21" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="BJ21" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="BN21" t="s">
-        <v>133</v>
+        <v>137</v>
+      </c>
+      <c r="BR21" t="s">
+        <v>138</v>
       </c>
     </row>
-    <row r="22" spans="1:66">
+    <row r="22" spans="1:70">
       <c r="A22" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B22" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C22">
         <v>191.71</v>
@@ -4147,7 +4252,7 @@
         <v>0.28</v>
       </c>
       <c r="F22" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G22">
         <v>222.71</v>
@@ -4159,7 +4264,7 @@
         <v>0.21</v>
       </c>
       <c r="J22" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="K22">
         <v>193.29</v>
@@ -4171,7 +4276,7 @@
         <v>0.26</v>
       </c>
       <c r="N22" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="O22">
         <v>197.43</v>
@@ -4183,7 +4288,7 @@
         <v>0.24</v>
       </c>
       <c r="R22" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="S22">
         <v>148.17</v>
@@ -4195,7 +4300,7 @@
         <v>0.39</v>
       </c>
       <c r="V22" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="W22">
         <v>140</v>
@@ -4207,7 +4312,7 @@
         <v>0.41</v>
       </c>
       <c r="Z22" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AA22">
         <v>138.57</v>
@@ -4219,7 +4324,7 @@
         <v>0.41</v>
       </c>
       <c r="AD22" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AE22">
         <v>180.57</v>
@@ -4231,7 +4336,7 @@
         <v>0.3</v>
       </c>
       <c r="AH22" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="AI22">
         <v>189.07</v>
@@ -4243,7 +4348,7 @@
         <v>0.26</v>
       </c>
       <c r="AL22" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="AM22">
         <v>165.36</v>
@@ -4255,7 +4360,7 @@
         <v>0.22</v>
       </c>
       <c r="AP22" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="AQ22">
         <v>238.33</v>
@@ -4267,7 +4372,7 @@
         <v>0.15</v>
       </c>
       <c r="AT22" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="AU22">
         <v>249.83</v>
@@ -4279,27 +4384,30 @@
         <v>0.13</v>
       </c>
       <c r="AX22" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="BB22" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="BF22" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="BJ22" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="BN22" t="s">
-        <v>133</v>
+        <v>137</v>
+      </c>
+      <c r="BR22" t="s">
+        <v>138</v>
       </c>
     </row>
-    <row r="23" spans="1:66">
+    <row r="23" spans="1:70">
       <c r="A23" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B23" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C23">
         <v>1326.43</v>
@@ -4311,7 +4419,7 @@
         <v>0.01</v>
       </c>
       <c r="F23" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G23">
         <v>1326.43</v>
@@ -4323,7 +4431,7 @@
         <v>0.01</v>
       </c>
       <c r="J23" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="K23">
         <v>1326.43</v>
@@ -4335,7 +4443,7 @@
         <v>0.01</v>
       </c>
       <c r="N23" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="O23">
         <v>1069.29</v>
@@ -4347,7 +4455,7 @@
         <v>0.01</v>
       </c>
       <c r="R23" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="S23">
         <v>996.6</v>
@@ -4359,7 +4467,7 @@
         <v>0.01</v>
       </c>
       <c r="V23" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="W23">
         <v>705.67</v>
@@ -4371,7 +4479,7 @@
         <v>0.03</v>
       </c>
       <c r="Z23" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AA23">
         <v>747.86</v>
@@ -4383,7 +4491,7 @@
         <v>0.02</v>
       </c>
       <c r="AD23" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AE23">
         <v>783.5700000000001</v>
@@ -4395,7 +4503,7 @@
         <v>0.02</v>
       </c>
       <c r="AH23" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="AI23">
         <v>526.4299999999999</v>
@@ -4407,7 +4515,7 @@
         <v>0.04</v>
       </c>
       <c r="AL23" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="AM23">
         <v>583.5700000000001</v>
@@ -4419,7 +4527,7 @@
         <v>0.02</v>
       </c>
       <c r="AP23" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="AQ23">
         <v>664</v>
@@ -4431,30 +4539,33 @@
         <v>0.02</v>
       </c>
       <c r="AT23" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="AX23" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="BB23" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="BF23" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="BJ23" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="BN23" t="s">
-        <v>133</v>
+        <v>137</v>
+      </c>
+      <c r="BR23" t="s">
+        <v>138</v>
       </c>
     </row>
-    <row r="24" spans="1:66">
+    <row r="24" spans="1:70">
       <c r="A24" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B24" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C24">
         <v>1069.29</v>
@@ -4466,7 +4577,7 @@
         <v>0.01</v>
       </c>
       <c r="F24" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G24">
         <v>1069.29</v>
@@ -4478,7 +4589,7 @@
         <v>0.01</v>
       </c>
       <c r="J24" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="K24">
         <v>1069.29</v>
@@ -4490,7 +4601,7 @@
         <v>0.01</v>
       </c>
       <c r="N24" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="O24">
         <v>1069.29</v>
@@ -4502,7 +4613,7 @@
         <v>0.01</v>
       </c>
       <c r="R24" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="S24">
         <v>1372.33</v>
@@ -4514,7 +4625,7 @@
         <v>0.01</v>
       </c>
       <c r="V24" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="W24">
         <v>1926.43</v>
@@ -4526,7 +4637,7 @@
         <v>0</v>
       </c>
       <c r="Z24" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AA24">
         <v>1926.43</v>
@@ -4538,42 +4649,45 @@
         <v>0</v>
       </c>
       <c r="AD24" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AH24" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="AL24" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="AP24" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="AT24" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="AX24" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="BB24" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="BF24" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="BJ24" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="BN24" t="s">
-        <v>133</v>
+        <v>137</v>
+      </c>
+      <c r="BR24" t="s">
+        <v>138</v>
       </c>
     </row>
-    <row r="25" spans="1:66">
+    <row r="25" spans="1:70">
       <c r="A25" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B25" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C25">
         <v>41.71</v>
@@ -4585,7 +4699,7 @@
         <v>1.95</v>
       </c>
       <c r="F25" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G25">
         <v>45.57</v>
@@ -4597,7 +4711,7 @@
         <v>1.73</v>
       </c>
       <c r="J25" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="K25">
         <v>47</v>
@@ -4609,7 +4723,7 @@
         <v>1.68</v>
       </c>
       <c r="N25" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="O25">
         <v>50.43</v>
@@ -4621,7 +4735,7 @@
         <v>1.52</v>
       </c>
       <c r="R25" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="S25">
         <v>48</v>
@@ -4633,7 +4747,7 @@
         <v>1.64</v>
       </c>
       <c r="V25" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="W25">
         <v>49.86</v>
@@ -4645,7 +4759,7 @@
         <v>1.56</v>
       </c>
       <c r="Z25" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AA25">
         <v>47</v>
@@ -4657,7 +4771,7 @@
         <v>1.66</v>
       </c>
       <c r="AD25" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AE25">
         <v>53.43</v>
@@ -4669,7 +4783,7 @@
         <v>1.47</v>
       </c>
       <c r="AH25" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="AI25">
         <v>37.29</v>
@@ -4681,7 +4795,7 @@
         <v>2.18</v>
       </c>
       <c r="AL25" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="AM25">
         <v>31.86</v>
@@ -4693,7 +4807,7 @@
         <v>2.31</v>
       </c>
       <c r="AP25" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="AQ25">
         <v>29.33</v>
@@ -4705,7 +4819,7 @@
         <v>2.79</v>
       </c>
       <c r="AT25" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="AU25">
         <v>25.5</v>
@@ -4717,7 +4831,7 @@
         <v>3.24</v>
       </c>
       <c r="AX25" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="AY25">
         <v>25</v>
@@ -4729,24 +4843,27 @@
         <v>3.4</v>
       </c>
       <c r="BB25" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="BF25" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="BJ25" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="BN25" t="s">
-        <v>133</v>
+        <v>137</v>
+      </c>
+      <c r="BR25" t="s">
+        <v>138</v>
       </c>
     </row>
-    <row r="26" spans="1:66">
+    <row r="26" spans="1:70">
       <c r="A26" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B26" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C26">
         <v>88.86</v>
@@ -4758,7 +4875,7 @@
         <v>0.8</v>
       </c>
       <c r="F26" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G26">
         <v>91.70999999999999</v>
@@ -4770,7 +4887,7 @@
         <v>0.74</v>
       </c>
       <c r="J26" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="K26">
         <v>91.70999999999999</v>
@@ -4782,7 +4899,7 @@
         <v>0.75</v>
       </c>
       <c r="N26" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="O26">
         <v>92.43000000000001</v>
@@ -4794,7 +4911,7 @@
         <v>0.72</v>
       </c>
       <c r="R26" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="S26">
         <v>110.83</v>
@@ -4806,7 +4923,7 @@
         <v>0.58</v>
       </c>
       <c r="V26" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="W26">
         <v>123</v>
@@ -4818,7 +4935,7 @@
         <v>0.5</v>
       </c>
       <c r="Z26" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AA26">
         <v>112.29</v>
@@ -4830,7 +4947,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AD26" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AE26">
         <v>132.29</v>
@@ -4842,7 +4959,7 @@
         <v>0.47</v>
       </c>
       <c r="AH26" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="AI26">
         <v>144.64</v>
@@ -4854,7 +4971,7 @@
         <v>0.39</v>
       </c>
       <c r="AL26" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="AM26">
         <v>146.07</v>
@@ -4866,7 +4983,7 @@
         <v>0.27</v>
       </c>
       <c r="AP26" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="AQ26">
         <v>173</v>
@@ -4878,30 +4995,33 @@
         <v>0.26</v>
       </c>
       <c r="AT26" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="AX26" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="BB26" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="BF26" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="BJ26" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="BN26" t="s">
-        <v>133</v>
+        <v>137</v>
+      </c>
+      <c r="BR26" t="s">
+        <v>138</v>
       </c>
     </row>
-    <row r="27" spans="1:66">
+    <row r="27" spans="1:70">
       <c r="A27" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B27" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C27">
         <v>49.86</v>
@@ -4913,7 +5033,7 @@
         <v>1.59</v>
       </c>
       <c r="F27" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G27">
         <v>50.57</v>
@@ -4925,7 +5045,7 @@
         <v>1.54</v>
       </c>
       <c r="J27" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="K27">
         <v>38.71</v>
@@ -4937,7 +5057,7 @@
         <v>2.1</v>
       </c>
       <c r="N27" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="O27">
         <v>37.71</v>
@@ -4949,7 +5069,7 @@
         <v>2.13</v>
       </c>
       <c r="R27" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="S27">
         <v>40.67</v>
@@ -4961,7 +5081,7 @@
         <v>1.98</v>
       </c>
       <c r="V27" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="W27">
         <v>32.86</v>
@@ -4973,7 +5093,7 @@
         <v>2.51</v>
       </c>
       <c r="Z27" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AA27">
         <v>35.14</v>
@@ -4985,7 +5105,7 @@
         <v>2.32</v>
       </c>
       <c r="AD27" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AE27">
         <v>43.14</v>
@@ -4997,7 +5117,7 @@
         <v>1.88</v>
       </c>
       <c r="AH27" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="AI27">
         <v>51.29</v>
@@ -5009,7 +5129,7 @@
         <v>1.51</v>
       </c>
       <c r="AL27" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="AM27">
         <v>21.57</v>
@@ -5021,7 +5141,7 @@
         <v>3.65</v>
       </c>
       <c r="AP27" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="AQ27">
         <v>27.33</v>
@@ -5033,7 +5153,7 @@
         <v>3.02</v>
       </c>
       <c r="AT27" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="AU27">
         <v>31.83</v>
@@ -5045,7 +5165,7 @@
         <v>2.51</v>
       </c>
       <c r="AX27" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="AY27">
         <v>30.5</v>
@@ -5057,7 +5177,7 @@
         <v>2.71</v>
       </c>
       <c r="BB27" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="BC27">
         <v>31.33</v>
@@ -5069,21 +5189,24 @@
         <v>2.58</v>
       </c>
       <c r="BF27" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="BJ27" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="BN27" t="s">
-        <v>133</v>
+        <v>137</v>
+      </c>
+      <c r="BR27" t="s">
+        <v>138</v>
       </c>
     </row>
-    <row r="28" spans="1:66">
+    <row r="28" spans="1:70">
       <c r="A28" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B28" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C28">
         <v>68.43000000000001</v>
@@ -5095,7 +5218,7 @@
         <v>1.1</v>
       </c>
       <c r="F28" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G28">
         <v>52.71</v>
@@ -5107,7 +5230,7 @@
         <v>1.46</v>
       </c>
       <c r="J28" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="K28">
         <v>52.71</v>
@@ -5119,7 +5242,7 @@
         <v>1.47</v>
       </c>
       <c r="N28" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="O28">
         <v>57.86</v>
@@ -5131,7 +5254,7 @@
         <v>1.29</v>
       </c>
       <c r="R28" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="S28">
         <v>47.17</v>
@@ -5143,7 +5266,7 @@
         <v>1.67</v>
       </c>
       <c r="V28" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="W28">
         <v>51.14</v>
@@ -5155,7 +5278,7 @@
         <v>1.51</v>
       </c>
       <c r="Z28" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AA28">
         <v>52.57</v>
@@ -5167,7 +5290,7 @@
         <v>1.46</v>
       </c>
       <c r="AD28" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AE28">
         <v>45.71</v>
@@ -5179,7 +5302,7 @@
         <v>1.76</v>
       </c>
       <c r="AH28" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="AI28">
         <v>50.57</v>
@@ -5191,7 +5314,7 @@
         <v>1.54</v>
       </c>
       <c r="AL28" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="AM28">
         <v>50.29</v>
@@ -5203,7 +5326,7 @@
         <v>1.31</v>
       </c>
       <c r="AP28" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="AQ28">
         <v>28.33</v>
@@ -5215,7 +5338,7 @@
         <v>2.9</v>
       </c>
       <c r="AT28" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="AU28">
         <v>28.83</v>
@@ -5227,7 +5350,7 @@
         <v>2.81</v>
       </c>
       <c r="AX28" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="AY28">
         <v>51</v>
@@ -5239,24 +5362,27 @@
         <v>1.47</v>
       </c>
       <c r="BB28" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="BF28" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="BJ28" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="BN28" t="s">
-        <v>133</v>
+        <v>137</v>
+      </c>
+      <c r="BR28" t="s">
+        <v>138</v>
       </c>
     </row>
-    <row r="29" spans="1:66">
+    <row r="29" spans="1:70">
       <c r="A29" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B29" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C29">
         <v>1197.86</v>
@@ -5268,7 +5394,7 @@
         <v>0.01</v>
       </c>
       <c r="F29" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G29">
         <v>1197.86</v>
@@ -5280,7 +5406,7 @@
         <v>0.01</v>
       </c>
       <c r="J29" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="K29">
         <v>1197.86</v>
@@ -5292,7 +5418,7 @@
         <v>0.01</v>
       </c>
       <c r="N29" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="O29">
         <v>819.29</v>
@@ -5304,7 +5430,7 @@
         <v>0.02</v>
       </c>
       <c r="R29" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="S29">
         <v>872.33</v>
@@ -5316,7 +5442,7 @@
         <v>0.02</v>
       </c>
       <c r="V29" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="W29">
         <v>890.71</v>
@@ -5328,7 +5454,7 @@
         <v>0.02</v>
       </c>
       <c r="Z29" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AA29">
         <v>890.71</v>
@@ -5340,7 +5466,7 @@
         <v>0.02</v>
       </c>
       <c r="AD29" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AE29">
         <v>926.4299999999999</v>
@@ -5352,39 +5478,42 @@
         <v>0.02</v>
       </c>
       <c r="AH29" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="AL29" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="AP29" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="AT29" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="AX29" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="BB29" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="BF29" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="BJ29" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="BN29" t="s">
-        <v>133</v>
+        <v>137</v>
+      </c>
+      <c r="BR29" t="s">
+        <v>138</v>
       </c>
     </row>
-    <row r="30" spans="1:66">
+    <row r="30" spans="1:70">
       <c r="A30" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B30" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C30">
         <v>21.29</v>
@@ -5396,7 +5525,7 @@
         <v>4.07</v>
       </c>
       <c r="F30" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G30">
         <v>20.29</v>
@@ -5408,7 +5537,7 @@
         <v>4.24</v>
       </c>
       <c r="J30" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="K30">
         <v>19.71</v>
@@ -5420,7 +5549,7 @@
         <v>4.38</v>
       </c>
       <c r="N30" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="O30">
         <v>20.14</v>
@@ -5432,7 +5561,7 @@
         <v>4.24</v>
       </c>
       <c r="R30" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="S30">
         <v>21</v>
@@ -5444,7 +5573,7 @@
         <v>4.09</v>
       </c>
       <c r="V30" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="W30">
         <v>17.53</v>
@@ -5456,7 +5585,7 @@
         <v>4.95</v>
       </c>
       <c r="Z30" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AA30">
         <v>17.23</v>
@@ -5468,7 +5597,7 @@
         <v>5.03</v>
       </c>
       <c r="AD30" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AE30">
         <v>15.96</v>
@@ -5480,7 +5609,7 @@
         <v>5.54</v>
       </c>
       <c r="AH30" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="AI30">
         <v>17.43</v>
@@ -5492,7 +5621,7 @@
         <v>5.01</v>
       </c>
       <c r="AL30" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="AM30">
         <v>17</v>
@@ -5504,33 +5633,36 @@
         <v>4.77</v>
       </c>
       <c r="AP30" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="AT30" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="AX30" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="BB30" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="BF30" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="BJ30" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="BN30" t="s">
-        <v>133</v>
+        <v>137</v>
+      </c>
+      <c r="BR30" t="s">
+        <v>138</v>
       </c>
     </row>
-    <row r="31" spans="1:66">
+    <row r="31" spans="1:70">
       <c r="A31" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B31" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C31">
         <v>32.29</v>
@@ -5542,7 +5674,7 @@
         <v>2.6</v>
       </c>
       <c r="F31" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G31">
         <v>33</v>
@@ -5554,7 +5686,7 @@
         <v>2.49</v>
       </c>
       <c r="J31" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="K31">
         <v>34.14</v>
@@ -5566,7 +5698,7 @@
         <v>2.42</v>
       </c>
       <c r="N31" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="O31">
         <v>30.43</v>
@@ -5578,7 +5710,7 @@
         <v>2.71</v>
       </c>
       <c r="R31" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="S31">
         <v>31.5</v>
@@ -5590,7 +5722,7 @@
         <v>2.64</v>
       </c>
       <c r="V31" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="W31">
         <v>36.57</v>
@@ -5602,7 +5734,7 @@
         <v>2.22</v>
       </c>
       <c r="Z31" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AA31">
         <v>32.43</v>
@@ -5614,7 +5746,7 @@
         <v>2.53</v>
       </c>
       <c r="AD31" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AE31">
         <v>32.71</v>
@@ -5626,7 +5758,7 @@
         <v>2.56</v>
       </c>
       <c r="AH31" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="AI31">
         <v>35.71</v>
@@ -5638,7 +5770,7 @@
         <v>2.29</v>
       </c>
       <c r="AL31" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="AM31">
         <v>37.71</v>
@@ -5650,7 +5782,7 @@
         <v>1.88</v>
       </c>
       <c r="AP31" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="AQ31">
         <v>37</v>
@@ -5662,7 +5794,7 @@
         <v>2.13</v>
       </c>
       <c r="AT31" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="AU31">
         <v>38.5</v>
@@ -5674,7 +5806,7 @@
         <v>2</v>
       </c>
       <c r="AX31" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="AY31">
         <v>21</v>
@@ -5686,7 +5818,7 @@
         <v>4.12</v>
       </c>
       <c r="BB31" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="BC31">
         <v>16.2</v>
@@ -5698,7 +5830,7 @@
         <v>5.44</v>
       </c>
       <c r="BF31" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="BG31">
         <v>16.28</v>
@@ -5710,18 +5842,21 @@
         <v>5.39</v>
       </c>
       <c r="BJ31" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="BN31" t="s">
-        <v>133</v>
+        <v>137</v>
+      </c>
+      <c r="BR31" t="s">
+        <v>138</v>
       </c>
     </row>
-    <row r="32" spans="1:66">
+    <row r="32" spans="1:70">
       <c r="A32" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B32" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C32">
         <v>1197.86</v>
@@ -5733,7 +5868,7 @@
         <v>0.01</v>
       </c>
       <c r="F32" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G32">
         <v>1197.86</v>
@@ -5745,7 +5880,7 @@
         <v>0.01</v>
       </c>
       <c r="J32" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="K32">
         <v>1197.86</v>
@@ -5757,7 +5892,7 @@
         <v>0.01</v>
       </c>
       <c r="N32" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="O32">
         <v>1197.86</v>
@@ -5769,7 +5904,7 @@
         <v>0.01</v>
       </c>
       <c r="R32" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="S32">
         <v>1247.33</v>
@@ -5781,7 +5916,7 @@
         <v>0.01</v>
       </c>
       <c r="V32" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="W32">
         <v>1212.14</v>
@@ -5793,7 +5928,7 @@
         <v>0.01</v>
       </c>
       <c r="Z32" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AA32">
         <v>1664</v>
@@ -5805,42 +5940,45 @@
         <v>0</v>
       </c>
       <c r="AD32" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AH32" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="AL32" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="AP32" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="AT32" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="AX32" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="BB32" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="BF32" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="BJ32" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="BN32" t="s">
-        <v>133</v>
+        <v>137</v>
+      </c>
+      <c r="BR32" t="s">
+        <v>138</v>
       </c>
     </row>
-    <row r="33" spans="1:66">
+    <row r="33" spans="1:70">
       <c r="A33" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B33" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C33">
         <v>243.29</v>
@@ -5852,7 +5990,7 @@
         <v>0.19</v>
       </c>
       <c r="F33" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G33">
         <v>455.57</v>
@@ -5864,7 +6002,7 @@
         <v>0.06</v>
       </c>
       <c r="J33" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="K33">
         <v>483.57</v>
@@ -5876,7 +6014,7 @@
         <v>0.06</v>
       </c>
       <c r="N33" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="O33">
         <v>490.71</v>
@@ -5888,7 +6026,7 @@
         <v>0.05</v>
       </c>
       <c r="R33" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="S33">
         <v>522.33</v>
@@ -5900,7 +6038,7 @@
         <v>0.05</v>
       </c>
       <c r="V33" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="W33">
         <v>324.29</v>
@@ -5912,7 +6050,7 @@
         <v>0.11</v>
       </c>
       <c r="Z33" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AA33">
         <v>320.14</v>
@@ -5924,7 +6062,7 @@
         <v>0.11</v>
       </c>
       <c r="AD33" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AE33">
         <v>327.14</v>
@@ -5936,7 +6074,7 @@
         <v>0.11</v>
       </c>
       <c r="AH33" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="AI33">
         <v>448.14</v>
@@ -5948,7 +6086,7 @@
         <v>0.06</v>
       </c>
       <c r="AL33" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="AM33">
         <v>212.57</v>
@@ -5960,7 +6098,7 @@
         <v>0.14</v>
       </c>
       <c r="AP33" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="AQ33">
         <v>302.17</v>
@@ -5972,7 +6110,7 @@
         <v>0.1</v>
       </c>
       <c r="AT33" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="AU33">
         <v>370.33</v>
@@ -5984,27 +6122,30 @@
         <v>0.06</v>
       </c>
       <c r="AX33" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="BB33" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="BF33" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="BJ33" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="BN33" t="s">
-        <v>133</v>
+        <v>137</v>
+      </c>
+      <c r="BR33" t="s">
+        <v>138</v>
       </c>
     </row>
-    <row r="34" spans="1:66">
+    <row r="34" spans="1:70">
       <c r="A34" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B34" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C34">
         <v>8.85</v>
@@ -6016,7 +6157,7 @@
         <v>10.17</v>
       </c>
       <c r="F34" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G34">
         <v>8.699999999999999</v>
@@ -6028,7 +6169,7 @@
         <v>10.26</v>
       </c>
       <c r="J34" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="K34">
         <v>8.630000000000001</v>
@@ -6040,7 +6181,7 @@
         <v>10.38</v>
       </c>
       <c r="N34" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="O34">
         <v>8.619999999999999</v>
@@ -6052,7 +6193,7 @@
         <v>10.32</v>
       </c>
       <c r="R34" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="S34">
         <v>10.63</v>
@@ -6064,7 +6205,7 @@
         <v>8.359999999999999</v>
       </c>
       <c r="V34" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="W34">
         <v>11.67</v>
@@ -6076,7 +6217,7 @@
         <v>7.59</v>
       </c>
       <c r="Z34" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AA34">
         <v>10.83</v>
@@ -6088,7 +6229,7 @@
         <v>8.19</v>
       </c>
       <c r="AD34" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AE34">
         <v>10.54</v>
@@ -6100,7 +6241,7 @@
         <v>8.529999999999999</v>
       </c>
       <c r="AH34" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="AI34">
         <v>13.39</v>
@@ -6112,7 +6253,7 @@
         <v>6.62</v>
       </c>
       <c r="AL34" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="AM34">
         <v>13.6</v>
@@ -6124,7 +6265,7 @@
         <v>6.09</v>
       </c>
       <c r="AP34" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="AQ34">
         <v>15.52</v>
@@ -6136,7 +6277,7 @@
         <v>5.62</v>
       </c>
       <c r="AT34" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="AU34">
         <v>13.95</v>
@@ -6148,7 +6289,7 @@
         <v>6.29</v>
       </c>
       <c r="AX34" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="AY34">
         <v>14.2</v>
@@ -6160,24 +6301,27 @@
         <v>6.3</v>
       </c>
       <c r="BB34" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="BF34" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="BJ34" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="BN34" t="s">
-        <v>133</v>
+        <v>137</v>
+      </c>
+      <c r="BR34" t="s">
+        <v>138</v>
       </c>
     </row>
-    <row r="35" spans="1:66">
+    <row r="35" spans="1:70">
       <c r="A35" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B35" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C35">
         <v>890.71</v>
@@ -6189,7 +6333,7 @@
         <v>0.02</v>
       </c>
       <c r="F35" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G35">
         <v>890.71</v>
@@ -6201,7 +6345,7 @@
         <v>0.02</v>
       </c>
       <c r="J35" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="K35">
         <v>890.71</v>
@@ -6213,7 +6357,7 @@
         <v>0.02</v>
       </c>
       <c r="N35" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="O35">
         <v>783.5700000000001</v>
@@ -6225,7 +6369,7 @@
         <v>0.02</v>
       </c>
       <c r="R35" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="S35">
         <v>789</v>
@@ -6237,7 +6381,7 @@
         <v>0.02</v>
       </c>
       <c r="V35" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="W35">
         <v>855</v>
@@ -6249,7 +6393,7 @@
         <v>0.02</v>
       </c>
       <c r="Z35" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AA35">
         <v>855</v>
@@ -6261,7 +6405,7 @@
         <v>0.02</v>
       </c>
       <c r="AD35" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AE35">
         <v>855</v>
@@ -6273,39 +6417,42 @@
         <v>0.02</v>
       </c>
       <c r="AH35" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="AL35" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="AP35" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="AT35" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="AX35" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="BB35" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="BF35" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="BJ35" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="BN35" t="s">
-        <v>133</v>
+        <v>137</v>
+      </c>
+      <c r="BR35" t="s">
+        <v>138</v>
       </c>
     </row>
-    <row r="36" spans="1:66">
+    <row r="36" spans="1:70">
       <c r="A36" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B36" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C36">
         <v>249.71</v>
@@ -6317,7 +6464,7 @@
         <v>0.18</v>
       </c>
       <c r="F36" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G36">
         <v>242.57</v>
@@ -6329,7 +6476,7 @@
         <v>0.18</v>
       </c>
       <c r="J36" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="K36">
         <v>228.14</v>
@@ -6341,7 +6488,7 @@
         <v>0.2</v>
       </c>
       <c r="N36" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="O36">
         <v>216.71</v>
@@ -6353,7 +6500,7 @@
         <v>0.21</v>
       </c>
       <c r="R36" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="S36">
         <v>234.17</v>
@@ -6365,7 +6512,7 @@
         <v>0.19</v>
       </c>
       <c r="V36" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="W36">
         <v>305.57</v>
@@ -6377,7 +6524,7 @@
         <v>0.12</v>
       </c>
       <c r="Z36" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AA36">
         <v>314.43</v>
@@ -6389,7 +6536,7 @@
         <v>0.11</v>
       </c>
       <c r="AD36" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AE36">
         <v>1569.29</v>
@@ -6401,7 +6548,7 @@
         <v>0.01</v>
       </c>
       <c r="AH36" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="AI36">
         <v>2539</v>
@@ -6413,36 +6560,39 @@
         <v>0</v>
       </c>
       <c r="AL36" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="AP36" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="AT36" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="AX36" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="BB36" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="BF36" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="BJ36" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="BN36" t="s">
-        <v>133</v>
+        <v>137</v>
+      </c>
+      <c r="BR36" t="s">
+        <v>138</v>
       </c>
     </row>
-    <row r="37" spans="1:66">
+    <row r="37" spans="1:70">
       <c r="A37" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B37" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C37">
         <v>141.29</v>
@@ -6454,7 +6604,7 @@
         <v>0.43</v>
       </c>
       <c r="F37" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G37">
         <v>145.57</v>
@@ -6466,7 +6616,7 @@
         <v>0.39</v>
       </c>
       <c r="J37" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="K37">
         <v>110.14</v>
@@ -6478,7 +6628,7 @@
         <v>0.59</v>
       </c>
       <c r="N37" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="O37">
         <v>105.86</v>
@@ -6490,7 +6640,7 @@
         <v>0.6</v>
       </c>
       <c r="R37" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="S37">
         <v>110</v>
@@ -6502,7 +6652,7 @@
         <v>0.59</v>
       </c>
       <c r="V37" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="W37">
         <v>171.86</v>
@@ -6514,7 +6664,7 @@
         <v>0.31</v>
       </c>
       <c r="Z37" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AA37">
         <v>188.29</v>
@@ -6526,7 +6676,7 @@
         <v>0.26</v>
       </c>
       <c r="AD37" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AE37">
         <v>205.43</v>
@@ -6538,7 +6688,7 @@
         <v>0.25</v>
       </c>
       <c r="AH37" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="AI37">
         <v>260.71</v>
@@ -6550,7 +6700,7 @@
         <v>0.16</v>
       </c>
       <c r="AL37" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="AM37">
         <v>229.71</v>
@@ -6562,33 +6712,36 @@
         <v>0.12</v>
       </c>
       <c r="AP37" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="AT37" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="AX37" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="BB37" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="BF37" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="BJ37" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="BN37" t="s">
-        <v>133</v>
+        <v>137</v>
+      </c>
+      <c r="BR37" t="s">
+        <v>138</v>
       </c>
     </row>
-    <row r="38" spans="1:66">
+    <row r="38" spans="1:70">
       <c r="A38" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B38" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C38">
         <v>74.43000000000001</v>
@@ -6600,7 +6753,7 @@
         <v>0.99</v>
       </c>
       <c r="F38" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G38">
         <v>75.14</v>
@@ -6612,7 +6765,7 @@
         <v>0.95</v>
       </c>
       <c r="J38" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="K38">
         <v>83.56999999999999</v>
@@ -6624,7 +6777,7 @@
         <v>0.84</v>
       </c>
       <c r="N38" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="O38">
         <v>87.70999999999999</v>
@@ -6636,7 +6789,7 @@
         <v>0.77</v>
       </c>
       <c r="R38" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="S38">
         <v>78</v>
@@ -6648,7 +6801,7 @@
         <v>0.92</v>
       </c>
       <c r="V38" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="W38">
         <v>81.43000000000001</v>
@@ -6660,7 +6813,7 @@
         <v>0.86</v>
       </c>
       <c r="Z38" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AA38">
         <v>80.14</v>
@@ -6672,7 +6825,7 @@
         <v>0.87</v>
       </c>
       <c r="AD38" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AE38">
         <v>76.43000000000001</v>
@@ -6684,7 +6837,7 @@
         <v>0.96</v>
       </c>
       <c r="AH38" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="AI38">
         <v>73.70999999999999</v>
@@ -6696,7 +6849,7 @@
         <v>0.97</v>
       </c>
       <c r="AL38" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="AM38">
         <v>78.70999999999999</v>
@@ -6708,7 +6861,7 @@
         <v>0.7</v>
       </c>
       <c r="AP38" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="AQ38">
         <v>86.33</v>
@@ -6720,7 +6873,7 @@
         <v>0.73</v>
       </c>
       <c r="AT38" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="AU38">
         <v>66</v>
@@ -6732,7 +6885,7 @@
         <v>1.01</v>
       </c>
       <c r="AX38" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="AY38">
         <v>71.33</v>
@@ -6744,7 +6897,7 @@
         <v>0.96</v>
       </c>
       <c r="BB38" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="BC38">
         <v>38.5</v>
@@ -6756,7 +6909,7 @@
         <v>2.01</v>
       </c>
       <c r="BF38" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="BG38">
         <v>37.83</v>
@@ -6768,18 +6921,21 @@
         <v>2.03</v>
       </c>
       <c r="BJ38" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="BN38" t="s">
-        <v>133</v>
+        <v>137</v>
+      </c>
+      <c r="BR38" t="s">
+        <v>138</v>
       </c>
     </row>
-    <row r="39" spans="1:66">
+    <row r="39" spans="1:70">
       <c r="A39" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B39" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C39">
         <v>101.29</v>
@@ -6791,7 +6947,7 @@
         <v>0.67</v>
       </c>
       <c r="F39" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G39">
         <v>106.14</v>
@@ -6803,7 +6959,7 @@
         <v>0.61</v>
       </c>
       <c r="J39" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="K39">
         <v>107.57</v>
@@ -6815,7 +6971,7 @@
         <v>0.61</v>
       </c>
       <c r="N39" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="O39">
         <v>119.57</v>
@@ -6827,7 +6983,7 @@
         <v>0.51</v>
       </c>
       <c r="R39" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="S39">
         <v>115.17</v>
@@ -6839,7 +6995,7 @@
         <v>0.55</v>
       </c>
       <c r="V39" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="W39">
         <v>125.86</v>
@@ -6851,7 +7007,7 @@
         <v>0.48</v>
       </c>
       <c r="Z39" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AA39">
         <v>153.57</v>
@@ -6863,7 +7019,7 @@
         <v>0.36</v>
       </c>
       <c r="AD39" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AE39">
         <v>165.71</v>
@@ -6875,7 +7031,7 @@
         <v>0.34</v>
       </c>
       <c r="AH39" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="AI39">
         <v>120.29</v>
@@ -6887,7 +7043,7 @@
         <v>0.51</v>
       </c>
       <c r="AL39" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="AM39">
         <v>121.71</v>
@@ -6899,33 +7055,36 @@
         <v>0.36</v>
       </c>
       <c r="AP39" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="AT39" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="AX39" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="BB39" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="BF39" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="BJ39" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="BN39" t="s">
-        <v>133</v>
+        <v>137</v>
+      </c>
+      <c r="BR39" t="s">
+        <v>138</v>
       </c>
     </row>
-    <row r="40" spans="1:66">
+    <row r="40" spans="1:70">
       <c r="A40" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B40" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C40">
         <v>890.71</v>
@@ -6937,7 +7096,7 @@
         <v>0.02</v>
       </c>
       <c r="F40" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G40">
         <v>1176.43</v>
@@ -6949,7 +7108,7 @@
         <v>0.01</v>
       </c>
       <c r="J40" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="K40">
         <v>1176.43</v>
@@ -6961,7 +7120,7 @@
         <v>0.01</v>
       </c>
       <c r="N40" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="O40">
         <v>1176.43</v>
@@ -6973,7 +7132,7 @@
         <v>0.01</v>
       </c>
       <c r="R40" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="S40">
         <v>1205.67</v>
@@ -6985,7 +7144,7 @@
         <v>0.01</v>
       </c>
       <c r="V40" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="W40">
         <v>1247.86</v>
@@ -6997,7 +7156,7 @@
         <v>0.01</v>
       </c>
       <c r="Z40" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AA40">
         <v>1247.86</v>
@@ -7009,7 +7168,7 @@
         <v>0.01</v>
       </c>
       <c r="AD40" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AE40">
         <v>569.29</v>
@@ -7021,7 +7180,7 @@
         <v>0.04</v>
       </c>
       <c r="AH40" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="AI40">
         <v>630</v>
@@ -7033,36 +7192,39 @@
         <v>0.03</v>
       </c>
       <c r="AL40" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="AP40" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="AT40" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="AX40" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="BB40" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="BF40" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="BJ40" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="BN40" t="s">
-        <v>133</v>
+        <v>137</v>
+      </c>
+      <c r="BR40" t="s">
+        <v>138</v>
       </c>
     </row>
-    <row r="41" spans="1:66">
+    <row r="41" spans="1:70">
       <c r="A41" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B41" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C41">
         <v>376.29</v>
@@ -7074,7 +7236,7 @@
         <v>0.09</v>
       </c>
       <c r="F41" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G41">
         <v>241</v>
@@ -7086,7 +7248,7 @@
         <v>0.18</v>
       </c>
       <c r="J41" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="K41">
         <v>224.29</v>
@@ -7098,7 +7260,7 @@
         <v>0.21</v>
       </c>
       <c r="N41" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="O41">
         <v>234</v>
@@ -7110,7 +7272,7 @@
         <v>0.18</v>
       </c>
       <c r="R41" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="S41">
         <v>256.33</v>
@@ -7122,7 +7284,7 @@
         <v>0.17</v>
       </c>
       <c r="V41" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="W41">
         <v>293.57</v>
@@ -7134,7 +7296,7 @@
         <v>0.13</v>
       </c>
       <c r="Z41" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AA41">
         <v>288</v>
@@ -7146,7 +7308,7 @@
         <v>0.13</v>
       </c>
       <c r="AD41" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AE41">
         <v>570</v>
@@ -7158,7 +7320,7 @@
         <v>0.04</v>
       </c>
       <c r="AH41" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="AI41">
         <v>964</v>
@@ -7170,36 +7332,39 @@
         <v>0.01</v>
       </c>
       <c r="AL41" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="AP41" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="AT41" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="AX41" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="BB41" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="BF41" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="BJ41" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="BN41" t="s">
-        <v>133</v>
+        <v>137</v>
+      </c>
+      <c r="BR41" t="s">
+        <v>138</v>
       </c>
     </row>
-    <row r="42" spans="1:66">
+    <row r="42" spans="1:70">
       <c r="A42" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B42" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C42">
         <v>299.29</v>
@@ -7211,7 +7376,7 @@
         <v>0.14</v>
       </c>
       <c r="F42" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G42">
         <v>497.86</v>
@@ -7223,7 +7388,7 @@
         <v>0.05</v>
       </c>
       <c r="J42" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="K42">
         <v>486.71</v>
@@ -7235,7 +7400,7 @@
         <v>0.06</v>
       </c>
       <c r="N42" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="O42">
         <v>497.86</v>
@@ -7247,7 +7412,7 @@
         <v>0.05</v>
       </c>
       <c r="R42" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="S42">
         <v>572.33</v>
@@ -7259,7 +7424,7 @@
         <v>0.04</v>
       </c>
       <c r="V42" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="W42">
         <v>547.86</v>
@@ -7271,7 +7436,7 @@
         <v>0.04</v>
       </c>
       <c r="Z42" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AA42">
         <v>583.5700000000001</v>
@@ -7283,42 +7448,45 @@
         <v>0.04</v>
       </c>
       <c r="AD42" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AH42" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="AL42" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="AP42" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="AT42" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="AX42" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="BB42" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="BF42" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="BJ42" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="BN42" t="s">
-        <v>133</v>
+        <v>137</v>
+      </c>
+      <c r="BR42" t="s">
+        <v>138</v>
       </c>
     </row>
-    <row r="43" spans="1:66">
+    <row r="43" spans="1:70">
       <c r="A43" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B43" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C43">
         <v>605</v>
@@ -7330,7 +7498,7 @@
         <v>0.04</v>
       </c>
       <c r="F43" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G43">
         <v>640.71</v>
@@ -7342,7 +7510,7 @@
         <v>0.03</v>
       </c>
       <c r="J43" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="K43">
         <v>890.71</v>
@@ -7354,7 +7522,7 @@
         <v>0.02</v>
       </c>
       <c r="N43" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="O43">
         <v>926.4299999999999</v>
@@ -7366,7 +7534,7 @@
         <v>0.01</v>
       </c>
       <c r="R43" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="S43">
         <v>955.67</v>
@@ -7378,48 +7546,51 @@
         <v>0.01</v>
       </c>
       <c r="V43" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="Z43" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AD43" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AH43" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="AL43" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="AP43" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="AT43" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="AX43" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="BB43" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="BF43" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="BJ43" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="BN43" t="s">
-        <v>133</v>
+        <v>137</v>
+      </c>
+      <c r="BR43" t="s">
+        <v>138</v>
       </c>
     </row>
-    <row r="44" spans="1:66">
+    <row r="44" spans="1:70">
       <c r="A44" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B44" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C44">
         <v>80</v>
@@ -7431,7 +7602,7 @@
         <v>0.91</v>
       </c>
       <c r="F44" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G44">
         <v>80</v>
@@ -7443,7 +7614,7 @@
         <v>0.88</v>
       </c>
       <c r="J44" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="K44">
         <v>133.14</v>
@@ -7455,7 +7626,7 @@
         <v>0.46</v>
       </c>
       <c r="N44" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="O44">
         <v>145.86</v>
@@ -7467,7 +7638,7 @@
         <v>0.38</v>
       </c>
       <c r="R44" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="S44">
         <v>152.33</v>
@@ -7479,48 +7650,51 @@
         <v>0.37</v>
       </c>
       <c r="V44" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="Z44" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AD44" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AH44" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="AL44" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="AP44" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="AT44" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="AX44" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="BB44" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="BF44" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="BJ44" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="BN44" t="s">
-        <v>133</v>
+        <v>137</v>
+      </c>
+      <c r="BR44" t="s">
+        <v>138</v>
       </c>
     </row>
-    <row r="45" spans="1:66">
+    <row r="45" spans="1:70">
       <c r="A45" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B45" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C45">
         <v>63.71</v>
@@ -7532,7 +7706,7 @@
         <v>1.2</v>
       </c>
       <c r="F45" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G45">
         <v>44.57</v>
@@ -7544,7 +7718,7 @@
         <v>1.78</v>
       </c>
       <c r="J45" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="K45">
         <v>43.86</v>
@@ -7556,7 +7730,7 @@
         <v>1.82</v>
       </c>
       <c r="N45" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="O45">
         <v>41.14</v>
@@ -7568,7 +7742,7 @@
         <v>1.93</v>
       </c>
       <c r="R45" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="S45">
         <v>42</v>
@@ -7580,7 +7754,7 @@
         <v>1.91</v>
       </c>
       <c r="V45" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="W45">
         <v>31.43</v>
@@ -7592,7 +7766,7 @@
         <v>2.63</v>
       </c>
       <c r="Z45" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AA45">
         <v>32.14</v>
@@ -7604,7 +7778,7 @@
         <v>2.56</v>
       </c>
       <c r="AD45" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AE45">
         <v>28.29</v>
@@ -7616,7 +7790,7 @@
         <v>3.01</v>
       </c>
       <c r="AH45" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="AI45">
         <v>31</v>
@@ -7628,7 +7802,7 @@
         <v>2.68</v>
       </c>
       <c r="AL45" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="AM45">
         <v>32.57</v>
@@ -7640,7 +7814,7 @@
         <v>2.25</v>
       </c>
       <c r="AP45" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="AQ45">
         <v>29.17</v>
@@ -7652,7 +7826,7 @@
         <v>2.8</v>
       </c>
       <c r="AT45" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="AU45">
         <v>29.83</v>
@@ -7664,7 +7838,7 @@
         <v>2.7</v>
       </c>
       <c r="AX45" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="AY45">
         <v>28.83</v>
@@ -7676,24 +7850,27 @@
         <v>2.89</v>
       </c>
       <c r="BB45" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="BF45" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="BJ45" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="BN45" t="s">
-        <v>133</v>
+        <v>137</v>
+      </c>
+      <c r="BR45" t="s">
+        <v>138</v>
       </c>
     </row>
-    <row r="46" spans="1:66">
+    <row r="46" spans="1:70">
       <c r="A46" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B46" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C46">
         <v>71.14</v>
@@ -7705,7 +7882,7 @@
         <v>1.05</v>
       </c>
       <c r="F46" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G46">
         <v>75.29000000000001</v>
@@ -7717,7 +7894,7 @@
         <v>0.95</v>
       </c>
       <c r="J46" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="K46">
         <v>75.29000000000001</v>
@@ -7729,7 +7906,7 @@
         <v>0.96</v>
       </c>
       <c r="N46" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="O46">
         <v>83</v>
@@ -7741,7 +7918,7 @@
         <v>0.83</v>
       </c>
       <c r="R46" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="S46">
         <v>88.83</v>
@@ -7753,7 +7930,7 @@
         <v>0.78</v>
       </c>
       <c r="V46" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="W46">
         <v>162.86</v>
@@ -7765,7 +7942,7 @@
         <v>0.33</v>
       </c>
       <c r="Z46" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AA46">
         <v>190</v>
@@ -7777,7 +7954,7 @@
         <v>0.26</v>
       </c>
       <c r="AD46" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AE46">
         <v>216.57</v>
@@ -7789,39 +7966,42 @@
         <v>0.23</v>
       </c>
       <c r="AH46" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="AL46" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="AP46" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="AT46" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="AX46" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="BB46" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="BF46" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="BJ46" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="BN46" t="s">
-        <v>133</v>
+        <v>137</v>
+      </c>
+      <c r="BR46" t="s">
+        <v>138</v>
       </c>
     </row>
-    <row r="47" spans="1:66">
+    <row r="47" spans="1:70">
       <c r="A47" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B47" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C47">
         <v>1197.86</v>
@@ -7833,7 +8013,7 @@
         <v>0.01</v>
       </c>
       <c r="F47" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G47">
         <v>1197.86</v>
@@ -7845,7 +8025,7 @@
         <v>0.01</v>
       </c>
       <c r="J47" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="K47">
         <v>1197.86</v>
@@ -7857,7 +8037,7 @@
         <v>0.01</v>
       </c>
       <c r="N47" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="O47">
         <v>1197.86</v>
@@ -7869,7 +8049,7 @@
         <v>0.01</v>
       </c>
       <c r="R47" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="S47">
         <v>1296.6</v>
@@ -7881,7 +8061,7 @@
         <v>0.01</v>
       </c>
       <c r="V47" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="W47">
         <v>1247.33</v>
@@ -7893,7 +8073,7 @@
         <v>0.01</v>
       </c>
       <c r="Z47" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AA47">
         <v>1212.14</v>
@@ -7905,7 +8085,7 @@
         <v>0.01</v>
       </c>
       <c r="AD47" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AE47">
         <v>1355</v>
@@ -7917,7 +8097,7 @@
         <v>0.01</v>
       </c>
       <c r="AH47" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="AI47">
         <v>2330.67</v>
@@ -7929,36 +8109,39 @@
         <v>0</v>
       </c>
       <c r="AL47" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="AP47" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="AT47" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="AX47" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="BB47" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="BF47" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="BJ47" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="BN47" t="s">
-        <v>133</v>
+        <v>137</v>
+      </c>
+      <c r="BR47" t="s">
+        <v>138</v>
       </c>
     </row>
-    <row r="48" spans="1:66">
+    <row r="48" spans="1:70">
       <c r="A48" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B48" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C48">
         <v>320.43</v>
@@ -7970,7 +8153,7 @@
         <v>0.12</v>
       </c>
       <c r="F48" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G48">
         <v>351.57</v>
@@ -7982,7 +8165,7 @@
         <v>0.1</v>
       </c>
       <c r="J48" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="K48">
         <v>341.71</v>
@@ -7994,7 +8177,7 @@
         <v>0.1</v>
       </c>
       <c r="N48" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="O48">
         <v>283.71</v>
@@ -8006,7 +8189,7 @@
         <v>0.13</v>
       </c>
       <c r="R48" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="S48">
         <v>302.5</v>
@@ -8018,7 +8201,7 @@
         <v>0.13</v>
       </c>
       <c r="V48" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="W48">
         <v>261.14</v>
@@ -8030,7 +8213,7 @@
         <v>0.16</v>
       </c>
       <c r="Z48" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AA48">
         <v>232.57</v>
@@ -8042,7 +8225,7 @@
         <v>0.19</v>
       </c>
       <c r="AD48" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AE48">
         <v>260.71</v>
@@ -8054,7 +8237,7 @@
         <v>0.17</v>
       </c>
       <c r="AH48" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="AI48">
         <v>273.57</v>
@@ -8066,7 +8249,7 @@
         <v>0.14</v>
       </c>
       <c r="AL48" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="AM48">
         <v>287.86</v>
@@ -8078,7 +8261,7 @@
         <v>0.08</v>
       </c>
       <c r="AP48" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="AQ48">
         <v>300.5</v>
@@ -8090,7 +8273,7 @@
         <v>0.1</v>
       </c>
       <c r="AT48" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="AU48">
         <v>272.33</v>
@@ -8102,7 +8285,7 @@
         <v>0.11</v>
       </c>
       <c r="AX48" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="AY48">
         <v>257.83</v>
@@ -8114,24 +8297,27 @@
         <v>0.13</v>
       </c>
       <c r="BB48" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="BF48" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="BJ48" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="BN48" t="s">
-        <v>133</v>
+        <v>137</v>
+      </c>
+      <c r="BR48" t="s">
+        <v>138</v>
       </c>
     </row>
-    <row r="49" spans="1:66">
+    <row r="49" spans="1:70">
       <c r="A49" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B49" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C49">
         <v>153</v>
@@ -8143,7 +8329,7 @@
         <v>0.39</v>
       </c>
       <c r="F49" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G49">
         <v>158.57</v>
@@ -8155,7 +8341,7 @@
         <v>0.35</v>
       </c>
       <c r="J49" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="K49">
         <v>157.14</v>
@@ -8167,7 +8353,7 @@
         <v>0.36</v>
       </c>
       <c r="N49" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="O49">
         <v>135.14</v>
@@ -8179,7 +8365,7 @@
         <v>0.43</v>
       </c>
       <c r="R49" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="S49">
         <v>144</v>
@@ -8191,7 +8377,7 @@
         <v>0.4</v>
       </c>
       <c r="V49" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="W49">
         <v>139.29</v>
@@ -8203,7 +8389,7 @@
         <v>0.42</v>
       </c>
       <c r="Z49" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AA49">
         <v>187.29</v>
@@ -8215,7 +8401,7 @@
         <v>0.26</v>
       </c>
       <c r="AD49" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AE49">
         <v>181.14</v>
@@ -8227,7 +8413,7 @@
         <v>0.3</v>
       </c>
       <c r="AH49" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="AI49">
         <v>272.29</v>
@@ -8239,7 +8425,7 @@
         <v>0.14</v>
       </c>
       <c r="AL49" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="AM49">
         <v>284.86</v>
@@ -8251,7 +8437,7 @@
         <v>0.08</v>
       </c>
       <c r="AP49" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="AQ49">
         <v>333.67</v>
@@ -8263,22 +8449,25 @@
         <v>0.08</v>
       </c>
       <c r="AT49" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="AX49" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="BB49" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="BF49" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="BJ49" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="BN49" t="s">
-        <v>133</v>
+        <v>137</v>
+      </c>
+      <c r="BR49" t="s">
+        <v>138</v>
       </c>
     </row>
   </sheetData>
